--- a/static/downloads/plantilla_empleados.xlsx
+++ b/static/downloads/plantilla_empleados.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU1000"/>
+  <dimension ref="A1:AT1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -471,13 +471,12 @@
     <col width="20" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
     <col width="20" customWidth="1" min="40" max="40"/>
-    <col width="20" customWidth="1" min="41" max="41"/>
-    <col width="21.6" customWidth="1" min="42" max="42"/>
+    <col width="21.6" customWidth="1" min="41" max="41"/>
+    <col width="20" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
-    <col width="20" customWidth="1" min="45" max="45"/>
-    <col width="21.6" customWidth="1" min="46" max="46"/>
-    <col width="20" customWidth="1" min="47" max="47"/>
+    <col width="21.6" customWidth="1" min="45" max="45"/>
+    <col width="20" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -673,45 +672,40 @@
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>Ajuste Inbursa</t>
+          <t>Caja de Ahorro</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>Caja de Ahorro</t>
+          <t>Viaticos</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>Viaticos</t>
+          <t>Pago Dia Festivo</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>Pago Dia Festivo</t>
+          <t>Pagos Efectivo</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>Pagos Efectivo</t>
+          <t>Folio Mov IDSE</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>Folio Mov IDSE</t>
+          <t>Tipo Pago</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>Tipo Pago</t>
+          <t>Ubicacion Estado</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>Ubicacion Estado</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
@@ -764,7 +758,6 @@
       <c r="AR2" s="2" t="n"/>
       <c r="AS2" s="2" t="n"/>
       <c r="AT2" s="2" t="n"/>
-      <c r="AU2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -813,7 +806,6 @@
       <c r="AR3" s="2" t="n"/>
       <c r="AS3" s="2" t="n"/>
       <c r="AT3" s="2" t="n"/>
-      <c r="AU3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
@@ -862,7 +854,6 @@
       <c r="AR4" s="2" t="n"/>
       <c r="AS4" s="2" t="n"/>
       <c r="AT4" s="2" t="n"/>
-      <c r="AU4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -911,7 +902,6 @@
       <c r="AR5" s="2" t="n"/>
       <c r="AS5" s="2" t="n"/>
       <c r="AT5" s="2" t="n"/>
-      <c r="AU5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -960,7 +950,6 @@
       <c r="AR6" s="2" t="n"/>
       <c r="AS6" s="2" t="n"/>
       <c r="AT6" s="2" t="n"/>
-      <c r="AU6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
@@ -1009,7 +998,6 @@
       <c r="AR7" s="2" t="n"/>
       <c r="AS7" s="2" t="n"/>
       <c r="AT7" s="2" t="n"/>
-      <c r="AU7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -1058,7 +1046,6 @@
       <c r="AR8" s="2" t="n"/>
       <c r="AS8" s="2" t="n"/>
       <c r="AT8" s="2" t="n"/>
-      <c r="AU8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -1107,7 +1094,6 @@
       <c r="AR9" s="2" t="n"/>
       <c r="AS9" s="2" t="n"/>
       <c r="AT9" s="2" t="n"/>
-      <c r="AU9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -1156,7 +1142,6 @@
       <c r="AR10" s="2" t="n"/>
       <c r="AS10" s="2" t="n"/>
       <c r="AT10" s="2" t="n"/>
-      <c r="AU10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -1205,7 +1190,6 @@
       <c r="AR11" s="2" t="n"/>
       <c r="AS11" s="2" t="n"/>
       <c r="AT11" s="2" t="n"/>
-      <c r="AU11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -1254,7 +1238,6 @@
       <c r="AR12" s="2" t="n"/>
       <c r="AS12" s="2" t="n"/>
       <c r="AT12" s="2" t="n"/>
-      <c r="AU12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -1303,7 +1286,6 @@
       <c r="AR13" s="2" t="n"/>
       <c r="AS13" s="2" t="n"/>
       <c r="AT13" s="2" t="n"/>
-      <c r="AU13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
@@ -1352,7 +1334,6 @@
       <c r="AR14" s="2" t="n"/>
       <c r="AS14" s="2" t="n"/>
       <c r="AT14" s="2" t="n"/>
-      <c r="AU14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
@@ -1401,7 +1382,6 @@
       <c r="AR15" s="2" t="n"/>
       <c r="AS15" s="2" t="n"/>
       <c r="AT15" s="2" t="n"/>
-      <c r="AU15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -1450,7 +1430,6 @@
       <c r="AR16" s="2" t="n"/>
       <c r="AS16" s="2" t="n"/>
       <c r="AT16" s="2" t="n"/>
-      <c r="AU16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
@@ -1499,7 +1478,6 @@
       <c r="AR17" s="2" t="n"/>
       <c r="AS17" s="2" t="n"/>
       <c r="AT17" s="2" t="n"/>
-      <c r="AU17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -1548,7 +1526,6 @@
       <c r="AR18" s="2" t="n"/>
       <c r="AS18" s="2" t="n"/>
       <c r="AT18" s="2" t="n"/>
-      <c r="AU18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
@@ -1597,7 +1574,6 @@
       <c r="AR19" s="2" t="n"/>
       <c r="AS19" s="2" t="n"/>
       <c r="AT19" s="2" t="n"/>
-      <c r="AU19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -1646,7 +1622,6 @@
       <c r="AR20" s="2" t="n"/>
       <c r="AS20" s="2" t="n"/>
       <c r="AT20" s="2" t="n"/>
-      <c r="AU20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
@@ -1695,7 +1670,6 @@
       <c r="AR21" s="2" t="n"/>
       <c r="AS21" s="2" t="n"/>
       <c r="AT21" s="2" t="n"/>
-      <c r="AU21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -1744,7 +1718,6 @@
       <c r="AR22" s="2" t="n"/>
       <c r="AS22" s="2" t="n"/>
       <c r="AT22" s="2" t="n"/>
-      <c r="AU22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
@@ -1793,7 +1766,6 @@
       <c r="AR23" s="2" t="n"/>
       <c r="AS23" s="2" t="n"/>
       <c r="AT23" s="2" t="n"/>
-      <c r="AU23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -1842,7 +1814,6 @@
       <c r="AR24" s="2" t="n"/>
       <c r="AS24" s="2" t="n"/>
       <c r="AT24" s="2" t="n"/>
-      <c r="AU24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
@@ -1891,7 +1862,6 @@
       <c r="AR25" s="2" t="n"/>
       <c r="AS25" s="2" t="n"/>
       <c r="AT25" s="2" t="n"/>
-      <c r="AU25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -1940,7 +1910,6 @@
       <c r="AR26" s="2" t="n"/>
       <c r="AS26" s="2" t="n"/>
       <c r="AT26" s="2" t="n"/>
-      <c r="AU26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
@@ -1989,7 +1958,6 @@
       <c r="AR27" s="2" t="n"/>
       <c r="AS27" s="2" t="n"/>
       <c r="AT27" s="2" t="n"/>
-      <c r="AU27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -2038,7 +2006,6 @@
       <c r="AR28" s="2" t="n"/>
       <c r="AS28" s="2" t="n"/>
       <c r="AT28" s="2" t="n"/>
-      <c r="AU28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -2087,7 +2054,6 @@
       <c r="AR29" s="2" t="n"/>
       <c r="AS29" s="2" t="n"/>
       <c r="AT29" s="2" t="n"/>
-      <c r="AU29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -2136,7 +2102,6 @@
       <c r="AR30" s="2" t="n"/>
       <c r="AS30" s="2" t="n"/>
       <c r="AT30" s="2" t="n"/>
-      <c r="AU30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
@@ -2185,7 +2150,6 @@
       <c r="AR31" s="2" t="n"/>
       <c r="AS31" s="2" t="n"/>
       <c r="AT31" s="2" t="n"/>
-      <c r="AU31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
@@ -2234,7 +2198,6 @@
       <c r="AR32" s="2" t="n"/>
       <c r="AS32" s="2" t="n"/>
       <c r="AT32" s="2" t="n"/>
-      <c r="AU32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
@@ -2283,7 +2246,6 @@
       <c r="AR33" s="2" t="n"/>
       <c r="AS33" s="2" t="n"/>
       <c r="AT33" s="2" t="n"/>
-      <c r="AU33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -2332,7 +2294,6 @@
       <c r="AR34" s="2" t="n"/>
       <c r="AS34" s="2" t="n"/>
       <c r="AT34" s="2" t="n"/>
-      <c r="AU34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
@@ -2381,7 +2342,6 @@
       <c r="AR35" s="2" t="n"/>
       <c r="AS35" s="2" t="n"/>
       <c r="AT35" s="2" t="n"/>
-      <c r="AU35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
@@ -2430,7 +2390,6 @@
       <c r="AR36" s="2" t="n"/>
       <c r="AS36" s="2" t="n"/>
       <c r="AT36" s="2" t="n"/>
-      <c r="AU36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
@@ -2479,7 +2438,6 @@
       <c r="AR37" s="2" t="n"/>
       <c r="AS37" s="2" t="n"/>
       <c r="AT37" s="2" t="n"/>
-      <c r="AU37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
@@ -2528,7 +2486,6 @@
       <c r="AR38" s="2" t="n"/>
       <c r="AS38" s="2" t="n"/>
       <c r="AT38" s="2" t="n"/>
-      <c r="AU38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>
@@ -2577,7 +2534,6 @@
       <c r="AR39" s="2" t="n"/>
       <c r="AS39" s="2" t="n"/>
       <c r="AT39" s="2" t="n"/>
-      <c r="AU39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
@@ -2626,7 +2582,6 @@
       <c r="AR40" s="2" t="n"/>
       <c r="AS40" s="2" t="n"/>
       <c r="AT40" s="2" t="n"/>
-      <c r="AU40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
@@ -2675,7 +2630,6 @@
       <c r="AR41" s="2" t="n"/>
       <c r="AS41" s="2" t="n"/>
       <c r="AT41" s="2" t="n"/>
-      <c r="AU41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -2724,7 +2678,6 @@
       <c r="AR42" s="2" t="n"/>
       <c r="AS42" s="2" t="n"/>
       <c r="AT42" s="2" t="n"/>
-      <c r="AU42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
@@ -2773,7 +2726,6 @@
       <c r="AR43" s="2" t="n"/>
       <c r="AS43" s="2" t="n"/>
       <c r="AT43" s="2" t="n"/>
-      <c r="AU43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
@@ -2822,7 +2774,6 @@
       <c r="AR44" s="2" t="n"/>
       <c r="AS44" s="2" t="n"/>
       <c r="AT44" s="2" t="n"/>
-      <c r="AU44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
@@ -2871,7 +2822,6 @@
       <c r="AR45" s="2" t="n"/>
       <c r="AS45" s="2" t="n"/>
       <c r="AT45" s="2" t="n"/>
-      <c r="AU45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n"/>
@@ -2920,7 +2870,6 @@
       <c r="AR46" s="2" t="n"/>
       <c r="AS46" s="2" t="n"/>
       <c r="AT46" s="2" t="n"/>
-      <c r="AU46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n"/>
@@ -2969,7 +2918,6 @@
       <c r="AR47" s="2" t="n"/>
       <c r="AS47" s="2" t="n"/>
       <c r="AT47" s="2" t="n"/>
-      <c r="AU47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n"/>
@@ -3018,7 +2966,6 @@
       <c r="AR48" s="2" t="n"/>
       <c r="AS48" s="2" t="n"/>
       <c r="AT48" s="2" t="n"/>
-      <c r="AU48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n"/>
@@ -3067,7 +3014,6 @@
       <c r="AR49" s="2" t="n"/>
       <c r="AS49" s="2" t="n"/>
       <c r="AT49" s="2" t="n"/>
-      <c r="AU49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n"/>
@@ -3116,7 +3062,6 @@
       <c r="AR50" s="2" t="n"/>
       <c r="AS50" s="2" t="n"/>
       <c r="AT50" s="2" t="n"/>
-      <c r="AU50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n"/>
@@ -3165,7 +3110,6 @@
       <c r="AR51" s="2" t="n"/>
       <c r="AS51" s="2" t="n"/>
       <c r="AT51" s="2" t="n"/>
-      <c r="AU51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n"/>
@@ -3214,7 +3158,6 @@
       <c r="AR52" s="2" t="n"/>
       <c r="AS52" s="2" t="n"/>
       <c r="AT52" s="2" t="n"/>
-      <c r="AU52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n"/>
@@ -3263,7 +3206,6 @@
       <c r="AR53" s="2" t="n"/>
       <c r="AS53" s="2" t="n"/>
       <c r="AT53" s="2" t="n"/>
-      <c r="AU53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n"/>
@@ -3312,7 +3254,6 @@
       <c r="AR54" s="2" t="n"/>
       <c r="AS54" s="2" t="n"/>
       <c r="AT54" s="2" t="n"/>
-      <c r="AU54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n"/>
@@ -3361,7 +3302,6 @@
       <c r="AR55" s="2" t="n"/>
       <c r="AS55" s="2" t="n"/>
       <c r="AT55" s="2" t="n"/>
-      <c r="AU55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n"/>
@@ -3410,7 +3350,6 @@
       <c r="AR56" s="2" t="n"/>
       <c r="AS56" s="2" t="n"/>
       <c r="AT56" s="2" t="n"/>
-      <c r="AU56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n"/>
@@ -3459,7 +3398,6 @@
       <c r="AR57" s="2" t="n"/>
       <c r="AS57" s="2" t="n"/>
       <c r="AT57" s="2" t="n"/>
-      <c r="AU57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n"/>
@@ -3508,7 +3446,6 @@
       <c r="AR58" s="2" t="n"/>
       <c r="AS58" s="2" t="n"/>
       <c r="AT58" s="2" t="n"/>
-      <c r="AU58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n"/>
@@ -3557,7 +3494,6 @@
       <c r="AR59" s="2" t="n"/>
       <c r="AS59" s="2" t="n"/>
       <c r="AT59" s="2" t="n"/>
-      <c r="AU59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n"/>
@@ -3606,7 +3542,6 @@
       <c r="AR60" s="2" t="n"/>
       <c r="AS60" s="2" t="n"/>
       <c r="AT60" s="2" t="n"/>
-      <c r="AU60" s="2" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n"/>
@@ -3655,7 +3590,6 @@
       <c r="AR61" s="2" t="n"/>
       <c r="AS61" s="2" t="n"/>
       <c r="AT61" s="2" t="n"/>
-      <c r="AU61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n"/>
@@ -3704,7 +3638,6 @@
       <c r="AR62" s="2" t="n"/>
       <c r="AS62" s="2" t="n"/>
       <c r="AT62" s="2" t="n"/>
-      <c r="AU62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n"/>
@@ -3753,7 +3686,6 @@
       <c r="AR63" s="2" t="n"/>
       <c r="AS63" s="2" t="n"/>
       <c r="AT63" s="2" t="n"/>
-      <c r="AU63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n"/>
@@ -3802,7 +3734,6 @@
       <c r="AR64" s="2" t="n"/>
       <c r="AS64" s="2" t="n"/>
       <c r="AT64" s="2" t="n"/>
-      <c r="AU64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n"/>
@@ -3851,7 +3782,6 @@
       <c r="AR65" s="2" t="n"/>
       <c r="AS65" s="2" t="n"/>
       <c r="AT65" s="2" t="n"/>
-      <c r="AU65" s="2" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n"/>
@@ -3900,7 +3830,6 @@
       <c r="AR66" s="2" t="n"/>
       <c r="AS66" s="2" t="n"/>
       <c r="AT66" s="2" t="n"/>
-      <c r="AU66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n"/>
@@ -3949,7 +3878,6 @@
       <c r="AR67" s="2" t="n"/>
       <c r="AS67" s="2" t="n"/>
       <c r="AT67" s="2" t="n"/>
-      <c r="AU67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n"/>
@@ -3998,7 +3926,6 @@
       <c r="AR68" s="2" t="n"/>
       <c r="AS68" s="2" t="n"/>
       <c r="AT68" s="2" t="n"/>
-      <c r="AU68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n"/>
@@ -4047,7 +3974,6 @@
       <c r="AR69" s="2" t="n"/>
       <c r="AS69" s="2" t="n"/>
       <c r="AT69" s="2" t="n"/>
-      <c r="AU69" s="2" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n"/>
@@ -4096,7 +4022,6 @@
       <c r="AR70" s="2" t="n"/>
       <c r="AS70" s="2" t="n"/>
       <c r="AT70" s="2" t="n"/>
-      <c r="AU70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n"/>
@@ -4145,7 +4070,6 @@
       <c r="AR71" s="2" t="n"/>
       <c r="AS71" s="2" t="n"/>
       <c r="AT71" s="2" t="n"/>
-      <c r="AU71" s="2" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n"/>
@@ -4194,7 +4118,6 @@
       <c r="AR72" s="2" t="n"/>
       <c r="AS72" s="2" t="n"/>
       <c r="AT72" s="2" t="n"/>
-      <c r="AU72" s="2" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n"/>
@@ -4243,7 +4166,6 @@
       <c r="AR73" s="2" t="n"/>
       <c r="AS73" s="2" t="n"/>
       <c r="AT73" s="2" t="n"/>
-      <c r="AU73" s="2" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n"/>
@@ -4292,7 +4214,6 @@
       <c r="AR74" s="2" t="n"/>
       <c r="AS74" s="2" t="n"/>
       <c r="AT74" s="2" t="n"/>
-      <c r="AU74" s="2" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n"/>
@@ -4341,7 +4262,6 @@
       <c r="AR75" s="2" t="n"/>
       <c r="AS75" s="2" t="n"/>
       <c r="AT75" s="2" t="n"/>
-      <c r="AU75" s="2" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n"/>
@@ -4390,7 +4310,6 @@
       <c r="AR76" s="2" t="n"/>
       <c r="AS76" s="2" t="n"/>
       <c r="AT76" s="2" t="n"/>
-      <c r="AU76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n"/>
@@ -4439,7 +4358,6 @@
       <c r="AR77" s="2" t="n"/>
       <c r="AS77" s="2" t="n"/>
       <c r="AT77" s="2" t="n"/>
-      <c r="AU77" s="2" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n"/>
@@ -4488,7 +4406,6 @@
       <c r="AR78" s="2" t="n"/>
       <c r="AS78" s="2" t="n"/>
       <c r="AT78" s="2" t="n"/>
-      <c r="AU78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n"/>
@@ -4537,7 +4454,6 @@
       <c r="AR79" s="2" t="n"/>
       <c r="AS79" s="2" t="n"/>
       <c r="AT79" s="2" t="n"/>
-      <c r="AU79" s="2" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n"/>
@@ -4586,7 +4502,6 @@
       <c r="AR80" s="2" t="n"/>
       <c r="AS80" s="2" t="n"/>
       <c r="AT80" s="2" t="n"/>
-      <c r="AU80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n"/>
@@ -4635,7 +4550,6 @@
       <c r="AR81" s="2" t="n"/>
       <c r="AS81" s="2" t="n"/>
       <c r="AT81" s="2" t="n"/>
-      <c r="AU81" s="2" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n"/>
@@ -4684,7 +4598,6 @@
       <c r="AR82" s="2" t="n"/>
       <c r="AS82" s="2" t="n"/>
       <c r="AT82" s="2" t="n"/>
-      <c r="AU82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n"/>
@@ -4733,7 +4646,6 @@
       <c r="AR83" s="2" t="n"/>
       <c r="AS83" s="2" t="n"/>
       <c r="AT83" s="2" t="n"/>
-      <c r="AU83" s="2" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n"/>
@@ -4782,7 +4694,6 @@
       <c r="AR84" s="2" t="n"/>
       <c r="AS84" s="2" t="n"/>
       <c r="AT84" s="2" t="n"/>
-      <c r="AU84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n"/>
@@ -4831,7 +4742,6 @@
       <c r="AR85" s="2" t="n"/>
       <c r="AS85" s="2" t="n"/>
       <c r="AT85" s="2" t="n"/>
-      <c r="AU85" s="2" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n"/>
@@ -4880,7 +4790,6 @@
       <c r="AR86" s="2" t="n"/>
       <c r="AS86" s="2" t="n"/>
       <c r="AT86" s="2" t="n"/>
-      <c r="AU86" s="2" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n"/>
@@ -4929,7 +4838,6 @@
       <c r="AR87" s="2" t="n"/>
       <c r="AS87" s="2" t="n"/>
       <c r="AT87" s="2" t="n"/>
-      <c r="AU87" s="2" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n"/>
@@ -4978,7 +4886,6 @@
       <c r="AR88" s="2" t="n"/>
       <c r="AS88" s="2" t="n"/>
       <c r="AT88" s="2" t="n"/>
-      <c r="AU88" s="2" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n"/>
@@ -5027,7 +4934,6 @@
       <c r="AR89" s="2" t="n"/>
       <c r="AS89" s="2" t="n"/>
       <c r="AT89" s="2" t="n"/>
-      <c r="AU89" s="2" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n"/>
@@ -5076,7 +4982,6 @@
       <c r="AR90" s="2" t="n"/>
       <c r="AS90" s="2" t="n"/>
       <c r="AT90" s="2" t="n"/>
-      <c r="AU90" s="2" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n"/>
@@ -5125,7 +5030,6 @@
       <c r="AR91" s="2" t="n"/>
       <c r="AS91" s="2" t="n"/>
       <c r="AT91" s="2" t="n"/>
-      <c r="AU91" s="2" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n"/>
@@ -5174,7 +5078,6 @@
       <c r="AR92" s="2" t="n"/>
       <c r="AS92" s="2" t="n"/>
       <c r="AT92" s="2" t="n"/>
-      <c r="AU92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n"/>
@@ -5223,7 +5126,6 @@
       <c r="AR93" s="2" t="n"/>
       <c r="AS93" s="2" t="n"/>
       <c r="AT93" s="2" t="n"/>
-      <c r="AU93" s="2" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n"/>
@@ -5272,7 +5174,6 @@
       <c r="AR94" s="2" t="n"/>
       <c r="AS94" s="2" t="n"/>
       <c r="AT94" s="2" t="n"/>
-      <c r="AU94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n"/>
@@ -5321,7 +5222,6 @@
       <c r="AR95" s="2" t="n"/>
       <c r="AS95" s="2" t="n"/>
       <c r="AT95" s="2" t="n"/>
-      <c r="AU95" s="2" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n"/>
@@ -5370,7 +5270,6 @@
       <c r="AR96" s="2" t="n"/>
       <c r="AS96" s="2" t="n"/>
       <c r="AT96" s="2" t="n"/>
-      <c r="AU96" s="2" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n"/>
@@ -5419,7 +5318,6 @@
       <c r="AR97" s="2" t="n"/>
       <c r="AS97" s="2" t="n"/>
       <c r="AT97" s="2" t="n"/>
-      <c r="AU97" s="2" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n"/>
@@ -5468,7 +5366,6 @@
       <c r="AR98" s="2" t="n"/>
       <c r="AS98" s="2" t="n"/>
       <c r="AT98" s="2" t="n"/>
-      <c r="AU98" s="2" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n"/>
@@ -5517,7 +5414,6 @@
       <c r="AR99" s="2" t="n"/>
       <c r="AS99" s="2" t="n"/>
       <c r="AT99" s="2" t="n"/>
-      <c r="AU99" s="2" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n"/>
@@ -5566,7 +5462,6 @@
       <c r="AR100" s="2" t="n"/>
       <c r="AS100" s="2" t="n"/>
       <c r="AT100" s="2" t="n"/>
-      <c r="AU100" s="2" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n"/>
@@ -5615,7 +5510,6 @@
       <c r="AR101" s="2" t="n"/>
       <c r="AS101" s="2" t="n"/>
       <c r="AT101" s="2" t="n"/>
-      <c r="AU101" s="2" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n"/>
@@ -5664,7 +5558,6 @@
       <c r="AR102" s="2" t="n"/>
       <c r="AS102" s="2" t="n"/>
       <c r="AT102" s="2" t="n"/>
-      <c r="AU102" s="2" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n"/>
@@ -5713,7 +5606,6 @@
       <c r="AR103" s="2" t="n"/>
       <c r="AS103" s="2" t="n"/>
       <c r="AT103" s="2" t="n"/>
-      <c r="AU103" s="2" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n"/>
@@ -5762,7 +5654,6 @@
       <c r="AR104" s="2" t="n"/>
       <c r="AS104" s="2" t="n"/>
       <c r="AT104" s="2" t="n"/>
-      <c r="AU104" s="2" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n"/>
@@ -5811,7 +5702,6 @@
       <c r="AR105" s="2" t="n"/>
       <c r="AS105" s="2" t="n"/>
       <c r="AT105" s="2" t="n"/>
-      <c r="AU105" s="2" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n"/>
@@ -5860,7 +5750,6 @@
       <c r="AR106" s="2" t="n"/>
       <c r="AS106" s="2" t="n"/>
       <c r="AT106" s="2" t="n"/>
-      <c r="AU106" s="2" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n"/>
@@ -5909,7 +5798,6 @@
       <c r="AR107" s="2" t="n"/>
       <c r="AS107" s="2" t="n"/>
       <c r="AT107" s="2" t="n"/>
-      <c r="AU107" s="2" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n"/>
@@ -5958,7 +5846,6 @@
       <c r="AR108" s="2" t="n"/>
       <c r="AS108" s="2" t="n"/>
       <c r="AT108" s="2" t="n"/>
-      <c r="AU108" s="2" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n"/>
@@ -6007,7 +5894,6 @@
       <c r="AR109" s="2" t="n"/>
       <c r="AS109" s="2" t="n"/>
       <c r="AT109" s="2" t="n"/>
-      <c r="AU109" s="2" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n"/>
@@ -6056,7 +5942,6 @@
       <c r="AR110" s="2" t="n"/>
       <c r="AS110" s="2" t="n"/>
       <c r="AT110" s="2" t="n"/>
-      <c r="AU110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n"/>
@@ -6105,7 +5990,6 @@
       <c r="AR111" s="2" t="n"/>
       <c r="AS111" s="2" t="n"/>
       <c r="AT111" s="2" t="n"/>
-      <c r="AU111" s="2" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n"/>
@@ -6154,7 +6038,6 @@
       <c r="AR112" s="2" t="n"/>
       <c r="AS112" s="2" t="n"/>
       <c r="AT112" s="2" t="n"/>
-      <c r="AU112" s="2" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n"/>
@@ -6203,7 +6086,6 @@
       <c r="AR113" s="2" t="n"/>
       <c r="AS113" s="2" t="n"/>
       <c r="AT113" s="2" t="n"/>
-      <c r="AU113" s="2" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n"/>
@@ -6252,7 +6134,6 @@
       <c r="AR114" s="2" t="n"/>
       <c r="AS114" s="2" t="n"/>
       <c r="AT114" s="2" t="n"/>
-      <c r="AU114" s="2" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n"/>
@@ -6301,7 +6182,6 @@
       <c r="AR115" s="2" t="n"/>
       <c r="AS115" s="2" t="n"/>
       <c r="AT115" s="2" t="n"/>
-      <c r="AU115" s="2" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n"/>
@@ -6350,7 +6230,6 @@
       <c r="AR116" s="2" t="n"/>
       <c r="AS116" s="2" t="n"/>
       <c r="AT116" s="2" t="n"/>
-      <c r="AU116" s="2" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n"/>
@@ -6399,7 +6278,6 @@
       <c r="AR117" s="2" t="n"/>
       <c r="AS117" s="2" t="n"/>
       <c r="AT117" s="2" t="n"/>
-      <c r="AU117" s="2" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n"/>
@@ -6448,7 +6326,6 @@
       <c r="AR118" s="2" t="n"/>
       <c r="AS118" s="2" t="n"/>
       <c r="AT118" s="2" t="n"/>
-      <c r="AU118" s="2" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n"/>
@@ -6497,7 +6374,6 @@
       <c r="AR119" s="2" t="n"/>
       <c r="AS119" s="2" t="n"/>
       <c r="AT119" s="2" t="n"/>
-      <c r="AU119" s="2" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n"/>
@@ -6546,7 +6422,6 @@
       <c r="AR120" s="2" t="n"/>
       <c r="AS120" s="2" t="n"/>
       <c r="AT120" s="2" t="n"/>
-      <c r="AU120" s="2" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n"/>
@@ -6595,7 +6470,6 @@
       <c r="AR121" s="2" t="n"/>
       <c r="AS121" s="2" t="n"/>
       <c r="AT121" s="2" t="n"/>
-      <c r="AU121" s="2" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n"/>
@@ -6644,7 +6518,6 @@
       <c r="AR122" s="2" t="n"/>
       <c r="AS122" s="2" t="n"/>
       <c r="AT122" s="2" t="n"/>
-      <c r="AU122" s="2" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n"/>
@@ -6693,7 +6566,6 @@
       <c r="AR123" s="2" t="n"/>
       <c r="AS123" s="2" t="n"/>
       <c r="AT123" s="2" t="n"/>
-      <c r="AU123" s="2" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n"/>
@@ -6742,7 +6614,6 @@
       <c r="AR124" s="2" t="n"/>
       <c r="AS124" s="2" t="n"/>
       <c r="AT124" s="2" t="n"/>
-      <c r="AU124" s="2" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n"/>
@@ -6791,7 +6662,6 @@
       <c r="AR125" s="2" t="n"/>
       <c r="AS125" s="2" t="n"/>
       <c r="AT125" s="2" t="n"/>
-      <c r="AU125" s="2" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n"/>
@@ -6840,7 +6710,6 @@
       <c r="AR126" s="2" t="n"/>
       <c r="AS126" s="2" t="n"/>
       <c r="AT126" s="2" t="n"/>
-      <c r="AU126" s="2" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n"/>
@@ -6889,7 +6758,6 @@
       <c r="AR127" s="2" t="n"/>
       <c r="AS127" s="2" t="n"/>
       <c r="AT127" s="2" t="n"/>
-      <c r="AU127" s="2" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n"/>
@@ -6938,7 +6806,6 @@
       <c r="AR128" s="2" t="n"/>
       <c r="AS128" s="2" t="n"/>
       <c r="AT128" s="2" t="n"/>
-      <c r="AU128" s="2" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n"/>
@@ -6987,7 +6854,6 @@
       <c r="AR129" s="2" t="n"/>
       <c r="AS129" s="2" t="n"/>
       <c r="AT129" s="2" t="n"/>
-      <c r="AU129" s="2" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n"/>
@@ -7036,7 +6902,6 @@
       <c r="AR130" s="2" t="n"/>
       <c r="AS130" s="2" t="n"/>
       <c r="AT130" s="2" t="n"/>
-      <c r="AU130" s="2" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n"/>
@@ -7085,7 +6950,6 @@
       <c r="AR131" s="2" t="n"/>
       <c r="AS131" s="2" t="n"/>
       <c r="AT131" s="2" t="n"/>
-      <c r="AU131" s="2" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n"/>
@@ -7134,7 +6998,6 @@
       <c r="AR132" s="2" t="n"/>
       <c r="AS132" s="2" t="n"/>
       <c r="AT132" s="2" t="n"/>
-      <c r="AU132" s="2" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n"/>
@@ -7183,7 +7046,6 @@
       <c r="AR133" s="2" t="n"/>
       <c r="AS133" s="2" t="n"/>
       <c r="AT133" s="2" t="n"/>
-      <c r="AU133" s="2" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n"/>
@@ -7232,7 +7094,6 @@
       <c r="AR134" s="2" t="n"/>
       <c r="AS134" s="2" t="n"/>
       <c r="AT134" s="2" t="n"/>
-      <c r="AU134" s="2" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n"/>
@@ -7281,7 +7142,6 @@
       <c r="AR135" s="2" t="n"/>
       <c r="AS135" s="2" t="n"/>
       <c r="AT135" s="2" t="n"/>
-      <c r="AU135" s="2" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n"/>
@@ -7330,7 +7190,6 @@
       <c r="AR136" s="2" t="n"/>
       <c r="AS136" s="2" t="n"/>
       <c r="AT136" s="2" t="n"/>
-      <c r="AU136" s="2" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n"/>
@@ -7379,7 +7238,6 @@
       <c r="AR137" s="2" t="n"/>
       <c r="AS137" s="2" t="n"/>
       <c r="AT137" s="2" t="n"/>
-      <c r="AU137" s="2" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n"/>
@@ -7428,7 +7286,6 @@
       <c r="AR138" s="2" t="n"/>
       <c r="AS138" s="2" t="n"/>
       <c r="AT138" s="2" t="n"/>
-      <c r="AU138" s="2" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n"/>
@@ -7477,7 +7334,6 @@
       <c r="AR139" s="2" t="n"/>
       <c r="AS139" s="2" t="n"/>
       <c r="AT139" s="2" t="n"/>
-      <c r="AU139" s="2" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n"/>
@@ -7526,7 +7382,6 @@
       <c r="AR140" s="2" t="n"/>
       <c r="AS140" s="2" t="n"/>
       <c r="AT140" s="2" t="n"/>
-      <c r="AU140" s="2" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n"/>
@@ -7575,7 +7430,6 @@
       <c r="AR141" s="2" t="n"/>
       <c r="AS141" s="2" t="n"/>
       <c r="AT141" s="2" t="n"/>
-      <c r="AU141" s="2" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n"/>
@@ -7624,7 +7478,6 @@
       <c r="AR142" s="2" t="n"/>
       <c r="AS142" s="2" t="n"/>
       <c r="AT142" s="2" t="n"/>
-      <c r="AU142" s="2" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n"/>
@@ -7673,7 +7526,6 @@
       <c r="AR143" s="2" t="n"/>
       <c r="AS143" s="2" t="n"/>
       <c r="AT143" s="2" t="n"/>
-      <c r="AU143" s="2" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n"/>
@@ -7722,7 +7574,6 @@
       <c r="AR144" s="2" t="n"/>
       <c r="AS144" s="2" t="n"/>
       <c r="AT144" s="2" t="n"/>
-      <c r="AU144" s="2" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n"/>
@@ -7771,7 +7622,6 @@
       <c r="AR145" s="2" t="n"/>
       <c r="AS145" s="2" t="n"/>
       <c r="AT145" s="2" t="n"/>
-      <c r="AU145" s="2" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n"/>
@@ -7820,7 +7670,6 @@
       <c r="AR146" s="2" t="n"/>
       <c r="AS146" s="2" t="n"/>
       <c r="AT146" s="2" t="n"/>
-      <c r="AU146" s="2" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n"/>
@@ -7869,7 +7718,6 @@
       <c r="AR147" s="2" t="n"/>
       <c r="AS147" s="2" t="n"/>
       <c r="AT147" s="2" t="n"/>
-      <c r="AU147" s="2" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n"/>
@@ -7918,7 +7766,6 @@
       <c r="AR148" s="2" t="n"/>
       <c r="AS148" s="2" t="n"/>
       <c r="AT148" s="2" t="n"/>
-      <c r="AU148" s="2" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n"/>
@@ -7967,7 +7814,6 @@
       <c r="AR149" s="2" t="n"/>
       <c r="AS149" s="2" t="n"/>
       <c r="AT149" s="2" t="n"/>
-      <c r="AU149" s="2" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n"/>
@@ -8016,7 +7862,6 @@
       <c r="AR150" s="2" t="n"/>
       <c r="AS150" s="2" t="n"/>
       <c r="AT150" s="2" t="n"/>
-      <c r="AU150" s="2" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n"/>
@@ -8065,7 +7910,6 @@
       <c r="AR151" s="2" t="n"/>
       <c r="AS151" s="2" t="n"/>
       <c r="AT151" s="2" t="n"/>
-      <c r="AU151" s="2" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n"/>
@@ -8114,7 +7958,6 @@
       <c r="AR152" s="2" t="n"/>
       <c r="AS152" s="2" t="n"/>
       <c r="AT152" s="2" t="n"/>
-      <c r="AU152" s="2" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n"/>
@@ -8163,7 +8006,6 @@
       <c r="AR153" s="2" t="n"/>
       <c r="AS153" s="2" t="n"/>
       <c r="AT153" s="2" t="n"/>
-      <c r="AU153" s="2" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n"/>
@@ -8212,7 +8054,6 @@
       <c r="AR154" s="2" t="n"/>
       <c r="AS154" s="2" t="n"/>
       <c r="AT154" s="2" t="n"/>
-      <c r="AU154" s="2" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n"/>
@@ -8261,7 +8102,6 @@
       <c r="AR155" s="2" t="n"/>
       <c r="AS155" s="2" t="n"/>
       <c r="AT155" s="2" t="n"/>
-      <c r="AU155" s="2" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n"/>
@@ -8310,7 +8150,6 @@
       <c r="AR156" s="2" t="n"/>
       <c r="AS156" s="2" t="n"/>
       <c r="AT156" s="2" t="n"/>
-      <c r="AU156" s="2" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n"/>
@@ -8359,7 +8198,6 @@
       <c r="AR157" s="2" t="n"/>
       <c r="AS157" s="2" t="n"/>
       <c r="AT157" s="2" t="n"/>
-      <c r="AU157" s="2" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n"/>
@@ -8408,7 +8246,6 @@
       <c r="AR158" s="2" t="n"/>
       <c r="AS158" s="2" t="n"/>
       <c r="AT158" s="2" t="n"/>
-      <c r="AU158" s="2" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n"/>
@@ -8457,7 +8294,6 @@
       <c r="AR159" s="2" t="n"/>
       <c r="AS159" s="2" t="n"/>
       <c r="AT159" s="2" t="n"/>
-      <c r="AU159" s="2" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n"/>
@@ -8506,7 +8342,6 @@
       <c r="AR160" s="2" t="n"/>
       <c r="AS160" s="2" t="n"/>
       <c r="AT160" s="2" t="n"/>
-      <c r="AU160" s="2" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n"/>
@@ -8555,7 +8390,6 @@
       <c r="AR161" s="2" t="n"/>
       <c r="AS161" s="2" t="n"/>
       <c r="AT161" s="2" t="n"/>
-      <c r="AU161" s="2" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n"/>
@@ -8604,7 +8438,6 @@
       <c r="AR162" s="2" t="n"/>
       <c r="AS162" s="2" t="n"/>
       <c r="AT162" s="2" t="n"/>
-      <c r="AU162" s="2" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n"/>
@@ -8653,7 +8486,6 @@
       <c r="AR163" s="2" t="n"/>
       <c r="AS163" s="2" t="n"/>
       <c r="AT163" s="2" t="n"/>
-      <c r="AU163" s="2" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n"/>
@@ -8702,7 +8534,6 @@
       <c r="AR164" s="2" t="n"/>
       <c r="AS164" s="2" t="n"/>
       <c r="AT164" s="2" t="n"/>
-      <c r="AU164" s="2" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n"/>
@@ -8751,7 +8582,6 @@
       <c r="AR165" s="2" t="n"/>
       <c r="AS165" s="2" t="n"/>
       <c r="AT165" s="2" t="n"/>
-      <c r="AU165" s="2" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n"/>
@@ -8800,7 +8630,6 @@
       <c r="AR166" s="2" t="n"/>
       <c r="AS166" s="2" t="n"/>
       <c r="AT166" s="2" t="n"/>
-      <c r="AU166" s="2" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n"/>
@@ -8849,7 +8678,6 @@
       <c r="AR167" s="2" t="n"/>
       <c r="AS167" s="2" t="n"/>
       <c r="AT167" s="2" t="n"/>
-      <c r="AU167" s="2" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n"/>
@@ -8898,7 +8726,6 @@
       <c r="AR168" s="2" t="n"/>
       <c r="AS168" s="2" t="n"/>
       <c r="AT168" s="2" t="n"/>
-      <c r="AU168" s="2" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n"/>
@@ -8947,7 +8774,6 @@
       <c r="AR169" s="2" t="n"/>
       <c r="AS169" s="2" t="n"/>
       <c r="AT169" s="2" t="n"/>
-      <c r="AU169" s="2" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n"/>
@@ -8996,7 +8822,6 @@
       <c r="AR170" s="2" t="n"/>
       <c r="AS170" s="2" t="n"/>
       <c r="AT170" s="2" t="n"/>
-      <c r="AU170" s="2" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n"/>
@@ -9045,7 +8870,6 @@
       <c r="AR171" s="2" t="n"/>
       <c r="AS171" s="2" t="n"/>
       <c r="AT171" s="2" t="n"/>
-      <c r="AU171" s="2" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n"/>
@@ -9094,7 +8918,6 @@
       <c r="AR172" s="2" t="n"/>
       <c r="AS172" s="2" t="n"/>
       <c r="AT172" s="2" t="n"/>
-      <c r="AU172" s="2" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n"/>
@@ -9143,7 +8966,6 @@
       <c r="AR173" s="2" t="n"/>
       <c r="AS173" s="2" t="n"/>
       <c r="AT173" s="2" t="n"/>
-      <c r="AU173" s="2" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n"/>
@@ -9192,7 +9014,6 @@
       <c r="AR174" s="2" t="n"/>
       <c r="AS174" s="2" t="n"/>
       <c r="AT174" s="2" t="n"/>
-      <c r="AU174" s="2" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n"/>
@@ -9241,7 +9062,6 @@
       <c r="AR175" s="2" t="n"/>
       <c r="AS175" s="2" t="n"/>
       <c r="AT175" s="2" t="n"/>
-      <c r="AU175" s="2" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n"/>
@@ -9290,7 +9110,6 @@
       <c r="AR176" s="2" t="n"/>
       <c r="AS176" s="2" t="n"/>
       <c r="AT176" s="2" t="n"/>
-      <c r="AU176" s="2" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n"/>
@@ -9339,7 +9158,6 @@
       <c r="AR177" s="2" t="n"/>
       <c r="AS177" s="2" t="n"/>
       <c r="AT177" s="2" t="n"/>
-      <c r="AU177" s="2" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n"/>
@@ -9388,7 +9206,6 @@
       <c r="AR178" s="2" t="n"/>
       <c r="AS178" s="2" t="n"/>
       <c r="AT178" s="2" t="n"/>
-      <c r="AU178" s="2" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n"/>
@@ -9437,7 +9254,6 @@
       <c r="AR179" s="2" t="n"/>
       <c r="AS179" s="2" t="n"/>
       <c r="AT179" s="2" t="n"/>
-      <c r="AU179" s="2" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n"/>
@@ -9486,7 +9302,6 @@
       <c r="AR180" s="2" t="n"/>
       <c r="AS180" s="2" t="n"/>
       <c r="AT180" s="2" t="n"/>
-      <c r="AU180" s="2" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n"/>
@@ -9535,7 +9350,6 @@
       <c r="AR181" s="2" t="n"/>
       <c r="AS181" s="2" t="n"/>
       <c r="AT181" s="2" t="n"/>
-      <c r="AU181" s="2" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n"/>
@@ -9584,7 +9398,6 @@
       <c r="AR182" s="2" t="n"/>
       <c r="AS182" s="2" t="n"/>
       <c r="AT182" s="2" t="n"/>
-      <c r="AU182" s="2" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n"/>
@@ -9633,7 +9446,6 @@
       <c r="AR183" s="2" t="n"/>
       <c r="AS183" s="2" t="n"/>
       <c r="AT183" s="2" t="n"/>
-      <c r="AU183" s="2" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n"/>
@@ -9682,7 +9494,6 @@
       <c r="AR184" s="2" t="n"/>
       <c r="AS184" s="2" t="n"/>
       <c r="AT184" s="2" t="n"/>
-      <c r="AU184" s="2" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n"/>
@@ -9731,7 +9542,6 @@
       <c r="AR185" s="2" t="n"/>
       <c r="AS185" s="2" t="n"/>
       <c r="AT185" s="2" t="n"/>
-      <c r="AU185" s="2" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n"/>
@@ -9780,7 +9590,6 @@
       <c r="AR186" s="2" t="n"/>
       <c r="AS186" s="2" t="n"/>
       <c r="AT186" s="2" t="n"/>
-      <c r="AU186" s="2" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n"/>
@@ -9829,7 +9638,6 @@
       <c r="AR187" s="2" t="n"/>
       <c r="AS187" s="2" t="n"/>
       <c r="AT187" s="2" t="n"/>
-      <c r="AU187" s="2" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n"/>
@@ -9878,7 +9686,6 @@
       <c r="AR188" s="2" t="n"/>
       <c r="AS188" s="2" t="n"/>
       <c r="AT188" s="2" t="n"/>
-      <c r="AU188" s="2" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n"/>
@@ -9927,7 +9734,6 @@
       <c r="AR189" s="2" t="n"/>
       <c r="AS189" s="2" t="n"/>
       <c r="AT189" s="2" t="n"/>
-      <c r="AU189" s="2" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n"/>
@@ -9976,7 +9782,6 @@
       <c r="AR190" s="2" t="n"/>
       <c r="AS190" s="2" t="n"/>
       <c r="AT190" s="2" t="n"/>
-      <c r="AU190" s="2" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n"/>
@@ -10025,7 +9830,6 @@
       <c r="AR191" s="2" t="n"/>
       <c r="AS191" s="2" t="n"/>
       <c r="AT191" s="2" t="n"/>
-      <c r="AU191" s="2" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n"/>
@@ -10074,7 +9878,6 @@
       <c r="AR192" s="2" t="n"/>
       <c r="AS192" s="2" t="n"/>
       <c r="AT192" s="2" t="n"/>
-      <c r="AU192" s="2" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n"/>
@@ -10123,7 +9926,6 @@
       <c r="AR193" s="2" t="n"/>
       <c r="AS193" s="2" t="n"/>
       <c r="AT193" s="2" t="n"/>
-      <c r="AU193" s="2" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n"/>
@@ -10172,7 +9974,6 @@
       <c r="AR194" s="2" t="n"/>
       <c r="AS194" s="2" t="n"/>
       <c r="AT194" s="2" t="n"/>
-      <c r="AU194" s="2" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n"/>
@@ -10221,7 +10022,6 @@
       <c r="AR195" s="2" t="n"/>
       <c r="AS195" s="2" t="n"/>
       <c r="AT195" s="2" t="n"/>
-      <c r="AU195" s="2" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n"/>
@@ -10270,7 +10070,6 @@
       <c r="AR196" s="2" t="n"/>
       <c r="AS196" s="2" t="n"/>
       <c r="AT196" s="2" t="n"/>
-      <c r="AU196" s="2" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n"/>
@@ -10319,7 +10118,6 @@
       <c r="AR197" s="2" t="n"/>
       <c r="AS197" s="2" t="n"/>
       <c r="AT197" s="2" t="n"/>
-      <c r="AU197" s="2" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n"/>
@@ -10368,7 +10166,6 @@
       <c r="AR198" s="2" t="n"/>
       <c r="AS198" s="2" t="n"/>
       <c r="AT198" s="2" t="n"/>
-      <c r="AU198" s="2" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n"/>
@@ -10417,7 +10214,6 @@
       <c r="AR199" s="2" t="n"/>
       <c r="AS199" s="2" t="n"/>
       <c r="AT199" s="2" t="n"/>
-      <c r="AU199" s="2" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n"/>
@@ -10466,7 +10262,6 @@
       <c r="AR200" s="2" t="n"/>
       <c r="AS200" s="2" t="n"/>
       <c r="AT200" s="2" t="n"/>
-      <c r="AU200" s="2" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n"/>
@@ -10515,7 +10310,6 @@
       <c r="AR201" s="2" t="n"/>
       <c r="AS201" s="2" t="n"/>
       <c r="AT201" s="2" t="n"/>
-      <c r="AU201" s="2" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n"/>
@@ -10564,7 +10358,6 @@
       <c r="AR202" s="2" t="n"/>
       <c r="AS202" s="2" t="n"/>
       <c r="AT202" s="2" t="n"/>
-      <c r="AU202" s="2" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n"/>
@@ -10613,7 +10406,6 @@
       <c r="AR203" s="2" t="n"/>
       <c r="AS203" s="2" t="n"/>
       <c r="AT203" s="2" t="n"/>
-      <c r="AU203" s="2" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n"/>
@@ -10662,7 +10454,6 @@
       <c r="AR204" s="2" t="n"/>
       <c r="AS204" s="2" t="n"/>
       <c r="AT204" s="2" t="n"/>
-      <c r="AU204" s="2" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n"/>
@@ -10711,7 +10502,6 @@
       <c r="AR205" s="2" t="n"/>
       <c r="AS205" s="2" t="n"/>
       <c r="AT205" s="2" t="n"/>
-      <c r="AU205" s="2" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n"/>
@@ -10760,7 +10550,6 @@
       <c r="AR206" s="2" t="n"/>
       <c r="AS206" s="2" t="n"/>
       <c r="AT206" s="2" t="n"/>
-      <c r="AU206" s="2" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n"/>
@@ -10809,7 +10598,6 @@
       <c r="AR207" s="2" t="n"/>
       <c r="AS207" s="2" t="n"/>
       <c r="AT207" s="2" t="n"/>
-      <c r="AU207" s="2" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n"/>
@@ -10858,7 +10646,6 @@
       <c r="AR208" s="2" t="n"/>
       <c r="AS208" s="2" t="n"/>
       <c r="AT208" s="2" t="n"/>
-      <c r="AU208" s="2" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n"/>
@@ -10907,7 +10694,6 @@
       <c r="AR209" s="2" t="n"/>
       <c r="AS209" s="2" t="n"/>
       <c r="AT209" s="2" t="n"/>
-      <c r="AU209" s="2" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n"/>
@@ -10956,7 +10742,6 @@
       <c r="AR210" s="2" t="n"/>
       <c r="AS210" s="2" t="n"/>
       <c r="AT210" s="2" t="n"/>
-      <c r="AU210" s="2" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n"/>
@@ -11005,7 +10790,6 @@
       <c r="AR211" s="2" t="n"/>
       <c r="AS211" s="2" t="n"/>
       <c r="AT211" s="2" t="n"/>
-      <c r="AU211" s="2" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n"/>
@@ -11054,7 +10838,6 @@
       <c r="AR212" s="2" t="n"/>
       <c r="AS212" s="2" t="n"/>
       <c r="AT212" s="2" t="n"/>
-      <c r="AU212" s="2" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n"/>
@@ -11103,7 +10886,6 @@
       <c r="AR213" s="2" t="n"/>
       <c r="AS213" s="2" t="n"/>
       <c r="AT213" s="2" t="n"/>
-      <c r="AU213" s="2" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n"/>
@@ -11152,7 +10934,6 @@
       <c r="AR214" s="2" t="n"/>
       <c r="AS214" s="2" t="n"/>
       <c r="AT214" s="2" t="n"/>
-      <c r="AU214" s="2" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n"/>
@@ -11201,7 +10982,6 @@
       <c r="AR215" s="2" t="n"/>
       <c r="AS215" s="2" t="n"/>
       <c r="AT215" s="2" t="n"/>
-      <c r="AU215" s="2" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n"/>
@@ -11250,7 +11030,6 @@
       <c r="AR216" s="2" t="n"/>
       <c r="AS216" s="2" t="n"/>
       <c r="AT216" s="2" t="n"/>
-      <c r="AU216" s="2" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n"/>
@@ -11299,7 +11078,6 @@
       <c r="AR217" s="2" t="n"/>
       <c r="AS217" s="2" t="n"/>
       <c r="AT217" s="2" t="n"/>
-      <c r="AU217" s="2" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n"/>
@@ -11348,7 +11126,6 @@
       <c r="AR218" s="2" t="n"/>
       <c r="AS218" s="2" t="n"/>
       <c r="AT218" s="2" t="n"/>
-      <c r="AU218" s="2" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n"/>
@@ -11397,7 +11174,6 @@
       <c r="AR219" s="2" t="n"/>
       <c r="AS219" s="2" t="n"/>
       <c r="AT219" s="2" t="n"/>
-      <c r="AU219" s="2" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n"/>
@@ -11446,7 +11222,6 @@
       <c r="AR220" s="2" t="n"/>
       <c r="AS220" s="2" t="n"/>
       <c r="AT220" s="2" t="n"/>
-      <c r="AU220" s="2" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n"/>
@@ -11495,7 +11270,6 @@
       <c r="AR221" s="2" t="n"/>
       <c r="AS221" s="2" t="n"/>
       <c r="AT221" s="2" t="n"/>
-      <c r="AU221" s="2" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n"/>
@@ -11544,7 +11318,6 @@
       <c r="AR222" s="2" t="n"/>
       <c r="AS222" s="2" t="n"/>
       <c r="AT222" s="2" t="n"/>
-      <c r="AU222" s="2" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n"/>
@@ -11593,7 +11366,6 @@
       <c r="AR223" s="2" t="n"/>
       <c r="AS223" s="2" t="n"/>
       <c r="AT223" s="2" t="n"/>
-      <c r="AU223" s="2" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n"/>
@@ -11642,7 +11414,6 @@
       <c r="AR224" s="2" t="n"/>
       <c r="AS224" s="2" t="n"/>
       <c r="AT224" s="2" t="n"/>
-      <c r="AU224" s="2" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n"/>
@@ -11691,7 +11462,6 @@
       <c r="AR225" s="2" t="n"/>
       <c r="AS225" s="2" t="n"/>
       <c r="AT225" s="2" t="n"/>
-      <c r="AU225" s="2" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n"/>
@@ -11740,7 +11510,6 @@
       <c r="AR226" s="2" t="n"/>
       <c r="AS226" s="2" t="n"/>
       <c r="AT226" s="2" t="n"/>
-      <c r="AU226" s="2" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n"/>
@@ -11789,7 +11558,6 @@
       <c r="AR227" s="2" t="n"/>
       <c r="AS227" s="2" t="n"/>
       <c r="AT227" s="2" t="n"/>
-      <c r="AU227" s="2" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n"/>
@@ -11838,7 +11606,6 @@
       <c r="AR228" s="2" t="n"/>
       <c r="AS228" s="2" t="n"/>
       <c r="AT228" s="2" t="n"/>
-      <c r="AU228" s="2" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n"/>
@@ -11887,7 +11654,6 @@
       <c r="AR229" s="2" t="n"/>
       <c r="AS229" s="2" t="n"/>
       <c r="AT229" s="2" t="n"/>
-      <c r="AU229" s="2" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n"/>
@@ -11936,7 +11702,6 @@
       <c r="AR230" s="2" t="n"/>
       <c r="AS230" s="2" t="n"/>
       <c r="AT230" s="2" t="n"/>
-      <c r="AU230" s="2" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n"/>
@@ -11985,7 +11750,6 @@
       <c r="AR231" s="2" t="n"/>
       <c r="AS231" s="2" t="n"/>
       <c r="AT231" s="2" t="n"/>
-      <c r="AU231" s="2" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n"/>
@@ -12034,7 +11798,6 @@
       <c r="AR232" s="2" t="n"/>
       <c r="AS232" s="2" t="n"/>
       <c r="AT232" s="2" t="n"/>
-      <c r="AU232" s="2" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n"/>
@@ -12083,7 +11846,6 @@
       <c r="AR233" s="2" t="n"/>
       <c r="AS233" s="2" t="n"/>
       <c r="AT233" s="2" t="n"/>
-      <c r="AU233" s="2" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n"/>
@@ -12132,7 +11894,6 @@
       <c r="AR234" s="2" t="n"/>
       <c r="AS234" s="2" t="n"/>
       <c r="AT234" s="2" t="n"/>
-      <c r="AU234" s="2" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n"/>
@@ -12181,7 +11942,6 @@
       <c r="AR235" s="2" t="n"/>
       <c r="AS235" s="2" t="n"/>
       <c r="AT235" s="2" t="n"/>
-      <c r="AU235" s="2" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n"/>
@@ -12230,7 +11990,6 @@
       <c r="AR236" s="2" t="n"/>
       <c r="AS236" s="2" t="n"/>
       <c r="AT236" s="2" t="n"/>
-      <c r="AU236" s="2" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n"/>
@@ -12279,7 +12038,6 @@
       <c r="AR237" s="2" t="n"/>
       <c r="AS237" s="2" t="n"/>
       <c r="AT237" s="2" t="n"/>
-      <c r="AU237" s="2" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n"/>
@@ -12328,7 +12086,6 @@
       <c r="AR238" s="2" t="n"/>
       <c r="AS238" s="2" t="n"/>
       <c r="AT238" s="2" t="n"/>
-      <c r="AU238" s="2" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n"/>
@@ -12377,7 +12134,6 @@
       <c r="AR239" s="2" t="n"/>
       <c r="AS239" s="2" t="n"/>
       <c r="AT239" s="2" t="n"/>
-      <c r="AU239" s="2" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n"/>
@@ -12426,7 +12182,6 @@
       <c r="AR240" s="2" t="n"/>
       <c r="AS240" s="2" t="n"/>
       <c r="AT240" s="2" t="n"/>
-      <c r="AU240" s="2" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n"/>
@@ -12475,7 +12230,6 @@
       <c r="AR241" s="2" t="n"/>
       <c r="AS241" s="2" t="n"/>
       <c r="AT241" s="2" t="n"/>
-      <c r="AU241" s="2" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n"/>
@@ -12524,7 +12278,6 @@
       <c r="AR242" s="2" t="n"/>
       <c r="AS242" s="2" t="n"/>
       <c r="AT242" s="2" t="n"/>
-      <c r="AU242" s="2" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n"/>
@@ -12573,7 +12326,6 @@
       <c r="AR243" s="2" t="n"/>
       <c r="AS243" s="2" t="n"/>
       <c r="AT243" s="2" t="n"/>
-      <c r="AU243" s="2" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n"/>
@@ -12622,7 +12374,6 @@
       <c r="AR244" s="2" t="n"/>
       <c r="AS244" s="2" t="n"/>
       <c r="AT244" s="2" t="n"/>
-      <c r="AU244" s="2" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n"/>
@@ -12671,7 +12422,6 @@
       <c r="AR245" s="2" t="n"/>
       <c r="AS245" s="2" t="n"/>
       <c r="AT245" s="2" t="n"/>
-      <c r="AU245" s="2" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n"/>
@@ -12720,7 +12470,6 @@
       <c r="AR246" s="2" t="n"/>
       <c r="AS246" s="2" t="n"/>
       <c r="AT246" s="2" t="n"/>
-      <c r="AU246" s="2" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n"/>
@@ -12769,7 +12518,6 @@
       <c r="AR247" s="2" t="n"/>
       <c r="AS247" s="2" t="n"/>
       <c r="AT247" s="2" t="n"/>
-      <c r="AU247" s="2" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n"/>
@@ -12818,7 +12566,6 @@
       <c r="AR248" s="2" t="n"/>
       <c r="AS248" s="2" t="n"/>
       <c r="AT248" s="2" t="n"/>
-      <c r="AU248" s="2" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n"/>
@@ -12867,7 +12614,6 @@
       <c r="AR249" s="2" t="n"/>
       <c r="AS249" s="2" t="n"/>
       <c r="AT249" s="2" t="n"/>
-      <c r="AU249" s="2" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n"/>
@@ -12916,7 +12662,6 @@
       <c r="AR250" s="2" t="n"/>
       <c r="AS250" s="2" t="n"/>
       <c r="AT250" s="2" t="n"/>
-      <c r="AU250" s="2" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n"/>
@@ -12965,7 +12710,6 @@
       <c r="AR251" s="2" t="n"/>
       <c r="AS251" s="2" t="n"/>
       <c r="AT251" s="2" t="n"/>
-      <c r="AU251" s="2" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n"/>
@@ -13014,7 +12758,6 @@
       <c r="AR252" s="2" t="n"/>
       <c r="AS252" s="2" t="n"/>
       <c r="AT252" s="2" t="n"/>
-      <c r="AU252" s="2" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n"/>
@@ -13063,7 +12806,6 @@
       <c r="AR253" s="2" t="n"/>
       <c r="AS253" s="2" t="n"/>
       <c r="AT253" s="2" t="n"/>
-      <c r="AU253" s="2" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n"/>
@@ -13112,7 +12854,6 @@
       <c r="AR254" s="2" t="n"/>
       <c r="AS254" s="2" t="n"/>
       <c r="AT254" s="2" t="n"/>
-      <c r="AU254" s="2" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n"/>
@@ -13161,7 +12902,6 @@
       <c r="AR255" s="2" t="n"/>
       <c r="AS255" s="2" t="n"/>
       <c r="AT255" s="2" t="n"/>
-      <c r="AU255" s="2" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n"/>
@@ -13210,7 +12950,6 @@
       <c r="AR256" s="2" t="n"/>
       <c r="AS256" s="2" t="n"/>
       <c r="AT256" s="2" t="n"/>
-      <c r="AU256" s="2" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n"/>
@@ -13259,7 +12998,6 @@
       <c r="AR257" s="2" t="n"/>
       <c r="AS257" s="2" t="n"/>
       <c r="AT257" s="2" t="n"/>
-      <c r="AU257" s="2" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n"/>
@@ -13308,7 +13046,6 @@
       <c r="AR258" s="2" t="n"/>
       <c r="AS258" s="2" t="n"/>
       <c r="AT258" s="2" t="n"/>
-      <c r="AU258" s="2" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n"/>
@@ -13357,7 +13094,6 @@
       <c r="AR259" s="2" t="n"/>
       <c r="AS259" s="2" t="n"/>
       <c r="AT259" s="2" t="n"/>
-      <c r="AU259" s="2" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n"/>
@@ -13406,7 +13142,6 @@
       <c r="AR260" s="2" t="n"/>
       <c r="AS260" s="2" t="n"/>
       <c r="AT260" s="2" t="n"/>
-      <c r="AU260" s="2" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n"/>
@@ -13455,7 +13190,6 @@
       <c r="AR261" s="2" t="n"/>
       <c r="AS261" s="2" t="n"/>
       <c r="AT261" s="2" t="n"/>
-      <c r="AU261" s="2" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n"/>
@@ -13504,7 +13238,6 @@
       <c r="AR262" s="2" t="n"/>
       <c r="AS262" s="2" t="n"/>
       <c r="AT262" s="2" t="n"/>
-      <c r="AU262" s="2" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n"/>
@@ -13553,7 +13286,6 @@
       <c r="AR263" s="2" t="n"/>
       <c r="AS263" s="2" t="n"/>
       <c r="AT263" s="2" t="n"/>
-      <c r="AU263" s="2" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n"/>
@@ -13602,7 +13334,6 @@
       <c r="AR264" s="2" t="n"/>
       <c r="AS264" s="2" t="n"/>
       <c r="AT264" s="2" t="n"/>
-      <c r="AU264" s="2" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n"/>
@@ -13651,7 +13382,6 @@
       <c r="AR265" s="2" t="n"/>
       <c r="AS265" s="2" t="n"/>
       <c r="AT265" s="2" t="n"/>
-      <c r="AU265" s="2" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n"/>
@@ -13700,7 +13430,6 @@
       <c r="AR266" s="2" t="n"/>
       <c r="AS266" s="2" t="n"/>
       <c r="AT266" s="2" t="n"/>
-      <c r="AU266" s="2" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n"/>
@@ -13749,7 +13478,6 @@
       <c r="AR267" s="2" t="n"/>
       <c r="AS267" s="2" t="n"/>
       <c r="AT267" s="2" t="n"/>
-      <c r="AU267" s="2" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n"/>
@@ -13798,7 +13526,6 @@
       <c r="AR268" s="2" t="n"/>
       <c r="AS268" s="2" t="n"/>
       <c r="AT268" s="2" t="n"/>
-      <c r="AU268" s="2" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n"/>
@@ -13847,7 +13574,6 @@
       <c r="AR269" s="2" t="n"/>
       <c r="AS269" s="2" t="n"/>
       <c r="AT269" s="2" t="n"/>
-      <c r="AU269" s="2" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n"/>
@@ -13896,7 +13622,6 @@
       <c r="AR270" s="2" t="n"/>
       <c r="AS270" s="2" t="n"/>
       <c r="AT270" s="2" t="n"/>
-      <c r="AU270" s="2" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n"/>
@@ -13945,7 +13670,6 @@
       <c r="AR271" s="2" t="n"/>
       <c r="AS271" s="2" t="n"/>
       <c r="AT271" s="2" t="n"/>
-      <c r="AU271" s="2" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n"/>
@@ -13994,7 +13718,6 @@
       <c r="AR272" s="2" t="n"/>
       <c r="AS272" s="2" t="n"/>
       <c r="AT272" s="2" t="n"/>
-      <c r="AU272" s="2" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n"/>
@@ -14043,7 +13766,6 @@
       <c r="AR273" s="2" t="n"/>
       <c r="AS273" s="2" t="n"/>
       <c r="AT273" s="2" t="n"/>
-      <c r="AU273" s="2" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n"/>
@@ -14092,7 +13814,6 @@
       <c r="AR274" s="2" t="n"/>
       <c r="AS274" s="2" t="n"/>
       <c r="AT274" s="2" t="n"/>
-      <c r="AU274" s="2" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n"/>
@@ -14141,7 +13862,6 @@
       <c r="AR275" s="2" t="n"/>
       <c r="AS275" s="2" t="n"/>
       <c r="AT275" s="2" t="n"/>
-      <c r="AU275" s="2" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n"/>
@@ -14190,7 +13910,6 @@
       <c r="AR276" s="2" t="n"/>
       <c r="AS276" s="2" t="n"/>
       <c r="AT276" s="2" t="n"/>
-      <c r="AU276" s="2" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n"/>
@@ -14239,7 +13958,6 @@
       <c r="AR277" s="2" t="n"/>
       <c r="AS277" s="2" t="n"/>
       <c r="AT277" s="2" t="n"/>
-      <c r="AU277" s="2" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n"/>
@@ -14288,7 +14006,6 @@
       <c r="AR278" s="2" t="n"/>
       <c r="AS278" s="2" t="n"/>
       <c r="AT278" s="2" t="n"/>
-      <c r="AU278" s="2" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n"/>
@@ -14337,7 +14054,6 @@
       <c r="AR279" s="2" t="n"/>
       <c r="AS279" s="2" t="n"/>
       <c r="AT279" s="2" t="n"/>
-      <c r="AU279" s="2" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n"/>
@@ -14386,7 +14102,6 @@
       <c r="AR280" s="2" t="n"/>
       <c r="AS280" s="2" t="n"/>
       <c r="AT280" s="2" t="n"/>
-      <c r="AU280" s="2" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n"/>
@@ -14435,7 +14150,6 @@
       <c r="AR281" s="2" t="n"/>
       <c r="AS281" s="2" t="n"/>
       <c r="AT281" s="2" t="n"/>
-      <c r="AU281" s="2" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n"/>
@@ -14484,7 +14198,6 @@
       <c r="AR282" s="2" t="n"/>
       <c r="AS282" s="2" t="n"/>
       <c r="AT282" s="2" t="n"/>
-      <c r="AU282" s="2" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n"/>
@@ -14533,7 +14246,6 @@
       <c r="AR283" s="2" t="n"/>
       <c r="AS283" s="2" t="n"/>
       <c r="AT283" s="2" t="n"/>
-      <c r="AU283" s="2" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n"/>
@@ -14582,7 +14294,6 @@
       <c r="AR284" s="2" t="n"/>
       <c r="AS284" s="2" t="n"/>
       <c r="AT284" s="2" t="n"/>
-      <c r="AU284" s="2" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n"/>
@@ -14631,7 +14342,6 @@
       <c r="AR285" s="2" t="n"/>
       <c r="AS285" s="2" t="n"/>
       <c r="AT285" s="2" t="n"/>
-      <c r="AU285" s="2" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n"/>
@@ -14680,7 +14390,6 @@
       <c r="AR286" s="2" t="n"/>
       <c r="AS286" s="2" t="n"/>
       <c r="AT286" s="2" t="n"/>
-      <c r="AU286" s="2" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n"/>
@@ -14729,7 +14438,6 @@
       <c r="AR287" s="2" t="n"/>
       <c r="AS287" s="2" t="n"/>
       <c r="AT287" s="2" t="n"/>
-      <c r="AU287" s="2" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n"/>
@@ -14778,7 +14486,6 @@
       <c r="AR288" s="2" t="n"/>
       <c r="AS288" s="2" t="n"/>
       <c r="AT288" s="2" t="n"/>
-      <c r="AU288" s="2" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n"/>
@@ -14827,7 +14534,6 @@
       <c r="AR289" s="2" t="n"/>
       <c r="AS289" s="2" t="n"/>
       <c r="AT289" s="2" t="n"/>
-      <c r="AU289" s="2" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n"/>
@@ -14876,7 +14582,6 @@
       <c r="AR290" s="2" t="n"/>
       <c r="AS290" s="2" t="n"/>
       <c r="AT290" s="2" t="n"/>
-      <c r="AU290" s="2" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n"/>
@@ -14925,7 +14630,6 @@
       <c r="AR291" s="2" t="n"/>
       <c r="AS291" s="2" t="n"/>
       <c r="AT291" s="2" t="n"/>
-      <c r="AU291" s="2" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n"/>
@@ -14974,7 +14678,6 @@
       <c r="AR292" s="2" t="n"/>
       <c r="AS292" s="2" t="n"/>
       <c r="AT292" s="2" t="n"/>
-      <c r="AU292" s="2" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n"/>
@@ -15023,7 +14726,6 @@
       <c r="AR293" s="2" t="n"/>
       <c r="AS293" s="2" t="n"/>
       <c r="AT293" s="2" t="n"/>
-      <c r="AU293" s="2" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n"/>
@@ -15072,7 +14774,6 @@
       <c r="AR294" s="2" t="n"/>
       <c r="AS294" s="2" t="n"/>
       <c r="AT294" s="2" t="n"/>
-      <c r="AU294" s="2" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n"/>
@@ -15121,7 +14822,6 @@
       <c r="AR295" s="2" t="n"/>
       <c r="AS295" s="2" t="n"/>
       <c r="AT295" s="2" t="n"/>
-      <c r="AU295" s="2" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n"/>
@@ -15170,7 +14870,6 @@
       <c r="AR296" s="2" t="n"/>
       <c r="AS296" s="2" t="n"/>
       <c r="AT296" s="2" t="n"/>
-      <c r="AU296" s="2" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n"/>
@@ -15219,7 +14918,6 @@
       <c r="AR297" s="2" t="n"/>
       <c r="AS297" s="2" t="n"/>
       <c r="AT297" s="2" t="n"/>
-      <c r="AU297" s="2" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n"/>
@@ -15268,7 +14966,6 @@
       <c r="AR298" s="2" t="n"/>
       <c r="AS298" s="2" t="n"/>
       <c r="AT298" s="2" t="n"/>
-      <c r="AU298" s="2" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n"/>
@@ -15317,7 +15014,6 @@
       <c r="AR299" s="2" t="n"/>
       <c r="AS299" s="2" t="n"/>
       <c r="AT299" s="2" t="n"/>
-      <c r="AU299" s="2" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n"/>
@@ -15366,7 +15062,6 @@
       <c r="AR300" s="2" t="n"/>
       <c r="AS300" s="2" t="n"/>
       <c r="AT300" s="2" t="n"/>
-      <c r="AU300" s="2" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n"/>
@@ -15415,7 +15110,6 @@
       <c r="AR301" s="2" t="n"/>
       <c r="AS301" s="2" t="n"/>
       <c r="AT301" s="2" t="n"/>
-      <c r="AU301" s="2" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="n"/>
@@ -15464,7 +15158,6 @@
       <c r="AR302" s="2" t="n"/>
       <c r="AS302" s="2" t="n"/>
       <c r="AT302" s="2" t="n"/>
-      <c r="AU302" s="2" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="2" t="n"/>
@@ -15513,7 +15206,6 @@
       <c r="AR303" s="2" t="n"/>
       <c r="AS303" s="2" t="n"/>
       <c r="AT303" s="2" t="n"/>
-      <c r="AU303" s="2" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="n"/>
@@ -15562,7 +15254,6 @@
       <c r="AR304" s="2" t="n"/>
       <c r="AS304" s="2" t="n"/>
       <c r="AT304" s="2" t="n"/>
-      <c r="AU304" s="2" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="n"/>
@@ -15611,7 +15302,6 @@
       <c r="AR305" s="2" t="n"/>
       <c r="AS305" s="2" t="n"/>
       <c r="AT305" s="2" t="n"/>
-      <c r="AU305" s="2" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="n"/>
@@ -15660,7 +15350,6 @@
       <c r="AR306" s="2" t="n"/>
       <c r="AS306" s="2" t="n"/>
       <c r="AT306" s="2" t="n"/>
-      <c r="AU306" s="2" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="2" t="n"/>
@@ -15709,7 +15398,6 @@
       <c r="AR307" s="2" t="n"/>
       <c r="AS307" s="2" t="n"/>
       <c r="AT307" s="2" t="n"/>
-      <c r="AU307" s="2" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="n"/>
@@ -15758,7 +15446,6 @@
       <c r="AR308" s="2" t="n"/>
       <c r="AS308" s="2" t="n"/>
       <c r="AT308" s="2" t="n"/>
-      <c r="AU308" s="2" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="n"/>
@@ -15807,7 +15494,6 @@
       <c r="AR309" s="2" t="n"/>
       <c r="AS309" s="2" t="n"/>
       <c r="AT309" s="2" t="n"/>
-      <c r="AU309" s="2" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="n"/>
@@ -15856,7 +15542,6 @@
       <c r="AR310" s="2" t="n"/>
       <c r="AS310" s="2" t="n"/>
       <c r="AT310" s="2" t="n"/>
-      <c r="AU310" s="2" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="2" t="n"/>
@@ -15905,7 +15590,6 @@
       <c r="AR311" s="2" t="n"/>
       <c r="AS311" s="2" t="n"/>
       <c r="AT311" s="2" t="n"/>
-      <c r="AU311" s="2" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="n"/>
@@ -15954,7 +15638,6 @@
       <c r="AR312" s="2" t="n"/>
       <c r="AS312" s="2" t="n"/>
       <c r="AT312" s="2" t="n"/>
-      <c r="AU312" s="2" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="2" t="n"/>
@@ -16003,7 +15686,6 @@
       <c r="AR313" s="2" t="n"/>
       <c r="AS313" s="2" t="n"/>
       <c r="AT313" s="2" t="n"/>
-      <c r="AU313" s="2" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="n"/>
@@ -16052,7 +15734,6 @@
       <c r="AR314" s="2" t="n"/>
       <c r="AS314" s="2" t="n"/>
       <c r="AT314" s="2" t="n"/>
-      <c r="AU314" s="2" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="n"/>
@@ -16101,7 +15782,6 @@
       <c r="AR315" s="2" t="n"/>
       <c r="AS315" s="2" t="n"/>
       <c r="AT315" s="2" t="n"/>
-      <c r="AU315" s="2" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="n"/>
@@ -16150,7 +15830,6 @@
       <c r="AR316" s="2" t="n"/>
       <c r="AS316" s="2" t="n"/>
       <c r="AT316" s="2" t="n"/>
-      <c r="AU316" s="2" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="2" t="n"/>
@@ -16199,7 +15878,6 @@
       <c r="AR317" s="2" t="n"/>
       <c r="AS317" s="2" t="n"/>
       <c r="AT317" s="2" t="n"/>
-      <c r="AU317" s="2" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="n"/>
@@ -16248,7 +15926,6 @@
       <c r="AR318" s="2" t="n"/>
       <c r="AS318" s="2" t="n"/>
       <c r="AT318" s="2" t="n"/>
-      <c r="AU318" s="2" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="n"/>
@@ -16297,7 +15974,6 @@
       <c r="AR319" s="2" t="n"/>
       <c r="AS319" s="2" t="n"/>
       <c r="AT319" s="2" t="n"/>
-      <c r="AU319" s="2" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="n"/>
@@ -16346,7 +16022,6 @@
       <c r="AR320" s="2" t="n"/>
       <c r="AS320" s="2" t="n"/>
       <c r="AT320" s="2" t="n"/>
-      <c r="AU320" s="2" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="2" t="n"/>
@@ -16395,7 +16070,6 @@
       <c r="AR321" s="2" t="n"/>
       <c r="AS321" s="2" t="n"/>
       <c r="AT321" s="2" t="n"/>
-      <c r="AU321" s="2" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="2" t="n"/>
@@ -16444,7 +16118,6 @@
       <c r="AR322" s="2" t="n"/>
       <c r="AS322" s="2" t="n"/>
       <c r="AT322" s="2" t="n"/>
-      <c r="AU322" s="2" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="2" t="n"/>
@@ -16493,7 +16166,6 @@
       <c r="AR323" s="2" t="n"/>
       <c r="AS323" s="2" t="n"/>
       <c r="AT323" s="2" t="n"/>
-      <c r="AU323" s="2" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="n"/>
@@ -16542,7 +16214,6 @@
       <c r="AR324" s="2" t="n"/>
       <c r="AS324" s="2" t="n"/>
       <c r="AT324" s="2" t="n"/>
-      <c r="AU324" s="2" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="2" t="n"/>
@@ -16591,7 +16262,6 @@
       <c r="AR325" s="2" t="n"/>
       <c r="AS325" s="2" t="n"/>
       <c r="AT325" s="2" t="n"/>
-      <c r="AU325" s="2" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="n"/>
@@ -16640,7 +16310,6 @@
       <c r="AR326" s="2" t="n"/>
       <c r="AS326" s="2" t="n"/>
       <c r="AT326" s="2" t="n"/>
-      <c r="AU326" s="2" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="n"/>
@@ -16689,7 +16358,6 @@
       <c r="AR327" s="2" t="n"/>
       <c r="AS327" s="2" t="n"/>
       <c r="AT327" s="2" t="n"/>
-      <c r="AU327" s="2" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="n"/>
@@ -16738,7 +16406,6 @@
       <c r="AR328" s="2" t="n"/>
       <c r="AS328" s="2" t="n"/>
       <c r="AT328" s="2" t="n"/>
-      <c r="AU328" s="2" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="2" t="n"/>
@@ -16787,7 +16454,6 @@
       <c r="AR329" s="2" t="n"/>
       <c r="AS329" s="2" t="n"/>
       <c r="AT329" s="2" t="n"/>
-      <c r="AU329" s="2" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="n"/>
@@ -16836,7 +16502,6 @@
       <c r="AR330" s="2" t="n"/>
       <c r="AS330" s="2" t="n"/>
       <c r="AT330" s="2" t="n"/>
-      <c r="AU330" s="2" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="2" t="n"/>
@@ -16885,7 +16550,6 @@
       <c r="AR331" s="2" t="n"/>
       <c r="AS331" s="2" t="n"/>
       <c r="AT331" s="2" t="n"/>
-      <c r="AU331" s="2" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="n"/>
@@ -16934,7 +16598,6 @@
       <c r="AR332" s="2" t="n"/>
       <c r="AS332" s="2" t="n"/>
       <c r="AT332" s="2" t="n"/>
-      <c r="AU332" s="2" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="2" t="n"/>
@@ -16983,7 +16646,6 @@
       <c r="AR333" s="2" t="n"/>
       <c r="AS333" s="2" t="n"/>
       <c r="AT333" s="2" t="n"/>
-      <c r="AU333" s="2" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="2" t="n"/>
@@ -17032,7 +16694,6 @@
       <c r="AR334" s="2" t="n"/>
       <c r="AS334" s="2" t="n"/>
       <c r="AT334" s="2" t="n"/>
-      <c r="AU334" s="2" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="2" t="n"/>
@@ -17081,7 +16742,6 @@
       <c r="AR335" s="2" t="n"/>
       <c r="AS335" s="2" t="n"/>
       <c r="AT335" s="2" t="n"/>
-      <c r="AU335" s="2" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="n"/>
@@ -17130,7 +16790,6 @@
       <c r="AR336" s="2" t="n"/>
       <c r="AS336" s="2" t="n"/>
       <c r="AT336" s="2" t="n"/>
-      <c r="AU336" s="2" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="2" t="n"/>
@@ -17179,7 +16838,6 @@
       <c r="AR337" s="2" t="n"/>
       <c r="AS337" s="2" t="n"/>
       <c r="AT337" s="2" t="n"/>
-      <c r="AU337" s="2" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="n"/>
@@ -17228,7 +16886,6 @@
       <c r="AR338" s="2" t="n"/>
       <c r="AS338" s="2" t="n"/>
       <c r="AT338" s="2" t="n"/>
-      <c r="AU338" s="2" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="2" t="n"/>
@@ -17277,7 +16934,6 @@
       <c r="AR339" s="2" t="n"/>
       <c r="AS339" s="2" t="n"/>
       <c r="AT339" s="2" t="n"/>
-      <c r="AU339" s="2" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="n"/>
@@ -17326,7 +16982,6 @@
       <c r="AR340" s="2" t="n"/>
       <c r="AS340" s="2" t="n"/>
       <c r="AT340" s="2" t="n"/>
-      <c r="AU340" s="2" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="2" t="n"/>
@@ -17375,7 +17030,6 @@
       <c r="AR341" s="2" t="n"/>
       <c r="AS341" s="2" t="n"/>
       <c r="AT341" s="2" t="n"/>
-      <c r="AU341" s="2" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="n"/>
@@ -17424,7 +17078,6 @@
       <c r="AR342" s="2" t="n"/>
       <c r="AS342" s="2" t="n"/>
       <c r="AT342" s="2" t="n"/>
-      <c r="AU342" s="2" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="2" t="n"/>
@@ -17473,7 +17126,6 @@
       <c r="AR343" s="2" t="n"/>
       <c r="AS343" s="2" t="n"/>
       <c r="AT343" s="2" t="n"/>
-      <c r="AU343" s="2" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="n"/>
@@ -17522,7 +17174,6 @@
       <c r="AR344" s="2" t="n"/>
       <c r="AS344" s="2" t="n"/>
       <c r="AT344" s="2" t="n"/>
-      <c r="AU344" s="2" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="2" t="n"/>
@@ -17571,7 +17222,6 @@
       <c r="AR345" s="2" t="n"/>
       <c r="AS345" s="2" t="n"/>
       <c r="AT345" s="2" t="n"/>
-      <c r="AU345" s="2" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="n"/>
@@ -17620,7 +17270,6 @@
       <c r="AR346" s="2" t="n"/>
       <c r="AS346" s="2" t="n"/>
       <c r="AT346" s="2" t="n"/>
-      <c r="AU346" s="2" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="n"/>
@@ -17669,7 +17318,6 @@
       <c r="AR347" s="2" t="n"/>
       <c r="AS347" s="2" t="n"/>
       <c r="AT347" s="2" t="n"/>
-      <c r="AU347" s="2" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="n"/>
@@ -17718,7 +17366,6 @@
       <c r="AR348" s="2" t="n"/>
       <c r="AS348" s="2" t="n"/>
       <c r="AT348" s="2" t="n"/>
-      <c r="AU348" s="2" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="2" t="n"/>
@@ -17767,7 +17414,6 @@
       <c r="AR349" s="2" t="n"/>
       <c r="AS349" s="2" t="n"/>
       <c r="AT349" s="2" t="n"/>
-      <c r="AU349" s="2" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="n"/>
@@ -17816,7 +17462,6 @@
       <c r="AR350" s="2" t="n"/>
       <c r="AS350" s="2" t="n"/>
       <c r="AT350" s="2" t="n"/>
-      <c r="AU350" s="2" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="2" t="n"/>
@@ -17865,7 +17510,6 @@
       <c r="AR351" s="2" t="n"/>
       <c r="AS351" s="2" t="n"/>
       <c r="AT351" s="2" t="n"/>
-      <c r="AU351" s="2" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="n"/>
@@ -17914,7 +17558,6 @@
       <c r="AR352" s="2" t="n"/>
       <c r="AS352" s="2" t="n"/>
       <c r="AT352" s="2" t="n"/>
-      <c r="AU352" s="2" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="2" t="n"/>
@@ -17963,7 +17606,6 @@
       <c r="AR353" s="2" t="n"/>
       <c r="AS353" s="2" t="n"/>
       <c r="AT353" s="2" t="n"/>
-      <c r="AU353" s="2" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="n"/>
@@ -18012,7 +17654,6 @@
       <c r="AR354" s="2" t="n"/>
       <c r="AS354" s="2" t="n"/>
       <c r="AT354" s="2" t="n"/>
-      <c r="AU354" s="2" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="2" t="n"/>
@@ -18061,7 +17702,6 @@
       <c r="AR355" s="2" t="n"/>
       <c r="AS355" s="2" t="n"/>
       <c r="AT355" s="2" t="n"/>
-      <c r="AU355" s="2" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="n"/>
@@ -18110,7 +17750,6 @@
       <c r="AR356" s="2" t="n"/>
       <c r="AS356" s="2" t="n"/>
       <c r="AT356" s="2" t="n"/>
-      <c r="AU356" s="2" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="n"/>
@@ -18159,7 +17798,6 @@
       <c r="AR357" s="2" t="n"/>
       <c r="AS357" s="2" t="n"/>
       <c r="AT357" s="2" t="n"/>
-      <c r="AU357" s="2" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="n"/>
@@ -18208,7 +17846,6 @@
       <c r="AR358" s="2" t="n"/>
       <c r="AS358" s="2" t="n"/>
       <c r="AT358" s="2" t="n"/>
-      <c r="AU358" s="2" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="2" t="n"/>
@@ -18257,7 +17894,6 @@
       <c r="AR359" s="2" t="n"/>
       <c r="AS359" s="2" t="n"/>
       <c r="AT359" s="2" t="n"/>
-      <c r="AU359" s="2" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="n"/>
@@ -18306,7 +17942,6 @@
       <c r="AR360" s="2" t="n"/>
       <c r="AS360" s="2" t="n"/>
       <c r="AT360" s="2" t="n"/>
-      <c r="AU360" s="2" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="2" t="n"/>
@@ -18355,7 +17990,6 @@
       <c r="AR361" s="2" t="n"/>
       <c r="AS361" s="2" t="n"/>
       <c r="AT361" s="2" t="n"/>
-      <c r="AU361" s="2" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="n"/>
@@ -18404,7 +18038,6 @@
       <c r="AR362" s="2" t="n"/>
       <c r="AS362" s="2" t="n"/>
       <c r="AT362" s="2" t="n"/>
-      <c r="AU362" s="2" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="2" t="n"/>
@@ -18453,7 +18086,6 @@
       <c r="AR363" s="2" t="n"/>
       <c r="AS363" s="2" t="n"/>
       <c r="AT363" s="2" t="n"/>
-      <c r="AU363" s="2" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="n"/>
@@ -18502,7 +18134,6 @@
       <c r="AR364" s="2" t="n"/>
       <c r="AS364" s="2" t="n"/>
       <c r="AT364" s="2" t="n"/>
-      <c r="AU364" s="2" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="n"/>
@@ -18551,7 +18182,6 @@
       <c r="AR365" s="2" t="n"/>
       <c r="AS365" s="2" t="n"/>
       <c r="AT365" s="2" t="n"/>
-      <c r="AU365" s="2" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="n"/>
@@ -18600,7 +18230,6 @@
       <c r="AR366" s="2" t="n"/>
       <c r="AS366" s="2" t="n"/>
       <c r="AT366" s="2" t="n"/>
-      <c r="AU366" s="2" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="n"/>
@@ -18649,7 +18278,6 @@
       <c r="AR367" s="2" t="n"/>
       <c r="AS367" s="2" t="n"/>
       <c r="AT367" s="2" t="n"/>
-      <c r="AU367" s="2" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="n"/>
@@ -18698,7 +18326,6 @@
       <c r="AR368" s="2" t="n"/>
       <c r="AS368" s="2" t="n"/>
       <c r="AT368" s="2" t="n"/>
-      <c r="AU368" s="2" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="2" t="n"/>
@@ -18747,7 +18374,6 @@
       <c r="AR369" s="2" t="n"/>
       <c r="AS369" s="2" t="n"/>
       <c r="AT369" s="2" t="n"/>
-      <c r="AU369" s="2" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="n"/>
@@ -18796,7 +18422,6 @@
       <c r="AR370" s="2" t="n"/>
       <c r="AS370" s="2" t="n"/>
       <c r="AT370" s="2" t="n"/>
-      <c r="AU370" s="2" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="n"/>
@@ -18845,7 +18470,6 @@
       <c r="AR371" s="2" t="n"/>
       <c r="AS371" s="2" t="n"/>
       <c r="AT371" s="2" t="n"/>
-      <c r="AU371" s="2" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="n"/>
@@ -18894,7 +18518,6 @@
       <c r="AR372" s="2" t="n"/>
       <c r="AS372" s="2" t="n"/>
       <c r="AT372" s="2" t="n"/>
-      <c r="AU372" s="2" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="2" t="n"/>
@@ -18943,7 +18566,6 @@
       <c r="AR373" s="2" t="n"/>
       <c r="AS373" s="2" t="n"/>
       <c r="AT373" s="2" t="n"/>
-      <c r="AU373" s="2" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="n"/>
@@ -18992,7 +18614,6 @@
       <c r="AR374" s="2" t="n"/>
       <c r="AS374" s="2" t="n"/>
       <c r="AT374" s="2" t="n"/>
-      <c r="AU374" s="2" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="2" t="n"/>
@@ -19041,7 +18662,6 @@
       <c r="AR375" s="2" t="n"/>
       <c r="AS375" s="2" t="n"/>
       <c r="AT375" s="2" t="n"/>
-      <c r="AU375" s="2" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="n"/>
@@ -19090,7 +18710,6 @@
       <c r="AR376" s="2" t="n"/>
       <c r="AS376" s="2" t="n"/>
       <c r="AT376" s="2" t="n"/>
-      <c r="AU376" s="2" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="2" t="n"/>
@@ -19139,7 +18758,6 @@
       <c r="AR377" s="2" t="n"/>
       <c r="AS377" s="2" t="n"/>
       <c r="AT377" s="2" t="n"/>
-      <c r="AU377" s="2" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="n"/>
@@ -19188,7 +18806,6 @@
       <c r="AR378" s="2" t="n"/>
       <c r="AS378" s="2" t="n"/>
       <c r="AT378" s="2" t="n"/>
-      <c r="AU378" s="2" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="2" t="n"/>
@@ -19237,7 +18854,6 @@
       <c r="AR379" s="2" t="n"/>
       <c r="AS379" s="2" t="n"/>
       <c r="AT379" s="2" t="n"/>
-      <c r="AU379" s="2" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="n"/>
@@ -19286,7 +18902,6 @@
       <c r="AR380" s="2" t="n"/>
       <c r="AS380" s="2" t="n"/>
       <c r="AT380" s="2" t="n"/>
-      <c r="AU380" s="2" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="2" t="n"/>
@@ -19335,7 +18950,6 @@
       <c r="AR381" s="2" t="n"/>
       <c r="AS381" s="2" t="n"/>
       <c r="AT381" s="2" t="n"/>
-      <c r="AU381" s="2" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="n"/>
@@ -19384,7 +18998,6 @@
       <c r="AR382" s="2" t="n"/>
       <c r="AS382" s="2" t="n"/>
       <c r="AT382" s="2" t="n"/>
-      <c r="AU382" s="2" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="2" t="n"/>
@@ -19433,7 +19046,6 @@
       <c r="AR383" s="2" t="n"/>
       <c r="AS383" s="2" t="n"/>
       <c r="AT383" s="2" t="n"/>
-      <c r="AU383" s="2" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n"/>
@@ -19482,7 +19094,6 @@
       <c r="AR384" s="2" t="n"/>
       <c r="AS384" s="2" t="n"/>
       <c r="AT384" s="2" t="n"/>
-      <c r="AU384" s="2" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="n"/>
@@ -19531,7 +19142,6 @@
       <c r="AR385" s="2" t="n"/>
       <c r="AS385" s="2" t="n"/>
       <c r="AT385" s="2" t="n"/>
-      <c r="AU385" s="2" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n"/>
@@ -19580,7 +19190,6 @@
       <c r="AR386" s="2" t="n"/>
       <c r="AS386" s="2" t="n"/>
       <c r="AT386" s="2" t="n"/>
-      <c r="AU386" s="2" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="2" t="n"/>
@@ -19629,7 +19238,6 @@
       <c r="AR387" s="2" t="n"/>
       <c r="AS387" s="2" t="n"/>
       <c r="AT387" s="2" t="n"/>
-      <c r="AU387" s="2" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="n"/>
@@ -19678,7 +19286,6 @@
       <c r="AR388" s="2" t="n"/>
       <c r="AS388" s="2" t="n"/>
       <c r="AT388" s="2" t="n"/>
-      <c r="AU388" s="2" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n"/>
@@ -19727,7 +19334,6 @@
       <c r="AR389" s="2" t="n"/>
       <c r="AS389" s="2" t="n"/>
       <c r="AT389" s="2" t="n"/>
-      <c r="AU389" s="2" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n"/>
@@ -19776,7 +19382,6 @@
       <c r="AR390" s="2" t="n"/>
       <c r="AS390" s="2" t="n"/>
       <c r="AT390" s="2" t="n"/>
-      <c r="AU390" s="2" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n"/>
@@ -19825,7 +19430,6 @@
       <c r="AR391" s="2" t="n"/>
       <c r="AS391" s="2" t="n"/>
       <c r="AT391" s="2" t="n"/>
-      <c r="AU391" s="2" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n"/>
@@ -19874,7 +19478,6 @@
       <c r="AR392" s="2" t="n"/>
       <c r="AS392" s="2" t="n"/>
       <c r="AT392" s="2" t="n"/>
-      <c r="AU392" s="2" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n"/>
@@ -19923,7 +19526,6 @@
       <c r="AR393" s="2" t="n"/>
       <c r="AS393" s="2" t="n"/>
       <c r="AT393" s="2" t="n"/>
-      <c r="AU393" s="2" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n"/>
@@ -19972,7 +19574,6 @@
       <c r="AR394" s="2" t="n"/>
       <c r="AS394" s="2" t="n"/>
       <c r="AT394" s="2" t="n"/>
-      <c r="AU394" s="2" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="2" t="n"/>
@@ -20021,7 +19622,6 @@
       <c r="AR395" s="2" t="n"/>
       <c r="AS395" s="2" t="n"/>
       <c r="AT395" s="2" t="n"/>
-      <c r="AU395" s="2" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="n"/>
@@ -20070,7 +19670,6 @@
       <c r="AR396" s="2" t="n"/>
       <c r="AS396" s="2" t="n"/>
       <c r="AT396" s="2" t="n"/>
-      <c r="AU396" s="2" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n"/>
@@ -20119,7 +19718,6 @@
       <c r="AR397" s="2" t="n"/>
       <c r="AS397" s="2" t="n"/>
       <c r="AT397" s="2" t="n"/>
-      <c r="AU397" s="2" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n"/>
@@ -20168,7 +19766,6 @@
       <c r="AR398" s="2" t="n"/>
       <c r="AS398" s="2" t="n"/>
       <c r="AT398" s="2" t="n"/>
-      <c r="AU398" s="2" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="2" t="n"/>
@@ -20217,7 +19814,6 @@
       <c r="AR399" s="2" t="n"/>
       <c r="AS399" s="2" t="n"/>
       <c r="AT399" s="2" t="n"/>
-      <c r="AU399" s="2" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n"/>
@@ -20266,7 +19862,6 @@
       <c r="AR400" s="2" t="n"/>
       <c r="AS400" s="2" t="n"/>
       <c r="AT400" s="2" t="n"/>
-      <c r="AU400" s="2" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="2" t="n"/>
@@ -20315,7 +19910,6 @@
       <c r="AR401" s="2" t="n"/>
       <c r="AS401" s="2" t="n"/>
       <c r="AT401" s="2" t="n"/>
-      <c r="AU401" s="2" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n"/>
@@ -20364,7 +19958,6 @@
       <c r="AR402" s="2" t="n"/>
       <c r="AS402" s="2" t="n"/>
       <c r="AT402" s="2" t="n"/>
-      <c r="AU402" s="2" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n"/>
@@ -20413,7 +20006,6 @@
       <c r="AR403" s="2" t="n"/>
       <c r="AS403" s="2" t="n"/>
       <c r="AT403" s="2" t="n"/>
-      <c r="AU403" s="2" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n"/>
@@ -20462,7 +20054,6 @@
       <c r="AR404" s="2" t="n"/>
       <c r="AS404" s="2" t="n"/>
       <c r="AT404" s="2" t="n"/>
-      <c r="AU404" s="2" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n"/>
@@ -20511,7 +20102,6 @@
       <c r="AR405" s="2" t="n"/>
       <c r="AS405" s="2" t="n"/>
       <c r="AT405" s="2" t="n"/>
-      <c r="AU405" s="2" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n"/>
@@ -20560,7 +20150,6 @@
       <c r="AR406" s="2" t="n"/>
       <c r="AS406" s="2" t="n"/>
       <c r="AT406" s="2" t="n"/>
-      <c r="AU406" s="2" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n"/>
@@ -20609,7 +20198,6 @@
       <c r="AR407" s="2" t="n"/>
       <c r="AS407" s="2" t="n"/>
       <c r="AT407" s="2" t="n"/>
-      <c r="AU407" s="2" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n"/>
@@ -20658,7 +20246,6 @@
       <c r="AR408" s="2" t="n"/>
       <c r="AS408" s="2" t="n"/>
       <c r="AT408" s="2" t="n"/>
-      <c r="AU408" s="2" t="n"/>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n"/>
@@ -20707,7 +20294,6 @@
       <c r="AR409" s="2" t="n"/>
       <c r="AS409" s="2" t="n"/>
       <c r="AT409" s="2" t="n"/>
-      <c r="AU409" s="2" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n"/>
@@ -20756,7 +20342,6 @@
       <c r="AR410" s="2" t="n"/>
       <c r="AS410" s="2" t="n"/>
       <c r="AT410" s="2" t="n"/>
-      <c r="AU410" s="2" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n"/>
@@ -20805,7 +20390,6 @@
       <c r="AR411" s="2" t="n"/>
       <c r="AS411" s="2" t="n"/>
       <c r="AT411" s="2" t="n"/>
-      <c r="AU411" s="2" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n"/>
@@ -20854,7 +20438,6 @@
       <c r="AR412" s="2" t="n"/>
       <c r="AS412" s="2" t="n"/>
       <c r="AT412" s="2" t="n"/>
-      <c r="AU412" s="2" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n"/>
@@ -20903,7 +20486,6 @@
       <c r="AR413" s="2" t="n"/>
       <c r="AS413" s="2" t="n"/>
       <c r="AT413" s="2" t="n"/>
-      <c r="AU413" s="2" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n"/>
@@ -20952,7 +20534,6 @@
       <c r="AR414" s="2" t="n"/>
       <c r="AS414" s="2" t="n"/>
       <c r="AT414" s="2" t="n"/>
-      <c r="AU414" s="2" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n"/>
@@ -21001,7 +20582,6 @@
       <c r="AR415" s="2" t="n"/>
       <c r="AS415" s="2" t="n"/>
       <c r="AT415" s="2" t="n"/>
-      <c r="AU415" s="2" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n"/>
@@ -21050,7 +20630,6 @@
       <c r="AR416" s="2" t="n"/>
       <c r="AS416" s="2" t="n"/>
       <c r="AT416" s="2" t="n"/>
-      <c r="AU416" s="2" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n"/>
@@ -21099,7 +20678,6 @@
       <c r="AR417" s="2" t="n"/>
       <c r="AS417" s="2" t="n"/>
       <c r="AT417" s="2" t="n"/>
-      <c r="AU417" s="2" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n"/>
@@ -21148,7 +20726,6 @@
       <c r="AR418" s="2" t="n"/>
       <c r="AS418" s="2" t="n"/>
       <c r="AT418" s="2" t="n"/>
-      <c r="AU418" s="2" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n"/>
@@ -21197,7 +20774,6 @@
       <c r="AR419" s="2" t="n"/>
       <c r="AS419" s="2" t="n"/>
       <c r="AT419" s="2" t="n"/>
-      <c r="AU419" s="2" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n"/>
@@ -21246,7 +20822,6 @@
       <c r="AR420" s="2" t="n"/>
       <c r="AS420" s="2" t="n"/>
       <c r="AT420" s="2" t="n"/>
-      <c r="AU420" s="2" t="n"/>
     </row>
     <row r="421">
       <c r="A421" s="2" t="n"/>
@@ -21295,7 +20870,6 @@
       <c r="AR421" s="2" t="n"/>
       <c r="AS421" s="2" t="n"/>
       <c r="AT421" s="2" t="n"/>
-      <c r="AU421" s="2" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n"/>
@@ -21344,7 +20918,6 @@
       <c r="AR422" s="2" t="n"/>
       <c r="AS422" s="2" t="n"/>
       <c r="AT422" s="2" t="n"/>
-      <c r="AU422" s="2" t="n"/>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n"/>
@@ -21393,7 +20966,6 @@
       <c r="AR423" s="2" t="n"/>
       <c r="AS423" s="2" t="n"/>
       <c r="AT423" s="2" t="n"/>
-      <c r="AU423" s="2" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n"/>
@@ -21442,7 +21014,6 @@
       <c r="AR424" s="2" t="n"/>
       <c r="AS424" s="2" t="n"/>
       <c r="AT424" s="2" t="n"/>
-      <c r="AU424" s="2" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="2" t="n"/>
@@ -21491,7 +21062,6 @@
       <c r="AR425" s="2" t="n"/>
       <c r="AS425" s="2" t="n"/>
       <c r="AT425" s="2" t="n"/>
-      <c r="AU425" s="2" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n"/>
@@ -21540,7 +21110,6 @@
       <c r="AR426" s="2" t="n"/>
       <c r="AS426" s="2" t="n"/>
       <c r="AT426" s="2" t="n"/>
-      <c r="AU426" s="2" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n"/>
@@ -21589,7 +21158,6 @@
       <c r="AR427" s="2" t="n"/>
       <c r="AS427" s="2" t="n"/>
       <c r="AT427" s="2" t="n"/>
-      <c r="AU427" s="2" t="n"/>
     </row>
     <row r="428">
       <c r="A428" s="2" t="n"/>
@@ -21638,7 +21206,6 @@
       <c r="AR428" s="2" t="n"/>
       <c r="AS428" s="2" t="n"/>
       <c r="AT428" s="2" t="n"/>
-      <c r="AU428" s="2" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="2" t="n"/>
@@ -21687,7 +21254,6 @@
       <c r="AR429" s="2" t="n"/>
       <c r="AS429" s="2" t="n"/>
       <c r="AT429" s="2" t="n"/>
-      <c r="AU429" s="2" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n"/>
@@ -21736,7 +21302,6 @@
       <c r="AR430" s="2" t="n"/>
       <c r="AS430" s="2" t="n"/>
       <c r="AT430" s="2" t="n"/>
-      <c r="AU430" s="2" t="n"/>
     </row>
     <row r="431">
       <c r="A431" s="2" t="n"/>
@@ -21785,7 +21350,6 @@
       <c r="AR431" s="2" t="n"/>
       <c r="AS431" s="2" t="n"/>
       <c r="AT431" s="2" t="n"/>
-      <c r="AU431" s="2" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="2" t="n"/>
@@ -21834,7 +21398,6 @@
       <c r="AR432" s="2" t="n"/>
       <c r="AS432" s="2" t="n"/>
       <c r="AT432" s="2" t="n"/>
-      <c r="AU432" s="2" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="2" t="n"/>
@@ -21883,7 +21446,6 @@
       <c r="AR433" s="2" t="n"/>
       <c r="AS433" s="2" t="n"/>
       <c r="AT433" s="2" t="n"/>
-      <c r="AU433" s="2" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="2" t="n"/>
@@ -21932,7 +21494,6 @@
       <c r="AR434" s="2" t="n"/>
       <c r="AS434" s="2" t="n"/>
       <c r="AT434" s="2" t="n"/>
-      <c r="AU434" s="2" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="2" t="n"/>
@@ -21981,7 +21542,6 @@
       <c r="AR435" s="2" t="n"/>
       <c r="AS435" s="2" t="n"/>
       <c r="AT435" s="2" t="n"/>
-      <c r="AU435" s="2" t="n"/>
     </row>
     <row r="436">
       <c r="A436" s="2" t="n"/>
@@ -22030,7 +21590,6 @@
       <c r="AR436" s="2" t="n"/>
       <c r="AS436" s="2" t="n"/>
       <c r="AT436" s="2" t="n"/>
-      <c r="AU436" s="2" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="2" t="n"/>
@@ -22079,7 +21638,6 @@
       <c r="AR437" s="2" t="n"/>
       <c r="AS437" s="2" t="n"/>
       <c r="AT437" s="2" t="n"/>
-      <c r="AU437" s="2" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="2" t="n"/>
@@ -22128,7 +21686,6 @@
       <c r="AR438" s="2" t="n"/>
       <c r="AS438" s="2" t="n"/>
       <c r="AT438" s="2" t="n"/>
-      <c r="AU438" s="2" t="n"/>
     </row>
     <row r="439">
       <c r="A439" s="2" t="n"/>
@@ -22177,7 +21734,6 @@
       <c r="AR439" s="2" t="n"/>
       <c r="AS439" s="2" t="n"/>
       <c r="AT439" s="2" t="n"/>
-      <c r="AU439" s="2" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="n"/>
@@ -22226,7 +21782,6 @@
       <c r="AR440" s="2" t="n"/>
       <c r="AS440" s="2" t="n"/>
       <c r="AT440" s="2" t="n"/>
-      <c r="AU440" s="2" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="2" t="n"/>
@@ -22275,7 +21830,6 @@
       <c r="AR441" s="2" t="n"/>
       <c r="AS441" s="2" t="n"/>
       <c r="AT441" s="2" t="n"/>
-      <c r="AU441" s="2" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n"/>
@@ -22324,7 +21878,6 @@
       <c r="AR442" s="2" t="n"/>
       <c r="AS442" s="2" t="n"/>
       <c r="AT442" s="2" t="n"/>
-      <c r="AU442" s="2" t="n"/>
     </row>
     <row r="443">
       <c r="A443" s="2" t="n"/>
@@ -22373,7 +21926,6 @@
       <c r="AR443" s="2" t="n"/>
       <c r="AS443" s="2" t="n"/>
       <c r="AT443" s="2" t="n"/>
-      <c r="AU443" s="2" t="n"/>
     </row>
     <row r="444">
       <c r="A444" s="2" t="n"/>
@@ -22422,7 +21974,6 @@
       <c r="AR444" s="2" t="n"/>
       <c r="AS444" s="2" t="n"/>
       <c r="AT444" s="2" t="n"/>
-      <c r="AU444" s="2" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="2" t="n"/>
@@ -22471,7 +22022,6 @@
       <c r="AR445" s="2" t="n"/>
       <c r="AS445" s="2" t="n"/>
       <c r="AT445" s="2" t="n"/>
-      <c r="AU445" s="2" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="2" t="n"/>
@@ -22520,7 +22070,6 @@
       <c r="AR446" s="2" t="n"/>
       <c r="AS446" s="2" t="n"/>
       <c r="AT446" s="2" t="n"/>
-      <c r="AU446" s="2" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="2" t="n"/>
@@ -22569,7 +22118,6 @@
       <c r="AR447" s="2" t="n"/>
       <c r="AS447" s="2" t="n"/>
       <c r="AT447" s="2" t="n"/>
-      <c r="AU447" s="2" t="n"/>
     </row>
     <row r="448">
       <c r="A448" s="2" t="n"/>
@@ -22618,7 +22166,6 @@
       <c r="AR448" s="2" t="n"/>
       <c r="AS448" s="2" t="n"/>
       <c r="AT448" s="2" t="n"/>
-      <c r="AU448" s="2" t="n"/>
     </row>
     <row r="449">
       <c r="A449" s="2" t="n"/>
@@ -22667,7 +22214,6 @@
       <c r="AR449" s="2" t="n"/>
       <c r="AS449" s="2" t="n"/>
       <c r="AT449" s="2" t="n"/>
-      <c r="AU449" s="2" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="n"/>
@@ -22716,7 +22262,6 @@
       <c r="AR450" s="2" t="n"/>
       <c r="AS450" s="2" t="n"/>
       <c r="AT450" s="2" t="n"/>
-      <c r="AU450" s="2" t="n"/>
     </row>
     <row r="451">
       <c r="A451" s="2" t="n"/>
@@ -22765,7 +22310,6 @@
       <c r="AR451" s="2" t="n"/>
       <c r="AS451" s="2" t="n"/>
       <c r="AT451" s="2" t="n"/>
-      <c r="AU451" s="2" t="n"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="n"/>
@@ -22814,7 +22358,6 @@
       <c r="AR452" s="2" t="n"/>
       <c r="AS452" s="2" t="n"/>
       <c r="AT452" s="2" t="n"/>
-      <c r="AU452" s="2" t="n"/>
     </row>
     <row r="453">
       <c r="A453" s="2" t="n"/>
@@ -22863,7 +22406,6 @@
       <c r="AR453" s="2" t="n"/>
       <c r="AS453" s="2" t="n"/>
       <c r="AT453" s="2" t="n"/>
-      <c r="AU453" s="2" t="n"/>
     </row>
     <row r="454">
       <c r="A454" s="2" t="n"/>
@@ -22912,7 +22454,6 @@
       <c r="AR454" s="2" t="n"/>
       <c r="AS454" s="2" t="n"/>
       <c r="AT454" s="2" t="n"/>
-      <c r="AU454" s="2" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="2" t="n"/>
@@ -22961,7 +22502,6 @@
       <c r="AR455" s="2" t="n"/>
       <c r="AS455" s="2" t="n"/>
       <c r="AT455" s="2" t="n"/>
-      <c r="AU455" s="2" t="n"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="n"/>
@@ -23010,7 +22550,6 @@
       <c r="AR456" s="2" t="n"/>
       <c r="AS456" s="2" t="n"/>
       <c r="AT456" s="2" t="n"/>
-      <c r="AU456" s="2" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="2" t="n"/>
@@ -23059,7 +22598,6 @@
       <c r="AR457" s="2" t="n"/>
       <c r="AS457" s="2" t="n"/>
       <c r="AT457" s="2" t="n"/>
-      <c r="AU457" s="2" t="n"/>
     </row>
     <row r="458">
       <c r="A458" s="2" t="n"/>
@@ -23108,7 +22646,6 @@
       <c r="AR458" s="2" t="n"/>
       <c r="AS458" s="2" t="n"/>
       <c r="AT458" s="2" t="n"/>
-      <c r="AU458" s="2" t="n"/>
     </row>
     <row r="459">
       <c r="A459" s="2" t="n"/>
@@ -23157,7 +22694,6 @@
       <c r="AR459" s="2" t="n"/>
       <c r="AS459" s="2" t="n"/>
       <c r="AT459" s="2" t="n"/>
-      <c r="AU459" s="2" t="n"/>
     </row>
     <row r="460">
       <c r="A460" s="2" t="n"/>
@@ -23206,7 +22742,6 @@
       <c r="AR460" s="2" t="n"/>
       <c r="AS460" s="2" t="n"/>
       <c r="AT460" s="2" t="n"/>
-      <c r="AU460" s="2" t="n"/>
     </row>
     <row r="461">
       <c r="A461" s="2" t="n"/>
@@ -23255,7 +22790,6 @@
       <c r="AR461" s="2" t="n"/>
       <c r="AS461" s="2" t="n"/>
       <c r="AT461" s="2" t="n"/>
-      <c r="AU461" s="2" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="2" t="n"/>
@@ -23304,7 +22838,6 @@
       <c r="AR462" s="2" t="n"/>
       <c r="AS462" s="2" t="n"/>
       <c r="AT462" s="2" t="n"/>
-      <c r="AU462" s="2" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="2" t="n"/>
@@ -23353,7 +22886,6 @@
       <c r="AR463" s="2" t="n"/>
       <c r="AS463" s="2" t="n"/>
       <c r="AT463" s="2" t="n"/>
-      <c r="AU463" s="2" t="n"/>
     </row>
     <row r="464">
       <c r="A464" s="2" t="n"/>
@@ -23402,7 +22934,6 @@
       <c r="AR464" s="2" t="n"/>
       <c r="AS464" s="2" t="n"/>
       <c r="AT464" s="2" t="n"/>
-      <c r="AU464" s="2" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="2" t="n"/>
@@ -23451,7 +22982,6 @@
       <c r="AR465" s="2" t="n"/>
       <c r="AS465" s="2" t="n"/>
       <c r="AT465" s="2" t="n"/>
-      <c r="AU465" s="2" t="n"/>
     </row>
     <row r="466">
       <c r="A466" s="2" t="n"/>
@@ -23500,7 +23030,6 @@
       <c r="AR466" s="2" t="n"/>
       <c r="AS466" s="2" t="n"/>
       <c r="AT466" s="2" t="n"/>
-      <c r="AU466" s="2" t="n"/>
     </row>
     <row r="467">
       <c r="A467" s="2" t="n"/>
@@ -23549,7 +23078,6 @@
       <c r="AR467" s="2" t="n"/>
       <c r="AS467" s="2" t="n"/>
       <c r="AT467" s="2" t="n"/>
-      <c r="AU467" s="2" t="n"/>
     </row>
     <row r="468">
       <c r="A468" s="2" t="n"/>
@@ -23598,7 +23126,6 @@
       <c r="AR468" s="2" t="n"/>
       <c r="AS468" s="2" t="n"/>
       <c r="AT468" s="2" t="n"/>
-      <c r="AU468" s="2" t="n"/>
     </row>
     <row r="469">
       <c r="A469" s="2" t="n"/>
@@ -23647,7 +23174,6 @@
       <c r="AR469" s="2" t="n"/>
       <c r="AS469" s="2" t="n"/>
       <c r="AT469" s="2" t="n"/>
-      <c r="AU469" s="2" t="n"/>
     </row>
     <row r="470">
       <c r="A470" s="2" t="n"/>
@@ -23696,7 +23222,6 @@
       <c r="AR470" s="2" t="n"/>
       <c r="AS470" s="2" t="n"/>
       <c r="AT470" s="2" t="n"/>
-      <c r="AU470" s="2" t="n"/>
     </row>
     <row r="471">
       <c r="A471" s="2" t="n"/>
@@ -23745,7 +23270,6 @@
       <c r="AR471" s="2" t="n"/>
       <c r="AS471" s="2" t="n"/>
       <c r="AT471" s="2" t="n"/>
-      <c r="AU471" s="2" t="n"/>
     </row>
     <row r="472">
       <c r="A472" s="2" t="n"/>
@@ -23794,7 +23318,6 @@
       <c r="AR472" s="2" t="n"/>
       <c r="AS472" s="2" t="n"/>
       <c r="AT472" s="2" t="n"/>
-      <c r="AU472" s="2" t="n"/>
     </row>
     <row r="473">
       <c r="A473" s="2" t="n"/>
@@ -23843,7 +23366,6 @@
       <c r="AR473" s="2" t="n"/>
       <c r="AS473" s="2" t="n"/>
       <c r="AT473" s="2" t="n"/>
-      <c r="AU473" s="2" t="n"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="n"/>
@@ -23892,7 +23414,6 @@
       <c r="AR474" s="2" t="n"/>
       <c r="AS474" s="2" t="n"/>
       <c r="AT474" s="2" t="n"/>
-      <c r="AU474" s="2" t="n"/>
     </row>
     <row r="475">
       <c r="A475" s="2" t="n"/>
@@ -23941,7 +23462,6 @@
       <c r="AR475" s="2" t="n"/>
       <c r="AS475" s="2" t="n"/>
       <c r="AT475" s="2" t="n"/>
-      <c r="AU475" s="2" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="2" t="n"/>
@@ -23990,7 +23510,6 @@
       <c r="AR476" s="2" t="n"/>
       <c r="AS476" s="2" t="n"/>
       <c r="AT476" s="2" t="n"/>
-      <c r="AU476" s="2" t="n"/>
     </row>
     <row r="477">
       <c r="A477" s="2" t="n"/>
@@ -24039,7 +23558,6 @@
       <c r="AR477" s="2" t="n"/>
       <c r="AS477" s="2" t="n"/>
       <c r="AT477" s="2" t="n"/>
-      <c r="AU477" s="2" t="n"/>
     </row>
     <row r="478">
       <c r="A478" s="2" t="n"/>
@@ -24088,7 +23606,6 @@
       <c r="AR478" s="2" t="n"/>
       <c r="AS478" s="2" t="n"/>
       <c r="AT478" s="2" t="n"/>
-      <c r="AU478" s="2" t="n"/>
     </row>
     <row r="479">
       <c r="A479" s="2" t="n"/>
@@ -24137,7 +23654,6 @@
       <c r="AR479" s="2" t="n"/>
       <c r="AS479" s="2" t="n"/>
       <c r="AT479" s="2" t="n"/>
-      <c r="AU479" s="2" t="n"/>
     </row>
     <row r="480">
       <c r="A480" s="2" t="n"/>
@@ -24186,7 +23702,6 @@
       <c r="AR480" s="2" t="n"/>
       <c r="AS480" s="2" t="n"/>
       <c r="AT480" s="2" t="n"/>
-      <c r="AU480" s="2" t="n"/>
     </row>
     <row r="481">
       <c r="A481" s="2" t="n"/>
@@ -24235,7 +23750,6 @@
       <c r="AR481" s="2" t="n"/>
       <c r="AS481" s="2" t="n"/>
       <c r="AT481" s="2" t="n"/>
-      <c r="AU481" s="2" t="n"/>
     </row>
     <row r="482">
       <c r="A482" s="2" t="n"/>
@@ -24284,7 +23798,6 @@
       <c r="AR482" s="2" t="n"/>
       <c r="AS482" s="2" t="n"/>
       <c r="AT482" s="2" t="n"/>
-      <c r="AU482" s="2" t="n"/>
     </row>
     <row r="483">
       <c r="A483" s="2" t="n"/>
@@ -24333,7 +23846,6 @@
       <c r="AR483" s="2" t="n"/>
       <c r="AS483" s="2" t="n"/>
       <c r="AT483" s="2" t="n"/>
-      <c r="AU483" s="2" t="n"/>
     </row>
     <row r="484">
       <c r="A484" s="2" t="n"/>
@@ -24382,7 +23894,6 @@
       <c r="AR484" s="2" t="n"/>
       <c r="AS484" s="2" t="n"/>
       <c r="AT484" s="2" t="n"/>
-      <c r="AU484" s="2" t="n"/>
     </row>
     <row r="485">
       <c r="A485" s="2" t="n"/>
@@ -24431,7 +23942,6 @@
       <c r="AR485" s="2" t="n"/>
       <c r="AS485" s="2" t="n"/>
       <c r="AT485" s="2" t="n"/>
-      <c r="AU485" s="2" t="n"/>
     </row>
     <row r="486">
       <c r="A486" s="2" t="n"/>
@@ -24480,7 +23990,6 @@
       <c r="AR486" s="2" t="n"/>
       <c r="AS486" s="2" t="n"/>
       <c r="AT486" s="2" t="n"/>
-      <c r="AU486" s="2" t="n"/>
     </row>
     <row r="487">
       <c r="A487" s="2" t="n"/>
@@ -24529,7 +24038,6 @@
       <c r="AR487" s="2" t="n"/>
       <c r="AS487" s="2" t="n"/>
       <c r="AT487" s="2" t="n"/>
-      <c r="AU487" s="2" t="n"/>
     </row>
     <row r="488">
       <c r="A488" s="2" t="n"/>
@@ -24578,7 +24086,6 @@
       <c r="AR488" s="2" t="n"/>
       <c r="AS488" s="2" t="n"/>
       <c r="AT488" s="2" t="n"/>
-      <c r="AU488" s="2" t="n"/>
     </row>
     <row r="489">
       <c r="A489" s="2" t="n"/>
@@ -24627,7 +24134,6 @@
       <c r="AR489" s="2" t="n"/>
       <c r="AS489" s="2" t="n"/>
       <c r="AT489" s="2" t="n"/>
-      <c r="AU489" s="2" t="n"/>
     </row>
     <row r="490">
       <c r="A490" s="2" t="n"/>
@@ -24676,7 +24182,6 @@
       <c r="AR490" s="2" t="n"/>
       <c r="AS490" s="2" t="n"/>
       <c r="AT490" s="2" t="n"/>
-      <c r="AU490" s="2" t="n"/>
     </row>
     <row r="491">
       <c r="A491" s="2" t="n"/>
@@ -24725,7 +24230,6 @@
       <c r="AR491" s="2" t="n"/>
       <c r="AS491" s="2" t="n"/>
       <c r="AT491" s="2" t="n"/>
-      <c r="AU491" s="2" t="n"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="n"/>
@@ -24774,7 +24278,6 @@
       <c r="AR492" s="2" t="n"/>
       <c r="AS492" s="2" t="n"/>
       <c r="AT492" s="2" t="n"/>
-      <c r="AU492" s="2" t="n"/>
     </row>
     <row r="493">
       <c r="A493" s="2" t="n"/>
@@ -24823,7 +24326,6 @@
       <c r="AR493" s="2" t="n"/>
       <c r="AS493" s="2" t="n"/>
       <c r="AT493" s="2" t="n"/>
-      <c r="AU493" s="2" t="n"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="n"/>
@@ -24872,7 +24374,6 @@
       <c r="AR494" s="2" t="n"/>
       <c r="AS494" s="2" t="n"/>
       <c r="AT494" s="2" t="n"/>
-      <c r="AU494" s="2" t="n"/>
     </row>
     <row r="495">
       <c r="A495" s="2" t="n"/>
@@ -24921,7 +24422,6 @@
       <c r="AR495" s="2" t="n"/>
       <c r="AS495" s="2" t="n"/>
       <c r="AT495" s="2" t="n"/>
-      <c r="AU495" s="2" t="n"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="n"/>
@@ -24970,7 +24470,6 @@
       <c r="AR496" s="2" t="n"/>
       <c r="AS496" s="2" t="n"/>
       <c r="AT496" s="2" t="n"/>
-      <c r="AU496" s="2" t="n"/>
     </row>
     <row r="497">
       <c r="A497" s="2" t="n"/>
@@ -25019,7 +24518,6 @@
       <c r="AR497" s="2" t="n"/>
       <c r="AS497" s="2" t="n"/>
       <c r="AT497" s="2" t="n"/>
-      <c r="AU497" s="2" t="n"/>
     </row>
     <row r="498">
       <c r="A498" s="2" t="n"/>
@@ -25068,7 +24566,6 @@
       <c r="AR498" s="2" t="n"/>
       <c r="AS498" s="2" t="n"/>
       <c r="AT498" s="2" t="n"/>
-      <c r="AU498" s="2" t="n"/>
     </row>
     <row r="499">
       <c r="A499" s="2" t="n"/>
@@ -25117,7 +24614,6 @@
       <c r="AR499" s="2" t="n"/>
       <c r="AS499" s="2" t="n"/>
       <c r="AT499" s="2" t="n"/>
-      <c r="AU499" s="2" t="n"/>
     </row>
     <row r="500">
       <c r="A500" s="2" t="n"/>
@@ -25166,7 +24662,6 @@
       <c r="AR500" s="2" t="n"/>
       <c r="AS500" s="2" t="n"/>
       <c r="AT500" s="2" t="n"/>
-      <c r="AU500" s="2" t="n"/>
     </row>
     <row r="501">
       <c r="A501" s="2" t="n"/>
@@ -25215,7 +24710,6 @@
       <c r="AR501" s="2" t="n"/>
       <c r="AS501" s="2" t="n"/>
       <c r="AT501" s="2" t="n"/>
-      <c r="AU501" s="2" t="n"/>
     </row>
     <row r="502">
       <c r="A502" s="2" t="n"/>
@@ -25264,7 +24758,6 @@
       <c r="AR502" s="2" t="n"/>
       <c r="AS502" s="2" t="n"/>
       <c r="AT502" s="2" t="n"/>
-      <c r="AU502" s="2" t="n"/>
     </row>
     <row r="503">
       <c r="A503" s="2" t="n"/>
@@ -25313,7 +24806,6 @@
       <c r="AR503" s="2" t="n"/>
       <c r="AS503" s="2" t="n"/>
       <c r="AT503" s="2" t="n"/>
-      <c r="AU503" s="2" t="n"/>
     </row>
     <row r="504">
       <c r="A504" s="2" t="n"/>
@@ -25362,7 +24854,6 @@
       <c r="AR504" s="2" t="n"/>
       <c r="AS504" s="2" t="n"/>
       <c r="AT504" s="2" t="n"/>
-      <c r="AU504" s="2" t="n"/>
     </row>
     <row r="505">
       <c r="A505" s="2" t="n"/>
@@ -25411,7 +24902,6 @@
       <c r="AR505" s="2" t="n"/>
       <c r="AS505" s="2" t="n"/>
       <c r="AT505" s="2" t="n"/>
-      <c r="AU505" s="2" t="n"/>
     </row>
     <row r="506">
       <c r="A506" s="2" t="n"/>
@@ -25460,7 +24950,6 @@
       <c r="AR506" s="2" t="n"/>
       <c r="AS506" s="2" t="n"/>
       <c r="AT506" s="2" t="n"/>
-      <c r="AU506" s="2" t="n"/>
     </row>
     <row r="507">
       <c r="A507" s="2" t="n"/>
@@ -25509,7 +24998,6 @@
       <c r="AR507" s="2" t="n"/>
       <c r="AS507" s="2" t="n"/>
       <c r="AT507" s="2" t="n"/>
-      <c r="AU507" s="2" t="n"/>
     </row>
     <row r="508">
       <c r="A508" s="2" t="n"/>
@@ -25558,7 +25046,6 @@
       <c r="AR508" s="2" t="n"/>
       <c r="AS508" s="2" t="n"/>
       <c r="AT508" s="2" t="n"/>
-      <c r="AU508" s="2" t="n"/>
     </row>
     <row r="509">
       <c r="A509" s="2" t="n"/>
@@ -25607,7 +25094,6 @@
       <c r="AR509" s="2" t="n"/>
       <c r="AS509" s="2" t="n"/>
       <c r="AT509" s="2" t="n"/>
-      <c r="AU509" s="2" t="n"/>
     </row>
     <row r="510">
       <c r="A510" s="2" t="n"/>
@@ -25656,7 +25142,6 @@
       <c r="AR510" s="2" t="n"/>
       <c r="AS510" s="2" t="n"/>
       <c r="AT510" s="2" t="n"/>
-      <c r="AU510" s="2" t="n"/>
     </row>
     <row r="511">
       <c r="A511" s="2" t="n"/>
@@ -25705,7 +25190,6 @@
       <c r="AR511" s="2" t="n"/>
       <c r="AS511" s="2" t="n"/>
       <c r="AT511" s="2" t="n"/>
-      <c r="AU511" s="2" t="n"/>
     </row>
     <row r="512">
       <c r="A512" s="2" t="n"/>
@@ -25754,7 +25238,6 @@
       <c r="AR512" s="2" t="n"/>
       <c r="AS512" s="2" t="n"/>
       <c r="AT512" s="2" t="n"/>
-      <c r="AU512" s="2" t="n"/>
     </row>
     <row r="513">
       <c r="A513" s="2" t="n"/>
@@ -25803,7 +25286,6 @@
       <c r="AR513" s="2" t="n"/>
       <c r="AS513" s="2" t="n"/>
       <c r="AT513" s="2" t="n"/>
-      <c r="AU513" s="2" t="n"/>
     </row>
     <row r="514">
       <c r="A514" s="2" t="n"/>
@@ -25852,7 +25334,6 @@
       <c r="AR514" s="2" t="n"/>
       <c r="AS514" s="2" t="n"/>
       <c r="AT514" s="2" t="n"/>
-      <c r="AU514" s="2" t="n"/>
     </row>
     <row r="515">
       <c r="A515" s="2" t="n"/>
@@ -25901,7 +25382,6 @@
       <c r="AR515" s="2" t="n"/>
       <c r="AS515" s="2" t="n"/>
       <c r="AT515" s="2" t="n"/>
-      <c r="AU515" s="2" t="n"/>
     </row>
     <row r="516">
       <c r="A516" s="2" t="n"/>
@@ -25950,7 +25430,6 @@
       <c r="AR516" s="2" t="n"/>
       <c r="AS516" s="2" t="n"/>
       <c r="AT516" s="2" t="n"/>
-      <c r="AU516" s="2" t="n"/>
     </row>
     <row r="517">
       <c r="A517" s="2" t="n"/>
@@ -25999,7 +25478,6 @@
       <c r="AR517" s="2" t="n"/>
       <c r="AS517" s="2" t="n"/>
       <c r="AT517" s="2" t="n"/>
-      <c r="AU517" s="2" t="n"/>
     </row>
     <row r="518">
       <c r="A518" s="2" t="n"/>
@@ -26048,7 +25526,6 @@
       <c r="AR518" s="2" t="n"/>
       <c r="AS518" s="2" t="n"/>
       <c r="AT518" s="2" t="n"/>
-      <c r="AU518" s="2" t="n"/>
     </row>
     <row r="519">
       <c r="A519" s="2" t="n"/>
@@ -26097,7 +25574,6 @@
       <c r="AR519" s="2" t="n"/>
       <c r="AS519" s="2" t="n"/>
       <c r="AT519" s="2" t="n"/>
-      <c r="AU519" s="2" t="n"/>
     </row>
     <row r="520">
       <c r="A520" s="2" t="n"/>
@@ -26146,7 +25622,6 @@
       <c r="AR520" s="2" t="n"/>
       <c r="AS520" s="2" t="n"/>
       <c r="AT520" s="2" t="n"/>
-      <c r="AU520" s="2" t="n"/>
     </row>
     <row r="521">
       <c r="A521" s="2" t="n"/>
@@ -26195,7 +25670,6 @@
       <c r="AR521" s="2" t="n"/>
       <c r="AS521" s="2" t="n"/>
       <c r="AT521" s="2" t="n"/>
-      <c r="AU521" s="2" t="n"/>
     </row>
     <row r="522">
       <c r="A522" s="2" t="n"/>
@@ -26244,7 +25718,6 @@
       <c r="AR522" s="2" t="n"/>
       <c r="AS522" s="2" t="n"/>
       <c r="AT522" s="2" t="n"/>
-      <c r="AU522" s="2" t="n"/>
     </row>
     <row r="523">
       <c r="A523" s="2" t="n"/>
@@ -26293,7 +25766,6 @@
       <c r="AR523" s="2" t="n"/>
       <c r="AS523" s="2" t="n"/>
       <c r="AT523" s="2" t="n"/>
-      <c r="AU523" s="2" t="n"/>
     </row>
     <row r="524">
       <c r="A524" s="2" t="n"/>
@@ -26342,7 +25814,6 @@
       <c r="AR524" s="2" t="n"/>
       <c r="AS524" s="2" t="n"/>
       <c r="AT524" s="2" t="n"/>
-      <c r="AU524" s="2" t="n"/>
     </row>
     <row r="525">
       <c r="A525" s="2" t="n"/>
@@ -26391,7 +25862,6 @@
       <c r="AR525" s="2" t="n"/>
       <c r="AS525" s="2" t="n"/>
       <c r="AT525" s="2" t="n"/>
-      <c r="AU525" s="2" t="n"/>
     </row>
     <row r="526">
       <c r="A526" s="2" t="n"/>
@@ -26440,7 +25910,6 @@
       <c r="AR526" s="2" t="n"/>
       <c r="AS526" s="2" t="n"/>
       <c r="AT526" s="2" t="n"/>
-      <c r="AU526" s="2" t="n"/>
     </row>
     <row r="527">
       <c r="A527" s="2" t="n"/>
@@ -26489,7 +25958,6 @@
       <c r="AR527" s="2" t="n"/>
       <c r="AS527" s="2" t="n"/>
       <c r="AT527" s="2" t="n"/>
-      <c r="AU527" s="2" t="n"/>
     </row>
     <row r="528">
       <c r="A528" s="2" t="n"/>
@@ -26538,7 +26006,6 @@
       <c r="AR528" s="2" t="n"/>
       <c r="AS528" s="2" t="n"/>
       <c r="AT528" s="2" t="n"/>
-      <c r="AU528" s="2" t="n"/>
     </row>
     <row r="529">
       <c r="A529" s="2" t="n"/>
@@ -26587,7 +26054,6 @@
       <c r="AR529" s="2" t="n"/>
       <c r="AS529" s="2" t="n"/>
       <c r="AT529" s="2" t="n"/>
-      <c r="AU529" s="2" t="n"/>
     </row>
     <row r="530">
       <c r="A530" s="2" t="n"/>
@@ -26636,7 +26102,6 @@
       <c r="AR530" s="2" t="n"/>
       <c r="AS530" s="2" t="n"/>
       <c r="AT530" s="2" t="n"/>
-      <c r="AU530" s="2" t="n"/>
     </row>
     <row r="531">
       <c r="A531" s="2" t="n"/>
@@ -26685,7 +26150,6 @@
       <c r="AR531" s="2" t="n"/>
       <c r="AS531" s="2" t="n"/>
       <c r="AT531" s="2" t="n"/>
-      <c r="AU531" s="2" t="n"/>
     </row>
     <row r="532">
       <c r="A532" s="2" t="n"/>
@@ -26734,7 +26198,6 @@
       <c r="AR532" s="2" t="n"/>
       <c r="AS532" s="2" t="n"/>
       <c r="AT532" s="2" t="n"/>
-      <c r="AU532" s="2" t="n"/>
     </row>
     <row r="533">
       <c r="A533" s="2" t="n"/>
@@ -26783,7 +26246,6 @@
       <c r="AR533" s="2" t="n"/>
       <c r="AS533" s="2" t="n"/>
       <c r="AT533" s="2" t="n"/>
-      <c r="AU533" s="2" t="n"/>
     </row>
     <row r="534">
       <c r="A534" s="2" t="n"/>
@@ -26832,7 +26294,6 @@
       <c r="AR534" s="2" t="n"/>
       <c r="AS534" s="2" t="n"/>
       <c r="AT534" s="2" t="n"/>
-      <c r="AU534" s="2" t="n"/>
     </row>
     <row r="535">
       <c r="A535" s="2" t="n"/>
@@ -26881,7 +26342,6 @@
       <c r="AR535" s="2" t="n"/>
       <c r="AS535" s="2" t="n"/>
       <c r="AT535" s="2" t="n"/>
-      <c r="AU535" s="2" t="n"/>
     </row>
     <row r="536">
       <c r="A536" s="2" t="n"/>
@@ -26930,7 +26390,6 @@
       <c r="AR536" s="2" t="n"/>
       <c r="AS536" s="2" t="n"/>
       <c r="AT536" s="2" t="n"/>
-      <c r="AU536" s="2" t="n"/>
     </row>
     <row r="537">
       <c r="A537" s="2" t="n"/>
@@ -26979,7 +26438,6 @@
       <c r="AR537" s="2" t="n"/>
       <c r="AS537" s="2" t="n"/>
       <c r="AT537" s="2" t="n"/>
-      <c r="AU537" s="2" t="n"/>
     </row>
     <row r="538">
       <c r="A538" s="2" t="n"/>
@@ -27028,7 +26486,6 @@
       <c r="AR538" s="2" t="n"/>
       <c r="AS538" s="2" t="n"/>
       <c r="AT538" s="2" t="n"/>
-      <c r="AU538" s="2" t="n"/>
     </row>
     <row r="539">
       <c r="A539" s="2" t="n"/>
@@ -27077,7 +26534,6 @@
       <c r="AR539" s="2" t="n"/>
       <c r="AS539" s="2" t="n"/>
       <c r="AT539" s="2" t="n"/>
-      <c r="AU539" s="2" t="n"/>
     </row>
     <row r="540">
       <c r="A540" s="2" t="n"/>
@@ -27126,7 +26582,6 @@
       <c r="AR540" s="2" t="n"/>
       <c r="AS540" s="2" t="n"/>
       <c r="AT540" s="2" t="n"/>
-      <c r="AU540" s="2" t="n"/>
     </row>
     <row r="541">
       <c r="A541" s="2" t="n"/>
@@ -27175,7 +26630,6 @@
       <c r="AR541" s="2" t="n"/>
       <c r="AS541" s="2" t="n"/>
       <c r="AT541" s="2" t="n"/>
-      <c r="AU541" s="2" t="n"/>
     </row>
     <row r="542">
       <c r="A542" s="2" t="n"/>
@@ -27224,7 +26678,6 @@
       <c r="AR542" s="2" t="n"/>
       <c r="AS542" s="2" t="n"/>
       <c r="AT542" s="2" t="n"/>
-      <c r="AU542" s="2" t="n"/>
     </row>
     <row r="543">
       <c r="A543" s="2" t="n"/>
@@ -27273,7 +26726,6 @@
       <c r="AR543" s="2" t="n"/>
       <c r="AS543" s="2" t="n"/>
       <c r="AT543" s="2" t="n"/>
-      <c r="AU543" s="2" t="n"/>
     </row>
     <row r="544">
       <c r="A544" s="2" t="n"/>
@@ -27322,7 +26774,6 @@
       <c r="AR544" s="2" t="n"/>
       <c r="AS544" s="2" t="n"/>
       <c r="AT544" s="2" t="n"/>
-      <c r="AU544" s="2" t="n"/>
     </row>
     <row r="545">
       <c r="A545" s="2" t="n"/>
@@ -27371,7 +26822,6 @@
       <c r="AR545" s="2" t="n"/>
       <c r="AS545" s="2" t="n"/>
       <c r="AT545" s="2" t="n"/>
-      <c r="AU545" s="2" t="n"/>
     </row>
     <row r="546">
       <c r="A546" s="2" t="n"/>
@@ -27420,7 +26870,6 @@
       <c r="AR546" s="2" t="n"/>
       <c r="AS546" s="2" t="n"/>
       <c r="AT546" s="2" t="n"/>
-      <c r="AU546" s="2" t="n"/>
     </row>
     <row r="547">
       <c r="A547" s="2" t="n"/>
@@ -27469,7 +26918,6 @@
       <c r="AR547" s="2" t="n"/>
       <c r="AS547" s="2" t="n"/>
       <c r="AT547" s="2" t="n"/>
-      <c r="AU547" s="2" t="n"/>
     </row>
     <row r="548">
       <c r="A548" s="2" t="n"/>
@@ -27518,7 +26966,6 @@
       <c r="AR548" s="2" t="n"/>
       <c r="AS548" s="2" t="n"/>
       <c r="AT548" s="2" t="n"/>
-      <c r="AU548" s="2" t="n"/>
     </row>
     <row r="549">
       <c r="A549" s="2" t="n"/>
@@ -27567,7 +27014,6 @@
       <c r="AR549" s="2" t="n"/>
       <c r="AS549" s="2" t="n"/>
       <c r="AT549" s="2" t="n"/>
-      <c r="AU549" s="2" t="n"/>
     </row>
     <row r="550">
       <c r="A550" s="2" t="n"/>
@@ -27616,7 +27062,6 @@
       <c r="AR550" s="2" t="n"/>
       <c r="AS550" s="2" t="n"/>
       <c r="AT550" s="2" t="n"/>
-      <c r="AU550" s="2" t="n"/>
     </row>
     <row r="551">
       <c r="A551" s="2" t="n"/>
@@ -27665,7 +27110,6 @@
       <c r="AR551" s="2" t="n"/>
       <c r="AS551" s="2" t="n"/>
       <c r="AT551" s="2" t="n"/>
-      <c r="AU551" s="2" t="n"/>
     </row>
     <row r="552">
       <c r="A552" s="2" t="n"/>
@@ -27714,7 +27158,6 @@
       <c r="AR552" s="2" t="n"/>
       <c r="AS552" s="2" t="n"/>
       <c r="AT552" s="2" t="n"/>
-      <c r="AU552" s="2" t="n"/>
     </row>
     <row r="553">
       <c r="A553" s="2" t="n"/>
@@ -27763,7 +27206,6 @@
       <c r="AR553" s="2" t="n"/>
       <c r="AS553" s="2" t="n"/>
       <c r="AT553" s="2" t="n"/>
-      <c r="AU553" s="2" t="n"/>
     </row>
     <row r="554">
       <c r="A554" s="2" t="n"/>
@@ -27812,7 +27254,6 @@
       <c r="AR554" s="2" t="n"/>
       <c r="AS554" s="2" t="n"/>
       <c r="AT554" s="2" t="n"/>
-      <c r="AU554" s="2" t="n"/>
     </row>
     <row r="555">
       <c r="A555" s="2" t="n"/>
@@ -27861,7 +27302,6 @@
       <c r="AR555" s="2" t="n"/>
       <c r="AS555" s="2" t="n"/>
       <c r="AT555" s="2" t="n"/>
-      <c r="AU555" s="2" t="n"/>
     </row>
     <row r="556">
       <c r="A556" s="2" t="n"/>
@@ -27910,7 +27350,6 @@
       <c r="AR556" s="2" t="n"/>
       <c r="AS556" s="2" t="n"/>
       <c r="AT556" s="2" t="n"/>
-      <c r="AU556" s="2" t="n"/>
     </row>
     <row r="557">
       <c r="A557" s="2" t="n"/>
@@ -27959,7 +27398,6 @@
       <c r="AR557" s="2" t="n"/>
       <c r="AS557" s="2" t="n"/>
       <c r="AT557" s="2" t="n"/>
-      <c r="AU557" s="2" t="n"/>
     </row>
     <row r="558">
       <c r="A558" s="2" t="n"/>
@@ -28008,7 +27446,6 @@
       <c r="AR558" s="2" t="n"/>
       <c r="AS558" s="2" t="n"/>
       <c r="AT558" s="2" t="n"/>
-      <c r="AU558" s="2" t="n"/>
     </row>
     <row r="559">
       <c r="A559" s="2" t="n"/>
@@ -28057,7 +27494,6 @@
       <c r="AR559" s="2" t="n"/>
       <c r="AS559" s="2" t="n"/>
       <c r="AT559" s="2" t="n"/>
-      <c r="AU559" s="2" t="n"/>
     </row>
     <row r="560">
       <c r="A560" s="2" t="n"/>
@@ -28106,7 +27542,6 @@
       <c r="AR560" s="2" t="n"/>
       <c r="AS560" s="2" t="n"/>
       <c r="AT560" s="2" t="n"/>
-      <c r="AU560" s="2" t="n"/>
     </row>
     <row r="561">
       <c r="A561" s="2" t="n"/>
@@ -28155,7 +27590,6 @@
       <c r="AR561" s="2" t="n"/>
       <c r="AS561" s="2" t="n"/>
       <c r="AT561" s="2" t="n"/>
-      <c r="AU561" s="2" t="n"/>
     </row>
     <row r="562">
       <c r="A562" s="2" t="n"/>
@@ -28204,7 +27638,6 @@
       <c r="AR562" s="2" t="n"/>
       <c r="AS562" s="2" t="n"/>
       <c r="AT562" s="2" t="n"/>
-      <c r="AU562" s="2" t="n"/>
     </row>
     <row r="563">
       <c r="A563" s="2" t="n"/>
@@ -28253,7 +27686,6 @@
       <c r="AR563" s="2" t="n"/>
       <c r="AS563" s="2" t="n"/>
       <c r="AT563" s="2" t="n"/>
-      <c r="AU563" s="2" t="n"/>
     </row>
     <row r="564">
       <c r="A564" s="2" t="n"/>
@@ -28302,7 +27734,6 @@
       <c r="AR564" s="2" t="n"/>
       <c r="AS564" s="2" t="n"/>
       <c r="AT564" s="2" t="n"/>
-      <c r="AU564" s="2" t="n"/>
     </row>
     <row r="565">
       <c r="A565" s="2" t="n"/>
@@ -28351,7 +27782,6 @@
       <c r="AR565" s="2" t="n"/>
       <c r="AS565" s="2" t="n"/>
       <c r="AT565" s="2" t="n"/>
-      <c r="AU565" s="2" t="n"/>
     </row>
     <row r="566">
       <c r="A566" s="2" t="n"/>
@@ -28400,7 +27830,6 @@
       <c r="AR566" s="2" t="n"/>
       <c r="AS566" s="2" t="n"/>
       <c r="AT566" s="2" t="n"/>
-      <c r="AU566" s="2" t="n"/>
     </row>
     <row r="567">
       <c r="A567" s="2" t="n"/>
@@ -28449,7 +27878,6 @@
       <c r="AR567" s="2" t="n"/>
       <c r="AS567" s="2" t="n"/>
       <c r="AT567" s="2" t="n"/>
-      <c r="AU567" s="2" t="n"/>
     </row>
     <row r="568">
       <c r="A568" s="2" t="n"/>
@@ -28498,7 +27926,6 @@
       <c r="AR568" s="2" t="n"/>
       <c r="AS568" s="2" t="n"/>
       <c r="AT568" s="2" t="n"/>
-      <c r="AU568" s="2" t="n"/>
     </row>
     <row r="569">
       <c r="A569" s="2" t="n"/>
@@ -28547,7 +27974,6 @@
       <c r="AR569" s="2" t="n"/>
       <c r="AS569" s="2" t="n"/>
       <c r="AT569" s="2" t="n"/>
-      <c r="AU569" s="2" t="n"/>
     </row>
     <row r="570">
       <c r="A570" s="2" t="n"/>
@@ -28596,7 +28022,6 @@
       <c r="AR570" s="2" t="n"/>
       <c r="AS570" s="2" t="n"/>
       <c r="AT570" s="2" t="n"/>
-      <c r="AU570" s="2" t="n"/>
     </row>
     <row r="571">
       <c r="A571" s="2" t="n"/>
@@ -28645,7 +28070,6 @@
       <c r="AR571" s="2" t="n"/>
       <c r="AS571" s="2" t="n"/>
       <c r="AT571" s="2" t="n"/>
-      <c r="AU571" s="2" t="n"/>
     </row>
     <row r="572">
       <c r="A572" s="2" t="n"/>
@@ -28694,7 +28118,6 @@
       <c r="AR572" s="2" t="n"/>
       <c r="AS572" s="2" t="n"/>
       <c r="AT572" s="2" t="n"/>
-      <c r="AU572" s="2" t="n"/>
     </row>
     <row r="573">
       <c r="A573" s="2" t="n"/>
@@ -28743,7 +28166,6 @@
       <c r="AR573" s="2" t="n"/>
       <c r="AS573" s="2" t="n"/>
       <c r="AT573" s="2" t="n"/>
-      <c r="AU573" s="2" t="n"/>
     </row>
     <row r="574">
       <c r="A574" s="2" t="n"/>
@@ -28792,7 +28214,6 @@
       <c r="AR574" s="2" t="n"/>
       <c r="AS574" s="2" t="n"/>
       <c r="AT574" s="2" t="n"/>
-      <c r="AU574" s="2" t="n"/>
     </row>
     <row r="575">
       <c r="A575" s="2" t="n"/>
@@ -28841,7 +28262,6 @@
       <c r="AR575" s="2" t="n"/>
       <c r="AS575" s="2" t="n"/>
       <c r="AT575" s="2" t="n"/>
-      <c r="AU575" s="2" t="n"/>
     </row>
     <row r="576">
       <c r="A576" s="2" t="n"/>
@@ -28890,7 +28310,6 @@
       <c r="AR576" s="2" t="n"/>
       <c r="AS576" s="2" t="n"/>
       <c r="AT576" s="2" t="n"/>
-      <c r="AU576" s="2" t="n"/>
     </row>
     <row r="577">
       <c r="A577" s="2" t="n"/>
@@ -28939,7 +28358,6 @@
       <c r="AR577" s="2" t="n"/>
       <c r="AS577" s="2" t="n"/>
       <c r="AT577" s="2" t="n"/>
-      <c r="AU577" s="2" t="n"/>
     </row>
     <row r="578">
       <c r="A578" s="2" t="n"/>
@@ -28988,7 +28406,6 @@
       <c r="AR578" s="2" t="n"/>
       <c r="AS578" s="2" t="n"/>
       <c r="AT578" s="2" t="n"/>
-      <c r="AU578" s="2" t="n"/>
     </row>
     <row r="579">
       <c r="A579" s="2" t="n"/>
@@ -29037,7 +28454,6 @@
       <c r="AR579" s="2" t="n"/>
       <c r="AS579" s="2" t="n"/>
       <c r="AT579" s="2" t="n"/>
-      <c r="AU579" s="2" t="n"/>
     </row>
     <row r="580">
       <c r="A580" s="2" t="n"/>
@@ -29086,7 +28502,6 @@
       <c r="AR580" s="2" t="n"/>
       <c r="AS580" s="2" t="n"/>
       <c r="AT580" s="2" t="n"/>
-      <c r="AU580" s="2" t="n"/>
     </row>
     <row r="581">
       <c r="A581" s="2" t="n"/>
@@ -29135,7 +28550,6 @@
       <c r="AR581" s="2" t="n"/>
       <c r="AS581" s="2" t="n"/>
       <c r="AT581" s="2" t="n"/>
-      <c r="AU581" s="2" t="n"/>
     </row>
     <row r="582">
       <c r="A582" s="2" t="n"/>
@@ -29184,7 +28598,6 @@
       <c r="AR582" s="2" t="n"/>
       <c r="AS582" s="2" t="n"/>
       <c r="AT582" s="2" t="n"/>
-      <c r="AU582" s="2" t="n"/>
     </row>
     <row r="583">
       <c r="A583" s="2" t="n"/>
@@ -29233,7 +28646,6 @@
       <c r="AR583" s="2" t="n"/>
       <c r="AS583" s="2" t="n"/>
       <c r="AT583" s="2" t="n"/>
-      <c r="AU583" s="2" t="n"/>
     </row>
     <row r="584">
       <c r="A584" s="2" t="n"/>
@@ -29282,7 +28694,6 @@
       <c r="AR584" s="2" t="n"/>
       <c r="AS584" s="2" t="n"/>
       <c r="AT584" s="2" t="n"/>
-      <c r="AU584" s="2" t="n"/>
     </row>
     <row r="585">
       <c r="A585" s="2" t="n"/>
@@ -29331,7 +28742,6 @@
       <c r="AR585" s="2" t="n"/>
       <c r="AS585" s="2" t="n"/>
       <c r="AT585" s="2" t="n"/>
-      <c r="AU585" s="2" t="n"/>
     </row>
     <row r="586">
       <c r="A586" s="2" t="n"/>
@@ -29380,7 +28790,6 @@
       <c r="AR586" s="2" t="n"/>
       <c r="AS586" s="2" t="n"/>
       <c r="AT586" s="2" t="n"/>
-      <c r="AU586" s="2" t="n"/>
     </row>
     <row r="587">
       <c r="A587" s="2" t="n"/>
@@ -29429,7 +28838,6 @@
       <c r="AR587" s="2" t="n"/>
       <c r="AS587" s="2" t="n"/>
       <c r="AT587" s="2" t="n"/>
-      <c r="AU587" s="2" t="n"/>
     </row>
     <row r="588">
       <c r="A588" s="2" t="n"/>
@@ -29478,7 +28886,6 @@
       <c r="AR588" s="2" t="n"/>
       <c r="AS588" s="2" t="n"/>
       <c r="AT588" s="2" t="n"/>
-      <c r="AU588" s="2" t="n"/>
     </row>
     <row r="589">
       <c r="A589" s="2" t="n"/>
@@ -29527,7 +28934,6 @@
       <c r="AR589" s="2" t="n"/>
       <c r="AS589" s="2" t="n"/>
       <c r="AT589" s="2" t="n"/>
-      <c r="AU589" s="2" t="n"/>
     </row>
     <row r="590">
       <c r="A590" s="2" t="n"/>
@@ -29576,7 +28982,6 @@
       <c r="AR590" s="2" t="n"/>
       <c r="AS590" s="2" t="n"/>
       <c r="AT590" s="2" t="n"/>
-      <c r="AU590" s="2" t="n"/>
     </row>
     <row r="591">
       <c r="A591" s="2" t="n"/>
@@ -29625,7 +29030,6 @@
       <c r="AR591" s="2" t="n"/>
       <c r="AS591" s="2" t="n"/>
       <c r="AT591" s="2" t="n"/>
-      <c r="AU591" s="2" t="n"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="n"/>
@@ -29674,7 +29078,6 @@
       <c r="AR592" s="2" t="n"/>
       <c r="AS592" s="2" t="n"/>
       <c r="AT592" s="2" t="n"/>
-      <c r="AU592" s="2" t="n"/>
     </row>
     <row r="593">
       <c r="A593" s="2" t="n"/>
@@ -29723,7 +29126,6 @@
       <c r="AR593" s="2" t="n"/>
       <c r="AS593" s="2" t="n"/>
       <c r="AT593" s="2" t="n"/>
-      <c r="AU593" s="2" t="n"/>
     </row>
     <row r="594">
       <c r="A594" s="2" t="n"/>
@@ -29772,7 +29174,6 @@
       <c r="AR594" s="2" t="n"/>
       <c r="AS594" s="2" t="n"/>
       <c r="AT594" s="2" t="n"/>
-      <c r="AU594" s="2" t="n"/>
     </row>
     <row r="595">
       <c r="A595" s="2" t="n"/>
@@ -29821,7 +29222,6 @@
       <c r="AR595" s="2" t="n"/>
       <c r="AS595" s="2" t="n"/>
       <c r="AT595" s="2" t="n"/>
-      <c r="AU595" s="2" t="n"/>
     </row>
     <row r="596">
       <c r="A596" s="2" t="n"/>
@@ -29870,7 +29270,6 @@
       <c r="AR596" s="2" t="n"/>
       <c r="AS596" s="2" t="n"/>
       <c r="AT596" s="2" t="n"/>
-      <c r="AU596" s="2" t="n"/>
     </row>
     <row r="597">
       <c r="A597" s="2" t="n"/>
@@ -29919,7 +29318,6 @@
       <c r="AR597" s="2" t="n"/>
       <c r="AS597" s="2" t="n"/>
       <c r="AT597" s="2" t="n"/>
-      <c r="AU597" s="2" t="n"/>
     </row>
     <row r="598">
       <c r="A598" s="2" t="n"/>
@@ -29968,7 +29366,6 @@
       <c r="AR598" s="2" t="n"/>
       <c r="AS598" s="2" t="n"/>
       <c r="AT598" s="2" t="n"/>
-      <c r="AU598" s="2" t="n"/>
     </row>
     <row r="599">
       <c r="A599" s="2" t="n"/>
@@ -30017,7 +29414,6 @@
       <c r="AR599" s="2" t="n"/>
       <c r="AS599" s="2" t="n"/>
       <c r="AT599" s="2" t="n"/>
-      <c r="AU599" s="2" t="n"/>
     </row>
     <row r="600">
       <c r="A600" s="2" t="n"/>
@@ -30066,7 +29462,6 @@
       <c r="AR600" s="2" t="n"/>
       <c r="AS600" s="2" t="n"/>
       <c r="AT600" s="2" t="n"/>
-      <c r="AU600" s="2" t="n"/>
     </row>
     <row r="601">
       <c r="A601" s="2" t="n"/>
@@ -30115,7 +29510,6 @@
       <c r="AR601" s="2" t="n"/>
       <c r="AS601" s="2" t="n"/>
       <c r="AT601" s="2" t="n"/>
-      <c r="AU601" s="2" t="n"/>
     </row>
     <row r="602">
       <c r="A602" s="2" t="n"/>
@@ -30164,7 +29558,6 @@
       <c r="AR602" s="2" t="n"/>
       <c r="AS602" s="2" t="n"/>
       <c r="AT602" s="2" t="n"/>
-      <c r="AU602" s="2" t="n"/>
     </row>
     <row r="603">
       <c r="A603" s="2" t="n"/>
@@ -30213,7 +29606,6 @@
       <c r="AR603" s="2" t="n"/>
       <c r="AS603" s="2" t="n"/>
       <c r="AT603" s="2" t="n"/>
-      <c r="AU603" s="2" t="n"/>
     </row>
     <row r="604">
       <c r="A604" s="2" t="n"/>
@@ -30262,7 +29654,6 @@
       <c r="AR604" s="2" t="n"/>
       <c r="AS604" s="2" t="n"/>
       <c r="AT604" s="2" t="n"/>
-      <c r="AU604" s="2" t="n"/>
     </row>
     <row r="605">
       <c r="A605" s="2" t="n"/>
@@ -30311,7 +29702,6 @@
       <c r="AR605" s="2" t="n"/>
       <c r="AS605" s="2" t="n"/>
       <c r="AT605" s="2" t="n"/>
-      <c r="AU605" s="2" t="n"/>
     </row>
     <row r="606">
       <c r="A606" s="2" t="n"/>
@@ -30360,7 +29750,6 @@
       <c r="AR606" s="2" t="n"/>
       <c r="AS606" s="2" t="n"/>
       <c r="AT606" s="2" t="n"/>
-      <c r="AU606" s="2" t="n"/>
     </row>
     <row r="607">
       <c r="A607" s="2" t="n"/>
@@ -30409,7 +29798,6 @@
       <c r="AR607" s="2" t="n"/>
       <c r="AS607" s="2" t="n"/>
       <c r="AT607" s="2" t="n"/>
-      <c r="AU607" s="2" t="n"/>
     </row>
     <row r="608">
       <c r="A608" s="2" t="n"/>
@@ -30458,7 +29846,6 @@
       <c r="AR608" s="2" t="n"/>
       <c r="AS608" s="2" t="n"/>
       <c r="AT608" s="2" t="n"/>
-      <c r="AU608" s="2" t="n"/>
     </row>
     <row r="609">
       <c r="A609" s="2" t="n"/>
@@ -30507,7 +29894,6 @@
       <c r="AR609" s="2" t="n"/>
       <c r="AS609" s="2" t="n"/>
       <c r="AT609" s="2" t="n"/>
-      <c r="AU609" s="2" t="n"/>
     </row>
     <row r="610">
       <c r="A610" s="2" t="n"/>
@@ -30556,7 +29942,6 @@
       <c r="AR610" s="2" t="n"/>
       <c r="AS610" s="2" t="n"/>
       <c r="AT610" s="2" t="n"/>
-      <c r="AU610" s="2" t="n"/>
     </row>
     <row r="611">
       <c r="A611" s="2" t="n"/>
@@ -30605,7 +29990,6 @@
       <c r="AR611" s="2" t="n"/>
       <c r="AS611" s="2" t="n"/>
       <c r="AT611" s="2" t="n"/>
-      <c r="AU611" s="2" t="n"/>
     </row>
     <row r="612">
       <c r="A612" s="2" t="n"/>
@@ -30654,7 +30038,6 @@
       <c r="AR612" s="2" t="n"/>
       <c r="AS612" s="2" t="n"/>
       <c r="AT612" s="2" t="n"/>
-      <c r="AU612" s="2" t="n"/>
     </row>
     <row r="613">
       <c r="A613" s="2" t="n"/>
@@ -30703,7 +30086,6 @@
       <c r="AR613" s="2" t="n"/>
       <c r="AS613" s="2" t="n"/>
       <c r="AT613" s="2" t="n"/>
-      <c r="AU613" s="2" t="n"/>
     </row>
     <row r="614">
       <c r="A614" s="2" t="n"/>
@@ -30752,7 +30134,6 @@
       <c r="AR614" s="2" t="n"/>
       <c r="AS614" s="2" t="n"/>
       <c r="AT614" s="2" t="n"/>
-      <c r="AU614" s="2" t="n"/>
     </row>
     <row r="615">
       <c r="A615" s="2" t="n"/>
@@ -30801,7 +30182,6 @@
       <c r="AR615" s="2" t="n"/>
       <c r="AS615" s="2" t="n"/>
       <c r="AT615" s="2" t="n"/>
-      <c r="AU615" s="2" t="n"/>
     </row>
     <row r="616">
       <c r="A616" s="2" t="n"/>
@@ -30850,7 +30230,6 @@
       <c r="AR616" s="2" t="n"/>
       <c r="AS616" s="2" t="n"/>
       <c r="AT616" s="2" t="n"/>
-      <c r="AU616" s="2" t="n"/>
     </row>
     <row r="617">
       <c r="A617" s="2" t="n"/>
@@ -30899,7 +30278,6 @@
       <c r="AR617" s="2" t="n"/>
       <c r="AS617" s="2" t="n"/>
       <c r="AT617" s="2" t="n"/>
-      <c r="AU617" s="2" t="n"/>
     </row>
     <row r="618">
       <c r="A618" s="2" t="n"/>
@@ -30948,7 +30326,6 @@
       <c r="AR618" s="2" t="n"/>
       <c r="AS618" s="2" t="n"/>
       <c r="AT618" s="2" t="n"/>
-      <c r="AU618" s="2" t="n"/>
     </row>
     <row r="619">
       <c r="A619" s="2" t="n"/>
@@ -30997,7 +30374,6 @@
       <c r="AR619" s="2" t="n"/>
       <c r="AS619" s="2" t="n"/>
       <c r="AT619" s="2" t="n"/>
-      <c r="AU619" s="2" t="n"/>
     </row>
     <row r="620">
       <c r="A620" s="2" t="n"/>
@@ -31046,7 +30422,6 @@
       <c r="AR620" s="2" t="n"/>
       <c r="AS620" s="2" t="n"/>
       <c r="AT620" s="2" t="n"/>
-      <c r="AU620" s="2" t="n"/>
     </row>
     <row r="621">
       <c r="A621" s="2" t="n"/>
@@ -31095,7 +30470,6 @@
       <c r="AR621" s="2" t="n"/>
       <c r="AS621" s="2" t="n"/>
       <c r="AT621" s="2" t="n"/>
-      <c r="AU621" s="2" t="n"/>
     </row>
     <row r="622">
       <c r="A622" s="2" t="n"/>
@@ -31144,7 +30518,6 @@
       <c r="AR622" s="2" t="n"/>
       <c r="AS622" s="2" t="n"/>
       <c r="AT622" s="2" t="n"/>
-      <c r="AU622" s="2" t="n"/>
     </row>
     <row r="623">
       <c r="A623" s="2" t="n"/>
@@ -31193,7 +30566,6 @@
       <c r="AR623" s="2" t="n"/>
       <c r="AS623" s="2" t="n"/>
       <c r="AT623" s="2" t="n"/>
-      <c r="AU623" s="2" t="n"/>
     </row>
     <row r="624">
       <c r="A624" s="2" t="n"/>
@@ -31242,7 +30614,6 @@
       <c r="AR624" s="2" t="n"/>
       <c r="AS624" s="2" t="n"/>
       <c r="AT624" s="2" t="n"/>
-      <c r="AU624" s="2" t="n"/>
     </row>
     <row r="625">
       <c r="A625" s="2" t="n"/>
@@ -31291,7 +30662,6 @@
       <c r="AR625" s="2" t="n"/>
       <c r="AS625" s="2" t="n"/>
       <c r="AT625" s="2" t="n"/>
-      <c r="AU625" s="2" t="n"/>
     </row>
     <row r="626">
       <c r="A626" s="2" t="n"/>
@@ -31340,7 +30710,6 @@
       <c r="AR626" s="2" t="n"/>
       <c r="AS626" s="2" t="n"/>
       <c r="AT626" s="2" t="n"/>
-      <c r="AU626" s="2" t="n"/>
     </row>
     <row r="627">
       <c r="A627" s="2" t="n"/>
@@ -31389,7 +30758,6 @@
       <c r="AR627" s="2" t="n"/>
       <c r="AS627" s="2" t="n"/>
       <c r="AT627" s="2" t="n"/>
-      <c r="AU627" s="2" t="n"/>
     </row>
     <row r="628">
       <c r="A628" s="2" t="n"/>
@@ -31438,7 +30806,6 @@
       <c r="AR628" s="2" t="n"/>
       <c r="AS628" s="2" t="n"/>
       <c r="AT628" s="2" t="n"/>
-      <c r="AU628" s="2" t="n"/>
     </row>
     <row r="629">
       <c r="A629" s="2" t="n"/>
@@ -31487,7 +30854,6 @@
       <c r="AR629" s="2" t="n"/>
       <c r="AS629" s="2" t="n"/>
       <c r="AT629" s="2" t="n"/>
-      <c r="AU629" s="2" t="n"/>
     </row>
     <row r="630">
       <c r="A630" s="2" t="n"/>
@@ -31536,7 +30902,6 @@
       <c r="AR630" s="2" t="n"/>
       <c r="AS630" s="2" t="n"/>
       <c r="AT630" s="2" t="n"/>
-      <c r="AU630" s="2" t="n"/>
     </row>
     <row r="631">
       <c r="A631" s="2" t="n"/>
@@ -31585,7 +30950,6 @@
       <c r="AR631" s="2" t="n"/>
       <c r="AS631" s="2" t="n"/>
       <c r="AT631" s="2" t="n"/>
-      <c r="AU631" s="2" t="n"/>
     </row>
     <row r="632">
       <c r="A632" s="2" t="n"/>
@@ -31634,7 +30998,6 @@
       <c r="AR632" s="2" t="n"/>
       <c r="AS632" s="2" t="n"/>
       <c r="AT632" s="2" t="n"/>
-      <c r="AU632" s="2" t="n"/>
     </row>
     <row r="633">
       <c r="A633" s="2" t="n"/>
@@ -31683,7 +31046,6 @@
       <c r="AR633" s="2" t="n"/>
       <c r="AS633" s="2" t="n"/>
       <c r="AT633" s="2" t="n"/>
-      <c r="AU633" s="2" t="n"/>
     </row>
     <row r="634">
       <c r="A634" s="2" t="n"/>
@@ -31732,7 +31094,6 @@
       <c r="AR634" s="2" t="n"/>
       <c r="AS634" s="2" t="n"/>
       <c r="AT634" s="2" t="n"/>
-      <c r="AU634" s="2" t="n"/>
     </row>
     <row r="635">
       <c r="A635" s="2" t="n"/>
@@ -31781,7 +31142,6 @@
       <c r="AR635" s="2" t="n"/>
       <c r="AS635" s="2" t="n"/>
       <c r="AT635" s="2" t="n"/>
-      <c r="AU635" s="2" t="n"/>
     </row>
     <row r="636">
       <c r="A636" s="2" t="n"/>
@@ -31830,7 +31190,6 @@
       <c r="AR636" s="2" t="n"/>
       <c r="AS636" s="2" t="n"/>
       <c r="AT636" s="2" t="n"/>
-      <c r="AU636" s="2" t="n"/>
     </row>
     <row r="637">
       <c r="A637" s="2" t="n"/>
@@ -31879,7 +31238,6 @@
       <c r="AR637" s="2" t="n"/>
       <c r="AS637" s="2" t="n"/>
       <c r="AT637" s="2" t="n"/>
-      <c r="AU637" s="2" t="n"/>
     </row>
     <row r="638">
       <c r="A638" s="2" t="n"/>
@@ -31928,7 +31286,6 @@
       <c r="AR638" s="2" t="n"/>
       <c r="AS638" s="2" t="n"/>
       <c r="AT638" s="2" t="n"/>
-      <c r="AU638" s="2" t="n"/>
     </row>
     <row r="639">
       <c r="A639" s="2" t="n"/>
@@ -31977,7 +31334,6 @@
       <c r="AR639" s="2" t="n"/>
       <c r="AS639" s="2" t="n"/>
       <c r="AT639" s="2" t="n"/>
-      <c r="AU639" s="2" t="n"/>
     </row>
     <row r="640">
       <c r="A640" s="2" t="n"/>
@@ -32026,7 +31382,6 @@
       <c r="AR640" s="2" t="n"/>
       <c r="AS640" s="2" t="n"/>
       <c r="AT640" s="2" t="n"/>
-      <c r="AU640" s="2" t="n"/>
     </row>
     <row r="641">
       <c r="A641" s="2" t="n"/>
@@ -32075,7 +31430,6 @@
       <c r="AR641" s="2" t="n"/>
       <c r="AS641" s="2" t="n"/>
       <c r="AT641" s="2" t="n"/>
-      <c r="AU641" s="2" t="n"/>
     </row>
     <row r="642">
       <c r="A642" s="2" t="n"/>
@@ -32124,7 +31478,6 @@
       <c r="AR642" s="2" t="n"/>
       <c r="AS642" s="2" t="n"/>
       <c r="AT642" s="2" t="n"/>
-      <c r="AU642" s="2" t="n"/>
     </row>
     <row r="643">
       <c r="A643" s="2" t="n"/>
@@ -32173,7 +31526,6 @@
       <c r="AR643" s="2" t="n"/>
       <c r="AS643" s="2" t="n"/>
       <c r="AT643" s="2" t="n"/>
-      <c r="AU643" s="2" t="n"/>
     </row>
     <row r="644">
       <c r="A644" s="2" t="n"/>
@@ -32222,7 +31574,6 @@
       <c r="AR644" s="2" t="n"/>
       <c r="AS644" s="2" t="n"/>
       <c r="AT644" s="2" t="n"/>
-      <c r="AU644" s="2" t="n"/>
     </row>
     <row r="645">
       <c r="A645" s="2" t="n"/>
@@ -32271,7 +31622,6 @@
       <c r="AR645" s="2" t="n"/>
       <c r="AS645" s="2" t="n"/>
       <c r="AT645" s="2" t="n"/>
-      <c r="AU645" s="2" t="n"/>
     </row>
     <row r="646">
       <c r="A646" s="2" t="n"/>
@@ -32320,7 +31670,6 @@
       <c r="AR646" s="2" t="n"/>
       <c r="AS646" s="2" t="n"/>
       <c r="AT646" s="2" t="n"/>
-      <c r="AU646" s="2" t="n"/>
     </row>
     <row r="647">
       <c r="A647" s="2" t="n"/>
@@ -32369,7 +31718,6 @@
       <c r="AR647" s="2" t="n"/>
       <c r="AS647" s="2" t="n"/>
       <c r="AT647" s="2" t="n"/>
-      <c r="AU647" s="2" t="n"/>
     </row>
     <row r="648">
       <c r="A648" s="2" t="n"/>
@@ -32418,7 +31766,6 @@
       <c r="AR648" s="2" t="n"/>
       <c r="AS648" s="2" t="n"/>
       <c r="AT648" s="2" t="n"/>
-      <c r="AU648" s="2" t="n"/>
     </row>
     <row r="649">
       <c r="A649" s="2" t="n"/>
@@ -32467,7 +31814,6 @@
       <c r="AR649" s="2" t="n"/>
       <c r="AS649" s="2" t="n"/>
       <c r="AT649" s="2" t="n"/>
-      <c r="AU649" s="2" t="n"/>
     </row>
     <row r="650">
       <c r="A650" s="2" t="n"/>
@@ -32516,7 +31862,6 @@
       <c r="AR650" s="2" t="n"/>
       <c r="AS650" s="2" t="n"/>
       <c r="AT650" s="2" t="n"/>
-      <c r="AU650" s="2" t="n"/>
     </row>
     <row r="651">
       <c r="A651" s="2" t="n"/>
@@ -32565,7 +31910,6 @@
       <c r="AR651" s="2" t="n"/>
       <c r="AS651" s="2" t="n"/>
       <c r="AT651" s="2" t="n"/>
-      <c r="AU651" s="2" t="n"/>
     </row>
     <row r="652">
       <c r="A652" s="2" t="n"/>
@@ -32614,7 +31958,6 @@
       <c r="AR652" s="2" t="n"/>
       <c r="AS652" s="2" t="n"/>
       <c r="AT652" s="2" t="n"/>
-      <c r="AU652" s="2" t="n"/>
     </row>
     <row r="653">
       <c r="A653" s="2" t="n"/>
@@ -32663,7 +32006,6 @@
       <c r="AR653" s="2" t="n"/>
       <c r="AS653" s="2" t="n"/>
       <c r="AT653" s="2" t="n"/>
-      <c r="AU653" s="2" t="n"/>
     </row>
     <row r="654">
       <c r="A654" s="2" t="n"/>
@@ -32712,7 +32054,6 @@
       <c r="AR654" s="2" t="n"/>
       <c r="AS654" s="2" t="n"/>
       <c r="AT654" s="2" t="n"/>
-      <c r="AU654" s="2" t="n"/>
     </row>
     <row r="655">
       <c r="A655" s="2" t="n"/>
@@ -32761,7 +32102,6 @@
       <c r="AR655" s="2" t="n"/>
       <c r="AS655" s="2" t="n"/>
       <c r="AT655" s="2" t="n"/>
-      <c r="AU655" s="2" t="n"/>
     </row>
     <row r="656">
       <c r="A656" s="2" t="n"/>
@@ -32810,7 +32150,6 @@
       <c r="AR656" s="2" t="n"/>
       <c r="AS656" s="2" t="n"/>
       <c r="AT656" s="2" t="n"/>
-      <c r="AU656" s="2" t="n"/>
     </row>
     <row r="657">
       <c r="A657" s="2" t="n"/>
@@ -32859,7 +32198,6 @@
       <c r="AR657" s="2" t="n"/>
       <c r="AS657" s="2" t="n"/>
       <c r="AT657" s="2" t="n"/>
-      <c r="AU657" s="2" t="n"/>
     </row>
     <row r="658">
       <c r="A658" s="2" t="n"/>
@@ -32908,7 +32246,6 @@
       <c r="AR658" s="2" t="n"/>
       <c r="AS658" s="2" t="n"/>
       <c r="AT658" s="2" t="n"/>
-      <c r="AU658" s="2" t="n"/>
     </row>
     <row r="659">
       <c r="A659" s="2" t="n"/>
@@ -32957,7 +32294,6 @@
       <c r="AR659" s="2" t="n"/>
       <c r="AS659" s="2" t="n"/>
       <c r="AT659" s="2" t="n"/>
-      <c r="AU659" s="2" t="n"/>
     </row>
     <row r="660">
       <c r="A660" s="2" t="n"/>
@@ -33006,7 +32342,6 @@
       <c r="AR660" s="2" t="n"/>
       <c r="AS660" s="2" t="n"/>
       <c r="AT660" s="2" t="n"/>
-      <c r="AU660" s="2" t="n"/>
     </row>
     <row r="661">
       <c r="A661" s="2" t="n"/>
@@ -33055,7 +32390,6 @@
       <c r="AR661" s="2" t="n"/>
       <c r="AS661" s="2" t="n"/>
       <c r="AT661" s="2" t="n"/>
-      <c r="AU661" s="2" t="n"/>
     </row>
     <row r="662">
       <c r="A662" s="2" t="n"/>
@@ -33104,7 +32438,6 @@
       <c r="AR662" s="2" t="n"/>
       <c r="AS662" s="2" t="n"/>
       <c r="AT662" s="2" t="n"/>
-      <c r="AU662" s="2" t="n"/>
     </row>
     <row r="663">
       <c r="A663" s="2" t="n"/>
@@ -33153,7 +32486,6 @@
       <c r="AR663" s="2" t="n"/>
       <c r="AS663" s="2" t="n"/>
       <c r="AT663" s="2" t="n"/>
-      <c r="AU663" s="2" t="n"/>
     </row>
     <row r="664">
       <c r="A664" s="2" t="n"/>
@@ -33202,7 +32534,6 @@
       <c r="AR664" s="2" t="n"/>
       <c r="AS664" s="2" t="n"/>
       <c r="AT664" s="2" t="n"/>
-      <c r="AU664" s="2" t="n"/>
     </row>
     <row r="665">
       <c r="A665" s="2" t="n"/>
@@ -33251,7 +32582,6 @@
       <c r="AR665" s="2" t="n"/>
       <c r="AS665" s="2" t="n"/>
       <c r="AT665" s="2" t="n"/>
-      <c r="AU665" s="2" t="n"/>
     </row>
     <row r="666">
       <c r="A666" s="2" t="n"/>
@@ -33300,7 +32630,6 @@
       <c r="AR666" s="2" t="n"/>
       <c r="AS666" s="2" t="n"/>
       <c r="AT666" s="2" t="n"/>
-      <c r="AU666" s="2" t="n"/>
     </row>
     <row r="667">
       <c r="A667" s="2" t="n"/>
@@ -33349,7 +32678,6 @@
       <c r="AR667" s="2" t="n"/>
       <c r="AS667" s="2" t="n"/>
       <c r="AT667" s="2" t="n"/>
-      <c r="AU667" s="2" t="n"/>
     </row>
     <row r="668">
       <c r="A668" s="2" t="n"/>
@@ -33398,7 +32726,6 @@
       <c r="AR668" s="2" t="n"/>
       <c r="AS668" s="2" t="n"/>
       <c r="AT668" s="2" t="n"/>
-      <c r="AU668" s="2" t="n"/>
     </row>
     <row r="669">
       <c r="A669" s="2" t="n"/>
@@ -33447,7 +32774,6 @@
       <c r="AR669" s="2" t="n"/>
       <c r="AS669" s="2" t="n"/>
       <c r="AT669" s="2" t="n"/>
-      <c r="AU669" s="2" t="n"/>
     </row>
     <row r="670">
       <c r="A670" s="2" t="n"/>
@@ -33496,7 +32822,6 @@
       <c r="AR670" s="2" t="n"/>
       <c r="AS670" s="2" t="n"/>
       <c r="AT670" s="2" t="n"/>
-      <c r="AU670" s="2" t="n"/>
     </row>
     <row r="671">
       <c r="A671" s="2" t="n"/>
@@ -33545,7 +32870,6 @@
       <c r="AR671" s="2" t="n"/>
       <c r="AS671" s="2" t="n"/>
       <c r="AT671" s="2" t="n"/>
-      <c r="AU671" s="2" t="n"/>
     </row>
     <row r="672">
       <c r="A672" s="2" t="n"/>
@@ -33594,7 +32918,6 @@
       <c r="AR672" s="2" t="n"/>
       <c r="AS672" s="2" t="n"/>
       <c r="AT672" s="2" t="n"/>
-      <c r="AU672" s="2" t="n"/>
     </row>
     <row r="673">
       <c r="A673" s="2" t="n"/>
@@ -33643,7 +32966,6 @@
       <c r="AR673" s="2" t="n"/>
       <c r="AS673" s="2" t="n"/>
       <c r="AT673" s="2" t="n"/>
-      <c r="AU673" s="2" t="n"/>
     </row>
     <row r="674">
       <c r="A674" s="2" t="n"/>
@@ -33692,7 +33014,6 @@
       <c r="AR674" s="2" t="n"/>
       <c r="AS674" s="2" t="n"/>
       <c r="AT674" s="2" t="n"/>
-      <c r="AU674" s="2" t="n"/>
     </row>
     <row r="675">
       <c r="A675" s="2" t="n"/>
@@ -33741,7 +33062,6 @@
       <c r="AR675" s="2" t="n"/>
       <c r="AS675" s="2" t="n"/>
       <c r="AT675" s="2" t="n"/>
-      <c r="AU675" s="2" t="n"/>
     </row>
     <row r="676">
       <c r="A676" s="2" t="n"/>
@@ -33790,7 +33110,6 @@
       <c r="AR676" s="2" t="n"/>
       <c r="AS676" s="2" t="n"/>
       <c r="AT676" s="2" t="n"/>
-      <c r="AU676" s="2" t="n"/>
     </row>
     <row r="677">
       <c r="A677" s="2" t="n"/>
@@ -33839,7 +33158,6 @@
       <c r="AR677" s="2" t="n"/>
       <c r="AS677" s="2" t="n"/>
       <c r="AT677" s="2" t="n"/>
-      <c r="AU677" s="2" t="n"/>
     </row>
     <row r="678">
       <c r="A678" s="2" t="n"/>
@@ -33888,7 +33206,6 @@
       <c r="AR678" s="2" t="n"/>
       <c r="AS678" s="2" t="n"/>
       <c r="AT678" s="2" t="n"/>
-      <c r="AU678" s="2" t="n"/>
     </row>
     <row r="679">
       <c r="A679" s="2" t="n"/>
@@ -33937,7 +33254,6 @@
       <c r="AR679" s="2" t="n"/>
       <c r="AS679" s="2" t="n"/>
       <c r="AT679" s="2" t="n"/>
-      <c r="AU679" s="2" t="n"/>
     </row>
     <row r="680">
       <c r="A680" s="2" t="n"/>
@@ -33986,7 +33302,6 @@
       <c r="AR680" s="2" t="n"/>
       <c r="AS680" s="2" t="n"/>
       <c r="AT680" s="2" t="n"/>
-      <c r="AU680" s="2" t="n"/>
     </row>
     <row r="681">
       <c r="A681" s="2" t="n"/>
@@ -34035,7 +33350,6 @@
       <c r="AR681" s="2" t="n"/>
       <c r="AS681" s="2" t="n"/>
       <c r="AT681" s="2" t="n"/>
-      <c r="AU681" s="2" t="n"/>
     </row>
     <row r="682">
       <c r="A682" s="2" t="n"/>
@@ -34084,7 +33398,6 @@
       <c r="AR682" s="2" t="n"/>
       <c r="AS682" s="2" t="n"/>
       <c r="AT682" s="2" t="n"/>
-      <c r="AU682" s="2" t="n"/>
     </row>
     <row r="683">
       <c r="A683" s="2" t="n"/>
@@ -34133,7 +33446,6 @@
       <c r="AR683" s="2" t="n"/>
       <c r="AS683" s="2" t="n"/>
       <c r="AT683" s="2" t="n"/>
-      <c r="AU683" s="2" t="n"/>
     </row>
     <row r="684">
       <c r="A684" s="2" t="n"/>
@@ -34182,7 +33494,6 @@
       <c r="AR684" s="2" t="n"/>
       <c r="AS684" s="2" t="n"/>
       <c r="AT684" s="2" t="n"/>
-      <c r="AU684" s="2" t="n"/>
     </row>
     <row r="685">
       <c r="A685" s="2" t="n"/>
@@ -34231,7 +33542,6 @@
       <c r="AR685" s="2" t="n"/>
       <c r="AS685" s="2" t="n"/>
       <c r="AT685" s="2" t="n"/>
-      <c r="AU685" s="2" t="n"/>
     </row>
     <row r="686">
       <c r="A686" s="2" t="n"/>
@@ -34280,7 +33590,6 @@
       <c r="AR686" s="2" t="n"/>
       <c r="AS686" s="2" t="n"/>
       <c r="AT686" s="2" t="n"/>
-      <c r="AU686" s="2" t="n"/>
     </row>
     <row r="687">
       <c r="A687" s="2" t="n"/>
@@ -34329,7 +33638,6 @@
       <c r="AR687" s="2" t="n"/>
       <c r="AS687" s="2" t="n"/>
       <c r="AT687" s="2" t="n"/>
-      <c r="AU687" s="2" t="n"/>
     </row>
     <row r="688">
       <c r="A688" s="2" t="n"/>
@@ -34378,7 +33686,6 @@
       <c r="AR688" s="2" t="n"/>
       <c r="AS688" s="2" t="n"/>
       <c r="AT688" s="2" t="n"/>
-      <c r="AU688" s="2" t="n"/>
     </row>
     <row r="689">
       <c r="A689" s="2" t="n"/>
@@ -34427,7 +33734,6 @@
       <c r="AR689" s="2" t="n"/>
       <c r="AS689" s="2" t="n"/>
       <c r="AT689" s="2" t="n"/>
-      <c r="AU689" s="2" t="n"/>
     </row>
     <row r="690">
       <c r="A690" s="2" t="n"/>
@@ -34476,7 +33782,6 @@
       <c r="AR690" s="2" t="n"/>
       <c r="AS690" s="2" t="n"/>
       <c r="AT690" s="2" t="n"/>
-      <c r="AU690" s="2" t="n"/>
     </row>
     <row r="691">
       <c r="A691" s="2" t="n"/>
@@ -34525,7 +33830,6 @@
       <c r="AR691" s="2" t="n"/>
       <c r="AS691" s="2" t="n"/>
       <c r="AT691" s="2" t="n"/>
-      <c r="AU691" s="2" t="n"/>
     </row>
     <row r="692">
       <c r="A692" s="2" t="n"/>
@@ -34574,7 +33878,6 @@
       <c r="AR692" s="2" t="n"/>
       <c r="AS692" s="2" t="n"/>
       <c r="AT692" s="2" t="n"/>
-      <c r="AU692" s="2" t="n"/>
     </row>
     <row r="693">
       <c r="A693" s="2" t="n"/>
@@ -34623,7 +33926,6 @@
       <c r="AR693" s="2" t="n"/>
       <c r="AS693" s="2" t="n"/>
       <c r="AT693" s="2" t="n"/>
-      <c r="AU693" s="2" t="n"/>
     </row>
     <row r="694">
       <c r="A694" s="2" t="n"/>
@@ -34672,7 +33974,6 @@
       <c r="AR694" s="2" t="n"/>
       <c r="AS694" s="2" t="n"/>
       <c r="AT694" s="2" t="n"/>
-      <c r="AU694" s="2" t="n"/>
     </row>
     <row r="695">
       <c r="A695" s="2" t="n"/>
@@ -34721,7 +34022,6 @@
       <c r="AR695" s="2" t="n"/>
       <c r="AS695" s="2" t="n"/>
       <c r="AT695" s="2" t="n"/>
-      <c r="AU695" s="2" t="n"/>
     </row>
     <row r="696">
       <c r="A696" s="2" t="n"/>
@@ -34770,7 +34070,6 @@
       <c r="AR696" s="2" t="n"/>
       <c r="AS696" s="2" t="n"/>
       <c r="AT696" s="2" t="n"/>
-      <c r="AU696" s="2" t="n"/>
     </row>
     <row r="697">
       <c r="A697" s="2" t="n"/>
@@ -34819,7 +34118,6 @@
       <c r="AR697" s="2" t="n"/>
       <c r="AS697" s="2" t="n"/>
       <c r="AT697" s="2" t="n"/>
-      <c r="AU697" s="2" t="n"/>
     </row>
     <row r="698">
       <c r="A698" s="2" t="n"/>
@@ -34868,7 +34166,6 @@
       <c r="AR698" s="2" t="n"/>
       <c r="AS698" s="2" t="n"/>
       <c r="AT698" s="2" t="n"/>
-      <c r="AU698" s="2" t="n"/>
     </row>
     <row r="699">
       <c r="A699" s="2" t="n"/>
@@ -34917,7 +34214,6 @@
       <c r="AR699" s="2" t="n"/>
       <c r="AS699" s="2" t="n"/>
       <c r="AT699" s="2" t="n"/>
-      <c r="AU699" s="2" t="n"/>
     </row>
     <row r="700">
       <c r="A700" s="2" t="n"/>
@@ -34966,7 +34262,6 @@
       <c r="AR700" s="2" t="n"/>
       <c r="AS700" s="2" t="n"/>
       <c r="AT700" s="2" t="n"/>
-      <c r="AU700" s="2" t="n"/>
     </row>
     <row r="701">
       <c r="A701" s="2" t="n"/>
@@ -35015,7 +34310,6 @@
       <c r="AR701" s="2" t="n"/>
       <c r="AS701" s="2" t="n"/>
       <c r="AT701" s="2" t="n"/>
-      <c r="AU701" s="2" t="n"/>
     </row>
     <row r="702">
       <c r="A702" s="2" t="n"/>
@@ -35064,7 +34358,6 @@
       <c r="AR702" s="2" t="n"/>
       <c r="AS702" s="2" t="n"/>
       <c r="AT702" s="2" t="n"/>
-      <c r="AU702" s="2" t="n"/>
     </row>
     <row r="703">
       <c r="A703" s="2" t="n"/>
@@ -35113,7 +34406,6 @@
       <c r="AR703" s="2" t="n"/>
       <c r="AS703" s="2" t="n"/>
       <c r="AT703" s="2" t="n"/>
-      <c r="AU703" s="2" t="n"/>
     </row>
     <row r="704">
       <c r="A704" s="2" t="n"/>
@@ -35162,7 +34454,6 @@
       <c r="AR704" s="2" t="n"/>
       <c r="AS704" s="2" t="n"/>
       <c r="AT704" s="2" t="n"/>
-      <c r="AU704" s="2" t="n"/>
     </row>
     <row r="705">
       <c r="A705" s="2" t="n"/>
@@ -35211,7 +34502,6 @@
       <c r="AR705" s="2" t="n"/>
       <c r="AS705" s="2" t="n"/>
       <c r="AT705" s="2" t="n"/>
-      <c r="AU705" s="2" t="n"/>
     </row>
     <row r="706">
       <c r="A706" s="2" t="n"/>
@@ -35260,7 +34550,6 @@
       <c r="AR706" s="2" t="n"/>
       <c r="AS706" s="2" t="n"/>
       <c r="AT706" s="2" t="n"/>
-      <c r="AU706" s="2" t="n"/>
     </row>
     <row r="707">
       <c r="A707" s="2" t="n"/>
@@ -35309,7 +34598,6 @@
       <c r="AR707" s="2" t="n"/>
       <c r="AS707" s="2" t="n"/>
       <c r="AT707" s="2" t="n"/>
-      <c r="AU707" s="2" t="n"/>
     </row>
     <row r="708">
       <c r="A708" s="2" t="n"/>
@@ -35358,7 +34646,6 @@
       <c r="AR708" s="2" t="n"/>
       <c r="AS708" s="2" t="n"/>
       <c r="AT708" s="2" t="n"/>
-      <c r="AU708" s="2" t="n"/>
     </row>
     <row r="709">
       <c r="A709" s="2" t="n"/>
@@ -35407,7 +34694,6 @@
       <c r="AR709" s="2" t="n"/>
       <c r="AS709" s="2" t="n"/>
       <c r="AT709" s="2" t="n"/>
-      <c r="AU709" s="2" t="n"/>
     </row>
     <row r="710">
       <c r="A710" s="2" t="n"/>
@@ -35456,7 +34742,6 @@
       <c r="AR710" s="2" t="n"/>
       <c r="AS710" s="2" t="n"/>
       <c r="AT710" s="2" t="n"/>
-      <c r="AU710" s="2" t="n"/>
     </row>
     <row r="711">
       <c r="A711" s="2" t="n"/>
@@ -35505,7 +34790,6 @@
       <c r="AR711" s="2" t="n"/>
       <c r="AS711" s="2" t="n"/>
       <c r="AT711" s="2" t="n"/>
-      <c r="AU711" s="2" t="n"/>
     </row>
     <row r="712">
       <c r="A712" s="2" t="n"/>
@@ -35554,7 +34838,6 @@
       <c r="AR712" s="2" t="n"/>
       <c r="AS712" s="2" t="n"/>
       <c r="AT712" s="2" t="n"/>
-      <c r="AU712" s="2" t="n"/>
     </row>
     <row r="713">
       <c r="A713" s="2" t="n"/>
@@ -35603,7 +34886,6 @@
       <c r="AR713" s="2" t="n"/>
       <c r="AS713" s="2" t="n"/>
       <c r="AT713" s="2" t="n"/>
-      <c r="AU713" s="2" t="n"/>
     </row>
     <row r="714">
       <c r="A714" s="2" t="n"/>
@@ -35652,7 +34934,6 @@
       <c r="AR714" s="2" t="n"/>
       <c r="AS714" s="2" t="n"/>
       <c r="AT714" s="2" t="n"/>
-      <c r="AU714" s="2" t="n"/>
     </row>
     <row r="715">
       <c r="A715" s="2" t="n"/>
@@ -35701,7 +34982,6 @@
       <c r="AR715" s="2" t="n"/>
       <c r="AS715" s="2" t="n"/>
       <c r="AT715" s="2" t="n"/>
-      <c r="AU715" s="2" t="n"/>
     </row>
     <row r="716">
       <c r="A716" s="2" t="n"/>
@@ -35750,7 +35030,6 @@
       <c r="AR716" s="2" t="n"/>
       <c r="AS716" s="2" t="n"/>
       <c r="AT716" s="2" t="n"/>
-      <c r="AU716" s="2" t="n"/>
     </row>
     <row r="717">
       <c r="A717" s="2" t="n"/>
@@ -35799,7 +35078,6 @@
       <c r="AR717" s="2" t="n"/>
       <c r="AS717" s="2" t="n"/>
       <c r="AT717" s="2" t="n"/>
-      <c r="AU717" s="2" t="n"/>
     </row>
     <row r="718">
       <c r="A718" s="2" t="n"/>
@@ -35848,7 +35126,6 @@
       <c r="AR718" s="2" t="n"/>
       <c r="AS718" s="2" t="n"/>
       <c r="AT718" s="2" t="n"/>
-      <c r="AU718" s="2" t="n"/>
     </row>
     <row r="719">
       <c r="A719" s="2" t="n"/>
@@ -35897,7 +35174,6 @@
       <c r="AR719" s="2" t="n"/>
       <c r="AS719" s="2" t="n"/>
       <c r="AT719" s="2" t="n"/>
-      <c r="AU719" s="2" t="n"/>
     </row>
     <row r="720">
       <c r="A720" s="2" t="n"/>
@@ -35946,7 +35222,6 @@
       <c r="AR720" s="2" t="n"/>
       <c r="AS720" s="2" t="n"/>
       <c r="AT720" s="2" t="n"/>
-      <c r="AU720" s="2" t="n"/>
     </row>
     <row r="721">
       <c r="A721" s="2" t="n"/>
@@ -35995,7 +35270,6 @@
       <c r="AR721" s="2" t="n"/>
       <c r="AS721" s="2" t="n"/>
       <c r="AT721" s="2" t="n"/>
-      <c r="AU721" s="2" t="n"/>
     </row>
     <row r="722">
       <c r="A722" s="2" t="n"/>
@@ -36044,7 +35318,6 @@
       <c r="AR722" s="2" t="n"/>
       <c r="AS722" s="2" t="n"/>
       <c r="AT722" s="2" t="n"/>
-      <c r="AU722" s="2" t="n"/>
     </row>
     <row r="723">
       <c r="A723" s="2" t="n"/>
@@ -36093,7 +35366,6 @@
       <c r="AR723" s="2" t="n"/>
       <c r="AS723" s="2" t="n"/>
       <c r="AT723" s="2" t="n"/>
-      <c r="AU723" s="2" t="n"/>
     </row>
     <row r="724">
       <c r="A724" s="2" t="n"/>
@@ -36142,7 +35414,6 @@
       <c r="AR724" s="2" t="n"/>
       <c r="AS724" s="2" t="n"/>
       <c r="AT724" s="2" t="n"/>
-      <c r="AU724" s="2" t="n"/>
     </row>
     <row r="725">
       <c r="A725" s="2" t="n"/>
@@ -36191,7 +35462,6 @@
       <c r="AR725" s="2" t="n"/>
       <c r="AS725" s="2" t="n"/>
       <c r="AT725" s="2" t="n"/>
-      <c r="AU725" s="2" t="n"/>
     </row>
     <row r="726">
       <c r="A726" s="2" t="n"/>
@@ -36240,7 +35510,6 @@
       <c r="AR726" s="2" t="n"/>
       <c r="AS726" s="2" t="n"/>
       <c r="AT726" s="2" t="n"/>
-      <c r="AU726" s="2" t="n"/>
     </row>
     <row r="727">
       <c r="A727" s="2" t="n"/>
@@ -36289,7 +35558,6 @@
       <c r="AR727" s="2" t="n"/>
       <c r="AS727" s="2" t="n"/>
       <c r="AT727" s="2" t="n"/>
-      <c r="AU727" s="2" t="n"/>
     </row>
     <row r="728">
       <c r="A728" s="2" t="n"/>
@@ -36338,7 +35606,6 @@
       <c r="AR728" s="2" t="n"/>
       <c r="AS728" s="2" t="n"/>
       <c r="AT728" s="2" t="n"/>
-      <c r="AU728" s="2" t="n"/>
     </row>
     <row r="729">
       <c r="A729" s="2" t="n"/>
@@ -36387,7 +35654,6 @@
       <c r="AR729" s="2" t="n"/>
       <c r="AS729" s="2" t="n"/>
       <c r="AT729" s="2" t="n"/>
-      <c r="AU729" s="2" t="n"/>
     </row>
     <row r="730">
       <c r="A730" s="2" t="n"/>
@@ -36436,7 +35702,6 @@
       <c r="AR730" s="2" t="n"/>
       <c r="AS730" s="2" t="n"/>
       <c r="AT730" s="2" t="n"/>
-      <c r="AU730" s="2" t="n"/>
     </row>
     <row r="731">
       <c r="A731" s="2" t="n"/>
@@ -36485,7 +35750,6 @@
       <c r="AR731" s="2" t="n"/>
       <c r="AS731" s="2" t="n"/>
       <c r="AT731" s="2" t="n"/>
-      <c r="AU731" s="2" t="n"/>
     </row>
     <row r="732">
       <c r="A732" s="2" t="n"/>
@@ -36534,7 +35798,6 @@
       <c r="AR732" s="2" t="n"/>
       <c r="AS732" s="2" t="n"/>
       <c r="AT732" s="2" t="n"/>
-      <c r="AU732" s="2" t="n"/>
     </row>
     <row r="733">
       <c r="A733" s="2" t="n"/>
@@ -36583,7 +35846,6 @@
       <c r="AR733" s="2" t="n"/>
       <c r="AS733" s="2" t="n"/>
       <c r="AT733" s="2" t="n"/>
-      <c r="AU733" s="2" t="n"/>
     </row>
     <row r="734">
       <c r="A734" s="2" t="n"/>
@@ -36632,7 +35894,6 @@
       <c r="AR734" s="2" t="n"/>
       <c r="AS734" s="2" t="n"/>
       <c r="AT734" s="2" t="n"/>
-      <c r="AU734" s="2" t="n"/>
     </row>
     <row r="735">
       <c r="A735" s="2" t="n"/>
@@ -36681,7 +35942,6 @@
       <c r="AR735" s="2" t="n"/>
       <c r="AS735" s="2" t="n"/>
       <c r="AT735" s="2" t="n"/>
-      <c r="AU735" s="2" t="n"/>
     </row>
     <row r="736">
       <c r="A736" s="2" t="n"/>
@@ -36730,7 +35990,6 @@
       <c r="AR736" s="2" t="n"/>
       <c r="AS736" s="2" t="n"/>
       <c r="AT736" s="2" t="n"/>
-      <c r="AU736" s="2" t="n"/>
     </row>
     <row r="737">
       <c r="A737" s="2" t="n"/>
@@ -36779,7 +36038,6 @@
       <c r="AR737" s="2" t="n"/>
       <c r="AS737" s="2" t="n"/>
       <c r="AT737" s="2" t="n"/>
-      <c r="AU737" s="2" t="n"/>
     </row>
     <row r="738">
       <c r="A738" s="2" t="n"/>
@@ -36828,7 +36086,6 @@
       <c r="AR738" s="2" t="n"/>
       <c r="AS738" s="2" t="n"/>
       <c r="AT738" s="2" t="n"/>
-      <c r="AU738" s="2" t="n"/>
     </row>
     <row r="739">
       <c r="A739" s="2" t="n"/>
@@ -36877,7 +36134,6 @@
       <c r="AR739" s="2" t="n"/>
       <c r="AS739" s="2" t="n"/>
       <c r="AT739" s="2" t="n"/>
-      <c r="AU739" s="2" t="n"/>
     </row>
     <row r="740">
       <c r="A740" s="2" t="n"/>
@@ -36926,7 +36182,6 @@
       <c r="AR740" s="2" t="n"/>
       <c r="AS740" s="2" t="n"/>
       <c r="AT740" s="2" t="n"/>
-      <c r="AU740" s="2" t="n"/>
     </row>
     <row r="741">
       <c r="A741" s="2" t="n"/>
@@ -36975,7 +36230,6 @@
       <c r="AR741" s="2" t="n"/>
       <c r="AS741" s="2" t="n"/>
       <c r="AT741" s="2" t="n"/>
-      <c r="AU741" s="2" t="n"/>
     </row>
     <row r="742">
       <c r="A742" s="2" t="n"/>
@@ -37024,7 +36278,6 @@
       <c r="AR742" s="2" t="n"/>
       <c r="AS742" s="2" t="n"/>
       <c r="AT742" s="2" t="n"/>
-      <c r="AU742" s="2" t="n"/>
     </row>
     <row r="743">
       <c r="A743" s="2" t="n"/>
@@ -37073,7 +36326,6 @@
       <c r="AR743" s="2" t="n"/>
       <c r="AS743" s="2" t="n"/>
       <c r="AT743" s="2" t="n"/>
-      <c r="AU743" s="2" t="n"/>
     </row>
     <row r="744">
       <c r="A744" s="2" t="n"/>
@@ -37122,7 +36374,6 @@
       <c r="AR744" s="2" t="n"/>
       <c r="AS744" s="2" t="n"/>
       <c r="AT744" s="2" t="n"/>
-      <c r="AU744" s="2" t="n"/>
     </row>
     <row r="745">
       <c r="A745" s="2" t="n"/>
@@ -37171,7 +36422,6 @@
       <c r="AR745" s="2" t="n"/>
       <c r="AS745" s="2" t="n"/>
       <c r="AT745" s="2" t="n"/>
-      <c r="AU745" s="2" t="n"/>
     </row>
     <row r="746">
       <c r="A746" s="2" t="n"/>
@@ -37220,7 +36470,6 @@
       <c r="AR746" s="2" t="n"/>
       <c r="AS746" s="2" t="n"/>
       <c r="AT746" s="2" t="n"/>
-      <c r="AU746" s="2" t="n"/>
     </row>
     <row r="747">
       <c r="A747" s="2" t="n"/>
@@ -37269,7 +36518,6 @@
       <c r="AR747" s="2" t="n"/>
       <c r="AS747" s="2" t="n"/>
       <c r="AT747" s="2" t="n"/>
-      <c r="AU747" s="2" t="n"/>
     </row>
     <row r="748">
       <c r="A748" s="2" t="n"/>
@@ -37318,7 +36566,6 @@
       <c r="AR748" s="2" t="n"/>
       <c r="AS748" s="2" t="n"/>
       <c r="AT748" s="2" t="n"/>
-      <c r="AU748" s="2" t="n"/>
     </row>
     <row r="749">
       <c r="A749" s="2" t="n"/>
@@ -37367,7 +36614,6 @@
       <c r="AR749" s="2" t="n"/>
       <c r="AS749" s="2" t="n"/>
       <c r="AT749" s="2" t="n"/>
-      <c r="AU749" s="2" t="n"/>
     </row>
     <row r="750">
       <c r="A750" s="2" t="n"/>
@@ -37416,7 +36662,6 @@
       <c r="AR750" s="2" t="n"/>
       <c r="AS750" s="2" t="n"/>
       <c r="AT750" s="2" t="n"/>
-      <c r="AU750" s="2" t="n"/>
     </row>
     <row r="751">
       <c r="A751" s="2" t="n"/>
@@ -37465,7 +36710,6 @@
       <c r="AR751" s="2" t="n"/>
       <c r="AS751" s="2" t="n"/>
       <c r="AT751" s="2" t="n"/>
-      <c r="AU751" s="2" t="n"/>
     </row>
     <row r="752">
       <c r="A752" s="2" t="n"/>
@@ -37514,7 +36758,6 @@
       <c r="AR752" s="2" t="n"/>
       <c r="AS752" s="2" t="n"/>
       <c r="AT752" s="2" t="n"/>
-      <c r="AU752" s="2" t="n"/>
     </row>
     <row r="753">
       <c r="A753" s="2" t="n"/>
@@ -37563,7 +36806,6 @@
       <c r="AR753" s="2" t="n"/>
       <c r="AS753" s="2" t="n"/>
       <c r="AT753" s="2" t="n"/>
-      <c r="AU753" s="2" t="n"/>
     </row>
     <row r="754">
       <c r="A754" s="2" t="n"/>
@@ -37612,7 +36854,6 @@
       <c r="AR754" s="2" t="n"/>
       <c r="AS754" s="2" t="n"/>
       <c r="AT754" s="2" t="n"/>
-      <c r="AU754" s="2" t="n"/>
     </row>
     <row r="755">
       <c r="A755" s="2" t="n"/>
@@ -37661,7 +36902,6 @@
       <c r="AR755" s="2" t="n"/>
       <c r="AS755" s="2" t="n"/>
       <c r="AT755" s="2" t="n"/>
-      <c r="AU755" s="2" t="n"/>
     </row>
     <row r="756">
       <c r="A756" s="2" t="n"/>
@@ -37710,7 +36950,6 @@
       <c r="AR756" s="2" t="n"/>
       <c r="AS756" s="2" t="n"/>
       <c r="AT756" s="2" t="n"/>
-      <c r="AU756" s="2" t="n"/>
     </row>
     <row r="757">
       <c r="A757" s="2" t="n"/>
@@ -37759,7 +36998,6 @@
       <c r="AR757" s="2" t="n"/>
       <c r="AS757" s="2" t="n"/>
       <c r="AT757" s="2" t="n"/>
-      <c r="AU757" s="2" t="n"/>
     </row>
     <row r="758">
       <c r="A758" s="2" t="n"/>
@@ -37808,7 +37046,6 @@
       <c r="AR758" s="2" t="n"/>
       <c r="AS758" s="2" t="n"/>
       <c r="AT758" s="2" t="n"/>
-      <c r="AU758" s="2" t="n"/>
     </row>
     <row r="759">
       <c r="A759" s="2" t="n"/>
@@ -37857,7 +37094,6 @@
       <c r="AR759" s="2" t="n"/>
       <c r="AS759" s="2" t="n"/>
       <c r="AT759" s="2" t="n"/>
-      <c r="AU759" s="2" t="n"/>
     </row>
     <row r="760">
       <c r="A760" s="2" t="n"/>
@@ -37906,7 +37142,6 @@
       <c r="AR760" s="2" t="n"/>
       <c r="AS760" s="2" t="n"/>
       <c r="AT760" s="2" t="n"/>
-      <c r="AU760" s="2" t="n"/>
     </row>
     <row r="761">
       <c r="A761" s="2" t="n"/>
@@ -37955,7 +37190,6 @@
       <c r="AR761" s="2" t="n"/>
       <c r="AS761" s="2" t="n"/>
       <c r="AT761" s="2" t="n"/>
-      <c r="AU761" s="2" t="n"/>
     </row>
     <row r="762">
       <c r="A762" s="2" t="n"/>
@@ -38004,7 +37238,6 @@
       <c r="AR762" s="2" t="n"/>
       <c r="AS762" s="2" t="n"/>
       <c r="AT762" s="2" t="n"/>
-      <c r="AU762" s="2" t="n"/>
     </row>
     <row r="763">
       <c r="A763" s="2" t="n"/>
@@ -38053,7 +37286,6 @@
       <c r="AR763" s="2" t="n"/>
       <c r="AS763" s="2" t="n"/>
       <c r="AT763" s="2" t="n"/>
-      <c r="AU763" s="2" t="n"/>
     </row>
     <row r="764">
       <c r="A764" s="2" t="n"/>
@@ -38102,7 +37334,6 @@
       <c r="AR764" s="2" t="n"/>
       <c r="AS764" s="2" t="n"/>
       <c r="AT764" s="2" t="n"/>
-      <c r="AU764" s="2" t="n"/>
     </row>
     <row r="765">
       <c r="A765" s="2" t="n"/>
@@ -38151,7 +37382,6 @@
       <c r="AR765" s="2" t="n"/>
       <c r="AS765" s="2" t="n"/>
       <c r="AT765" s="2" t="n"/>
-      <c r="AU765" s="2" t="n"/>
     </row>
     <row r="766">
       <c r="A766" s="2" t="n"/>
@@ -38200,7 +37430,6 @@
       <c r="AR766" s="2" t="n"/>
       <c r="AS766" s="2" t="n"/>
       <c r="AT766" s="2" t="n"/>
-      <c r="AU766" s="2" t="n"/>
     </row>
     <row r="767">
       <c r="A767" s="2" t="n"/>
@@ -38249,7 +37478,6 @@
       <c r="AR767" s="2" t="n"/>
       <c r="AS767" s="2" t="n"/>
       <c r="AT767" s="2" t="n"/>
-      <c r="AU767" s="2" t="n"/>
     </row>
     <row r="768">
       <c r="A768" s="2" t="n"/>
@@ -38298,7 +37526,6 @@
       <c r="AR768" s="2" t="n"/>
       <c r="AS768" s="2" t="n"/>
       <c r="AT768" s="2" t="n"/>
-      <c r="AU768" s="2" t="n"/>
     </row>
     <row r="769">
       <c r="A769" s="2" t="n"/>
@@ -38347,7 +37574,6 @@
       <c r="AR769" s="2" t="n"/>
       <c r="AS769" s="2" t="n"/>
       <c r="AT769" s="2" t="n"/>
-      <c r="AU769" s="2" t="n"/>
     </row>
     <row r="770">
       <c r="A770" s="2" t="n"/>
@@ -38396,7 +37622,6 @@
       <c r="AR770" s="2" t="n"/>
       <c r="AS770" s="2" t="n"/>
       <c r="AT770" s="2" t="n"/>
-      <c r="AU770" s="2" t="n"/>
     </row>
     <row r="771">
       <c r="A771" s="2" t="n"/>
@@ -38445,7 +37670,6 @@
       <c r="AR771" s="2" t="n"/>
       <c r="AS771" s="2" t="n"/>
       <c r="AT771" s="2" t="n"/>
-      <c r="AU771" s="2" t="n"/>
     </row>
     <row r="772">
       <c r="A772" s="2" t="n"/>
@@ -38494,7 +37718,6 @@
       <c r="AR772" s="2" t="n"/>
       <c r="AS772" s="2" t="n"/>
       <c r="AT772" s="2" t="n"/>
-      <c r="AU772" s="2" t="n"/>
     </row>
     <row r="773">
       <c r="A773" s="2" t="n"/>
@@ -38543,7 +37766,6 @@
       <c r="AR773" s="2" t="n"/>
       <c r="AS773" s="2" t="n"/>
       <c r="AT773" s="2" t="n"/>
-      <c r="AU773" s="2" t="n"/>
     </row>
     <row r="774">
       <c r="A774" s="2" t="n"/>
@@ -38592,7 +37814,6 @@
       <c r="AR774" s="2" t="n"/>
       <c r="AS774" s="2" t="n"/>
       <c r="AT774" s="2" t="n"/>
-      <c r="AU774" s="2" t="n"/>
     </row>
     <row r="775">
       <c r="A775" s="2" t="n"/>
@@ -38641,7 +37862,6 @@
       <c r="AR775" s="2" t="n"/>
       <c r="AS775" s="2" t="n"/>
       <c r="AT775" s="2" t="n"/>
-      <c r="AU775" s="2" t="n"/>
     </row>
     <row r="776">
       <c r="A776" s="2" t="n"/>
@@ -38690,7 +37910,6 @@
       <c r="AR776" s="2" t="n"/>
       <c r="AS776" s="2" t="n"/>
       <c r="AT776" s="2" t="n"/>
-      <c r="AU776" s="2" t="n"/>
     </row>
     <row r="777">
       <c r="A777" s="2" t="n"/>
@@ -38739,7 +37958,6 @@
       <c r="AR777" s="2" t="n"/>
       <c r="AS777" s="2" t="n"/>
       <c r="AT777" s="2" t="n"/>
-      <c r="AU777" s="2" t="n"/>
     </row>
     <row r="778">
       <c r="A778" s="2" t="n"/>
@@ -38788,7 +38006,6 @@
       <c r="AR778" s="2" t="n"/>
       <c r="AS778" s="2" t="n"/>
       <c r="AT778" s="2" t="n"/>
-      <c r="AU778" s="2" t="n"/>
     </row>
     <row r="779">
       <c r="A779" s="2" t="n"/>
@@ -38837,7 +38054,6 @@
       <c r="AR779" s="2" t="n"/>
       <c r="AS779" s="2" t="n"/>
       <c r="AT779" s="2" t="n"/>
-      <c r="AU779" s="2" t="n"/>
     </row>
     <row r="780">
       <c r="A780" s="2" t="n"/>
@@ -38886,7 +38102,6 @@
       <c r="AR780" s="2" t="n"/>
       <c r="AS780" s="2" t="n"/>
       <c r="AT780" s="2" t="n"/>
-      <c r="AU780" s="2" t="n"/>
     </row>
     <row r="781">
       <c r="A781" s="2" t="n"/>
@@ -38935,7 +38150,6 @@
       <c r="AR781" s="2" t="n"/>
       <c r="AS781" s="2" t="n"/>
       <c r="AT781" s="2" t="n"/>
-      <c r="AU781" s="2" t="n"/>
     </row>
     <row r="782">
       <c r="A782" s="2" t="n"/>
@@ -38984,7 +38198,6 @@
       <c r="AR782" s="2" t="n"/>
       <c r="AS782" s="2" t="n"/>
       <c r="AT782" s="2" t="n"/>
-      <c r="AU782" s="2" t="n"/>
     </row>
     <row r="783">
       <c r="A783" s="2" t="n"/>
@@ -39033,7 +38246,6 @@
       <c r="AR783" s="2" t="n"/>
       <c r="AS783" s="2" t="n"/>
       <c r="AT783" s="2" t="n"/>
-      <c r="AU783" s="2" t="n"/>
     </row>
     <row r="784">
       <c r="A784" s="2" t="n"/>
@@ -39082,7 +38294,6 @@
       <c r="AR784" s="2" t="n"/>
       <c r="AS784" s="2" t="n"/>
       <c r="AT784" s="2" t="n"/>
-      <c r="AU784" s="2" t="n"/>
     </row>
     <row r="785">
       <c r="A785" s="2" t="n"/>
@@ -39131,7 +38342,6 @@
       <c r="AR785" s="2" t="n"/>
       <c r="AS785" s="2" t="n"/>
       <c r="AT785" s="2" t="n"/>
-      <c r="AU785" s="2" t="n"/>
     </row>
     <row r="786">
       <c r="A786" s="2" t="n"/>
@@ -39180,7 +38390,6 @@
       <c r="AR786" s="2" t="n"/>
       <c r="AS786" s="2" t="n"/>
       <c r="AT786" s="2" t="n"/>
-      <c r="AU786" s="2" t="n"/>
     </row>
     <row r="787">
       <c r="A787" s="2" t="n"/>
@@ -39229,7 +38438,6 @@
       <c r="AR787" s="2" t="n"/>
       <c r="AS787" s="2" t="n"/>
       <c r="AT787" s="2" t="n"/>
-      <c r="AU787" s="2" t="n"/>
     </row>
     <row r="788">
       <c r="A788" s="2" t="n"/>
@@ -39278,7 +38486,6 @@
       <c r="AR788" s="2" t="n"/>
       <c r="AS788" s="2" t="n"/>
       <c r="AT788" s="2" t="n"/>
-      <c r="AU788" s="2" t="n"/>
     </row>
     <row r="789">
       <c r="A789" s="2" t="n"/>
@@ -39327,7 +38534,6 @@
       <c r="AR789" s="2" t="n"/>
       <c r="AS789" s="2" t="n"/>
       <c r="AT789" s="2" t="n"/>
-      <c r="AU789" s="2" t="n"/>
     </row>
     <row r="790">
       <c r="A790" s="2" t="n"/>
@@ -39376,7 +38582,6 @@
       <c r="AR790" s="2" t="n"/>
       <c r="AS790" s="2" t="n"/>
       <c r="AT790" s="2" t="n"/>
-      <c r="AU790" s="2" t="n"/>
     </row>
     <row r="791">
       <c r="A791" s="2" t="n"/>
@@ -39425,7 +38630,6 @@
       <c r="AR791" s="2" t="n"/>
       <c r="AS791" s="2" t="n"/>
       <c r="AT791" s="2" t="n"/>
-      <c r="AU791" s="2" t="n"/>
     </row>
     <row r="792">
       <c r="A792" s="2" t="n"/>
@@ -39474,7 +38678,6 @@
       <c r="AR792" s="2" t="n"/>
       <c r="AS792" s="2" t="n"/>
       <c r="AT792" s="2" t="n"/>
-      <c r="AU792" s="2" t="n"/>
     </row>
     <row r="793">
       <c r="A793" s="2" t="n"/>
@@ -39523,7 +38726,6 @@
       <c r="AR793" s="2" t="n"/>
       <c r="AS793" s="2" t="n"/>
       <c r="AT793" s="2" t="n"/>
-      <c r="AU793" s="2" t="n"/>
     </row>
     <row r="794">
       <c r="A794" s="2" t="n"/>
@@ -39572,7 +38774,6 @@
       <c r="AR794" s="2" t="n"/>
       <c r="AS794" s="2" t="n"/>
       <c r="AT794" s="2" t="n"/>
-      <c r="AU794" s="2" t="n"/>
     </row>
     <row r="795">
       <c r="A795" s="2" t="n"/>
@@ -39621,7 +38822,6 @@
       <c r="AR795" s="2" t="n"/>
       <c r="AS795" s="2" t="n"/>
       <c r="AT795" s="2" t="n"/>
-      <c r="AU795" s="2" t="n"/>
     </row>
     <row r="796">
       <c r="A796" s="2" t="n"/>
@@ -39670,7 +38870,6 @@
       <c r="AR796" s="2" t="n"/>
       <c r="AS796" s="2" t="n"/>
       <c r="AT796" s="2" t="n"/>
-      <c r="AU796" s="2" t="n"/>
     </row>
     <row r="797">
       <c r="A797" s="2" t="n"/>
@@ -39719,7 +38918,6 @@
       <c r="AR797" s="2" t="n"/>
       <c r="AS797" s="2" t="n"/>
       <c r="AT797" s="2" t="n"/>
-      <c r="AU797" s="2" t="n"/>
     </row>
     <row r="798">
       <c r="A798" s="2" t="n"/>
@@ -39768,7 +38966,6 @@
       <c r="AR798" s="2" t="n"/>
       <c r="AS798" s="2" t="n"/>
       <c r="AT798" s="2" t="n"/>
-      <c r="AU798" s="2" t="n"/>
     </row>
     <row r="799">
       <c r="A799" s="2" t="n"/>
@@ -39817,7 +39014,6 @@
       <c r="AR799" s="2" t="n"/>
       <c r="AS799" s="2" t="n"/>
       <c r="AT799" s="2" t="n"/>
-      <c r="AU799" s="2" t="n"/>
     </row>
     <row r="800">
       <c r="A800" s="2" t="n"/>
@@ -39866,7 +39062,6 @@
       <c r="AR800" s="2" t="n"/>
       <c r="AS800" s="2" t="n"/>
       <c r="AT800" s="2" t="n"/>
-      <c r="AU800" s="2" t="n"/>
     </row>
     <row r="801">
       <c r="A801" s="2" t="n"/>
@@ -39915,7 +39110,6 @@
       <c r="AR801" s="2" t="n"/>
       <c r="AS801" s="2" t="n"/>
       <c r="AT801" s="2" t="n"/>
-      <c r="AU801" s="2" t="n"/>
     </row>
     <row r="802">
       <c r="A802" s="2" t="n"/>
@@ -39964,7 +39158,6 @@
       <c r="AR802" s="2" t="n"/>
       <c r="AS802" s="2" t="n"/>
       <c r="AT802" s="2" t="n"/>
-      <c r="AU802" s="2" t="n"/>
     </row>
     <row r="803">
       <c r="A803" s="2" t="n"/>
@@ -40013,7 +39206,6 @@
       <c r="AR803" s="2" t="n"/>
       <c r="AS803" s="2" t="n"/>
       <c r="AT803" s="2" t="n"/>
-      <c r="AU803" s="2" t="n"/>
     </row>
     <row r="804">
       <c r="A804" s="2" t="n"/>
@@ -40062,7 +39254,6 @@
       <c r="AR804" s="2" t="n"/>
       <c r="AS804" s="2" t="n"/>
       <c r="AT804" s="2" t="n"/>
-      <c r="AU804" s="2" t="n"/>
     </row>
     <row r="805">
       <c r="A805" s="2" t="n"/>
@@ -40111,7 +39302,6 @@
       <c r="AR805" s="2" t="n"/>
       <c r="AS805" s="2" t="n"/>
       <c r="AT805" s="2" t="n"/>
-      <c r="AU805" s="2" t="n"/>
     </row>
     <row r="806">
       <c r="A806" s="2" t="n"/>
@@ -40160,7 +39350,6 @@
       <c r="AR806" s="2" t="n"/>
       <c r="AS806" s="2" t="n"/>
       <c r="AT806" s="2" t="n"/>
-      <c r="AU806" s="2" t="n"/>
     </row>
     <row r="807">
       <c r="A807" s="2" t="n"/>
@@ -40209,7 +39398,6 @@
       <c r="AR807" s="2" t="n"/>
       <c r="AS807" s="2" t="n"/>
       <c r="AT807" s="2" t="n"/>
-      <c r="AU807" s="2" t="n"/>
     </row>
     <row r="808">
       <c r="A808" s="2" t="n"/>
@@ -40258,7 +39446,6 @@
       <c r="AR808" s="2" t="n"/>
       <c r="AS808" s="2" t="n"/>
       <c r="AT808" s="2" t="n"/>
-      <c r="AU808" s="2" t="n"/>
     </row>
     <row r="809">
       <c r="A809" s="2" t="n"/>
@@ -40307,7 +39494,6 @@
       <c r="AR809" s="2" t="n"/>
       <c r="AS809" s="2" t="n"/>
       <c r="AT809" s="2" t="n"/>
-      <c r="AU809" s="2" t="n"/>
     </row>
     <row r="810">
       <c r="A810" s="2" t="n"/>
@@ -40356,7 +39542,6 @@
       <c r="AR810" s="2" t="n"/>
       <c r="AS810" s="2" t="n"/>
       <c r="AT810" s="2" t="n"/>
-      <c r="AU810" s="2" t="n"/>
     </row>
     <row r="811">
       <c r="A811" s="2" t="n"/>
@@ -40405,7 +39590,6 @@
       <c r="AR811" s="2" t="n"/>
       <c r="AS811" s="2" t="n"/>
       <c r="AT811" s="2" t="n"/>
-      <c r="AU811" s="2" t="n"/>
     </row>
     <row r="812">
       <c r="A812" s="2" t="n"/>
@@ -40454,7 +39638,6 @@
       <c r="AR812" s="2" t="n"/>
       <c r="AS812" s="2" t="n"/>
       <c r="AT812" s="2" t="n"/>
-      <c r="AU812" s="2" t="n"/>
     </row>
     <row r="813">
       <c r="A813" s="2" t="n"/>
@@ -40503,7 +39686,6 @@
       <c r="AR813" s="2" t="n"/>
       <c r="AS813" s="2" t="n"/>
       <c r="AT813" s="2" t="n"/>
-      <c r="AU813" s="2" t="n"/>
     </row>
     <row r="814">
       <c r="A814" s="2" t="n"/>
@@ -40552,7 +39734,6 @@
       <c r="AR814" s="2" t="n"/>
       <c r="AS814" s="2" t="n"/>
       <c r="AT814" s="2" t="n"/>
-      <c r="AU814" s="2" t="n"/>
     </row>
     <row r="815">
       <c r="A815" s="2" t="n"/>
@@ -40601,7 +39782,6 @@
       <c r="AR815" s="2" t="n"/>
       <c r="AS815" s="2" t="n"/>
       <c r="AT815" s="2" t="n"/>
-      <c r="AU815" s="2" t="n"/>
     </row>
     <row r="816">
       <c r="A816" s="2" t="n"/>
@@ -40650,7 +39830,6 @@
       <c r="AR816" s="2" t="n"/>
       <c r="AS816" s="2" t="n"/>
       <c r="AT816" s="2" t="n"/>
-      <c r="AU816" s="2" t="n"/>
     </row>
     <row r="817">
       <c r="A817" s="2" t="n"/>
@@ -40699,7 +39878,6 @@
       <c r="AR817" s="2" t="n"/>
       <c r="AS817" s="2" t="n"/>
       <c r="AT817" s="2" t="n"/>
-      <c r="AU817" s="2" t="n"/>
     </row>
     <row r="818">
       <c r="A818" s="2" t="n"/>
@@ -40748,7 +39926,6 @@
       <c r="AR818" s="2" t="n"/>
       <c r="AS818" s="2" t="n"/>
       <c r="AT818" s="2" t="n"/>
-      <c r="AU818" s="2" t="n"/>
     </row>
     <row r="819">
       <c r="A819" s="2" t="n"/>
@@ -40797,7 +39974,6 @@
       <c r="AR819" s="2" t="n"/>
       <c r="AS819" s="2" t="n"/>
       <c r="AT819" s="2" t="n"/>
-      <c r="AU819" s="2" t="n"/>
     </row>
     <row r="820">
       <c r="A820" s="2" t="n"/>
@@ -40846,7 +40022,6 @@
       <c r="AR820" s="2" t="n"/>
       <c r="AS820" s="2" t="n"/>
       <c r="AT820" s="2" t="n"/>
-      <c r="AU820" s="2" t="n"/>
     </row>
     <row r="821">
       <c r="A821" s="2" t="n"/>
@@ -40895,7 +40070,6 @@
       <c r="AR821" s="2" t="n"/>
       <c r="AS821" s="2" t="n"/>
       <c r="AT821" s="2" t="n"/>
-      <c r="AU821" s="2" t="n"/>
     </row>
     <row r="822">
       <c r="A822" s="2" t="n"/>
@@ -40944,7 +40118,6 @@
       <c r="AR822" s="2" t="n"/>
       <c r="AS822" s="2" t="n"/>
       <c r="AT822" s="2" t="n"/>
-      <c r="AU822" s="2" t="n"/>
     </row>
     <row r="823">
       <c r="A823" s="2" t="n"/>
@@ -40993,7 +40166,6 @@
       <c r="AR823" s="2" t="n"/>
       <c r="AS823" s="2" t="n"/>
       <c r="AT823" s="2" t="n"/>
-      <c r="AU823" s="2" t="n"/>
     </row>
     <row r="824">
       <c r="A824" s="2" t="n"/>
@@ -41042,7 +40214,6 @@
       <c r="AR824" s="2" t="n"/>
       <c r="AS824" s="2" t="n"/>
       <c r="AT824" s="2" t="n"/>
-      <c r="AU824" s="2" t="n"/>
     </row>
     <row r="825">
       <c r="A825" s="2" t="n"/>
@@ -41091,7 +40262,6 @@
       <c r="AR825" s="2" t="n"/>
       <c r="AS825" s="2" t="n"/>
       <c r="AT825" s="2" t="n"/>
-      <c r="AU825" s="2" t="n"/>
     </row>
     <row r="826">
       <c r="A826" s="2" t="n"/>
@@ -41140,7 +40310,6 @@
       <c r="AR826" s="2" t="n"/>
       <c r="AS826" s="2" t="n"/>
       <c r="AT826" s="2" t="n"/>
-      <c r="AU826" s="2" t="n"/>
     </row>
     <row r="827">
       <c r="A827" s="2" t="n"/>
@@ -41189,7 +40358,6 @@
       <c r="AR827" s="2" t="n"/>
       <c r="AS827" s="2" t="n"/>
       <c r="AT827" s="2" t="n"/>
-      <c r="AU827" s="2" t="n"/>
     </row>
     <row r="828">
       <c r="A828" s="2" t="n"/>
@@ -41238,7 +40406,6 @@
       <c r="AR828" s="2" t="n"/>
       <c r="AS828" s="2" t="n"/>
       <c r="AT828" s="2" t="n"/>
-      <c r="AU828" s="2" t="n"/>
     </row>
     <row r="829">
       <c r="A829" s="2" t="n"/>
@@ -41287,7 +40454,6 @@
       <c r="AR829" s="2" t="n"/>
       <c r="AS829" s="2" t="n"/>
       <c r="AT829" s="2" t="n"/>
-      <c r="AU829" s="2" t="n"/>
     </row>
     <row r="830">
       <c r="A830" s="2" t="n"/>
@@ -41336,7 +40502,6 @@
       <c r="AR830" s="2" t="n"/>
       <c r="AS830" s="2" t="n"/>
       <c r="AT830" s="2" t="n"/>
-      <c r="AU830" s="2" t="n"/>
     </row>
     <row r="831">
       <c r="A831" s="2" t="n"/>
@@ -41385,7 +40550,6 @@
       <c r="AR831" s="2" t="n"/>
       <c r="AS831" s="2" t="n"/>
       <c r="AT831" s="2" t="n"/>
-      <c r="AU831" s="2" t="n"/>
     </row>
     <row r="832">
       <c r="A832" s="2" t="n"/>
@@ -41434,7 +40598,6 @@
       <c r="AR832" s="2" t="n"/>
       <c r="AS832" s="2" t="n"/>
       <c r="AT832" s="2" t="n"/>
-      <c r="AU832" s="2" t="n"/>
     </row>
     <row r="833">
       <c r="A833" s="2" t="n"/>
@@ -41483,7 +40646,6 @@
       <c r="AR833" s="2" t="n"/>
       <c r="AS833" s="2" t="n"/>
       <c r="AT833" s="2" t="n"/>
-      <c r="AU833" s="2" t="n"/>
     </row>
     <row r="834">
       <c r="A834" s="2" t="n"/>
@@ -41532,7 +40694,6 @@
       <c r="AR834" s="2" t="n"/>
       <c r="AS834" s="2" t="n"/>
       <c r="AT834" s="2" t="n"/>
-      <c r="AU834" s="2" t="n"/>
     </row>
     <row r="835">
       <c r="A835" s="2" t="n"/>
@@ -41581,7 +40742,6 @@
       <c r="AR835" s="2" t="n"/>
       <c r="AS835" s="2" t="n"/>
       <c r="AT835" s="2" t="n"/>
-      <c r="AU835" s="2" t="n"/>
     </row>
     <row r="836">
       <c r="A836" s="2" t="n"/>
@@ -41630,7 +40790,6 @@
       <c r="AR836" s="2" t="n"/>
       <c r="AS836" s="2" t="n"/>
       <c r="AT836" s="2" t="n"/>
-      <c r="AU836" s="2" t="n"/>
     </row>
     <row r="837">
       <c r="A837" s="2" t="n"/>
@@ -41679,7 +40838,6 @@
       <c r="AR837" s="2" t="n"/>
       <c r="AS837" s="2" t="n"/>
       <c r="AT837" s="2" t="n"/>
-      <c r="AU837" s="2" t="n"/>
     </row>
     <row r="838">
       <c r="A838" s="2" t="n"/>
@@ -41728,7 +40886,6 @@
       <c r="AR838" s="2" t="n"/>
       <c r="AS838" s="2" t="n"/>
       <c r="AT838" s="2" t="n"/>
-      <c r="AU838" s="2" t="n"/>
     </row>
     <row r="839">
       <c r="A839" s="2" t="n"/>
@@ -41777,7 +40934,6 @@
       <c r="AR839" s="2" t="n"/>
       <c r="AS839" s="2" t="n"/>
       <c r="AT839" s="2" t="n"/>
-      <c r="AU839" s="2" t="n"/>
     </row>
     <row r="840">
       <c r="A840" s="2" t="n"/>
@@ -41826,7 +40982,6 @@
       <c r="AR840" s="2" t="n"/>
       <c r="AS840" s="2" t="n"/>
       <c r="AT840" s="2" t="n"/>
-      <c r="AU840" s="2" t="n"/>
     </row>
     <row r="841">
       <c r="A841" s="2" t="n"/>
@@ -41875,7 +41030,6 @@
       <c r="AR841" s="2" t="n"/>
       <c r="AS841" s="2" t="n"/>
       <c r="AT841" s="2" t="n"/>
-      <c r="AU841" s="2" t="n"/>
     </row>
     <row r="842">
       <c r="A842" s="2" t="n"/>
@@ -41924,7 +41078,6 @@
       <c r="AR842" s="2" t="n"/>
       <c r="AS842" s="2" t="n"/>
       <c r="AT842" s="2" t="n"/>
-      <c r="AU842" s="2" t="n"/>
     </row>
     <row r="843">
       <c r="A843" s="2" t="n"/>
@@ -41973,7 +41126,6 @@
       <c r="AR843" s="2" t="n"/>
       <c r="AS843" s="2" t="n"/>
       <c r="AT843" s="2" t="n"/>
-      <c r="AU843" s="2" t="n"/>
     </row>
     <row r="844">
       <c r="A844" s="2" t="n"/>
@@ -42022,7 +41174,6 @@
       <c r="AR844" s="2" t="n"/>
       <c r="AS844" s="2" t="n"/>
       <c r="AT844" s="2" t="n"/>
-      <c r="AU844" s="2" t="n"/>
     </row>
     <row r="845">
       <c r="A845" s="2" t="n"/>
@@ -42071,7 +41222,6 @@
       <c r="AR845" s="2" t="n"/>
       <c r="AS845" s="2" t="n"/>
       <c r="AT845" s="2" t="n"/>
-      <c r="AU845" s="2" t="n"/>
     </row>
     <row r="846">
       <c r="A846" s="2" t="n"/>
@@ -42120,7 +41270,6 @@
       <c r="AR846" s="2" t="n"/>
       <c r="AS846" s="2" t="n"/>
       <c r="AT846" s="2" t="n"/>
-      <c r="AU846" s="2" t="n"/>
     </row>
     <row r="847">
       <c r="A847" s="2" t="n"/>
@@ -42169,7 +41318,6 @@
       <c r="AR847" s="2" t="n"/>
       <c r="AS847" s="2" t="n"/>
       <c r="AT847" s="2" t="n"/>
-      <c r="AU847" s="2" t="n"/>
     </row>
     <row r="848">
       <c r="A848" s="2" t="n"/>
@@ -42218,7 +41366,6 @@
       <c r="AR848" s="2" t="n"/>
       <c r="AS848" s="2" t="n"/>
       <c r="AT848" s="2" t="n"/>
-      <c r="AU848" s="2" t="n"/>
     </row>
     <row r="849">
       <c r="A849" s="2" t="n"/>
@@ -42267,7 +41414,6 @@
       <c r="AR849" s="2" t="n"/>
       <c r="AS849" s="2" t="n"/>
       <c r="AT849" s="2" t="n"/>
-      <c r="AU849" s="2" t="n"/>
     </row>
     <row r="850">
       <c r="A850" s="2" t="n"/>
@@ -42316,7 +41462,6 @@
       <c r="AR850" s="2" t="n"/>
       <c r="AS850" s="2" t="n"/>
       <c r="AT850" s="2" t="n"/>
-      <c r="AU850" s="2" t="n"/>
     </row>
     <row r="851">
       <c r="A851" s="2" t="n"/>
@@ -42365,7 +41510,6 @@
       <c r="AR851" s="2" t="n"/>
       <c r="AS851" s="2" t="n"/>
       <c r="AT851" s="2" t="n"/>
-      <c r="AU851" s="2" t="n"/>
     </row>
     <row r="852">
       <c r="A852" s="2" t="n"/>
@@ -42414,7 +41558,6 @@
       <c r="AR852" s="2" t="n"/>
       <c r="AS852" s="2" t="n"/>
       <c r="AT852" s="2" t="n"/>
-      <c r="AU852" s="2" t="n"/>
     </row>
     <row r="853">
       <c r="A853" s="2" t="n"/>
@@ -42463,7 +41606,6 @@
       <c r="AR853" s="2" t="n"/>
       <c r="AS853" s="2" t="n"/>
       <c r="AT853" s="2" t="n"/>
-      <c r="AU853" s="2" t="n"/>
     </row>
     <row r="854">
       <c r="A854" s="2" t="n"/>
@@ -42512,7 +41654,6 @@
       <c r="AR854" s="2" t="n"/>
       <c r="AS854" s="2" t="n"/>
       <c r="AT854" s="2" t="n"/>
-      <c r="AU854" s="2" t="n"/>
     </row>
     <row r="855">
       <c r="A855" s="2" t="n"/>
@@ -42561,7 +41702,6 @@
       <c r="AR855" s="2" t="n"/>
       <c r="AS855" s="2" t="n"/>
       <c r="AT855" s="2" t="n"/>
-      <c r="AU855" s="2" t="n"/>
     </row>
     <row r="856">
       <c r="A856" s="2" t="n"/>
@@ -42610,7 +41750,6 @@
       <c r="AR856" s="2" t="n"/>
       <c r="AS856" s="2" t="n"/>
       <c r="AT856" s="2" t="n"/>
-      <c r="AU856" s="2" t="n"/>
     </row>
     <row r="857">
       <c r="A857" s="2" t="n"/>
@@ -42659,7 +41798,6 @@
       <c r="AR857" s="2" t="n"/>
       <c r="AS857" s="2" t="n"/>
       <c r="AT857" s="2" t="n"/>
-      <c r="AU857" s="2" t="n"/>
     </row>
     <row r="858">
       <c r="A858" s="2" t="n"/>
@@ -42708,7 +41846,6 @@
       <c r="AR858" s="2" t="n"/>
       <c r="AS858" s="2" t="n"/>
       <c r="AT858" s="2" t="n"/>
-      <c r="AU858" s="2" t="n"/>
     </row>
     <row r="859">
       <c r="A859" s="2" t="n"/>
@@ -42757,7 +41894,6 @@
       <c r="AR859" s="2" t="n"/>
       <c r="AS859" s="2" t="n"/>
       <c r="AT859" s="2" t="n"/>
-      <c r="AU859" s="2" t="n"/>
     </row>
     <row r="860">
       <c r="A860" s="2" t="n"/>
@@ -42806,7 +41942,6 @@
       <c r="AR860" s="2" t="n"/>
       <c r="AS860" s="2" t="n"/>
       <c r="AT860" s="2" t="n"/>
-      <c r="AU860" s="2" t="n"/>
     </row>
     <row r="861">
       <c r="A861" s="2" t="n"/>
@@ -42855,7 +41990,6 @@
       <c r="AR861" s="2" t="n"/>
       <c r="AS861" s="2" t="n"/>
       <c r="AT861" s="2" t="n"/>
-      <c r="AU861" s="2" t="n"/>
     </row>
     <row r="862">
       <c r="A862" s="2" t="n"/>
@@ -42904,7 +42038,6 @@
       <c r="AR862" s="2" t="n"/>
       <c r="AS862" s="2" t="n"/>
       <c r="AT862" s="2" t="n"/>
-      <c r="AU862" s="2" t="n"/>
     </row>
     <row r="863">
       <c r="A863" s="2" t="n"/>
@@ -42953,7 +42086,6 @@
       <c r="AR863" s="2" t="n"/>
       <c r="AS863" s="2" t="n"/>
       <c r="AT863" s="2" t="n"/>
-      <c r="AU863" s="2" t="n"/>
     </row>
     <row r="864">
       <c r="A864" s="2" t="n"/>
@@ -43002,7 +42134,6 @@
       <c r="AR864" s="2" t="n"/>
       <c r="AS864" s="2" t="n"/>
       <c r="AT864" s="2" t="n"/>
-      <c r="AU864" s="2" t="n"/>
     </row>
     <row r="865">
       <c r="A865" s="2" t="n"/>
@@ -43051,7 +42182,6 @@
       <c r="AR865" s="2" t="n"/>
       <c r="AS865" s="2" t="n"/>
       <c r="AT865" s="2" t="n"/>
-      <c r="AU865" s="2" t="n"/>
     </row>
     <row r="866">
       <c r="A866" s="2" t="n"/>
@@ -43100,7 +42230,6 @@
       <c r="AR866" s="2" t="n"/>
       <c r="AS866" s="2" t="n"/>
       <c r="AT866" s="2" t="n"/>
-      <c r="AU866" s="2" t="n"/>
     </row>
     <row r="867">
       <c r="A867" s="2" t="n"/>
@@ -43149,7 +42278,6 @@
       <c r="AR867" s="2" t="n"/>
       <c r="AS867" s="2" t="n"/>
       <c r="AT867" s="2" t="n"/>
-      <c r="AU867" s="2" t="n"/>
     </row>
     <row r="868">
       <c r="A868" s="2" t="n"/>
@@ -43198,7 +42326,6 @@
       <c r="AR868" s="2" t="n"/>
       <c r="AS868" s="2" t="n"/>
       <c r="AT868" s="2" t="n"/>
-      <c r="AU868" s="2" t="n"/>
     </row>
     <row r="869">
       <c r="A869" s="2" t="n"/>
@@ -43247,7 +42374,6 @@
       <c r="AR869" s="2" t="n"/>
       <c r="AS869" s="2" t="n"/>
       <c r="AT869" s="2" t="n"/>
-      <c r="AU869" s="2" t="n"/>
     </row>
     <row r="870">
       <c r="A870" s="2" t="n"/>
@@ -43296,7 +42422,6 @@
       <c r="AR870" s="2" t="n"/>
       <c r="AS870" s="2" t="n"/>
       <c r="AT870" s="2" t="n"/>
-      <c r="AU870" s="2" t="n"/>
     </row>
     <row r="871">
       <c r="A871" s="2" t="n"/>
@@ -43345,7 +42470,6 @@
       <c r="AR871" s="2" t="n"/>
       <c r="AS871" s="2" t="n"/>
       <c r="AT871" s="2" t="n"/>
-      <c r="AU871" s="2" t="n"/>
     </row>
     <row r="872">
       <c r="A872" s="2" t="n"/>
@@ -43394,7 +42518,6 @@
       <c r="AR872" s="2" t="n"/>
       <c r="AS872" s="2" t="n"/>
       <c r="AT872" s="2" t="n"/>
-      <c r="AU872" s="2" t="n"/>
     </row>
     <row r="873">
       <c r="A873" s="2" t="n"/>
@@ -43443,7 +42566,6 @@
       <c r="AR873" s="2" t="n"/>
       <c r="AS873" s="2" t="n"/>
       <c r="AT873" s="2" t="n"/>
-      <c r="AU873" s="2" t="n"/>
     </row>
     <row r="874">
       <c r="A874" s="2" t="n"/>
@@ -43492,7 +42614,6 @@
       <c r="AR874" s="2" t="n"/>
       <c r="AS874" s="2" t="n"/>
       <c r="AT874" s="2" t="n"/>
-      <c r="AU874" s="2" t="n"/>
     </row>
     <row r="875">
       <c r="A875" s="2" t="n"/>
@@ -43541,7 +42662,6 @@
       <c r="AR875" s="2" t="n"/>
       <c r="AS875" s="2" t="n"/>
       <c r="AT875" s="2" t="n"/>
-      <c r="AU875" s="2" t="n"/>
     </row>
     <row r="876">
       <c r="A876" s="2" t="n"/>
@@ -43590,7 +42710,6 @@
       <c r="AR876" s="2" t="n"/>
       <c r="AS876" s="2" t="n"/>
       <c r="AT876" s="2" t="n"/>
-      <c r="AU876" s="2" t="n"/>
     </row>
     <row r="877">
       <c r="A877" s="2" t="n"/>
@@ -43639,7 +42758,6 @@
       <c r="AR877" s="2" t="n"/>
       <c r="AS877" s="2" t="n"/>
       <c r="AT877" s="2" t="n"/>
-      <c r="AU877" s="2" t="n"/>
     </row>
     <row r="878">
       <c r="A878" s="2" t="n"/>
@@ -43688,7 +42806,6 @@
       <c r="AR878" s="2" t="n"/>
       <c r="AS878" s="2" t="n"/>
       <c r="AT878" s="2" t="n"/>
-      <c r="AU878" s="2" t="n"/>
     </row>
     <row r="879">
       <c r="A879" s="2" t="n"/>
@@ -43737,7 +42854,6 @@
       <c r="AR879" s="2" t="n"/>
       <c r="AS879" s="2" t="n"/>
       <c r="AT879" s="2" t="n"/>
-      <c r="AU879" s="2" t="n"/>
     </row>
     <row r="880">
       <c r="A880" s="2" t="n"/>
@@ -43786,7 +42902,6 @@
       <c r="AR880" s="2" t="n"/>
       <c r="AS880" s="2" t="n"/>
       <c r="AT880" s="2" t="n"/>
-      <c r="AU880" s="2" t="n"/>
     </row>
     <row r="881">
       <c r="A881" s="2" t="n"/>
@@ -43835,7 +42950,6 @@
       <c r="AR881" s="2" t="n"/>
       <c r="AS881" s="2" t="n"/>
       <c r="AT881" s="2" t="n"/>
-      <c r="AU881" s="2" t="n"/>
     </row>
     <row r="882">
       <c r="A882" s="2" t="n"/>
@@ -43884,7 +42998,6 @@
       <c r="AR882" s="2" t="n"/>
       <c r="AS882" s="2" t="n"/>
       <c r="AT882" s="2" t="n"/>
-      <c r="AU882" s="2" t="n"/>
     </row>
     <row r="883">
       <c r="A883" s="2" t="n"/>
@@ -43933,7 +43046,6 @@
       <c r="AR883" s="2" t="n"/>
       <c r="AS883" s="2" t="n"/>
       <c r="AT883" s="2" t="n"/>
-      <c r="AU883" s="2" t="n"/>
     </row>
     <row r="884">
       <c r="A884" s="2" t="n"/>
@@ -43982,7 +43094,6 @@
       <c r="AR884" s="2" t="n"/>
       <c r="AS884" s="2" t="n"/>
       <c r="AT884" s="2" t="n"/>
-      <c r="AU884" s="2" t="n"/>
     </row>
     <row r="885">
       <c r="A885" s="2" t="n"/>
@@ -44031,7 +43142,6 @@
       <c r="AR885" s="2" t="n"/>
       <c r="AS885" s="2" t="n"/>
       <c r="AT885" s="2" t="n"/>
-      <c r="AU885" s="2" t="n"/>
     </row>
     <row r="886">
       <c r="A886" s="2" t="n"/>
@@ -44080,7 +43190,6 @@
       <c r="AR886" s="2" t="n"/>
       <c r="AS886" s="2" t="n"/>
       <c r="AT886" s="2" t="n"/>
-      <c r="AU886" s="2" t="n"/>
     </row>
     <row r="887">
       <c r="A887" s="2" t="n"/>
@@ -44129,7 +43238,6 @@
       <c r="AR887" s="2" t="n"/>
       <c r="AS887" s="2" t="n"/>
       <c r="AT887" s="2" t="n"/>
-      <c r="AU887" s="2" t="n"/>
     </row>
     <row r="888">
       <c r="A888" s="2" t="n"/>
@@ -44178,7 +43286,6 @@
       <c r="AR888" s="2" t="n"/>
       <c r="AS888" s="2" t="n"/>
       <c r="AT888" s="2" t="n"/>
-      <c r="AU888" s="2" t="n"/>
     </row>
     <row r="889">
       <c r="A889" s="2" t="n"/>
@@ -44227,7 +43334,6 @@
       <c r="AR889" s="2" t="n"/>
       <c r="AS889" s="2" t="n"/>
       <c r="AT889" s="2" t="n"/>
-      <c r="AU889" s="2" t="n"/>
     </row>
     <row r="890">
       <c r="A890" s="2" t="n"/>
@@ -44276,7 +43382,6 @@
       <c r="AR890" s="2" t="n"/>
       <c r="AS890" s="2" t="n"/>
       <c r="AT890" s="2" t="n"/>
-      <c r="AU890" s="2" t="n"/>
     </row>
     <row r="891">
       <c r="A891" s="2" t="n"/>
@@ -44325,7 +43430,6 @@
       <c r="AR891" s="2" t="n"/>
       <c r="AS891" s="2" t="n"/>
       <c r="AT891" s="2" t="n"/>
-      <c r="AU891" s="2" t="n"/>
     </row>
     <row r="892">
       <c r="A892" s="2" t="n"/>
@@ -44374,7 +43478,6 @@
       <c r="AR892" s="2" t="n"/>
       <c r="AS892" s="2" t="n"/>
       <c r="AT892" s="2" t="n"/>
-      <c r="AU892" s="2" t="n"/>
     </row>
     <row r="893">
       <c r="A893" s="2" t="n"/>
@@ -44423,7 +43526,6 @@
       <c r="AR893" s="2" t="n"/>
       <c r="AS893" s="2" t="n"/>
       <c r="AT893" s="2" t="n"/>
-      <c r="AU893" s="2" t="n"/>
     </row>
     <row r="894">
       <c r="A894" s="2" t="n"/>
@@ -44472,7 +43574,6 @@
       <c r="AR894" s="2" t="n"/>
       <c r="AS894" s="2" t="n"/>
       <c r="AT894" s="2" t="n"/>
-      <c r="AU894" s="2" t="n"/>
     </row>
     <row r="895">
       <c r="A895" s="2" t="n"/>
@@ -44521,7 +43622,6 @@
       <c r="AR895" s="2" t="n"/>
       <c r="AS895" s="2" t="n"/>
       <c r="AT895" s="2" t="n"/>
-      <c r="AU895" s="2" t="n"/>
     </row>
     <row r="896">
       <c r="A896" s="2" t="n"/>
@@ -44570,7 +43670,6 @@
       <c r="AR896" s="2" t="n"/>
       <c r="AS896" s="2" t="n"/>
       <c r="AT896" s="2" t="n"/>
-      <c r="AU896" s="2" t="n"/>
     </row>
     <row r="897">
       <c r="A897" s="2" t="n"/>
@@ -44619,7 +43718,6 @@
       <c r="AR897" s="2" t="n"/>
       <c r="AS897" s="2" t="n"/>
       <c r="AT897" s="2" t="n"/>
-      <c r="AU897" s="2" t="n"/>
     </row>
     <row r="898">
       <c r="A898" s="2" t="n"/>
@@ -44668,7 +43766,6 @@
       <c r="AR898" s="2" t="n"/>
       <c r="AS898" s="2" t="n"/>
       <c r="AT898" s="2" t="n"/>
-      <c r="AU898" s="2" t="n"/>
     </row>
     <row r="899">
       <c r="A899" s="2" t="n"/>
@@ -44717,7 +43814,6 @@
       <c r="AR899" s="2" t="n"/>
       <c r="AS899" s="2" t="n"/>
       <c r="AT899" s="2" t="n"/>
-      <c r="AU899" s="2" t="n"/>
     </row>
     <row r="900">
       <c r="A900" s="2" t="n"/>
@@ -44766,7 +43862,6 @@
       <c r="AR900" s="2" t="n"/>
       <c r="AS900" s="2" t="n"/>
       <c r="AT900" s="2" t="n"/>
-      <c r="AU900" s="2" t="n"/>
     </row>
     <row r="901">
       <c r="A901" s="2" t="n"/>
@@ -44815,7 +43910,6 @@
       <c r="AR901" s="2" t="n"/>
       <c r="AS901" s="2" t="n"/>
       <c r="AT901" s="2" t="n"/>
-      <c r="AU901" s="2" t="n"/>
     </row>
     <row r="902">
       <c r="A902" s="2" t="n"/>
@@ -44864,7 +43958,6 @@
       <c r="AR902" s="2" t="n"/>
       <c r="AS902" s="2" t="n"/>
       <c r="AT902" s="2" t="n"/>
-      <c r="AU902" s="2" t="n"/>
     </row>
     <row r="903">
       <c r="A903" s="2" t="n"/>
@@ -44913,7 +44006,6 @@
       <c r="AR903" s="2" t="n"/>
       <c r="AS903" s="2" t="n"/>
       <c r="AT903" s="2" t="n"/>
-      <c r="AU903" s="2" t="n"/>
     </row>
     <row r="904">
       <c r="A904" s="2" t="n"/>
@@ -44962,7 +44054,6 @@
       <c r="AR904" s="2" t="n"/>
       <c r="AS904" s="2" t="n"/>
       <c r="AT904" s="2" t="n"/>
-      <c r="AU904" s="2" t="n"/>
     </row>
     <row r="905">
       <c r="A905" s="2" t="n"/>
@@ -45011,7 +44102,6 @@
       <c r="AR905" s="2" t="n"/>
       <c r="AS905" s="2" t="n"/>
       <c r="AT905" s="2" t="n"/>
-      <c r="AU905" s="2" t="n"/>
     </row>
     <row r="906">
       <c r="A906" s="2" t="n"/>
@@ -45060,7 +44150,6 @@
       <c r="AR906" s="2" t="n"/>
       <c r="AS906" s="2" t="n"/>
       <c r="AT906" s="2" t="n"/>
-      <c r="AU906" s="2" t="n"/>
     </row>
     <row r="907">
       <c r="A907" s="2" t="n"/>
@@ -45109,7 +44198,6 @@
       <c r="AR907" s="2" t="n"/>
       <c r="AS907" s="2" t="n"/>
       <c r="AT907" s="2" t="n"/>
-      <c r="AU907" s="2" t="n"/>
     </row>
     <row r="908">
       <c r="A908" s="2" t="n"/>
@@ -45158,7 +44246,6 @@
       <c r="AR908" s="2" t="n"/>
       <c r="AS908" s="2" t="n"/>
       <c r="AT908" s="2" t="n"/>
-      <c r="AU908" s="2" t="n"/>
     </row>
     <row r="909">
       <c r="A909" s="2" t="n"/>
@@ -45207,7 +44294,6 @@
       <c r="AR909" s="2" t="n"/>
       <c r="AS909" s="2" t="n"/>
       <c r="AT909" s="2" t="n"/>
-      <c r="AU909" s="2" t="n"/>
     </row>
     <row r="910">
       <c r="A910" s="2" t="n"/>
@@ -45256,7 +44342,6 @@
       <c r="AR910" s="2" t="n"/>
       <c r="AS910" s="2" t="n"/>
       <c r="AT910" s="2" t="n"/>
-      <c r="AU910" s="2" t="n"/>
     </row>
     <row r="911">
       <c r="A911" s="2" t="n"/>
@@ -45305,7 +44390,6 @@
       <c r="AR911" s="2" t="n"/>
       <c r="AS911" s="2" t="n"/>
       <c r="AT911" s="2" t="n"/>
-      <c r="AU911" s="2" t="n"/>
     </row>
     <row r="912">
       <c r="A912" s="2" t="n"/>
@@ -45354,7 +44438,6 @@
       <c r="AR912" s="2" t="n"/>
       <c r="AS912" s="2" t="n"/>
       <c r="AT912" s="2" t="n"/>
-      <c r="AU912" s="2" t="n"/>
     </row>
     <row r="913">
       <c r="A913" s="2" t="n"/>
@@ -45403,7 +44486,6 @@
       <c r="AR913" s="2" t="n"/>
       <c r="AS913" s="2" t="n"/>
       <c r="AT913" s="2" t="n"/>
-      <c r="AU913" s="2" t="n"/>
     </row>
     <row r="914">
       <c r="A914" s="2" t="n"/>
@@ -45452,7 +44534,6 @@
       <c r="AR914" s="2" t="n"/>
       <c r="AS914" s="2" t="n"/>
       <c r="AT914" s="2" t="n"/>
-      <c r="AU914" s="2" t="n"/>
     </row>
     <row r="915">
       <c r="A915" s="2" t="n"/>
@@ -45501,7 +44582,6 @@
       <c r="AR915" s="2" t="n"/>
       <c r="AS915" s="2" t="n"/>
       <c r="AT915" s="2" t="n"/>
-      <c r="AU915" s="2" t="n"/>
     </row>
     <row r="916">
       <c r="A916" s="2" t="n"/>
@@ -45550,7 +44630,6 @@
       <c r="AR916" s="2" t="n"/>
       <c r="AS916" s="2" t="n"/>
       <c r="AT916" s="2" t="n"/>
-      <c r="AU916" s="2" t="n"/>
     </row>
     <row r="917">
       <c r="A917" s="2" t="n"/>
@@ -45599,7 +44678,6 @@
       <c r="AR917" s="2" t="n"/>
       <c r="AS917" s="2" t="n"/>
       <c r="AT917" s="2" t="n"/>
-      <c r="AU917" s="2" t="n"/>
     </row>
     <row r="918">
       <c r="A918" s="2" t="n"/>
@@ -45648,7 +44726,6 @@
       <c r="AR918" s="2" t="n"/>
       <c r="AS918" s="2" t="n"/>
       <c r="AT918" s="2" t="n"/>
-      <c r="AU918" s="2" t="n"/>
     </row>
     <row r="919">
       <c r="A919" s="2" t="n"/>
@@ -45697,7 +44774,6 @@
       <c r="AR919" s="2" t="n"/>
       <c r="AS919" s="2" t="n"/>
       <c r="AT919" s="2" t="n"/>
-      <c r="AU919" s="2" t="n"/>
     </row>
     <row r="920">
       <c r="A920" s="2" t="n"/>
@@ -45746,7 +44822,6 @@
       <c r="AR920" s="2" t="n"/>
       <c r="AS920" s="2" t="n"/>
       <c r="AT920" s="2" t="n"/>
-      <c r="AU920" s="2" t="n"/>
     </row>
     <row r="921">
       <c r="A921" s="2" t="n"/>
@@ -45795,7 +44870,6 @@
       <c r="AR921" s="2" t="n"/>
       <c r="AS921" s="2" t="n"/>
       <c r="AT921" s="2" t="n"/>
-      <c r="AU921" s="2" t="n"/>
     </row>
     <row r="922">
       <c r="A922" s="2" t="n"/>
@@ -45844,7 +44918,6 @@
       <c r="AR922" s="2" t="n"/>
       <c r="AS922" s="2" t="n"/>
       <c r="AT922" s="2" t="n"/>
-      <c r="AU922" s="2" t="n"/>
     </row>
     <row r="923">
       <c r="A923" s="2" t="n"/>
@@ -45893,7 +44966,6 @@
       <c r="AR923" s="2" t="n"/>
       <c r="AS923" s="2" t="n"/>
       <c r="AT923" s="2" t="n"/>
-      <c r="AU923" s="2" t="n"/>
     </row>
     <row r="924">
       <c r="A924" s="2" t="n"/>
@@ -45942,7 +45014,6 @@
       <c r="AR924" s="2" t="n"/>
       <c r="AS924" s="2" t="n"/>
       <c r="AT924" s="2" t="n"/>
-      <c r="AU924" s="2" t="n"/>
     </row>
     <row r="925">
       <c r="A925" s="2" t="n"/>
@@ -45991,7 +45062,6 @@
       <c r="AR925" s="2" t="n"/>
       <c r="AS925" s="2" t="n"/>
       <c r="AT925" s="2" t="n"/>
-      <c r="AU925" s="2" t="n"/>
     </row>
     <row r="926">
       <c r="A926" s="2" t="n"/>
@@ -46040,7 +45110,6 @@
       <c r="AR926" s="2" t="n"/>
       <c r="AS926" s="2" t="n"/>
       <c r="AT926" s="2" t="n"/>
-      <c r="AU926" s="2" t="n"/>
     </row>
     <row r="927">
       <c r="A927" s="2" t="n"/>
@@ -46089,7 +45158,6 @@
       <c r="AR927" s="2" t="n"/>
       <c r="AS927" s="2" t="n"/>
       <c r="AT927" s="2" t="n"/>
-      <c r="AU927" s="2" t="n"/>
     </row>
     <row r="928">
       <c r="A928" s="2" t="n"/>
@@ -46138,7 +45206,6 @@
       <c r="AR928" s="2" t="n"/>
       <c r="AS928" s="2" t="n"/>
       <c r="AT928" s="2" t="n"/>
-      <c r="AU928" s="2" t="n"/>
     </row>
     <row r="929">
       <c r="A929" s="2" t="n"/>
@@ -46187,7 +45254,6 @@
       <c r="AR929" s="2" t="n"/>
       <c r="AS929" s="2" t="n"/>
       <c r="AT929" s="2" t="n"/>
-      <c r="AU929" s="2" t="n"/>
     </row>
     <row r="930">
       <c r="A930" s="2" t="n"/>
@@ -46236,7 +45302,6 @@
       <c r="AR930" s="2" t="n"/>
       <c r="AS930" s="2" t="n"/>
       <c r="AT930" s="2" t="n"/>
-      <c r="AU930" s="2" t="n"/>
     </row>
     <row r="931">
       <c r="A931" s="2" t="n"/>
@@ -46285,7 +45350,6 @@
       <c r="AR931" s="2" t="n"/>
       <c r="AS931" s="2" t="n"/>
       <c r="AT931" s="2" t="n"/>
-      <c r="AU931" s="2" t="n"/>
     </row>
     <row r="932">
       <c r="A932" s="2" t="n"/>
@@ -46334,7 +45398,6 @@
       <c r="AR932" s="2" t="n"/>
       <c r="AS932" s="2" t="n"/>
       <c r="AT932" s="2" t="n"/>
-      <c r="AU932" s="2" t="n"/>
     </row>
     <row r="933">
       <c r="A933" s="2" t="n"/>
@@ -46383,7 +45446,6 @@
       <c r="AR933" s="2" t="n"/>
       <c r="AS933" s="2" t="n"/>
       <c r="AT933" s="2" t="n"/>
-      <c r="AU933" s="2" t="n"/>
     </row>
     <row r="934">
       <c r="A934" s="2" t="n"/>
@@ -46432,7 +45494,6 @@
       <c r="AR934" s="2" t="n"/>
       <c r="AS934" s="2" t="n"/>
       <c r="AT934" s="2" t="n"/>
-      <c r="AU934" s="2" t="n"/>
     </row>
     <row r="935">
       <c r="A935" s="2" t="n"/>
@@ -46481,7 +45542,6 @@
       <c r="AR935" s="2" t="n"/>
       <c r="AS935" s="2" t="n"/>
       <c r="AT935" s="2" t="n"/>
-      <c r="AU935" s="2" t="n"/>
     </row>
     <row r="936">
       <c r="A936" s="2" t="n"/>
@@ -46530,7 +45590,6 @@
       <c r="AR936" s="2" t="n"/>
       <c r="AS936" s="2" t="n"/>
       <c r="AT936" s="2" t="n"/>
-      <c r="AU936" s="2" t="n"/>
     </row>
     <row r="937">
       <c r="A937" s="2" t="n"/>
@@ -46579,7 +45638,6 @@
       <c r="AR937" s="2" t="n"/>
       <c r="AS937" s="2" t="n"/>
       <c r="AT937" s="2" t="n"/>
-      <c r="AU937" s="2" t="n"/>
     </row>
     <row r="938">
       <c r="A938" s="2" t="n"/>
@@ -46628,7 +45686,6 @@
       <c r="AR938" s="2" t="n"/>
       <c r="AS938" s="2" t="n"/>
       <c r="AT938" s="2" t="n"/>
-      <c r="AU938" s="2" t="n"/>
     </row>
     <row r="939">
       <c r="A939" s="2" t="n"/>
@@ -46677,7 +45734,6 @@
       <c r="AR939" s="2" t="n"/>
       <c r="AS939" s="2" t="n"/>
       <c r="AT939" s="2" t="n"/>
-      <c r="AU939" s="2" t="n"/>
     </row>
     <row r="940">
       <c r="A940" s="2" t="n"/>
@@ -46726,7 +45782,6 @@
       <c r="AR940" s="2" t="n"/>
       <c r="AS940" s="2" t="n"/>
       <c r="AT940" s="2" t="n"/>
-      <c r="AU940" s="2" t="n"/>
     </row>
     <row r="941">
       <c r="A941" s="2" t="n"/>
@@ -46775,7 +45830,6 @@
       <c r="AR941" s="2" t="n"/>
       <c r="AS941" s="2" t="n"/>
       <c r="AT941" s="2" t="n"/>
-      <c r="AU941" s="2" t="n"/>
     </row>
     <row r="942">
       <c r="A942" s="2" t="n"/>
@@ -46824,7 +45878,6 @@
       <c r="AR942" s="2" t="n"/>
       <c r="AS942" s="2" t="n"/>
       <c r="AT942" s="2" t="n"/>
-      <c r="AU942" s="2" t="n"/>
     </row>
     <row r="943">
       <c r="A943" s="2" t="n"/>
@@ -46873,7 +45926,6 @@
       <c r="AR943" s="2" t="n"/>
       <c r="AS943" s="2" t="n"/>
       <c r="AT943" s="2" t="n"/>
-      <c r="AU943" s="2" t="n"/>
     </row>
     <row r="944">
       <c r="A944" s="2" t="n"/>
@@ -46922,7 +45974,6 @@
       <c r="AR944" s="2" t="n"/>
       <c r="AS944" s="2" t="n"/>
       <c r="AT944" s="2" t="n"/>
-      <c r="AU944" s="2" t="n"/>
     </row>
     <row r="945">
       <c r="A945" s="2" t="n"/>
@@ -46971,7 +46022,6 @@
       <c r="AR945" s="2" t="n"/>
       <c r="AS945" s="2" t="n"/>
       <c r="AT945" s="2" t="n"/>
-      <c r="AU945" s="2" t="n"/>
     </row>
     <row r="946">
       <c r="A946" s="2" t="n"/>
@@ -47020,7 +46070,6 @@
       <c r="AR946" s="2" t="n"/>
       <c r="AS946" s="2" t="n"/>
       <c r="AT946" s="2" t="n"/>
-      <c r="AU946" s="2" t="n"/>
     </row>
     <row r="947">
       <c r="A947" s="2" t="n"/>
@@ -47069,7 +46118,6 @@
       <c r="AR947" s="2" t="n"/>
       <c r="AS947" s="2" t="n"/>
       <c r="AT947" s="2" t="n"/>
-      <c r="AU947" s="2" t="n"/>
     </row>
     <row r="948">
       <c r="A948" s="2" t="n"/>
@@ -47118,7 +46166,6 @@
       <c r="AR948" s="2" t="n"/>
       <c r="AS948" s="2" t="n"/>
       <c r="AT948" s="2" t="n"/>
-      <c r="AU948" s="2" t="n"/>
     </row>
     <row r="949">
       <c r="A949" s="2" t="n"/>
@@ -47167,7 +46214,6 @@
       <c r="AR949" s="2" t="n"/>
       <c r="AS949" s="2" t="n"/>
       <c r="AT949" s="2" t="n"/>
-      <c r="AU949" s="2" t="n"/>
     </row>
     <row r="950">
       <c r="A950" s="2" t="n"/>
@@ -47216,7 +46262,6 @@
       <c r="AR950" s="2" t="n"/>
       <c r="AS950" s="2" t="n"/>
       <c r="AT950" s="2" t="n"/>
-      <c r="AU950" s="2" t="n"/>
     </row>
     <row r="951">
       <c r="A951" s="2" t="n"/>
@@ -47265,7 +46310,6 @@
       <c r="AR951" s="2" t="n"/>
       <c r="AS951" s="2" t="n"/>
       <c r="AT951" s="2" t="n"/>
-      <c r="AU951" s="2" t="n"/>
     </row>
     <row r="952">
       <c r="A952" s="2" t="n"/>
@@ -47314,7 +46358,6 @@
       <c r="AR952" s="2" t="n"/>
       <c r="AS952" s="2" t="n"/>
       <c r="AT952" s="2" t="n"/>
-      <c r="AU952" s="2" t="n"/>
     </row>
     <row r="953">
       <c r="A953" s="2" t="n"/>
@@ -47363,7 +46406,6 @@
       <c r="AR953" s="2" t="n"/>
       <c r="AS953" s="2" t="n"/>
       <c r="AT953" s="2" t="n"/>
-      <c r="AU953" s="2" t="n"/>
     </row>
     <row r="954">
       <c r="A954" s="2" t="n"/>
@@ -47412,7 +46454,6 @@
       <c r="AR954" s="2" t="n"/>
       <c r="AS954" s="2" t="n"/>
       <c r="AT954" s="2" t="n"/>
-      <c r="AU954" s="2" t="n"/>
     </row>
     <row r="955">
       <c r="A955" s="2" t="n"/>
@@ -47461,7 +46502,6 @@
       <c r="AR955" s="2" t="n"/>
       <c r="AS955" s="2" t="n"/>
       <c r="AT955" s="2" t="n"/>
-      <c r="AU955" s="2" t="n"/>
     </row>
     <row r="956">
       <c r="A956" s="2" t="n"/>
@@ -47510,7 +46550,6 @@
       <c r="AR956" s="2" t="n"/>
       <c r="AS956" s="2" t="n"/>
       <c r="AT956" s="2" t="n"/>
-      <c r="AU956" s="2" t="n"/>
     </row>
     <row r="957">
       <c r="A957" s="2" t="n"/>
@@ -47559,7 +46598,6 @@
       <c r="AR957" s="2" t="n"/>
       <c r="AS957" s="2" t="n"/>
       <c r="AT957" s="2" t="n"/>
-      <c r="AU957" s="2" t="n"/>
     </row>
     <row r="958">
       <c r="A958" s="2" t="n"/>
@@ -47608,7 +46646,6 @@
       <c r="AR958" s="2" t="n"/>
       <c r="AS958" s="2" t="n"/>
       <c r="AT958" s="2" t="n"/>
-      <c r="AU958" s="2" t="n"/>
     </row>
     <row r="959">
       <c r="A959" s="2" t="n"/>
@@ -47657,7 +46694,6 @@
       <c r="AR959" s="2" t="n"/>
       <c r="AS959" s="2" t="n"/>
       <c r="AT959" s="2" t="n"/>
-      <c r="AU959" s="2" t="n"/>
     </row>
     <row r="960">
       <c r="A960" s="2" t="n"/>
@@ -47706,7 +46742,6 @@
       <c r="AR960" s="2" t="n"/>
       <c r="AS960" s="2" t="n"/>
       <c r="AT960" s="2" t="n"/>
-      <c r="AU960" s="2" t="n"/>
     </row>
     <row r="961">
       <c r="A961" s="2" t="n"/>
@@ -47755,7 +46790,6 @@
       <c r="AR961" s="2" t="n"/>
       <c r="AS961" s="2" t="n"/>
       <c r="AT961" s="2" t="n"/>
-      <c r="AU961" s="2" t="n"/>
     </row>
     <row r="962">
       <c r="A962" s="2" t="n"/>
@@ -47804,7 +46838,6 @@
       <c r="AR962" s="2" t="n"/>
       <c r="AS962" s="2" t="n"/>
       <c r="AT962" s="2" t="n"/>
-      <c r="AU962" s="2" t="n"/>
     </row>
     <row r="963">
       <c r="A963" s="2" t="n"/>
@@ -47853,7 +46886,6 @@
       <c r="AR963" s="2" t="n"/>
       <c r="AS963" s="2" t="n"/>
       <c r="AT963" s="2" t="n"/>
-      <c r="AU963" s="2" t="n"/>
     </row>
     <row r="964">
       <c r="A964" s="2" t="n"/>
@@ -47902,7 +46934,6 @@
       <c r="AR964" s="2" t="n"/>
       <c r="AS964" s="2" t="n"/>
       <c r="AT964" s="2" t="n"/>
-      <c r="AU964" s="2" t="n"/>
     </row>
     <row r="965">
       <c r="A965" s="2" t="n"/>
@@ -47951,7 +46982,6 @@
       <c r="AR965" s="2" t="n"/>
       <c r="AS965" s="2" t="n"/>
       <c r="AT965" s="2" t="n"/>
-      <c r="AU965" s="2" t="n"/>
     </row>
     <row r="966">
       <c r="A966" s="2" t="n"/>
@@ -48000,7 +47030,6 @@
       <c r="AR966" s="2" t="n"/>
       <c r="AS966" s="2" t="n"/>
       <c r="AT966" s="2" t="n"/>
-      <c r="AU966" s="2" t="n"/>
     </row>
     <row r="967">
       <c r="A967" s="2" t="n"/>
@@ -48049,7 +47078,6 @@
       <c r="AR967" s="2" t="n"/>
       <c r="AS967" s="2" t="n"/>
       <c r="AT967" s="2" t="n"/>
-      <c r="AU967" s="2" t="n"/>
     </row>
     <row r="968">
       <c r="A968" s="2" t="n"/>
@@ -48098,7 +47126,6 @@
       <c r="AR968" s="2" t="n"/>
       <c r="AS968" s="2" t="n"/>
       <c r="AT968" s="2" t="n"/>
-      <c r="AU968" s="2" t="n"/>
     </row>
     <row r="969">
       <c r="A969" s="2" t="n"/>
@@ -48147,7 +47174,6 @@
       <c r="AR969" s="2" t="n"/>
       <c r="AS969" s="2" t="n"/>
       <c r="AT969" s="2" t="n"/>
-      <c r="AU969" s="2" t="n"/>
     </row>
     <row r="970">
       <c r="A970" s="2" t="n"/>
@@ -48196,7 +47222,6 @@
       <c r="AR970" s="2" t="n"/>
       <c r="AS970" s="2" t="n"/>
       <c r="AT970" s="2" t="n"/>
-      <c r="AU970" s="2" t="n"/>
     </row>
     <row r="971">
       <c r="A971" s="2" t="n"/>
@@ -48245,7 +47270,6 @@
       <c r="AR971" s="2" t="n"/>
       <c r="AS971" s="2" t="n"/>
       <c r="AT971" s="2" t="n"/>
-      <c r="AU971" s="2" t="n"/>
     </row>
     <row r="972">
       <c r="A972" s="2" t="n"/>
@@ -48294,7 +47318,6 @@
       <c r="AR972" s="2" t="n"/>
       <c r="AS972" s="2" t="n"/>
       <c r="AT972" s="2" t="n"/>
-      <c r="AU972" s="2" t="n"/>
     </row>
     <row r="973">
       <c r="A973" s="2" t="n"/>
@@ -48343,7 +47366,6 @@
       <c r="AR973" s="2" t="n"/>
       <c r="AS973" s="2" t="n"/>
       <c r="AT973" s="2" t="n"/>
-      <c r="AU973" s="2" t="n"/>
     </row>
     <row r="974">
       <c r="A974" s="2" t="n"/>
@@ -48392,7 +47414,6 @@
       <c r="AR974" s="2" t="n"/>
       <c r="AS974" s="2" t="n"/>
       <c r="AT974" s="2" t="n"/>
-      <c r="AU974" s="2" t="n"/>
     </row>
     <row r="975">
       <c r="A975" s="2" t="n"/>
@@ -48441,7 +47462,6 @@
       <c r="AR975" s="2" t="n"/>
       <c r="AS975" s="2" t="n"/>
       <c r="AT975" s="2" t="n"/>
-      <c r="AU975" s="2" t="n"/>
     </row>
     <row r="976">
       <c r="A976" s="2" t="n"/>
@@ -48490,7 +47510,6 @@
       <c r="AR976" s="2" t="n"/>
       <c r="AS976" s="2" t="n"/>
       <c r="AT976" s="2" t="n"/>
-      <c r="AU976" s="2" t="n"/>
     </row>
     <row r="977">
       <c r="A977" s="2" t="n"/>
@@ -48539,7 +47558,6 @@
       <c r="AR977" s="2" t="n"/>
       <c r="AS977" s="2" t="n"/>
       <c r="AT977" s="2" t="n"/>
-      <c r="AU977" s="2" t="n"/>
     </row>
     <row r="978">
       <c r="A978" s="2" t="n"/>
@@ -48588,7 +47606,6 @@
       <c r="AR978" s="2" t="n"/>
       <c r="AS978" s="2" t="n"/>
       <c r="AT978" s="2" t="n"/>
-      <c r="AU978" s="2" t="n"/>
     </row>
     <row r="979">
       <c r="A979" s="2" t="n"/>
@@ -48637,7 +47654,6 @@
       <c r="AR979" s="2" t="n"/>
       <c r="AS979" s="2" t="n"/>
       <c r="AT979" s="2" t="n"/>
-      <c r="AU979" s="2" t="n"/>
     </row>
     <row r="980">
       <c r="A980" s="2" t="n"/>
@@ -48686,7 +47702,6 @@
       <c r="AR980" s="2" t="n"/>
       <c r="AS980" s="2" t="n"/>
       <c r="AT980" s="2" t="n"/>
-      <c r="AU980" s="2" t="n"/>
     </row>
     <row r="981">
       <c r="A981" s="2" t="n"/>
@@ -48735,7 +47750,6 @@
       <c r="AR981" s="2" t="n"/>
       <c r="AS981" s="2" t="n"/>
       <c r="AT981" s="2" t="n"/>
-      <c r="AU981" s="2" t="n"/>
     </row>
     <row r="982">
       <c r="A982" s="2" t="n"/>
@@ -48784,7 +47798,6 @@
       <c r="AR982" s="2" t="n"/>
       <c r="AS982" s="2" t="n"/>
       <c r="AT982" s="2" t="n"/>
-      <c r="AU982" s="2" t="n"/>
     </row>
     <row r="983">
       <c r="A983" s="2" t="n"/>
@@ -48833,7 +47846,6 @@
       <c r="AR983" s="2" t="n"/>
       <c r="AS983" s="2" t="n"/>
       <c r="AT983" s="2" t="n"/>
-      <c r="AU983" s="2" t="n"/>
     </row>
     <row r="984">
       <c r="A984" s="2" t="n"/>
@@ -48882,7 +47894,6 @@
       <c r="AR984" s="2" t="n"/>
       <c r="AS984" s="2" t="n"/>
       <c r="AT984" s="2" t="n"/>
-      <c r="AU984" s="2" t="n"/>
     </row>
     <row r="985">
       <c r="A985" s="2" t="n"/>
@@ -48931,7 +47942,6 @@
       <c r="AR985" s="2" t="n"/>
       <c r="AS985" s="2" t="n"/>
       <c r="AT985" s="2" t="n"/>
-      <c r="AU985" s="2" t="n"/>
     </row>
     <row r="986">
       <c r="A986" s="2" t="n"/>
@@ -48980,7 +47990,6 @@
       <c r="AR986" s="2" t="n"/>
       <c r="AS986" s="2" t="n"/>
       <c r="AT986" s="2" t="n"/>
-      <c r="AU986" s="2" t="n"/>
     </row>
     <row r="987">
       <c r="A987" s="2" t="n"/>
@@ -49029,7 +48038,6 @@
       <c r="AR987" s="2" t="n"/>
       <c r="AS987" s="2" t="n"/>
       <c r="AT987" s="2" t="n"/>
-      <c r="AU987" s="2" t="n"/>
     </row>
     <row r="988">
       <c r="A988" s="2" t="n"/>
@@ -49078,7 +48086,6 @@
       <c r="AR988" s="2" t="n"/>
       <c r="AS988" s="2" t="n"/>
       <c r="AT988" s="2" t="n"/>
-      <c r="AU988" s="2" t="n"/>
     </row>
     <row r="989">
       <c r="A989" s="2" t="n"/>
@@ -49127,7 +48134,6 @@
       <c r="AR989" s="2" t="n"/>
       <c r="AS989" s="2" t="n"/>
       <c r="AT989" s="2" t="n"/>
-      <c r="AU989" s="2" t="n"/>
     </row>
     <row r="990">
       <c r="A990" s="2" t="n"/>
@@ -49176,7 +48182,6 @@
       <c r="AR990" s="2" t="n"/>
       <c r="AS990" s="2" t="n"/>
       <c r="AT990" s="2" t="n"/>
-      <c r="AU990" s="2" t="n"/>
     </row>
     <row r="991">
       <c r="A991" s="2" t="n"/>
@@ -49225,7 +48230,6 @@
       <c r="AR991" s="2" t="n"/>
       <c r="AS991" s="2" t="n"/>
       <c r="AT991" s="2" t="n"/>
-      <c r="AU991" s="2" t="n"/>
     </row>
     <row r="992">
       <c r="A992" s="2" t="n"/>
@@ -49274,7 +48278,6 @@
       <c r="AR992" s="2" t="n"/>
       <c r="AS992" s="2" t="n"/>
       <c r="AT992" s="2" t="n"/>
-      <c r="AU992" s="2" t="n"/>
     </row>
     <row r="993">
       <c r="A993" s="2" t="n"/>
@@ -49323,7 +48326,6 @@
       <c r="AR993" s="2" t="n"/>
       <c r="AS993" s="2" t="n"/>
       <c r="AT993" s="2" t="n"/>
-      <c r="AU993" s="2" t="n"/>
     </row>
     <row r="994">
       <c r="A994" s="2" t="n"/>
@@ -49372,7 +48374,6 @@
       <c r="AR994" s="2" t="n"/>
       <c r="AS994" s="2" t="n"/>
       <c r="AT994" s="2" t="n"/>
-      <c r="AU994" s="2" t="n"/>
     </row>
     <row r="995">
       <c r="A995" s="2" t="n"/>
@@ -49421,7 +48422,6 @@
       <c r="AR995" s="2" t="n"/>
       <c r="AS995" s="2" t="n"/>
       <c r="AT995" s="2" t="n"/>
-      <c r="AU995" s="2" t="n"/>
     </row>
     <row r="996">
       <c r="A996" s="2" t="n"/>
@@ -49470,7 +48470,6 @@
       <c r="AR996" s="2" t="n"/>
       <c r="AS996" s="2" t="n"/>
       <c r="AT996" s="2" t="n"/>
-      <c r="AU996" s="2" t="n"/>
     </row>
     <row r="997">
       <c r="A997" s="2" t="n"/>
@@ -49519,7 +48518,6 @@
       <c r="AR997" s="2" t="n"/>
       <c r="AS997" s="2" t="n"/>
       <c r="AT997" s="2" t="n"/>
-      <c r="AU997" s="2" t="n"/>
     </row>
     <row r="998">
       <c r="A998" s="2" t="n"/>
@@ -49568,7 +48566,6 @@
       <c r="AR998" s="2" t="n"/>
       <c r="AS998" s="2" t="n"/>
       <c r="AT998" s="2" t="n"/>
-      <c r="AU998" s="2" t="n"/>
     </row>
     <row r="999">
       <c r="A999" s="2" t="n"/>
@@ -49617,7 +48614,6 @@
       <c r="AR999" s="2" t="n"/>
       <c r="AS999" s="2" t="n"/>
       <c r="AT999" s="2" t="n"/>
-      <c r="AU999" s="2" t="n"/>
     </row>
     <row r="1000">
       <c r="A1000" s="2" t="n"/>
@@ -49666,7 +48662,6 @@
       <c r="AR1000" s="2" t="n"/>
       <c r="AS1000" s="2" t="n"/>
       <c r="AT1000" s="2" t="n"/>
-      <c r="AU1000" s="2" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="4">
@@ -49679,7 +48674,7 @@
     <dataValidation sqref="AG2:AG1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Si,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="AS2:AS1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AR2:AR1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"EFECTIVO,TRANSFERENCIA"</formula1>
     </dataValidation>
   </dataValidations>

--- a/static/downloads/plantilla_empleados.xlsx
+++ b/static/downloads/plantilla_empleados.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,13 +28,24 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -57,8 +68,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -428,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT1000"/>
+  <dimension ref="A1:AU1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -436,47 +447,48 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="52.8" customWidth="1" min="6" max="6"/>
-    <col width="39.6" customWidth="1" min="7" max="7"/>
-    <col width="21.6" customWidth="1" min="8" max="8"/>
-    <col width="38.4" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="21.6" customWidth="1" min="7" max="7"/>
+    <col width="20.4" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
     <col width="33.6" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="32.4" customWidth="1" min="11" max="11"/>
+    <col width="38.4" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="37.2" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="21.6" customWidth="1" min="19" max="19"/>
-    <col width="20.4" customWidth="1" min="20" max="20"/>
-    <col width="30" customWidth="1" min="21" max="21"/>
-    <col width="32.4" customWidth="1" min="22" max="22"/>
-    <col width="38.4" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
     <col width="20" customWidth="1" min="24" max="24"/>
     <col width="20" customWidth="1" min="25" max="25"/>
-    <col width="20" customWidth="1" min="26" max="26"/>
-    <col width="20" customWidth="1" min="27" max="27"/>
-    <col width="20" customWidth="1" min="28" max="28"/>
-    <col width="27.6" customWidth="1" min="29" max="29"/>
-    <col width="28.8" customWidth="1" min="30" max="30"/>
-    <col width="30" customWidth="1" min="31" max="31"/>
-    <col width="33.6" customWidth="1" min="32" max="32"/>
-    <col width="24" customWidth="1" min="33" max="33"/>
-    <col width="34.8" customWidth="1" min="34" max="34"/>
-    <col width="20" customWidth="1" min="35" max="35"/>
-    <col width="20" customWidth="1" min="36" max="36"/>
+    <col width="27.6" customWidth="1" min="26" max="26"/>
+    <col width="28.8" customWidth="1" min="27" max="27"/>
+    <col width="30" customWidth="1" min="28" max="28"/>
+    <col width="33.6" customWidth="1" min="29" max="29"/>
+    <col width="24" customWidth="1" min="30" max="30"/>
+    <col width="34.8" customWidth="1" min="31" max="31"/>
+    <col width="20" customWidth="1" min="32" max="32"/>
+    <col width="52.8" customWidth="1" min="33" max="33"/>
+    <col width="39.6" customWidth="1" min="34" max="34"/>
+    <col width="21.6" customWidth="1" min="35" max="35"/>
+    <col width="38.4" customWidth="1" min="36" max="36"/>
     <col width="20" customWidth="1" min="37" max="37"/>
     <col width="20" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
     <col width="20" customWidth="1" min="40" max="40"/>
-    <col width="21.6" customWidth="1" min="41" max="41"/>
-    <col width="20" customWidth="1" min="42" max="42"/>
+    <col width="20" customWidth="1" min="41" max="41"/>
+    <col width="21.6" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
-    <col width="21.6" customWidth="1" min="45" max="45"/>
-    <col width="20" customWidth="1" min="46" max="46"/>
+    <col width="20" customWidth="1" min="45" max="45"/>
+    <col width="21.6" customWidth="1" min="46" max="46"/>
+    <col width="20" customWidth="1" min="47" max="47"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -507,22 +519,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Tipo de Nomina (Semanal/Por hora/Cuadrado)</t>
+          <t>Tipo de Movimiento</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Salario Real Pactado por Semana</t>
+          <t>Tipo de Contrato</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Sueldo Base (SB)</t>
+          <t>Tipo de Jornada</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Salario Diario Integrado (SDI)</t>
+          <t>Descripcion de Servicio</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -532,180 +544,185 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>RFC</t>
+          <t>Fecha Inicio (YYYY-MM-DD)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CURP</t>
+          <t>Termino de Prueba (YYYY-MM-DD)</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>NSS</t>
+          <t>CURP</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Correo</t>
+          <t>RFC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Celular</t>
+          <t>NSS</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Sexo (M/F)</t>
+          <t>Fecha Nacimiento (YYYY-MM-DD)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Estado Civil</t>
+          <t>Edad</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Tipo de Movimiento</t>
+          <t>Sexo (M/F)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Tipo de Contrato</t>
+          <t>Estado Civil</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Tipo de Jornada</t>
+          <t>Nacionalidad</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Descripcion de Servicio</t>
+          <t>Domicilio</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Fecha Inicio (YYYY-MM-DD)</t>
+          <t>Correo</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Termino de Prueba (YYYY-MM-DD)</t>
+          <t>Celular</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Nacionalidad</t>
+          <t>Tipo de Sangre</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Edad</t>
+          <t>Alergias</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Domicilio</t>
+          <t>Enfermedades Cronicas</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Tipo de Sangre</t>
+          <t>Contacto de Emergencia</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Alergias</t>
+          <t>Parentesco del Contacto</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Enfermedades Cronicas</t>
+          <t>Numero Contacto Emergencia</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Contacto de Emergencia</t>
+          <t>Usa Lentes (Si/No)</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Parentesco del Contacto</t>
+          <t>Licencia de Conducir (Tipo)</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Numero Contacto Emergencia</t>
+          <t>Estatura</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Usa Lentes (Si/No)</t>
+          <t>Tipo de Nomina (Semanal/Por hora/Cuadrado)</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Licencia de Conducir (Tipo)</t>
+          <t>Salario Real Pactado por Semana</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Estatura</t>
+          <t>Sueldo Base (SB)</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>Letra</t>
+          <t>Salario Diario Integrado (SDI)</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>Horas Extra</t>
+          <t>Letra</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>Infonavit</t>
+          <t>Horas Extra</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>Caja de Ahorro</t>
+          <t>Infonavit</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>Viaticos</t>
+          <t>Caja de Ahorro</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>Pago Dia Festivo</t>
+          <t>Viaticos</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>Pagos Efectivo</t>
+          <t>Pago Dia Festivo</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>Folio Mov IDSE</t>
+          <t>Pagos Efectivo</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>Tipo Pago</t>
+          <t>Folio Mov IDSE</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
+          <t>Tipo Pago</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
           <t>Ubicacion Estado</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
@@ -758,6 +775,7 @@
       <c r="AR2" s="2" t="n"/>
       <c r="AS2" s="2" t="n"/>
       <c r="AT2" s="2" t="n"/>
+      <c r="AU2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -806,6 +824,7 @@
       <c r="AR3" s="2" t="n"/>
       <c r="AS3" s="2" t="n"/>
       <c r="AT3" s="2" t="n"/>
+      <c r="AU3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
@@ -854,6 +873,7 @@
       <c r="AR4" s="2" t="n"/>
       <c r="AS4" s="2" t="n"/>
       <c r="AT4" s="2" t="n"/>
+      <c r="AU4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -902,6 +922,7 @@
       <c r="AR5" s="2" t="n"/>
       <c r="AS5" s="2" t="n"/>
       <c r="AT5" s="2" t="n"/>
+      <c r="AU5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -950,6 +971,7 @@
       <c r="AR6" s="2" t="n"/>
       <c r="AS6" s="2" t="n"/>
       <c r="AT6" s="2" t="n"/>
+      <c r="AU6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
@@ -998,6 +1020,7 @@
       <c r="AR7" s="2" t="n"/>
       <c r="AS7" s="2" t="n"/>
       <c r="AT7" s="2" t="n"/>
+      <c r="AU7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -1046,6 +1069,7 @@
       <c r="AR8" s="2" t="n"/>
       <c r="AS8" s="2" t="n"/>
       <c r="AT8" s="2" t="n"/>
+      <c r="AU8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -1094,6 +1118,7 @@
       <c r="AR9" s="2" t="n"/>
       <c r="AS9" s="2" t="n"/>
       <c r="AT9" s="2" t="n"/>
+      <c r="AU9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -1142,6 +1167,7 @@
       <c r="AR10" s="2" t="n"/>
       <c r="AS10" s="2" t="n"/>
       <c r="AT10" s="2" t="n"/>
+      <c r="AU10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -1190,6 +1216,7 @@
       <c r="AR11" s="2" t="n"/>
       <c r="AS11" s="2" t="n"/>
       <c r="AT11" s="2" t="n"/>
+      <c r="AU11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -1238,6 +1265,7 @@
       <c r="AR12" s="2" t="n"/>
       <c r="AS12" s="2" t="n"/>
       <c r="AT12" s="2" t="n"/>
+      <c r="AU12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -1286,6 +1314,7 @@
       <c r="AR13" s="2" t="n"/>
       <c r="AS13" s="2" t="n"/>
       <c r="AT13" s="2" t="n"/>
+      <c r="AU13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
@@ -1334,6 +1363,7 @@
       <c r="AR14" s="2" t="n"/>
       <c r="AS14" s="2" t="n"/>
       <c r="AT14" s="2" t="n"/>
+      <c r="AU14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
@@ -1382,6 +1412,7 @@
       <c r="AR15" s="2" t="n"/>
       <c r="AS15" s="2" t="n"/>
       <c r="AT15" s="2" t="n"/>
+      <c r="AU15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -1430,6 +1461,7 @@
       <c r="AR16" s="2" t="n"/>
       <c r="AS16" s="2" t="n"/>
       <c r="AT16" s="2" t="n"/>
+      <c r="AU16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
@@ -1478,6 +1510,7 @@
       <c r="AR17" s="2" t="n"/>
       <c r="AS17" s="2" t="n"/>
       <c r="AT17" s="2" t="n"/>
+      <c r="AU17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -1526,6 +1559,7 @@
       <c r="AR18" s="2" t="n"/>
       <c r="AS18" s="2" t="n"/>
       <c r="AT18" s="2" t="n"/>
+      <c r="AU18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
@@ -1574,6 +1608,7 @@
       <c r="AR19" s="2" t="n"/>
       <c r="AS19" s="2" t="n"/>
       <c r="AT19" s="2" t="n"/>
+      <c r="AU19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -1622,6 +1657,7 @@
       <c r="AR20" s="2" t="n"/>
       <c r="AS20" s="2" t="n"/>
       <c r="AT20" s="2" t="n"/>
+      <c r="AU20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
@@ -1670,6 +1706,7 @@
       <c r="AR21" s="2" t="n"/>
       <c r="AS21" s="2" t="n"/>
       <c r="AT21" s="2" t="n"/>
+      <c r="AU21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -1718,6 +1755,7 @@
       <c r="AR22" s="2" t="n"/>
       <c r="AS22" s="2" t="n"/>
       <c r="AT22" s="2" t="n"/>
+      <c r="AU22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
@@ -1766,6 +1804,7 @@
       <c r="AR23" s="2" t="n"/>
       <c r="AS23" s="2" t="n"/>
       <c r="AT23" s="2" t="n"/>
+      <c r="AU23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -1814,6 +1853,7 @@
       <c r="AR24" s="2" t="n"/>
       <c r="AS24" s="2" t="n"/>
       <c r="AT24" s="2" t="n"/>
+      <c r="AU24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
@@ -1862,6 +1902,7 @@
       <c r="AR25" s="2" t="n"/>
       <c r="AS25" s="2" t="n"/>
       <c r="AT25" s="2" t="n"/>
+      <c r="AU25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -1910,6 +1951,7 @@
       <c r="AR26" s="2" t="n"/>
       <c r="AS26" s="2" t="n"/>
       <c r="AT26" s="2" t="n"/>
+      <c r="AU26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
@@ -1958,6 +2000,7 @@
       <c r="AR27" s="2" t="n"/>
       <c r="AS27" s="2" t="n"/>
       <c r="AT27" s="2" t="n"/>
+      <c r="AU27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -2006,6 +2049,7 @@
       <c r="AR28" s="2" t="n"/>
       <c r="AS28" s="2" t="n"/>
       <c r="AT28" s="2" t="n"/>
+      <c r="AU28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -2054,6 +2098,7 @@
       <c r="AR29" s="2" t="n"/>
       <c r="AS29" s="2" t="n"/>
       <c r="AT29" s="2" t="n"/>
+      <c r="AU29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -2102,6 +2147,7 @@
       <c r="AR30" s="2" t="n"/>
       <c r="AS30" s="2" t="n"/>
       <c r="AT30" s="2" t="n"/>
+      <c r="AU30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
@@ -2150,6 +2196,7 @@
       <c r="AR31" s="2" t="n"/>
       <c r="AS31" s="2" t="n"/>
       <c r="AT31" s="2" t="n"/>
+      <c r="AU31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
@@ -2198,6 +2245,7 @@
       <c r="AR32" s="2" t="n"/>
       <c r="AS32" s="2" t="n"/>
       <c r="AT32" s="2" t="n"/>
+      <c r="AU32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
@@ -2246,6 +2294,7 @@
       <c r="AR33" s="2" t="n"/>
       <c r="AS33" s="2" t="n"/>
       <c r="AT33" s="2" t="n"/>
+      <c r="AU33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -2294,6 +2343,7 @@
       <c r="AR34" s="2" t="n"/>
       <c r="AS34" s="2" t="n"/>
       <c r="AT34" s="2" t="n"/>
+      <c r="AU34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
@@ -2342,6 +2392,7 @@
       <c r="AR35" s="2" t="n"/>
       <c r="AS35" s="2" t="n"/>
       <c r="AT35" s="2" t="n"/>
+      <c r="AU35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
@@ -2390,6 +2441,7 @@
       <c r="AR36" s="2" t="n"/>
       <c r="AS36" s="2" t="n"/>
       <c r="AT36" s="2" t="n"/>
+      <c r="AU36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
@@ -2438,6 +2490,7 @@
       <c r="AR37" s="2" t="n"/>
       <c r="AS37" s="2" t="n"/>
       <c r="AT37" s="2" t="n"/>
+      <c r="AU37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
@@ -2486,6 +2539,7 @@
       <c r="AR38" s="2" t="n"/>
       <c r="AS38" s="2" t="n"/>
       <c r="AT38" s="2" t="n"/>
+      <c r="AU38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>
@@ -2534,6 +2588,7 @@
       <c r="AR39" s="2" t="n"/>
       <c r="AS39" s="2" t="n"/>
       <c r="AT39" s="2" t="n"/>
+      <c r="AU39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
@@ -2582,6 +2637,7 @@
       <c r="AR40" s="2" t="n"/>
       <c r="AS40" s="2" t="n"/>
       <c r="AT40" s="2" t="n"/>
+      <c r="AU40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
@@ -2630,6 +2686,7 @@
       <c r="AR41" s="2" t="n"/>
       <c r="AS41" s="2" t="n"/>
       <c r="AT41" s="2" t="n"/>
+      <c r="AU41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -2678,6 +2735,7 @@
       <c r="AR42" s="2" t="n"/>
       <c r="AS42" s="2" t="n"/>
       <c r="AT42" s="2" t="n"/>
+      <c r="AU42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
@@ -2726,6 +2784,7 @@
       <c r="AR43" s="2" t="n"/>
       <c r="AS43" s="2" t="n"/>
       <c r="AT43" s="2" t="n"/>
+      <c r="AU43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
@@ -2774,6 +2833,7 @@
       <c r="AR44" s="2" t="n"/>
       <c r="AS44" s="2" t="n"/>
       <c r="AT44" s="2" t="n"/>
+      <c r="AU44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
@@ -2822,6 +2882,7 @@
       <c r="AR45" s="2" t="n"/>
       <c r="AS45" s="2" t="n"/>
       <c r="AT45" s="2" t="n"/>
+      <c r="AU45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n"/>
@@ -2870,6 +2931,7 @@
       <c r="AR46" s="2" t="n"/>
       <c r="AS46" s="2" t="n"/>
       <c r="AT46" s="2" t="n"/>
+      <c r="AU46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n"/>
@@ -2918,6 +2980,7 @@
       <c r="AR47" s="2" t="n"/>
       <c r="AS47" s="2" t="n"/>
       <c r="AT47" s="2" t="n"/>
+      <c r="AU47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n"/>
@@ -2966,6 +3029,7 @@
       <c r="AR48" s="2" t="n"/>
       <c r="AS48" s="2" t="n"/>
       <c r="AT48" s="2" t="n"/>
+      <c r="AU48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n"/>
@@ -3014,6 +3078,7 @@
       <c r="AR49" s="2" t="n"/>
       <c r="AS49" s="2" t="n"/>
       <c r="AT49" s="2" t="n"/>
+      <c r="AU49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n"/>
@@ -3062,6 +3127,7 @@
       <c r="AR50" s="2" t="n"/>
       <c r="AS50" s="2" t="n"/>
       <c r="AT50" s="2" t="n"/>
+      <c r="AU50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n"/>
@@ -3110,6 +3176,7 @@
       <c r="AR51" s="2" t="n"/>
       <c r="AS51" s="2" t="n"/>
       <c r="AT51" s="2" t="n"/>
+      <c r="AU51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n"/>
@@ -3158,6 +3225,7 @@
       <c r="AR52" s="2" t="n"/>
       <c r="AS52" s="2" t="n"/>
       <c r="AT52" s="2" t="n"/>
+      <c r="AU52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n"/>
@@ -3206,6 +3274,7 @@
       <c r="AR53" s="2" t="n"/>
       <c r="AS53" s="2" t="n"/>
       <c r="AT53" s="2" t="n"/>
+      <c r="AU53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n"/>
@@ -3254,6 +3323,7 @@
       <c r="AR54" s="2" t="n"/>
       <c r="AS54" s="2" t="n"/>
       <c r="AT54" s="2" t="n"/>
+      <c r="AU54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n"/>
@@ -3302,6 +3372,7 @@
       <c r="AR55" s="2" t="n"/>
       <c r="AS55" s="2" t="n"/>
       <c r="AT55" s="2" t="n"/>
+      <c r="AU55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n"/>
@@ -3350,6 +3421,7 @@
       <c r="AR56" s="2" t="n"/>
       <c r="AS56" s="2" t="n"/>
       <c r="AT56" s="2" t="n"/>
+      <c r="AU56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n"/>
@@ -3398,6 +3470,7 @@
       <c r="AR57" s="2" t="n"/>
       <c r="AS57" s="2" t="n"/>
       <c r="AT57" s="2" t="n"/>
+      <c r="AU57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n"/>
@@ -3446,6 +3519,7 @@
       <c r="AR58" s="2" t="n"/>
       <c r="AS58" s="2" t="n"/>
       <c r="AT58" s="2" t="n"/>
+      <c r="AU58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n"/>
@@ -3494,6 +3568,7 @@
       <c r="AR59" s="2" t="n"/>
       <c r="AS59" s="2" t="n"/>
       <c r="AT59" s="2" t="n"/>
+      <c r="AU59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n"/>
@@ -3542,6 +3617,7 @@
       <c r="AR60" s="2" t="n"/>
       <c r="AS60" s="2" t="n"/>
       <c r="AT60" s="2" t="n"/>
+      <c r="AU60" s="2" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n"/>
@@ -3590,6 +3666,7 @@
       <c r="AR61" s="2" t="n"/>
       <c r="AS61" s="2" t="n"/>
       <c r="AT61" s="2" t="n"/>
+      <c r="AU61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n"/>
@@ -3638,6 +3715,7 @@
       <c r="AR62" s="2" t="n"/>
       <c r="AS62" s="2" t="n"/>
       <c r="AT62" s="2" t="n"/>
+      <c r="AU62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n"/>
@@ -3686,6 +3764,7 @@
       <c r="AR63" s="2" t="n"/>
       <c r="AS63" s="2" t="n"/>
       <c r="AT63" s="2" t="n"/>
+      <c r="AU63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n"/>
@@ -3734,6 +3813,7 @@
       <c r="AR64" s="2" t="n"/>
       <c r="AS64" s="2" t="n"/>
       <c r="AT64" s="2" t="n"/>
+      <c r="AU64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n"/>
@@ -3782,6 +3862,7 @@
       <c r="AR65" s="2" t="n"/>
       <c r="AS65" s="2" t="n"/>
       <c r="AT65" s="2" t="n"/>
+      <c r="AU65" s="2" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n"/>
@@ -3830,6 +3911,7 @@
       <c r="AR66" s="2" t="n"/>
       <c r="AS66" s="2" t="n"/>
       <c r="AT66" s="2" t="n"/>
+      <c r="AU66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n"/>
@@ -3878,6 +3960,7 @@
       <c r="AR67" s="2" t="n"/>
       <c r="AS67" s="2" t="n"/>
       <c r="AT67" s="2" t="n"/>
+      <c r="AU67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n"/>
@@ -3926,6 +4009,7 @@
       <c r="AR68" s="2" t="n"/>
       <c r="AS68" s="2" t="n"/>
       <c r="AT68" s="2" t="n"/>
+      <c r="AU68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n"/>
@@ -3974,6 +4058,7 @@
       <c r="AR69" s="2" t="n"/>
       <c r="AS69" s="2" t="n"/>
       <c r="AT69" s="2" t="n"/>
+      <c r="AU69" s="2" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n"/>
@@ -4022,6 +4107,7 @@
       <c r="AR70" s="2" t="n"/>
       <c r="AS70" s="2" t="n"/>
       <c r="AT70" s="2" t="n"/>
+      <c r="AU70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n"/>
@@ -4070,6 +4156,7 @@
       <c r="AR71" s="2" t="n"/>
       <c r="AS71" s="2" t="n"/>
       <c r="AT71" s="2" t="n"/>
+      <c r="AU71" s="2" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n"/>
@@ -4118,6 +4205,7 @@
       <c r="AR72" s="2" t="n"/>
       <c r="AS72" s="2" t="n"/>
       <c r="AT72" s="2" t="n"/>
+      <c r="AU72" s="2" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n"/>
@@ -4166,6 +4254,7 @@
       <c r="AR73" s="2" t="n"/>
       <c r="AS73" s="2" t="n"/>
       <c r="AT73" s="2" t="n"/>
+      <c r="AU73" s="2" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n"/>
@@ -4214,6 +4303,7 @@
       <c r="AR74" s="2" t="n"/>
       <c r="AS74" s="2" t="n"/>
       <c r="AT74" s="2" t="n"/>
+      <c r="AU74" s="2" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n"/>
@@ -4262,6 +4352,7 @@
       <c r="AR75" s="2" t="n"/>
       <c r="AS75" s="2" t="n"/>
       <c r="AT75" s="2" t="n"/>
+      <c r="AU75" s="2" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n"/>
@@ -4310,6 +4401,7 @@
       <c r="AR76" s="2" t="n"/>
       <c r="AS76" s="2" t="n"/>
       <c r="AT76" s="2" t="n"/>
+      <c r="AU76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n"/>
@@ -4358,6 +4450,7 @@
       <c r="AR77" s="2" t="n"/>
       <c r="AS77" s="2" t="n"/>
       <c r="AT77" s="2" t="n"/>
+      <c r="AU77" s="2" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n"/>
@@ -4406,6 +4499,7 @@
       <c r="AR78" s="2" t="n"/>
       <c r="AS78" s="2" t="n"/>
       <c r="AT78" s="2" t="n"/>
+      <c r="AU78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n"/>
@@ -4454,6 +4548,7 @@
       <c r="AR79" s="2" t="n"/>
       <c r="AS79" s="2" t="n"/>
       <c r="AT79" s="2" t="n"/>
+      <c r="AU79" s="2" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n"/>
@@ -4502,6 +4597,7 @@
       <c r="AR80" s="2" t="n"/>
       <c r="AS80" s="2" t="n"/>
       <c r="AT80" s="2" t="n"/>
+      <c r="AU80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n"/>
@@ -4550,6 +4646,7 @@
       <c r="AR81" s="2" t="n"/>
       <c r="AS81" s="2" t="n"/>
       <c r="AT81" s="2" t="n"/>
+      <c r="AU81" s="2" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n"/>
@@ -4598,6 +4695,7 @@
       <c r="AR82" s="2" t="n"/>
       <c r="AS82" s="2" t="n"/>
       <c r="AT82" s="2" t="n"/>
+      <c r="AU82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n"/>
@@ -4646,6 +4744,7 @@
       <c r="AR83" s="2" t="n"/>
       <c r="AS83" s="2" t="n"/>
       <c r="AT83" s="2" t="n"/>
+      <c r="AU83" s="2" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n"/>
@@ -4694,6 +4793,7 @@
       <c r="AR84" s="2" t="n"/>
       <c r="AS84" s="2" t="n"/>
       <c r="AT84" s="2" t="n"/>
+      <c r="AU84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n"/>
@@ -4742,6 +4842,7 @@
       <c r="AR85" s="2" t="n"/>
       <c r="AS85" s="2" t="n"/>
       <c r="AT85" s="2" t="n"/>
+      <c r="AU85" s="2" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n"/>
@@ -4790,6 +4891,7 @@
       <c r="AR86" s="2" t="n"/>
       <c r="AS86" s="2" t="n"/>
       <c r="AT86" s="2" t="n"/>
+      <c r="AU86" s="2" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n"/>
@@ -4838,6 +4940,7 @@
       <c r="AR87" s="2" t="n"/>
       <c r="AS87" s="2" t="n"/>
       <c r="AT87" s="2" t="n"/>
+      <c r="AU87" s="2" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n"/>
@@ -4886,6 +4989,7 @@
       <c r="AR88" s="2" t="n"/>
       <c r="AS88" s="2" t="n"/>
       <c r="AT88" s="2" t="n"/>
+      <c r="AU88" s="2" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n"/>
@@ -4934,6 +5038,7 @@
       <c r="AR89" s="2" t="n"/>
       <c r="AS89" s="2" t="n"/>
       <c r="AT89" s="2" t="n"/>
+      <c r="AU89" s="2" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n"/>
@@ -4982,6 +5087,7 @@
       <c r="AR90" s="2" t="n"/>
       <c r="AS90" s="2" t="n"/>
       <c r="AT90" s="2" t="n"/>
+      <c r="AU90" s="2" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n"/>
@@ -5030,6 +5136,7 @@
       <c r="AR91" s="2" t="n"/>
       <c r="AS91" s="2" t="n"/>
       <c r="AT91" s="2" t="n"/>
+      <c r="AU91" s="2" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n"/>
@@ -5078,6 +5185,7 @@
       <c r="AR92" s="2" t="n"/>
       <c r="AS92" s="2" t="n"/>
       <c r="AT92" s="2" t="n"/>
+      <c r="AU92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n"/>
@@ -5126,6 +5234,7 @@
       <c r="AR93" s="2" t="n"/>
       <c r="AS93" s="2" t="n"/>
       <c r="AT93" s="2" t="n"/>
+      <c r="AU93" s="2" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n"/>
@@ -5174,6 +5283,7 @@
       <c r="AR94" s="2" t="n"/>
       <c r="AS94" s="2" t="n"/>
       <c r="AT94" s="2" t="n"/>
+      <c r="AU94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n"/>
@@ -5222,6 +5332,7 @@
       <c r="AR95" s="2" t="n"/>
       <c r="AS95" s="2" t="n"/>
       <c r="AT95" s="2" t="n"/>
+      <c r="AU95" s="2" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n"/>
@@ -5270,6 +5381,7 @@
       <c r="AR96" s="2" t="n"/>
       <c r="AS96" s="2" t="n"/>
       <c r="AT96" s="2" t="n"/>
+      <c r="AU96" s="2" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n"/>
@@ -5318,6 +5430,7 @@
       <c r="AR97" s="2" t="n"/>
       <c r="AS97" s="2" t="n"/>
       <c r="AT97" s="2" t="n"/>
+      <c r="AU97" s="2" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n"/>
@@ -5366,6 +5479,7 @@
       <c r="AR98" s="2" t="n"/>
       <c r="AS98" s="2" t="n"/>
       <c r="AT98" s="2" t="n"/>
+      <c r="AU98" s="2" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n"/>
@@ -5414,6 +5528,7 @@
       <c r="AR99" s="2" t="n"/>
       <c r="AS99" s="2" t="n"/>
       <c r="AT99" s="2" t="n"/>
+      <c r="AU99" s="2" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n"/>
@@ -5462,6 +5577,7 @@
       <c r="AR100" s="2" t="n"/>
       <c r="AS100" s="2" t="n"/>
       <c r="AT100" s="2" t="n"/>
+      <c r="AU100" s="2" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n"/>
@@ -5510,6 +5626,7 @@
       <c r="AR101" s="2" t="n"/>
       <c r="AS101" s="2" t="n"/>
       <c r="AT101" s="2" t="n"/>
+      <c r="AU101" s="2" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n"/>
@@ -5558,6 +5675,7 @@
       <c r="AR102" s="2" t="n"/>
       <c r="AS102" s="2" t="n"/>
       <c r="AT102" s="2" t="n"/>
+      <c r="AU102" s="2" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n"/>
@@ -5606,6 +5724,7 @@
       <c r="AR103" s="2" t="n"/>
       <c r="AS103" s="2" t="n"/>
       <c r="AT103" s="2" t="n"/>
+      <c r="AU103" s="2" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n"/>
@@ -5654,6 +5773,7 @@
       <c r="AR104" s="2" t="n"/>
       <c r="AS104" s="2" t="n"/>
       <c r="AT104" s="2" t="n"/>
+      <c r="AU104" s="2" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n"/>
@@ -5702,6 +5822,7 @@
       <c r="AR105" s="2" t="n"/>
       <c r="AS105" s="2" t="n"/>
       <c r="AT105" s="2" t="n"/>
+      <c r="AU105" s="2" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n"/>
@@ -5750,6 +5871,7 @@
       <c r="AR106" s="2" t="n"/>
       <c r="AS106" s="2" t="n"/>
       <c r="AT106" s="2" t="n"/>
+      <c r="AU106" s="2" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n"/>
@@ -5798,6 +5920,7 @@
       <c r="AR107" s="2" t="n"/>
       <c r="AS107" s="2" t="n"/>
       <c r="AT107" s="2" t="n"/>
+      <c r="AU107" s="2" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n"/>
@@ -5846,6 +5969,7 @@
       <c r="AR108" s="2" t="n"/>
       <c r="AS108" s="2" t="n"/>
       <c r="AT108" s="2" t="n"/>
+      <c r="AU108" s="2" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n"/>
@@ -5894,6 +6018,7 @@
       <c r="AR109" s="2" t="n"/>
       <c r="AS109" s="2" t="n"/>
       <c r="AT109" s="2" t="n"/>
+      <c r="AU109" s="2" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n"/>
@@ -5942,6 +6067,7 @@
       <c r="AR110" s="2" t="n"/>
       <c r="AS110" s="2" t="n"/>
       <c r="AT110" s="2" t="n"/>
+      <c r="AU110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n"/>
@@ -5990,6 +6116,7 @@
       <c r="AR111" s="2" t="n"/>
       <c r="AS111" s="2" t="n"/>
       <c r="AT111" s="2" t="n"/>
+      <c r="AU111" s="2" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n"/>
@@ -6038,6 +6165,7 @@
       <c r="AR112" s="2" t="n"/>
       <c r="AS112" s="2" t="n"/>
       <c r="AT112" s="2" t="n"/>
+      <c r="AU112" s="2" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n"/>
@@ -6086,6 +6214,7 @@
       <c r="AR113" s="2" t="n"/>
       <c r="AS113" s="2" t="n"/>
       <c r="AT113" s="2" t="n"/>
+      <c r="AU113" s="2" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n"/>
@@ -6134,6 +6263,7 @@
       <c r="AR114" s="2" t="n"/>
       <c r="AS114" s="2" t="n"/>
       <c r="AT114" s="2" t="n"/>
+      <c r="AU114" s="2" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n"/>
@@ -6182,6 +6312,7 @@
       <c r="AR115" s="2" t="n"/>
       <c r="AS115" s="2" t="n"/>
       <c r="AT115" s="2" t="n"/>
+      <c r="AU115" s="2" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n"/>
@@ -6230,6 +6361,7 @@
       <c r="AR116" s="2" t="n"/>
       <c r="AS116" s="2" t="n"/>
       <c r="AT116" s="2" t="n"/>
+      <c r="AU116" s="2" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n"/>
@@ -6278,6 +6410,7 @@
       <c r="AR117" s="2" t="n"/>
       <c r="AS117" s="2" t="n"/>
       <c r="AT117" s="2" t="n"/>
+      <c r="AU117" s="2" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n"/>
@@ -6326,6 +6459,7 @@
       <c r="AR118" s="2" t="n"/>
       <c r="AS118" s="2" t="n"/>
       <c r="AT118" s="2" t="n"/>
+      <c r="AU118" s="2" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n"/>
@@ -6374,6 +6508,7 @@
       <c r="AR119" s="2" t="n"/>
       <c r="AS119" s="2" t="n"/>
       <c r="AT119" s="2" t="n"/>
+      <c r="AU119" s="2" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n"/>
@@ -6422,6 +6557,7 @@
       <c r="AR120" s="2" t="n"/>
       <c r="AS120" s="2" t="n"/>
       <c r="AT120" s="2" t="n"/>
+      <c r="AU120" s="2" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n"/>
@@ -6470,6 +6606,7 @@
       <c r="AR121" s="2" t="n"/>
       <c r="AS121" s="2" t="n"/>
       <c r="AT121" s="2" t="n"/>
+      <c r="AU121" s="2" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n"/>
@@ -6518,6 +6655,7 @@
       <c r="AR122" s="2" t="n"/>
       <c r="AS122" s="2" t="n"/>
       <c r="AT122" s="2" t="n"/>
+      <c r="AU122" s="2" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n"/>
@@ -6566,6 +6704,7 @@
       <c r="AR123" s="2" t="n"/>
       <c r="AS123" s="2" t="n"/>
       <c r="AT123" s="2" t="n"/>
+      <c r="AU123" s="2" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n"/>
@@ -6614,6 +6753,7 @@
       <c r="AR124" s="2" t="n"/>
       <c r="AS124" s="2" t="n"/>
       <c r="AT124" s="2" t="n"/>
+      <c r="AU124" s="2" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n"/>
@@ -6662,6 +6802,7 @@
       <c r="AR125" s="2" t="n"/>
       <c r="AS125" s="2" t="n"/>
       <c r="AT125" s="2" t="n"/>
+      <c r="AU125" s="2" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n"/>
@@ -6710,6 +6851,7 @@
       <c r="AR126" s="2" t="n"/>
       <c r="AS126" s="2" t="n"/>
       <c r="AT126" s="2" t="n"/>
+      <c r="AU126" s="2" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n"/>
@@ -6758,6 +6900,7 @@
       <c r="AR127" s="2" t="n"/>
       <c r="AS127" s="2" t="n"/>
       <c r="AT127" s="2" t="n"/>
+      <c r="AU127" s="2" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n"/>
@@ -6806,6 +6949,7 @@
       <c r="AR128" s="2" t="n"/>
       <c r="AS128" s="2" t="n"/>
       <c r="AT128" s="2" t="n"/>
+      <c r="AU128" s="2" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n"/>
@@ -6854,6 +6998,7 @@
       <c r="AR129" s="2" t="n"/>
       <c r="AS129" s="2" t="n"/>
       <c r="AT129" s="2" t="n"/>
+      <c r="AU129" s="2" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n"/>
@@ -6902,6 +7047,7 @@
       <c r="AR130" s="2" t="n"/>
       <c r="AS130" s="2" t="n"/>
       <c r="AT130" s="2" t="n"/>
+      <c r="AU130" s="2" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n"/>
@@ -6950,6 +7096,7 @@
       <c r="AR131" s="2" t="n"/>
       <c r="AS131" s="2" t="n"/>
       <c r="AT131" s="2" t="n"/>
+      <c r="AU131" s="2" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n"/>
@@ -6998,6 +7145,7 @@
       <c r="AR132" s="2" t="n"/>
       <c r="AS132" s="2" t="n"/>
       <c r="AT132" s="2" t="n"/>
+      <c r="AU132" s="2" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n"/>
@@ -7046,6 +7194,7 @@
       <c r="AR133" s="2" t="n"/>
       <c r="AS133" s="2" t="n"/>
       <c r="AT133" s="2" t="n"/>
+      <c r="AU133" s="2" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n"/>
@@ -7094,6 +7243,7 @@
       <c r="AR134" s="2" t="n"/>
       <c r="AS134" s="2" t="n"/>
       <c r="AT134" s="2" t="n"/>
+      <c r="AU134" s="2" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n"/>
@@ -7142,6 +7292,7 @@
       <c r="AR135" s="2" t="n"/>
       <c r="AS135" s="2" t="n"/>
       <c r="AT135" s="2" t="n"/>
+      <c r="AU135" s="2" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n"/>
@@ -7190,6 +7341,7 @@
       <c r="AR136" s="2" t="n"/>
       <c r="AS136" s="2" t="n"/>
       <c r="AT136" s="2" t="n"/>
+      <c r="AU136" s="2" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n"/>
@@ -7238,6 +7390,7 @@
       <c r="AR137" s="2" t="n"/>
       <c r="AS137" s="2" t="n"/>
       <c r="AT137" s="2" t="n"/>
+      <c r="AU137" s="2" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n"/>
@@ -7286,6 +7439,7 @@
       <c r="AR138" s="2" t="n"/>
       <c r="AS138" s="2" t="n"/>
       <c r="AT138" s="2" t="n"/>
+      <c r="AU138" s="2" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n"/>
@@ -7334,6 +7488,7 @@
       <c r="AR139" s="2" t="n"/>
       <c r="AS139" s="2" t="n"/>
       <c r="AT139" s="2" t="n"/>
+      <c r="AU139" s="2" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n"/>
@@ -7382,6 +7537,7 @@
       <c r="AR140" s="2" t="n"/>
       <c r="AS140" s="2" t="n"/>
       <c r="AT140" s="2" t="n"/>
+      <c r="AU140" s="2" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n"/>
@@ -7430,6 +7586,7 @@
       <c r="AR141" s="2" t="n"/>
       <c r="AS141" s="2" t="n"/>
       <c r="AT141" s="2" t="n"/>
+      <c r="AU141" s="2" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n"/>
@@ -7478,6 +7635,7 @@
       <c r="AR142" s="2" t="n"/>
       <c r="AS142" s="2" t="n"/>
       <c r="AT142" s="2" t="n"/>
+      <c r="AU142" s="2" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n"/>
@@ -7526,6 +7684,7 @@
       <c r="AR143" s="2" t="n"/>
       <c r="AS143" s="2" t="n"/>
       <c r="AT143" s="2" t="n"/>
+      <c r="AU143" s="2" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n"/>
@@ -7574,6 +7733,7 @@
       <c r="AR144" s="2" t="n"/>
       <c r="AS144" s="2" t="n"/>
       <c r="AT144" s="2" t="n"/>
+      <c r="AU144" s="2" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n"/>
@@ -7622,6 +7782,7 @@
       <c r="AR145" s="2" t="n"/>
       <c r="AS145" s="2" t="n"/>
       <c r="AT145" s="2" t="n"/>
+      <c r="AU145" s="2" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n"/>
@@ -7670,6 +7831,7 @@
       <c r="AR146" s="2" t="n"/>
       <c r="AS146" s="2" t="n"/>
       <c r="AT146" s="2" t="n"/>
+      <c r="AU146" s="2" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n"/>
@@ -7718,6 +7880,7 @@
       <c r="AR147" s="2" t="n"/>
       <c r="AS147" s="2" t="n"/>
       <c r="AT147" s="2" t="n"/>
+      <c r="AU147" s="2" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n"/>
@@ -7766,6 +7929,7 @@
       <c r="AR148" s="2" t="n"/>
       <c r="AS148" s="2" t="n"/>
       <c r="AT148" s="2" t="n"/>
+      <c r="AU148" s="2" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n"/>
@@ -7814,6 +7978,7 @@
       <c r="AR149" s="2" t="n"/>
       <c r="AS149" s="2" t="n"/>
       <c r="AT149" s="2" t="n"/>
+      <c r="AU149" s="2" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n"/>
@@ -7862,6 +8027,7 @@
       <c r="AR150" s="2" t="n"/>
       <c r="AS150" s="2" t="n"/>
       <c r="AT150" s="2" t="n"/>
+      <c r="AU150" s="2" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n"/>
@@ -7910,6 +8076,7 @@
       <c r="AR151" s="2" t="n"/>
       <c r="AS151" s="2" t="n"/>
       <c r="AT151" s="2" t="n"/>
+      <c r="AU151" s="2" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n"/>
@@ -7958,6 +8125,7 @@
       <c r="AR152" s="2" t="n"/>
       <c r="AS152" s="2" t="n"/>
       <c r="AT152" s="2" t="n"/>
+      <c r="AU152" s="2" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n"/>
@@ -8006,6 +8174,7 @@
       <c r="AR153" s="2" t="n"/>
       <c r="AS153" s="2" t="n"/>
       <c r="AT153" s="2" t="n"/>
+      <c r="AU153" s="2" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n"/>
@@ -8054,6 +8223,7 @@
       <c r="AR154" s="2" t="n"/>
       <c r="AS154" s="2" t="n"/>
       <c r="AT154" s="2" t="n"/>
+      <c r="AU154" s="2" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n"/>
@@ -8102,6 +8272,7 @@
       <c r="AR155" s="2" t="n"/>
       <c r="AS155" s="2" t="n"/>
       <c r="AT155" s="2" t="n"/>
+      <c r="AU155" s="2" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n"/>
@@ -8150,6 +8321,7 @@
       <c r="AR156" s="2" t="n"/>
       <c r="AS156" s="2" t="n"/>
       <c r="AT156" s="2" t="n"/>
+      <c r="AU156" s="2" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n"/>
@@ -8198,6 +8370,7 @@
       <c r="AR157" s="2" t="n"/>
       <c r="AS157" s="2" t="n"/>
       <c r="AT157" s="2" t="n"/>
+      <c r="AU157" s="2" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n"/>
@@ -8246,6 +8419,7 @@
       <c r="AR158" s="2" t="n"/>
       <c r="AS158" s="2" t="n"/>
       <c r="AT158" s="2" t="n"/>
+      <c r="AU158" s="2" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n"/>
@@ -8294,6 +8468,7 @@
       <c r="AR159" s="2" t="n"/>
       <c r="AS159" s="2" t="n"/>
       <c r="AT159" s="2" t="n"/>
+      <c r="AU159" s="2" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n"/>
@@ -8342,6 +8517,7 @@
       <c r="AR160" s="2" t="n"/>
       <c r="AS160" s="2" t="n"/>
       <c r="AT160" s="2" t="n"/>
+      <c r="AU160" s="2" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n"/>
@@ -8390,6 +8566,7 @@
       <c r="AR161" s="2" t="n"/>
       <c r="AS161" s="2" t="n"/>
       <c r="AT161" s="2" t="n"/>
+      <c r="AU161" s="2" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n"/>
@@ -8438,6 +8615,7 @@
       <c r="AR162" s="2" t="n"/>
       <c r="AS162" s="2" t="n"/>
       <c r="AT162" s="2" t="n"/>
+      <c r="AU162" s="2" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n"/>
@@ -8486,6 +8664,7 @@
       <c r="AR163" s="2" t="n"/>
       <c r="AS163" s="2" t="n"/>
       <c r="AT163" s="2" t="n"/>
+      <c r="AU163" s="2" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n"/>
@@ -8534,6 +8713,7 @@
       <c r="AR164" s="2" t="n"/>
       <c r="AS164" s="2" t="n"/>
       <c r="AT164" s="2" t="n"/>
+      <c r="AU164" s="2" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n"/>
@@ -8582,6 +8762,7 @@
       <c r="AR165" s="2" t="n"/>
       <c r="AS165" s="2" t="n"/>
       <c r="AT165" s="2" t="n"/>
+      <c r="AU165" s="2" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n"/>
@@ -8630,6 +8811,7 @@
       <c r="AR166" s="2" t="n"/>
       <c r="AS166" s="2" t="n"/>
       <c r="AT166" s="2" t="n"/>
+      <c r="AU166" s="2" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n"/>
@@ -8678,6 +8860,7 @@
       <c r="AR167" s="2" t="n"/>
       <c r="AS167" s="2" t="n"/>
       <c r="AT167" s="2" t="n"/>
+      <c r="AU167" s="2" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n"/>
@@ -8726,6 +8909,7 @@
       <c r="AR168" s="2" t="n"/>
       <c r="AS168" s="2" t="n"/>
       <c r="AT168" s="2" t="n"/>
+      <c r="AU168" s="2" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n"/>
@@ -8774,6 +8958,7 @@
       <c r="AR169" s="2" t="n"/>
       <c r="AS169" s="2" t="n"/>
       <c r="AT169" s="2" t="n"/>
+      <c r="AU169" s="2" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n"/>
@@ -8822,6 +9007,7 @@
       <c r="AR170" s="2" t="n"/>
       <c r="AS170" s="2" t="n"/>
       <c r="AT170" s="2" t="n"/>
+      <c r="AU170" s="2" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n"/>
@@ -8870,6 +9056,7 @@
       <c r="AR171" s="2" t="n"/>
       <c r="AS171" s="2" t="n"/>
       <c r="AT171" s="2" t="n"/>
+      <c r="AU171" s="2" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n"/>
@@ -8918,6 +9105,7 @@
       <c r="AR172" s="2" t="n"/>
       <c r="AS172" s="2" t="n"/>
       <c r="AT172" s="2" t="n"/>
+      <c r="AU172" s="2" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n"/>
@@ -8966,6 +9154,7 @@
       <c r="AR173" s="2" t="n"/>
       <c r="AS173" s="2" t="n"/>
       <c r="AT173" s="2" t="n"/>
+      <c r="AU173" s="2" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n"/>
@@ -9014,6 +9203,7 @@
       <c r="AR174" s="2" t="n"/>
       <c r="AS174" s="2" t="n"/>
       <c r="AT174" s="2" t="n"/>
+      <c r="AU174" s="2" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n"/>
@@ -9062,6 +9252,7 @@
       <c r="AR175" s="2" t="n"/>
       <c r="AS175" s="2" t="n"/>
       <c r="AT175" s="2" t="n"/>
+      <c r="AU175" s="2" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n"/>
@@ -9110,6 +9301,7 @@
       <c r="AR176" s="2" t="n"/>
       <c r="AS176" s="2" t="n"/>
       <c r="AT176" s="2" t="n"/>
+      <c r="AU176" s="2" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n"/>
@@ -9158,6 +9350,7 @@
       <c r="AR177" s="2" t="n"/>
       <c r="AS177" s="2" t="n"/>
       <c r="AT177" s="2" t="n"/>
+      <c r="AU177" s="2" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n"/>
@@ -9206,6 +9399,7 @@
       <c r="AR178" s="2" t="n"/>
       <c r="AS178" s="2" t="n"/>
       <c r="AT178" s="2" t="n"/>
+      <c r="AU178" s="2" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n"/>
@@ -9254,6 +9448,7 @@
       <c r="AR179" s="2" t="n"/>
       <c r="AS179" s="2" t="n"/>
       <c r="AT179" s="2" t="n"/>
+      <c r="AU179" s="2" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n"/>
@@ -9302,6 +9497,7 @@
       <c r="AR180" s="2" t="n"/>
       <c r="AS180" s="2" t="n"/>
       <c r="AT180" s="2" t="n"/>
+      <c r="AU180" s="2" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n"/>
@@ -9350,6 +9546,7 @@
       <c r="AR181" s="2" t="n"/>
       <c r="AS181" s="2" t="n"/>
       <c r="AT181" s="2" t="n"/>
+      <c r="AU181" s="2" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n"/>
@@ -9398,6 +9595,7 @@
       <c r="AR182" s="2" t="n"/>
       <c r="AS182" s="2" t="n"/>
       <c r="AT182" s="2" t="n"/>
+      <c r="AU182" s="2" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n"/>
@@ -9446,6 +9644,7 @@
       <c r="AR183" s="2" t="n"/>
       <c r="AS183" s="2" t="n"/>
       <c r="AT183" s="2" t="n"/>
+      <c r="AU183" s="2" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n"/>
@@ -9494,6 +9693,7 @@
       <c r="AR184" s="2" t="n"/>
       <c r="AS184" s="2" t="n"/>
       <c r="AT184" s="2" t="n"/>
+      <c r="AU184" s="2" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n"/>
@@ -9542,6 +9742,7 @@
       <c r="AR185" s="2" t="n"/>
       <c r="AS185" s="2" t="n"/>
       <c r="AT185" s="2" t="n"/>
+      <c r="AU185" s="2" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n"/>
@@ -9590,6 +9791,7 @@
       <c r="AR186" s="2" t="n"/>
       <c r="AS186" s="2" t="n"/>
       <c r="AT186" s="2" t="n"/>
+      <c r="AU186" s="2" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n"/>
@@ -9638,6 +9840,7 @@
       <c r="AR187" s="2" t="n"/>
       <c r="AS187" s="2" t="n"/>
       <c r="AT187" s="2" t="n"/>
+      <c r="AU187" s="2" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n"/>
@@ -9686,6 +9889,7 @@
       <c r="AR188" s="2" t="n"/>
       <c r="AS188" s="2" t="n"/>
       <c r="AT188" s="2" t="n"/>
+      <c r="AU188" s="2" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n"/>
@@ -9734,6 +9938,7 @@
       <c r="AR189" s="2" t="n"/>
       <c r="AS189" s="2" t="n"/>
       <c r="AT189" s="2" t="n"/>
+      <c r="AU189" s="2" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n"/>
@@ -9782,6 +9987,7 @@
       <c r="AR190" s="2" t="n"/>
       <c r="AS190" s="2" t="n"/>
       <c r="AT190" s="2" t="n"/>
+      <c r="AU190" s="2" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n"/>
@@ -9830,6 +10036,7 @@
       <c r="AR191" s="2" t="n"/>
       <c r="AS191" s="2" t="n"/>
       <c r="AT191" s="2" t="n"/>
+      <c r="AU191" s="2" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n"/>
@@ -9878,6 +10085,7 @@
       <c r="AR192" s="2" t="n"/>
       <c r="AS192" s="2" t="n"/>
       <c r="AT192" s="2" t="n"/>
+      <c r="AU192" s="2" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n"/>
@@ -9926,6 +10134,7 @@
       <c r="AR193" s="2" t="n"/>
       <c r="AS193" s="2" t="n"/>
       <c r="AT193" s="2" t="n"/>
+      <c r="AU193" s="2" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n"/>
@@ -9974,6 +10183,7 @@
       <c r="AR194" s="2" t="n"/>
       <c r="AS194" s="2" t="n"/>
       <c r="AT194" s="2" t="n"/>
+      <c r="AU194" s="2" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n"/>
@@ -10022,6 +10232,7 @@
       <c r="AR195" s="2" t="n"/>
       <c r="AS195" s="2" t="n"/>
       <c r="AT195" s="2" t="n"/>
+      <c r="AU195" s="2" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n"/>
@@ -10070,6 +10281,7 @@
       <c r="AR196" s="2" t="n"/>
       <c r="AS196" s="2" t="n"/>
       <c r="AT196" s="2" t="n"/>
+      <c r="AU196" s="2" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n"/>
@@ -10118,6 +10330,7 @@
       <c r="AR197" s="2" t="n"/>
       <c r="AS197" s="2" t="n"/>
       <c r="AT197" s="2" t="n"/>
+      <c r="AU197" s="2" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n"/>
@@ -10166,6 +10379,7 @@
       <c r="AR198" s="2" t="n"/>
       <c r="AS198" s="2" t="n"/>
       <c r="AT198" s="2" t="n"/>
+      <c r="AU198" s="2" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n"/>
@@ -10214,6 +10428,7 @@
       <c r="AR199" s="2" t="n"/>
       <c r="AS199" s="2" t="n"/>
       <c r="AT199" s="2" t="n"/>
+      <c r="AU199" s="2" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n"/>
@@ -10262,6 +10477,7 @@
       <c r="AR200" s="2" t="n"/>
       <c r="AS200" s="2" t="n"/>
       <c r="AT200" s="2" t="n"/>
+      <c r="AU200" s="2" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n"/>
@@ -10310,6 +10526,7 @@
       <c r="AR201" s="2" t="n"/>
       <c r="AS201" s="2" t="n"/>
       <c r="AT201" s="2" t="n"/>
+      <c r="AU201" s="2" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n"/>
@@ -10358,6 +10575,7 @@
       <c r="AR202" s="2" t="n"/>
       <c r="AS202" s="2" t="n"/>
       <c r="AT202" s="2" t="n"/>
+      <c r="AU202" s="2" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n"/>
@@ -10406,6 +10624,7 @@
       <c r="AR203" s="2" t="n"/>
       <c r="AS203" s="2" t="n"/>
       <c r="AT203" s="2" t="n"/>
+      <c r="AU203" s="2" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n"/>
@@ -10454,6 +10673,7 @@
       <c r="AR204" s="2" t="n"/>
       <c r="AS204" s="2" t="n"/>
       <c r="AT204" s="2" t="n"/>
+      <c r="AU204" s="2" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n"/>
@@ -10502,6 +10722,7 @@
       <c r="AR205" s="2" t="n"/>
       <c r="AS205" s="2" t="n"/>
       <c r="AT205" s="2" t="n"/>
+      <c r="AU205" s="2" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n"/>
@@ -10550,6 +10771,7 @@
       <c r="AR206" s="2" t="n"/>
       <c r="AS206" s="2" t="n"/>
       <c r="AT206" s="2" t="n"/>
+      <c r="AU206" s="2" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n"/>
@@ -10598,6 +10820,7 @@
       <c r="AR207" s="2" t="n"/>
       <c r="AS207" s="2" t="n"/>
       <c r="AT207" s="2" t="n"/>
+      <c r="AU207" s="2" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n"/>
@@ -10646,6 +10869,7 @@
       <c r="AR208" s="2" t="n"/>
       <c r="AS208" s="2" t="n"/>
       <c r="AT208" s="2" t="n"/>
+      <c r="AU208" s="2" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n"/>
@@ -10694,6 +10918,7 @@
       <c r="AR209" s="2" t="n"/>
       <c r="AS209" s="2" t="n"/>
       <c r="AT209" s="2" t="n"/>
+      <c r="AU209" s="2" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n"/>
@@ -10742,6 +10967,7 @@
       <c r="AR210" s="2" t="n"/>
       <c r="AS210" s="2" t="n"/>
       <c r="AT210" s="2" t="n"/>
+      <c r="AU210" s="2" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n"/>
@@ -10790,6 +11016,7 @@
       <c r="AR211" s="2" t="n"/>
       <c r="AS211" s="2" t="n"/>
       <c r="AT211" s="2" t="n"/>
+      <c r="AU211" s="2" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n"/>
@@ -10838,6 +11065,7 @@
       <c r="AR212" s="2" t="n"/>
       <c r="AS212" s="2" t="n"/>
       <c r="AT212" s="2" t="n"/>
+      <c r="AU212" s="2" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n"/>
@@ -10886,6 +11114,7 @@
       <c r="AR213" s="2" t="n"/>
       <c r="AS213" s="2" t="n"/>
       <c r="AT213" s="2" t="n"/>
+      <c r="AU213" s="2" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n"/>
@@ -10934,6 +11163,7 @@
       <c r="AR214" s="2" t="n"/>
       <c r="AS214" s="2" t="n"/>
       <c r="AT214" s="2" t="n"/>
+      <c r="AU214" s="2" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n"/>
@@ -10982,6 +11212,7 @@
       <c r="AR215" s="2" t="n"/>
       <c r="AS215" s="2" t="n"/>
       <c r="AT215" s="2" t="n"/>
+      <c r="AU215" s="2" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n"/>
@@ -11030,6 +11261,7 @@
       <c r="AR216" s="2" t="n"/>
       <c r="AS216" s="2" t="n"/>
       <c r="AT216" s="2" t="n"/>
+      <c r="AU216" s="2" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n"/>
@@ -11078,6 +11310,7 @@
       <c r="AR217" s="2" t="n"/>
       <c r="AS217" s="2" t="n"/>
       <c r="AT217" s="2" t="n"/>
+      <c r="AU217" s="2" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n"/>
@@ -11126,6 +11359,7 @@
       <c r="AR218" s="2" t="n"/>
       <c r="AS218" s="2" t="n"/>
       <c r="AT218" s="2" t="n"/>
+      <c r="AU218" s="2" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n"/>
@@ -11174,6 +11408,7 @@
       <c r="AR219" s="2" t="n"/>
       <c r="AS219" s="2" t="n"/>
       <c r="AT219" s="2" t="n"/>
+      <c r="AU219" s="2" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n"/>
@@ -11222,6 +11457,7 @@
       <c r="AR220" s="2" t="n"/>
       <c r="AS220" s="2" t="n"/>
       <c r="AT220" s="2" t="n"/>
+      <c r="AU220" s="2" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n"/>
@@ -11270,6 +11506,7 @@
       <c r="AR221" s="2" t="n"/>
       <c r="AS221" s="2" t="n"/>
       <c r="AT221" s="2" t="n"/>
+      <c r="AU221" s="2" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n"/>
@@ -11318,6 +11555,7 @@
       <c r="AR222" s="2" t="n"/>
       <c r="AS222" s="2" t="n"/>
       <c r="AT222" s="2" t="n"/>
+      <c r="AU222" s="2" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n"/>
@@ -11366,6 +11604,7 @@
       <c r="AR223" s="2" t="n"/>
       <c r="AS223" s="2" t="n"/>
       <c r="AT223" s="2" t="n"/>
+      <c r="AU223" s="2" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n"/>
@@ -11414,6 +11653,7 @@
       <c r="AR224" s="2" t="n"/>
       <c r="AS224" s="2" t="n"/>
       <c r="AT224" s="2" t="n"/>
+      <c r="AU224" s="2" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n"/>
@@ -11462,6 +11702,7 @@
       <c r="AR225" s="2" t="n"/>
       <c r="AS225" s="2" t="n"/>
       <c r="AT225" s="2" t="n"/>
+      <c r="AU225" s="2" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n"/>
@@ -11510,6 +11751,7 @@
       <c r="AR226" s="2" t="n"/>
       <c r="AS226" s="2" t="n"/>
       <c r="AT226" s="2" t="n"/>
+      <c r="AU226" s="2" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n"/>
@@ -11558,6 +11800,7 @@
       <c r="AR227" s="2" t="n"/>
       <c r="AS227" s="2" t="n"/>
       <c r="AT227" s="2" t="n"/>
+      <c r="AU227" s="2" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n"/>
@@ -11606,6 +11849,7 @@
       <c r="AR228" s="2" t="n"/>
       <c r="AS228" s="2" t="n"/>
       <c r="AT228" s="2" t="n"/>
+      <c r="AU228" s="2" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n"/>
@@ -11654,6 +11898,7 @@
       <c r="AR229" s="2" t="n"/>
       <c r="AS229" s="2" t="n"/>
       <c r="AT229" s="2" t="n"/>
+      <c r="AU229" s="2" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n"/>
@@ -11702,6 +11947,7 @@
       <c r="AR230" s="2" t="n"/>
       <c r="AS230" s="2" t="n"/>
       <c r="AT230" s="2" t="n"/>
+      <c r="AU230" s="2" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n"/>
@@ -11750,6 +11996,7 @@
       <c r="AR231" s="2" t="n"/>
       <c r="AS231" s="2" t="n"/>
       <c r="AT231" s="2" t="n"/>
+      <c r="AU231" s="2" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n"/>
@@ -11798,6 +12045,7 @@
       <c r="AR232" s="2" t="n"/>
       <c r="AS232" s="2" t="n"/>
       <c r="AT232" s="2" t="n"/>
+      <c r="AU232" s="2" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n"/>
@@ -11846,6 +12094,7 @@
       <c r="AR233" s="2" t="n"/>
       <c r="AS233" s="2" t="n"/>
       <c r="AT233" s="2" t="n"/>
+      <c r="AU233" s="2" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n"/>
@@ -11894,6 +12143,7 @@
       <c r="AR234" s="2" t="n"/>
       <c r="AS234" s="2" t="n"/>
       <c r="AT234" s="2" t="n"/>
+      <c r="AU234" s="2" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n"/>
@@ -11942,6 +12192,7 @@
       <c r="AR235" s="2" t="n"/>
       <c r="AS235" s="2" t="n"/>
       <c r="AT235" s="2" t="n"/>
+      <c r="AU235" s="2" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n"/>
@@ -11990,6 +12241,7 @@
       <c r="AR236" s="2" t="n"/>
       <c r="AS236" s="2" t="n"/>
       <c r="AT236" s="2" t="n"/>
+      <c r="AU236" s="2" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n"/>
@@ -12038,6 +12290,7 @@
       <c r="AR237" s="2" t="n"/>
       <c r="AS237" s="2" t="n"/>
       <c r="AT237" s="2" t="n"/>
+      <c r="AU237" s="2" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n"/>
@@ -12086,6 +12339,7 @@
       <c r="AR238" s="2" t="n"/>
       <c r="AS238" s="2" t="n"/>
       <c r="AT238" s="2" t="n"/>
+      <c r="AU238" s="2" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n"/>
@@ -12134,6 +12388,7 @@
       <c r="AR239" s="2" t="n"/>
       <c r="AS239" s="2" t="n"/>
       <c r="AT239" s="2" t="n"/>
+      <c r="AU239" s="2" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n"/>
@@ -12182,6 +12437,7 @@
       <c r="AR240" s="2" t="n"/>
       <c r="AS240" s="2" t="n"/>
       <c r="AT240" s="2" t="n"/>
+      <c r="AU240" s="2" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n"/>
@@ -12230,6 +12486,7 @@
       <c r="AR241" s="2" t="n"/>
       <c r="AS241" s="2" t="n"/>
       <c r="AT241" s="2" t="n"/>
+      <c r="AU241" s="2" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n"/>
@@ -12278,6 +12535,7 @@
       <c r="AR242" s="2" t="n"/>
       <c r="AS242" s="2" t="n"/>
       <c r="AT242" s="2" t="n"/>
+      <c r="AU242" s="2" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n"/>
@@ -12326,6 +12584,7 @@
       <c r="AR243" s="2" t="n"/>
       <c r="AS243" s="2" t="n"/>
       <c r="AT243" s="2" t="n"/>
+      <c r="AU243" s="2" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n"/>
@@ -12374,6 +12633,7 @@
       <c r="AR244" s="2" t="n"/>
       <c r="AS244" s="2" t="n"/>
       <c r="AT244" s="2" t="n"/>
+      <c r="AU244" s="2" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n"/>
@@ -12422,6 +12682,7 @@
       <c r="AR245" s="2" t="n"/>
       <c r="AS245" s="2" t="n"/>
       <c r="AT245" s="2" t="n"/>
+      <c r="AU245" s="2" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n"/>
@@ -12470,6 +12731,7 @@
       <c r="AR246" s="2" t="n"/>
       <c r="AS246" s="2" t="n"/>
       <c r="AT246" s="2" t="n"/>
+      <c r="AU246" s="2" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n"/>
@@ -12518,6 +12780,7 @@
       <c r="AR247" s="2" t="n"/>
       <c r="AS247" s="2" t="n"/>
       <c r="AT247" s="2" t="n"/>
+      <c r="AU247" s="2" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n"/>
@@ -12566,6 +12829,7 @@
       <c r="AR248" s="2" t="n"/>
       <c r="AS248" s="2" t="n"/>
       <c r="AT248" s="2" t="n"/>
+      <c r="AU248" s="2" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n"/>
@@ -12614,6 +12878,7 @@
       <c r="AR249" s="2" t="n"/>
       <c r="AS249" s="2" t="n"/>
       <c r="AT249" s="2" t="n"/>
+      <c r="AU249" s="2" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n"/>
@@ -12662,6 +12927,7 @@
       <c r="AR250" s="2" t="n"/>
       <c r="AS250" s="2" t="n"/>
       <c r="AT250" s="2" t="n"/>
+      <c r="AU250" s="2" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n"/>
@@ -12710,6 +12976,7 @@
       <c r="AR251" s="2" t="n"/>
       <c r="AS251" s="2" t="n"/>
       <c r="AT251" s="2" t="n"/>
+      <c r="AU251" s="2" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n"/>
@@ -12758,6 +13025,7 @@
       <c r="AR252" s="2" t="n"/>
       <c r="AS252" s="2" t="n"/>
       <c r="AT252" s="2" t="n"/>
+      <c r="AU252" s="2" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n"/>
@@ -12806,6 +13074,7 @@
       <c r="AR253" s="2" t="n"/>
       <c r="AS253" s="2" t="n"/>
       <c r="AT253" s="2" t="n"/>
+      <c r="AU253" s="2" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n"/>
@@ -12854,6 +13123,7 @@
       <c r="AR254" s="2" t="n"/>
       <c r="AS254" s="2" t="n"/>
       <c r="AT254" s="2" t="n"/>
+      <c r="AU254" s="2" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n"/>
@@ -12902,6 +13172,7 @@
       <c r="AR255" s="2" t="n"/>
       <c r="AS255" s="2" t="n"/>
       <c r="AT255" s="2" t="n"/>
+      <c r="AU255" s="2" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n"/>
@@ -12950,6 +13221,7 @@
       <c r="AR256" s="2" t="n"/>
       <c r="AS256" s="2" t="n"/>
       <c r="AT256" s="2" t="n"/>
+      <c r="AU256" s="2" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n"/>
@@ -12998,6 +13270,7 @@
       <c r="AR257" s="2" t="n"/>
       <c r="AS257" s="2" t="n"/>
       <c r="AT257" s="2" t="n"/>
+      <c r="AU257" s="2" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n"/>
@@ -13046,6 +13319,7 @@
       <c r="AR258" s="2" t="n"/>
       <c r="AS258" s="2" t="n"/>
       <c r="AT258" s="2" t="n"/>
+      <c r="AU258" s="2" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n"/>
@@ -13094,6 +13368,7 @@
       <c r="AR259" s="2" t="n"/>
       <c r="AS259" s="2" t="n"/>
       <c r="AT259" s="2" t="n"/>
+      <c r="AU259" s="2" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n"/>
@@ -13142,6 +13417,7 @@
       <c r="AR260" s="2" t="n"/>
       <c r="AS260" s="2" t="n"/>
       <c r="AT260" s="2" t="n"/>
+      <c r="AU260" s="2" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n"/>
@@ -13190,6 +13466,7 @@
       <c r="AR261" s="2" t="n"/>
       <c r="AS261" s="2" t="n"/>
       <c r="AT261" s="2" t="n"/>
+      <c r="AU261" s="2" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n"/>
@@ -13238,6 +13515,7 @@
       <c r="AR262" s="2" t="n"/>
       <c r="AS262" s="2" t="n"/>
       <c r="AT262" s="2" t="n"/>
+      <c r="AU262" s="2" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n"/>
@@ -13286,6 +13564,7 @@
       <c r="AR263" s="2" t="n"/>
       <c r="AS263" s="2" t="n"/>
       <c r="AT263" s="2" t="n"/>
+      <c r="AU263" s="2" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n"/>
@@ -13334,6 +13613,7 @@
       <c r="AR264" s="2" t="n"/>
       <c r="AS264" s="2" t="n"/>
       <c r="AT264" s="2" t="n"/>
+      <c r="AU264" s="2" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n"/>
@@ -13382,6 +13662,7 @@
       <c r="AR265" s="2" t="n"/>
       <c r="AS265" s="2" t="n"/>
       <c r="AT265" s="2" t="n"/>
+      <c r="AU265" s="2" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n"/>
@@ -13430,6 +13711,7 @@
       <c r="AR266" s="2" t="n"/>
       <c r="AS266" s="2" t="n"/>
       <c r="AT266" s="2" t="n"/>
+      <c r="AU266" s="2" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n"/>
@@ -13478,6 +13760,7 @@
       <c r="AR267" s="2" t="n"/>
       <c r="AS267" s="2" t="n"/>
       <c r="AT267" s="2" t="n"/>
+      <c r="AU267" s="2" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n"/>
@@ -13526,6 +13809,7 @@
       <c r="AR268" s="2" t="n"/>
       <c r="AS268" s="2" t="n"/>
       <c r="AT268" s="2" t="n"/>
+      <c r="AU268" s="2" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n"/>
@@ -13574,6 +13858,7 @@
       <c r="AR269" s="2" t="n"/>
       <c r="AS269" s="2" t="n"/>
       <c r="AT269" s="2" t="n"/>
+      <c r="AU269" s="2" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n"/>
@@ -13622,6 +13907,7 @@
       <c r="AR270" s="2" t="n"/>
       <c r="AS270" s="2" t="n"/>
       <c r="AT270" s="2" t="n"/>
+      <c r="AU270" s="2" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n"/>
@@ -13670,6 +13956,7 @@
       <c r="AR271" s="2" t="n"/>
       <c r="AS271" s="2" t="n"/>
       <c r="AT271" s="2" t="n"/>
+      <c r="AU271" s="2" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n"/>
@@ -13718,6 +14005,7 @@
       <c r="AR272" s="2" t="n"/>
       <c r="AS272" s="2" t="n"/>
       <c r="AT272" s="2" t="n"/>
+      <c r="AU272" s="2" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n"/>
@@ -13766,6 +14054,7 @@
       <c r="AR273" s="2" t="n"/>
       <c r="AS273" s="2" t="n"/>
       <c r="AT273" s="2" t="n"/>
+      <c r="AU273" s="2" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n"/>
@@ -13814,6 +14103,7 @@
       <c r="AR274" s="2" t="n"/>
       <c r="AS274" s="2" t="n"/>
       <c r="AT274" s="2" t="n"/>
+      <c r="AU274" s="2" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n"/>
@@ -13862,6 +14152,7 @@
       <c r="AR275" s="2" t="n"/>
       <c r="AS275" s="2" t="n"/>
       <c r="AT275" s="2" t="n"/>
+      <c r="AU275" s="2" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n"/>
@@ -13910,6 +14201,7 @@
       <c r="AR276" s="2" t="n"/>
       <c r="AS276" s="2" t="n"/>
       <c r="AT276" s="2" t="n"/>
+      <c r="AU276" s="2" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n"/>
@@ -13958,6 +14250,7 @@
       <c r="AR277" s="2" t="n"/>
       <c r="AS277" s="2" t="n"/>
       <c r="AT277" s="2" t="n"/>
+      <c r="AU277" s="2" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n"/>
@@ -14006,6 +14299,7 @@
       <c r="AR278" s="2" t="n"/>
       <c r="AS278" s="2" t="n"/>
       <c r="AT278" s="2" t="n"/>
+      <c r="AU278" s="2" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n"/>
@@ -14054,6 +14348,7 @@
       <c r="AR279" s="2" t="n"/>
       <c r="AS279" s="2" t="n"/>
       <c r="AT279" s="2" t="n"/>
+      <c r="AU279" s="2" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n"/>
@@ -14102,6 +14397,7 @@
       <c r="AR280" s="2" t="n"/>
       <c r="AS280" s="2" t="n"/>
       <c r="AT280" s="2" t="n"/>
+      <c r="AU280" s="2" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n"/>
@@ -14150,6 +14446,7 @@
       <c r="AR281" s="2" t="n"/>
       <c r="AS281" s="2" t="n"/>
       <c r="AT281" s="2" t="n"/>
+      <c r="AU281" s="2" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n"/>
@@ -14198,6 +14495,7 @@
       <c r="AR282" s="2" t="n"/>
       <c r="AS282" s="2" t="n"/>
       <c r="AT282" s="2" t="n"/>
+      <c r="AU282" s="2" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n"/>
@@ -14246,6 +14544,7 @@
       <c r="AR283" s="2" t="n"/>
       <c r="AS283" s="2" t="n"/>
       <c r="AT283" s="2" t="n"/>
+      <c r="AU283" s="2" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n"/>
@@ -14294,6 +14593,7 @@
       <c r="AR284" s="2" t="n"/>
       <c r="AS284" s="2" t="n"/>
       <c r="AT284" s="2" t="n"/>
+      <c r="AU284" s="2" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n"/>
@@ -14342,6 +14642,7 @@
       <c r="AR285" s="2" t="n"/>
       <c r="AS285" s="2" t="n"/>
       <c r="AT285" s="2" t="n"/>
+      <c r="AU285" s="2" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n"/>
@@ -14390,6 +14691,7 @@
       <c r="AR286" s="2" t="n"/>
       <c r="AS286" s="2" t="n"/>
       <c r="AT286" s="2" t="n"/>
+      <c r="AU286" s="2" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n"/>
@@ -14438,6 +14740,7 @@
       <c r="AR287" s="2" t="n"/>
       <c r="AS287" s="2" t="n"/>
       <c r="AT287" s="2" t="n"/>
+      <c r="AU287" s="2" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n"/>
@@ -14486,6 +14789,7 @@
       <c r="AR288" s="2" t="n"/>
       <c r="AS288" s="2" t="n"/>
       <c r="AT288" s="2" t="n"/>
+      <c r="AU288" s="2" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n"/>
@@ -14534,6 +14838,7 @@
       <c r="AR289" s="2" t="n"/>
       <c r="AS289" s="2" t="n"/>
       <c r="AT289" s="2" t="n"/>
+      <c r="AU289" s="2" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n"/>
@@ -14582,6 +14887,7 @@
       <c r="AR290" s="2" t="n"/>
       <c r="AS290" s="2" t="n"/>
       <c r="AT290" s="2" t="n"/>
+      <c r="AU290" s="2" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n"/>
@@ -14630,6 +14936,7 @@
       <c r="AR291" s="2" t="n"/>
       <c r="AS291" s="2" t="n"/>
       <c r="AT291" s="2" t="n"/>
+      <c r="AU291" s="2" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n"/>
@@ -14678,6 +14985,7 @@
       <c r="AR292" s="2" t="n"/>
       <c r="AS292" s="2" t="n"/>
       <c r="AT292" s="2" t="n"/>
+      <c r="AU292" s="2" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n"/>
@@ -14726,6 +15034,7 @@
       <c r="AR293" s="2" t="n"/>
       <c r="AS293" s="2" t="n"/>
       <c r="AT293" s="2" t="n"/>
+      <c r="AU293" s="2" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n"/>
@@ -14774,6 +15083,7 @@
       <c r="AR294" s="2" t="n"/>
       <c r="AS294" s="2" t="n"/>
       <c r="AT294" s="2" t="n"/>
+      <c r="AU294" s="2" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n"/>
@@ -14822,6 +15132,7 @@
       <c r="AR295" s="2" t="n"/>
       <c r="AS295" s="2" t="n"/>
       <c r="AT295" s="2" t="n"/>
+      <c r="AU295" s="2" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n"/>
@@ -14870,6 +15181,7 @@
       <c r="AR296" s="2" t="n"/>
       <c r="AS296" s="2" t="n"/>
       <c r="AT296" s="2" t="n"/>
+      <c r="AU296" s="2" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n"/>
@@ -14918,6 +15230,7 @@
       <c r="AR297" s="2" t="n"/>
       <c r="AS297" s="2" t="n"/>
       <c r="AT297" s="2" t="n"/>
+      <c r="AU297" s="2" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n"/>
@@ -14966,6 +15279,7 @@
       <c r="AR298" s="2" t="n"/>
       <c r="AS298" s="2" t="n"/>
       <c r="AT298" s="2" t="n"/>
+      <c r="AU298" s="2" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n"/>
@@ -15014,6 +15328,7 @@
       <c r="AR299" s="2" t="n"/>
       <c r="AS299" s="2" t="n"/>
       <c r="AT299" s="2" t="n"/>
+      <c r="AU299" s="2" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n"/>
@@ -15062,6 +15377,7 @@
       <c r="AR300" s="2" t="n"/>
       <c r="AS300" s="2" t="n"/>
       <c r="AT300" s="2" t="n"/>
+      <c r="AU300" s="2" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n"/>
@@ -15110,6 +15426,7 @@
       <c r="AR301" s="2" t="n"/>
       <c r="AS301" s="2" t="n"/>
       <c r="AT301" s="2" t="n"/>
+      <c r="AU301" s="2" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="n"/>
@@ -15158,6 +15475,7 @@
       <c r="AR302" s="2" t="n"/>
       <c r="AS302" s="2" t="n"/>
       <c r="AT302" s="2" t="n"/>
+      <c r="AU302" s="2" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="2" t="n"/>
@@ -15206,6 +15524,7 @@
       <c r="AR303" s="2" t="n"/>
       <c r="AS303" s="2" t="n"/>
       <c r="AT303" s="2" t="n"/>
+      <c r="AU303" s="2" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="n"/>
@@ -15254,6 +15573,7 @@
       <c r="AR304" s="2" t="n"/>
       <c r="AS304" s="2" t="n"/>
       <c r="AT304" s="2" t="n"/>
+      <c r="AU304" s="2" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="n"/>
@@ -15302,6 +15622,7 @@
       <c r="AR305" s="2" t="n"/>
       <c r="AS305" s="2" t="n"/>
       <c r="AT305" s="2" t="n"/>
+      <c r="AU305" s="2" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="n"/>
@@ -15350,6 +15671,7 @@
       <c r="AR306" s="2" t="n"/>
       <c r="AS306" s="2" t="n"/>
       <c r="AT306" s="2" t="n"/>
+      <c r="AU306" s="2" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="2" t="n"/>
@@ -15398,6 +15720,7 @@
       <c r="AR307" s="2" t="n"/>
       <c r="AS307" s="2" t="n"/>
       <c r="AT307" s="2" t="n"/>
+      <c r="AU307" s="2" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="n"/>
@@ -15446,6 +15769,7 @@
       <c r="AR308" s="2" t="n"/>
       <c r="AS308" s="2" t="n"/>
       <c r="AT308" s="2" t="n"/>
+      <c r="AU308" s="2" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="n"/>
@@ -15494,6 +15818,7 @@
       <c r="AR309" s="2" t="n"/>
       <c r="AS309" s="2" t="n"/>
       <c r="AT309" s="2" t="n"/>
+      <c r="AU309" s="2" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="n"/>
@@ -15542,6 +15867,7 @@
       <c r="AR310" s="2" t="n"/>
       <c r="AS310" s="2" t="n"/>
       <c r="AT310" s="2" t="n"/>
+      <c r="AU310" s="2" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="2" t="n"/>
@@ -15590,6 +15916,7 @@
       <c r="AR311" s="2" t="n"/>
       <c r="AS311" s="2" t="n"/>
       <c r="AT311" s="2" t="n"/>
+      <c r="AU311" s="2" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="n"/>
@@ -15638,6 +15965,7 @@
       <c r="AR312" s="2" t="n"/>
       <c r="AS312" s="2" t="n"/>
       <c r="AT312" s="2" t="n"/>
+      <c r="AU312" s="2" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="2" t="n"/>
@@ -15686,6 +16014,7 @@
       <c r="AR313" s="2" t="n"/>
       <c r="AS313" s="2" t="n"/>
       <c r="AT313" s="2" t="n"/>
+      <c r="AU313" s="2" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="n"/>
@@ -15734,6 +16063,7 @@
       <c r="AR314" s="2" t="n"/>
       <c r="AS314" s="2" t="n"/>
       <c r="AT314" s="2" t="n"/>
+      <c r="AU314" s="2" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="n"/>
@@ -15782,6 +16112,7 @@
       <c r="AR315" s="2" t="n"/>
       <c r="AS315" s="2" t="n"/>
       <c r="AT315" s="2" t="n"/>
+      <c r="AU315" s="2" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="n"/>
@@ -15830,6 +16161,7 @@
       <c r="AR316" s="2" t="n"/>
       <c r="AS316" s="2" t="n"/>
       <c r="AT316" s="2" t="n"/>
+      <c r="AU316" s="2" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="2" t="n"/>
@@ -15878,6 +16210,7 @@
       <c r="AR317" s="2" t="n"/>
       <c r="AS317" s="2" t="n"/>
       <c r="AT317" s="2" t="n"/>
+      <c r="AU317" s="2" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="n"/>
@@ -15926,6 +16259,7 @@
       <c r="AR318" s="2" t="n"/>
       <c r="AS318" s="2" t="n"/>
       <c r="AT318" s="2" t="n"/>
+      <c r="AU318" s="2" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="n"/>
@@ -15974,6 +16308,7 @@
       <c r="AR319" s="2" t="n"/>
       <c r="AS319" s="2" t="n"/>
       <c r="AT319" s="2" t="n"/>
+      <c r="AU319" s="2" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="n"/>
@@ -16022,6 +16357,7 @@
       <c r="AR320" s="2" t="n"/>
       <c r="AS320" s="2" t="n"/>
       <c r="AT320" s="2" t="n"/>
+      <c r="AU320" s="2" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="2" t="n"/>
@@ -16070,6 +16406,7 @@
       <c r="AR321" s="2" t="n"/>
       <c r="AS321" s="2" t="n"/>
       <c r="AT321" s="2" t="n"/>
+      <c r="AU321" s="2" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="2" t="n"/>
@@ -16118,6 +16455,7 @@
       <c r="AR322" s="2" t="n"/>
       <c r="AS322" s="2" t="n"/>
       <c r="AT322" s="2" t="n"/>
+      <c r="AU322" s="2" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="2" t="n"/>
@@ -16166,6 +16504,7 @@
       <c r="AR323" s="2" t="n"/>
       <c r="AS323" s="2" t="n"/>
       <c r="AT323" s="2" t="n"/>
+      <c r="AU323" s="2" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="n"/>
@@ -16214,6 +16553,7 @@
       <c r="AR324" s="2" t="n"/>
       <c r="AS324" s="2" t="n"/>
       <c r="AT324" s="2" t="n"/>
+      <c r="AU324" s="2" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="2" t="n"/>
@@ -16262,6 +16602,7 @@
       <c r="AR325" s="2" t="n"/>
       <c r="AS325" s="2" t="n"/>
       <c r="AT325" s="2" t="n"/>
+      <c r="AU325" s="2" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="n"/>
@@ -16310,6 +16651,7 @@
       <c r="AR326" s="2" t="n"/>
       <c r="AS326" s="2" t="n"/>
       <c r="AT326" s="2" t="n"/>
+      <c r="AU326" s="2" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="n"/>
@@ -16358,6 +16700,7 @@
       <c r="AR327" s="2" t="n"/>
       <c r="AS327" s="2" t="n"/>
       <c r="AT327" s="2" t="n"/>
+      <c r="AU327" s="2" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="n"/>
@@ -16406,6 +16749,7 @@
       <c r="AR328" s="2" t="n"/>
       <c r="AS328" s="2" t="n"/>
       <c r="AT328" s="2" t="n"/>
+      <c r="AU328" s="2" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="2" t="n"/>
@@ -16454,6 +16798,7 @@
       <c r="AR329" s="2" t="n"/>
       <c r="AS329" s="2" t="n"/>
       <c r="AT329" s="2" t="n"/>
+      <c r="AU329" s="2" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="n"/>
@@ -16502,6 +16847,7 @@
       <c r="AR330" s="2" t="n"/>
       <c r="AS330" s="2" t="n"/>
       <c r="AT330" s="2" t="n"/>
+      <c r="AU330" s="2" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="2" t="n"/>
@@ -16550,6 +16896,7 @@
       <c r="AR331" s="2" t="n"/>
       <c r="AS331" s="2" t="n"/>
       <c r="AT331" s="2" t="n"/>
+      <c r="AU331" s="2" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="n"/>
@@ -16598,6 +16945,7 @@
       <c r="AR332" s="2" t="n"/>
       <c r="AS332" s="2" t="n"/>
       <c r="AT332" s="2" t="n"/>
+      <c r="AU332" s="2" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="2" t="n"/>
@@ -16646,6 +16994,7 @@
       <c r="AR333" s="2" t="n"/>
       <c r="AS333" s="2" t="n"/>
       <c r="AT333" s="2" t="n"/>
+      <c r="AU333" s="2" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="2" t="n"/>
@@ -16694,6 +17043,7 @@
       <c r="AR334" s="2" t="n"/>
       <c r="AS334" s="2" t="n"/>
       <c r="AT334" s="2" t="n"/>
+      <c r="AU334" s="2" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="2" t="n"/>
@@ -16742,6 +17092,7 @@
       <c r="AR335" s="2" t="n"/>
       <c r="AS335" s="2" t="n"/>
       <c r="AT335" s="2" t="n"/>
+      <c r="AU335" s="2" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="n"/>
@@ -16790,6 +17141,7 @@
       <c r="AR336" s="2" t="n"/>
       <c r="AS336" s="2" t="n"/>
       <c r="AT336" s="2" t="n"/>
+      <c r="AU336" s="2" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="2" t="n"/>
@@ -16838,6 +17190,7 @@
       <c r="AR337" s="2" t="n"/>
       <c r="AS337" s="2" t="n"/>
       <c r="AT337" s="2" t="n"/>
+      <c r="AU337" s="2" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="n"/>
@@ -16886,6 +17239,7 @@
       <c r="AR338" s="2" t="n"/>
       <c r="AS338" s="2" t="n"/>
       <c r="AT338" s="2" t="n"/>
+      <c r="AU338" s="2" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="2" t="n"/>
@@ -16934,6 +17288,7 @@
       <c r="AR339" s="2" t="n"/>
       <c r="AS339" s="2" t="n"/>
       <c r="AT339" s="2" t="n"/>
+      <c r="AU339" s="2" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="n"/>
@@ -16982,6 +17337,7 @@
       <c r="AR340" s="2" t="n"/>
       <c r="AS340" s="2" t="n"/>
       <c r="AT340" s="2" t="n"/>
+      <c r="AU340" s="2" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="2" t="n"/>
@@ -17030,6 +17386,7 @@
       <c r="AR341" s="2" t="n"/>
       <c r="AS341" s="2" t="n"/>
       <c r="AT341" s="2" t="n"/>
+      <c r="AU341" s="2" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="n"/>
@@ -17078,6 +17435,7 @@
       <c r="AR342" s="2" t="n"/>
       <c r="AS342" s="2" t="n"/>
       <c r="AT342" s="2" t="n"/>
+      <c r="AU342" s="2" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="2" t="n"/>
@@ -17126,6 +17484,7 @@
       <c r="AR343" s="2" t="n"/>
       <c r="AS343" s="2" t="n"/>
       <c r="AT343" s="2" t="n"/>
+      <c r="AU343" s="2" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="n"/>
@@ -17174,6 +17533,7 @@
       <c r="AR344" s="2" t="n"/>
       <c r="AS344" s="2" t="n"/>
       <c r="AT344" s="2" t="n"/>
+      <c r="AU344" s="2" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="2" t="n"/>
@@ -17222,6 +17582,7 @@
       <c r="AR345" s="2" t="n"/>
       <c r="AS345" s="2" t="n"/>
       <c r="AT345" s="2" t="n"/>
+      <c r="AU345" s="2" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="n"/>
@@ -17270,6 +17631,7 @@
       <c r="AR346" s="2" t="n"/>
       <c r="AS346" s="2" t="n"/>
       <c r="AT346" s="2" t="n"/>
+      <c r="AU346" s="2" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="n"/>
@@ -17318,6 +17680,7 @@
       <c r="AR347" s="2" t="n"/>
       <c r="AS347" s="2" t="n"/>
       <c r="AT347" s="2" t="n"/>
+      <c r="AU347" s="2" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="n"/>
@@ -17366,6 +17729,7 @@
       <c r="AR348" s="2" t="n"/>
       <c r="AS348" s="2" t="n"/>
       <c r="AT348" s="2" t="n"/>
+      <c r="AU348" s="2" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="2" t="n"/>
@@ -17414,6 +17778,7 @@
       <c r="AR349" s="2" t="n"/>
       <c r="AS349" s="2" t="n"/>
       <c r="AT349" s="2" t="n"/>
+      <c r="AU349" s="2" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="n"/>
@@ -17462,6 +17827,7 @@
       <c r="AR350" s="2" t="n"/>
       <c r="AS350" s="2" t="n"/>
       <c r="AT350" s="2" t="n"/>
+      <c r="AU350" s="2" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="2" t="n"/>
@@ -17510,6 +17876,7 @@
       <c r="AR351" s="2" t="n"/>
       <c r="AS351" s="2" t="n"/>
       <c r="AT351" s="2" t="n"/>
+      <c r="AU351" s="2" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="n"/>
@@ -17558,6 +17925,7 @@
       <c r="AR352" s="2" t="n"/>
       <c r="AS352" s="2" t="n"/>
       <c r="AT352" s="2" t="n"/>
+      <c r="AU352" s="2" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="2" t="n"/>
@@ -17606,6 +17974,7 @@
       <c r="AR353" s="2" t="n"/>
       <c r="AS353" s="2" t="n"/>
       <c r="AT353" s="2" t="n"/>
+      <c r="AU353" s="2" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="n"/>
@@ -17654,6 +18023,7 @@
       <c r="AR354" s="2" t="n"/>
       <c r="AS354" s="2" t="n"/>
       <c r="AT354" s="2" t="n"/>
+      <c r="AU354" s="2" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="2" t="n"/>
@@ -17702,6 +18072,7 @@
       <c r="AR355" s="2" t="n"/>
       <c r="AS355" s="2" t="n"/>
       <c r="AT355" s="2" t="n"/>
+      <c r="AU355" s="2" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="n"/>
@@ -17750,6 +18121,7 @@
       <c r="AR356" s="2" t="n"/>
       <c r="AS356" s="2" t="n"/>
       <c r="AT356" s="2" t="n"/>
+      <c r="AU356" s="2" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="n"/>
@@ -17798,6 +18170,7 @@
       <c r="AR357" s="2" t="n"/>
       <c r="AS357" s="2" t="n"/>
       <c r="AT357" s="2" t="n"/>
+      <c r="AU357" s="2" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="n"/>
@@ -17846,6 +18219,7 @@
       <c r="AR358" s="2" t="n"/>
       <c r="AS358" s="2" t="n"/>
       <c r="AT358" s="2" t="n"/>
+      <c r="AU358" s="2" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="2" t="n"/>
@@ -17894,6 +18268,7 @@
       <c r="AR359" s="2" t="n"/>
       <c r="AS359" s="2" t="n"/>
       <c r="AT359" s="2" t="n"/>
+      <c r="AU359" s="2" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="n"/>
@@ -17942,6 +18317,7 @@
       <c r="AR360" s="2" t="n"/>
       <c r="AS360" s="2" t="n"/>
       <c r="AT360" s="2" t="n"/>
+      <c r="AU360" s="2" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="2" t="n"/>
@@ -17990,6 +18366,7 @@
       <c r="AR361" s="2" t="n"/>
       <c r="AS361" s="2" t="n"/>
       <c r="AT361" s="2" t="n"/>
+      <c r="AU361" s="2" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="n"/>
@@ -18038,6 +18415,7 @@
       <c r="AR362" s="2" t="n"/>
       <c r="AS362" s="2" t="n"/>
       <c r="AT362" s="2" t="n"/>
+      <c r="AU362" s="2" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="2" t="n"/>
@@ -18086,6 +18464,7 @@
       <c r="AR363" s="2" t="n"/>
       <c r="AS363" s="2" t="n"/>
       <c r="AT363" s="2" t="n"/>
+      <c r="AU363" s="2" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="n"/>
@@ -18134,6 +18513,7 @@
       <c r="AR364" s="2" t="n"/>
       <c r="AS364" s="2" t="n"/>
       <c r="AT364" s="2" t="n"/>
+      <c r="AU364" s="2" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="n"/>
@@ -18182,6 +18562,7 @@
       <c r="AR365" s="2" t="n"/>
       <c r="AS365" s="2" t="n"/>
       <c r="AT365" s="2" t="n"/>
+      <c r="AU365" s="2" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="n"/>
@@ -18230,6 +18611,7 @@
       <c r="AR366" s="2" t="n"/>
       <c r="AS366" s="2" t="n"/>
       <c r="AT366" s="2" t="n"/>
+      <c r="AU366" s="2" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="n"/>
@@ -18278,6 +18660,7 @@
       <c r="AR367" s="2" t="n"/>
       <c r="AS367" s="2" t="n"/>
       <c r="AT367" s="2" t="n"/>
+      <c r="AU367" s="2" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="n"/>
@@ -18326,6 +18709,7 @@
       <c r="AR368" s="2" t="n"/>
       <c r="AS368" s="2" t="n"/>
       <c r="AT368" s="2" t="n"/>
+      <c r="AU368" s="2" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="2" t="n"/>
@@ -18374,6 +18758,7 @@
       <c r="AR369" s="2" t="n"/>
       <c r="AS369" s="2" t="n"/>
       <c r="AT369" s="2" t="n"/>
+      <c r="AU369" s="2" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="n"/>
@@ -18422,6 +18807,7 @@
       <c r="AR370" s="2" t="n"/>
       <c r="AS370" s="2" t="n"/>
       <c r="AT370" s="2" t="n"/>
+      <c r="AU370" s="2" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="n"/>
@@ -18470,6 +18856,7 @@
       <c r="AR371" s="2" t="n"/>
       <c r="AS371" s="2" t="n"/>
       <c r="AT371" s="2" t="n"/>
+      <c r="AU371" s="2" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="n"/>
@@ -18518,6 +18905,7 @@
       <c r="AR372" s="2" t="n"/>
       <c r="AS372" s="2" t="n"/>
       <c r="AT372" s="2" t="n"/>
+      <c r="AU372" s="2" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="2" t="n"/>
@@ -18566,6 +18954,7 @@
       <c r="AR373" s="2" t="n"/>
       <c r="AS373" s="2" t="n"/>
       <c r="AT373" s="2" t="n"/>
+      <c r="AU373" s="2" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="n"/>
@@ -18614,6 +19003,7 @@
       <c r="AR374" s="2" t="n"/>
       <c r="AS374" s="2" t="n"/>
       <c r="AT374" s="2" t="n"/>
+      <c r="AU374" s="2" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="2" t="n"/>
@@ -18662,6 +19052,7 @@
       <c r="AR375" s="2" t="n"/>
       <c r="AS375" s="2" t="n"/>
       <c r="AT375" s="2" t="n"/>
+      <c r="AU375" s="2" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="n"/>
@@ -18710,6 +19101,7 @@
       <c r="AR376" s="2" t="n"/>
       <c r="AS376" s="2" t="n"/>
       <c r="AT376" s="2" t="n"/>
+      <c r="AU376" s="2" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="2" t="n"/>
@@ -18758,6 +19150,7 @@
       <c r="AR377" s="2" t="n"/>
       <c r="AS377" s="2" t="n"/>
       <c r="AT377" s="2" t="n"/>
+      <c r="AU377" s="2" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="n"/>
@@ -18806,6 +19199,7 @@
       <c r="AR378" s="2" t="n"/>
       <c r="AS378" s="2" t="n"/>
       <c r="AT378" s="2" t="n"/>
+      <c r="AU378" s="2" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="2" t="n"/>
@@ -18854,6 +19248,7 @@
       <c r="AR379" s="2" t="n"/>
       <c r="AS379" s="2" t="n"/>
       <c r="AT379" s="2" t="n"/>
+      <c r="AU379" s="2" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="n"/>
@@ -18902,6 +19297,7 @@
       <c r="AR380" s="2" t="n"/>
       <c r="AS380" s="2" t="n"/>
       <c r="AT380" s="2" t="n"/>
+      <c r="AU380" s="2" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="2" t="n"/>
@@ -18950,6 +19346,7 @@
       <c r="AR381" s="2" t="n"/>
       <c r="AS381" s="2" t="n"/>
       <c r="AT381" s="2" t="n"/>
+      <c r="AU381" s="2" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="n"/>
@@ -18998,6 +19395,7 @@
       <c r="AR382" s="2" t="n"/>
       <c r="AS382" s="2" t="n"/>
       <c r="AT382" s="2" t="n"/>
+      <c r="AU382" s="2" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="2" t="n"/>
@@ -19046,6 +19444,7 @@
       <c r="AR383" s="2" t="n"/>
       <c r="AS383" s="2" t="n"/>
       <c r="AT383" s="2" t="n"/>
+      <c r="AU383" s="2" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n"/>
@@ -19094,6 +19493,7 @@
       <c r="AR384" s="2" t="n"/>
       <c r="AS384" s="2" t="n"/>
       <c r="AT384" s="2" t="n"/>
+      <c r="AU384" s="2" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="n"/>
@@ -19142,6 +19542,7 @@
       <c r="AR385" s="2" t="n"/>
       <c r="AS385" s="2" t="n"/>
       <c r="AT385" s="2" t="n"/>
+      <c r="AU385" s="2" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n"/>
@@ -19190,6 +19591,7 @@
       <c r="AR386" s="2" t="n"/>
       <c r="AS386" s="2" t="n"/>
       <c r="AT386" s="2" t="n"/>
+      <c r="AU386" s="2" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="2" t="n"/>
@@ -19238,6 +19640,7 @@
       <c r="AR387" s="2" t="n"/>
       <c r="AS387" s="2" t="n"/>
       <c r="AT387" s="2" t="n"/>
+      <c r="AU387" s="2" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="n"/>
@@ -19286,6 +19689,7 @@
       <c r="AR388" s="2" t="n"/>
       <c r="AS388" s="2" t="n"/>
       <c r="AT388" s="2" t="n"/>
+      <c r="AU388" s="2" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n"/>
@@ -19334,6 +19738,7 @@
       <c r="AR389" s="2" t="n"/>
       <c r="AS389" s="2" t="n"/>
       <c r="AT389" s="2" t="n"/>
+      <c r="AU389" s="2" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n"/>
@@ -19382,6 +19787,7 @@
       <c r="AR390" s="2" t="n"/>
       <c r="AS390" s="2" t="n"/>
       <c r="AT390" s="2" t="n"/>
+      <c r="AU390" s="2" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n"/>
@@ -19430,6 +19836,7 @@
       <c r="AR391" s="2" t="n"/>
       <c r="AS391" s="2" t="n"/>
       <c r="AT391" s="2" t="n"/>
+      <c r="AU391" s="2" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n"/>
@@ -19478,6 +19885,7 @@
       <c r="AR392" s="2" t="n"/>
       <c r="AS392" s="2" t="n"/>
       <c r="AT392" s="2" t="n"/>
+      <c r="AU392" s="2" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n"/>
@@ -19526,6 +19934,7 @@
       <c r="AR393" s="2" t="n"/>
       <c r="AS393" s="2" t="n"/>
       <c r="AT393" s="2" t="n"/>
+      <c r="AU393" s="2" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n"/>
@@ -19574,6 +19983,7 @@
       <c r="AR394" s="2" t="n"/>
       <c r="AS394" s="2" t="n"/>
       <c r="AT394" s="2" t="n"/>
+      <c r="AU394" s="2" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="2" t="n"/>
@@ -19622,6 +20032,7 @@
       <c r="AR395" s="2" t="n"/>
       <c r="AS395" s="2" t="n"/>
       <c r="AT395" s="2" t="n"/>
+      <c r="AU395" s="2" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="n"/>
@@ -19670,6 +20081,7 @@
       <c r="AR396" s="2" t="n"/>
       <c r="AS396" s="2" t="n"/>
       <c r="AT396" s="2" t="n"/>
+      <c r="AU396" s="2" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n"/>
@@ -19718,6 +20130,7 @@
       <c r="AR397" s="2" t="n"/>
       <c r="AS397" s="2" t="n"/>
       <c r="AT397" s="2" t="n"/>
+      <c r="AU397" s="2" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n"/>
@@ -19766,6 +20179,7 @@
       <c r="AR398" s="2" t="n"/>
       <c r="AS398" s="2" t="n"/>
       <c r="AT398" s="2" t="n"/>
+      <c r="AU398" s="2" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="2" t="n"/>
@@ -19814,6 +20228,7 @@
       <c r="AR399" s="2" t="n"/>
       <c r="AS399" s="2" t="n"/>
       <c r="AT399" s="2" t="n"/>
+      <c r="AU399" s="2" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n"/>
@@ -19862,6 +20277,7 @@
       <c r="AR400" s="2" t="n"/>
       <c r="AS400" s="2" t="n"/>
       <c r="AT400" s="2" t="n"/>
+      <c r="AU400" s="2" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="2" t="n"/>
@@ -19910,6 +20326,7 @@
       <c r="AR401" s="2" t="n"/>
       <c r="AS401" s="2" t="n"/>
       <c r="AT401" s="2" t="n"/>
+      <c r="AU401" s="2" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n"/>
@@ -19958,6 +20375,7 @@
       <c r="AR402" s="2" t="n"/>
       <c r="AS402" s="2" t="n"/>
       <c r="AT402" s="2" t="n"/>
+      <c r="AU402" s="2" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n"/>
@@ -20006,6 +20424,7 @@
       <c r="AR403" s="2" t="n"/>
       <c r="AS403" s="2" t="n"/>
       <c r="AT403" s="2" t="n"/>
+      <c r="AU403" s="2" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n"/>
@@ -20054,6 +20473,7 @@
       <c r="AR404" s="2" t="n"/>
       <c r="AS404" s="2" t="n"/>
       <c r="AT404" s="2" t="n"/>
+      <c r="AU404" s="2" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n"/>
@@ -20102,6 +20522,7 @@
       <c r="AR405" s="2" t="n"/>
       <c r="AS405" s="2" t="n"/>
       <c r="AT405" s="2" t="n"/>
+      <c r="AU405" s="2" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n"/>
@@ -20150,6 +20571,7 @@
       <c r="AR406" s="2" t="n"/>
       <c r="AS406" s="2" t="n"/>
       <c r="AT406" s="2" t="n"/>
+      <c r="AU406" s="2" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n"/>
@@ -20198,6 +20620,7 @@
       <c r="AR407" s="2" t="n"/>
       <c r="AS407" s="2" t="n"/>
       <c r="AT407" s="2" t="n"/>
+      <c r="AU407" s="2" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n"/>
@@ -20246,6 +20669,7 @@
       <c r="AR408" s="2" t="n"/>
       <c r="AS408" s="2" t="n"/>
       <c r="AT408" s="2" t="n"/>
+      <c r="AU408" s="2" t="n"/>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n"/>
@@ -20294,6 +20718,7 @@
       <c r="AR409" s="2" t="n"/>
       <c r="AS409" s="2" t="n"/>
       <c r="AT409" s="2" t="n"/>
+      <c r="AU409" s="2" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n"/>
@@ -20342,6 +20767,7 @@
       <c r="AR410" s="2" t="n"/>
       <c r="AS410" s="2" t="n"/>
       <c r="AT410" s="2" t="n"/>
+      <c r="AU410" s="2" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n"/>
@@ -20390,6 +20816,7 @@
       <c r="AR411" s="2" t="n"/>
       <c r="AS411" s="2" t="n"/>
       <c r="AT411" s="2" t="n"/>
+      <c r="AU411" s="2" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n"/>
@@ -20438,6 +20865,7 @@
       <c r="AR412" s="2" t="n"/>
       <c r="AS412" s="2" t="n"/>
       <c r="AT412" s="2" t="n"/>
+      <c r="AU412" s="2" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n"/>
@@ -20486,6 +20914,7 @@
       <c r="AR413" s="2" t="n"/>
       <c r="AS413" s="2" t="n"/>
       <c r="AT413" s="2" t="n"/>
+      <c r="AU413" s="2" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n"/>
@@ -20534,6 +20963,7 @@
       <c r="AR414" s="2" t="n"/>
       <c r="AS414" s="2" t="n"/>
       <c r="AT414" s="2" t="n"/>
+      <c r="AU414" s="2" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n"/>
@@ -20582,6 +21012,7 @@
       <c r="AR415" s="2" t="n"/>
       <c r="AS415" s="2" t="n"/>
       <c r="AT415" s="2" t="n"/>
+      <c r="AU415" s="2" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n"/>
@@ -20630,6 +21061,7 @@
       <c r="AR416" s="2" t="n"/>
       <c r="AS416" s="2" t="n"/>
       <c r="AT416" s="2" t="n"/>
+      <c r="AU416" s="2" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n"/>
@@ -20678,6 +21110,7 @@
       <c r="AR417" s="2" t="n"/>
       <c r="AS417" s="2" t="n"/>
       <c r="AT417" s="2" t="n"/>
+      <c r="AU417" s="2" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n"/>
@@ -20726,6 +21159,7 @@
       <c r="AR418" s="2" t="n"/>
       <c r="AS418" s="2" t="n"/>
       <c r="AT418" s="2" t="n"/>
+      <c r="AU418" s="2" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n"/>
@@ -20774,6 +21208,7 @@
       <c r="AR419" s="2" t="n"/>
       <c r="AS419" s="2" t="n"/>
       <c r="AT419" s="2" t="n"/>
+      <c r="AU419" s="2" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n"/>
@@ -20822,6 +21257,7 @@
       <c r="AR420" s="2" t="n"/>
       <c r="AS420" s="2" t="n"/>
       <c r="AT420" s="2" t="n"/>
+      <c r="AU420" s="2" t="n"/>
     </row>
     <row r="421">
       <c r="A421" s="2" t="n"/>
@@ -20870,6 +21306,7 @@
       <c r="AR421" s="2" t="n"/>
       <c r="AS421" s="2" t="n"/>
       <c r="AT421" s="2" t="n"/>
+      <c r="AU421" s="2" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n"/>
@@ -20918,6 +21355,7 @@
       <c r="AR422" s="2" t="n"/>
       <c r="AS422" s="2" t="n"/>
       <c r="AT422" s="2" t="n"/>
+      <c r="AU422" s="2" t="n"/>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n"/>
@@ -20966,6 +21404,7 @@
       <c r="AR423" s="2" t="n"/>
       <c r="AS423" s="2" t="n"/>
       <c r="AT423" s="2" t="n"/>
+      <c r="AU423" s="2" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n"/>
@@ -21014,6 +21453,7 @@
       <c r="AR424" s="2" t="n"/>
       <c r="AS424" s="2" t="n"/>
       <c r="AT424" s="2" t="n"/>
+      <c r="AU424" s="2" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="2" t="n"/>
@@ -21062,6 +21502,7 @@
       <c r="AR425" s="2" t="n"/>
       <c r="AS425" s="2" t="n"/>
       <c r="AT425" s="2" t="n"/>
+      <c r="AU425" s="2" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n"/>
@@ -21110,6 +21551,7 @@
       <c r="AR426" s="2" t="n"/>
       <c r="AS426" s="2" t="n"/>
       <c r="AT426" s="2" t="n"/>
+      <c r="AU426" s="2" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n"/>
@@ -21158,6 +21600,7 @@
       <c r="AR427" s="2" t="n"/>
       <c r="AS427" s="2" t="n"/>
       <c r="AT427" s="2" t="n"/>
+      <c r="AU427" s="2" t="n"/>
     </row>
     <row r="428">
       <c r="A428" s="2" t="n"/>
@@ -21206,6 +21649,7 @@
       <c r="AR428" s="2" t="n"/>
       <c r="AS428" s="2" t="n"/>
       <c r="AT428" s="2" t="n"/>
+      <c r="AU428" s="2" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="2" t="n"/>
@@ -21254,6 +21698,7 @@
       <c r="AR429" s="2" t="n"/>
       <c r="AS429" s="2" t="n"/>
       <c r="AT429" s="2" t="n"/>
+      <c r="AU429" s="2" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n"/>
@@ -21302,6 +21747,7 @@
       <c r="AR430" s="2" t="n"/>
       <c r="AS430" s="2" t="n"/>
       <c r="AT430" s="2" t="n"/>
+      <c r="AU430" s="2" t="n"/>
     </row>
     <row r="431">
       <c r="A431" s="2" t="n"/>
@@ -21350,6 +21796,7 @@
       <c r="AR431" s="2" t="n"/>
       <c r="AS431" s="2" t="n"/>
       <c r="AT431" s="2" t="n"/>
+      <c r="AU431" s="2" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="2" t="n"/>
@@ -21398,6 +21845,7 @@
       <c r="AR432" s="2" t="n"/>
       <c r="AS432" s="2" t="n"/>
       <c r="AT432" s="2" t="n"/>
+      <c r="AU432" s="2" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="2" t="n"/>
@@ -21446,6 +21894,7 @@
       <c r="AR433" s="2" t="n"/>
       <c r="AS433" s="2" t="n"/>
       <c r="AT433" s="2" t="n"/>
+      <c r="AU433" s="2" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="2" t="n"/>
@@ -21494,6 +21943,7 @@
       <c r="AR434" s="2" t="n"/>
       <c r="AS434" s="2" t="n"/>
       <c r="AT434" s="2" t="n"/>
+      <c r="AU434" s="2" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="2" t="n"/>
@@ -21542,6 +21992,7 @@
       <c r="AR435" s="2" t="n"/>
       <c r="AS435" s="2" t="n"/>
       <c r="AT435" s="2" t="n"/>
+      <c r="AU435" s="2" t="n"/>
     </row>
     <row r="436">
       <c r="A436" s="2" t="n"/>
@@ -21590,6 +22041,7 @@
       <c r="AR436" s="2" t="n"/>
       <c r="AS436" s="2" t="n"/>
       <c r="AT436" s="2" t="n"/>
+      <c r="AU436" s="2" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="2" t="n"/>
@@ -21638,6 +22090,7 @@
       <c r="AR437" s="2" t="n"/>
       <c r="AS437" s="2" t="n"/>
       <c r="AT437" s="2" t="n"/>
+      <c r="AU437" s="2" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="2" t="n"/>
@@ -21686,6 +22139,7 @@
       <c r="AR438" s="2" t="n"/>
       <c r="AS438" s="2" t="n"/>
       <c r="AT438" s="2" t="n"/>
+      <c r="AU438" s="2" t="n"/>
     </row>
     <row r="439">
       <c r="A439" s="2" t="n"/>
@@ -21734,6 +22188,7 @@
       <c r="AR439" s="2" t="n"/>
       <c r="AS439" s="2" t="n"/>
       <c r="AT439" s="2" t="n"/>
+      <c r="AU439" s="2" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="n"/>
@@ -21782,6 +22237,7 @@
       <c r="AR440" s="2" t="n"/>
       <c r="AS440" s="2" t="n"/>
       <c r="AT440" s="2" t="n"/>
+      <c r="AU440" s="2" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="2" t="n"/>
@@ -21830,6 +22286,7 @@
       <c r="AR441" s="2" t="n"/>
       <c r="AS441" s="2" t="n"/>
       <c r="AT441" s="2" t="n"/>
+      <c r="AU441" s="2" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n"/>
@@ -21878,6 +22335,7 @@
       <c r="AR442" s="2" t="n"/>
       <c r="AS442" s="2" t="n"/>
       <c r="AT442" s="2" t="n"/>
+      <c r="AU442" s="2" t="n"/>
     </row>
     <row r="443">
       <c r="A443" s="2" t="n"/>
@@ -21926,6 +22384,7 @@
       <c r="AR443" s="2" t="n"/>
       <c r="AS443" s="2" t="n"/>
       <c r="AT443" s="2" t="n"/>
+      <c r="AU443" s="2" t="n"/>
     </row>
     <row r="444">
       <c r="A444" s="2" t="n"/>
@@ -21974,6 +22433,7 @@
       <c r="AR444" s="2" t="n"/>
       <c r="AS444" s="2" t="n"/>
       <c r="AT444" s="2" t="n"/>
+      <c r="AU444" s="2" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="2" t="n"/>
@@ -22022,6 +22482,7 @@
       <c r="AR445" s="2" t="n"/>
       <c r="AS445" s="2" t="n"/>
       <c r="AT445" s="2" t="n"/>
+      <c r="AU445" s="2" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="2" t="n"/>
@@ -22070,6 +22531,7 @@
       <c r="AR446" s="2" t="n"/>
       <c r="AS446" s="2" t="n"/>
       <c r="AT446" s="2" t="n"/>
+      <c r="AU446" s="2" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="2" t="n"/>
@@ -22118,6 +22580,7 @@
       <c r="AR447" s="2" t="n"/>
       <c r="AS447" s="2" t="n"/>
       <c r="AT447" s="2" t="n"/>
+      <c r="AU447" s="2" t="n"/>
     </row>
     <row r="448">
       <c r="A448" s="2" t="n"/>
@@ -22166,6 +22629,7 @@
       <c r="AR448" s="2" t="n"/>
       <c r="AS448" s="2" t="n"/>
       <c r="AT448" s="2" t="n"/>
+      <c r="AU448" s="2" t="n"/>
     </row>
     <row r="449">
       <c r="A449" s="2" t="n"/>
@@ -22214,6 +22678,7 @@
       <c r="AR449" s="2" t="n"/>
       <c r="AS449" s="2" t="n"/>
       <c r="AT449" s="2" t="n"/>
+      <c r="AU449" s="2" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="n"/>
@@ -22262,6 +22727,7 @@
       <c r="AR450" s="2" t="n"/>
       <c r="AS450" s="2" t="n"/>
       <c r="AT450" s="2" t="n"/>
+      <c r="AU450" s="2" t="n"/>
     </row>
     <row r="451">
       <c r="A451" s="2" t="n"/>
@@ -22310,6 +22776,7 @@
       <c r="AR451" s="2" t="n"/>
       <c r="AS451" s="2" t="n"/>
       <c r="AT451" s="2" t="n"/>
+      <c r="AU451" s="2" t="n"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="n"/>
@@ -22358,6 +22825,7 @@
       <c r="AR452" s="2" t="n"/>
       <c r="AS452" s="2" t="n"/>
       <c r="AT452" s="2" t="n"/>
+      <c r="AU452" s="2" t="n"/>
     </row>
     <row r="453">
       <c r="A453" s="2" t="n"/>
@@ -22406,6 +22874,7 @@
       <c r="AR453" s="2" t="n"/>
       <c r="AS453" s="2" t="n"/>
       <c r="AT453" s="2" t="n"/>
+      <c r="AU453" s="2" t="n"/>
     </row>
     <row r="454">
       <c r="A454" s="2" t="n"/>
@@ -22454,6 +22923,7 @@
       <c r="AR454" s="2" t="n"/>
       <c r="AS454" s="2" t="n"/>
       <c r="AT454" s="2" t="n"/>
+      <c r="AU454" s="2" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="2" t="n"/>
@@ -22502,6 +22972,7 @@
       <c r="AR455" s="2" t="n"/>
       <c r="AS455" s="2" t="n"/>
       <c r="AT455" s="2" t="n"/>
+      <c r="AU455" s="2" t="n"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="n"/>
@@ -22550,6 +23021,7 @@
       <c r="AR456" s="2" t="n"/>
       <c r="AS456" s="2" t="n"/>
       <c r="AT456" s="2" t="n"/>
+      <c r="AU456" s="2" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="2" t="n"/>
@@ -22598,6 +23070,7 @@
       <c r="AR457" s="2" t="n"/>
       <c r="AS457" s="2" t="n"/>
       <c r="AT457" s="2" t="n"/>
+      <c r="AU457" s="2" t="n"/>
     </row>
     <row r="458">
       <c r="A458" s="2" t="n"/>
@@ -22646,6 +23119,7 @@
       <c r="AR458" s="2" t="n"/>
       <c r="AS458" s="2" t="n"/>
       <c r="AT458" s="2" t="n"/>
+      <c r="AU458" s="2" t="n"/>
     </row>
     <row r="459">
       <c r="A459" s="2" t="n"/>
@@ -22694,6 +23168,7 @@
       <c r="AR459" s="2" t="n"/>
       <c r="AS459" s="2" t="n"/>
       <c r="AT459" s="2" t="n"/>
+      <c r="AU459" s="2" t="n"/>
     </row>
     <row r="460">
       <c r="A460" s="2" t="n"/>
@@ -22742,6 +23217,7 @@
       <c r="AR460" s="2" t="n"/>
       <c r="AS460" s="2" t="n"/>
       <c r="AT460" s="2" t="n"/>
+      <c r="AU460" s="2" t="n"/>
     </row>
     <row r="461">
       <c r="A461" s="2" t="n"/>
@@ -22790,6 +23266,7 @@
       <c r="AR461" s="2" t="n"/>
       <c r="AS461" s="2" t="n"/>
       <c r="AT461" s="2" t="n"/>
+      <c r="AU461" s="2" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="2" t="n"/>
@@ -22838,6 +23315,7 @@
       <c r="AR462" s="2" t="n"/>
       <c r="AS462" s="2" t="n"/>
       <c r="AT462" s="2" t="n"/>
+      <c r="AU462" s="2" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="2" t="n"/>
@@ -22886,6 +23364,7 @@
       <c r="AR463" s="2" t="n"/>
       <c r="AS463" s="2" t="n"/>
       <c r="AT463" s="2" t="n"/>
+      <c r="AU463" s="2" t="n"/>
     </row>
     <row r="464">
       <c r="A464" s="2" t="n"/>
@@ -22934,6 +23413,7 @@
       <c r="AR464" s="2" t="n"/>
       <c r="AS464" s="2" t="n"/>
       <c r="AT464" s="2" t="n"/>
+      <c r="AU464" s="2" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="2" t="n"/>
@@ -22982,6 +23462,7 @@
       <c r="AR465" s="2" t="n"/>
       <c r="AS465" s="2" t="n"/>
       <c r="AT465" s="2" t="n"/>
+      <c r="AU465" s="2" t="n"/>
     </row>
     <row r="466">
       <c r="A466" s="2" t="n"/>
@@ -23030,6 +23511,7 @@
       <c r="AR466" s="2" t="n"/>
       <c r="AS466" s="2" t="n"/>
       <c r="AT466" s="2" t="n"/>
+      <c r="AU466" s="2" t="n"/>
     </row>
     <row r="467">
       <c r="A467" s="2" t="n"/>
@@ -23078,6 +23560,7 @@
       <c r="AR467" s="2" t="n"/>
       <c r="AS467" s="2" t="n"/>
       <c r="AT467" s="2" t="n"/>
+      <c r="AU467" s="2" t="n"/>
     </row>
     <row r="468">
       <c r="A468" s="2" t="n"/>
@@ -23126,6 +23609,7 @@
       <c r="AR468" s="2" t="n"/>
       <c r="AS468" s="2" t="n"/>
       <c r="AT468" s="2" t="n"/>
+      <c r="AU468" s="2" t="n"/>
     </row>
     <row r="469">
       <c r="A469" s="2" t="n"/>
@@ -23174,6 +23658,7 @@
       <c r="AR469" s="2" t="n"/>
       <c r="AS469" s="2" t="n"/>
       <c r="AT469" s="2" t="n"/>
+      <c r="AU469" s="2" t="n"/>
     </row>
     <row r="470">
       <c r="A470" s="2" t="n"/>
@@ -23222,6 +23707,7 @@
       <c r="AR470" s="2" t="n"/>
       <c r="AS470" s="2" t="n"/>
       <c r="AT470" s="2" t="n"/>
+      <c r="AU470" s="2" t="n"/>
     </row>
     <row r="471">
       <c r="A471" s="2" t="n"/>
@@ -23270,6 +23756,7 @@
       <c r="AR471" s="2" t="n"/>
       <c r="AS471" s="2" t="n"/>
       <c r="AT471" s="2" t="n"/>
+      <c r="AU471" s="2" t="n"/>
     </row>
     <row r="472">
       <c r="A472" s="2" t="n"/>
@@ -23318,6 +23805,7 @@
       <c r="AR472" s="2" t="n"/>
       <c r="AS472" s="2" t="n"/>
       <c r="AT472" s="2" t="n"/>
+      <c r="AU472" s="2" t="n"/>
     </row>
     <row r="473">
       <c r="A473" s="2" t="n"/>
@@ -23366,6 +23854,7 @@
       <c r="AR473" s="2" t="n"/>
       <c r="AS473" s="2" t="n"/>
       <c r="AT473" s="2" t="n"/>
+      <c r="AU473" s="2" t="n"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="n"/>
@@ -23414,6 +23903,7 @@
       <c r="AR474" s="2" t="n"/>
       <c r="AS474" s="2" t="n"/>
       <c r="AT474" s="2" t="n"/>
+      <c r="AU474" s="2" t="n"/>
     </row>
     <row r="475">
       <c r="A475" s="2" t="n"/>
@@ -23462,6 +23952,7 @@
       <c r="AR475" s="2" t="n"/>
       <c r="AS475" s="2" t="n"/>
       <c r="AT475" s="2" t="n"/>
+      <c r="AU475" s="2" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="2" t="n"/>
@@ -23510,6 +24001,7 @@
       <c r="AR476" s="2" t="n"/>
       <c r="AS476" s="2" t="n"/>
       <c r="AT476" s="2" t="n"/>
+      <c r="AU476" s="2" t="n"/>
     </row>
     <row r="477">
       <c r="A477" s="2" t="n"/>
@@ -23558,6 +24050,7 @@
       <c r="AR477" s="2" t="n"/>
       <c r="AS477" s="2" t="n"/>
       <c r="AT477" s="2" t="n"/>
+      <c r="AU477" s="2" t="n"/>
     </row>
     <row r="478">
       <c r="A478" s="2" t="n"/>
@@ -23606,6 +24099,7 @@
       <c r="AR478" s="2" t="n"/>
       <c r="AS478" s="2" t="n"/>
       <c r="AT478" s="2" t="n"/>
+      <c r="AU478" s="2" t="n"/>
     </row>
     <row r="479">
       <c r="A479" s="2" t="n"/>
@@ -23654,6 +24148,7 @@
       <c r="AR479" s="2" t="n"/>
       <c r="AS479" s="2" t="n"/>
       <c r="AT479" s="2" t="n"/>
+      <c r="AU479" s="2" t="n"/>
     </row>
     <row r="480">
       <c r="A480" s="2" t="n"/>
@@ -23702,6 +24197,7 @@
       <c r="AR480" s="2" t="n"/>
       <c r="AS480" s="2" t="n"/>
       <c r="AT480" s="2" t="n"/>
+      <c r="AU480" s="2" t="n"/>
     </row>
     <row r="481">
       <c r="A481" s="2" t="n"/>
@@ -23750,6 +24246,7 @@
       <c r="AR481" s="2" t="n"/>
       <c r="AS481" s="2" t="n"/>
       <c r="AT481" s="2" t="n"/>
+      <c r="AU481" s="2" t="n"/>
     </row>
     <row r="482">
       <c r="A482" s="2" t="n"/>
@@ -23798,6 +24295,7 @@
       <c r="AR482" s="2" t="n"/>
       <c r="AS482" s="2" t="n"/>
       <c r="AT482" s="2" t="n"/>
+      <c r="AU482" s="2" t="n"/>
     </row>
     <row r="483">
       <c r="A483" s="2" t="n"/>
@@ -23846,6 +24344,7 @@
       <c r="AR483" s="2" t="n"/>
       <c r="AS483" s="2" t="n"/>
       <c r="AT483" s="2" t="n"/>
+      <c r="AU483" s="2" t="n"/>
     </row>
     <row r="484">
       <c r="A484" s="2" t="n"/>
@@ -23894,6 +24393,7 @@
       <c r="AR484" s="2" t="n"/>
       <c r="AS484" s="2" t="n"/>
       <c r="AT484" s="2" t="n"/>
+      <c r="AU484" s="2" t="n"/>
     </row>
     <row r="485">
       <c r="A485" s="2" t="n"/>
@@ -23942,6 +24442,7 @@
       <c r="AR485" s="2" t="n"/>
       <c r="AS485" s="2" t="n"/>
       <c r="AT485" s="2" t="n"/>
+      <c r="AU485" s="2" t="n"/>
     </row>
     <row r="486">
       <c r="A486" s="2" t="n"/>
@@ -23990,6 +24491,7 @@
       <c r="AR486" s="2" t="n"/>
       <c r="AS486" s="2" t="n"/>
       <c r="AT486" s="2" t="n"/>
+      <c r="AU486" s="2" t="n"/>
     </row>
     <row r="487">
       <c r="A487" s="2" t="n"/>
@@ -24038,6 +24540,7 @@
       <c r="AR487" s="2" t="n"/>
       <c r="AS487" s="2" t="n"/>
       <c r="AT487" s="2" t="n"/>
+      <c r="AU487" s="2" t="n"/>
     </row>
     <row r="488">
       <c r="A488" s="2" t="n"/>
@@ -24086,6 +24589,7 @@
       <c r="AR488" s="2" t="n"/>
       <c r="AS488" s="2" t="n"/>
       <c r="AT488" s="2" t="n"/>
+      <c r="AU488" s="2" t="n"/>
     </row>
     <row r="489">
       <c r="A489" s="2" t="n"/>
@@ -24134,6 +24638,7 @@
       <c r="AR489" s="2" t="n"/>
       <c r="AS489" s="2" t="n"/>
       <c r="AT489" s="2" t="n"/>
+      <c r="AU489" s="2" t="n"/>
     </row>
     <row r="490">
       <c r="A490" s="2" t="n"/>
@@ -24182,6 +24687,7 @@
       <c r="AR490" s="2" t="n"/>
       <c r="AS490" s="2" t="n"/>
       <c r="AT490" s="2" t="n"/>
+      <c r="AU490" s="2" t="n"/>
     </row>
     <row r="491">
       <c r="A491" s="2" t="n"/>
@@ -24230,6 +24736,7 @@
       <c r="AR491" s="2" t="n"/>
       <c r="AS491" s="2" t="n"/>
       <c r="AT491" s="2" t="n"/>
+      <c r="AU491" s="2" t="n"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="n"/>
@@ -24278,6 +24785,7 @@
       <c r="AR492" s="2" t="n"/>
       <c r="AS492" s="2" t="n"/>
       <c r="AT492" s="2" t="n"/>
+      <c r="AU492" s="2" t="n"/>
     </row>
     <row r="493">
       <c r="A493" s="2" t="n"/>
@@ -24326,6 +24834,7 @@
       <c r="AR493" s="2" t="n"/>
       <c r="AS493" s="2" t="n"/>
       <c r="AT493" s="2" t="n"/>
+      <c r="AU493" s="2" t="n"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="n"/>
@@ -24374,6 +24883,7 @@
       <c r="AR494" s="2" t="n"/>
       <c r="AS494" s="2" t="n"/>
       <c r="AT494" s="2" t="n"/>
+      <c r="AU494" s="2" t="n"/>
     </row>
     <row r="495">
       <c r="A495" s="2" t="n"/>
@@ -24422,6 +24932,7 @@
       <c r="AR495" s="2" t="n"/>
       <c r="AS495" s="2" t="n"/>
       <c r="AT495" s="2" t="n"/>
+      <c r="AU495" s="2" t="n"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="n"/>
@@ -24470,6 +24981,7 @@
       <c r="AR496" s="2" t="n"/>
       <c r="AS496" s="2" t="n"/>
       <c r="AT496" s="2" t="n"/>
+      <c r="AU496" s="2" t="n"/>
     </row>
     <row r="497">
       <c r="A497" s="2" t="n"/>
@@ -24518,6 +25030,7 @@
       <c r="AR497" s="2" t="n"/>
       <c r="AS497" s="2" t="n"/>
       <c r="AT497" s="2" t="n"/>
+      <c r="AU497" s="2" t="n"/>
     </row>
     <row r="498">
       <c r="A498" s="2" t="n"/>
@@ -24566,6 +25079,7 @@
       <c r="AR498" s="2" t="n"/>
       <c r="AS498" s="2" t="n"/>
       <c r="AT498" s="2" t="n"/>
+      <c r="AU498" s="2" t="n"/>
     </row>
     <row r="499">
       <c r="A499" s="2" t="n"/>
@@ -24614,6 +25128,7 @@
       <c r="AR499" s="2" t="n"/>
       <c r="AS499" s="2" t="n"/>
       <c r="AT499" s="2" t="n"/>
+      <c r="AU499" s="2" t="n"/>
     </row>
     <row r="500">
       <c r="A500" s="2" t="n"/>
@@ -24662,6 +25177,7 @@
       <c r="AR500" s="2" t="n"/>
       <c r="AS500" s="2" t="n"/>
       <c r="AT500" s="2" t="n"/>
+      <c r="AU500" s="2" t="n"/>
     </row>
     <row r="501">
       <c r="A501" s="2" t="n"/>
@@ -24710,6 +25226,7 @@
       <c r="AR501" s="2" t="n"/>
       <c r="AS501" s="2" t="n"/>
       <c r="AT501" s="2" t="n"/>
+      <c r="AU501" s="2" t="n"/>
     </row>
     <row r="502">
       <c r="A502" s="2" t="n"/>
@@ -24758,6 +25275,7 @@
       <c r="AR502" s="2" t="n"/>
       <c r="AS502" s="2" t="n"/>
       <c r="AT502" s="2" t="n"/>
+      <c r="AU502" s="2" t="n"/>
     </row>
     <row r="503">
       <c r="A503" s="2" t="n"/>
@@ -24806,6 +25324,7 @@
       <c r="AR503" s="2" t="n"/>
       <c r="AS503" s="2" t="n"/>
       <c r="AT503" s="2" t="n"/>
+      <c r="AU503" s="2" t="n"/>
     </row>
     <row r="504">
       <c r="A504" s="2" t="n"/>
@@ -24854,6 +25373,7 @@
       <c r="AR504" s="2" t="n"/>
       <c r="AS504" s="2" t="n"/>
       <c r="AT504" s="2" t="n"/>
+      <c r="AU504" s="2" t="n"/>
     </row>
     <row r="505">
       <c r="A505" s="2" t="n"/>
@@ -24902,6 +25422,7 @@
       <c r="AR505" s="2" t="n"/>
       <c r="AS505" s="2" t="n"/>
       <c r="AT505" s="2" t="n"/>
+      <c r="AU505" s="2" t="n"/>
     </row>
     <row r="506">
       <c r="A506" s="2" t="n"/>
@@ -24950,6 +25471,7 @@
       <c r="AR506" s="2" t="n"/>
       <c r="AS506" s="2" t="n"/>
       <c r="AT506" s="2" t="n"/>
+      <c r="AU506" s="2" t="n"/>
     </row>
     <row r="507">
       <c r="A507" s="2" t="n"/>
@@ -24998,6 +25520,7 @@
       <c r="AR507" s="2" t="n"/>
       <c r="AS507" s="2" t="n"/>
       <c r="AT507" s="2" t="n"/>
+      <c r="AU507" s="2" t="n"/>
     </row>
     <row r="508">
       <c r="A508" s="2" t="n"/>
@@ -25046,6 +25569,7 @@
       <c r="AR508" s="2" t="n"/>
       <c r="AS508" s="2" t="n"/>
       <c r="AT508" s="2" t="n"/>
+      <c r="AU508" s="2" t="n"/>
     </row>
     <row r="509">
       <c r="A509" s="2" t="n"/>
@@ -25094,6 +25618,7 @@
       <c r="AR509" s="2" t="n"/>
       <c r="AS509" s="2" t="n"/>
       <c r="AT509" s="2" t="n"/>
+      <c r="AU509" s="2" t="n"/>
     </row>
     <row r="510">
       <c r="A510" s="2" t="n"/>
@@ -25142,6 +25667,7 @@
       <c r="AR510" s="2" t="n"/>
       <c r="AS510" s="2" t="n"/>
       <c r="AT510" s="2" t="n"/>
+      <c r="AU510" s="2" t="n"/>
     </row>
     <row r="511">
       <c r="A511" s="2" t="n"/>
@@ -25190,6 +25716,7 @@
       <c r="AR511" s="2" t="n"/>
       <c r="AS511" s="2" t="n"/>
       <c r="AT511" s="2" t="n"/>
+      <c r="AU511" s="2" t="n"/>
     </row>
     <row r="512">
       <c r="A512" s="2" t="n"/>
@@ -25238,6 +25765,7 @@
       <c r="AR512" s="2" t="n"/>
       <c r="AS512" s="2" t="n"/>
       <c r="AT512" s="2" t="n"/>
+      <c r="AU512" s="2" t="n"/>
     </row>
     <row r="513">
       <c r="A513" s="2" t="n"/>
@@ -25286,6 +25814,7 @@
       <c r="AR513" s="2" t="n"/>
       <c r="AS513" s="2" t="n"/>
       <c r="AT513" s="2" t="n"/>
+      <c r="AU513" s="2" t="n"/>
     </row>
     <row r="514">
       <c r="A514" s="2" t="n"/>
@@ -25334,6 +25863,7 @@
       <c r="AR514" s="2" t="n"/>
       <c r="AS514" s="2" t="n"/>
       <c r="AT514" s="2" t="n"/>
+      <c r="AU514" s="2" t="n"/>
     </row>
     <row r="515">
       <c r="A515" s="2" t="n"/>
@@ -25382,6 +25912,7 @@
       <c r="AR515" s="2" t="n"/>
       <c r="AS515" s="2" t="n"/>
       <c r="AT515" s="2" t="n"/>
+      <c r="AU515" s="2" t="n"/>
     </row>
     <row r="516">
       <c r="A516" s="2" t="n"/>
@@ -25430,6 +25961,7 @@
       <c r="AR516" s="2" t="n"/>
       <c r="AS516" s="2" t="n"/>
       <c r="AT516" s="2" t="n"/>
+      <c r="AU516" s="2" t="n"/>
     </row>
     <row r="517">
       <c r="A517" s="2" t="n"/>
@@ -25478,6 +26010,7 @@
       <c r="AR517" s="2" t="n"/>
       <c r="AS517" s="2" t="n"/>
       <c r="AT517" s="2" t="n"/>
+      <c r="AU517" s="2" t="n"/>
     </row>
     <row r="518">
       <c r="A518" s="2" t="n"/>
@@ -25526,6 +26059,7 @@
       <c r="AR518" s="2" t="n"/>
       <c r="AS518" s="2" t="n"/>
       <c r="AT518" s="2" t="n"/>
+      <c r="AU518" s="2" t="n"/>
     </row>
     <row r="519">
       <c r="A519" s="2" t="n"/>
@@ -25574,6 +26108,7 @@
       <c r="AR519" s="2" t="n"/>
       <c r="AS519" s="2" t="n"/>
       <c r="AT519" s="2" t="n"/>
+      <c r="AU519" s="2" t="n"/>
     </row>
     <row r="520">
       <c r="A520" s="2" t="n"/>
@@ -25622,6 +26157,7 @@
       <c r="AR520" s="2" t="n"/>
       <c r="AS520" s="2" t="n"/>
       <c r="AT520" s="2" t="n"/>
+      <c r="AU520" s="2" t="n"/>
     </row>
     <row r="521">
       <c r="A521" s="2" t="n"/>
@@ -25670,6 +26206,7 @@
       <c r="AR521" s="2" t="n"/>
       <c r="AS521" s="2" t="n"/>
       <c r="AT521" s="2" t="n"/>
+      <c r="AU521" s="2" t="n"/>
     </row>
     <row r="522">
       <c r="A522" s="2" t="n"/>
@@ -25718,6 +26255,7 @@
       <c r="AR522" s="2" t="n"/>
       <c r="AS522" s="2" t="n"/>
       <c r="AT522" s="2" t="n"/>
+      <c r="AU522" s="2" t="n"/>
     </row>
     <row r="523">
       <c r="A523" s="2" t="n"/>
@@ -25766,6 +26304,7 @@
       <c r="AR523" s="2" t="n"/>
       <c r="AS523" s="2" t="n"/>
       <c r="AT523" s="2" t="n"/>
+      <c r="AU523" s="2" t="n"/>
     </row>
     <row r="524">
       <c r="A524" s="2" t="n"/>
@@ -25814,6 +26353,7 @@
       <c r="AR524" s="2" t="n"/>
       <c r="AS524" s="2" t="n"/>
       <c r="AT524" s="2" t="n"/>
+      <c r="AU524" s="2" t="n"/>
     </row>
     <row r="525">
       <c r="A525" s="2" t="n"/>
@@ -25862,6 +26402,7 @@
       <c r="AR525" s="2" t="n"/>
       <c r="AS525" s="2" t="n"/>
       <c r="AT525" s="2" t="n"/>
+      <c r="AU525" s="2" t="n"/>
     </row>
     <row r="526">
       <c r="A526" s="2" t="n"/>
@@ -25910,6 +26451,7 @@
       <c r="AR526" s="2" t="n"/>
       <c r="AS526" s="2" t="n"/>
       <c r="AT526" s="2" t="n"/>
+      <c r="AU526" s="2" t="n"/>
     </row>
     <row r="527">
       <c r="A527" s="2" t="n"/>
@@ -25958,6 +26500,7 @@
       <c r="AR527" s="2" t="n"/>
       <c r="AS527" s="2" t="n"/>
       <c r="AT527" s="2" t="n"/>
+      <c r="AU527" s="2" t="n"/>
     </row>
     <row r="528">
       <c r="A528" s="2" t="n"/>
@@ -26006,6 +26549,7 @@
       <c r="AR528" s="2" t="n"/>
       <c r="AS528" s="2" t="n"/>
       <c r="AT528" s="2" t="n"/>
+      <c r="AU528" s="2" t="n"/>
     </row>
     <row r="529">
       <c r="A529" s="2" t="n"/>
@@ -26054,6 +26598,7 @@
       <c r="AR529" s="2" t="n"/>
       <c r="AS529" s="2" t="n"/>
       <c r="AT529" s="2" t="n"/>
+      <c r="AU529" s="2" t="n"/>
     </row>
     <row r="530">
       <c r="A530" s="2" t="n"/>
@@ -26102,6 +26647,7 @@
       <c r="AR530" s="2" t="n"/>
       <c r="AS530" s="2" t="n"/>
       <c r="AT530" s="2" t="n"/>
+      <c r="AU530" s="2" t="n"/>
     </row>
     <row r="531">
       <c r="A531" s="2" t="n"/>
@@ -26150,6 +26696,7 @@
       <c r="AR531" s="2" t="n"/>
       <c r="AS531" s="2" t="n"/>
       <c r="AT531" s="2" t="n"/>
+      <c r="AU531" s="2" t="n"/>
     </row>
     <row r="532">
       <c r="A532" s="2" t="n"/>
@@ -26198,6 +26745,7 @@
       <c r="AR532" s="2" t="n"/>
       <c r="AS532" s="2" t="n"/>
       <c r="AT532" s="2" t="n"/>
+      <c r="AU532" s="2" t="n"/>
     </row>
     <row r="533">
       <c r="A533" s="2" t="n"/>
@@ -26246,6 +26794,7 @@
       <c r="AR533" s="2" t="n"/>
       <c r="AS533" s="2" t="n"/>
       <c r="AT533" s="2" t="n"/>
+      <c r="AU533" s="2" t="n"/>
     </row>
     <row r="534">
       <c r="A534" s="2" t="n"/>
@@ -26294,6 +26843,7 @@
       <c r="AR534" s="2" t="n"/>
       <c r="AS534" s="2" t="n"/>
       <c r="AT534" s="2" t="n"/>
+      <c r="AU534" s="2" t="n"/>
     </row>
     <row r="535">
       <c r="A535" s="2" t="n"/>
@@ -26342,6 +26892,7 @@
       <c r="AR535" s="2" t="n"/>
       <c r="AS535" s="2" t="n"/>
       <c r="AT535" s="2" t="n"/>
+      <c r="AU535" s="2" t="n"/>
     </row>
     <row r="536">
       <c r="A536" s="2" t="n"/>
@@ -26390,6 +26941,7 @@
       <c r="AR536" s="2" t="n"/>
       <c r="AS536" s="2" t="n"/>
       <c r="AT536" s="2" t="n"/>
+      <c r="AU536" s="2" t="n"/>
     </row>
     <row r="537">
       <c r="A537" s="2" t="n"/>
@@ -26438,6 +26990,7 @@
       <c r="AR537" s="2" t="n"/>
       <c r="AS537" s="2" t="n"/>
       <c r="AT537" s="2" t="n"/>
+      <c r="AU537" s="2" t="n"/>
     </row>
     <row r="538">
       <c r="A538" s="2" t="n"/>
@@ -26486,6 +27039,7 @@
       <c r="AR538" s="2" t="n"/>
       <c r="AS538" s="2" t="n"/>
       <c r="AT538" s="2" t="n"/>
+      <c r="AU538" s="2" t="n"/>
     </row>
     <row r="539">
       <c r="A539" s="2" t="n"/>
@@ -26534,6 +27088,7 @@
       <c r="AR539" s="2" t="n"/>
       <c r="AS539" s="2" t="n"/>
       <c r="AT539" s="2" t="n"/>
+      <c r="AU539" s="2" t="n"/>
     </row>
     <row r="540">
       <c r="A540" s="2" t="n"/>
@@ -26582,6 +27137,7 @@
       <c r="AR540" s="2" t="n"/>
       <c r="AS540" s="2" t="n"/>
       <c r="AT540" s="2" t="n"/>
+      <c r="AU540" s="2" t="n"/>
     </row>
     <row r="541">
       <c r="A541" s="2" t="n"/>
@@ -26630,6 +27186,7 @@
       <c r="AR541" s="2" t="n"/>
       <c r="AS541" s="2" t="n"/>
       <c r="AT541" s="2" t="n"/>
+      <c r="AU541" s="2" t="n"/>
     </row>
     <row r="542">
       <c r="A542" s="2" t="n"/>
@@ -26678,6 +27235,7 @@
       <c r="AR542" s="2" t="n"/>
       <c r="AS542" s="2" t="n"/>
       <c r="AT542" s="2" t="n"/>
+      <c r="AU542" s="2" t="n"/>
     </row>
     <row r="543">
       <c r="A543" s="2" t="n"/>
@@ -26726,6 +27284,7 @@
       <c r="AR543" s="2" t="n"/>
       <c r="AS543" s="2" t="n"/>
       <c r="AT543" s="2" t="n"/>
+      <c r="AU543" s="2" t="n"/>
     </row>
     <row r="544">
       <c r="A544" s="2" t="n"/>
@@ -26774,6 +27333,7 @@
       <c r="AR544" s="2" t="n"/>
       <c r="AS544" s="2" t="n"/>
       <c r="AT544" s="2" t="n"/>
+      <c r="AU544" s="2" t="n"/>
     </row>
     <row r="545">
       <c r="A545" s="2" t="n"/>
@@ -26822,6 +27382,7 @@
       <c r="AR545" s="2" t="n"/>
       <c r="AS545" s="2" t="n"/>
       <c r="AT545" s="2" t="n"/>
+      <c r="AU545" s="2" t="n"/>
     </row>
     <row r="546">
       <c r="A546" s="2" t="n"/>
@@ -26870,6 +27431,7 @@
       <c r="AR546" s="2" t="n"/>
       <c r="AS546" s="2" t="n"/>
       <c r="AT546" s="2" t="n"/>
+      <c r="AU546" s="2" t="n"/>
     </row>
     <row r="547">
       <c r="A547" s="2" t="n"/>
@@ -26918,6 +27480,7 @@
       <c r="AR547" s="2" t="n"/>
       <c r="AS547" s="2" t="n"/>
       <c r="AT547" s="2" t="n"/>
+      <c r="AU547" s="2" t="n"/>
     </row>
     <row r="548">
       <c r="A548" s="2" t="n"/>
@@ -26966,6 +27529,7 @@
       <c r="AR548" s="2" t="n"/>
       <c r="AS548" s="2" t="n"/>
       <c r="AT548" s="2" t="n"/>
+      <c r="AU548" s="2" t="n"/>
     </row>
     <row r="549">
       <c r="A549" s="2" t="n"/>
@@ -27014,6 +27578,7 @@
       <c r="AR549" s="2" t="n"/>
       <c r="AS549" s="2" t="n"/>
       <c r="AT549" s="2" t="n"/>
+      <c r="AU549" s="2" t="n"/>
     </row>
     <row r="550">
       <c r="A550" s="2" t="n"/>
@@ -27062,6 +27627,7 @@
       <c r="AR550" s="2" t="n"/>
       <c r="AS550" s="2" t="n"/>
       <c r="AT550" s="2" t="n"/>
+      <c r="AU550" s="2" t="n"/>
     </row>
     <row r="551">
       <c r="A551" s="2" t="n"/>
@@ -27110,6 +27676,7 @@
       <c r="AR551" s="2" t="n"/>
       <c r="AS551" s="2" t="n"/>
       <c r="AT551" s="2" t="n"/>
+      <c r="AU551" s="2" t="n"/>
     </row>
     <row r="552">
       <c r="A552" s="2" t="n"/>
@@ -27158,6 +27725,7 @@
       <c r="AR552" s="2" t="n"/>
       <c r="AS552" s="2" t="n"/>
       <c r="AT552" s="2" t="n"/>
+      <c r="AU552" s="2" t="n"/>
     </row>
     <row r="553">
       <c r="A553" s="2" t="n"/>
@@ -27206,6 +27774,7 @@
       <c r="AR553" s="2" t="n"/>
       <c r="AS553" s="2" t="n"/>
       <c r="AT553" s="2" t="n"/>
+      <c r="AU553" s="2" t="n"/>
     </row>
     <row r="554">
       <c r="A554" s="2" t="n"/>
@@ -27254,6 +27823,7 @@
       <c r="AR554" s="2" t="n"/>
       <c r="AS554" s="2" t="n"/>
       <c r="AT554" s="2" t="n"/>
+      <c r="AU554" s="2" t="n"/>
     </row>
     <row r="555">
       <c r="A555" s="2" t="n"/>
@@ -27302,6 +27872,7 @@
       <c r="AR555" s="2" t="n"/>
       <c r="AS555" s="2" t="n"/>
       <c r="AT555" s="2" t="n"/>
+      <c r="AU555" s="2" t="n"/>
     </row>
     <row r="556">
       <c r="A556" s="2" t="n"/>
@@ -27350,6 +27921,7 @@
       <c r="AR556" s="2" t="n"/>
       <c r="AS556" s="2" t="n"/>
       <c r="AT556" s="2" t="n"/>
+      <c r="AU556" s="2" t="n"/>
     </row>
     <row r="557">
       <c r="A557" s="2" t="n"/>
@@ -27398,6 +27970,7 @@
       <c r="AR557" s="2" t="n"/>
       <c r="AS557" s="2" t="n"/>
       <c r="AT557" s="2" t="n"/>
+      <c r="AU557" s="2" t="n"/>
     </row>
     <row r="558">
       <c r="A558" s="2" t="n"/>
@@ -27446,6 +28019,7 @@
       <c r="AR558" s="2" t="n"/>
       <c r="AS558" s="2" t="n"/>
       <c r="AT558" s="2" t="n"/>
+      <c r="AU558" s="2" t="n"/>
     </row>
     <row r="559">
       <c r="A559" s="2" t="n"/>
@@ -27494,6 +28068,7 @@
       <c r="AR559" s="2" t="n"/>
       <c r="AS559" s="2" t="n"/>
       <c r="AT559" s="2" t="n"/>
+      <c r="AU559" s="2" t="n"/>
     </row>
     <row r="560">
       <c r="A560" s="2" t="n"/>
@@ -27542,6 +28117,7 @@
       <c r="AR560" s="2" t="n"/>
       <c r="AS560" s="2" t="n"/>
       <c r="AT560" s="2" t="n"/>
+      <c r="AU560" s="2" t="n"/>
     </row>
     <row r="561">
       <c r="A561" s="2" t="n"/>
@@ -27590,6 +28166,7 @@
       <c r="AR561" s="2" t="n"/>
       <c r="AS561" s="2" t="n"/>
       <c r="AT561" s="2" t="n"/>
+      <c r="AU561" s="2" t="n"/>
     </row>
     <row r="562">
       <c r="A562" s="2" t="n"/>
@@ -27638,6 +28215,7 @@
       <c r="AR562" s="2" t="n"/>
       <c r="AS562" s="2" t="n"/>
       <c r="AT562" s="2" t="n"/>
+      <c r="AU562" s="2" t="n"/>
     </row>
     <row r="563">
       <c r="A563" s="2" t="n"/>
@@ -27686,6 +28264,7 @@
       <c r="AR563" s="2" t="n"/>
       <c r="AS563" s="2" t="n"/>
       <c r="AT563" s="2" t="n"/>
+      <c r="AU563" s="2" t="n"/>
     </row>
     <row r="564">
       <c r="A564" s="2" t="n"/>
@@ -27734,6 +28313,7 @@
       <c r="AR564" s="2" t="n"/>
       <c r="AS564" s="2" t="n"/>
       <c r="AT564" s="2" t="n"/>
+      <c r="AU564" s="2" t="n"/>
     </row>
     <row r="565">
       <c r="A565" s="2" t="n"/>
@@ -27782,6 +28362,7 @@
       <c r="AR565" s="2" t="n"/>
       <c r="AS565" s="2" t="n"/>
       <c r="AT565" s="2" t="n"/>
+      <c r="AU565" s="2" t="n"/>
     </row>
     <row r="566">
       <c r="A566" s="2" t="n"/>
@@ -27830,6 +28411,7 @@
       <c r="AR566" s="2" t="n"/>
       <c r="AS566" s="2" t="n"/>
       <c r="AT566" s="2" t="n"/>
+      <c r="AU566" s="2" t="n"/>
     </row>
     <row r="567">
       <c r="A567" s="2" t="n"/>
@@ -27878,6 +28460,7 @@
       <c r="AR567" s="2" t="n"/>
       <c r="AS567" s="2" t="n"/>
       <c r="AT567" s="2" t="n"/>
+      <c r="AU567" s="2" t="n"/>
     </row>
     <row r="568">
       <c r="A568" s="2" t="n"/>
@@ -27926,6 +28509,7 @@
       <c r="AR568" s="2" t="n"/>
       <c r="AS568" s="2" t="n"/>
       <c r="AT568" s="2" t="n"/>
+      <c r="AU568" s="2" t="n"/>
     </row>
     <row r="569">
       <c r="A569" s="2" t="n"/>
@@ -27974,6 +28558,7 @@
       <c r="AR569" s="2" t="n"/>
       <c r="AS569" s="2" t="n"/>
       <c r="AT569" s="2" t="n"/>
+      <c r="AU569" s="2" t="n"/>
     </row>
     <row r="570">
       <c r="A570" s="2" t="n"/>
@@ -28022,6 +28607,7 @@
       <c r="AR570" s="2" t="n"/>
       <c r="AS570" s="2" t="n"/>
       <c r="AT570" s="2" t="n"/>
+      <c r="AU570" s="2" t="n"/>
     </row>
     <row r="571">
       <c r="A571" s="2" t="n"/>
@@ -28070,6 +28656,7 @@
       <c r="AR571" s="2" t="n"/>
       <c r="AS571" s="2" t="n"/>
       <c r="AT571" s="2" t="n"/>
+      <c r="AU571" s="2" t="n"/>
     </row>
     <row r="572">
       <c r="A572" s="2" t="n"/>
@@ -28118,6 +28705,7 @@
       <c r="AR572" s="2" t="n"/>
       <c r="AS572" s="2" t="n"/>
       <c r="AT572" s="2" t="n"/>
+      <c r="AU572" s="2" t="n"/>
     </row>
     <row r="573">
       <c r="A573" s="2" t="n"/>
@@ -28166,6 +28754,7 @@
       <c r="AR573" s="2" t="n"/>
       <c r="AS573" s="2" t="n"/>
       <c r="AT573" s="2" t="n"/>
+      <c r="AU573" s="2" t="n"/>
     </row>
     <row r="574">
       <c r="A574" s="2" t="n"/>
@@ -28214,6 +28803,7 @@
       <c r="AR574" s="2" t="n"/>
       <c r="AS574" s="2" t="n"/>
       <c r="AT574" s="2" t="n"/>
+      <c r="AU574" s="2" t="n"/>
     </row>
     <row r="575">
       <c r="A575" s="2" t="n"/>
@@ -28262,6 +28852,7 @@
       <c r="AR575" s="2" t="n"/>
       <c r="AS575" s="2" t="n"/>
       <c r="AT575" s="2" t="n"/>
+      <c r="AU575" s="2" t="n"/>
     </row>
     <row r="576">
       <c r="A576" s="2" t="n"/>
@@ -28310,6 +28901,7 @@
       <c r="AR576" s="2" t="n"/>
       <c r="AS576" s="2" t="n"/>
       <c r="AT576" s="2" t="n"/>
+      <c r="AU576" s="2" t="n"/>
     </row>
     <row r="577">
       <c r="A577" s="2" t="n"/>
@@ -28358,6 +28950,7 @@
       <c r="AR577" s="2" t="n"/>
       <c r="AS577" s="2" t="n"/>
       <c r="AT577" s="2" t="n"/>
+      <c r="AU577" s="2" t="n"/>
     </row>
     <row r="578">
       <c r="A578" s="2" t="n"/>
@@ -28406,6 +28999,7 @@
       <c r="AR578" s="2" t="n"/>
       <c r="AS578" s="2" t="n"/>
       <c r="AT578" s="2" t="n"/>
+      <c r="AU578" s="2" t="n"/>
     </row>
     <row r="579">
       <c r="A579" s="2" t="n"/>
@@ -28454,6 +29048,7 @@
       <c r="AR579" s="2" t="n"/>
       <c r="AS579" s="2" t="n"/>
       <c r="AT579" s="2" t="n"/>
+      <c r="AU579" s="2" t="n"/>
     </row>
     <row r="580">
       <c r="A580" s="2" t="n"/>
@@ -28502,6 +29097,7 @@
       <c r="AR580" s="2" t="n"/>
       <c r="AS580" s="2" t="n"/>
       <c r="AT580" s="2" t="n"/>
+      <c r="AU580" s="2" t="n"/>
     </row>
     <row r="581">
       <c r="A581" s="2" t="n"/>
@@ -28550,6 +29146,7 @@
       <c r="AR581" s="2" t="n"/>
       <c r="AS581" s="2" t="n"/>
       <c r="AT581" s="2" t="n"/>
+      <c r="AU581" s="2" t="n"/>
     </row>
     <row r="582">
       <c r="A582" s="2" t="n"/>
@@ -28598,6 +29195,7 @@
       <c r="AR582" s="2" t="n"/>
       <c r="AS582" s="2" t="n"/>
       <c r="AT582" s="2" t="n"/>
+      <c r="AU582" s="2" t="n"/>
     </row>
     <row r="583">
       <c r="A583" s="2" t="n"/>
@@ -28646,6 +29244,7 @@
       <c r="AR583" s="2" t="n"/>
       <c r="AS583" s="2" t="n"/>
       <c r="AT583" s="2" t="n"/>
+      <c r="AU583" s="2" t="n"/>
     </row>
     <row r="584">
       <c r="A584" s="2" t="n"/>
@@ -28694,6 +29293,7 @@
       <c r="AR584" s="2" t="n"/>
       <c r="AS584" s="2" t="n"/>
       <c r="AT584" s="2" t="n"/>
+      <c r="AU584" s="2" t="n"/>
     </row>
     <row r="585">
       <c r="A585" s="2" t="n"/>
@@ -28742,6 +29342,7 @@
       <c r="AR585" s="2" t="n"/>
       <c r="AS585" s="2" t="n"/>
       <c r="AT585" s="2" t="n"/>
+      <c r="AU585" s="2" t="n"/>
     </row>
     <row r="586">
       <c r="A586" s="2" t="n"/>
@@ -28790,6 +29391,7 @@
       <c r="AR586" s="2" t="n"/>
       <c r="AS586" s="2" t="n"/>
       <c r="AT586" s="2" t="n"/>
+      <c r="AU586" s="2" t="n"/>
     </row>
     <row r="587">
       <c r="A587" s="2" t="n"/>
@@ -28838,6 +29440,7 @@
       <c r="AR587" s="2" t="n"/>
       <c r="AS587" s="2" t="n"/>
       <c r="AT587" s="2" t="n"/>
+      <c r="AU587" s="2" t="n"/>
     </row>
     <row r="588">
       <c r="A588" s="2" t="n"/>
@@ -28886,6 +29489,7 @@
       <c r="AR588" s="2" t="n"/>
       <c r="AS588" s="2" t="n"/>
       <c r="AT588" s="2" t="n"/>
+      <c r="AU588" s="2" t="n"/>
     </row>
     <row r="589">
       <c r="A589" s="2" t="n"/>
@@ -28934,6 +29538,7 @@
       <c r="AR589" s="2" t="n"/>
       <c r="AS589" s="2" t="n"/>
       <c r="AT589" s="2" t="n"/>
+      <c r="AU589" s="2" t="n"/>
     </row>
     <row r="590">
       <c r="A590" s="2" t="n"/>
@@ -28982,6 +29587,7 @@
       <c r="AR590" s="2" t="n"/>
       <c r="AS590" s="2" t="n"/>
       <c r="AT590" s="2" t="n"/>
+      <c r="AU590" s="2" t="n"/>
     </row>
     <row r="591">
       <c r="A591" s="2" t="n"/>
@@ -29030,6 +29636,7 @@
       <c r="AR591" s="2" t="n"/>
       <c r="AS591" s="2" t="n"/>
       <c r="AT591" s="2" t="n"/>
+      <c r="AU591" s="2" t="n"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="n"/>
@@ -29078,6 +29685,7 @@
       <c r="AR592" s="2" t="n"/>
       <c r="AS592" s="2" t="n"/>
       <c r="AT592" s="2" t="n"/>
+      <c r="AU592" s="2" t="n"/>
     </row>
     <row r="593">
       <c r="A593" s="2" t="n"/>
@@ -29126,6 +29734,7 @@
       <c r="AR593" s="2" t="n"/>
       <c r="AS593" s="2" t="n"/>
       <c r="AT593" s="2" t="n"/>
+      <c r="AU593" s="2" t="n"/>
     </row>
     <row r="594">
       <c r="A594" s="2" t="n"/>
@@ -29174,6 +29783,7 @@
       <c r="AR594" s="2" t="n"/>
       <c r="AS594" s="2" t="n"/>
       <c r="AT594" s="2" t="n"/>
+      <c r="AU594" s="2" t="n"/>
     </row>
     <row r="595">
       <c r="A595" s="2" t="n"/>
@@ -29222,6 +29832,7 @@
       <c r="AR595" s="2" t="n"/>
       <c r="AS595" s="2" t="n"/>
       <c r="AT595" s="2" t="n"/>
+      <c r="AU595" s="2" t="n"/>
     </row>
     <row r="596">
       <c r="A596" s="2" t="n"/>
@@ -29270,6 +29881,7 @@
       <c r="AR596" s="2" t="n"/>
       <c r="AS596" s="2" t="n"/>
       <c r="AT596" s="2" t="n"/>
+      <c r="AU596" s="2" t="n"/>
     </row>
     <row r="597">
       <c r="A597" s="2" t="n"/>
@@ -29318,6 +29930,7 @@
       <c r="AR597" s="2" t="n"/>
       <c r="AS597" s="2" t="n"/>
       <c r="AT597" s="2" t="n"/>
+      <c r="AU597" s="2" t="n"/>
     </row>
     <row r="598">
       <c r="A598" s="2" t="n"/>
@@ -29366,6 +29979,7 @@
       <c r="AR598" s="2" t="n"/>
       <c r="AS598" s="2" t="n"/>
       <c r="AT598" s="2" t="n"/>
+      <c r="AU598" s="2" t="n"/>
     </row>
     <row r="599">
       <c r="A599" s="2" t="n"/>
@@ -29414,6 +30028,7 @@
       <c r="AR599" s="2" t="n"/>
       <c r="AS599" s="2" t="n"/>
       <c r="AT599" s="2" t="n"/>
+      <c r="AU599" s="2" t="n"/>
     </row>
     <row r="600">
       <c r="A600" s="2" t="n"/>
@@ -29462,6 +30077,7 @@
       <c r="AR600" s="2" t="n"/>
       <c r="AS600" s="2" t="n"/>
       <c r="AT600" s="2" t="n"/>
+      <c r="AU600" s="2" t="n"/>
     </row>
     <row r="601">
       <c r="A601" s="2" t="n"/>
@@ -29510,6 +30126,7 @@
       <c r="AR601" s="2" t="n"/>
       <c r="AS601" s="2" t="n"/>
       <c r="AT601" s="2" t="n"/>
+      <c r="AU601" s="2" t="n"/>
     </row>
     <row r="602">
       <c r="A602" s="2" t="n"/>
@@ -29558,6 +30175,7 @@
       <c r="AR602" s="2" t="n"/>
       <c r="AS602" s="2" t="n"/>
       <c r="AT602" s="2" t="n"/>
+      <c r="AU602" s="2" t="n"/>
     </row>
     <row r="603">
       <c r="A603" s="2" t="n"/>
@@ -29606,6 +30224,7 @@
       <c r="AR603" s="2" t="n"/>
       <c r="AS603" s="2" t="n"/>
       <c r="AT603" s="2" t="n"/>
+      <c r="AU603" s="2" t="n"/>
     </row>
     <row r="604">
       <c r="A604" s="2" t="n"/>
@@ -29654,6 +30273,7 @@
       <c r="AR604" s="2" t="n"/>
       <c r="AS604" s="2" t="n"/>
       <c r="AT604" s="2" t="n"/>
+      <c r="AU604" s="2" t="n"/>
     </row>
     <row r="605">
       <c r="A605" s="2" t="n"/>
@@ -29702,6 +30322,7 @@
       <c r="AR605" s="2" t="n"/>
       <c r="AS605" s="2" t="n"/>
       <c r="AT605" s="2" t="n"/>
+      <c r="AU605" s="2" t="n"/>
     </row>
     <row r="606">
       <c r="A606" s="2" t="n"/>
@@ -29750,6 +30371,7 @@
       <c r="AR606" s="2" t="n"/>
       <c r="AS606" s="2" t="n"/>
       <c r="AT606" s="2" t="n"/>
+      <c r="AU606" s="2" t="n"/>
     </row>
     <row r="607">
       <c r="A607" s="2" t="n"/>
@@ -29798,6 +30420,7 @@
       <c r="AR607" s="2" t="n"/>
       <c r="AS607" s="2" t="n"/>
       <c r="AT607" s="2" t="n"/>
+      <c r="AU607" s="2" t="n"/>
     </row>
     <row r="608">
       <c r="A608" s="2" t="n"/>
@@ -29846,6 +30469,7 @@
       <c r="AR608" s="2" t="n"/>
       <c r="AS608" s="2" t="n"/>
       <c r="AT608" s="2" t="n"/>
+      <c r="AU608" s="2" t="n"/>
     </row>
     <row r="609">
       <c r="A609" s="2" t="n"/>
@@ -29894,6 +30518,7 @@
       <c r="AR609" s="2" t="n"/>
       <c r="AS609" s="2" t="n"/>
       <c r="AT609" s="2" t="n"/>
+      <c r="AU609" s="2" t="n"/>
     </row>
     <row r="610">
       <c r="A610" s="2" t="n"/>
@@ -29942,6 +30567,7 @@
       <c r="AR610" s="2" t="n"/>
       <c r="AS610" s="2" t="n"/>
       <c r="AT610" s="2" t="n"/>
+      <c r="AU610" s="2" t="n"/>
     </row>
     <row r="611">
       <c r="A611" s="2" t="n"/>
@@ -29990,6 +30616,7 @@
       <c r="AR611" s="2" t="n"/>
       <c r="AS611" s="2" t="n"/>
       <c r="AT611" s="2" t="n"/>
+      <c r="AU611" s="2" t="n"/>
     </row>
     <row r="612">
       <c r="A612" s="2" t="n"/>
@@ -30038,6 +30665,7 @@
       <c r="AR612" s="2" t="n"/>
       <c r="AS612" s="2" t="n"/>
       <c r="AT612" s="2" t="n"/>
+      <c r="AU612" s="2" t="n"/>
     </row>
     <row r="613">
       <c r="A613" s="2" t="n"/>
@@ -30086,6 +30714,7 @@
       <c r="AR613" s="2" t="n"/>
       <c r="AS613" s="2" t="n"/>
       <c r="AT613" s="2" t="n"/>
+      <c r="AU613" s="2" t="n"/>
     </row>
     <row r="614">
       <c r="A614" s="2" t="n"/>
@@ -30134,6 +30763,7 @@
       <c r="AR614" s="2" t="n"/>
       <c r="AS614" s="2" t="n"/>
       <c r="AT614" s="2" t="n"/>
+      <c r="AU614" s="2" t="n"/>
     </row>
     <row r="615">
       <c r="A615" s="2" t="n"/>
@@ -30182,6 +30812,7 @@
       <c r="AR615" s="2" t="n"/>
       <c r="AS615" s="2" t="n"/>
       <c r="AT615" s="2" t="n"/>
+      <c r="AU615" s="2" t="n"/>
     </row>
     <row r="616">
       <c r="A616" s="2" t="n"/>
@@ -30230,6 +30861,7 @@
       <c r="AR616" s="2" t="n"/>
       <c r="AS616" s="2" t="n"/>
       <c r="AT616" s="2" t="n"/>
+      <c r="AU616" s="2" t="n"/>
     </row>
     <row r="617">
       <c r="A617" s="2" t="n"/>
@@ -30278,6 +30910,7 @@
       <c r="AR617" s="2" t="n"/>
       <c r="AS617" s="2" t="n"/>
       <c r="AT617" s="2" t="n"/>
+      <c r="AU617" s="2" t="n"/>
     </row>
     <row r="618">
       <c r="A618" s="2" t="n"/>
@@ -30326,6 +30959,7 @@
       <c r="AR618" s="2" t="n"/>
       <c r="AS618" s="2" t="n"/>
       <c r="AT618" s="2" t="n"/>
+      <c r="AU618" s="2" t="n"/>
     </row>
     <row r="619">
       <c r="A619" s="2" t="n"/>
@@ -30374,6 +31008,7 @@
       <c r="AR619" s="2" t="n"/>
       <c r="AS619" s="2" t="n"/>
       <c r="AT619" s="2" t="n"/>
+      <c r="AU619" s="2" t="n"/>
     </row>
     <row r="620">
       <c r="A620" s="2" t="n"/>
@@ -30422,6 +31057,7 @@
       <c r="AR620" s="2" t="n"/>
       <c r="AS620" s="2" t="n"/>
       <c r="AT620" s="2" t="n"/>
+      <c r="AU620" s="2" t="n"/>
     </row>
     <row r="621">
       <c r="A621" s="2" t="n"/>
@@ -30470,6 +31106,7 @@
       <c r="AR621" s="2" t="n"/>
       <c r="AS621" s="2" t="n"/>
       <c r="AT621" s="2" t="n"/>
+      <c r="AU621" s="2" t="n"/>
     </row>
     <row r="622">
       <c r="A622" s="2" t="n"/>
@@ -30518,6 +31155,7 @@
       <c r="AR622" s="2" t="n"/>
       <c r="AS622" s="2" t="n"/>
       <c r="AT622" s="2" t="n"/>
+      <c r="AU622" s="2" t="n"/>
     </row>
     <row r="623">
       <c r="A623" s="2" t="n"/>
@@ -30566,6 +31204,7 @@
       <c r="AR623" s="2" t="n"/>
       <c r="AS623" s="2" t="n"/>
       <c r="AT623" s="2" t="n"/>
+      <c r="AU623" s="2" t="n"/>
     </row>
     <row r="624">
       <c r="A624" s="2" t="n"/>
@@ -30614,6 +31253,7 @@
       <c r="AR624" s="2" t="n"/>
       <c r="AS624" s="2" t="n"/>
       <c r="AT624" s="2" t="n"/>
+      <c r="AU624" s="2" t="n"/>
     </row>
     <row r="625">
       <c r="A625" s="2" t="n"/>
@@ -30662,6 +31302,7 @@
       <c r="AR625" s="2" t="n"/>
       <c r="AS625" s="2" t="n"/>
       <c r="AT625" s="2" t="n"/>
+      <c r="AU625" s="2" t="n"/>
     </row>
     <row r="626">
       <c r="A626" s="2" t="n"/>
@@ -30710,6 +31351,7 @@
       <c r="AR626" s="2" t="n"/>
       <c r="AS626" s="2" t="n"/>
       <c r="AT626" s="2" t="n"/>
+      <c r="AU626" s="2" t="n"/>
     </row>
     <row r="627">
       <c r="A627" s="2" t="n"/>
@@ -30758,6 +31400,7 @@
       <c r="AR627" s="2" t="n"/>
       <c r="AS627" s="2" t="n"/>
       <c r="AT627" s="2" t="n"/>
+      <c r="AU627" s="2" t="n"/>
     </row>
     <row r="628">
       <c r="A628" s="2" t="n"/>
@@ -30806,6 +31449,7 @@
       <c r="AR628" s="2" t="n"/>
       <c r="AS628" s="2" t="n"/>
       <c r="AT628" s="2" t="n"/>
+      <c r="AU628" s="2" t="n"/>
     </row>
     <row r="629">
       <c r="A629" s="2" t="n"/>
@@ -30854,6 +31498,7 @@
       <c r="AR629" s="2" t="n"/>
       <c r="AS629" s="2" t="n"/>
       <c r="AT629" s="2" t="n"/>
+      <c r="AU629" s="2" t="n"/>
     </row>
     <row r="630">
       <c r="A630" s="2" t="n"/>
@@ -30902,6 +31547,7 @@
       <c r="AR630" s="2" t="n"/>
       <c r="AS630" s="2" t="n"/>
       <c r="AT630" s="2" t="n"/>
+      <c r="AU630" s="2" t="n"/>
     </row>
     <row r="631">
       <c r="A631" s="2" t="n"/>
@@ -30950,6 +31596,7 @@
       <c r="AR631" s="2" t="n"/>
       <c r="AS631" s="2" t="n"/>
       <c r="AT631" s="2" t="n"/>
+      <c r="AU631" s="2" t="n"/>
     </row>
     <row r="632">
       <c r="A632" s="2" t="n"/>
@@ -30998,6 +31645,7 @@
       <c r="AR632" s="2" t="n"/>
       <c r="AS632" s="2" t="n"/>
       <c r="AT632" s="2" t="n"/>
+      <c r="AU632" s="2" t="n"/>
     </row>
     <row r="633">
       <c r="A633" s="2" t="n"/>
@@ -31046,6 +31694,7 @@
       <c r="AR633" s="2" t="n"/>
       <c r="AS633" s="2" t="n"/>
       <c r="AT633" s="2" t="n"/>
+      <c r="AU633" s="2" t="n"/>
     </row>
     <row r="634">
       <c r="A634" s="2" t="n"/>
@@ -31094,6 +31743,7 @@
       <c r="AR634" s="2" t="n"/>
       <c r="AS634" s="2" t="n"/>
       <c r="AT634" s="2" t="n"/>
+      <c r="AU634" s="2" t="n"/>
     </row>
     <row r="635">
       <c r="A635" s="2" t="n"/>
@@ -31142,6 +31792,7 @@
       <c r="AR635" s="2" t="n"/>
       <c r="AS635" s="2" t="n"/>
       <c r="AT635" s="2" t="n"/>
+      <c r="AU635" s="2" t="n"/>
     </row>
     <row r="636">
       <c r="A636" s="2" t="n"/>
@@ -31190,6 +31841,7 @@
       <c r="AR636" s="2" t="n"/>
       <c r="AS636" s="2" t="n"/>
       <c r="AT636" s="2" t="n"/>
+      <c r="AU636" s="2" t="n"/>
     </row>
     <row r="637">
       <c r="A637" s="2" t="n"/>
@@ -31238,6 +31890,7 @@
       <c r="AR637" s="2" t="n"/>
       <c r="AS637" s="2" t="n"/>
       <c r="AT637" s="2" t="n"/>
+      <c r="AU637" s="2" t="n"/>
     </row>
     <row r="638">
       <c r="A638" s="2" t="n"/>
@@ -31286,6 +31939,7 @@
       <c r="AR638" s="2" t="n"/>
       <c r="AS638" s="2" t="n"/>
       <c r="AT638" s="2" t="n"/>
+      <c r="AU638" s="2" t="n"/>
     </row>
     <row r="639">
       <c r="A639" s="2" t="n"/>
@@ -31334,6 +31988,7 @@
       <c r="AR639" s="2" t="n"/>
       <c r="AS639" s="2" t="n"/>
       <c r="AT639" s="2" t="n"/>
+      <c r="AU639" s="2" t="n"/>
     </row>
     <row r="640">
       <c r="A640" s="2" t="n"/>
@@ -31382,6 +32037,7 @@
       <c r="AR640" s="2" t="n"/>
       <c r="AS640" s="2" t="n"/>
       <c r="AT640" s="2" t="n"/>
+      <c r="AU640" s="2" t="n"/>
     </row>
     <row r="641">
       <c r="A641" s="2" t="n"/>
@@ -31430,6 +32086,7 @@
       <c r="AR641" s="2" t="n"/>
       <c r="AS641" s="2" t="n"/>
       <c r="AT641" s="2" t="n"/>
+      <c r="AU641" s="2" t="n"/>
     </row>
     <row r="642">
       <c r="A642" s="2" t="n"/>
@@ -31478,6 +32135,7 @@
       <c r="AR642" s="2" t="n"/>
       <c r="AS642" s="2" t="n"/>
       <c r="AT642" s="2" t="n"/>
+      <c r="AU642" s="2" t="n"/>
     </row>
     <row r="643">
       <c r="A643" s="2" t="n"/>
@@ -31526,6 +32184,7 @@
       <c r="AR643" s="2" t="n"/>
       <c r="AS643" s="2" t="n"/>
       <c r="AT643" s="2" t="n"/>
+      <c r="AU643" s="2" t="n"/>
     </row>
     <row r="644">
       <c r="A644" s="2" t="n"/>
@@ -31574,6 +32233,7 @@
       <c r="AR644" s="2" t="n"/>
       <c r="AS644" s="2" t="n"/>
       <c r="AT644" s="2" t="n"/>
+      <c r="AU644" s="2" t="n"/>
     </row>
     <row r="645">
       <c r="A645" s="2" t="n"/>
@@ -31622,6 +32282,7 @@
       <c r="AR645" s="2" t="n"/>
       <c r="AS645" s="2" t="n"/>
       <c r="AT645" s="2" t="n"/>
+      <c r="AU645" s="2" t="n"/>
     </row>
     <row r="646">
       <c r="A646" s="2" t="n"/>
@@ -31670,6 +32331,7 @@
       <c r="AR646" s="2" t="n"/>
       <c r="AS646" s="2" t="n"/>
       <c r="AT646" s="2" t="n"/>
+      <c r="AU646" s="2" t="n"/>
     </row>
     <row r="647">
       <c r="A647" s="2" t="n"/>
@@ -31718,6 +32380,7 @@
       <c r="AR647" s="2" t="n"/>
       <c r="AS647" s="2" t="n"/>
       <c r="AT647" s="2" t="n"/>
+      <c r="AU647" s="2" t="n"/>
     </row>
     <row r="648">
       <c r="A648" s="2" t="n"/>
@@ -31766,6 +32429,7 @@
       <c r="AR648" s="2" t="n"/>
       <c r="AS648" s="2" t="n"/>
       <c r="AT648" s="2" t="n"/>
+      <c r="AU648" s="2" t="n"/>
     </row>
     <row r="649">
       <c r="A649" s="2" t="n"/>
@@ -31814,6 +32478,7 @@
       <c r="AR649" s="2" t="n"/>
       <c r="AS649" s="2" t="n"/>
       <c r="AT649" s="2" t="n"/>
+      <c r="AU649" s="2" t="n"/>
     </row>
     <row r="650">
       <c r="A650" s="2" t="n"/>
@@ -31862,6 +32527,7 @@
       <c r="AR650" s="2" t="n"/>
       <c r="AS650" s="2" t="n"/>
       <c r="AT650" s="2" t="n"/>
+      <c r="AU650" s="2" t="n"/>
     </row>
     <row r="651">
       <c r="A651" s="2" t="n"/>
@@ -31910,6 +32576,7 @@
       <c r="AR651" s="2" t="n"/>
       <c r="AS651" s="2" t="n"/>
       <c r="AT651" s="2" t="n"/>
+      <c r="AU651" s="2" t="n"/>
     </row>
     <row r="652">
       <c r="A652" s="2" t="n"/>
@@ -31958,6 +32625,7 @@
       <c r="AR652" s="2" t="n"/>
       <c r="AS652" s="2" t="n"/>
       <c r="AT652" s="2" t="n"/>
+      <c r="AU652" s="2" t="n"/>
     </row>
     <row r="653">
       <c r="A653" s="2" t="n"/>
@@ -32006,6 +32674,7 @@
       <c r="AR653" s="2" t="n"/>
       <c r="AS653" s="2" t="n"/>
       <c r="AT653" s="2" t="n"/>
+      <c r="AU653" s="2" t="n"/>
     </row>
     <row r="654">
       <c r="A654" s="2" t="n"/>
@@ -32054,6 +32723,7 @@
       <c r="AR654" s="2" t="n"/>
       <c r="AS654" s="2" t="n"/>
       <c r="AT654" s="2" t="n"/>
+      <c r="AU654" s="2" t="n"/>
     </row>
     <row r="655">
       <c r="A655" s="2" t="n"/>
@@ -32102,6 +32772,7 @@
       <c r="AR655" s="2" t="n"/>
       <c r="AS655" s="2" t="n"/>
       <c r="AT655" s="2" t="n"/>
+      <c r="AU655" s="2" t="n"/>
     </row>
     <row r="656">
       <c r="A656" s="2" t="n"/>
@@ -32150,6 +32821,7 @@
       <c r="AR656" s="2" t="n"/>
       <c r="AS656" s="2" t="n"/>
       <c r="AT656" s="2" t="n"/>
+      <c r="AU656" s="2" t="n"/>
     </row>
     <row r="657">
       <c r="A657" s="2" t="n"/>
@@ -32198,6 +32870,7 @@
       <c r="AR657" s="2" t="n"/>
       <c r="AS657" s="2" t="n"/>
       <c r="AT657" s="2" t="n"/>
+      <c r="AU657" s="2" t="n"/>
     </row>
     <row r="658">
       <c r="A658" s="2" t="n"/>
@@ -32246,6 +32919,7 @@
       <c r="AR658" s="2" t="n"/>
       <c r="AS658" s="2" t="n"/>
       <c r="AT658" s="2" t="n"/>
+      <c r="AU658" s="2" t="n"/>
     </row>
     <row r="659">
       <c r="A659" s="2" t="n"/>
@@ -32294,6 +32968,7 @@
       <c r="AR659" s="2" t="n"/>
       <c r="AS659" s="2" t="n"/>
       <c r="AT659" s="2" t="n"/>
+      <c r="AU659" s="2" t="n"/>
     </row>
     <row r="660">
       <c r="A660" s="2" t="n"/>
@@ -32342,6 +33017,7 @@
       <c r="AR660" s="2" t="n"/>
       <c r="AS660" s="2" t="n"/>
       <c r="AT660" s="2" t="n"/>
+      <c r="AU660" s="2" t="n"/>
     </row>
     <row r="661">
       <c r="A661" s="2" t="n"/>
@@ -32390,6 +33066,7 @@
       <c r="AR661" s="2" t="n"/>
       <c r="AS661" s="2" t="n"/>
       <c r="AT661" s="2" t="n"/>
+      <c r="AU661" s="2" t="n"/>
     </row>
     <row r="662">
       <c r="A662" s="2" t="n"/>
@@ -32438,6 +33115,7 @@
       <c r="AR662" s="2" t="n"/>
       <c r="AS662" s="2" t="n"/>
       <c r="AT662" s="2" t="n"/>
+      <c r="AU662" s="2" t="n"/>
     </row>
     <row r="663">
       <c r="A663" s="2" t="n"/>
@@ -32486,6 +33164,7 @@
       <c r="AR663" s="2" t="n"/>
       <c r="AS663" s="2" t="n"/>
       <c r="AT663" s="2" t="n"/>
+      <c r="AU663" s="2" t="n"/>
     </row>
     <row r="664">
       <c r="A664" s="2" t="n"/>
@@ -32534,6 +33213,7 @@
       <c r="AR664" s="2" t="n"/>
       <c r="AS664" s="2" t="n"/>
       <c r="AT664" s="2" t="n"/>
+      <c r="AU664" s="2" t="n"/>
     </row>
     <row r="665">
       <c r="A665" s="2" t="n"/>
@@ -32582,6 +33262,7 @@
       <c r="AR665" s="2" t="n"/>
       <c r="AS665" s="2" t="n"/>
       <c r="AT665" s="2" t="n"/>
+      <c r="AU665" s="2" t="n"/>
     </row>
     <row r="666">
       <c r="A666" s="2" t="n"/>
@@ -32630,6 +33311,7 @@
       <c r="AR666" s="2" t="n"/>
       <c r="AS666" s="2" t="n"/>
       <c r="AT666" s="2" t="n"/>
+      <c r="AU666" s="2" t="n"/>
     </row>
     <row r="667">
       <c r="A667" s="2" t="n"/>
@@ -32678,6 +33360,7 @@
       <c r="AR667" s="2" t="n"/>
       <c r="AS667" s="2" t="n"/>
       <c r="AT667" s="2" t="n"/>
+      <c r="AU667" s="2" t="n"/>
     </row>
     <row r="668">
       <c r="A668" s="2" t="n"/>
@@ -32726,6 +33409,7 @@
       <c r="AR668" s="2" t="n"/>
       <c r="AS668" s="2" t="n"/>
       <c r="AT668" s="2" t="n"/>
+      <c r="AU668" s="2" t="n"/>
     </row>
     <row r="669">
       <c r="A669" s="2" t="n"/>
@@ -32774,6 +33458,7 @@
       <c r="AR669" s="2" t="n"/>
       <c r="AS669" s="2" t="n"/>
       <c r="AT669" s="2" t="n"/>
+      <c r="AU669" s="2" t="n"/>
     </row>
     <row r="670">
       <c r="A670" s="2" t="n"/>
@@ -32822,6 +33507,7 @@
       <c r="AR670" s="2" t="n"/>
       <c r="AS670" s="2" t="n"/>
       <c r="AT670" s="2" t="n"/>
+      <c r="AU670" s="2" t="n"/>
     </row>
     <row r="671">
       <c r="A671" s="2" t="n"/>
@@ -32870,6 +33556,7 @@
       <c r="AR671" s="2" t="n"/>
       <c r="AS671" s="2" t="n"/>
       <c r="AT671" s="2" t="n"/>
+      <c r="AU671" s="2" t="n"/>
     </row>
     <row r="672">
       <c r="A672" s="2" t="n"/>
@@ -32918,6 +33605,7 @@
       <c r="AR672" s="2" t="n"/>
       <c r="AS672" s="2" t="n"/>
       <c r="AT672" s="2" t="n"/>
+      <c r="AU672" s="2" t="n"/>
     </row>
     <row r="673">
       <c r="A673" s="2" t="n"/>
@@ -32966,6 +33654,7 @@
       <c r="AR673" s="2" t="n"/>
       <c r="AS673" s="2" t="n"/>
       <c r="AT673" s="2" t="n"/>
+      <c r="AU673" s="2" t="n"/>
     </row>
     <row r="674">
       <c r="A674" s="2" t="n"/>
@@ -33014,6 +33703,7 @@
       <c r="AR674" s="2" t="n"/>
       <c r="AS674" s="2" t="n"/>
       <c r="AT674" s="2" t="n"/>
+      <c r="AU674" s="2" t="n"/>
     </row>
     <row r="675">
       <c r="A675" s="2" t="n"/>
@@ -33062,6 +33752,7 @@
       <c r="AR675" s="2" t="n"/>
       <c r="AS675" s="2" t="n"/>
       <c r="AT675" s="2" t="n"/>
+      <c r="AU675" s="2" t="n"/>
     </row>
     <row r="676">
       <c r="A676" s="2" t="n"/>
@@ -33110,6 +33801,7 @@
       <c r="AR676" s="2" t="n"/>
       <c r="AS676" s="2" t="n"/>
       <c r="AT676" s="2" t="n"/>
+      <c r="AU676" s="2" t="n"/>
     </row>
     <row r="677">
       <c r="A677" s="2" t="n"/>
@@ -33158,6 +33850,7 @@
       <c r="AR677" s="2" t="n"/>
       <c r="AS677" s="2" t="n"/>
       <c r="AT677" s="2" t="n"/>
+      <c r="AU677" s="2" t="n"/>
     </row>
     <row r="678">
       <c r="A678" s="2" t="n"/>
@@ -33206,6 +33899,7 @@
       <c r="AR678" s="2" t="n"/>
       <c r="AS678" s="2" t="n"/>
       <c r="AT678" s="2" t="n"/>
+      <c r="AU678" s="2" t="n"/>
     </row>
     <row r="679">
       <c r="A679" s="2" t="n"/>
@@ -33254,6 +33948,7 @@
       <c r="AR679" s="2" t="n"/>
       <c r="AS679" s="2" t="n"/>
       <c r="AT679" s="2" t="n"/>
+      <c r="AU679" s="2" t="n"/>
     </row>
     <row r="680">
       <c r="A680" s="2" t="n"/>
@@ -33302,6 +33997,7 @@
       <c r="AR680" s="2" t="n"/>
       <c r="AS680" s="2" t="n"/>
       <c r="AT680" s="2" t="n"/>
+      <c r="AU680" s="2" t="n"/>
     </row>
     <row r="681">
       <c r="A681" s="2" t="n"/>
@@ -33350,6 +34046,7 @@
       <c r="AR681" s="2" t="n"/>
       <c r="AS681" s="2" t="n"/>
       <c r="AT681" s="2" t="n"/>
+      <c r="AU681" s="2" t="n"/>
     </row>
     <row r="682">
       <c r="A682" s="2" t="n"/>
@@ -33398,6 +34095,7 @@
       <c r="AR682" s="2" t="n"/>
       <c r="AS682" s="2" t="n"/>
       <c r="AT682" s="2" t="n"/>
+      <c r="AU682" s="2" t="n"/>
     </row>
     <row r="683">
       <c r="A683" s="2" t="n"/>
@@ -33446,6 +34144,7 @@
       <c r="AR683" s="2" t="n"/>
       <c r="AS683" s="2" t="n"/>
       <c r="AT683" s="2" t="n"/>
+      <c r="AU683" s="2" t="n"/>
     </row>
     <row r="684">
       <c r="A684" s="2" t="n"/>
@@ -33494,6 +34193,7 @@
       <c r="AR684" s="2" t="n"/>
       <c r="AS684" s="2" t="n"/>
       <c r="AT684" s="2" t="n"/>
+      <c r="AU684" s="2" t="n"/>
     </row>
     <row r="685">
       <c r="A685" s="2" t="n"/>
@@ -33542,6 +34242,7 @@
       <c r="AR685" s="2" t="n"/>
       <c r="AS685" s="2" t="n"/>
       <c r="AT685" s="2" t="n"/>
+      <c r="AU685" s="2" t="n"/>
     </row>
     <row r="686">
       <c r="A686" s="2" t="n"/>
@@ -33590,6 +34291,7 @@
       <c r="AR686" s="2" t="n"/>
       <c r="AS686" s="2" t="n"/>
       <c r="AT686" s="2" t="n"/>
+      <c r="AU686" s="2" t="n"/>
     </row>
     <row r="687">
       <c r="A687" s="2" t="n"/>
@@ -33638,6 +34340,7 @@
       <c r="AR687" s="2" t="n"/>
       <c r="AS687" s="2" t="n"/>
       <c r="AT687" s="2" t="n"/>
+      <c r="AU687" s="2" t="n"/>
     </row>
     <row r="688">
       <c r="A688" s="2" t="n"/>
@@ -33686,6 +34389,7 @@
       <c r="AR688" s="2" t="n"/>
       <c r="AS688" s="2" t="n"/>
       <c r="AT688" s="2" t="n"/>
+      <c r="AU688" s="2" t="n"/>
     </row>
     <row r="689">
       <c r="A689" s="2" t="n"/>
@@ -33734,6 +34438,7 @@
       <c r="AR689" s="2" t="n"/>
       <c r="AS689" s="2" t="n"/>
       <c r="AT689" s="2" t="n"/>
+      <c r="AU689" s="2" t="n"/>
     </row>
     <row r="690">
       <c r="A690" s="2" t="n"/>
@@ -33782,6 +34487,7 @@
       <c r="AR690" s="2" t="n"/>
       <c r="AS690" s="2" t="n"/>
       <c r="AT690" s="2" t="n"/>
+      <c r="AU690" s="2" t="n"/>
     </row>
     <row r="691">
       <c r="A691" s="2" t="n"/>
@@ -33830,6 +34536,7 @@
       <c r="AR691" s="2" t="n"/>
       <c r="AS691" s="2" t="n"/>
       <c r="AT691" s="2" t="n"/>
+      <c r="AU691" s="2" t="n"/>
     </row>
     <row r="692">
       <c r="A692" s="2" t="n"/>
@@ -33878,6 +34585,7 @@
       <c r="AR692" s="2" t="n"/>
       <c r="AS692" s="2" t="n"/>
       <c r="AT692" s="2" t="n"/>
+      <c r="AU692" s="2" t="n"/>
     </row>
     <row r="693">
       <c r="A693" s="2" t="n"/>
@@ -33926,6 +34634,7 @@
       <c r="AR693" s="2" t="n"/>
       <c r="AS693" s="2" t="n"/>
       <c r="AT693" s="2" t="n"/>
+      <c r="AU693" s="2" t="n"/>
     </row>
     <row r="694">
       <c r="A694" s="2" t="n"/>
@@ -33974,6 +34683,7 @@
       <c r="AR694" s="2" t="n"/>
       <c r="AS694" s="2" t="n"/>
       <c r="AT694" s="2" t="n"/>
+      <c r="AU694" s="2" t="n"/>
     </row>
     <row r="695">
       <c r="A695" s="2" t="n"/>
@@ -34022,6 +34732,7 @@
       <c r="AR695" s="2" t="n"/>
       <c r="AS695" s="2" t="n"/>
       <c r="AT695" s="2" t="n"/>
+      <c r="AU695" s="2" t="n"/>
     </row>
     <row r="696">
       <c r="A696" s="2" t="n"/>
@@ -34070,6 +34781,7 @@
       <c r="AR696" s="2" t="n"/>
       <c r="AS696" s="2" t="n"/>
       <c r="AT696" s="2" t="n"/>
+      <c r="AU696" s="2" t="n"/>
     </row>
     <row r="697">
       <c r="A697" s="2" t="n"/>
@@ -34118,6 +34830,7 @@
       <c r="AR697" s="2" t="n"/>
       <c r="AS697" s="2" t="n"/>
       <c r="AT697" s="2" t="n"/>
+      <c r="AU697" s="2" t="n"/>
     </row>
     <row r="698">
       <c r="A698" s="2" t="n"/>
@@ -34166,6 +34879,7 @@
       <c r="AR698" s="2" t="n"/>
       <c r="AS698" s="2" t="n"/>
       <c r="AT698" s="2" t="n"/>
+      <c r="AU698" s="2" t="n"/>
     </row>
     <row r="699">
       <c r="A699" s="2" t="n"/>
@@ -34214,6 +34928,7 @@
       <c r="AR699" s="2" t="n"/>
       <c r="AS699" s="2" t="n"/>
       <c r="AT699" s="2" t="n"/>
+      <c r="AU699" s="2" t="n"/>
     </row>
     <row r="700">
       <c r="A700" s="2" t="n"/>
@@ -34262,6 +34977,7 @@
       <c r="AR700" s="2" t="n"/>
       <c r="AS700" s="2" t="n"/>
       <c r="AT700" s="2" t="n"/>
+      <c r="AU700" s="2" t="n"/>
     </row>
     <row r="701">
       <c r="A701" s="2" t="n"/>
@@ -34310,6 +35026,7 @@
       <c r="AR701" s="2" t="n"/>
       <c r="AS701" s="2" t="n"/>
       <c r="AT701" s="2" t="n"/>
+      <c r="AU701" s="2" t="n"/>
     </row>
     <row r="702">
       <c r="A702" s="2" t="n"/>
@@ -34358,6 +35075,7 @@
       <c r="AR702" s="2" t="n"/>
       <c r="AS702" s="2" t="n"/>
       <c r="AT702" s="2" t="n"/>
+      <c r="AU702" s="2" t="n"/>
     </row>
     <row r="703">
       <c r="A703" s="2" t="n"/>
@@ -34406,6 +35124,7 @@
       <c r="AR703" s="2" t="n"/>
       <c r="AS703" s="2" t="n"/>
       <c r="AT703" s="2" t="n"/>
+      <c r="AU703" s="2" t="n"/>
     </row>
     <row r="704">
       <c r="A704" s="2" t="n"/>
@@ -34454,6 +35173,7 @@
       <c r="AR704" s="2" t="n"/>
       <c r="AS704" s="2" t="n"/>
       <c r="AT704" s="2" t="n"/>
+      <c r="AU704" s="2" t="n"/>
     </row>
     <row r="705">
       <c r="A705" s="2" t="n"/>
@@ -34502,6 +35222,7 @@
       <c r="AR705" s="2" t="n"/>
       <c r="AS705" s="2" t="n"/>
       <c r="AT705" s="2" t="n"/>
+      <c r="AU705" s="2" t="n"/>
     </row>
     <row r="706">
       <c r="A706" s="2" t="n"/>
@@ -34550,6 +35271,7 @@
       <c r="AR706" s="2" t="n"/>
       <c r="AS706" s="2" t="n"/>
       <c r="AT706" s="2" t="n"/>
+      <c r="AU706" s="2" t="n"/>
     </row>
     <row r="707">
       <c r="A707" s="2" t="n"/>
@@ -34598,6 +35320,7 @@
       <c r="AR707" s="2" t="n"/>
       <c r="AS707" s="2" t="n"/>
       <c r="AT707" s="2" t="n"/>
+      <c r="AU707" s="2" t="n"/>
     </row>
     <row r="708">
       <c r="A708" s="2" t="n"/>
@@ -34646,6 +35369,7 @@
       <c r="AR708" s="2" t="n"/>
       <c r="AS708" s="2" t="n"/>
       <c r="AT708" s="2" t="n"/>
+      <c r="AU708" s="2" t="n"/>
     </row>
     <row r="709">
       <c r="A709" s="2" t="n"/>
@@ -34694,6 +35418,7 @@
       <c r="AR709" s="2" t="n"/>
       <c r="AS709" s="2" t="n"/>
       <c r="AT709" s="2" t="n"/>
+      <c r="AU709" s="2" t="n"/>
     </row>
     <row r="710">
       <c r="A710" s="2" t="n"/>
@@ -34742,6 +35467,7 @@
       <c r="AR710" s="2" t="n"/>
       <c r="AS710" s="2" t="n"/>
       <c r="AT710" s="2" t="n"/>
+      <c r="AU710" s="2" t="n"/>
     </row>
     <row r="711">
       <c r="A711" s="2" t="n"/>
@@ -34790,6 +35516,7 @@
       <c r="AR711" s="2" t="n"/>
       <c r="AS711" s="2" t="n"/>
       <c r="AT711" s="2" t="n"/>
+      <c r="AU711" s="2" t="n"/>
     </row>
     <row r="712">
       <c r="A712" s="2" t="n"/>
@@ -34838,6 +35565,7 @@
       <c r="AR712" s="2" t="n"/>
       <c r="AS712" s="2" t="n"/>
       <c r="AT712" s="2" t="n"/>
+      <c r="AU712" s="2" t="n"/>
     </row>
     <row r="713">
       <c r="A713" s="2" t="n"/>
@@ -34886,6 +35614,7 @@
       <c r="AR713" s="2" t="n"/>
       <c r="AS713" s="2" t="n"/>
       <c r="AT713" s="2" t="n"/>
+      <c r="AU713" s="2" t="n"/>
     </row>
     <row r="714">
       <c r="A714" s="2" t="n"/>
@@ -34934,6 +35663,7 @@
       <c r="AR714" s="2" t="n"/>
       <c r="AS714" s="2" t="n"/>
       <c r="AT714" s="2" t="n"/>
+      <c r="AU714" s="2" t="n"/>
     </row>
     <row r="715">
       <c r="A715" s="2" t="n"/>
@@ -34982,6 +35712,7 @@
       <c r="AR715" s="2" t="n"/>
       <c r="AS715" s="2" t="n"/>
       <c r="AT715" s="2" t="n"/>
+      <c r="AU715" s="2" t="n"/>
     </row>
     <row r="716">
       <c r="A716" s="2" t="n"/>
@@ -35030,6 +35761,7 @@
       <c r="AR716" s="2" t="n"/>
       <c r="AS716" s="2" t="n"/>
       <c r="AT716" s="2" t="n"/>
+      <c r="AU716" s="2" t="n"/>
     </row>
     <row r="717">
       <c r="A717" s="2" t="n"/>
@@ -35078,6 +35810,7 @@
       <c r="AR717" s="2" t="n"/>
       <c r="AS717" s="2" t="n"/>
       <c r="AT717" s="2" t="n"/>
+      <c r="AU717" s="2" t="n"/>
     </row>
     <row r="718">
       <c r="A718" s="2" t="n"/>
@@ -35126,6 +35859,7 @@
       <c r="AR718" s="2" t="n"/>
       <c r="AS718" s="2" t="n"/>
       <c r="AT718" s="2" t="n"/>
+      <c r="AU718" s="2" t="n"/>
     </row>
     <row r="719">
       <c r="A719" s="2" t="n"/>
@@ -35174,6 +35908,7 @@
       <c r="AR719" s="2" t="n"/>
       <c r="AS719" s="2" t="n"/>
       <c r="AT719" s="2" t="n"/>
+      <c r="AU719" s="2" t="n"/>
     </row>
     <row r="720">
       <c r="A720" s="2" t="n"/>
@@ -35222,6 +35957,7 @@
       <c r="AR720" s="2" t="n"/>
       <c r="AS720" s="2" t="n"/>
       <c r="AT720" s="2" t="n"/>
+      <c r="AU720" s="2" t="n"/>
     </row>
     <row r="721">
       <c r="A721" s="2" t="n"/>
@@ -35270,6 +36006,7 @@
       <c r="AR721" s="2" t="n"/>
       <c r="AS721" s="2" t="n"/>
       <c r="AT721" s="2" t="n"/>
+      <c r="AU721" s="2" t="n"/>
     </row>
     <row r="722">
       <c r="A722" s="2" t="n"/>
@@ -35318,6 +36055,7 @@
       <c r="AR722" s="2" t="n"/>
       <c r="AS722" s="2" t="n"/>
       <c r="AT722" s="2" t="n"/>
+      <c r="AU722" s="2" t="n"/>
     </row>
     <row r="723">
       <c r="A723" s="2" t="n"/>
@@ -35366,6 +36104,7 @@
       <c r="AR723" s="2" t="n"/>
       <c r="AS723" s="2" t="n"/>
       <c r="AT723" s="2" t="n"/>
+      <c r="AU723" s="2" t="n"/>
     </row>
     <row r="724">
       <c r="A724" s="2" t="n"/>
@@ -35414,6 +36153,7 @@
       <c r="AR724" s="2" t="n"/>
       <c r="AS724" s="2" t="n"/>
       <c r="AT724" s="2" t="n"/>
+      <c r="AU724" s="2" t="n"/>
     </row>
     <row r="725">
       <c r="A725" s="2" t="n"/>
@@ -35462,6 +36202,7 @@
       <c r="AR725" s="2" t="n"/>
       <c r="AS725" s="2" t="n"/>
       <c r="AT725" s="2" t="n"/>
+      <c r="AU725" s="2" t="n"/>
     </row>
     <row r="726">
       <c r="A726" s="2" t="n"/>
@@ -35510,6 +36251,7 @@
       <c r="AR726" s="2" t="n"/>
       <c r="AS726" s="2" t="n"/>
       <c r="AT726" s="2" t="n"/>
+      <c r="AU726" s="2" t="n"/>
     </row>
     <row r="727">
       <c r="A727" s="2" t="n"/>
@@ -35558,6 +36300,7 @@
       <c r="AR727" s="2" t="n"/>
       <c r="AS727" s="2" t="n"/>
       <c r="AT727" s="2" t="n"/>
+      <c r="AU727" s="2" t="n"/>
     </row>
     <row r="728">
       <c r="A728" s="2" t="n"/>
@@ -35606,6 +36349,7 @@
       <c r="AR728" s="2" t="n"/>
       <c r="AS728" s="2" t="n"/>
       <c r="AT728" s="2" t="n"/>
+      <c r="AU728" s="2" t="n"/>
     </row>
     <row r="729">
       <c r="A729" s="2" t="n"/>
@@ -35654,6 +36398,7 @@
       <c r="AR729" s="2" t="n"/>
       <c r="AS729" s="2" t="n"/>
       <c r="AT729" s="2" t="n"/>
+      <c r="AU729" s="2" t="n"/>
     </row>
     <row r="730">
       <c r="A730" s="2" t="n"/>
@@ -35702,6 +36447,7 @@
       <c r="AR730" s="2" t="n"/>
       <c r="AS730" s="2" t="n"/>
       <c r="AT730" s="2" t="n"/>
+      <c r="AU730" s="2" t="n"/>
     </row>
     <row r="731">
       <c r="A731" s="2" t="n"/>
@@ -35750,6 +36496,7 @@
       <c r="AR731" s="2" t="n"/>
       <c r="AS731" s="2" t="n"/>
       <c r="AT731" s="2" t="n"/>
+      <c r="AU731" s="2" t="n"/>
     </row>
     <row r="732">
       <c r="A732" s="2" t="n"/>
@@ -35798,6 +36545,7 @@
       <c r="AR732" s="2" t="n"/>
       <c r="AS732" s="2" t="n"/>
       <c r="AT732" s="2" t="n"/>
+      <c r="AU732" s="2" t="n"/>
     </row>
     <row r="733">
       <c r="A733" s="2" t="n"/>
@@ -35846,6 +36594,7 @@
       <c r="AR733" s="2" t="n"/>
       <c r="AS733" s="2" t="n"/>
       <c r="AT733" s="2" t="n"/>
+      <c r="AU733" s="2" t="n"/>
     </row>
     <row r="734">
       <c r="A734" s="2" t="n"/>
@@ -35894,6 +36643,7 @@
       <c r="AR734" s="2" t="n"/>
       <c r="AS734" s="2" t="n"/>
       <c r="AT734" s="2" t="n"/>
+      <c r="AU734" s="2" t="n"/>
     </row>
     <row r="735">
       <c r="A735" s="2" t="n"/>
@@ -35942,6 +36692,7 @@
       <c r="AR735" s="2" t="n"/>
       <c r="AS735" s="2" t="n"/>
       <c r="AT735" s="2" t="n"/>
+      <c r="AU735" s="2" t="n"/>
     </row>
     <row r="736">
       <c r="A736" s="2" t="n"/>
@@ -35990,6 +36741,7 @@
       <c r="AR736" s="2" t="n"/>
       <c r="AS736" s="2" t="n"/>
       <c r="AT736" s="2" t="n"/>
+      <c r="AU736" s="2" t="n"/>
     </row>
     <row r="737">
       <c r="A737" s="2" t="n"/>
@@ -36038,6 +36790,7 @@
       <c r="AR737" s="2" t="n"/>
       <c r="AS737" s="2" t="n"/>
       <c r="AT737" s="2" t="n"/>
+      <c r="AU737" s="2" t="n"/>
     </row>
     <row r="738">
       <c r="A738" s="2" t="n"/>
@@ -36086,6 +36839,7 @@
       <c r="AR738" s="2" t="n"/>
       <c r="AS738" s="2" t="n"/>
       <c r="AT738" s="2" t="n"/>
+      <c r="AU738" s="2" t="n"/>
     </row>
     <row r="739">
       <c r="A739" s="2" t="n"/>
@@ -36134,6 +36888,7 @@
       <c r="AR739" s="2" t="n"/>
       <c r="AS739" s="2" t="n"/>
       <c r="AT739" s="2" t="n"/>
+      <c r="AU739" s="2" t="n"/>
     </row>
     <row r="740">
       <c r="A740" s="2" t="n"/>
@@ -36182,6 +36937,7 @@
       <c r="AR740" s="2" t="n"/>
       <c r="AS740" s="2" t="n"/>
       <c r="AT740" s="2" t="n"/>
+      <c r="AU740" s="2" t="n"/>
     </row>
     <row r="741">
       <c r="A741" s="2" t="n"/>
@@ -36230,6 +36986,7 @@
       <c r="AR741" s="2" t="n"/>
       <c r="AS741" s="2" t="n"/>
       <c r="AT741" s="2" t="n"/>
+      <c r="AU741" s="2" t="n"/>
     </row>
     <row r="742">
       <c r="A742" s="2" t="n"/>
@@ -36278,6 +37035,7 @@
       <c r="AR742" s="2" t="n"/>
       <c r="AS742" s="2" t="n"/>
       <c r="AT742" s="2" t="n"/>
+      <c r="AU742" s="2" t="n"/>
     </row>
     <row r="743">
       <c r="A743" s="2" t="n"/>
@@ -36326,6 +37084,7 @@
       <c r="AR743" s="2" t="n"/>
       <c r="AS743" s="2" t="n"/>
       <c r="AT743" s="2" t="n"/>
+      <c r="AU743" s="2" t="n"/>
     </row>
     <row r="744">
       <c r="A744" s="2" t="n"/>
@@ -36374,6 +37133,7 @@
       <c r="AR744" s="2" t="n"/>
       <c r="AS744" s="2" t="n"/>
       <c r="AT744" s="2" t="n"/>
+      <c r="AU744" s="2" t="n"/>
     </row>
     <row r="745">
       <c r="A745" s="2" t="n"/>
@@ -36422,6 +37182,7 @@
       <c r="AR745" s="2" t="n"/>
       <c r="AS745" s="2" t="n"/>
       <c r="AT745" s="2" t="n"/>
+      <c r="AU745" s="2" t="n"/>
     </row>
     <row r="746">
       <c r="A746" s="2" t="n"/>
@@ -36470,6 +37231,7 @@
       <c r="AR746" s="2" t="n"/>
       <c r="AS746" s="2" t="n"/>
       <c r="AT746" s="2" t="n"/>
+      <c r="AU746" s="2" t="n"/>
     </row>
     <row r="747">
       <c r="A747" s="2" t="n"/>
@@ -36518,6 +37280,7 @@
       <c r="AR747" s="2" t="n"/>
       <c r="AS747" s="2" t="n"/>
       <c r="AT747" s="2" t="n"/>
+      <c r="AU747" s="2" t="n"/>
     </row>
     <row r="748">
       <c r="A748" s="2" t="n"/>
@@ -36566,6 +37329,7 @@
       <c r="AR748" s="2" t="n"/>
       <c r="AS748" s="2" t="n"/>
       <c r="AT748" s="2" t="n"/>
+      <c r="AU748" s="2" t="n"/>
     </row>
     <row r="749">
       <c r="A749" s="2" t="n"/>
@@ -36614,6 +37378,7 @@
       <c r="AR749" s="2" t="n"/>
       <c r="AS749" s="2" t="n"/>
       <c r="AT749" s="2" t="n"/>
+      <c r="AU749" s="2" t="n"/>
     </row>
     <row r="750">
       <c r="A750" s="2" t="n"/>
@@ -36662,6 +37427,7 @@
       <c r="AR750" s="2" t="n"/>
       <c r="AS750" s="2" t="n"/>
       <c r="AT750" s="2" t="n"/>
+      <c r="AU750" s="2" t="n"/>
     </row>
     <row r="751">
       <c r="A751" s="2" t="n"/>
@@ -36710,6 +37476,7 @@
       <c r="AR751" s="2" t="n"/>
       <c r="AS751" s="2" t="n"/>
       <c r="AT751" s="2" t="n"/>
+      <c r="AU751" s="2" t="n"/>
     </row>
     <row r="752">
       <c r="A752" s="2" t="n"/>
@@ -36758,6 +37525,7 @@
       <c r="AR752" s="2" t="n"/>
       <c r="AS752" s="2" t="n"/>
       <c r="AT752" s="2" t="n"/>
+      <c r="AU752" s="2" t="n"/>
     </row>
     <row r="753">
       <c r="A753" s="2" t="n"/>
@@ -36806,6 +37574,7 @@
       <c r="AR753" s="2" t="n"/>
       <c r="AS753" s="2" t="n"/>
       <c r="AT753" s="2" t="n"/>
+      <c r="AU753" s="2" t="n"/>
     </row>
     <row r="754">
       <c r="A754" s="2" t="n"/>
@@ -36854,6 +37623,7 @@
       <c r="AR754" s="2" t="n"/>
       <c r="AS754" s="2" t="n"/>
       <c r="AT754" s="2" t="n"/>
+      <c r="AU754" s="2" t="n"/>
     </row>
     <row r="755">
       <c r="A755" s="2" t="n"/>
@@ -36902,6 +37672,7 @@
       <c r="AR755" s="2" t="n"/>
       <c r="AS755" s="2" t="n"/>
       <c r="AT755" s="2" t="n"/>
+      <c r="AU755" s="2" t="n"/>
     </row>
     <row r="756">
       <c r="A756" s="2" t="n"/>
@@ -36950,6 +37721,7 @@
       <c r="AR756" s="2" t="n"/>
       <c r="AS756" s="2" t="n"/>
       <c r="AT756" s="2" t="n"/>
+      <c r="AU756" s="2" t="n"/>
     </row>
     <row r="757">
       <c r="A757" s="2" t="n"/>
@@ -36998,6 +37770,7 @@
       <c r="AR757" s="2" t="n"/>
       <c r="AS757" s="2" t="n"/>
       <c r="AT757" s="2" t="n"/>
+      <c r="AU757" s="2" t="n"/>
     </row>
     <row r="758">
       <c r="A758" s="2" t="n"/>
@@ -37046,6 +37819,7 @@
       <c r="AR758" s="2" t="n"/>
       <c r="AS758" s="2" t="n"/>
       <c r="AT758" s="2" t="n"/>
+      <c r="AU758" s="2" t="n"/>
     </row>
     <row r="759">
       <c r="A759" s="2" t="n"/>
@@ -37094,6 +37868,7 @@
       <c r="AR759" s="2" t="n"/>
       <c r="AS759" s="2" t="n"/>
       <c r="AT759" s="2" t="n"/>
+      <c r="AU759" s="2" t="n"/>
     </row>
     <row r="760">
       <c r="A760" s="2" t="n"/>
@@ -37142,6 +37917,7 @@
       <c r="AR760" s="2" t="n"/>
       <c r="AS760" s="2" t="n"/>
       <c r="AT760" s="2" t="n"/>
+      <c r="AU760" s="2" t="n"/>
     </row>
     <row r="761">
       <c r="A761" s="2" t="n"/>
@@ -37190,6 +37966,7 @@
       <c r="AR761" s="2" t="n"/>
       <c r="AS761" s="2" t="n"/>
       <c r="AT761" s="2" t="n"/>
+      <c r="AU761" s="2" t="n"/>
     </row>
     <row r="762">
       <c r="A762" s="2" t="n"/>
@@ -37238,6 +38015,7 @@
       <c r="AR762" s="2" t="n"/>
       <c r="AS762" s="2" t="n"/>
       <c r="AT762" s="2" t="n"/>
+      <c r="AU762" s="2" t="n"/>
     </row>
     <row r="763">
       <c r="A763" s="2" t="n"/>
@@ -37286,6 +38064,7 @@
       <c r="AR763" s="2" t="n"/>
       <c r="AS763" s="2" t="n"/>
       <c r="AT763" s="2" t="n"/>
+      <c r="AU763" s="2" t="n"/>
     </row>
     <row r="764">
       <c r="A764" s="2" t="n"/>
@@ -37334,6 +38113,7 @@
       <c r="AR764" s="2" t="n"/>
       <c r="AS764" s="2" t="n"/>
       <c r="AT764" s="2" t="n"/>
+      <c r="AU764" s="2" t="n"/>
     </row>
     <row r="765">
       <c r="A765" s="2" t="n"/>
@@ -37382,6 +38162,7 @@
       <c r="AR765" s="2" t="n"/>
       <c r="AS765" s="2" t="n"/>
       <c r="AT765" s="2" t="n"/>
+      <c r="AU765" s="2" t="n"/>
     </row>
     <row r="766">
       <c r="A766" s="2" t="n"/>
@@ -37430,6 +38211,7 @@
       <c r="AR766" s="2" t="n"/>
       <c r="AS766" s="2" t="n"/>
       <c r="AT766" s="2" t="n"/>
+      <c r="AU766" s="2" t="n"/>
     </row>
     <row r="767">
       <c r="A767" s="2" t="n"/>
@@ -37478,6 +38260,7 @@
       <c r="AR767" s="2" t="n"/>
       <c r="AS767" s="2" t="n"/>
       <c r="AT767" s="2" t="n"/>
+      <c r="AU767" s="2" t="n"/>
     </row>
     <row r="768">
       <c r="A768" s="2" t="n"/>
@@ -37526,6 +38309,7 @@
       <c r="AR768" s="2" t="n"/>
       <c r="AS768" s="2" t="n"/>
       <c r="AT768" s="2" t="n"/>
+      <c r="AU768" s="2" t="n"/>
     </row>
     <row r="769">
       <c r="A769" s="2" t="n"/>
@@ -37574,6 +38358,7 @@
       <c r="AR769" s="2" t="n"/>
       <c r="AS769" s="2" t="n"/>
       <c r="AT769" s="2" t="n"/>
+      <c r="AU769" s="2" t="n"/>
     </row>
     <row r="770">
       <c r="A770" s="2" t="n"/>
@@ -37622,6 +38407,7 @@
       <c r="AR770" s="2" t="n"/>
       <c r="AS770" s="2" t="n"/>
       <c r="AT770" s="2" t="n"/>
+      <c r="AU770" s="2" t="n"/>
     </row>
     <row r="771">
       <c r="A771" s="2" t="n"/>
@@ -37670,6 +38456,7 @@
       <c r="AR771" s="2" t="n"/>
       <c r="AS771" s="2" t="n"/>
       <c r="AT771" s="2" t="n"/>
+      <c r="AU771" s="2" t="n"/>
     </row>
     <row r="772">
       <c r="A772" s="2" t="n"/>
@@ -37718,6 +38505,7 @@
       <c r="AR772" s="2" t="n"/>
       <c r="AS772" s="2" t="n"/>
       <c r="AT772" s="2" t="n"/>
+      <c r="AU772" s="2" t="n"/>
     </row>
     <row r="773">
       <c r="A773" s="2" t="n"/>
@@ -37766,6 +38554,7 @@
       <c r="AR773" s="2" t="n"/>
       <c r="AS773" s="2" t="n"/>
       <c r="AT773" s="2" t="n"/>
+      <c r="AU773" s="2" t="n"/>
     </row>
     <row r="774">
       <c r="A774" s="2" t="n"/>
@@ -37814,6 +38603,7 @@
       <c r="AR774" s="2" t="n"/>
       <c r="AS774" s="2" t="n"/>
       <c r="AT774" s="2" t="n"/>
+      <c r="AU774" s="2" t="n"/>
     </row>
     <row r="775">
       <c r="A775" s="2" t="n"/>
@@ -37862,6 +38652,7 @@
       <c r="AR775" s="2" t="n"/>
       <c r="AS775" s="2" t="n"/>
       <c r="AT775" s="2" t="n"/>
+      <c r="AU775" s="2" t="n"/>
     </row>
     <row r="776">
       <c r="A776" s="2" t="n"/>
@@ -37910,6 +38701,7 @@
       <c r="AR776" s="2" t="n"/>
       <c r="AS776" s="2" t="n"/>
       <c r="AT776" s="2" t="n"/>
+      <c r="AU776" s="2" t="n"/>
     </row>
     <row r="777">
       <c r="A777" s="2" t="n"/>
@@ -37958,6 +38750,7 @@
       <c r="AR777" s="2" t="n"/>
       <c r="AS777" s="2" t="n"/>
       <c r="AT777" s="2" t="n"/>
+      <c r="AU777" s="2" t="n"/>
     </row>
     <row r="778">
       <c r="A778" s="2" t="n"/>
@@ -38006,6 +38799,7 @@
       <c r="AR778" s="2" t="n"/>
       <c r="AS778" s="2" t="n"/>
       <c r="AT778" s="2" t="n"/>
+      <c r="AU778" s="2" t="n"/>
     </row>
     <row r="779">
       <c r="A779" s="2" t="n"/>
@@ -38054,6 +38848,7 @@
       <c r="AR779" s="2" t="n"/>
       <c r="AS779" s="2" t="n"/>
       <c r="AT779" s="2" t="n"/>
+      <c r="AU779" s="2" t="n"/>
     </row>
     <row r="780">
       <c r="A780" s="2" t="n"/>
@@ -38102,6 +38897,7 @@
       <c r="AR780" s="2" t="n"/>
       <c r="AS780" s="2" t="n"/>
       <c r="AT780" s="2" t="n"/>
+      <c r="AU780" s="2" t="n"/>
     </row>
     <row r="781">
       <c r="A781" s="2" t="n"/>
@@ -38150,6 +38946,7 @@
       <c r="AR781" s="2" t="n"/>
       <c r="AS781" s="2" t="n"/>
       <c r="AT781" s="2" t="n"/>
+      <c r="AU781" s="2" t="n"/>
     </row>
     <row r="782">
       <c r="A782" s="2" t="n"/>
@@ -38198,6 +38995,7 @@
       <c r="AR782" s="2" t="n"/>
       <c r="AS782" s="2" t="n"/>
       <c r="AT782" s="2" t="n"/>
+      <c r="AU782" s="2" t="n"/>
     </row>
     <row r="783">
       <c r="A783" s="2" t="n"/>
@@ -38246,6 +39044,7 @@
       <c r="AR783" s="2" t="n"/>
       <c r="AS783" s="2" t="n"/>
       <c r="AT783" s="2" t="n"/>
+      <c r="AU783" s="2" t="n"/>
     </row>
     <row r="784">
       <c r="A784" s="2" t="n"/>
@@ -38294,6 +39093,7 @@
       <c r="AR784" s="2" t="n"/>
       <c r="AS784" s="2" t="n"/>
       <c r="AT784" s="2" t="n"/>
+      <c r="AU784" s="2" t="n"/>
     </row>
     <row r="785">
       <c r="A785" s="2" t="n"/>
@@ -38342,6 +39142,7 @@
       <c r="AR785" s="2" t="n"/>
       <c r="AS785" s="2" t="n"/>
       <c r="AT785" s="2" t="n"/>
+      <c r="AU785" s="2" t="n"/>
     </row>
     <row r="786">
       <c r="A786" s="2" t="n"/>
@@ -38390,6 +39191,7 @@
       <c r="AR786" s="2" t="n"/>
       <c r="AS786" s="2" t="n"/>
       <c r="AT786" s="2" t="n"/>
+      <c r="AU786" s="2" t="n"/>
     </row>
     <row r="787">
       <c r="A787" s="2" t="n"/>
@@ -38438,6 +39240,7 @@
       <c r="AR787" s="2" t="n"/>
       <c r="AS787" s="2" t="n"/>
       <c r="AT787" s="2" t="n"/>
+      <c r="AU787" s="2" t="n"/>
     </row>
     <row r="788">
       <c r="A788" s="2" t="n"/>
@@ -38486,6 +39289,7 @@
       <c r="AR788" s="2" t="n"/>
       <c r="AS788" s="2" t="n"/>
       <c r="AT788" s="2" t="n"/>
+      <c r="AU788" s="2" t="n"/>
     </row>
     <row r="789">
       <c r="A789" s="2" t="n"/>
@@ -38534,6 +39338,7 @@
       <c r="AR789" s="2" t="n"/>
       <c r="AS789" s="2" t="n"/>
       <c r="AT789" s="2" t="n"/>
+      <c r="AU789" s="2" t="n"/>
     </row>
     <row r="790">
       <c r="A790" s="2" t="n"/>
@@ -38582,6 +39387,7 @@
       <c r="AR790" s="2" t="n"/>
       <c r="AS790" s="2" t="n"/>
       <c r="AT790" s="2" t="n"/>
+      <c r="AU790" s="2" t="n"/>
     </row>
     <row r="791">
       <c r="A791" s="2" t="n"/>
@@ -38630,6 +39436,7 @@
       <c r="AR791" s="2" t="n"/>
       <c r="AS791" s="2" t="n"/>
       <c r="AT791" s="2" t="n"/>
+      <c r="AU791" s="2" t="n"/>
     </row>
     <row r="792">
       <c r="A792" s="2" t="n"/>
@@ -38678,6 +39485,7 @@
       <c r="AR792" s="2" t="n"/>
       <c r="AS792" s="2" t="n"/>
       <c r="AT792" s="2" t="n"/>
+      <c r="AU792" s="2" t="n"/>
     </row>
     <row r="793">
       <c r="A793" s="2" t="n"/>
@@ -38726,6 +39534,7 @@
       <c r="AR793" s="2" t="n"/>
       <c r="AS793" s="2" t="n"/>
       <c r="AT793" s="2" t="n"/>
+      <c r="AU793" s="2" t="n"/>
     </row>
     <row r="794">
       <c r="A794" s="2" t="n"/>
@@ -38774,6 +39583,7 @@
       <c r="AR794" s="2" t="n"/>
       <c r="AS794" s="2" t="n"/>
       <c r="AT794" s="2" t="n"/>
+      <c r="AU794" s="2" t="n"/>
     </row>
     <row r="795">
       <c r="A795" s="2" t="n"/>
@@ -38822,6 +39632,7 @@
       <c r="AR795" s="2" t="n"/>
       <c r="AS795" s="2" t="n"/>
       <c r="AT795" s="2" t="n"/>
+      <c r="AU795" s="2" t="n"/>
     </row>
     <row r="796">
       <c r="A796" s="2" t="n"/>
@@ -38870,6 +39681,7 @@
       <c r="AR796" s="2" t="n"/>
       <c r="AS796" s="2" t="n"/>
       <c r="AT796" s="2" t="n"/>
+      <c r="AU796" s="2" t="n"/>
     </row>
     <row r="797">
       <c r="A797" s="2" t="n"/>
@@ -38918,6 +39730,7 @@
       <c r="AR797" s="2" t="n"/>
       <c r="AS797" s="2" t="n"/>
       <c r="AT797" s="2" t="n"/>
+      <c r="AU797" s="2" t="n"/>
     </row>
     <row r="798">
       <c r="A798" s="2" t="n"/>
@@ -38966,6 +39779,7 @@
       <c r="AR798" s="2" t="n"/>
       <c r="AS798" s="2" t="n"/>
       <c r="AT798" s="2" t="n"/>
+      <c r="AU798" s="2" t="n"/>
     </row>
     <row r="799">
       <c r="A799" s="2" t="n"/>
@@ -39014,6 +39828,7 @@
       <c r="AR799" s="2" t="n"/>
       <c r="AS799" s="2" t="n"/>
       <c r="AT799" s="2" t="n"/>
+      <c r="AU799" s="2" t="n"/>
     </row>
     <row r="800">
       <c r="A800" s="2" t="n"/>
@@ -39062,6 +39877,7 @@
       <c r="AR800" s="2" t="n"/>
       <c r="AS800" s="2" t="n"/>
       <c r="AT800" s="2" t="n"/>
+      <c r="AU800" s="2" t="n"/>
     </row>
     <row r="801">
       <c r="A801" s="2" t="n"/>
@@ -39110,6 +39926,7 @@
       <c r="AR801" s="2" t="n"/>
       <c r="AS801" s="2" t="n"/>
       <c r="AT801" s="2" t="n"/>
+      <c r="AU801" s="2" t="n"/>
     </row>
     <row r="802">
       <c r="A802" s="2" t="n"/>
@@ -39158,6 +39975,7 @@
       <c r="AR802" s="2" t="n"/>
       <c r="AS802" s="2" t="n"/>
       <c r="AT802" s="2" t="n"/>
+      <c r="AU802" s="2" t="n"/>
     </row>
     <row r="803">
       <c r="A803" s="2" t="n"/>
@@ -39206,6 +40024,7 @@
       <c r="AR803" s="2" t="n"/>
       <c r="AS803" s="2" t="n"/>
       <c r="AT803" s="2" t="n"/>
+      <c r="AU803" s="2" t="n"/>
     </row>
     <row r="804">
       <c r="A804" s="2" t="n"/>
@@ -39254,6 +40073,7 @@
       <c r="AR804" s="2" t="n"/>
       <c r="AS804" s="2" t="n"/>
       <c r="AT804" s="2" t="n"/>
+      <c r="AU804" s="2" t="n"/>
     </row>
     <row r="805">
       <c r="A805" s="2" t="n"/>
@@ -39302,6 +40122,7 @@
       <c r="AR805" s="2" t="n"/>
       <c r="AS805" s="2" t="n"/>
       <c r="AT805" s="2" t="n"/>
+      <c r="AU805" s="2" t="n"/>
     </row>
     <row r="806">
       <c r="A806" s="2" t="n"/>
@@ -39350,6 +40171,7 @@
       <c r="AR806" s="2" t="n"/>
       <c r="AS806" s="2" t="n"/>
       <c r="AT806" s="2" t="n"/>
+      <c r="AU806" s="2" t="n"/>
     </row>
     <row r="807">
       <c r="A807" s="2" t="n"/>
@@ -39398,6 +40220,7 @@
       <c r="AR807" s="2" t="n"/>
       <c r="AS807" s="2" t="n"/>
       <c r="AT807" s="2" t="n"/>
+      <c r="AU807" s="2" t="n"/>
     </row>
     <row r="808">
       <c r="A808" s="2" t="n"/>
@@ -39446,6 +40269,7 @@
       <c r="AR808" s="2" t="n"/>
       <c r="AS808" s="2" t="n"/>
       <c r="AT808" s="2" t="n"/>
+      <c r="AU808" s="2" t="n"/>
     </row>
     <row r="809">
       <c r="A809" s="2" t="n"/>
@@ -39494,6 +40318,7 @@
       <c r="AR809" s="2" t="n"/>
       <c r="AS809" s="2" t="n"/>
       <c r="AT809" s="2" t="n"/>
+      <c r="AU809" s="2" t="n"/>
     </row>
     <row r="810">
       <c r="A810" s="2" t="n"/>
@@ -39542,6 +40367,7 @@
       <c r="AR810" s="2" t="n"/>
       <c r="AS810" s="2" t="n"/>
       <c r="AT810" s="2" t="n"/>
+      <c r="AU810" s="2" t="n"/>
     </row>
     <row r="811">
       <c r="A811" s="2" t="n"/>
@@ -39590,6 +40416,7 @@
       <c r="AR811" s="2" t="n"/>
       <c r="AS811" s="2" t="n"/>
       <c r="AT811" s="2" t="n"/>
+      <c r="AU811" s="2" t="n"/>
     </row>
     <row r="812">
       <c r="A812" s="2" t="n"/>
@@ -39638,6 +40465,7 @@
       <c r="AR812" s="2" t="n"/>
       <c r="AS812" s="2" t="n"/>
       <c r="AT812" s="2" t="n"/>
+      <c r="AU812" s="2" t="n"/>
     </row>
     <row r="813">
       <c r="A813" s="2" t="n"/>
@@ -39686,6 +40514,7 @@
       <c r="AR813" s="2" t="n"/>
       <c r="AS813" s="2" t="n"/>
       <c r="AT813" s="2" t="n"/>
+      <c r="AU813" s="2" t="n"/>
     </row>
     <row r="814">
       <c r="A814" s="2" t="n"/>
@@ -39734,6 +40563,7 @@
       <c r="AR814" s="2" t="n"/>
       <c r="AS814" s="2" t="n"/>
       <c r="AT814" s="2" t="n"/>
+      <c r="AU814" s="2" t="n"/>
     </row>
     <row r="815">
       <c r="A815" s="2" t="n"/>
@@ -39782,6 +40612,7 @@
       <c r="AR815" s="2" t="n"/>
       <c r="AS815" s="2" t="n"/>
       <c r="AT815" s="2" t="n"/>
+      <c r="AU815" s="2" t="n"/>
     </row>
     <row r="816">
       <c r="A816" s="2" t="n"/>
@@ -39830,6 +40661,7 @@
       <c r="AR816" s="2" t="n"/>
       <c r="AS816" s="2" t="n"/>
       <c r="AT816" s="2" t="n"/>
+      <c r="AU816" s="2" t="n"/>
     </row>
     <row r="817">
       <c r="A817" s="2" t="n"/>
@@ -39878,6 +40710,7 @@
       <c r="AR817" s="2" t="n"/>
       <c r="AS817" s="2" t="n"/>
       <c r="AT817" s="2" t="n"/>
+      <c r="AU817" s="2" t="n"/>
     </row>
     <row r="818">
       <c r="A818" s="2" t="n"/>
@@ -39926,6 +40759,7 @@
       <c r="AR818" s="2" t="n"/>
       <c r="AS818" s="2" t="n"/>
       <c r="AT818" s="2" t="n"/>
+      <c r="AU818" s="2" t="n"/>
     </row>
     <row r="819">
       <c r="A819" s="2" t="n"/>
@@ -39974,6 +40808,7 @@
       <c r="AR819" s="2" t="n"/>
       <c r="AS819" s="2" t="n"/>
       <c r="AT819" s="2" t="n"/>
+      <c r="AU819" s="2" t="n"/>
     </row>
     <row r="820">
       <c r="A820" s="2" t="n"/>
@@ -40022,6 +40857,7 @@
       <c r="AR820" s="2" t="n"/>
       <c r="AS820" s="2" t="n"/>
       <c r="AT820" s="2" t="n"/>
+      <c r="AU820" s="2" t="n"/>
     </row>
     <row r="821">
       <c r="A821" s="2" t="n"/>
@@ -40070,6 +40906,7 @@
       <c r="AR821" s="2" t="n"/>
       <c r="AS821" s="2" t="n"/>
       <c r="AT821" s="2" t="n"/>
+      <c r="AU821" s="2" t="n"/>
     </row>
     <row r="822">
       <c r="A822" s="2" t="n"/>
@@ -40118,6 +40955,7 @@
       <c r="AR822" s="2" t="n"/>
       <c r="AS822" s="2" t="n"/>
       <c r="AT822" s="2" t="n"/>
+      <c r="AU822" s="2" t="n"/>
     </row>
     <row r="823">
       <c r="A823" s="2" t="n"/>
@@ -40166,6 +41004,7 @@
       <c r="AR823" s="2" t="n"/>
       <c r="AS823" s="2" t="n"/>
       <c r="AT823" s="2" t="n"/>
+      <c r="AU823" s="2" t="n"/>
     </row>
     <row r="824">
       <c r="A824" s="2" t="n"/>
@@ -40214,6 +41053,7 @@
       <c r="AR824" s="2" t="n"/>
       <c r="AS824" s="2" t="n"/>
       <c r="AT824" s="2" t="n"/>
+      <c r="AU824" s="2" t="n"/>
     </row>
     <row r="825">
       <c r="A825" s="2" t="n"/>
@@ -40262,6 +41102,7 @@
       <c r="AR825" s="2" t="n"/>
       <c r="AS825" s="2" t="n"/>
       <c r="AT825" s="2" t="n"/>
+      <c r="AU825" s="2" t="n"/>
     </row>
     <row r="826">
       <c r="A826" s="2" t="n"/>
@@ -40310,6 +41151,7 @@
       <c r="AR826" s="2" t="n"/>
       <c r="AS826" s="2" t="n"/>
       <c r="AT826" s="2" t="n"/>
+      <c r="AU826" s="2" t="n"/>
     </row>
     <row r="827">
       <c r="A827" s="2" t="n"/>
@@ -40358,6 +41200,7 @@
       <c r="AR827" s="2" t="n"/>
       <c r="AS827" s="2" t="n"/>
       <c r="AT827" s="2" t="n"/>
+      <c r="AU827" s="2" t="n"/>
     </row>
     <row r="828">
       <c r="A828" s="2" t="n"/>
@@ -40406,6 +41249,7 @@
       <c r="AR828" s="2" t="n"/>
       <c r="AS828" s="2" t="n"/>
       <c r="AT828" s="2" t="n"/>
+      <c r="AU828" s="2" t="n"/>
     </row>
     <row r="829">
       <c r="A829" s="2" t="n"/>
@@ -40454,6 +41298,7 @@
       <c r="AR829" s="2" t="n"/>
       <c r="AS829" s="2" t="n"/>
       <c r="AT829" s="2" t="n"/>
+      <c r="AU829" s="2" t="n"/>
     </row>
     <row r="830">
       <c r="A830" s="2" t="n"/>
@@ -40502,6 +41347,7 @@
       <c r="AR830" s="2" t="n"/>
       <c r="AS830" s="2" t="n"/>
       <c r="AT830" s="2" t="n"/>
+      <c r="AU830" s="2" t="n"/>
     </row>
     <row r="831">
       <c r="A831" s="2" t="n"/>
@@ -40550,6 +41396,7 @@
       <c r="AR831" s="2" t="n"/>
       <c r="AS831" s="2" t="n"/>
       <c r="AT831" s="2" t="n"/>
+      <c r="AU831" s="2" t="n"/>
     </row>
     <row r="832">
       <c r="A832" s="2" t="n"/>
@@ -40598,6 +41445,7 @@
       <c r="AR832" s="2" t="n"/>
       <c r="AS832" s="2" t="n"/>
       <c r="AT832" s="2" t="n"/>
+      <c r="AU832" s="2" t="n"/>
     </row>
     <row r="833">
       <c r="A833" s="2" t="n"/>
@@ -40646,6 +41494,7 @@
       <c r="AR833" s="2" t="n"/>
       <c r="AS833" s="2" t="n"/>
       <c r="AT833" s="2" t="n"/>
+      <c r="AU833" s="2" t="n"/>
     </row>
     <row r="834">
       <c r="A834" s="2" t="n"/>
@@ -40694,6 +41543,7 @@
       <c r="AR834" s="2" t="n"/>
       <c r="AS834" s="2" t="n"/>
       <c r="AT834" s="2" t="n"/>
+      <c r="AU834" s="2" t="n"/>
     </row>
     <row r="835">
       <c r="A835" s="2" t="n"/>
@@ -40742,6 +41592,7 @@
       <c r="AR835" s="2" t="n"/>
       <c r="AS835" s="2" t="n"/>
       <c r="AT835" s="2" t="n"/>
+      <c r="AU835" s="2" t="n"/>
     </row>
     <row r="836">
       <c r="A836" s="2" t="n"/>
@@ -40790,6 +41641,7 @@
       <c r="AR836" s="2" t="n"/>
       <c r="AS836" s="2" t="n"/>
       <c r="AT836" s="2" t="n"/>
+      <c r="AU836" s="2" t="n"/>
     </row>
     <row r="837">
       <c r="A837" s="2" t="n"/>
@@ -40838,6 +41690,7 @@
       <c r="AR837" s="2" t="n"/>
       <c r="AS837" s="2" t="n"/>
       <c r="AT837" s="2" t="n"/>
+      <c r="AU837" s="2" t="n"/>
     </row>
     <row r="838">
       <c r="A838" s="2" t="n"/>
@@ -40886,6 +41739,7 @@
       <c r="AR838" s="2" t="n"/>
       <c r="AS838" s="2" t="n"/>
       <c r="AT838" s="2" t="n"/>
+      <c r="AU838" s="2" t="n"/>
     </row>
     <row r="839">
       <c r="A839" s="2" t="n"/>
@@ -40934,6 +41788,7 @@
       <c r="AR839" s="2" t="n"/>
       <c r="AS839" s="2" t="n"/>
       <c r="AT839" s="2" t="n"/>
+      <c r="AU839" s="2" t="n"/>
     </row>
     <row r="840">
       <c r="A840" s="2" t="n"/>
@@ -40982,6 +41837,7 @@
       <c r="AR840" s="2" t="n"/>
       <c r="AS840" s="2" t="n"/>
       <c r="AT840" s="2" t="n"/>
+      <c r="AU840" s="2" t="n"/>
     </row>
     <row r="841">
       <c r="A841" s="2" t="n"/>
@@ -41030,6 +41886,7 @@
       <c r="AR841" s="2" t="n"/>
       <c r="AS841" s="2" t="n"/>
       <c r="AT841" s="2" t="n"/>
+      <c r="AU841" s="2" t="n"/>
     </row>
     <row r="842">
       <c r="A842" s="2" t="n"/>
@@ -41078,6 +41935,7 @@
       <c r="AR842" s="2" t="n"/>
       <c r="AS842" s="2" t="n"/>
       <c r="AT842" s="2" t="n"/>
+      <c r="AU842" s="2" t="n"/>
     </row>
     <row r="843">
       <c r="A843" s="2" t="n"/>
@@ -41126,6 +41984,7 @@
       <c r="AR843" s="2" t="n"/>
       <c r="AS843" s="2" t="n"/>
       <c r="AT843" s="2" t="n"/>
+      <c r="AU843" s="2" t="n"/>
     </row>
     <row r="844">
       <c r="A844" s="2" t="n"/>
@@ -41174,6 +42033,7 @@
       <c r="AR844" s="2" t="n"/>
       <c r="AS844" s="2" t="n"/>
       <c r="AT844" s="2" t="n"/>
+      <c r="AU844" s="2" t="n"/>
     </row>
     <row r="845">
       <c r="A845" s="2" t="n"/>
@@ -41222,6 +42082,7 @@
       <c r="AR845" s="2" t="n"/>
       <c r="AS845" s="2" t="n"/>
       <c r="AT845" s="2" t="n"/>
+      <c r="AU845" s="2" t="n"/>
     </row>
     <row r="846">
       <c r="A846" s="2" t="n"/>
@@ -41270,6 +42131,7 @@
       <c r="AR846" s="2" t="n"/>
       <c r="AS846" s="2" t="n"/>
       <c r="AT846" s="2" t="n"/>
+      <c r="AU846" s="2" t="n"/>
     </row>
     <row r="847">
       <c r="A847" s="2" t="n"/>
@@ -41318,6 +42180,7 @@
       <c r="AR847" s="2" t="n"/>
       <c r="AS847" s="2" t="n"/>
       <c r="AT847" s="2" t="n"/>
+      <c r="AU847" s="2" t="n"/>
     </row>
     <row r="848">
       <c r="A848" s="2" t="n"/>
@@ -41366,6 +42229,7 @@
       <c r="AR848" s="2" t="n"/>
       <c r="AS848" s="2" t="n"/>
       <c r="AT848" s="2" t="n"/>
+      <c r="AU848" s="2" t="n"/>
     </row>
     <row r="849">
       <c r="A849" s="2" t="n"/>
@@ -41414,6 +42278,7 @@
       <c r="AR849" s="2" t="n"/>
       <c r="AS849" s="2" t="n"/>
       <c r="AT849" s="2" t="n"/>
+      <c r="AU849" s="2" t="n"/>
     </row>
     <row r="850">
       <c r="A850" s="2" t="n"/>
@@ -41462,6 +42327,7 @@
       <c r="AR850" s="2" t="n"/>
       <c r="AS850" s="2" t="n"/>
       <c r="AT850" s="2" t="n"/>
+      <c r="AU850" s="2" t="n"/>
     </row>
     <row r="851">
       <c r="A851" s="2" t="n"/>
@@ -41510,6 +42376,7 @@
       <c r="AR851" s="2" t="n"/>
       <c r="AS851" s="2" t="n"/>
       <c r="AT851" s="2" t="n"/>
+      <c r="AU851" s="2" t="n"/>
     </row>
     <row r="852">
       <c r="A852" s="2" t="n"/>
@@ -41558,6 +42425,7 @@
       <c r="AR852" s="2" t="n"/>
       <c r="AS852" s="2" t="n"/>
       <c r="AT852" s="2" t="n"/>
+      <c r="AU852" s="2" t="n"/>
     </row>
     <row r="853">
       <c r="A853" s="2" t="n"/>
@@ -41606,6 +42474,7 @@
       <c r="AR853" s="2" t="n"/>
       <c r="AS853" s="2" t="n"/>
       <c r="AT853" s="2" t="n"/>
+      <c r="AU853" s="2" t="n"/>
     </row>
     <row r="854">
       <c r="A854" s="2" t="n"/>
@@ -41654,6 +42523,7 @@
       <c r="AR854" s="2" t="n"/>
       <c r="AS854" s="2" t="n"/>
       <c r="AT854" s="2" t="n"/>
+      <c r="AU854" s="2" t="n"/>
     </row>
     <row r="855">
       <c r="A855" s="2" t="n"/>
@@ -41702,6 +42572,7 @@
       <c r="AR855" s="2" t="n"/>
       <c r="AS855" s="2" t="n"/>
       <c r="AT855" s="2" t="n"/>
+      <c r="AU855" s="2" t="n"/>
     </row>
     <row r="856">
       <c r="A856" s="2" t="n"/>
@@ -41750,6 +42621,7 @@
       <c r="AR856" s="2" t="n"/>
       <c r="AS856" s="2" t="n"/>
       <c r="AT856" s="2" t="n"/>
+      <c r="AU856" s="2" t="n"/>
     </row>
     <row r="857">
       <c r="A857" s="2" t="n"/>
@@ -41798,6 +42670,7 @@
       <c r="AR857" s="2" t="n"/>
       <c r="AS857" s="2" t="n"/>
       <c r="AT857" s="2" t="n"/>
+      <c r="AU857" s="2" t="n"/>
     </row>
     <row r="858">
       <c r="A858" s="2" t="n"/>
@@ -41846,6 +42719,7 @@
       <c r="AR858" s="2" t="n"/>
       <c r="AS858" s="2" t="n"/>
       <c r="AT858" s="2" t="n"/>
+      <c r="AU858" s="2" t="n"/>
     </row>
     <row r="859">
       <c r="A859" s="2" t="n"/>
@@ -41894,6 +42768,7 @@
       <c r="AR859" s="2" t="n"/>
       <c r="AS859" s="2" t="n"/>
       <c r="AT859" s="2" t="n"/>
+      <c r="AU859" s="2" t="n"/>
     </row>
     <row r="860">
       <c r="A860" s="2" t="n"/>
@@ -41942,6 +42817,7 @@
       <c r="AR860" s="2" t="n"/>
       <c r="AS860" s="2" t="n"/>
       <c r="AT860" s="2" t="n"/>
+      <c r="AU860" s="2" t="n"/>
     </row>
     <row r="861">
       <c r="A861" s="2" t="n"/>
@@ -41990,6 +42866,7 @@
       <c r="AR861" s="2" t="n"/>
       <c r="AS861" s="2" t="n"/>
       <c r="AT861" s="2" t="n"/>
+      <c r="AU861" s="2" t="n"/>
     </row>
     <row r="862">
       <c r="A862" s="2" t="n"/>
@@ -42038,6 +42915,7 @@
       <c r="AR862" s="2" t="n"/>
       <c r="AS862" s="2" t="n"/>
       <c r="AT862" s="2" t="n"/>
+      <c r="AU862" s="2" t="n"/>
     </row>
     <row r="863">
       <c r="A863" s="2" t="n"/>
@@ -42086,6 +42964,7 @@
       <c r="AR863" s="2" t="n"/>
       <c r="AS863" s="2" t="n"/>
       <c r="AT863" s="2" t="n"/>
+      <c r="AU863" s="2" t="n"/>
     </row>
     <row r="864">
       <c r="A864" s="2" t="n"/>
@@ -42134,6 +43013,7 @@
       <c r="AR864" s="2" t="n"/>
       <c r="AS864" s="2" t="n"/>
       <c r="AT864" s="2" t="n"/>
+      <c r="AU864" s="2" t="n"/>
     </row>
     <row r="865">
       <c r="A865" s="2" t="n"/>
@@ -42182,6 +43062,7 @@
       <c r="AR865" s="2" t="n"/>
       <c r="AS865" s="2" t="n"/>
       <c r="AT865" s="2" t="n"/>
+      <c r="AU865" s="2" t="n"/>
     </row>
     <row r="866">
       <c r="A866" s="2" t="n"/>
@@ -42230,6 +43111,7 @@
       <c r="AR866" s="2" t="n"/>
       <c r="AS866" s="2" t="n"/>
       <c r="AT866" s="2" t="n"/>
+      <c r="AU866" s="2" t="n"/>
     </row>
     <row r="867">
       <c r="A867" s="2" t="n"/>
@@ -42278,6 +43160,7 @@
       <c r="AR867" s="2" t="n"/>
       <c r="AS867" s="2" t="n"/>
       <c r="AT867" s="2" t="n"/>
+      <c r="AU867" s="2" t="n"/>
     </row>
     <row r="868">
       <c r="A868" s="2" t="n"/>
@@ -42326,6 +43209,7 @@
       <c r="AR868" s="2" t="n"/>
       <c r="AS868" s="2" t="n"/>
       <c r="AT868" s="2" t="n"/>
+      <c r="AU868" s="2" t="n"/>
     </row>
     <row r="869">
       <c r="A869" s="2" t="n"/>
@@ -42374,6 +43258,7 @@
       <c r="AR869" s="2" t="n"/>
       <c r="AS869" s="2" t="n"/>
       <c r="AT869" s="2" t="n"/>
+      <c r="AU869" s="2" t="n"/>
     </row>
     <row r="870">
       <c r="A870" s="2" t="n"/>
@@ -42422,6 +43307,7 @@
       <c r="AR870" s="2" t="n"/>
       <c r="AS870" s="2" t="n"/>
       <c r="AT870" s="2" t="n"/>
+      <c r="AU870" s="2" t="n"/>
     </row>
     <row r="871">
       <c r="A871" s="2" t="n"/>
@@ -42470,6 +43356,7 @@
       <c r="AR871" s="2" t="n"/>
       <c r="AS871" s="2" t="n"/>
       <c r="AT871" s="2" t="n"/>
+      <c r="AU871" s="2" t="n"/>
     </row>
     <row r="872">
       <c r="A872" s="2" t="n"/>
@@ -42518,6 +43405,7 @@
       <c r="AR872" s="2" t="n"/>
       <c r="AS872" s="2" t="n"/>
       <c r="AT872" s="2" t="n"/>
+      <c r="AU872" s="2" t="n"/>
     </row>
     <row r="873">
       <c r="A873" s="2" t="n"/>
@@ -42566,6 +43454,7 @@
       <c r="AR873" s="2" t="n"/>
       <c r="AS873" s="2" t="n"/>
       <c r="AT873" s="2" t="n"/>
+      <c r="AU873" s="2" t="n"/>
     </row>
     <row r="874">
       <c r="A874" s="2" t="n"/>
@@ -42614,6 +43503,7 @@
       <c r="AR874" s="2" t="n"/>
       <c r="AS874" s="2" t="n"/>
       <c r="AT874" s="2" t="n"/>
+      <c r="AU874" s="2" t="n"/>
     </row>
     <row r="875">
       <c r="A875" s="2" t="n"/>
@@ -42662,6 +43552,7 @@
       <c r="AR875" s="2" t="n"/>
       <c r="AS875" s="2" t="n"/>
       <c r="AT875" s="2" t="n"/>
+      <c r="AU875" s="2" t="n"/>
     </row>
     <row r="876">
       <c r="A876" s="2" t="n"/>
@@ -42710,6 +43601,7 @@
       <c r="AR876" s="2" t="n"/>
       <c r="AS876" s="2" t="n"/>
       <c r="AT876" s="2" t="n"/>
+      <c r="AU876" s="2" t="n"/>
     </row>
     <row r="877">
       <c r="A877" s="2" t="n"/>
@@ -42758,6 +43650,7 @@
       <c r="AR877" s="2" t="n"/>
       <c r="AS877" s="2" t="n"/>
       <c r="AT877" s="2" t="n"/>
+      <c r="AU877" s="2" t="n"/>
     </row>
     <row r="878">
       <c r="A878" s="2" t="n"/>
@@ -42806,6 +43699,7 @@
       <c r="AR878" s="2" t="n"/>
       <c r="AS878" s="2" t="n"/>
       <c r="AT878" s="2" t="n"/>
+      <c r="AU878" s="2" t="n"/>
     </row>
     <row r="879">
       <c r="A879" s="2" t="n"/>
@@ -42854,6 +43748,7 @@
       <c r="AR879" s="2" t="n"/>
       <c r="AS879" s="2" t="n"/>
       <c r="AT879" s="2" t="n"/>
+      <c r="AU879" s="2" t="n"/>
     </row>
     <row r="880">
       <c r="A880" s="2" t="n"/>
@@ -42902,6 +43797,7 @@
       <c r="AR880" s="2" t="n"/>
       <c r="AS880" s="2" t="n"/>
       <c r="AT880" s="2" t="n"/>
+      <c r="AU880" s="2" t="n"/>
     </row>
     <row r="881">
       <c r="A881" s="2" t="n"/>
@@ -42950,6 +43846,7 @@
       <c r="AR881" s="2" t="n"/>
       <c r="AS881" s="2" t="n"/>
       <c r="AT881" s="2" t="n"/>
+      <c r="AU881" s="2" t="n"/>
     </row>
     <row r="882">
       <c r="A882" s="2" t="n"/>
@@ -42998,6 +43895,7 @@
       <c r="AR882" s="2" t="n"/>
       <c r="AS882" s="2" t="n"/>
       <c r="AT882" s="2" t="n"/>
+      <c r="AU882" s="2" t="n"/>
     </row>
     <row r="883">
       <c r="A883" s="2" t="n"/>
@@ -43046,6 +43944,7 @@
       <c r="AR883" s="2" t="n"/>
       <c r="AS883" s="2" t="n"/>
       <c r="AT883" s="2" t="n"/>
+      <c r="AU883" s="2" t="n"/>
     </row>
     <row r="884">
       <c r="A884" s="2" t="n"/>
@@ -43094,6 +43993,7 @@
       <c r="AR884" s="2" t="n"/>
       <c r="AS884" s="2" t="n"/>
       <c r="AT884" s="2" t="n"/>
+      <c r="AU884" s="2" t="n"/>
     </row>
     <row r="885">
       <c r="A885" s="2" t="n"/>
@@ -43142,6 +44042,7 @@
       <c r="AR885" s="2" t="n"/>
       <c r="AS885" s="2" t="n"/>
       <c r="AT885" s="2" t="n"/>
+      <c r="AU885" s="2" t="n"/>
     </row>
     <row r="886">
       <c r="A886" s="2" t="n"/>
@@ -43190,6 +44091,7 @@
       <c r="AR886" s="2" t="n"/>
       <c r="AS886" s="2" t="n"/>
       <c r="AT886" s="2" t="n"/>
+      <c r="AU886" s="2" t="n"/>
     </row>
     <row r="887">
       <c r="A887" s="2" t="n"/>
@@ -43238,6 +44140,7 @@
       <c r="AR887" s="2" t="n"/>
       <c r="AS887" s="2" t="n"/>
       <c r="AT887" s="2" t="n"/>
+      <c r="AU887" s="2" t="n"/>
     </row>
     <row r="888">
       <c r="A888" s="2" t="n"/>
@@ -43286,6 +44189,7 @@
       <c r="AR888" s="2" t="n"/>
       <c r="AS888" s="2" t="n"/>
       <c r="AT888" s="2" t="n"/>
+      <c r="AU888" s="2" t="n"/>
     </row>
     <row r="889">
       <c r="A889" s="2" t="n"/>
@@ -43334,6 +44238,7 @@
       <c r="AR889" s="2" t="n"/>
       <c r="AS889" s="2" t="n"/>
       <c r="AT889" s="2" t="n"/>
+      <c r="AU889" s="2" t="n"/>
     </row>
     <row r="890">
       <c r="A890" s="2" t="n"/>
@@ -43382,6 +44287,7 @@
       <c r="AR890" s="2" t="n"/>
       <c r="AS890" s="2" t="n"/>
       <c r="AT890" s="2" t="n"/>
+      <c r="AU890" s="2" t="n"/>
     </row>
     <row r="891">
       <c r="A891" s="2" t="n"/>
@@ -43430,6 +44336,7 @@
       <c r="AR891" s="2" t="n"/>
       <c r="AS891" s="2" t="n"/>
       <c r="AT891" s="2" t="n"/>
+      <c r="AU891" s="2" t="n"/>
     </row>
     <row r="892">
       <c r="A892" s="2" t="n"/>
@@ -43478,6 +44385,7 @@
       <c r="AR892" s="2" t="n"/>
       <c r="AS892" s="2" t="n"/>
       <c r="AT892" s="2" t="n"/>
+      <c r="AU892" s="2" t="n"/>
     </row>
     <row r="893">
       <c r="A893" s="2" t="n"/>
@@ -43526,6 +44434,7 @@
       <c r="AR893" s="2" t="n"/>
       <c r="AS893" s="2" t="n"/>
       <c r="AT893" s="2" t="n"/>
+      <c r="AU893" s="2" t="n"/>
     </row>
     <row r="894">
       <c r="A894" s="2" t="n"/>
@@ -43574,6 +44483,7 @@
       <c r="AR894" s="2" t="n"/>
       <c r="AS894" s="2" t="n"/>
       <c r="AT894" s="2" t="n"/>
+      <c r="AU894" s="2" t="n"/>
     </row>
     <row r="895">
       <c r="A895" s="2" t="n"/>
@@ -43622,6 +44532,7 @@
       <c r="AR895" s="2" t="n"/>
       <c r="AS895" s="2" t="n"/>
       <c r="AT895" s="2" t="n"/>
+      <c r="AU895" s="2" t="n"/>
     </row>
     <row r="896">
       <c r="A896" s="2" t="n"/>
@@ -43670,6 +44581,7 @@
       <c r="AR896" s="2" t="n"/>
       <c r="AS896" s="2" t="n"/>
       <c r="AT896" s="2" t="n"/>
+      <c r="AU896" s="2" t="n"/>
     </row>
     <row r="897">
       <c r="A897" s="2" t="n"/>
@@ -43718,6 +44630,7 @@
       <c r="AR897" s="2" t="n"/>
       <c r="AS897" s="2" t="n"/>
       <c r="AT897" s="2" t="n"/>
+      <c r="AU897" s="2" t="n"/>
     </row>
     <row r="898">
       <c r="A898" s="2" t="n"/>
@@ -43766,6 +44679,7 @@
       <c r="AR898" s="2" t="n"/>
       <c r="AS898" s="2" t="n"/>
       <c r="AT898" s="2" t="n"/>
+      <c r="AU898" s="2" t="n"/>
     </row>
     <row r="899">
       <c r="A899" s="2" t="n"/>
@@ -43814,6 +44728,7 @@
       <c r="AR899" s="2" t="n"/>
       <c r="AS899" s="2" t="n"/>
       <c r="AT899" s="2" t="n"/>
+      <c r="AU899" s="2" t="n"/>
     </row>
     <row r="900">
       <c r="A900" s="2" t="n"/>
@@ -43862,6 +44777,7 @@
       <c r="AR900" s="2" t="n"/>
       <c r="AS900" s="2" t="n"/>
       <c r="AT900" s="2" t="n"/>
+      <c r="AU900" s="2" t="n"/>
     </row>
     <row r="901">
       <c r="A901" s="2" t="n"/>
@@ -43910,6 +44826,7 @@
       <c r="AR901" s="2" t="n"/>
       <c r="AS901" s="2" t="n"/>
       <c r="AT901" s="2" t="n"/>
+      <c r="AU901" s="2" t="n"/>
     </row>
     <row r="902">
       <c r="A902" s="2" t="n"/>
@@ -43958,6 +44875,7 @@
       <c r="AR902" s="2" t="n"/>
       <c r="AS902" s="2" t="n"/>
       <c r="AT902" s="2" t="n"/>
+      <c r="AU902" s="2" t="n"/>
     </row>
     <row r="903">
       <c r="A903" s="2" t="n"/>
@@ -44006,6 +44924,7 @@
       <c r="AR903" s="2" t="n"/>
       <c r="AS903" s="2" t="n"/>
       <c r="AT903" s="2" t="n"/>
+      <c r="AU903" s="2" t="n"/>
     </row>
     <row r="904">
       <c r="A904" s="2" t="n"/>
@@ -44054,6 +44973,7 @@
       <c r="AR904" s="2" t="n"/>
       <c r="AS904" s="2" t="n"/>
       <c r="AT904" s="2" t="n"/>
+      <c r="AU904" s="2" t="n"/>
     </row>
     <row r="905">
       <c r="A905" s="2" t="n"/>
@@ -44102,6 +45022,7 @@
       <c r="AR905" s="2" t="n"/>
       <c r="AS905" s="2" t="n"/>
       <c r="AT905" s="2" t="n"/>
+      <c r="AU905" s="2" t="n"/>
     </row>
     <row r="906">
       <c r="A906" s="2" t="n"/>
@@ -44150,6 +45071,7 @@
       <c r="AR906" s="2" t="n"/>
       <c r="AS906" s="2" t="n"/>
       <c r="AT906" s="2" t="n"/>
+      <c r="AU906" s="2" t="n"/>
     </row>
     <row r="907">
       <c r="A907" s="2" t="n"/>
@@ -44198,6 +45120,7 @@
       <c r="AR907" s="2" t="n"/>
       <c r="AS907" s="2" t="n"/>
       <c r="AT907" s="2" t="n"/>
+      <c r="AU907" s="2" t="n"/>
     </row>
     <row r="908">
       <c r="A908" s="2" t="n"/>
@@ -44246,6 +45169,7 @@
       <c r="AR908" s="2" t="n"/>
       <c r="AS908" s="2" t="n"/>
       <c r="AT908" s="2" t="n"/>
+      <c r="AU908" s="2" t="n"/>
     </row>
     <row r="909">
       <c r="A909" s="2" t="n"/>
@@ -44294,6 +45218,7 @@
       <c r="AR909" s="2" t="n"/>
       <c r="AS909" s="2" t="n"/>
       <c r="AT909" s="2" t="n"/>
+      <c r="AU909" s="2" t="n"/>
     </row>
     <row r="910">
       <c r="A910" s="2" t="n"/>
@@ -44342,6 +45267,7 @@
       <c r="AR910" s="2" t="n"/>
       <c r="AS910" s="2" t="n"/>
       <c r="AT910" s="2" t="n"/>
+      <c r="AU910" s="2" t="n"/>
     </row>
     <row r="911">
       <c r="A911" s="2" t="n"/>
@@ -44390,6 +45316,7 @@
       <c r="AR911" s="2" t="n"/>
       <c r="AS911" s="2" t="n"/>
       <c r="AT911" s="2" t="n"/>
+      <c r="AU911" s="2" t="n"/>
     </row>
     <row r="912">
       <c r="A912" s="2" t="n"/>
@@ -44438,6 +45365,7 @@
       <c r="AR912" s="2" t="n"/>
       <c r="AS912" s="2" t="n"/>
       <c r="AT912" s="2" t="n"/>
+      <c r="AU912" s="2" t="n"/>
     </row>
     <row r="913">
       <c r="A913" s="2" t="n"/>
@@ -44486,6 +45414,7 @@
       <c r="AR913" s="2" t="n"/>
       <c r="AS913" s="2" t="n"/>
       <c r="AT913" s="2" t="n"/>
+      <c r="AU913" s="2" t="n"/>
     </row>
     <row r="914">
       <c r="A914" s="2" t="n"/>
@@ -44534,6 +45463,7 @@
       <c r="AR914" s="2" t="n"/>
       <c r="AS914" s="2" t="n"/>
       <c r="AT914" s="2" t="n"/>
+      <c r="AU914" s="2" t="n"/>
     </row>
     <row r="915">
       <c r="A915" s="2" t="n"/>
@@ -44582,6 +45512,7 @@
       <c r="AR915" s="2" t="n"/>
       <c r="AS915" s="2" t="n"/>
       <c r="AT915" s="2" t="n"/>
+      <c r="AU915" s="2" t="n"/>
     </row>
     <row r="916">
       <c r="A916" s="2" t="n"/>
@@ -44630,6 +45561,7 @@
       <c r="AR916" s="2" t="n"/>
       <c r="AS916" s="2" t="n"/>
       <c r="AT916" s="2" t="n"/>
+      <c r="AU916" s="2" t="n"/>
     </row>
     <row r="917">
       <c r="A917" s="2" t="n"/>
@@ -44678,6 +45610,7 @@
       <c r="AR917" s="2" t="n"/>
       <c r="AS917" s="2" t="n"/>
       <c r="AT917" s="2" t="n"/>
+      <c r="AU917" s="2" t="n"/>
     </row>
     <row r="918">
       <c r="A918" s="2" t="n"/>
@@ -44726,6 +45659,7 @@
       <c r="AR918" s="2" t="n"/>
       <c r="AS918" s="2" t="n"/>
       <c r="AT918" s="2" t="n"/>
+      <c r="AU918" s="2" t="n"/>
     </row>
     <row r="919">
       <c r="A919" s="2" t="n"/>
@@ -44774,6 +45708,7 @@
       <c r="AR919" s="2" t="n"/>
       <c r="AS919" s="2" t="n"/>
       <c r="AT919" s="2" t="n"/>
+      <c r="AU919" s="2" t="n"/>
     </row>
     <row r="920">
       <c r="A920" s="2" t="n"/>
@@ -44822,6 +45757,7 @@
       <c r="AR920" s="2" t="n"/>
       <c r="AS920" s="2" t="n"/>
       <c r="AT920" s="2" t="n"/>
+      <c r="AU920" s="2" t="n"/>
     </row>
     <row r="921">
       <c r="A921" s="2" t="n"/>
@@ -44870,6 +45806,7 @@
       <c r="AR921" s="2" t="n"/>
       <c r="AS921" s="2" t="n"/>
       <c r="AT921" s="2" t="n"/>
+      <c r="AU921" s="2" t="n"/>
     </row>
     <row r="922">
       <c r="A922" s="2" t="n"/>
@@ -44918,6 +45855,7 @@
       <c r="AR922" s="2" t="n"/>
       <c r="AS922" s="2" t="n"/>
       <c r="AT922" s="2" t="n"/>
+      <c r="AU922" s="2" t="n"/>
     </row>
     <row r="923">
       <c r="A923" s="2" t="n"/>
@@ -44966,6 +45904,7 @@
       <c r="AR923" s="2" t="n"/>
       <c r="AS923" s="2" t="n"/>
       <c r="AT923" s="2" t="n"/>
+      <c r="AU923" s="2" t="n"/>
     </row>
     <row r="924">
       <c r="A924" s="2" t="n"/>
@@ -45014,6 +45953,7 @@
       <c r="AR924" s="2" t="n"/>
       <c r="AS924" s="2" t="n"/>
       <c r="AT924" s="2" t="n"/>
+      <c r="AU924" s="2" t="n"/>
     </row>
     <row r="925">
       <c r="A925" s="2" t="n"/>
@@ -45062,6 +46002,7 @@
       <c r="AR925" s="2" t="n"/>
       <c r="AS925" s="2" t="n"/>
       <c r="AT925" s="2" t="n"/>
+      <c r="AU925" s="2" t="n"/>
     </row>
     <row r="926">
       <c r="A926" s="2" t="n"/>
@@ -45110,6 +46051,7 @@
       <c r="AR926" s="2" t="n"/>
       <c r="AS926" s="2" t="n"/>
       <c r="AT926" s="2" t="n"/>
+      <c r="AU926" s="2" t="n"/>
     </row>
     <row r="927">
       <c r="A927" s="2" t="n"/>
@@ -45158,6 +46100,7 @@
       <c r="AR927" s="2" t="n"/>
       <c r="AS927" s="2" t="n"/>
       <c r="AT927" s="2" t="n"/>
+      <c r="AU927" s="2" t="n"/>
     </row>
     <row r="928">
       <c r="A928" s="2" t="n"/>
@@ -45206,6 +46149,7 @@
       <c r="AR928" s="2" t="n"/>
       <c r="AS928" s="2" t="n"/>
       <c r="AT928" s="2" t="n"/>
+      <c r="AU928" s="2" t="n"/>
     </row>
     <row r="929">
       <c r="A929" s="2" t="n"/>
@@ -45254,6 +46198,7 @@
       <c r="AR929" s="2" t="n"/>
       <c r="AS929" s="2" t="n"/>
       <c r="AT929" s="2" t="n"/>
+      <c r="AU929" s="2" t="n"/>
     </row>
     <row r="930">
       <c r="A930" s="2" t="n"/>
@@ -45302,6 +46247,7 @@
       <c r="AR930" s="2" t="n"/>
       <c r="AS930" s="2" t="n"/>
       <c r="AT930" s="2" t="n"/>
+      <c r="AU930" s="2" t="n"/>
     </row>
     <row r="931">
       <c r="A931" s="2" t="n"/>
@@ -45350,6 +46296,7 @@
       <c r="AR931" s="2" t="n"/>
       <c r="AS931" s="2" t="n"/>
       <c r="AT931" s="2" t="n"/>
+      <c r="AU931" s="2" t="n"/>
     </row>
     <row r="932">
       <c r="A932" s="2" t="n"/>
@@ -45398,6 +46345,7 @@
       <c r="AR932" s="2" t="n"/>
       <c r="AS932" s="2" t="n"/>
       <c r="AT932" s="2" t="n"/>
+      <c r="AU932" s="2" t="n"/>
     </row>
     <row r="933">
       <c r="A933" s="2" t="n"/>
@@ -45446,6 +46394,7 @@
       <c r="AR933" s="2" t="n"/>
       <c r="AS933" s="2" t="n"/>
       <c r="AT933" s="2" t="n"/>
+      <c r="AU933" s="2" t="n"/>
     </row>
     <row r="934">
       <c r="A934" s="2" t="n"/>
@@ -45494,6 +46443,7 @@
       <c r="AR934" s="2" t="n"/>
       <c r="AS934" s="2" t="n"/>
       <c r="AT934" s="2" t="n"/>
+      <c r="AU934" s="2" t="n"/>
     </row>
     <row r="935">
       <c r="A935" s="2" t="n"/>
@@ -45542,6 +46492,7 @@
       <c r="AR935" s="2" t="n"/>
       <c r="AS935" s="2" t="n"/>
       <c r="AT935" s="2" t="n"/>
+      <c r="AU935" s="2" t="n"/>
     </row>
     <row r="936">
       <c r="A936" s="2" t="n"/>
@@ -45590,6 +46541,7 @@
       <c r="AR936" s="2" t="n"/>
       <c r="AS936" s="2" t="n"/>
       <c r="AT936" s="2" t="n"/>
+      <c r="AU936" s="2" t="n"/>
     </row>
     <row r="937">
       <c r="A937" s="2" t="n"/>
@@ -45638,6 +46590,7 @@
       <c r="AR937" s="2" t="n"/>
       <c r="AS937" s="2" t="n"/>
       <c r="AT937" s="2" t="n"/>
+      <c r="AU937" s="2" t="n"/>
     </row>
     <row r="938">
       <c r="A938" s="2" t="n"/>
@@ -45686,6 +46639,7 @@
       <c r="AR938" s="2" t="n"/>
       <c r="AS938" s="2" t="n"/>
       <c r="AT938" s="2" t="n"/>
+      <c r="AU938" s="2" t="n"/>
     </row>
     <row r="939">
       <c r="A939" s="2" t="n"/>
@@ -45734,6 +46688,7 @@
       <c r="AR939" s="2" t="n"/>
       <c r="AS939" s="2" t="n"/>
       <c r="AT939" s="2" t="n"/>
+      <c r="AU939" s="2" t="n"/>
     </row>
     <row r="940">
       <c r="A940" s="2" t="n"/>
@@ -45782,6 +46737,7 @@
       <c r="AR940" s="2" t="n"/>
       <c r="AS940" s="2" t="n"/>
       <c r="AT940" s="2" t="n"/>
+      <c r="AU940" s="2" t="n"/>
     </row>
     <row r="941">
       <c r="A941" s="2" t="n"/>
@@ -45830,6 +46786,7 @@
       <c r="AR941" s="2" t="n"/>
       <c r="AS941" s="2" t="n"/>
       <c r="AT941" s="2" t="n"/>
+      <c r="AU941" s="2" t="n"/>
     </row>
     <row r="942">
       <c r="A942" s="2" t="n"/>
@@ -45878,6 +46835,7 @@
       <c r="AR942" s="2" t="n"/>
       <c r="AS942" s="2" t="n"/>
       <c r="AT942" s="2" t="n"/>
+      <c r="AU942" s="2" t="n"/>
     </row>
     <row r="943">
       <c r="A943" s="2" t="n"/>
@@ -45926,6 +46884,7 @@
       <c r="AR943" s="2" t="n"/>
       <c r="AS943" s="2" t="n"/>
       <c r="AT943" s="2" t="n"/>
+      <c r="AU943" s="2" t="n"/>
     </row>
     <row r="944">
       <c r="A944" s="2" t="n"/>
@@ -45974,6 +46933,7 @@
       <c r="AR944" s="2" t="n"/>
       <c r="AS944" s="2" t="n"/>
       <c r="AT944" s="2" t="n"/>
+      <c r="AU944" s="2" t="n"/>
     </row>
     <row r="945">
       <c r="A945" s="2" t="n"/>
@@ -46022,6 +46982,7 @@
       <c r="AR945" s="2" t="n"/>
       <c r="AS945" s="2" t="n"/>
       <c r="AT945" s="2" t="n"/>
+      <c r="AU945" s="2" t="n"/>
     </row>
     <row r="946">
       <c r="A946" s="2" t="n"/>
@@ -46070,6 +47031,7 @@
       <c r="AR946" s="2" t="n"/>
       <c r="AS946" s="2" t="n"/>
       <c r="AT946" s="2" t="n"/>
+      <c r="AU946" s="2" t="n"/>
     </row>
     <row r="947">
       <c r="A947" s="2" t="n"/>
@@ -46118,6 +47080,7 @@
       <c r="AR947" s="2" t="n"/>
       <c r="AS947" s="2" t="n"/>
       <c r="AT947" s="2" t="n"/>
+      <c r="AU947" s="2" t="n"/>
     </row>
     <row r="948">
       <c r="A948" s="2" t="n"/>
@@ -46166,6 +47129,7 @@
       <c r="AR948" s="2" t="n"/>
       <c r="AS948" s="2" t="n"/>
       <c r="AT948" s="2" t="n"/>
+      <c r="AU948" s="2" t="n"/>
     </row>
     <row r="949">
       <c r="A949" s="2" t="n"/>
@@ -46214,6 +47178,7 @@
       <c r="AR949" s="2" t="n"/>
       <c r="AS949" s="2" t="n"/>
       <c r="AT949" s="2" t="n"/>
+      <c r="AU949" s="2" t="n"/>
     </row>
     <row r="950">
       <c r="A950" s="2" t="n"/>
@@ -46262,6 +47227,7 @@
       <c r="AR950" s="2" t="n"/>
       <c r="AS950" s="2" t="n"/>
       <c r="AT950" s="2" t="n"/>
+      <c r="AU950" s="2" t="n"/>
     </row>
     <row r="951">
       <c r="A951" s="2" t="n"/>
@@ -46310,6 +47276,7 @@
       <c r="AR951" s="2" t="n"/>
       <c r="AS951" s="2" t="n"/>
       <c r="AT951" s="2" t="n"/>
+      <c r="AU951" s="2" t="n"/>
     </row>
     <row r="952">
       <c r="A952" s="2" t="n"/>
@@ -46358,6 +47325,7 @@
       <c r="AR952" s="2" t="n"/>
       <c r="AS952" s="2" t="n"/>
       <c r="AT952" s="2" t="n"/>
+      <c r="AU952" s="2" t="n"/>
     </row>
     <row r="953">
       <c r="A953" s="2" t="n"/>
@@ -46406,6 +47374,7 @@
       <c r="AR953" s="2" t="n"/>
       <c r="AS953" s="2" t="n"/>
       <c r="AT953" s="2" t="n"/>
+      <c r="AU953" s="2" t="n"/>
     </row>
     <row r="954">
       <c r="A954" s="2" t="n"/>
@@ -46454,6 +47423,7 @@
       <c r="AR954" s="2" t="n"/>
       <c r="AS954" s="2" t="n"/>
       <c r="AT954" s="2" t="n"/>
+      <c r="AU954" s="2" t="n"/>
     </row>
     <row r="955">
       <c r="A955" s="2" t="n"/>
@@ -46502,6 +47472,7 @@
       <c r="AR955" s="2" t="n"/>
       <c r="AS955" s="2" t="n"/>
       <c r="AT955" s="2" t="n"/>
+      <c r="AU955" s="2" t="n"/>
     </row>
     <row r="956">
       <c r="A956" s="2" t="n"/>
@@ -46550,6 +47521,7 @@
       <c r="AR956" s="2" t="n"/>
       <c r="AS956" s="2" t="n"/>
       <c r="AT956" s="2" t="n"/>
+      <c r="AU956" s="2" t="n"/>
     </row>
     <row r="957">
       <c r="A957" s="2" t="n"/>
@@ -46598,6 +47570,7 @@
       <c r="AR957" s="2" t="n"/>
       <c r="AS957" s="2" t="n"/>
       <c r="AT957" s="2" t="n"/>
+      <c r="AU957" s="2" t="n"/>
     </row>
     <row r="958">
       <c r="A958" s="2" t="n"/>
@@ -46646,6 +47619,7 @@
       <c r="AR958" s="2" t="n"/>
       <c r="AS958" s="2" t="n"/>
       <c r="AT958" s="2" t="n"/>
+      <c r="AU958" s="2" t="n"/>
     </row>
     <row r="959">
       <c r="A959" s="2" t="n"/>
@@ -46694,6 +47668,7 @@
       <c r="AR959" s="2" t="n"/>
       <c r="AS959" s="2" t="n"/>
       <c r="AT959" s="2" t="n"/>
+      <c r="AU959" s="2" t="n"/>
     </row>
     <row r="960">
       <c r="A960" s="2" t="n"/>
@@ -46742,6 +47717,7 @@
       <c r="AR960" s="2" t="n"/>
       <c r="AS960" s="2" t="n"/>
       <c r="AT960" s="2" t="n"/>
+      <c r="AU960" s="2" t="n"/>
     </row>
     <row r="961">
       <c r="A961" s="2" t="n"/>
@@ -46790,6 +47766,7 @@
       <c r="AR961" s="2" t="n"/>
       <c r="AS961" s="2" t="n"/>
       <c r="AT961" s="2" t="n"/>
+      <c r="AU961" s="2" t="n"/>
     </row>
     <row r="962">
       <c r="A962" s="2" t="n"/>
@@ -46838,6 +47815,7 @@
       <c r="AR962" s="2" t="n"/>
       <c r="AS962" s="2" t="n"/>
       <c r="AT962" s="2" t="n"/>
+      <c r="AU962" s="2" t="n"/>
     </row>
     <row r="963">
       <c r="A963" s="2" t="n"/>
@@ -46886,6 +47864,7 @@
       <c r="AR963" s="2" t="n"/>
       <c r="AS963" s="2" t="n"/>
       <c r="AT963" s="2" t="n"/>
+      <c r="AU963" s="2" t="n"/>
     </row>
     <row r="964">
       <c r="A964" s="2" t="n"/>
@@ -46934,6 +47913,7 @@
       <c r="AR964" s="2" t="n"/>
       <c r="AS964" s="2" t="n"/>
       <c r="AT964" s="2" t="n"/>
+      <c r="AU964" s="2" t="n"/>
     </row>
     <row r="965">
       <c r="A965" s="2" t="n"/>
@@ -46982,6 +47962,7 @@
       <c r="AR965" s="2" t="n"/>
       <c r="AS965" s="2" t="n"/>
       <c r="AT965" s="2" t="n"/>
+      <c r="AU965" s="2" t="n"/>
     </row>
     <row r="966">
       <c r="A966" s="2" t="n"/>
@@ -47030,6 +48011,7 @@
       <c r="AR966" s="2" t="n"/>
       <c r="AS966" s="2" t="n"/>
       <c r="AT966" s="2" t="n"/>
+      <c r="AU966" s="2" t="n"/>
     </row>
     <row r="967">
       <c r="A967" s="2" t="n"/>
@@ -47078,6 +48060,7 @@
       <c r="AR967" s="2" t="n"/>
       <c r="AS967" s="2" t="n"/>
       <c r="AT967" s="2" t="n"/>
+      <c r="AU967" s="2" t="n"/>
     </row>
     <row r="968">
       <c r="A968" s="2" t="n"/>
@@ -47126,6 +48109,7 @@
       <c r="AR968" s="2" t="n"/>
       <c r="AS968" s="2" t="n"/>
       <c r="AT968" s="2" t="n"/>
+      <c r="AU968" s="2" t="n"/>
     </row>
     <row r="969">
       <c r="A969" s="2" t="n"/>
@@ -47174,6 +48158,7 @@
       <c r="AR969" s="2" t="n"/>
       <c r="AS969" s="2" t="n"/>
       <c r="AT969" s="2" t="n"/>
+      <c r="AU969" s="2" t="n"/>
     </row>
     <row r="970">
       <c r="A970" s="2" t="n"/>
@@ -47222,6 +48207,7 @@
       <c r="AR970" s="2" t="n"/>
       <c r="AS970" s="2" t="n"/>
       <c r="AT970" s="2" t="n"/>
+      <c r="AU970" s="2" t="n"/>
     </row>
     <row r="971">
       <c r="A971" s="2" t="n"/>
@@ -47270,6 +48256,7 @@
       <c r="AR971" s="2" t="n"/>
       <c r="AS971" s="2" t="n"/>
       <c r="AT971" s="2" t="n"/>
+      <c r="AU971" s="2" t="n"/>
     </row>
     <row r="972">
       <c r="A972" s="2" t="n"/>
@@ -47318,6 +48305,7 @@
       <c r="AR972" s="2" t="n"/>
       <c r="AS972" s="2" t="n"/>
       <c r="AT972" s="2" t="n"/>
+      <c r="AU972" s="2" t="n"/>
     </row>
     <row r="973">
       <c r="A973" s="2" t="n"/>
@@ -47366,6 +48354,7 @@
       <c r="AR973" s="2" t="n"/>
       <c r="AS973" s="2" t="n"/>
       <c r="AT973" s="2" t="n"/>
+      <c r="AU973" s="2" t="n"/>
     </row>
     <row r="974">
       <c r="A974" s="2" t="n"/>
@@ -47414,6 +48403,7 @@
       <c r="AR974" s="2" t="n"/>
       <c r="AS974" s="2" t="n"/>
       <c r="AT974" s="2" t="n"/>
+      <c r="AU974" s="2" t="n"/>
     </row>
     <row r="975">
       <c r="A975" s="2" t="n"/>
@@ -47462,6 +48452,7 @@
       <c r="AR975" s="2" t="n"/>
       <c r="AS975" s="2" t="n"/>
       <c r="AT975" s="2" t="n"/>
+      <c r="AU975" s="2" t="n"/>
     </row>
     <row r="976">
       <c r="A976" s="2" t="n"/>
@@ -47510,6 +48501,7 @@
       <c r="AR976" s="2" t="n"/>
       <c r="AS976" s="2" t="n"/>
       <c r="AT976" s="2" t="n"/>
+      <c r="AU976" s="2" t="n"/>
     </row>
     <row r="977">
       <c r="A977" s="2" t="n"/>
@@ -47558,6 +48550,7 @@
       <c r="AR977" s="2" t="n"/>
       <c r="AS977" s="2" t="n"/>
       <c r="AT977" s="2" t="n"/>
+      <c r="AU977" s="2" t="n"/>
     </row>
     <row r="978">
       <c r="A978" s="2" t="n"/>
@@ -47606,6 +48599,7 @@
       <c r="AR978" s="2" t="n"/>
       <c r="AS978" s="2" t="n"/>
       <c r="AT978" s="2" t="n"/>
+      <c r="AU978" s="2" t="n"/>
     </row>
     <row r="979">
       <c r="A979" s="2" t="n"/>
@@ -47654,6 +48648,7 @@
       <c r="AR979" s="2" t="n"/>
       <c r="AS979" s="2" t="n"/>
       <c r="AT979" s="2" t="n"/>
+      <c r="AU979" s="2" t="n"/>
     </row>
     <row r="980">
       <c r="A980" s="2" t="n"/>
@@ -47702,6 +48697,7 @@
       <c r="AR980" s="2" t="n"/>
       <c r="AS980" s="2" t="n"/>
       <c r="AT980" s="2" t="n"/>
+      <c r="AU980" s="2" t="n"/>
     </row>
     <row r="981">
       <c r="A981" s="2" t="n"/>
@@ -47750,6 +48746,7 @@
       <c r="AR981" s="2" t="n"/>
       <c r="AS981" s="2" t="n"/>
       <c r="AT981" s="2" t="n"/>
+      <c r="AU981" s="2" t="n"/>
     </row>
     <row r="982">
       <c r="A982" s="2" t="n"/>
@@ -47798,6 +48795,7 @@
       <c r="AR982" s="2" t="n"/>
       <c r="AS982" s="2" t="n"/>
       <c r="AT982" s="2" t="n"/>
+      <c r="AU982" s="2" t="n"/>
     </row>
     <row r="983">
       <c r="A983" s="2" t="n"/>
@@ -47846,6 +48844,7 @@
       <c r="AR983" s="2" t="n"/>
       <c r="AS983" s="2" t="n"/>
       <c r="AT983" s="2" t="n"/>
+      <c r="AU983" s="2" t="n"/>
     </row>
     <row r="984">
       <c r="A984" s="2" t="n"/>
@@ -47894,6 +48893,7 @@
       <c r="AR984" s="2" t="n"/>
       <c r="AS984" s="2" t="n"/>
       <c r="AT984" s="2" t="n"/>
+      <c r="AU984" s="2" t="n"/>
     </row>
     <row r="985">
       <c r="A985" s="2" t="n"/>
@@ -47942,6 +48942,7 @@
       <c r="AR985" s="2" t="n"/>
       <c r="AS985" s="2" t="n"/>
       <c r="AT985" s="2" t="n"/>
+      <c r="AU985" s="2" t="n"/>
     </row>
     <row r="986">
       <c r="A986" s="2" t="n"/>
@@ -47990,6 +48991,7 @@
       <c r="AR986" s="2" t="n"/>
       <c r="AS986" s="2" t="n"/>
       <c r="AT986" s="2" t="n"/>
+      <c r="AU986" s="2" t="n"/>
     </row>
     <row r="987">
       <c r="A987" s="2" t="n"/>
@@ -48038,6 +49040,7 @@
       <c r="AR987" s="2" t="n"/>
       <c r="AS987" s="2" t="n"/>
       <c r="AT987" s="2" t="n"/>
+      <c r="AU987" s="2" t="n"/>
     </row>
     <row r="988">
       <c r="A988" s="2" t="n"/>
@@ -48086,6 +49089,7 @@
       <c r="AR988" s="2" t="n"/>
       <c r="AS988" s="2" t="n"/>
       <c r="AT988" s="2" t="n"/>
+      <c r="AU988" s="2" t="n"/>
     </row>
     <row r="989">
       <c r="A989" s="2" t="n"/>
@@ -48134,6 +49138,7 @@
       <c r="AR989" s="2" t="n"/>
       <c r="AS989" s="2" t="n"/>
       <c r="AT989" s="2" t="n"/>
+      <c r="AU989" s="2" t="n"/>
     </row>
     <row r="990">
       <c r="A990" s="2" t="n"/>
@@ -48182,6 +49187,7 @@
       <c r="AR990" s="2" t="n"/>
       <c r="AS990" s="2" t="n"/>
       <c r="AT990" s="2" t="n"/>
+      <c r="AU990" s="2" t="n"/>
     </row>
     <row r="991">
       <c r="A991" s="2" t="n"/>
@@ -48230,6 +49236,7 @@
       <c r="AR991" s="2" t="n"/>
       <c r="AS991" s="2" t="n"/>
       <c r="AT991" s="2" t="n"/>
+      <c r="AU991" s="2" t="n"/>
     </row>
     <row r="992">
       <c r="A992" s="2" t="n"/>
@@ -48278,6 +49285,7 @@
       <c r="AR992" s="2" t="n"/>
       <c r="AS992" s="2" t="n"/>
       <c r="AT992" s="2" t="n"/>
+      <c r="AU992" s="2" t="n"/>
     </row>
     <row r="993">
       <c r="A993" s="2" t="n"/>
@@ -48326,6 +49334,7 @@
       <c r="AR993" s="2" t="n"/>
       <c r="AS993" s="2" t="n"/>
       <c r="AT993" s="2" t="n"/>
+      <c r="AU993" s="2" t="n"/>
     </row>
     <row r="994">
       <c r="A994" s="2" t="n"/>
@@ -48374,6 +49383,7 @@
       <c r="AR994" s="2" t="n"/>
       <c r="AS994" s="2" t="n"/>
       <c r="AT994" s="2" t="n"/>
+      <c r="AU994" s="2" t="n"/>
     </row>
     <row r="995">
       <c r="A995" s="2" t="n"/>
@@ -48422,6 +49432,7 @@
       <c r="AR995" s="2" t="n"/>
       <c r="AS995" s="2" t="n"/>
       <c r="AT995" s="2" t="n"/>
+      <c r="AU995" s="2" t="n"/>
     </row>
     <row r="996">
       <c r="A996" s="2" t="n"/>
@@ -48470,6 +49481,7 @@
       <c r="AR996" s="2" t="n"/>
       <c r="AS996" s="2" t="n"/>
       <c r="AT996" s="2" t="n"/>
+      <c r="AU996" s="2" t="n"/>
     </row>
     <row r="997">
       <c r="A997" s="2" t="n"/>
@@ -48518,6 +49530,7 @@
       <c r="AR997" s="2" t="n"/>
       <c r="AS997" s="2" t="n"/>
       <c r="AT997" s="2" t="n"/>
+      <c r="AU997" s="2" t="n"/>
     </row>
     <row r="998">
       <c r="A998" s="2" t="n"/>
@@ -48566,6 +49579,7 @@
       <c r="AR998" s="2" t="n"/>
       <c r="AS998" s="2" t="n"/>
       <c r="AT998" s="2" t="n"/>
+      <c r="AU998" s="2" t="n"/>
     </row>
     <row r="999">
       <c r="A999" s="2" t="n"/>
@@ -48614,6 +49628,7 @@
       <c r="AR999" s="2" t="n"/>
       <c r="AS999" s="2" t="n"/>
       <c r="AT999" s="2" t="n"/>
+      <c r="AU999" s="2" t="n"/>
     </row>
     <row r="1000">
       <c r="A1000" s="2" t="n"/>
@@ -48662,20 +49677,42 @@
       <c r="AR1000" s="2" t="n"/>
       <c r="AS1000" s="2" t="n"/>
       <c r="AT1000" s="2" t="n"/>
+      <c r="AU1000" s="2" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="11">
+    <dataValidation sqref="AG2:AG1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción no válida" error="Por favor selecciona una opción válida para Tipo de Nomina (Semanal/Por hora/Cuadrado)" type="list">
       <formula1>"Semanal,Por hora,Cuadrado"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"M,F,X"</formula1>
+    <dataValidation sqref="R2:R1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción no válida" error="Por favor selecciona una opción válida para Sexo (M/F)" type="list">
+      <formula1>"M,F"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG2:AG1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AD2:AD1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción no válida" error="Por favor selecciona una opción válida para Usa Lentes (Si/No)" type="list">
       <formula1>"Si,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="AR2:AR1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AS2:AS1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción no válida" error="Por favor selecciona una opción válida para Tipo Pago" type="list">
       <formula1>"EFECTIVO,TRANSFERENCIA"</formula1>
+    </dataValidation>
+    <dataValidation sqref="S2:S1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción no válida" error="Por favor selecciona una opción válida para Estado Civil" type="list">
+      <formula1>"Soltero(a),Casado(a),Union Libre,Divorciado(a),Viudo(a)"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción no válida" error="Por favor selecciona una opción válida para Tipo de Movimiento" type="list">
+      <formula1>"Alta,Reingreso,Modificacion de salario"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción no válida" error="Por favor selecciona una opción válida para Tipo de Contrato" type="list">
+      <formula1>"Indefinido,Temporal,Por obra determinada,Periodo de prueba"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción no válida" error="Por favor selecciona una opción válida para Tipo de Jornada" type="list">
+      <formula1>"Diurna,Nocturna,Mixta"</formula1>
+    </dataValidation>
+    <dataValidation sqref="X2:X1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción no válida" error="Por favor selecciona una opción válida para Tipo de Sangre" type="list">
+      <formula1>"O+,O-,A+,A-,B+,B-,AB+,AB-"</formula1>
+    </dataValidation>
+    <dataValidation sqref="AE2:AE1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción no válida" error="Por favor selecciona una opción válida para Licencia de Conducir (Tipo)" type="list">
+      <formula1>"No tiene,Tipo A,Tipo B,Tipo C,Tipo D,Tipo E"</formula1>
+    </dataValidation>
+    <dataValidation sqref="T2:T1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción no válida" error="Por favor selecciona una opción válida para Nacionalidad" type="list">
+      <formula1>"Mexicana,Otra"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/static/downloads/plantilla_empleados.xlsx
+++ b/static/downloads/plantilla_empleados.xlsx
@@ -447,37 +447,37 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="21.6" customWidth="1" min="7" max="7"/>
-    <col width="20.4" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="33.6" customWidth="1" min="10" max="10"/>
-    <col width="32.4" customWidth="1" min="11" max="11"/>
-    <col width="38.4" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="37.2" customWidth="1" min="16" max="16"/>
+    <col width="52.8" customWidth="1" min="6" max="6"/>
+    <col width="39.6" customWidth="1" min="7" max="7"/>
+    <col width="21.6" customWidth="1" min="8" max="8"/>
+    <col width="38.4" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="21.6" customWidth="1" min="11" max="11"/>
+    <col width="20.4" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="33.6" customWidth="1" min="14" max="14"/>
+    <col width="32.4" customWidth="1" min="15" max="15"/>
+    <col width="38.4" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="37.2" customWidth="1" min="20" max="20"/>
     <col width="20" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="20" customWidth="1" min="23" max="23"/>
     <col width="20" customWidth="1" min="24" max="24"/>
     <col width="20" customWidth="1" min="25" max="25"/>
-    <col width="27.6" customWidth="1" min="26" max="26"/>
-    <col width="28.8" customWidth="1" min="27" max="27"/>
-    <col width="30" customWidth="1" min="28" max="28"/>
-    <col width="33.6" customWidth="1" min="29" max="29"/>
-    <col width="24" customWidth="1" min="30" max="30"/>
-    <col width="34.8" customWidth="1" min="31" max="31"/>
-    <col width="20" customWidth="1" min="32" max="32"/>
-    <col width="52.8" customWidth="1" min="33" max="33"/>
-    <col width="39.6" customWidth="1" min="34" max="34"/>
-    <col width="21.6" customWidth="1" min="35" max="35"/>
-    <col width="38.4" customWidth="1" min="36" max="36"/>
+    <col width="20" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="27" max="27"/>
+    <col width="20" customWidth="1" min="28" max="28"/>
+    <col width="20" customWidth="1" min="29" max="29"/>
+    <col width="27.6" customWidth="1" min="30" max="30"/>
+    <col width="28.8" customWidth="1" min="31" max="31"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="33.6" customWidth="1" min="33" max="33"/>
+    <col width="24" customWidth="1" min="34" max="34"/>
+    <col width="34.8" customWidth="1" min="35" max="35"/>
+    <col width="20" customWidth="1" min="36" max="36"/>
     <col width="20" customWidth="1" min="37" max="37"/>
     <col width="20" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
@@ -519,157 +519,157 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Tipo de Movimiento</t>
+          <t>Tipo de Nomina (Semanal/Por hora/Cuadrado)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Tipo de Contrato</t>
+          <t>Salario Real Pactado por Semana</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Tipo de Jornada</t>
+          <t>Sueldo Base (SB)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Descripcion de Servicio</t>
+          <t>Salario Diario Integrado (SDI)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Fecha Ingreso (YYYY-MM-DD)</t>
+          <t>Tipo de Movimiento</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Fecha Inicio (YYYY-MM-DD)</t>
+          <t>Tipo de Contrato</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Termino de Prueba (YYYY-MM-DD)</t>
+          <t>Tipo de Jornada</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CURP</t>
+          <t>Descripcion de Servicio</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>RFC</t>
+          <t>Fecha Ingreso (YYYY-MM-DD)</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>NSS</t>
+          <t>Fecha Inicio (YYYY-MM-DD)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Fecha Nacimiento (YYYY-MM-DD)</t>
+          <t>Termino de Prueba (YYYY-MM-DD)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Edad</t>
+          <t>CURP</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Sexo (M/F)</t>
+          <t>RFC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Estado Civil</t>
+          <t>NSS</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Nacionalidad</t>
+          <t>Fecha Nacimiento (YYYY-MM-DD)</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Domicilio</t>
+          <t>Edad</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Correo</t>
+          <t>Sexo (M/F)</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Celular</t>
+          <t>Estado Civil</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Tipo de Sangre</t>
+          <t>Nacionalidad</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Alergias</t>
+          <t>Domicilio</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Enfermedades Cronicas</t>
+          <t>Correo</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Contacto de Emergencia</t>
+          <t>Celular</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Parentesco del Contacto</t>
+          <t>Tipo de Sangre</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Numero Contacto Emergencia</t>
+          <t>Alergias</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Usa Lentes (Si/No)</t>
+          <t>Enfermedades Cronicas</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Licencia de Conducir (Tipo)</t>
+          <t>Contacto de Emergencia</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Estatura</t>
+          <t>Parentesco del Contacto</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Tipo de Nomina (Semanal/Por hora/Cuadrado)</t>
+          <t>Numero Contacto Emergencia</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Salario Real Pactado por Semana</t>
+          <t>Usa Lentes (Si/No)</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Sueldo Base (SB)</t>
+          <t>Licencia de Conducir (Tipo)</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>Salario Diario Integrado (SDI)</t>
+          <t>Estatura</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
@@ -49680,39 +49680,18 @@
       <c r="AU1000" s="2" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="11">
-    <dataValidation sqref="AG2:AG1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción no válida" error="Por favor selecciona una opción válida para Tipo de Nomina (Semanal/Por hora/Cuadrado)" type="list">
+  <dataValidations count="4">
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="warning">
       <formula1>"Semanal,Por hora,Cuadrado"</formula1>
     </dataValidation>
-    <dataValidation sqref="R2:R1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción no válida" error="Por favor selecciona una opción válida para Sexo (M/F)" type="list">
+    <dataValidation sqref="V2:V1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="warning">
       <formula1>"M,F"</formula1>
     </dataValidation>
-    <dataValidation sqref="AD2:AD1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción no válida" error="Por favor selecciona una opción válida para Usa Lentes (Si/No)" type="list">
+    <dataValidation sqref="AH2:AH1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="warning">
       <formula1>"Si,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="AS2:AS1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción no válida" error="Por favor selecciona una opción válida para Tipo Pago" type="list">
+    <dataValidation sqref="AS2:AS1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="warning">
       <formula1>"EFECTIVO,TRANSFERENCIA"</formula1>
-    </dataValidation>
-    <dataValidation sqref="S2:S1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción no válida" error="Por favor selecciona una opción válida para Estado Civil" type="list">
-      <formula1>"Soltero(a),Casado(a),Union Libre,Divorciado(a),Viudo(a)"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción no válida" error="Por favor selecciona una opción válida para Tipo de Movimiento" type="list">
-      <formula1>"Alta,Reingreso,Modificacion de salario"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción no válida" error="Por favor selecciona una opción válida para Tipo de Contrato" type="list">
-      <formula1>"Indefinido,Temporal,Por obra determinada,Periodo de prueba"</formula1>
-    </dataValidation>
-    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción no válida" error="Por favor selecciona una opción válida para Tipo de Jornada" type="list">
-      <formula1>"Diurna,Nocturna,Mixta"</formula1>
-    </dataValidation>
-    <dataValidation sqref="X2:X1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción no válida" error="Por favor selecciona una opción válida para Tipo de Sangre" type="list">
-      <formula1>"O+,O-,A+,A-,B+,B-,AB+,AB-"</formula1>
-    </dataValidation>
-    <dataValidation sqref="AE2:AE1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción no válida" error="Por favor selecciona una opción válida para Licencia de Conducir (Tipo)" type="list">
-      <formula1>"No tiene,Tipo A,Tipo B,Tipo C,Tipo D,Tipo E"</formula1>
-    </dataValidation>
-    <dataValidation sqref="T2:T1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción no válida" error="Por favor selecciona una opción válida para Nacionalidad" type="list">
-      <formula1>"Mexicana,Otra"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/static/downloads/plantilla_empleados.xlsx
+++ b/static/downloads/plantilla_empleados.xlsx
@@ -451,39 +451,39 @@
     <col width="39.6" customWidth="1" min="7" max="7"/>
     <col width="21.6" customWidth="1" min="8" max="8"/>
     <col width="38.4" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="21.6" customWidth="1" min="11" max="11"/>
-    <col width="20.4" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="33.6" customWidth="1" min="14" max="14"/>
-    <col width="32.4" customWidth="1" min="15" max="15"/>
-    <col width="38.4" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="37.2" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="21.6" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="21.6" customWidth="1" min="17" max="17"/>
+    <col width="20.4" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
+    <col width="33.6" customWidth="1" min="20" max="20"/>
+    <col width="32.4" customWidth="1" min="21" max="21"/>
+    <col width="38.4" customWidth="1" min="22" max="22"/>
     <col width="20" customWidth="1" min="23" max="23"/>
     <col width="20" customWidth="1" min="24" max="24"/>
     <col width="20" customWidth="1" min="25" max="25"/>
-    <col width="20" customWidth="1" min="26" max="26"/>
+    <col width="37.2" customWidth="1" min="26" max="26"/>
     <col width="20" customWidth="1" min="27" max="27"/>
     <col width="20" customWidth="1" min="28" max="28"/>
     <col width="20" customWidth="1" min="29" max="29"/>
-    <col width="27.6" customWidth="1" min="30" max="30"/>
-    <col width="28.8" customWidth="1" min="31" max="31"/>
-    <col width="30" customWidth="1" min="32" max="32"/>
-    <col width="33.6" customWidth="1" min="33" max="33"/>
-    <col width="24" customWidth="1" min="34" max="34"/>
-    <col width="34.8" customWidth="1" min="35" max="35"/>
-    <col width="20" customWidth="1" min="36" max="36"/>
-    <col width="20" customWidth="1" min="37" max="37"/>
-    <col width="20" customWidth="1" min="38" max="38"/>
-    <col width="20" customWidth="1" min="39" max="39"/>
-    <col width="20" customWidth="1" min="40" max="40"/>
-    <col width="20" customWidth="1" min="41" max="41"/>
-    <col width="21.6" customWidth="1" min="42" max="42"/>
+    <col width="20" customWidth="1" min="30" max="30"/>
+    <col width="20" customWidth="1" min="31" max="31"/>
+    <col width="20" customWidth="1" min="32" max="32"/>
+    <col width="20" customWidth="1" min="33" max="33"/>
+    <col width="20" customWidth="1" min="34" max="34"/>
+    <col width="20" customWidth="1" min="35" max="35"/>
+    <col width="27.6" customWidth="1" min="36" max="36"/>
+    <col width="28.8" customWidth="1" min="37" max="37"/>
+    <col width="30" customWidth="1" min="38" max="38"/>
+    <col width="33.6" customWidth="1" min="39" max="39"/>
+    <col width="24" customWidth="1" min="40" max="40"/>
+    <col width="34.8" customWidth="1" min="41" max="41"/>
+    <col width="20" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
     <col width="20" customWidth="1" min="45" max="45"/>
@@ -539,167 +539,167 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Tipo de Movimiento</t>
+          <t>Letra</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Tipo de Contrato</t>
+          <t>Horas Extra</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Tipo de Jornada</t>
+          <t>Infonavit</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Descripcion de Servicio</t>
+          <t>Caja de Ahorro</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Fecha Ingreso (YYYY-MM-DD)</t>
+          <t>Viaticos</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Fecha Inicio (YYYY-MM-DD)</t>
+          <t>Pago Dia Festivo</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Termino de Prueba (YYYY-MM-DD)</t>
+          <t>Tipo de Movimiento</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CURP</t>
+          <t>Tipo de Contrato</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>RFC</t>
+          <t>Tipo de Jornada</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>NSS</t>
+          <t>Descripcion de Servicio</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Fecha Nacimiento (YYYY-MM-DD)</t>
+          <t>Fecha Ingreso (YYYY-MM-DD)</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Edad</t>
+          <t>Fecha Inicio (YYYY-MM-DD)</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Sexo (M/F)</t>
+          <t>Termino de Prueba (YYYY-MM-DD)</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Estado Civil</t>
+          <t>CURP</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Nacionalidad</t>
+          <t>RFC</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Domicilio</t>
+          <t>NSS</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Correo</t>
+          <t>Fecha Nacimiento (YYYY-MM-DD)</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Celular</t>
+          <t>Edad</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Tipo de Sangre</t>
+          <t>Sexo (M/F)</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Alergias</t>
+          <t>Estado Civil</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Enfermedades Cronicas</t>
+          <t>Nacionalidad</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Contacto de Emergencia</t>
+          <t>Domicilio</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Parentesco del Contacto</t>
+          <t>Correo</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Numero Contacto Emergencia</t>
+          <t>Celular</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Usa Lentes (Si/No)</t>
+          <t>Tipo de Sangre</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Licencia de Conducir (Tipo)</t>
+          <t>Alergias</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>Estatura</t>
+          <t>Enfermedades Cronicas</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>Letra</t>
+          <t>Contacto de Emergencia</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>Horas Extra</t>
+          <t>Parentesco del Contacto</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>Infonavit</t>
+          <t>Numero Contacto Emergencia</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>Caja de Ahorro</t>
+          <t>Usa Lentes (Si/No)</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>Viaticos</t>
+          <t>Licencia de Conducir (Tipo)</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>Pago Dia Festivo</t>
+          <t>Estatura</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
@@ -49684,10 +49684,10 @@
     <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="warning">
       <formula1>"Semanal,Por hora,Cuadrado"</formula1>
     </dataValidation>
-    <dataValidation sqref="V2:V1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="warning">
+    <dataValidation sqref="AB2:AB1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="warning">
       <formula1>"M,F"</formula1>
     </dataValidation>
-    <dataValidation sqref="AH2:AH1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="warning">
+    <dataValidation sqref="AN2:AN1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="warning">
       <formula1>"Si,No"</formula1>
     </dataValidation>
     <dataValidation sqref="AS2:AS1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="warning">

--- a/static/downloads/plantilla_empleados.xlsx
+++ b/static/downloads/plantilla_empleados.xlsx
@@ -49680,7 +49680,7 @@
       <c r="AU1000" s="2" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="3">
     <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="warning">
       <formula1>"Semanal,Por hora,Cuadrado"</formula1>
     </dataValidation>
@@ -49690,9 +49690,6 @@
     <dataValidation sqref="AN2:AN1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="warning">
       <formula1>"Si,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="AS2:AS1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="warning">
-      <formula1>"EFECTIVO,TRANSFERENCIA"</formula1>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/static/downloads/plantilla_empleados.xlsx
+++ b/static/downloads/plantilla_empleados.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU1000"/>
+  <dimension ref="A1:AT1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -486,9 +486,8 @@
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
-    <col width="20" customWidth="1" min="45" max="45"/>
-    <col width="21.6" customWidth="1" min="46" max="46"/>
-    <col width="20" customWidth="1" min="47" max="47"/>
+    <col width="21.6" customWidth="1" min="45" max="45"/>
+    <col width="20" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -704,25 +703,20 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>Pagos Efectivo</t>
+          <t>Folio Mov IDSE</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>Folio Mov IDSE</t>
+          <t>Tipo Pago</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>Tipo Pago</t>
+          <t>Ubicacion Estado</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>Ubicacion Estado</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
@@ -775,7 +769,6 @@
       <c r="AR2" s="2" t="n"/>
       <c r="AS2" s="2" t="n"/>
       <c r="AT2" s="2" t="n"/>
-      <c r="AU2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -824,7 +817,6 @@
       <c r="AR3" s="2" t="n"/>
       <c r="AS3" s="2" t="n"/>
       <c r="AT3" s="2" t="n"/>
-      <c r="AU3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
@@ -873,7 +865,6 @@
       <c r="AR4" s="2" t="n"/>
       <c r="AS4" s="2" t="n"/>
       <c r="AT4" s="2" t="n"/>
-      <c r="AU4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -922,7 +913,6 @@
       <c r="AR5" s="2" t="n"/>
       <c r="AS5" s="2" t="n"/>
       <c r="AT5" s="2" t="n"/>
-      <c r="AU5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -971,7 +961,6 @@
       <c r="AR6" s="2" t="n"/>
       <c r="AS6" s="2" t="n"/>
       <c r="AT6" s="2" t="n"/>
-      <c r="AU6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
@@ -1020,7 +1009,6 @@
       <c r="AR7" s="2" t="n"/>
       <c r="AS7" s="2" t="n"/>
       <c r="AT7" s="2" t="n"/>
-      <c r="AU7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -1069,7 +1057,6 @@
       <c r="AR8" s="2" t="n"/>
       <c r="AS8" s="2" t="n"/>
       <c r="AT8" s="2" t="n"/>
-      <c r="AU8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -1118,7 +1105,6 @@
       <c r="AR9" s="2" t="n"/>
       <c r="AS9" s="2" t="n"/>
       <c r="AT9" s="2" t="n"/>
-      <c r="AU9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -1167,7 +1153,6 @@
       <c r="AR10" s="2" t="n"/>
       <c r="AS10" s="2" t="n"/>
       <c r="AT10" s="2" t="n"/>
-      <c r="AU10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -1216,7 +1201,6 @@
       <c r="AR11" s="2" t="n"/>
       <c r="AS11" s="2" t="n"/>
       <c r="AT11" s="2" t="n"/>
-      <c r="AU11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -1265,7 +1249,6 @@
       <c r="AR12" s="2" t="n"/>
       <c r="AS12" s="2" t="n"/>
       <c r="AT12" s="2" t="n"/>
-      <c r="AU12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -1314,7 +1297,6 @@
       <c r="AR13" s="2" t="n"/>
       <c r="AS13" s="2" t="n"/>
       <c r="AT13" s="2" t="n"/>
-      <c r="AU13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
@@ -1363,7 +1345,6 @@
       <c r="AR14" s="2" t="n"/>
       <c r="AS14" s="2" t="n"/>
       <c r="AT14" s="2" t="n"/>
-      <c r="AU14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
@@ -1412,7 +1393,6 @@
       <c r="AR15" s="2" t="n"/>
       <c r="AS15" s="2" t="n"/>
       <c r="AT15" s="2" t="n"/>
-      <c r="AU15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -1461,7 +1441,6 @@
       <c r="AR16" s="2" t="n"/>
       <c r="AS16" s="2" t="n"/>
       <c r="AT16" s="2" t="n"/>
-      <c r="AU16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
@@ -1510,7 +1489,6 @@
       <c r="AR17" s="2" t="n"/>
       <c r="AS17" s="2" t="n"/>
       <c r="AT17" s="2" t="n"/>
-      <c r="AU17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -1559,7 +1537,6 @@
       <c r="AR18" s="2" t="n"/>
       <c r="AS18" s="2" t="n"/>
       <c r="AT18" s="2" t="n"/>
-      <c r="AU18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
@@ -1608,7 +1585,6 @@
       <c r="AR19" s="2" t="n"/>
       <c r="AS19" s="2" t="n"/>
       <c r="AT19" s="2" t="n"/>
-      <c r="AU19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -1657,7 +1633,6 @@
       <c r="AR20" s="2" t="n"/>
       <c r="AS20" s="2" t="n"/>
       <c r="AT20" s="2" t="n"/>
-      <c r="AU20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
@@ -1706,7 +1681,6 @@
       <c r="AR21" s="2" t="n"/>
       <c r="AS21" s="2" t="n"/>
       <c r="AT21" s="2" t="n"/>
-      <c r="AU21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -1755,7 +1729,6 @@
       <c r="AR22" s="2" t="n"/>
       <c r="AS22" s="2" t="n"/>
       <c r="AT22" s="2" t="n"/>
-      <c r="AU22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
@@ -1804,7 +1777,6 @@
       <c r="AR23" s="2" t="n"/>
       <c r="AS23" s="2" t="n"/>
       <c r="AT23" s="2" t="n"/>
-      <c r="AU23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -1853,7 +1825,6 @@
       <c r="AR24" s="2" t="n"/>
       <c r="AS24" s="2" t="n"/>
       <c r="AT24" s="2" t="n"/>
-      <c r="AU24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
@@ -1902,7 +1873,6 @@
       <c r="AR25" s="2" t="n"/>
       <c r="AS25" s="2" t="n"/>
       <c r="AT25" s="2" t="n"/>
-      <c r="AU25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -1951,7 +1921,6 @@
       <c r="AR26" s="2" t="n"/>
       <c r="AS26" s="2" t="n"/>
       <c r="AT26" s="2" t="n"/>
-      <c r="AU26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
@@ -2000,7 +1969,6 @@
       <c r="AR27" s="2" t="n"/>
       <c r="AS27" s="2" t="n"/>
       <c r="AT27" s="2" t="n"/>
-      <c r="AU27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -2049,7 +2017,6 @@
       <c r="AR28" s="2" t="n"/>
       <c r="AS28" s="2" t="n"/>
       <c r="AT28" s="2" t="n"/>
-      <c r="AU28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -2098,7 +2065,6 @@
       <c r="AR29" s="2" t="n"/>
       <c r="AS29" s="2" t="n"/>
       <c r="AT29" s="2" t="n"/>
-      <c r="AU29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -2147,7 +2113,6 @@
       <c r="AR30" s="2" t="n"/>
       <c r="AS30" s="2" t="n"/>
       <c r="AT30" s="2" t="n"/>
-      <c r="AU30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
@@ -2196,7 +2161,6 @@
       <c r="AR31" s="2" t="n"/>
       <c r="AS31" s="2" t="n"/>
       <c r="AT31" s="2" t="n"/>
-      <c r="AU31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
@@ -2245,7 +2209,6 @@
       <c r="AR32" s="2" t="n"/>
       <c r="AS32" s="2" t="n"/>
       <c r="AT32" s="2" t="n"/>
-      <c r="AU32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
@@ -2294,7 +2257,6 @@
       <c r="AR33" s="2" t="n"/>
       <c r="AS33" s="2" t="n"/>
       <c r="AT33" s="2" t="n"/>
-      <c r="AU33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -2343,7 +2305,6 @@
       <c r="AR34" s="2" t="n"/>
       <c r="AS34" s="2" t="n"/>
       <c r="AT34" s="2" t="n"/>
-      <c r="AU34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
@@ -2392,7 +2353,6 @@
       <c r="AR35" s="2" t="n"/>
       <c r="AS35" s="2" t="n"/>
       <c r="AT35" s="2" t="n"/>
-      <c r="AU35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
@@ -2441,7 +2401,6 @@
       <c r="AR36" s="2" t="n"/>
       <c r="AS36" s="2" t="n"/>
       <c r="AT36" s="2" t="n"/>
-      <c r="AU36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
@@ -2490,7 +2449,6 @@
       <c r="AR37" s="2" t="n"/>
       <c r="AS37" s="2" t="n"/>
       <c r="AT37" s="2" t="n"/>
-      <c r="AU37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
@@ -2539,7 +2497,6 @@
       <c r="AR38" s="2" t="n"/>
       <c r="AS38" s="2" t="n"/>
       <c r="AT38" s="2" t="n"/>
-      <c r="AU38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>
@@ -2588,7 +2545,6 @@
       <c r="AR39" s="2" t="n"/>
       <c r="AS39" s="2" t="n"/>
       <c r="AT39" s="2" t="n"/>
-      <c r="AU39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
@@ -2637,7 +2593,6 @@
       <c r="AR40" s="2" t="n"/>
       <c r="AS40" s="2" t="n"/>
       <c r="AT40" s="2" t="n"/>
-      <c r="AU40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
@@ -2686,7 +2641,6 @@
       <c r="AR41" s="2" t="n"/>
       <c r="AS41" s="2" t="n"/>
       <c r="AT41" s="2" t="n"/>
-      <c r="AU41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -2735,7 +2689,6 @@
       <c r="AR42" s="2" t="n"/>
       <c r="AS42" s="2" t="n"/>
       <c r="AT42" s="2" t="n"/>
-      <c r="AU42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
@@ -2784,7 +2737,6 @@
       <c r="AR43" s="2" t="n"/>
       <c r="AS43" s="2" t="n"/>
       <c r="AT43" s="2" t="n"/>
-      <c r="AU43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
@@ -2833,7 +2785,6 @@
       <c r="AR44" s="2" t="n"/>
       <c r="AS44" s="2" t="n"/>
       <c r="AT44" s="2" t="n"/>
-      <c r="AU44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
@@ -2882,7 +2833,6 @@
       <c r="AR45" s="2" t="n"/>
       <c r="AS45" s="2" t="n"/>
       <c r="AT45" s="2" t="n"/>
-      <c r="AU45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n"/>
@@ -2931,7 +2881,6 @@
       <c r="AR46" s="2" t="n"/>
       <c r="AS46" s="2" t="n"/>
       <c r="AT46" s="2" t="n"/>
-      <c r="AU46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n"/>
@@ -2980,7 +2929,6 @@
       <c r="AR47" s="2" t="n"/>
       <c r="AS47" s="2" t="n"/>
       <c r="AT47" s="2" t="n"/>
-      <c r="AU47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n"/>
@@ -3029,7 +2977,6 @@
       <c r="AR48" s="2" t="n"/>
       <c r="AS48" s="2" t="n"/>
       <c r="AT48" s="2" t="n"/>
-      <c r="AU48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n"/>
@@ -3078,7 +3025,6 @@
       <c r="AR49" s="2" t="n"/>
       <c r="AS49" s="2" t="n"/>
       <c r="AT49" s="2" t="n"/>
-      <c r="AU49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n"/>
@@ -3127,7 +3073,6 @@
       <c r="AR50" s="2" t="n"/>
       <c r="AS50" s="2" t="n"/>
       <c r="AT50" s="2" t="n"/>
-      <c r="AU50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n"/>
@@ -3176,7 +3121,6 @@
       <c r="AR51" s="2" t="n"/>
       <c r="AS51" s="2" t="n"/>
       <c r="AT51" s="2" t="n"/>
-      <c r="AU51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n"/>
@@ -3225,7 +3169,6 @@
       <c r="AR52" s="2" t="n"/>
       <c r="AS52" s="2" t="n"/>
       <c r="AT52" s="2" t="n"/>
-      <c r="AU52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n"/>
@@ -3274,7 +3217,6 @@
       <c r="AR53" s="2" t="n"/>
       <c r="AS53" s="2" t="n"/>
       <c r="AT53" s="2" t="n"/>
-      <c r="AU53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n"/>
@@ -3323,7 +3265,6 @@
       <c r="AR54" s="2" t="n"/>
       <c r="AS54" s="2" t="n"/>
       <c r="AT54" s="2" t="n"/>
-      <c r="AU54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n"/>
@@ -3372,7 +3313,6 @@
       <c r="AR55" s="2" t="n"/>
       <c r="AS55" s="2" t="n"/>
       <c r="AT55" s="2" t="n"/>
-      <c r="AU55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n"/>
@@ -3421,7 +3361,6 @@
       <c r="AR56" s="2" t="n"/>
       <c r="AS56" s="2" t="n"/>
       <c r="AT56" s="2" t="n"/>
-      <c r="AU56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n"/>
@@ -3470,7 +3409,6 @@
       <c r="AR57" s="2" t="n"/>
       <c r="AS57" s="2" t="n"/>
       <c r="AT57" s="2" t="n"/>
-      <c r="AU57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n"/>
@@ -3519,7 +3457,6 @@
       <c r="AR58" s="2" t="n"/>
       <c r="AS58" s="2" t="n"/>
       <c r="AT58" s="2" t="n"/>
-      <c r="AU58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n"/>
@@ -3568,7 +3505,6 @@
       <c r="AR59" s="2" t="n"/>
       <c r="AS59" s="2" t="n"/>
       <c r="AT59" s="2" t="n"/>
-      <c r="AU59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n"/>
@@ -3617,7 +3553,6 @@
       <c r="AR60" s="2" t="n"/>
       <c r="AS60" s="2" t="n"/>
       <c r="AT60" s="2" t="n"/>
-      <c r="AU60" s="2" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n"/>
@@ -3666,7 +3601,6 @@
       <c r="AR61" s="2" t="n"/>
       <c r="AS61" s="2" t="n"/>
       <c r="AT61" s="2" t="n"/>
-      <c r="AU61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n"/>
@@ -3715,7 +3649,6 @@
       <c r="AR62" s="2" t="n"/>
       <c r="AS62" s="2" t="n"/>
       <c r="AT62" s="2" t="n"/>
-      <c r="AU62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n"/>
@@ -3764,7 +3697,6 @@
       <c r="AR63" s="2" t="n"/>
       <c r="AS63" s="2" t="n"/>
       <c r="AT63" s="2" t="n"/>
-      <c r="AU63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n"/>
@@ -3813,7 +3745,6 @@
       <c r="AR64" s="2" t="n"/>
       <c r="AS64" s="2" t="n"/>
       <c r="AT64" s="2" t="n"/>
-      <c r="AU64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n"/>
@@ -3862,7 +3793,6 @@
       <c r="AR65" s="2" t="n"/>
       <c r="AS65" s="2" t="n"/>
       <c r="AT65" s="2" t="n"/>
-      <c r="AU65" s="2" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n"/>
@@ -3911,7 +3841,6 @@
       <c r="AR66" s="2" t="n"/>
       <c r="AS66" s="2" t="n"/>
       <c r="AT66" s="2" t="n"/>
-      <c r="AU66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n"/>
@@ -3960,7 +3889,6 @@
       <c r="AR67" s="2" t="n"/>
       <c r="AS67" s="2" t="n"/>
       <c r="AT67" s="2" t="n"/>
-      <c r="AU67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n"/>
@@ -4009,7 +3937,6 @@
       <c r="AR68" s="2" t="n"/>
       <c r="AS68" s="2" t="n"/>
       <c r="AT68" s="2" t="n"/>
-      <c r="AU68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n"/>
@@ -4058,7 +3985,6 @@
       <c r="AR69" s="2" t="n"/>
       <c r="AS69" s="2" t="n"/>
       <c r="AT69" s="2" t="n"/>
-      <c r="AU69" s="2" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n"/>
@@ -4107,7 +4033,6 @@
       <c r="AR70" s="2" t="n"/>
       <c r="AS70" s="2" t="n"/>
       <c r="AT70" s="2" t="n"/>
-      <c r="AU70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n"/>
@@ -4156,7 +4081,6 @@
       <c r="AR71" s="2" t="n"/>
       <c r="AS71" s="2" t="n"/>
       <c r="AT71" s="2" t="n"/>
-      <c r="AU71" s="2" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n"/>
@@ -4205,7 +4129,6 @@
       <c r="AR72" s="2" t="n"/>
       <c r="AS72" s="2" t="n"/>
       <c r="AT72" s="2" t="n"/>
-      <c r="AU72" s="2" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n"/>
@@ -4254,7 +4177,6 @@
       <c r="AR73" s="2" t="n"/>
       <c r="AS73" s="2" t="n"/>
       <c r="AT73" s="2" t="n"/>
-      <c r="AU73" s="2" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n"/>
@@ -4303,7 +4225,6 @@
       <c r="AR74" s="2" t="n"/>
       <c r="AS74" s="2" t="n"/>
       <c r="AT74" s="2" t="n"/>
-      <c r="AU74" s="2" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n"/>
@@ -4352,7 +4273,6 @@
       <c r="AR75" s="2" t="n"/>
       <c r="AS75" s="2" t="n"/>
       <c r="AT75" s="2" t="n"/>
-      <c r="AU75" s="2" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n"/>
@@ -4401,7 +4321,6 @@
       <c r="AR76" s="2" t="n"/>
       <c r="AS76" s="2" t="n"/>
       <c r="AT76" s="2" t="n"/>
-      <c r="AU76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n"/>
@@ -4450,7 +4369,6 @@
       <c r="AR77" s="2" t="n"/>
       <c r="AS77" s="2" t="n"/>
       <c r="AT77" s="2" t="n"/>
-      <c r="AU77" s="2" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n"/>
@@ -4499,7 +4417,6 @@
       <c r="AR78" s="2" t="n"/>
       <c r="AS78" s="2" t="n"/>
       <c r="AT78" s="2" t="n"/>
-      <c r="AU78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n"/>
@@ -4548,7 +4465,6 @@
       <c r="AR79" s="2" t="n"/>
       <c r="AS79" s="2" t="n"/>
       <c r="AT79" s="2" t="n"/>
-      <c r="AU79" s="2" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n"/>
@@ -4597,7 +4513,6 @@
       <c r="AR80" s="2" t="n"/>
       <c r="AS80" s="2" t="n"/>
       <c r="AT80" s="2" t="n"/>
-      <c r="AU80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n"/>
@@ -4646,7 +4561,6 @@
       <c r="AR81" s="2" t="n"/>
       <c r="AS81" s="2" t="n"/>
       <c r="AT81" s="2" t="n"/>
-      <c r="AU81" s="2" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n"/>
@@ -4695,7 +4609,6 @@
       <c r="AR82" s="2" t="n"/>
       <c r="AS82" s="2" t="n"/>
       <c r="AT82" s="2" t="n"/>
-      <c r="AU82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n"/>
@@ -4744,7 +4657,6 @@
       <c r="AR83" s="2" t="n"/>
       <c r="AS83" s="2" t="n"/>
       <c r="AT83" s="2" t="n"/>
-      <c r="AU83" s="2" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n"/>
@@ -4793,7 +4705,6 @@
       <c r="AR84" s="2" t="n"/>
       <c r="AS84" s="2" t="n"/>
       <c r="AT84" s="2" t="n"/>
-      <c r="AU84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n"/>
@@ -4842,7 +4753,6 @@
       <c r="AR85" s="2" t="n"/>
       <c r="AS85" s="2" t="n"/>
       <c r="AT85" s="2" t="n"/>
-      <c r="AU85" s="2" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n"/>
@@ -4891,7 +4801,6 @@
       <c r="AR86" s="2" t="n"/>
       <c r="AS86" s="2" t="n"/>
       <c r="AT86" s="2" t="n"/>
-      <c r="AU86" s="2" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n"/>
@@ -4940,7 +4849,6 @@
       <c r="AR87" s="2" t="n"/>
       <c r="AS87" s="2" t="n"/>
       <c r="AT87" s="2" t="n"/>
-      <c r="AU87" s="2" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n"/>
@@ -4989,7 +4897,6 @@
       <c r="AR88" s="2" t="n"/>
       <c r="AS88" s="2" t="n"/>
       <c r="AT88" s="2" t="n"/>
-      <c r="AU88" s="2" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n"/>
@@ -5038,7 +4945,6 @@
       <c r="AR89" s="2" t="n"/>
       <c r="AS89" s="2" t="n"/>
       <c r="AT89" s="2" t="n"/>
-      <c r="AU89" s="2" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n"/>
@@ -5087,7 +4993,6 @@
       <c r="AR90" s="2" t="n"/>
       <c r="AS90" s="2" t="n"/>
       <c r="AT90" s="2" t="n"/>
-      <c r="AU90" s="2" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n"/>
@@ -5136,7 +5041,6 @@
       <c r="AR91" s="2" t="n"/>
       <c r="AS91" s="2" t="n"/>
       <c r="AT91" s="2" t="n"/>
-      <c r="AU91" s="2" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n"/>
@@ -5185,7 +5089,6 @@
       <c r="AR92" s="2" t="n"/>
       <c r="AS92" s="2" t="n"/>
       <c r="AT92" s="2" t="n"/>
-      <c r="AU92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n"/>
@@ -5234,7 +5137,6 @@
       <c r="AR93" s="2" t="n"/>
       <c r="AS93" s="2" t="n"/>
       <c r="AT93" s="2" t="n"/>
-      <c r="AU93" s="2" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n"/>
@@ -5283,7 +5185,6 @@
       <c r="AR94" s="2" t="n"/>
       <c r="AS94" s="2" t="n"/>
       <c r="AT94" s="2" t="n"/>
-      <c r="AU94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n"/>
@@ -5332,7 +5233,6 @@
       <c r="AR95" s="2" t="n"/>
       <c r="AS95" s="2" t="n"/>
       <c r="AT95" s="2" t="n"/>
-      <c r="AU95" s="2" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n"/>
@@ -5381,7 +5281,6 @@
       <c r="AR96" s="2" t="n"/>
       <c r="AS96" s="2" t="n"/>
       <c r="AT96" s="2" t="n"/>
-      <c r="AU96" s="2" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n"/>
@@ -5430,7 +5329,6 @@
       <c r="AR97" s="2" t="n"/>
       <c r="AS97" s="2" t="n"/>
       <c r="AT97" s="2" t="n"/>
-      <c r="AU97" s="2" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n"/>
@@ -5479,7 +5377,6 @@
       <c r="AR98" s="2" t="n"/>
       <c r="AS98" s="2" t="n"/>
       <c r="AT98" s="2" t="n"/>
-      <c r="AU98" s="2" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n"/>
@@ -5528,7 +5425,6 @@
       <c r="AR99" s="2" t="n"/>
       <c r="AS99" s="2" t="n"/>
       <c r="AT99" s="2" t="n"/>
-      <c r="AU99" s="2" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n"/>
@@ -5577,7 +5473,6 @@
       <c r="AR100" s="2" t="n"/>
       <c r="AS100" s="2" t="n"/>
       <c r="AT100" s="2" t="n"/>
-      <c r="AU100" s="2" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n"/>
@@ -5626,7 +5521,6 @@
       <c r="AR101" s="2" t="n"/>
       <c r="AS101" s="2" t="n"/>
       <c r="AT101" s="2" t="n"/>
-      <c r="AU101" s="2" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n"/>
@@ -5675,7 +5569,6 @@
       <c r="AR102" s="2" t="n"/>
       <c r="AS102" s="2" t="n"/>
       <c r="AT102" s="2" t="n"/>
-      <c r="AU102" s="2" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n"/>
@@ -5724,7 +5617,6 @@
       <c r="AR103" s="2" t="n"/>
       <c r="AS103" s="2" t="n"/>
       <c r="AT103" s="2" t="n"/>
-      <c r="AU103" s="2" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n"/>
@@ -5773,7 +5665,6 @@
       <c r="AR104" s="2" t="n"/>
       <c r="AS104" s="2" t="n"/>
       <c r="AT104" s="2" t="n"/>
-      <c r="AU104" s="2" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n"/>
@@ -5822,7 +5713,6 @@
       <c r="AR105" s="2" t="n"/>
       <c r="AS105" s="2" t="n"/>
       <c r="AT105" s="2" t="n"/>
-      <c r="AU105" s="2" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n"/>
@@ -5871,7 +5761,6 @@
       <c r="AR106" s="2" t="n"/>
       <c r="AS106" s="2" t="n"/>
       <c r="AT106" s="2" t="n"/>
-      <c r="AU106" s="2" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n"/>
@@ -5920,7 +5809,6 @@
       <c r="AR107" s="2" t="n"/>
       <c r="AS107" s="2" t="n"/>
       <c r="AT107" s="2" t="n"/>
-      <c r="AU107" s="2" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n"/>
@@ -5969,7 +5857,6 @@
       <c r="AR108" s="2" t="n"/>
       <c r="AS108" s="2" t="n"/>
       <c r="AT108" s="2" t="n"/>
-      <c r="AU108" s="2" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n"/>
@@ -6018,7 +5905,6 @@
       <c r="AR109" s="2" t="n"/>
       <c r="AS109" s="2" t="n"/>
       <c r="AT109" s="2" t="n"/>
-      <c r="AU109" s="2" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n"/>
@@ -6067,7 +5953,6 @@
       <c r="AR110" s="2" t="n"/>
       <c r="AS110" s="2" t="n"/>
       <c r="AT110" s="2" t="n"/>
-      <c r="AU110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n"/>
@@ -6116,7 +6001,6 @@
       <c r="AR111" s="2" t="n"/>
       <c r="AS111" s="2" t="n"/>
       <c r="AT111" s="2" t="n"/>
-      <c r="AU111" s="2" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n"/>
@@ -6165,7 +6049,6 @@
       <c r="AR112" s="2" t="n"/>
       <c r="AS112" s="2" t="n"/>
       <c r="AT112" s="2" t="n"/>
-      <c r="AU112" s="2" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n"/>
@@ -6214,7 +6097,6 @@
       <c r="AR113" s="2" t="n"/>
       <c r="AS113" s="2" t="n"/>
       <c r="AT113" s="2" t="n"/>
-      <c r="AU113" s="2" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n"/>
@@ -6263,7 +6145,6 @@
       <c r="AR114" s="2" t="n"/>
       <c r="AS114" s="2" t="n"/>
       <c r="AT114" s="2" t="n"/>
-      <c r="AU114" s="2" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n"/>
@@ -6312,7 +6193,6 @@
       <c r="AR115" s="2" t="n"/>
       <c r="AS115" s="2" t="n"/>
       <c r="AT115" s="2" t="n"/>
-      <c r="AU115" s="2" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n"/>
@@ -6361,7 +6241,6 @@
       <c r="AR116" s="2" t="n"/>
       <c r="AS116" s="2" t="n"/>
       <c r="AT116" s="2" t="n"/>
-      <c r="AU116" s="2" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n"/>
@@ -6410,7 +6289,6 @@
       <c r="AR117" s="2" t="n"/>
       <c r="AS117" s="2" t="n"/>
       <c r="AT117" s="2" t="n"/>
-      <c r="AU117" s="2" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n"/>
@@ -6459,7 +6337,6 @@
       <c r="AR118" s="2" t="n"/>
       <c r="AS118" s="2" t="n"/>
       <c r="AT118" s="2" t="n"/>
-      <c r="AU118" s="2" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n"/>
@@ -6508,7 +6385,6 @@
       <c r="AR119" s="2" t="n"/>
       <c r="AS119" s="2" t="n"/>
       <c r="AT119" s="2" t="n"/>
-      <c r="AU119" s="2" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n"/>
@@ -6557,7 +6433,6 @@
       <c r="AR120" s="2" t="n"/>
       <c r="AS120" s="2" t="n"/>
       <c r="AT120" s="2" t="n"/>
-      <c r="AU120" s="2" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n"/>
@@ -6606,7 +6481,6 @@
       <c r="AR121" s="2" t="n"/>
       <c r="AS121" s="2" t="n"/>
       <c r="AT121" s="2" t="n"/>
-      <c r="AU121" s="2" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n"/>
@@ -6655,7 +6529,6 @@
       <c r="AR122" s="2" t="n"/>
       <c r="AS122" s="2" t="n"/>
       <c r="AT122" s="2" t="n"/>
-      <c r="AU122" s="2" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n"/>
@@ -6704,7 +6577,6 @@
       <c r="AR123" s="2" t="n"/>
       <c r="AS123" s="2" t="n"/>
       <c r="AT123" s="2" t="n"/>
-      <c r="AU123" s="2" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n"/>
@@ -6753,7 +6625,6 @@
       <c r="AR124" s="2" t="n"/>
       <c r="AS124" s="2" t="n"/>
       <c r="AT124" s="2" t="n"/>
-      <c r="AU124" s="2" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n"/>
@@ -6802,7 +6673,6 @@
       <c r="AR125" s="2" t="n"/>
       <c r="AS125" s="2" t="n"/>
       <c r="AT125" s="2" t="n"/>
-      <c r="AU125" s="2" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n"/>
@@ -6851,7 +6721,6 @@
       <c r="AR126" s="2" t="n"/>
       <c r="AS126" s="2" t="n"/>
       <c r="AT126" s="2" t="n"/>
-      <c r="AU126" s="2" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n"/>
@@ -6900,7 +6769,6 @@
       <c r="AR127" s="2" t="n"/>
       <c r="AS127" s="2" t="n"/>
       <c r="AT127" s="2" t="n"/>
-      <c r="AU127" s="2" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n"/>
@@ -6949,7 +6817,6 @@
       <c r="AR128" s="2" t="n"/>
       <c r="AS128" s="2" t="n"/>
       <c r="AT128" s="2" t="n"/>
-      <c r="AU128" s="2" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n"/>
@@ -6998,7 +6865,6 @@
       <c r="AR129" s="2" t="n"/>
       <c r="AS129" s="2" t="n"/>
       <c r="AT129" s="2" t="n"/>
-      <c r="AU129" s="2" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n"/>
@@ -7047,7 +6913,6 @@
       <c r="AR130" s="2" t="n"/>
       <c r="AS130" s="2" t="n"/>
       <c r="AT130" s="2" t="n"/>
-      <c r="AU130" s="2" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n"/>
@@ -7096,7 +6961,6 @@
       <c r="AR131" s="2" t="n"/>
       <c r="AS131" s="2" t="n"/>
       <c r="AT131" s="2" t="n"/>
-      <c r="AU131" s="2" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n"/>
@@ -7145,7 +7009,6 @@
       <c r="AR132" s="2" t="n"/>
       <c r="AS132" s="2" t="n"/>
       <c r="AT132" s="2" t="n"/>
-      <c r="AU132" s="2" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n"/>
@@ -7194,7 +7057,6 @@
       <c r="AR133" s="2" t="n"/>
       <c r="AS133" s="2" t="n"/>
       <c r="AT133" s="2" t="n"/>
-      <c r="AU133" s="2" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n"/>
@@ -7243,7 +7105,6 @@
       <c r="AR134" s="2" t="n"/>
       <c r="AS134" s="2" t="n"/>
       <c r="AT134" s="2" t="n"/>
-      <c r="AU134" s="2" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n"/>
@@ -7292,7 +7153,6 @@
       <c r="AR135" s="2" t="n"/>
       <c r="AS135" s="2" t="n"/>
       <c r="AT135" s="2" t="n"/>
-      <c r="AU135" s="2" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n"/>
@@ -7341,7 +7201,6 @@
       <c r="AR136" s="2" t="n"/>
       <c r="AS136" s="2" t="n"/>
       <c r="AT136" s="2" t="n"/>
-      <c r="AU136" s="2" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n"/>
@@ -7390,7 +7249,6 @@
       <c r="AR137" s="2" t="n"/>
       <c r="AS137" s="2" t="n"/>
       <c r="AT137" s="2" t="n"/>
-      <c r="AU137" s="2" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n"/>
@@ -7439,7 +7297,6 @@
       <c r="AR138" s="2" t="n"/>
       <c r="AS138" s="2" t="n"/>
       <c r="AT138" s="2" t="n"/>
-      <c r="AU138" s="2" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n"/>
@@ -7488,7 +7345,6 @@
       <c r="AR139" s="2" t="n"/>
       <c r="AS139" s="2" t="n"/>
       <c r="AT139" s="2" t="n"/>
-      <c r="AU139" s="2" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n"/>
@@ -7537,7 +7393,6 @@
       <c r="AR140" s="2" t="n"/>
       <c r="AS140" s="2" t="n"/>
       <c r="AT140" s="2" t="n"/>
-      <c r="AU140" s="2" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n"/>
@@ -7586,7 +7441,6 @@
       <c r="AR141" s="2" t="n"/>
       <c r="AS141" s="2" t="n"/>
       <c r="AT141" s="2" t="n"/>
-      <c r="AU141" s="2" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n"/>
@@ -7635,7 +7489,6 @@
       <c r="AR142" s="2" t="n"/>
       <c r="AS142" s="2" t="n"/>
       <c r="AT142" s="2" t="n"/>
-      <c r="AU142" s="2" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n"/>
@@ -7684,7 +7537,6 @@
       <c r="AR143" s="2" t="n"/>
       <c r="AS143" s="2" t="n"/>
       <c r="AT143" s="2" t="n"/>
-      <c r="AU143" s="2" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n"/>
@@ -7733,7 +7585,6 @@
       <c r="AR144" s="2" t="n"/>
       <c r="AS144" s="2" t="n"/>
       <c r="AT144" s="2" t="n"/>
-      <c r="AU144" s="2" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n"/>
@@ -7782,7 +7633,6 @@
       <c r="AR145" s="2" t="n"/>
       <c r="AS145" s="2" t="n"/>
       <c r="AT145" s="2" t="n"/>
-      <c r="AU145" s="2" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n"/>
@@ -7831,7 +7681,6 @@
       <c r="AR146" s="2" t="n"/>
       <c r="AS146" s="2" t="n"/>
       <c r="AT146" s="2" t="n"/>
-      <c r="AU146" s="2" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n"/>
@@ -7880,7 +7729,6 @@
       <c r="AR147" s="2" t="n"/>
       <c r="AS147" s="2" t="n"/>
       <c r="AT147" s="2" t="n"/>
-      <c r="AU147" s="2" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n"/>
@@ -7929,7 +7777,6 @@
       <c r="AR148" s="2" t="n"/>
       <c r="AS148" s="2" t="n"/>
       <c r="AT148" s="2" t="n"/>
-      <c r="AU148" s="2" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n"/>
@@ -7978,7 +7825,6 @@
       <c r="AR149" s="2" t="n"/>
       <c r="AS149" s="2" t="n"/>
       <c r="AT149" s="2" t="n"/>
-      <c r="AU149" s="2" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n"/>
@@ -8027,7 +7873,6 @@
       <c r="AR150" s="2" t="n"/>
       <c r="AS150" s="2" t="n"/>
       <c r="AT150" s="2" t="n"/>
-      <c r="AU150" s="2" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n"/>
@@ -8076,7 +7921,6 @@
       <c r="AR151" s="2" t="n"/>
       <c r="AS151" s="2" t="n"/>
       <c r="AT151" s="2" t="n"/>
-      <c r="AU151" s="2" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n"/>
@@ -8125,7 +7969,6 @@
       <c r="AR152" s="2" t="n"/>
       <c r="AS152" s="2" t="n"/>
       <c r="AT152" s="2" t="n"/>
-      <c r="AU152" s="2" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n"/>
@@ -8174,7 +8017,6 @@
       <c r="AR153" s="2" t="n"/>
       <c r="AS153" s="2" t="n"/>
       <c r="AT153" s="2" t="n"/>
-      <c r="AU153" s="2" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n"/>
@@ -8223,7 +8065,6 @@
       <c r="AR154" s="2" t="n"/>
       <c r="AS154" s="2" t="n"/>
       <c r="AT154" s="2" t="n"/>
-      <c r="AU154" s="2" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n"/>
@@ -8272,7 +8113,6 @@
       <c r="AR155" s="2" t="n"/>
       <c r="AS155" s="2" t="n"/>
       <c r="AT155" s="2" t="n"/>
-      <c r="AU155" s="2" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n"/>
@@ -8321,7 +8161,6 @@
       <c r="AR156" s="2" t="n"/>
       <c r="AS156" s="2" t="n"/>
       <c r="AT156" s="2" t="n"/>
-      <c r="AU156" s="2" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n"/>
@@ -8370,7 +8209,6 @@
       <c r="AR157" s="2" t="n"/>
       <c r="AS157" s="2" t="n"/>
       <c r="AT157" s="2" t="n"/>
-      <c r="AU157" s="2" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n"/>
@@ -8419,7 +8257,6 @@
       <c r="AR158" s="2" t="n"/>
       <c r="AS158" s="2" t="n"/>
       <c r="AT158" s="2" t="n"/>
-      <c r="AU158" s="2" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n"/>
@@ -8468,7 +8305,6 @@
       <c r="AR159" s="2" t="n"/>
       <c r="AS159" s="2" t="n"/>
       <c r="AT159" s="2" t="n"/>
-      <c r="AU159" s="2" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n"/>
@@ -8517,7 +8353,6 @@
       <c r="AR160" s="2" t="n"/>
       <c r="AS160" s="2" t="n"/>
       <c r="AT160" s="2" t="n"/>
-      <c r="AU160" s="2" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n"/>
@@ -8566,7 +8401,6 @@
       <c r="AR161" s="2" t="n"/>
       <c r="AS161" s="2" t="n"/>
       <c r="AT161" s="2" t="n"/>
-      <c r="AU161" s="2" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n"/>
@@ -8615,7 +8449,6 @@
       <c r="AR162" s="2" t="n"/>
       <c r="AS162" s="2" t="n"/>
       <c r="AT162" s="2" t="n"/>
-      <c r="AU162" s="2" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n"/>
@@ -8664,7 +8497,6 @@
       <c r="AR163" s="2" t="n"/>
       <c r="AS163" s="2" t="n"/>
       <c r="AT163" s="2" t="n"/>
-      <c r="AU163" s="2" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n"/>
@@ -8713,7 +8545,6 @@
       <c r="AR164" s="2" t="n"/>
       <c r="AS164" s="2" t="n"/>
       <c r="AT164" s="2" t="n"/>
-      <c r="AU164" s="2" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n"/>
@@ -8762,7 +8593,6 @@
       <c r="AR165" s="2" t="n"/>
       <c r="AS165" s="2" t="n"/>
       <c r="AT165" s="2" t="n"/>
-      <c r="AU165" s="2" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n"/>
@@ -8811,7 +8641,6 @@
       <c r="AR166" s="2" t="n"/>
       <c r="AS166" s="2" t="n"/>
       <c r="AT166" s="2" t="n"/>
-      <c r="AU166" s="2" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n"/>
@@ -8860,7 +8689,6 @@
       <c r="AR167" s="2" t="n"/>
       <c r="AS167" s="2" t="n"/>
       <c r="AT167" s="2" t="n"/>
-      <c r="AU167" s="2" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n"/>
@@ -8909,7 +8737,6 @@
       <c r="AR168" s="2" t="n"/>
       <c r="AS168" s="2" t="n"/>
       <c r="AT168" s="2" t="n"/>
-      <c r="AU168" s="2" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n"/>
@@ -8958,7 +8785,6 @@
       <c r="AR169" s="2" t="n"/>
       <c r="AS169" s="2" t="n"/>
       <c r="AT169" s="2" t="n"/>
-      <c r="AU169" s="2" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n"/>
@@ -9007,7 +8833,6 @@
       <c r="AR170" s="2" t="n"/>
       <c r="AS170" s="2" t="n"/>
       <c r="AT170" s="2" t="n"/>
-      <c r="AU170" s="2" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n"/>
@@ -9056,7 +8881,6 @@
       <c r="AR171" s="2" t="n"/>
       <c r="AS171" s="2" t="n"/>
       <c r="AT171" s="2" t="n"/>
-      <c r="AU171" s="2" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n"/>
@@ -9105,7 +8929,6 @@
       <c r="AR172" s="2" t="n"/>
       <c r="AS172" s="2" t="n"/>
       <c r="AT172" s="2" t="n"/>
-      <c r="AU172" s="2" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n"/>
@@ -9154,7 +8977,6 @@
       <c r="AR173" s="2" t="n"/>
       <c r="AS173" s="2" t="n"/>
       <c r="AT173" s="2" t="n"/>
-      <c r="AU173" s="2" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n"/>
@@ -9203,7 +9025,6 @@
       <c r="AR174" s="2" t="n"/>
       <c r="AS174" s="2" t="n"/>
       <c r="AT174" s="2" t="n"/>
-      <c r="AU174" s="2" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n"/>
@@ -9252,7 +9073,6 @@
       <c r="AR175" s="2" t="n"/>
       <c r="AS175" s="2" t="n"/>
       <c r="AT175" s="2" t="n"/>
-      <c r="AU175" s="2" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n"/>
@@ -9301,7 +9121,6 @@
       <c r="AR176" s="2" t="n"/>
       <c r="AS176" s="2" t="n"/>
       <c r="AT176" s="2" t="n"/>
-      <c r="AU176" s="2" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n"/>
@@ -9350,7 +9169,6 @@
       <c r="AR177" s="2" t="n"/>
       <c r="AS177" s="2" t="n"/>
       <c r="AT177" s="2" t="n"/>
-      <c r="AU177" s="2" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n"/>
@@ -9399,7 +9217,6 @@
       <c r="AR178" s="2" t="n"/>
       <c r="AS178" s="2" t="n"/>
       <c r="AT178" s="2" t="n"/>
-      <c r="AU178" s="2" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n"/>
@@ -9448,7 +9265,6 @@
       <c r="AR179" s="2" t="n"/>
       <c r="AS179" s="2" t="n"/>
       <c r="AT179" s="2" t="n"/>
-      <c r="AU179" s="2" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n"/>
@@ -9497,7 +9313,6 @@
       <c r="AR180" s="2" t="n"/>
       <c r="AS180" s="2" t="n"/>
       <c r="AT180" s="2" t="n"/>
-      <c r="AU180" s="2" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n"/>
@@ -9546,7 +9361,6 @@
       <c r="AR181" s="2" t="n"/>
       <c r="AS181" s="2" t="n"/>
       <c r="AT181" s="2" t="n"/>
-      <c r="AU181" s="2" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n"/>
@@ -9595,7 +9409,6 @@
       <c r="AR182" s="2" t="n"/>
       <c r="AS182" s="2" t="n"/>
       <c r="AT182" s="2" t="n"/>
-      <c r="AU182" s="2" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n"/>
@@ -9644,7 +9457,6 @@
       <c r="AR183" s="2" t="n"/>
       <c r="AS183" s="2" t="n"/>
       <c r="AT183" s="2" t="n"/>
-      <c r="AU183" s="2" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n"/>
@@ -9693,7 +9505,6 @@
       <c r="AR184" s="2" t="n"/>
       <c r="AS184" s="2" t="n"/>
       <c r="AT184" s="2" t="n"/>
-      <c r="AU184" s="2" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n"/>
@@ -9742,7 +9553,6 @@
       <c r="AR185" s="2" t="n"/>
       <c r="AS185" s="2" t="n"/>
       <c r="AT185" s="2" t="n"/>
-      <c r="AU185" s="2" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n"/>
@@ -9791,7 +9601,6 @@
       <c r="AR186" s="2" t="n"/>
       <c r="AS186" s="2" t="n"/>
       <c r="AT186" s="2" t="n"/>
-      <c r="AU186" s="2" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n"/>
@@ -9840,7 +9649,6 @@
       <c r="AR187" s="2" t="n"/>
       <c r="AS187" s="2" t="n"/>
       <c r="AT187" s="2" t="n"/>
-      <c r="AU187" s="2" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n"/>
@@ -9889,7 +9697,6 @@
       <c r="AR188" s="2" t="n"/>
       <c r="AS188" s="2" t="n"/>
       <c r="AT188" s="2" t="n"/>
-      <c r="AU188" s="2" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n"/>
@@ -9938,7 +9745,6 @@
       <c r="AR189" s="2" t="n"/>
       <c r="AS189" s="2" t="n"/>
       <c r="AT189" s="2" t="n"/>
-      <c r="AU189" s="2" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n"/>
@@ -9987,7 +9793,6 @@
       <c r="AR190" s="2" t="n"/>
       <c r="AS190" s="2" t="n"/>
       <c r="AT190" s="2" t="n"/>
-      <c r="AU190" s="2" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n"/>
@@ -10036,7 +9841,6 @@
       <c r="AR191" s="2" t="n"/>
       <c r="AS191" s="2" t="n"/>
       <c r="AT191" s="2" t="n"/>
-      <c r="AU191" s="2" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n"/>
@@ -10085,7 +9889,6 @@
       <c r="AR192" s="2" t="n"/>
       <c r="AS192" s="2" t="n"/>
       <c r="AT192" s="2" t="n"/>
-      <c r="AU192" s="2" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n"/>
@@ -10134,7 +9937,6 @@
       <c r="AR193" s="2" t="n"/>
       <c r="AS193" s="2" t="n"/>
       <c r="AT193" s="2" t="n"/>
-      <c r="AU193" s="2" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n"/>
@@ -10183,7 +9985,6 @@
       <c r="AR194" s="2" t="n"/>
       <c r="AS194" s="2" t="n"/>
       <c r="AT194" s="2" t="n"/>
-      <c r="AU194" s="2" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n"/>
@@ -10232,7 +10033,6 @@
       <c r="AR195" s="2" t="n"/>
       <c r="AS195" s="2" t="n"/>
       <c r="AT195" s="2" t="n"/>
-      <c r="AU195" s="2" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n"/>
@@ -10281,7 +10081,6 @@
       <c r="AR196" s="2" t="n"/>
       <c r="AS196" s="2" t="n"/>
       <c r="AT196" s="2" t="n"/>
-      <c r="AU196" s="2" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n"/>
@@ -10330,7 +10129,6 @@
       <c r="AR197" s="2" t="n"/>
       <c r="AS197" s="2" t="n"/>
       <c r="AT197" s="2" t="n"/>
-      <c r="AU197" s="2" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n"/>
@@ -10379,7 +10177,6 @@
       <c r="AR198" s="2" t="n"/>
       <c r="AS198" s="2" t="n"/>
       <c r="AT198" s="2" t="n"/>
-      <c r="AU198" s="2" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n"/>
@@ -10428,7 +10225,6 @@
       <c r="AR199" s="2" t="n"/>
       <c r="AS199" s="2" t="n"/>
       <c r="AT199" s="2" t="n"/>
-      <c r="AU199" s="2" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n"/>
@@ -10477,7 +10273,6 @@
       <c r="AR200" s="2" t="n"/>
       <c r="AS200" s="2" t="n"/>
       <c r="AT200" s="2" t="n"/>
-      <c r="AU200" s="2" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n"/>
@@ -10526,7 +10321,6 @@
       <c r="AR201" s="2" t="n"/>
       <c r="AS201" s="2" t="n"/>
       <c r="AT201" s="2" t="n"/>
-      <c r="AU201" s="2" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n"/>
@@ -10575,7 +10369,6 @@
       <c r="AR202" s="2" t="n"/>
       <c r="AS202" s="2" t="n"/>
       <c r="AT202" s="2" t="n"/>
-      <c r="AU202" s="2" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n"/>
@@ -10624,7 +10417,6 @@
       <c r="AR203" s="2" t="n"/>
       <c r="AS203" s="2" t="n"/>
       <c r="AT203" s="2" t="n"/>
-      <c r="AU203" s="2" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n"/>
@@ -10673,7 +10465,6 @@
       <c r="AR204" s="2" t="n"/>
       <c r="AS204" s="2" t="n"/>
       <c r="AT204" s="2" t="n"/>
-      <c r="AU204" s="2" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n"/>
@@ -10722,7 +10513,6 @@
       <c r="AR205" s="2" t="n"/>
       <c r="AS205" s="2" t="n"/>
       <c r="AT205" s="2" t="n"/>
-      <c r="AU205" s="2" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n"/>
@@ -10771,7 +10561,6 @@
       <c r="AR206" s="2" t="n"/>
       <c r="AS206" s="2" t="n"/>
       <c r="AT206" s="2" t="n"/>
-      <c r="AU206" s="2" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n"/>
@@ -10820,7 +10609,6 @@
       <c r="AR207" s="2" t="n"/>
       <c r="AS207" s="2" t="n"/>
       <c r="AT207" s="2" t="n"/>
-      <c r="AU207" s="2" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n"/>
@@ -10869,7 +10657,6 @@
       <c r="AR208" s="2" t="n"/>
       <c r="AS208" s="2" t="n"/>
       <c r="AT208" s="2" t="n"/>
-      <c r="AU208" s="2" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n"/>
@@ -10918,7 +10705,6 @@
       <c r="AR209" s="2" t="n"/>
       <c r="AS209" s="2" t="n"/>
       <c r="AT209" s="2" t="n"/>
-      <c r="AU209" s="2" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n"/>
@@ -10967,7 +10753,6 @@
       <c r="AR210" s="2" t="n"/>
       <c r="AS210" s="2" t="n"/>
       <c r="AT210" s="2" t="n"/>
-      <c r="AU210" s="2" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n"/>
@@ -11016,7 +10801,6 @@
       <c r="AR211" s="2" t="n"/>
       <c r="AS211" s="2" t="n"/>
       <c r="AT211" s="2" t="n"/>
-      <c r="AU211" s="2" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n"/>
@@ -11065,7 +10849,6 @@
       <c r="AR212" s="2" t="n"/>
       <c r="AS212" s="2" t="n"/>
       <c r="AT212" s="2" t="n"/>
-      <c r="AU212" s="2" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n"/>
@@ -11114,7 +10897,6 @@
       <c r="AR213" s="2" t="n"/>
       <c r="AS213" s="2" t="n"/>
       <c r="AT213" s="2" t="n"/>
-      <c r="AU213" s="2" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n"/>
@@ -11163,7 +10945,6 @@
       <c r="AR214" s="2" t="n"/>
       <c r="AS214" s="2" t="n"/>
       <c r="AT214" s="2" t="n"/>
-      <c r="AU214" s="2" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n"/>
@@ -11212,7 +10993,6 @@
       <c r="AR215" s="2" t="n"/>
       <c r="AS215" s="2" t="n"/>
       <c r="AT215" s="2" t="n"/>
-      <c r="AU215" s="2" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n"/>
@@ -11261,7 +11041,6 @@
       <c r="AR216" s="2" t="n"/>
       <c r="AS216" s="2" t="n"/>
       <c r="AT216" s="2" t="n"/>
-      <c r="AU216" s="2" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n"/>
@@ -11310,7 +11089,6 @@
       <c r="AR217" s="2" t="n"/>
       <c r="AS217" s="2" t="n"/>
       <c r="AT217" s="2" t="n"/>
-      <c r="AU217" s="2" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n"/>
@@ -11359,7 +11137,6 @@
       <c r="AR218" s="2" t="n"/>
       <c r="AS218" s="2" t="n"/>
       <c r="AT218" s="2" t="n"/>
-      <c r="AU218" s="2" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n"/>
@@ -11408,7 +11185,6 @@
       <c r="AR219" s="2" t="n"/>
       <c r="AS219" s="2" t="n"/>
       <c r="AT219" s="2" t="n"/>
-      <c r="AU219" s="2" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n"/>
@@ -11457,7 +11233,6 @@
       <c r="AR220" s="2" t="n"/>
       <c r="AS220" s="2" t="n"/>
       <c r="AT220" s="2" t="n"/>
-      <c r="AU220" s="2" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n"/>
@@ -11506,7 +11281,6 @@
       <c r="AR221" s="2" t="n"/>
       <c r="AS221" s="2" t="n"/>
       <c r="AT221" s="2" t="n"/>
-      <c r="AU221" s="2" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n"/>
@@ -11555,7 +11329,6 @@
       <c r="AR222" s="2" t="n"/>
       <c r="AS222" s="2" t="n"/>
       <c r="AT222" s="2" t="n"/>
-      <c r="AU222" s="2" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n"/>
@@ -11604,7 +11377,6 @@
       <c r="AR223" s="2" t="n"/>
       <c r="AS223" s="2" t="n"/>
       <c r="AT223" s="2" t="n"/>
-      <c r="AU223" s="2" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n"/>
@@ -11653,7 +11425,6 @@
       <c r="AR224" s="2" t="n"/>
       <c r="AS224" s="2" t="n"/>
       <c r="AT224" s="2" t="n"/>
-      <c r="AU224" s="2" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n"/>
@@ -11702,7 +11473,6 @@
       <c r="AR225" s="2" t="n"/>
       <c r="AS225" s="2" t="n"/>
       <c r="AT225" s="2" t="n"/>
-      <c r="AU225" s="2" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n"/>
@@ -11751,7 +11521,6 @@
       <c r="AR226" s="2" t="n"/>
       <c r="AS226" s="2" t="n"/>
       <c r="AT226" s="2" t="n"/>
-      <c r="AU226" s="2" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n"/>
@@ -11800,7 +11569,6 @@
       <c r="AR227" s="2" t="n"/>
       <c r="AS227" s="2" t="n"/>
       <c r="AT227" s="2" t="n"/>
-      <c r="AU227" s="2" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n"/>
@@ -11849,7 +11617,6 @@
       <c r="AR228" s="2" t="n"/>
       <c r="AS228" s="2" t="n"/>
       <c r="AT228" s="2" t="n"/>
-      <c r="AU228" s="2" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n"/>
@@ -11898,7 +11665,6 @@
       <c r="AR229" s="2" t="n"/>
       <c r="AS229" s="2" t="n"/>
       <c r="AT229" s="2" t="n"/>
-      <c r="AU229" s="2" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n"/>
@@ -11947,7 +11713,6 @@
       <c r="AR230" s="2" t="n"/>
       <c r="AS230" s="2" t="n"/>
       <c r="AT230" s="2" t="n"/>
-      <c r="AU230" s="2" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n"/>
@@ -11996,7 +11761,6 @@
       <c r="AR231" s="2" t="n"/>
       <c r="AS231" s="2" t="n"/>
       <c r="AT231" s="2" t="n"/>
-      <c r="AU231" s="2" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n"/>
@@ -12045,7 +11809,6 @@
       <c r="AR232" s="2" t="n"/>
       <c r="AS232" s="2" t="n"/>
       <c r="AT232" s="2" t="n"/>
-      <c r="AU232" s="2" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n"/>
@@ -12094,7 +11857,6 @@
       <c r="AR233" s="2" t="n"/>
       <c r="AS233" s="2" t="n"/>
       <c r="AT233" s="2" t="n"/>
-      <c r="AU233" s="2" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n"/>
@@ -12143,7 +11905,6 @@
       <c r="AR234" s="2" t="n"/>
       <c r="AS234" s="2" t="n"/>
       <c r="AT234" s="2" t="n"/>
-      <c r="AU234" s="2" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n"/>
@@ -12192,7 +11953,6 @@
       <c r="AR235" s="2" t="n"/>
       <c r="AS235" s="2" t="n"/>
       <c r="AT235" s="2" t="n"/>
-      <c r="AU235" s="2" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n"/>
@@ -12241,7 +12001,6 @@
       <c r="AR236" s="2" t="n"/>
       <c r="AS236" s="2" t="n"/>
       <c r="AT236" s="2" t="n"/>
-      <c r="AU236" s="2" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n"/>
@@ -12290,7 +12049,6 @@
       <c r="AR237" s="2" t="n"/>
       <c r="AS237" s="2" t="n"/>
       <c r="AT237" s="2" t="n"/>
-      <c r="AU237" s="2" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n"/>
@@ -12339,7 +12097,6 @@
       <c r="AR238" s="2" t="n"/>
       <c r="AS238" s="2" t="n"/>
       <c r="AT238" s="2" t="n"/>
-      <c r="AU238" s="2" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n"/>
@@ -12388,7 +12145,6 @@
       <c r="AR239" s="2" t="n"/>
       <c r="AS239" s="2" t="n"/>
       <c r="AT239" s="2" t="n"/>
-      <c r="AU239" s="2" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n"/>
@@ -12437,7 +12193,6 @@
       <c r="AR240" s="2" t="n"/>
       <c r="AS240" s="2" t="n"/>
       <c r="AT240" s="2" t="n"/>
-      <c r="AU240" s="2" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n"/>
@@ -12486,7 +12241,6 @@
       <c r="AR241" s="2" t="n"/>
       <c r="AS241" s="2" t="n"/>
       <c r="AT241" s="2" t="n"/>
-      <c r="AU241" s="2" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n"/>
@@ -12535,7 +12289,6 @@
       <c r="AR242" s="2" t="n"/>
       <c r="AS242" s="2" t="n"/>
       <c r="AT242" s="2" t="n"/>
-      <c r="AU242" s="2" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n"/>
@@ -12584,7 +12337,6 @@
       <c r="AR243" s="2" t="n"/>
       <c r="AS243" s="2" t="n"/>
       <c r="AT243" s="2" t="n"/>
-      <c r="AU243" s="2" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n"/>
@@ -12633,7 +12385,6 @@
       <c r="AR244" s="2" t="n"/>
       <c r="AS244" s="2" t="n"/>
       <c r="AT244" s="2" t="n"/>
-      <c r="AU244" s="2" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n"/>
@@ -12682,7 +12433,6 @@
       <c r="AR245" s="2" t="n"/>
       <c r="AS245" s="2" t="n"/>
       <c r="AT245" s="2" t="n"/>
-      <c r="AU245" s="2" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n"/>
@@ -12731,7 +12481,6 @@
       <c r="AR246" s="2" t="n"/>
       <c r="AS246" s="2" t="n"/>
       <c r="AT246" s="2" t="n"/>
-      <c r="AU246" s="2" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n"/>
@@ -12780,7 +12529,6 @@
       <c r="AR247" s="2" t="n"/>
       <c r="AS247" s="2" t="n"/>
       <c r="AT247" s="2" t="n"/>
-      <c r="AU247" s="2" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n"/>
@@ -12829,7 +12577,6 @@
       <c r="AR248" s="2" t="n"/>
       <c r="AS248" s="2" t="n"/>
       <c r="AT248" s="2" t="n"/>
-      <c r="AU248" s="2" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n"/>
@@ -12878,7 +12625,6 @@
       <c r="AR249" s="2" t="n"/>
       <c r="AS249" s="2" t="n"/>
       <c r="AT249" s="2" t="n"/>
-      <c r="AU249" s="2" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n"/>
@@ -12927,7 +12673,6 @@
       <c r="AR250" s="2" t="n"/>
       <c r="AS250" s="2" t="n"/>
       <c r="AT250" s="2" t="n"/>
-      <c r="AU250" s="2" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n"/>
@@ -12976,7 +12721,6 @@
       <c r="AR251" s="2" t="n"/>
       <c r="AS251" s="2" t="n"/>
       <c r="AT251" s="2" t="n"/>
-      <c r="AU251" s="2" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n"/>
@@ -13025,7 +12769,6 @@
       <c r="AR252" s="2" t="n"/>
       <c r="AS252" s="2" t="n"/>
       <c r="AT252" s="2" t="n"/>
-      <c r="AU252" s="2" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n"/>
@@ -13074,7 +12817,6 @@
       <c r="AR253" s="2" t="n"/>
       <c r="AS253" s="2" t="n"/>
       <c r="AT253" s="2" t="n"/>
-      <c r="AU253" s="2" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n"/>
@@ -13123,7 +12865,6 @@
       <c r="AR254" s="2" t="n"/>
       <c r="AS254" s="2" t="n"/>
       <c r="AT254" s="2" t="n"/>
-      <c r="AU254" s="2" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n"/>
@@ -13172,7 +12913,6 @@
       <c r="AR255" s="2" t="n"/>
       <c r="AS255" s="2" t="n"/>
       <c r="AT255" s="2" t="n"/>
-      <c r="AU255" s="2" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n"/>
@@ -13221,7 +12961,6 @@
       <c r="AR256" s="2" t="n"/>
       <c r="AS256" s="2" t="n"/>
       <c r="AT256" s="2" t="n"/>
-      <c r="AU256" s="2" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n"/>
@@ -13270,7 +13009,6 @@
       <c r="AR257" s="2" t="n"/>
       <c r="AS257" s="2" t="n"/>
       <c r="AT257" s="2" t="n"/>
-      <c r="AU257" s="2" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n"/>
@@ -13319,7 +13057,6 @@
       <c r="AR258" s="2" t="n"/>
       <c r="AS258" s="2" t="n"/>
       <c r="AT258" s="2" t="n"/>
-      <c r="AU258" s="2" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n"/>
@@ -13368,7 +13105,6 @@
       <c r="AR259" s="2" t="n"/>
       <c r="AS259" s="2" t="n"/>
       <c r="AT259" s="2" t="n"/>
-      <c r="AU259" s="2" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n"/>
@@ -13417,7 +13153,6 @@
       <c r="AR260" s="2" t="n"/>
       <c r="AS260" s="2" t="n"/>
       <c r="AT260" s="2" t="n"/>
-      <c r="AU260" s="2" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n"/>
@@ -13466,7 +13201,6 @@
       <c r="AR261" s="2" t="n"/>
       <c r="AS261" s="2" t="n"/>
       <c r="AT261" s="2" t="n"/>
-      <c r="AU261" s="2" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n"/>
@@ -13515,7 +13249,6 @@
       <c r="AR262" s="2" t="n"/>
       <c r="AS262" s="2" t="n"/>
       <c r="AT262" s="2" t="n"/>
-      <c r="AU262" s="2" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n"/>
@@ -13564,7 +13297,6 @@
       <c r="AR263" s="2" t="n"/>
       <c r="AS263" s="2" t="n"/>
       <c r="AT263" s="2" t="n"/>
-      <c r="AU263" s="2" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n"/>
@@ -13613,7 +13345,6 @@
       <c r="AR264" s="2" t="n"/>
       <c r="AS264" s="2" t="n"/>
       <c r="AT264" s="2" t="n"/>
-      <c r="AU264" s="2" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n"/>
@@ -13662,7 +13393,6 @@
       <c r="AR265" s="2" t="n"/>
       <c r="AS265" s="2" t="n"/>
       <c r="AT265" s="2" t="n"/>
-      <c r="AU265" s="2" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n"/>
@@ -13711,7 +13441,6 @@
       <c r="AR266" s="2" t="n"/>
       <c r="AS266" s="2" t="n"/>
       <c r="AT266" s="2" t="n"/>
-      <c r="AU266" s="2" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n"/>
@@ -13760,7 +13489,6 @@
       <c r="AR267" s="2" t="n"/>
       <c r="AS267" s="2" t="n"/>
       <c r="AT267" s="2" t="n"/>
-      <c r="AU267" s="2" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n"/>
@@ -13809,7 +13537,6 @@
       <c r="AR268" s="2" t="n"/>
       <c r="AS268" s="2" t="n"/>
       <c r="AT268" s="2" t="n"/>
-      <c r="AU268" s="2" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n"/>
@@ -13858,7 +13585,6 @@
       <c r="AR269" s="2" t="n"/>
       <c r="AS269" s="2" t="n"/>
       <c r="AT269" s="2" t="n"/>
-      <c r="AU269" s="2" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n"/>
@@ -13907,7 +13633,6 @@
       <c r="AR270" s="2" t="n"/>
       <c r="AS270" s="2" t="n"/>
       <c r="AT270" s="2" t="n"/>
-      <c r="AU270" s="2" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n"/>
@@ -13956,7 +13681,6 @@
       <c r="AR271" s="2" t="n"/>
       <c r="AS271" s="2" t="n"/>
       <c r="AT271" s="2" t="n"/>
-      <c r="AU271" s="2" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n"/>
@@ -14005,7 +13729,6 @@
       <c r="AR272" s="2" t="n"/>
       <c r="AS272" s="2" t="n"/>
       <c r="AT272" s="2" t="n"/>
-      <c r="AU272" s="2" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n"/>
@@ -14054,7 +13777,6 @@
       <c r="AR273" s="2" t="n"/>
       <c r="AS273" s="2" t="n"/>
       <c r="AT273" s="2" t="n"/>
-      <c r="AU273" s="2" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n"/>
@@ -14103,7 +13825,6 @@
       <c r="AR274" s="2" t="n"/>
       <c r="AS274" s="2" t="n"/>
       <c r="AT274" s="2" t="n"/>
-      <c r="AU274" s="2" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n"/>
@@ -14152,7 +13873,6 @@
       <c r="AR275" s="2" t="n"/>
       <c r="AS275" s="2" t="n"/>
       <c r="AT275" s="2" t="n"/>
-      <c r="AU275" s="2" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n"/>
@@ -14201,7 +13921,6 @@
       <c r="AR276" s="2" t="n"/>
       <c r="AS276" s="2" t="n"/>
       <c r="AT276" s="2" t="n"/>
-      <c r="AU276" s="2" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n"/>
@@ -14250,7 +13969,6 @@
       <c r="AR277" s="2" t="n"/>
       <c r="AS277" s="2" t="n"/>
       <c r="AT277" s="2" t="n"/>
-      <c r="AU277" s="2" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n"/>
@@ -14299,7 +14017,6 @@
       <c r="AR278" s="2" t="n"/>
       <c r="AS278" s="2" t="n"/>
       <c r="AT278" s="2" t="n"/>
-      <c r="AU278" s="2" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n"/>
@@ -14348,7 +14065,6 @@
       <c r="AR279" s="2" t="n"/>
       <c r="AS279" s="2" t="n"/>
       <c r="AT279" s="2" t="n"/>
-      <c r="AU279" s="2" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n"/>
@@ -14397,7 +14113,6 @@
       <c r="AR280" s="2" t="n"/>
       <c r="AS280" s="2" t="n"/>
       <c r="AT280" s="2" t="n"/>
-      <c r="AU280" s="2" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n"/>
@@ -14446,7 +14161,6 @@
       <c r="AR281" s="2" t="n"/>
       <c r="AS281" s="2" t="n"/>
       <c r="AT281" s="2" t="n"/>
-      <c r="AU281" s="2" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n"/>
@@ -14495,7 +14209,6 @@
       <c r="AR282" s="2" t="n"/>
       <c r="AS282" s="2" t="n"/>
       <c r="AT282" s="2" t="n"/>
-      <c r="AU282" s="2" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n"/>
@@ -14544,7 +14257,6 @@
       <c r="AR283" s="2" t="n"/>
       <c r="AS283" s="2" t="n"/>
       <c r="AT283" s="2" t="n"/>
-      <c r="AU283" s="2" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n"/>
@@ -14593,7 +14305,6 @@
       <c r="AR284" s="2" t="n"/>
       <c r="AS284" s="2" t="n"/>
       <c r="AT284" s="2" t="n"/>
-      <c r="AU284" s="2" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n"/>
@@ -14642,7 +14353,6 @@
       <c r="AR285" s="2" t="n"/>
       <c r="AS285" s="2" t="n"/>
       <c r="AT285" s="2" t="n"/>
-      <c r="AU285" s="2" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n"/>
@@ -14691,7 +14401,6 @@
       <c r="AR286" s="2" t="n"/>
       <c r="AS286" s="2" t="n"/>
       <c r="AT286" s="2" t="n"/>
-      <c r="AU286" s="2" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n"/>
@@ -14740,7 +14449,6 @@
       <c r="AR287" s="2" t="n"/>
       <c r="AS287" s="2" t="n"/>
       <c r="AT287" s="2" t="n"/>
-      <c r="AU287" s="2" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n"/>
@@ -14789,7 +14497,6 @@
       <c r="AR288" s="2" t="n"/>
       <c r="AS288" s="2" t="n"/>
       <c r="AT288" s="2" t="n"/>
-      <c r="AU288" s="2" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n"/>
@@ -14838,7 +14545,6 @@
       <c r="AR289" s="2" t="n"/>
       <c r="AS289" s="2" t="n"/>
       <c r="AT289" s="2" t="n"/>
-      <c r="AU289" s="2" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n"/>
@@ -14887,7 +14593,6 @@
       <c r="AR290" s="2" t="n"/>
       <c r="AS290" s="2" t="n"/>
       <c r="AT290" s="2" t="n"/>
-      <c r="AU290" s="2" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n"/>
@@ -14936,7 +14641,6 @@
       <c r="AR291" s="2" t="n"/>
       <c r="AS291" s="2" t="n"/>
       <c r="AT291" s="2" t="n"/>
-      <c r="AU291" s="2" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n"/>
@@ -14985,7 +14689,6 @@
       <c r="AR292" s="2" t="n"/>
       <c r="AS292" s="2" t="n"/>
       <c r="AT292" s="2" t="n"/>
-      <c r="AU292" s="2" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n"/>
@@ -15034,7 +14737,6 @@
       <c r="AR293" s="2" t="n"/>
       <c r="AS293" s="2" t="n"/>
       <c r="AT293" s="2" t="n"/>
-      <c r="AU293" s="2" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n"/>
@@ -15083,7 +14785,6 @@
       <c r="AR294" s="2" t="n"/>
       <c r="AS294" s="2" t="n"/>
       <c r="AT294" s="2" t="n"/>
-      <c r="AU294" s="2" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n"/>
@@ -15132,7 +14833,6 @@
       <c r="AR295" s="2" t="n"/>
       <c r="AS295" s="2" t="n"/>
       <c r="AT295" s="2" t="n"/>
-      <c r="AU295" s="2" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n"/>
@@ -15181,7 +14881,6 @@
       <c r="AR296" s="2" t="n"/>
       <c r="AS296" s="2" t="n"/>
       <c r="AT296" s="2" t="n"/>
-      <c r="AU296" s="2" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n"/>
@@ -15230,7 +14929,6 @@
       <c r="AR297" s="2" t="n"/>
       <c r="AS297" s="2" t="n"/>
       <c r="AT297" s="2" t="n"/>
-      <c r="AU297" s="2" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n"/>
@@ -15279,7 +14977,6 @@
       <c r="AR298" s="2" t="n"/>
       <c r="AS298" s="2" t="n"/>
       <c r="AT298" s="2" t="n"/>
-      <c r="AU298" s="2" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n"/>
@@ -15328,7 +15025,6 @@
       <c r="AR299" s="2" t="n"/>
       <c r="AS299" s="2" t="n"/>
       <c r="AT299" s="2" t="n"/>
-      <c r="AU299" s="2" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n"/>
@@ -15377,7 +15073,6 @@
       <c r="AR300" s="2" t="n"/>
       <c r="AS300" s="2" t="n"/>
       <c r="AT300" s="2" t="n"/>
-      <c r="AU300" s="2" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n"/>
@@ -15426,7 +15121,6 @@
       <c r="AR301" s="2" t="n"/>
       <c r="AS301" s="2" t="n"/>
       <c r="AT301" s="2" t="n"/>
-      <c r="AU301" s="2" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="n"/>
@@ -15475,7 +15169,6 @@
       <c r="AR302" s="2" t="n"/>
       <c r="AS302" s="2" t="n"/>
       <c r="AT302" s="2" t="n"/>
-      <c r="AU302" s="2" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="2" t="n"/>
@@ -15524,7 +15217,6 @@
       <c r="AR303" s="2" t="n"/>
       <c r="AS303" s="2" t="n"/>
       <c r="AT303" s="2" t="n"/>
-      <c r="AU303" s="2" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="n"/>
@@ -15573,7 +15265,6 @@
       <c r="AR304" s="2" t="n"/>
       <c r="AS304" s="2" t="n"/>
       <c r="AT304" s="2" t="n"/>
-      <c r="AU304" s="2" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="n"/>
@@ -15622,7 +15313,6 @@
       <c r="AR305" s="2" t="n"/>
       <c r="AS305" s="2" t="n"/>
       <c r="AT305" s="2" t="n"/>
-      <c r="AU305" s="2" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="n"/>
@@ -15671,7 +15361,6 @@
       <c r="AR306" s="2" t="n"/>
       <c r="AS306" s="2" t="n"/>
       <c r="AT306" s="2" t="n"/>
-      <c r="AU306" s="2" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="2" t="n"/>
@@ -15720,7 +15409,6 @@
       <c r="AR307" s="2" t="n"/>
       <c r="AS307" s="2" t="n"/>
       <c r="AT307" s="2" t="n"/>
-      <c r="AU307" s="2" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="n"/>
@@ -15769,7 +15457,6 @@
       <c r="AR308" s="2" t="n"/>
       <c r="AS308" s="2" t="n"/>
       <c r="AT308" s="2" t="n"/>
-      <c r="AU308" s="2" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="n"/>
@@ -15818,7 +15505,6 @@
       <c r="AR309" s="2" t="n"/>
       <c r="AS309" s="2" t="n"/>
       <c r="AT309" s="2" t="n"/>
-      <c r="AU309" s="2" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="n"/>
@@ -15867,7 +15553,6 @@
       <c r="AR310" s="2" t="n"/>
       <c r="AS310" s="2" t="n"/>
       <c r="AT310" s="2" t="n"/>
-      <c r="AU310" s="2" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="2" t="n"/>
@@ -15916,7 +15601,6 @@
       <c r="AR311" s="2" t="n"/>
       <c r="AS311" s="2" t="n"/>
       <c r="AT311" s="2" t="n"/>
-      <c r="AU311" s="2" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="n"/>
@@ -15965,7 +15649,6 @@
       <c r="AR312" s="2" t="n"/>
       <c r="AS312" s="2" t="n"/>
       <c r="AT312" s="2" t="n"/>
-      <c r="AU312" s="2" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="2" t="n"/>
@@ -16014,7 +15697,6 @@
       <c r="AR313" s="2" t="n"/>
       <c r="AS313" s="2" t="n"/>
       <c r="AT313" s="2" t="n"/>
-      <c r="AU313" s="2" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="n"/>
@@ -16063,7 +15745,6 @@
       <c r="AR314" s="2" t="n"/>
       <c r="AS314" s="2" t="n"/>
       <c r="AT314" s="2" t="n"/>
-      <c r="AU314" s="2" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="n"/>
@@ -16112,7 +15793,6 @@
       <c r="AR315" s="2" t="n"/>
       <c r="AS315" s="2" t="n"/>
       <c r="AT315" s="2" t="n"/>
-      <c r="AU315" s="2" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="n"/>
@@ -16161,7 +15841,6 @@
       <c r="AR316" s="2" t="n"/>
       <c r="AS316" s="2" t="n"/>
       <c r="AT316" s="2" t="n"/>
-      <c r="AU316" s="2" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="2" t="n"/>
@@ -16210,7 +15889,6 @@
       <c r="AR317" s="2" t="n"/>
       <c r="AS317" s="2" t="n"/>
       <c r="AT317" s="2" t="n"/>
-      <c r="AU317" s="2" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="n"/>
@@ -16259,7 +15937,6 @@
       <c r="AR318" s="2" t="n"/>
       <c r="AS318" s="2" t="n"/>
       <c r="AT318" s="2" t="n"/>
-      <c r="AU318" s="2" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="n"/>
@@ -16308,7 +15985,6 @@
       <c r="AR319" s="2" t="n"/>
       <c r="AS319" s="2" t="n"/>
       <c r="AT319" s="2" t="n"/>
-      <c r="AU319" s="2" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="n"/>
@@ -16357,7 +16033,6 @@
       <c r="AR320" s="2" t="n"/>
       <c r="AS320" s="2" t="n"/>
       <c r="AT320" s="2" t="n"/>
-      <c r="AU320" s="2" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="2" t="n"/>
@@ -16406,7 +16081,6 @@
       <c r="AR321" s="2" t="n"/>
       <c r="AS321" s="2" t="n"/>
       <c r="AT321" s="2" t="n"/>
-      <c r="AU321" s="2" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="2" t="n"/>
@@ -16455,7 +16129,6 @@
       <c r="AR322" s="2" t="n"/>
       <c r="AS322" s="2" t="n"/>
       <c r="AT322" s="2" t="n"/>
-      <c r="AU322" s="2" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="2" t="n"/>
@@ -16504,7 +16177,6 @@
       <c r="AR323" s="2" t="n"/>
       <c r="AS323" s="2" t="n"/>
       <c r="AT323" s="2" t="n"/>
-      <c r="AU323" s="2" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="n"/>
@@ -16553,7 +16225,6 @@
       <c r="AR324" s="2" t="n"/>
       <c r="AS324" s="2" t="n"/>
       <c r="AT324" s="2" t="n"/>
-      <c r="AU324" s="2" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="2" t="n"/>
@@ -16602,7 +16273,6 @@
       <c r="AR325" s="2" t="n"/>
       <c r="AS325" s="2" t="n"/>
       <c r="AT325" s="2" t="n"/>
-      <c r="AU325" s="2" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="n"/>
@@ -16651,7 +16321,6 @@
       <c r="AR326" s="2" t="n"/>
       <c r="AS326" s="2" t="n"/>
       <c r="AT326" s="2" t="n"/>
-      <c r="AU326" s="2" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="n"/>
@@ -16700,7 +16369,6 @@
       <c r="AR327" s="2" t="n"/>
       <c r="AS327" s="2" t="n"/>
       <c r="AT327" s="2" t="n"/>
-      <c r="AU327" s="2" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="n"/>
@@ -16749,7 +16417,6 @@
       <c r="AR328" s="2" t="n"/>
       <c r="AS328" s="2" t="n"/>
       <c r="AT328" s="2" t="n"/>
-      <c r="AU328" s="2" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="2" t="n"/>
@@ -16798,7 +16465,6 @@
       <c r="AR329" s="2" t="n"/>
       <c r="AS329" s="2" t="n"/>
       <c r="AT329" s="2" t="n"/>
-      <c r="AU329" s="2" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="n"/>
@@ -16847,7 +16513,6 @@
       <c r="AR330" s="2" t="n"/>
       <c r="AS330" s="2" t="n"/>
       <c r="AT330" s="2" t="n"/>
-      <c r="AU330" s="2" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="2" t="n"/>
@@ -16896,7 +16561,6 @@
       <c r="AR331" s="2" t="n"/>
       <c r="AS331" s="2" t="n"/>
       <c r="AT331" s="2" t="n"/>
-      <c r="AU331" s="2" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="n"/>
@@ -16945,7 +16609,6 @@
       <c r="AR332" s="2" t="n"/>
       <c r="AS332" s="2" t="n"/>
       <c r="AT332" s="2" t="n"/>
-      <c r="AU332" s="2" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="2" t="n"/>
@@ -16994,7 +16657,6 @@
       <c r="AR333" s="2" t="n"/>
       <c r="AS333" s="2" t="n"/>
       <c r="AT333" s="2" t="n"/>
-      <c r="AU333" s="2" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="2" t="n"/>
@@ -17043,7 +16705,6 @@
       <c r="AR334" s="2" t="n"/>
       <c r="AS334" s="2" t="n"/>
       <c r="AT334" s="2" t="n"/>
-      <c r="AU334" s="2" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="2" t="n"/>
@@ -17092,7 +16753,6 @@
       <c r="AR335" s="2" t="n"/>
       <c r="AS335" s="2" t="n"/>
       <c r="AT335" s="2" t="n"/>
-      <c r="AU335" s="2" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="n"/>
@@ -17141,7 +16801,6 @@
       <c r="AR336" s="2" t="n"/>
       <c r="AS336" s="2" t="n"/>
       <c r="AT336" s="2" t="n"/>
-      <c r="AU336" s="2" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="2" t="n"/>
@@ -17190,7 +16849,6 @@
       <c r="AR337" s="2" t="n"/>
       <c r="AS337" s="2" t="n"/>
       <c r="AT337" s="2" t="n"/>
-      <c r="AU337" s="2" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="n"/>
@@ -17239,7 +16897,6 @@
       <c r="AR338" s="2" t="n"/>
       <c r="AS338" s="2" t="n"/>
       <c r="AT338" s="2" t="n"/>
-      <c r="AU338" s="2" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="2" t="n"/>
@@ -17288,7 +16945,6 @@
       <c r="AR339" s="2" t="n"/>
       <c r="AS339" s="2" t="n"/>
       <c r="AT339" s="2" t="n"/>
-      <c r="AU339" s="2" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="n"/>
@@ -17337,7 +16993,6 @@
       <c r="AR340" s="2" t="n"/>
       <c r="AS340" s="2" t="n"/>
       <c r="AT340" s="2" t="n"/>
-      <c r="AU340" s="2" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="2" t="n"/>
@@ -17386,7 +17041,6 @@
       <c r="AR341" s="2" t="n"/>
       <c r="AS341" s="2" t="n"/>
       <c r="AT341" s="2" t="n"/>
-      <c r="AU341" s="2" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="n"/>
@@ -17435,7 +17089,6 @@
       <c r="AR342" s="2" t="n"/>
       <c r="AS342" s="2" t="n"/>
       <c r="AT342" s="2" t="n"/>
-      <c r="AU342" s="2" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="2" t="n"/>
@@ -17484,7 +17137,6 @@
       <c r="AR343" s="2" t="n"/>
       <c r="AS343" s="2" t="n"/>
       <c r="AT343" s="2" t="n"/>
-      <c r="AU343" s="2" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="n"/>
@@ -17533,7 +17185,6 @@
       <c r="AR344" s="2" t="n"/>
       <c r="AS344" s="2" t="n"/>
       <c r="AT344" s="2" t="n"/>
-      <c r="AU344" s="2" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="2" t="n"/>
@@ -17582,7 +17233,6 @@
       <c r="AR345" s="2" t="n"/>
       <c r="AS345" s="2" t="n"/>
       <c r="AT345" s="2" t="n"/>
-      <c r="AU345" s="2" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="n"/>
@@ -17631,7 +17281,6 @@
       <c r="AR346" s="2" t="n"/>
       <c r="AS346" s="2" t="n"/>
       <c r="AT346" s="2" t="n"/>
-      <c r="AU346" s="2" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="n"/>
@@ -17680,7 +17329,6 @@
       <c r="AR347" s="2" t="n"/>
       <c r="AS347" s="2" t="n"/>
       <c r="AT347" s="2" t="n"/>
-      <c r="AU347" s="2" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="n"/>
@@ -17729,7 +17377,6 @@
       <c r="AR348" s="2" t="n"/>
       <c r="AS348" s="2" t="n"/>
       <c r="AT348" s="2" t="n"/>
-      <c r="AU348" s="2" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="2" t="n"/>
@@ -17778,7 +17425,6 @@
       <c r="AR349" s="2" t="n"/>
       <c r="AS349" s="2" t="n"/>
       <c r="AT349" s="2" t="n"/>
-      <c r="AU349" s="2" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="n"/>
@@ -17827,7 +17473,6 @@
       <c r="AR350" s="2" t="n"/>
       <c r="AS350" s="2" t="n"/>
       <c r="AT350" s="2" t="n"/>
-      <c r="AU350" s="2" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="2" t="n"/>
@@ -17876,7 +17521,6 @@
       <c r="AR351" s="2" t="n"/>
       <c r="AS351" s="2" t="n"/>
       <c r="AT351" s="2" t="n"/>
-      <c r="AU351" s="2" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="n"/>
@@ -17925,7 +17569,6 @@
       <c r="AR352" s="2" t="n"/>
       <c r="AS352" s="2" t="n"/>
       <c r="AT352" s="2" t="n"/>
-      <c r="AU352" s="2" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="2" t="n"/>
@@ -17974,7 +17617,6 @@
       <c r="AR353" s="2" t="n"/>
       <c r="AS353" s="2" t="n"/>
       <c r="AT353" s="2" t="n"/>
-      <c r="AU353" s="2" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="n"/>
@@ -18023,7 +17665,6 @@
       <c r="AR354" s="2" t="n"/>
       <c r="AS354" s="2" t="n"/>
       <c r="AT354" s="2" t="n"/>
-      <c r="AU354" s="2" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="2" t="n"/>
@@ -18072,7 +17713,6 @@
       <c r="AR355" s="2" t="n"/>
       <c r="AS355" s="2" t="n"/>
       <c r="AT355" s="2" t="n"/>
-      <c r="AU355" s="2" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="n"/>
@@ -18121,7 +17761,6 @@
       <c r="AR356" s="2" t="n"/>
       <c r="AS356" s="2" t="n"/>
       <c r="AT356" s="2" t="n"/>
-      <c r="AU356" s="2" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="n"/>
@@ -18170,7 +17809,6 @@
       <c r="AR357" s="2" t="n"/>
       <c r="AS357" s="2" t="n"/>
       <c r="AT357" s="2" t="n"/>
-      <c r="AU357" s="2" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="n"/>
@@ -18219,7 +17857,6 @@
       <c r="AR358" s="2" t="n"/>
       <c r="AS358" s="2" t="n"/>
       <c r="AT358" s="2" t="n"/>
-      <c r="AU358" s="2" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="2" t="n"/>
@@ -18268,7 +17905,6 @@
       <c r="AR359" s="2" t="n"/>
       <c r="AS359" s="2" t="n"/>
       <c r="AT359" s="2" t="n"/>
-      <c r="AU359" s="2" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="n"/>
@@ -18317,7 +17953,6 @@
       <c r="AR360" s="2" t="n"/>
       <c r="AS360" s="2" t="n"/>
       <c r="AT360" s="2" t="n"/>
-      <c r="AU360" s="2" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="2" t="n"/>
@@ -18366,7 +18001,6 @@
       <c r="AR361" s="2" t="n"/>
       <c r="AS361" s="2" t="n"/>
       <c r="AT361" s="2" t="n"/>
-      <c r="AU361" s="2" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="n"/>
@@ -18415,7 +18049,6 @@
       <c r="AR362" s="2" t="n"/>
       <c r="AS362" s="2" t="n"/>
       <c r="AT362" s="2" t="n"/>
-      <c r="AU362" s="2" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="2" t="n"/>
@@ -18464,7 +18097,6 @@
       <c r="AR363" s="2" t="n"/>
       <c r="AS363" s="2" t="n"/>
       <c r="AT363" s="2" t="n"/>
-      <c r="AU363" s="2" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="n"/>
@@ -18513,7 +18145,6 @@
       <c r="AR364" s="2" t="n"/>
       <c r="AS364" s="2" t="n"/>
       <c r="AT364" s="2" t="n"/>
-      <c r="AU364" s="2" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="n"/>
@@ -18562,7 +18193,6 @@
       <c r="AR365" s="2" t="n"/>
       <c r="AS365" s="2" t="n"/>
       <c r="AT365" s="2" t="n"/>
-      <c r="AU365" s="2" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="n"/>
@@ -18611,7 +18241,6 @@
       <c r="AR366" s="2" t="n"/>
       <c r="AS366" s="2" t="n"/>
       <c r="AT366" s="2" t="n"/>
-      <c r="AU366" s="2" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="n"/>
@@ -18660,7 +18289,6 @@
       <c r="AR367" s="2" t="n"/>
       <c r="AS367" s="2" t="n"/>
       <c r="AT367" s="2" t="n"/>
-      <c r="AU367" s="2" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="n"/>
@@ -18709,7 +18337,6 @@
       <c r="AR368" s="2" t="n"/>
       <c r="AS368" s="2" t="n"/>
       <c r="AT368" s="2" t="n"/>
-      <c r="AU368" s="2" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="2" t="n"/>
@@ -18758,7 +18385,6 @@
       <c r="AR369" s="2" t="n"/>
       <c r="AS369" s="2" t="n"/>
       <c r="AT369" s="2" t="n"/>
-      <c r="AU369" s="2" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="n"/>
@@ -18807,7 +18433,6 @@
       <c r="AR370" s="2" t="n"/>
       <c r="AS370" s="2" t="n"/>
       <c r="AT370" s="2" t="n"/>
-      <c r="AU370" s="2" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="n"/>
@@ -18856,7 +18481,6 @@
       <c r="AR371" s="2" t="n"/>
       <c r="AS371" s="2" t="n"/>
       <c r="AT371" s="2" t="n"/>
-      <c r="AU371" s="2" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="n"/>
@@ -18905,7 +18529,6 @@
       <c r="AR372" s="2" t="n"/>
       <c r="AS372" s="2" t="n"/>
       <c r="AT372" s="2" t="n"/>
-      <c r="AU372" s="2" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="2" t="n"/>
@@ -18954,7 +18577,6 @@
       <c r="AR373" s="2" t="n"/>
       <c r="AS373" s="2" t="n"/>
       <c r="AT373" s="2" t="n"/>
-      <c r="AU373" s="2" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="n"/>
@@ -19003,7 +18625,6 @@
       <c r="AR374" s="2" t="n"/>
       <c r="AS374" s="2" t="n"/>
       <c r="AT374" s="2" t="n"/>
-      <c r="AU374" s="2" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="2" t="n"/>
@@ -19052,7 +18673,6 @@
       <c r="AR375" s="2" t="n"/>
       <c r="AS375" s="2" t="n"/>
       <c r="AT375" s="2" t="n"/>
-      <c r="AU375" s="2" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="n"/>
@@ -19101,7 +18721,6 @@
       <c r="AR376" s="2" t="n"/>
       <c r="AS376" s="2" t="n"/>
       <c r="AT376" s="2" t="n"/>
-      <c r="AU376" s="2" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="2" t="n"/>
@@ -19150,7 +18769,6 @@
       <c r="AR377" s="2" t="n"/>
       <c r="AS377" s="2" t="n"/>
       <c r="AT377" s="2" t="n"/>
-      <c r="AU377" s="2" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="n"/>
@@ -19199,7 +18817,6 @@
       <c r="AR378" s="2" t="n"/>
       <c r="AS378" s="2" t="n"/>
       <c r="AT378" s="2" t="n"/>
-      <c r="AU378" s="2" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="2" t="n"/>
@@ -19248,7 +18865,6 @@
       <c r="AR379" s="2" t="n"/>
       <c r="AS379" s="2" t="n"/>
       <c r="AT379" s="2" t="n"/>
-      <c r="AU379" s="2" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="n"/>
@@ -19297,7 +18913,6 @@
       <c r="AR380" s="2" t="n"/>
       <c r="AS380" s="2" t="n"/>
       <c r="AT380" s="2" t="n"/>
-      <c r="AU380" s="2" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="2" t="n"/>
@@ -19346,7 +18961,6 @@
       <c r="AR381" s="2" t="n"/>
       <c r="AS381" s="2" t="n"/>
       <c r="AT381" s="2" t="n"/>
-      <c r="AU381" s="2" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="n"/>
@@ -19395,7 +19009,6 @@
       <c r="AR382" s="2" t="n"/>
       <c r="AS382" s="2" t="n"/>
       <c r="AT382" s="2" t="n"/>
-      <c r="AU382" s="2" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="2" t="n"/>
@@ -19444,7 +19057,6 @@
       <c r="AR383" s="2" t="n"/>
       <c r="AS383" s="2" t="n"/>
       <c r="AT383" s="2" t="n"/>
-      <c r="AU383" s="2" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n"/>
@@ -19493,7 +19105,6 @@
       <c r="AR384" s="2" t="n"/>
       <c r="AS384" s="2" t="n"/>
       <c r="AT384" s="2" t="n"/>
-      <c r="AU384" s="2" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="n"/>
@@ -19542,7 +19153,6 @@
       <c r="AR385" s="2" t="n"/>
       <c r="AS385" s="2" t="n"/>
       <c r="AT385" s="2" t="n"/>
-      <c r="AU385" s="2" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n"/>
@@ -19591,7 +19201,6 @@
       <c r="AR386" s="2" t="n"/>
       <c r="AS386" s="2" t="n"/>
       <c r="AT386" s="2" t="n"/>
-      <c r="AU386" s="2" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="2" t="n"/>
@@ -19640,7 +19249,6 @@
       <c r="AR387" s="2" t="n"/>
       <c r="AS387" s="2" t="n"/>
       <c r="AT387" s="2" t="n"/>
-      <c r="AU387" s="2" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="n"/>
@@ -19689,7 +19297,6 @@
       <c r="AR388" s="2" t="n"/>
       <c r="AS388" s="2" t="n"/>
       <c r="AT388" s="2" t="n"/>
-      <c r="AU388" s="2" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n"/>
@@ -19738,7 +19345,6 @@
       <c r="AR389" s="2" t="n"/>
       <c r="AS389" s="2" t="n"/>
       <c r="AT389" s="2" t="n"/>
-      <c r="AU389" s="2" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n"/>
@@ -19787,7 +19393,6 @@
       <c r="AR390" s="2" t="n"/>
       <c r="AS390" s="2" t="n"/>
       <c r="AT390" s="2" t="n"/>
-      <c r="AU390" s="2" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n"/>
@@ -19836,7 +19441,6 @@
       <c r="AR391" s="2" t="n"/>
       <c r="AS391" s="2" t="n"/>
       <c r="AT391" s="2" t="n"/>
-      <c r="AU391" s="2" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n"/>
@@ -19885,7 +19489,6 @@
       <c r="AR392" s="2" t="n"/>
       <c r="AS392" s="2" t="n"/>
       <c r="AT392" s="2" t="n"/>
-      <c r="AU392" s="2" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n"/>
@@ -19934,7 +19537,6 @@
       <c r="AR393" s="2" t="n"/>
       <c r="AS393" s="2" t="n"/>
       <c r="AT393" s="2" t="n"/>
-      <c r="AU393" s="2" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n"/>
@@ -19983,7 +19585,6 @@
       <c r="AR394" s="2" t="n"/>
       <c r="AS394" s="2" t="n"/>
       <c r="AT394" s="2" t="n"/>
-      <c r="AU394" s="2" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="2" t="n"/>
@@ -20032,7 +19633,6 @@
       <c r="AR395" s="2" t="n"/>
       <c r="AS395" s="2" t="n"/>
       <c r="AT395" s="2" t="n"/>
-      <c r="AU395" s="2" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="n"/>
@@ -20081,7 +19681,6 @@
       <c r="AR396" s="2" t="n"/>
       <c r="AS396" s="2" t="n"/>
       <c r="AT396" s="2" t="n"/>
-      <c r="AU396" s="2" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n"/>
@@ -20130,7 +19729,6 @@
       <c r="AR397" s="2" t="n"/>
       <c r="AS397" s="2" t="n"/>
       <c r="AT397" s="2" t="n"/>
-      <c r="AU397" s="2" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n"/>
@@ -20179,7 +19777,6 @@
       <c r="AR398" s="2" t="n"/>
       <c r="AS398" s="2" t="n"/>
       <c r="AT398" s="2" t="n"/>
-      <c r="AU398" s="2" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="2" t="n"/>
@@ -20228,7 +19825,6 @@
       <c r="AR399" s="2" t="n"/>
       <c r="AS399" s="2" t="n"/>
       <c r="AT399" s="2" t="n"/>
-      <c r="AU399" s="2" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n"/>
@@ -20277,7 +19873,6 @@
       <c r="AR400" s="2" t="n"/>
       <c r="AS400" s="2" t="n"/>
       <c r="AT400" s="2" t="n"/>
-      <c r="AU400" s="2" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="2" t="n"/>
@@ -20326,7 +19921,6 @@
       <c r="AR401" s="2" t="n"/>
       <c r="AS401" s="2" t="n"/>
       <c r="AT401" s="2" t="n"/>
-      <c r="AU401" s="2" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n"/>
@@ -20375,7 +19969,6 @@
       <c r="AR402" s="2" t="n"/>
       <c r="AS402" s="2" t="n"/>
       <c r="AT402" s="2" t="n"/>
-      <c r="AU402" s="2" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n"/>
@@ -20424,7 +20017,6 @@
       <c r="AR403" s="2" t="n"/>
       <c r="AS403" s="2" t="n"/>
       <c r="AT403" s="2" t="n"/>
-      <c r="AU403" s="2" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n"/>
@@ -20473,7 +20065,6 @@
       <c r="AR404" s="2" t="n"/>
       <c r="AS404" s="2" t="n"/>
       <c r="AT404" s="2" t="n"/>
-      <c r="AU404" s="2" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n"/>
@@ -20522,7 +20113,6 @@
       <c r="AR405" s="2" t="n"/>
       <c r="AS405" s="2" t="n"/>
       <c r="AT405" s="2" t="n"/>
-      <c r="AU405" s="2" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n"/>
@@ -20571,7 +20161,6 @@
       <c r="AR406" s="2" t="n"/>
       <c r="AS406" s="2" t="n"/>
       <c r="AT406" s="2" t="n"/>
-      <c r="AU406" s="2" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n"/>
@@ -20620,7 +20209,6 @@
       <c r="AR407" s="2" t="n"/>
       <c r="AS407" s="2" t="n"/>
       <c r="AT407" s="2" t="n"/>
-      <c r="AU407" s="2" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n"/>
@@ -20669,7 +20257,6 @@
       <c r="AR408" s="2" t="n"/>
       <c r="AS408" s="2" t="n"/>
       <c r="AT408" s="2" t="n"/>
-      <c r="AU408" s="2" t="n"/>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n"/>
@@ -20718,7 +20305,6 @@
       <c r="AR409" s="2" t="n"/>
       <c r="AS409" s="2" t="n"/>
       <c r="AT409" s="2" t="n"/>
-      <c r="AU409" s="2" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n"/>
@@ -20767,7 +20353,6 @@
       <c r="AR410" s="2" t="n"/>
       <c r="AS410" s="2" t="n"/>
       <c r="AT410" s="2" t="n"/>
-      <c r="AU410" s="2" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n"/>
@@ -20816,7 +20401,6 @@
       <c r="AR411" s="2" t="n"/>
       <c r="AS411" s="2" t="n"/>
       <c r="AT411" s="2" t="n"/>
-      <c r="AU411" s="2" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n"/>
@@ -20865,7 +20449,6 @@
       <c r="AR412" s="2" t="n"/>
       <c r="AS412" s="2" t="n"/>
       <c r="AT412" s="2" t="n"/>
-      <c r="AU412" s="2" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n"/>
@@ -20914,7 +20497,6 @@
       <c r="AR413" s="2" t="n"/>
       <c r="AS413" s="2" t="n"/>
       <c r="AT413" s="2" t="n"/>
-      <c r="AU413" s="2" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n"/>
@@ -20963,7 +20545,6 @@
       <c r="AR414" s="2" t="n"/>
       <c r="AS414" s="2" t="n"/>
       <c r="AT414" s="2" t="n"/>
-      <c r="AU414" s="2" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n"/>
@@ -21012,7 +20593,6 @@
       <c r="AR415" s="2" t="n"/>
       <c r="AS415" s="2" t="n"/>
       <c r="AT415" s="2" t="n"/>
-      <c r="AU415" s="2" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n"/>
@@ -21061,7 +20641,6 @@
       <c r="AR416" s="2" t="n"/>
       <c r="AS416" s="2" t="n"/>
       <c r="AT416" s="2" t="n"/>
-      <c r="AU416" s="2" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n"/>
@@ -21110,7 +20689,6 @@
       <c r="AR417" s="2" t="n"/>
       <c r="AS417" s="2" t="n"/>
       <c r="AT417" s="2" t="n"/>
-      <c r="AU417" s="2" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n"/>
@@ -21159,7 +20737,6 @@
       <c r="AR418" s="2" t="n"/>
       <c r="AS418" s="2" t="n"/>
       <c r="AT418" s="2" t="n"/>
-      <c r="AU418" s="2" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n"/>
@@ -21208,7 +20785,6 @@
       <c r="AR419" s="2" t="n"/>
       <c r="AS419" s="2" t="n"/>
       <c r="AT419" s="2" t="n"/>
-      <c r="AU419" s="2" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n"/>
@@ -21257,7 +20833,6 @@
       <c r="AR420" s="2" t="n"/>
       <c r="AS420" s="2" t="n"/>
       <c r="AT420" s="2" t="n"/>
-      <c r="AU420" s="2" t="n"/>
     </row>
     <row r="421">
       <c r="A421" s="2" t="n"/>
@@ -21306,7 +20881,6 @@
       <c r="AR421" s="2" t="n"/>
       <c r="AS421" s="2" t="n"/>
       <c r="AT421" s="2" t="n"/>
-      <c r="AU421" s="2" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n"/>
@@ -21355,7 +20929,6 @@
       <c r="AR422" s="2" t="n"/>
       <c r="AS422" s="2" t="n"/>
       <c r="AT422" s="2" t="n"/>
-      <c r="AU422" s="2" t="n"/>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n"/>
@@ -21404,7 +20977,6 @@
       <c r="AR423" s="2" t="n"/>
       <c r="AS423" s="2" t="n"/>
       <c r="AT423" s="2" t="n"/>
-      <c r="AU423" s="2" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n"/>
@@ -21453,7 +21025,6 @@
       <c r="AR424" s="2" t="n"/>
       <c r="AS424" s="2" t="n"/>
       <c r="AT424" s="2" t="n"/>
-      <c r="AU424" s="2" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="2" t="n"/>
@@ -21502,7 +21073,6 @@
       <c r="AR425" s="2" t="n"/>
       <c r="AS425" s="2" t="n"/>
       <c r="AT425" s="2" t="n"/>
-      <c r="AU425" s="2" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n"/>
@@ -21551,7 +21121,6 @@
       <c r="AR426" s="2" t="n"/>
       <c r="AS426" s="2" t="n"/>
       <c r="AT426" s="2" t="n"/>
-      <c r="AU426" s="2" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n"/>
@@ -21600,7 +21169,6 @@
       <c r="AR427" s="2" t="n"/>
       <c r="AS427" s="2" t="n"/>
       <c r="AT427" s="2" t="n"/>
-      <c r="AU427" s="2" t="n"/>
     </row>
     <row r="428">
       <c r="A428" s="2" t="n"/>
@@ -21649,7 +21217,6 @@
       <c r="AR428" s="2" t="n"/>
       <c r="AS428" s="2" t="n"/>
       <c r="AT428" s="2" t="n"/>
-      <c r="AU428" s="2" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="2" t="n"/>
@@ -21698,7 +21265,6 @@
       <c r="AR429" s="2" t="n"/>
       <c r="AS429" s="2" t="n"/>
       <c r="AT429" s="2" t="n"/>
-      <c r="AU429" s="2" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n"/>
@@ -21747,7 +21313,6 @@
       <c r="AR430" s="2" t="n"/>
       <c r="AS430" s="2" t="n"/>
       <c r="AT430" s="2" t="n"/>
-      <c r="AU430" s="2" t="n"/>
     </row>
     <row r="431">
       <c r="A431" s="2" t="n"/>
@@ -21796,7 +21361,6 @@
       <c r="AR431" s="2" t="n"/>
       <c r="AS431" s="2" t="n"/>
       <c r="AT431" s="2" t="n"/>
-      <c r="AU431" s="2" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="2" t="n"/>
@@ -21845,7 +21409,6 @@
       <c r="AR432" s="2" t="n"/>
       <c r="AS432" s="2" t="n"/>
       <c r="AT432" s="2" t="n"/>
-      <c r="AU432" s="2" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="2" t="n"/>
@@ -21894,7 +21457,6 @@
       <c r="AR433" s="2" t="n"/>
       <c r="AS433" s="2" t="n"/>
       <c r="AT433" s="2" t="n"/>
-      <c r="AU433" s="2" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="2" t="n"/>
@@ -21943,7 +21505,6 @@
       <c r="AR434" s="2" t="n"/>
       <c r="AS434" s="2" t="n"/>
       <c r="AT434" s="2" t="n"/>
-      <c r="AU434" s="2" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="2" t="n"/>
@@ -21992,7 +21553,6 @@
       <c r="AR435" s="2" t="n"/>
       <c r="AS435" s="2" t="n"/>
       <c r="AT435" s="2" t="n"/>
-      <c r="AU435" s="2" t="n"/>
     </row>
     <row r="436">
       <c r="A436" s="2" t="n"/>
@@ -22041,7 +21601,6 @@
       <c r="AR436" s="2" t="n"/>
       <c r="AS436" s="2" t="n"/>
       <c r="AT436" s="2" t="n"/>
-      <c r="AU436" s="2" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="2" t="n"/>
@@ -22090,7 +21649,6 @@
       <c r="AR437" s="2" t="n"/>
       <c r="AS437" s="2" t="n"/>
       <c r="AT437" s="2" t="n"/>
-      <c r="AU437" s="2" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="2" t="n"/>
@@ -22139,7 +21697,6 @@
       <c r="AR438" s="2" t="n"/>
       <c r="AS438" s="2" t="n"/>
       <c r="AT438" s="2" t="n"/>
-      <c r="AU438" s="2" t="n"/>
     </row>
     <row r="439">
       <c r="A439" s="2" t="n"/>
@@ -22188,7 +21745,6 @@
       <c r="AR439" s="2" t="n"/>
       <c r="AS439" s="2" t="n"/>
       <c r="AT439" s="2" t="n"/>
-      <c r="AU439" s="2" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="n"/>
@@ -22237,7 +21793,6 @@
       <c r="AR440" s="2" t="n"/>
       <c r="AS440" s="2" t="n"/>
       <c r="AT440" s="2" t="n"/>
-      <c r="AU440" s="2" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="2" t="n"/>
@@ -22286,7 +21841,6 @@
       <c r="AR441" s="2" t="n"/>
       <c r="AS441" s="2" t="n"/>
       <c r="AT441" s="2" t="n"/>
-      <c r="AU441" s="2" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n"/>
@@ -22335,7 +21889,6 @@
       <c r="AR442" s="2" t="n"/>
       <c r="AS442" s="2" t="n"/>
       <c r="AT442" s="2" t="n"/>
-      <c r="AU442" s="2" t="n"/>
     </row>
     <row r="443">
       <c r="A443" s="2" t="n"/>
@@ -22384,7 +21937,6 @@
       <c r="AR443" s="2" t="n"/>
       <c r="AS443" s="2" t="n"/>
       <c r="AT443" s="2" t="n"/>
-      <c r="AU443" s="2" t="n"/>
     </row>
     <row r="444">
       <c r="A444" s="2" t="n"/>
@@ -22433,7 +21985,6 @@
       <c r="AR444" s="2" t="n"/>
       <c r="AS444" s="2" t="n"/>
       <c r="AT444" s="2" t="n"/>
-      <c r="AU444" s="2" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="2" t="n"/>
@@ -22482,7 +22033,6 @@
       <c r="AR445" s="2" t="n"/>
       <c r="AS445" s="2" t="n"/>
       <c r="AT445" s="2" t="n"/>
-      <c r="AU445" s="2" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="2" t="n"/>
@@ -22531,7 +22081,6 @@
       <c r="AR446" s="2" t="n"/>
       <c r="AS446" s="2" t="n"/>
       <c r="AT446" s="2" t="n"/>
-      <c r="AU446" s="2" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="2" t="n"/>
@@ -22580,7 +22129,6 @@
       <c r="AR447" s="2" t="n"/>
       <c r="AS447" s="2" t="n"/>
       <c r="AT447" s="2" t="n"/>
-      <c r="AU447" s="2" t="n"/>
     </row>
     <row r="448">
       <c r="A448" s="2" t="n"/>
@@ -22629,7 +22177,6 @@
       <c r="AR448" s="2" t="n"/>
       <c r="AS448" s="2" t="n"/>
       <c r="AT448" s="2" t="n"/>
-      <c r="AU448" s="2" t="n"/>
     </row>
     <row r="449">
       <c r="A449" s="2" t="n"/>
@@ -22678,7 +22225,6 @@
       <c r="AR449" s="2" t="n"/>
       <c r="AS449" s="2" t="n"/>
       <c r="AT449" s="2" t="n"/>
-      <c r="AU449" s="2" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="n"/>
@@ -22727,7 +22273,6 @@
       <c r="AR450" s="2" t="n"/>
       <c r="AS450" s="2" t="n"/>
       <c r="AT450" s="2" t="n"/>
-      <c r="AU450" s="2" t="n"/>
     </row>
     <row r="451">
       <c r="A451" s="2" t="n"/>
@@ -22776,7 +22321,6 @@
       <c r="AR451" s="2" t="n"/>
       <c r="AS451" s="2" t="n"/>
       <c r="AT451" s="2" t="n"/>
-      <c r="AU451" s="2" t="n"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="n"/>
@@ -22825,7 +22369,6 @@
       <c r="AR452" s="2" t="n"/>
       <c r="AS452" s="2" t="n"/>
       <c r="AT452" s="2" t="n"/>
-      <c r="AU452" s="2" t="n"/>
     </row>
     <row r="453">
       <c r="A453" s="2" t="n"/>
@@ -22874,7 +22417,6 @@
       <c r="AR453" s="2" t="n"/>
       <c r="AS453" s="2" t="n"/>
       <c r="AT453" s="2" t="n"/>
-      <c r="AU453" s="2" t="n"/>
     </row>
     <row r="454">
       <c r="A454" s="2" t="n"/>
@@ -22923,7 +22465,6 @@
       <c r="AR454" s="2" t="n"/>
       <c r="AS454" s="2" t="n"/>
       <c r="AT454" s="2" t="n"/>
-      <c r="AU454" s="2" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="2" t="n"/>
@@ -22972,7 +22513,6 @@
       <c r="AR455" s="2" t="n"/>
       <c r="AS455" s="2" t="n"/>
       <c r="AT455" s="2" t="n"/>
-      <c r="AU455" s="2" t="n"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="n"/>
@@ -23021,7 +22561,6 @@
       <c r="AR456" s="2" t="n"/>
       <c r="AS456" s="2" t="n"/>
       <c r="AT456" s="2" t="n"/>
-      <c r="AU456" s="2" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="2" t="n"/>
@@ -23070,7 +22609,6 @@
       <c r="AR457" s="2" t="n"/>
       <c r="AS457" s="2" t="n"/>
       <c r="AT457" s="2" t="n"/>
-      <c r="AU457" s="2" t="n"/>
     </row>
     <row r="458">
       <c r="A458" s="2" t="n"/>
@@ -23119,7 +22657,6 @@
       <c r="AR458" s="2" t="n"/>
       <c r="AS458" s="2" t="n"/>
       <c r="AT458" s="2" t="n"/>
-      <c r="AU458" s="2" t="n"/>
     </row>
     <row r="459">
       <c r="A459" s="2" t="n"/>
@@ -23168,7 +22705,6 @@
       <c r="AR459" s="2" t="n"/>
       <c r="AS459" s="2" t="n"/>
       <c r="AT459" s="2" t="n"/>
-      <c r="AU459" s="2" t="n"/>
     </row>
     <row r="460">
       <c r="A460" s="2" t="n"/>
@@ -23217,7 +22753,6 @@
       <c r="AR460" s="2" t="n"/>
       <c r="AS460" s="2" t="n"/>
       <c r="AT460" s="2" t="n"/>
-      <c r="AU460" s="2" t="n"/>
     </row>
     <row r="461">
       <c r="A461" s="2" t="n"/>
@@ -23266,7 +22801,6 @@
       <c r="AR461" s="2" t="n"/>
       <c r="AS461" s="2" t="n"/>
       <c r="AT461" s="2" t="n"/>
-      <c r="AU461" s="2" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="2" t="n"/>
@@ -23315,7 +22849,6 @@
       <c r="AR462" s="2" t="n"/>
       <c r="AS462" s="2" t="n"/>
       <c r="AT462" s="2" t="n"/>
-      <c r="AU462" s="2" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="2" t="n"/>
@@ -23364,7 +22897,6 @@
       <c r="AR463" s="2" t="n"/>
       <c r="AS463" s="2" t="n"/>
       <c r="AT463" s="2" t="n"/>
-      <c r="AU463" s="2" t="n"/>
     </row>
     <row r="464">
       <c r="A464" s="2" t="n"/>
@@ -23413,7 +22945,6 @@
       <c r="AR464" s="2" t="n"/>
       <c r="AS464" s="2" t="n"/>
       <c r="AT464" s="2" t="n"/>
-      <c r="AU464" s="2" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="2" t="n"/>
@@ -23462,7 +22993,6 @@
       <c r="AR465" s="2" t="n"/>
       <c r="AS465" s="2" t="n"/>
       <c r="AT465" s="2" t="n"/>
-      <c r="AU465" s="2" t="n"/>
     </row>
     <row r="466">
       <c r="A466" s="2" t="n"/>
@@ -23511,7 +23041,6 @@
       <c r="AR466" s="2" t="n"/>
       <c r="AS466" s="2" t="n"/>
       <c r="AT466" s="2" t="n"/>
-      <c r="AU466" s="2" t="n"/>
     </row>
     <row r="467">
       <c r="A467" s="2" t="n"/>
@@ -23560,7 +23089,6 @@
       <c r="AR467" s="2" t="n"/>
       <c r="AS467" s="2" t="n"/>
       <c r="AT467" s="2" t="n"/>
-      <c r="AU467" s="2" t="n"/>
     </row>
     <row r="468">
       <c r="A468" s="2" t="n"/>
@@ -23609,7 +23137,6 @@
       <c r="AR468" s="2" t="n"/>
       <c r="AS468" s="2" t="n"/>
       <c r="AT468" s="2" t="n"/>
-      <c r="AU468" s="2" t="n"/>
     </row>
     <row r="469">
       <c r="A469" s="2" t="n"/>
@@ -23658,7 +23185,6 @@
       <c r="AR469" s="2" t="n"/>
       <c r="AS469" s="2" t="n"/>
       <c r="AT469" s="2" t="n"/>
-      <c r="AU469" s="2" t="n"/>
     </row>
     <row r="470">
       <c r="A470" s="2" t="n"/>
@@ -23707,7 +23233,6 @@
       <c r="AR470" s="2" t="n"/>
       <c r="AS470" s="2" t="n"/>
       <c r="AT470" s="2" t="n"/>
-      <c r="AU470" s="2" t="n"/>
     </row>
     <row r="471">
       <c r="A471" s="2" t="n"/>
@@ -23756,7 +23281,6 @@
       <c r="AR471" s="2" t="n"/>
       <c r="AS471" s="2" t="n"/>
       <c r="AT471" s="2" t="n"/>
-      <c r="AU471" s="2" t="n"/>
     </row>
     <row r="472">
       <c r="A472" s="2" t="n"/>
@@ -23805,7 +23329,6 @@
       <c r="AR472" s="2" t="n"/>
       <c r="AS472" s="2" t="n"/>
       <c r="AT472" s="2" t="n"/>
-      <c r="AU472" s="2" t="n"/>
     </row>
     <row r="473">
       <c r="A473" s="2" t="n"/>
@@ -23854,7 +23377,6 @@
       <c r="AR473" s="2" t="n"/>
       <c r="AS473" s="2" t="n"/>
       <c r="AT473" s="2" t="n"/>
-      <c r="AU473" s="2" t="n"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="n"/>
@@ -23903,7 +23425,6 @@
       <c r="AR474" s="2" t="n"/>
       <c r="AS474" s="2" t="n"/>
       <c r="AT474" s="2" t="n"/>
-      <c r="AU474" s="2" t="n"/>
     </row>
     <row r="475">
       <c r="A475" s="2" t="n"/>
@@ -23952,7 +23473,6 @@
       <c r="AR475" s="2" t="n"/>
       <c r="AS475" s="2" t="n"/>
       <c r="AT475" s="2" t="n"/>
-      <c r="AU475" s="2" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="2" t="n"/>
@@ -24001,7 +23521,6 @@
       <c r="AR476" s="2" t="n"/>
       <c r="AS476" s="2" t="n"/>
       <c r="AT476" s="2" t="n"/>
-      <c r="AU476" s="2" t="n"/>
     </row>
     <row r="477">
       <c r="A477" s="2" t="n"/>
@@ -24050,7 +23569,6 @@
       <c r="AR477" s="2" t="n"/>
       <c r="AS477" s="2" t="n"/>
       <c r="AT477" s="2" t="n"/>
-      <c r="AU477" s="2" t="n"/>
     </row>
     <row r="478">
       <c r="A478" s="2" t="n"/>
@@ -24099,7 +23617,6 @@
       <c r="AR478" s="2" t="n"/>
       <c r="AS478" s="2" t="n"/>
       <c r="AT478" s="2" t="n"/>
-      <c r="AU478" s="2" t="n"/>
     </row>
     <row r="479">
       <c r="A479" s="2" t="n"/>
@@ -24148,7 +23665,6 @@
       <c r="AR479" s="2" t="n"/>
       <c r="AS479" s="2" t="n"/>
       <c r="AT479" s="2" t="n"/>
-      <c r="AU479" s="2" t="n"/>
     </row>
     <row r="480">
       <c r="A480" s="2" t="n"/>
@@ -24197,7 +23713,6 @@
       <c r="AR480" s="2" t="n"/>
       <c r="AS480" s="2" t="n"/>
       <c r="AT480" s="2" t="n"/>
-      <c r="AU480" s="2" t="n"/>
     </row>
     <row r="481">
       <c r="A481" s="2" t="n"/>
@@ -24246,7 +23761,6 @@
       <c r="AR481" s="2" t="n"/>
       <c r="AS481" s="2" t="n"/>
       <c r="AT481" s="2" t="n"/>
-      <c r="AU481" s="2" t="n"/>
     </row>
     <row r="482">
       <c r="A482" s="2" t="n"/>
@@ -24295,7 +23809,6 @@
       <c r="AR482" s="2" t="n"/>
       <c r="AS482" s="2" t="n"/>
       <c r="AT482" s="2" t="n"/>
-      <c r="AU482" s="2" t="n"/>
     </row>
     <row r="483">
       <c r="A483" s="2" t="n"/>
@@ -24344,7 +23857,6 @@
       <c r="AR483" s="2" t="n"/>
       <c r="AS483" s="2" t="n"/>
       <c r="AT483" s="2" t="n"/>
-      <c r="AU483" s="2" t="n"/>
     </row>
     <row r="484">
       <c r="A484" s="2" t="n"/>
@@ -24393,7 +23905,6 @@
       <c r="AR484" s="2" t="n"/>
       <c r="AS484" s="2" t="n"/>
       <c r="AT484" s="2" t="n"/>
-      <c r="AU484" s="2" t="n"/>
     </row>
     <row r="485">
       <c r="A485" s="2" t="n"/>
@@ -24442,7 +23953,6 @@
       <c r="AR485" s="2" t="n"/>
       <c r="AS485" s="2" t="n"/>
       <c r="AT485" s="2" t="n"/>
-      <c r="AU485" s="2" t="n"/>
     </row>
     <row r="486">
       <c r="A486" s="2" t="n"/>
@@ -24491,7 +24001,6 @@
       <c r="AR486" s="2" t="n"/>
       <c r="AS486" s="2" t="n"/>
       <c r="AT486" s="2" t="n"/>
-      <c r="AU486" s="2" t="n"/>
     </row>
     <row r="487">
       <c r="A487" s="2" t="n"/>
@@ -24540,7 +24049,6 @@
       <c r="AR487" s="2" t="n"/>
       <c r="AS487" s="2" t="n"/>
       <c r="AT487" s="2" t="n"/>
-      <c r="AU487" s="2" t="n"/>
     </row>
     <row r="488">
       <c r="A488" s="2" t="n"/>
@@ -24589,7 +24097,6 @@
       <c r="AR488" s="2" t="n"/>
       <c r="AS488" s="2" t="n"/>
       <c r="AT488" s="2" t="n"/>
-      <c r="AU488" s="2" t="n"/>
     </row>
     <row r="489">
       <c r="A489" s="2" t="n"/>
@@ -24638,7 +24145,6 @@
       <c r="AR489" s="2" t="n"/>
       <c r="AS489" s="2" t="n"/>
       <c r="AT489" s="2" t="n"/>
-      <c r="AU489" s="2" t="n"/>
     </row>
     <row r="490">
       <c r="A490" s="2" t="n"/>
@@ -24687,7 +24193,6 @@
       <c r="AR490" s="2" t="n"/>
       <c r="AS490" s="2" t="n"/>
       <c r="AT490" s="2" t="n"/>
-      <c r="AU490" s="2" t="n"/>
     </row>
     <row r="491">
       <c r="A491" s="2" t="n"/>
@@ -24736,7 +24241,6 @@
       <c r="AR491" s="2" t="n"/>
       <c r="AS491" s="2" t="n"/>
       <c r="AT491" s="2" t="n"/>
-      <c r="AU491" s="2" t="n"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="n"/>
@@ -24785,7 +24289,6 @@
       <c r="AR492" s="2" t="n"/>
       <c r="AS492" s="2" t="n"/>
       <c r="AT492" s="2" t="n"/>
-      <c r="AU492" s="2" t="n"/>
     </row>
     <row r="493">
       <c r="A493" s="2" t="n"/>
@@ -24834,7 +24337,6 @@
       <c r="AR493" s="2" t="n"/>
       <c r="AS493" s="2" t="n"/>
       <c r="AT493" s="2" t="n"/>
-      <c r="AU493" s="2" t="n"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="n"/>
@@ -24883,7 +24385,6 @@
       <c r="AR494" s="2" t="n"/>
       <c r="AS494" s="2" t="n"/>
       <c r="AT494" s="2" t="n"/>
-      <c r="AU494" s="2" t="n"/>
     </row>
     <row r="495">
       <c r="A495" s="2" t="n"/>
@@ -24932,7 +24433,6 @@
       <c r="AR495" s="2" t="n"/>
       <c r="AS495" s="2" t="n"/>
       <c r="AT495" s="2" t="n"/>
-      <c r="AU495" s="2" t="n"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="n"/>
@@ -24981,7 +24481,6 @@
       <c r="AR496" s="2" t="n"/>
       <c r="AS496" s="2" t="n"/>
       <c r="AT496" s="2" t="n"/>
-      <c r="AU496" s="2" t="n"/>
     </row>
     <row r="497">
       <c r="A497" s="2" t="n"/>
@@ -25030,7 +24529,6 @@
       <c r="AR497" s="2" t="n"/>
       <c r="AS497" s="2" t="n"/>
       <c r="AT497" s="2" t="n"/>
-      <c r="AU497" s="2" t="n"/>
     </row>
     <row r="498">
       <c r="A498" s="2" t="n"/>
@@ -25079,7 +24577,6 @@
       <c r="AR498" s="2" t="n"/>
       <c r="AS498" s="2" t="n"/>
       <c r="AT498" s="2" t="n"/>
-      <c r="AU498" s="2" t="n"/>
     </row>
     <row r="499">
       <c r="A499" s="2" t="n"/>
@@ -25128,7 +24625,6 @@
       <c r="AR499" s="2" t="n"/>
       <c r="AS499" s="2" t="n"/>
       <c r="AT499" s="2" t="n"/>
-      <c r="AU499" s="2" t="n"/>
     </row>
     <row r="500">
       <c r="A500" s="2" t="n"/>
@@ -25177,7 +24673,6 @@
       <c r="AR500" s="2" t="n"/>
       <c r="AS500" s="2" t="n"/>
       <c r="AT500" s="2" t="n"/>
-      <c r="AU500" s="2" t="n"/>
     </row>
     <row r="501">
       <c r="A501" s="2" t="n"/>
@@ -25226,7 +24721,6 @@
       <c r="AR501" s="2" t="n"/>
       <c r="AS501" s="2" t="n"/>
       <c r="AT501" s="2" t="n"/>
-      <c r="AU501" s="2" t="n"/>
     </row>
     <row r="502">
       <c r="A502" s="2" t="n"/>
@@ -25275,7 +24769,6 @@
       <c r="AR502" s="2" t="n"/>
       <c r="AS502" s="2" t="n"/>
       <c r="AT502" s="2" t="n"/>
-      <c r="AU502" s="2" t="n"/>
     </row>
     <row r="503">
       <c r="A503" s="2" t="n"/>
@@ -25324,7 +24817,6 @@
       <c r="AR503" s="2" t="n"/>
       <c r="AS503" s="2" t="n"/>
       <c r="AT503" s="2" t="n"/>
-      <c r="AU503" s="2" t="n"/>
     </row>
     <row r="504">
       <c r="A504" s="2" t="n"/>
@@ -25373,7 +24865,6 @@
       <c r="AR504" s="2" t="n"/>
       <c r="AS504" s="2" t="n"/>
       <c r="AT504" s="2" t="n"/>
-      <c r="AU504" s="2" t="n"/>
     </row>
     <row r="505">
       <c r="A505" s="2" t="n"/>
@@ -25422,7 +24913,6 @@
       <c r="AR505" s="2" t="n"/>
       <c r="AS505" s="2" t="n"/>
       <c r="AT505" s="2" t="n"/>
-      <c r="AU505" s="2" t="n"/>
     </row>
     <row r="506">
       <c r="A506" s="2" t="n"/>
@@ -25471,7 +24961,6 @@
       <c r="AR506" s="2" t="n"/>
       <c r="AS506" s="2" t="n"/>
       <c r="AT506" s="2" t="n"/>
-      <c r="AU506" s="2" t="n"/>
     </row>
     <row r="507">
       <c r="A507" s="2" t="n"/>
@@ -25520,7 +25009,6 @@
       <c r="AR507" s="2" t="n"/>
       <c r="AS507" s="2" t="n"/>
       <c r="AT507" s="2" t="n"/>
-      <c r="AU507" s="2" t="n"/>
     </row>
     <row r="508">
       <c r="A508" s="2" t="n"/>
@@ -25569,7 +25057,6 @@
       <c r="AR508" s="2" t="n"/>
       <c r="AS508" s="2" t="n"/>
       <c r="AT508" s="2" t="n"/>
-      <c r="AU508" s="2" t="n"/>
     </row>
     <row r="509">
       <c r="A509" s="2" t="n"/>
@@ -25618,7 +25105,6 @@
       <c r="AR509" s="2" t="n"/>
       <c r="AS509" s="2" t="n"/>
       <c r="AT509" s="2" t="n"/>
-      <c r="AU509" s="2" t="n"/>
     </row>
     <row r="510">
       <c r="A510" s="2" t="n"/>
@@ -25667,7 +25153,6 @@
       <c r="AR510" s="2" t="n"/>
       <c r="AS510" s="2" t="n"/>
       <c r="AT510" s="2" t="n"/>
-      <c r="AU510" s="2" t="n"/>
     </row>
     <row r="511">
       <c r="A511" s="2" t="n"/>
@@ -25716,7 +25201,6 @@
       <c r="AR511" s="2" t="n"/>
       <c r="AS511" s="2" t="n"/>
       <c r="AT511" s="2" t="n"/>
-      <c r="AU511" s="2" t="n"/>
     </row>
     <row r="512">
       <c r="A512" s="2" t="n"/>
@@ -25765,7 +25249,6 @@
       <c r="AR512" s="2" t="n"/>
       <c r="AS512" s="2" t="n"/>
       <c r="AT512" s="2" t="n"/>
-      <c r="AU512" s="2" t="n"/>
     </row>
     <row r="513">
       <c r="A513" s="2" t="n"/>
@@ -25814,7 +25297,6 @@
       <c r="AR513" s="2" t="n"/>
       <c r="AS513" s="2" t="n"/>
       <c r="AT513" s="2" t="n"/>
-      <c r="AU513" s="2" t="n"/>
     </row>
     <row r="514">
       <c r="A514" s="2" t="n"/>
@@ -25863,7 +25345,6 @@
       <c r="AR514" s="2" t="n"/>
       <c r="AS514" s="2" t="n"/>
       <c r="AT514" s="2" t="n"/>
-      <c r="AU514" s="2" t="n"/>
     </row>
     <row r="515">
       <c r="A515" s="2" t="n"/>
@@ -25912,7 +25393,6 @@
       <c r="AR515" s="2" t="n"/>
       <c r="AS515" s="2" t="n"/>
       <c r="AT515" s="2" t="n"/>
-      <c r="AU515" s="2" t="n"/>
     </row>
     <row r="516">
       <c r="A516" s="2" t="n"/>
@@ -25961,7 +25441,6 @@
       <c r="AR516" s="2" t="n"/>
       <c r="AS516" s="2" t="n"/>
       <c r="AT516" s="2" t="n"/>
-      <c r="AU516" s="2" t="n"/>
     </row>
     <row r="517">
       <c r="A517" s="2" t="n"/>
@@ -26010,7 +25489,6 @@
       <c r="AR517" s="2" t="n"/>
       <c r="AS517" s="2" t="n"/>
       <c r="AT517" s="2" t="n"/>
-      <c r="AU517" s="2" t="n"/>
     </row>
     <row r="518">
       <c r="A518" s="2" t="n"/>
@@ -26059,7 +25537,6 @@
       <c r="AR518" s="2" t="n"/>
       <c r="AS518" s="2" t="n"/>
       <c r="AT518" s="2" t="n"/>
-      <c r="AU518" s="2" t="n"/>
     </row>
     <row r="519">
       <c r="A519" s="2" t="n"/>
@@ -26108,7 +25585,6 @@
       <c r="AR519" s="2" t="n"/>
       <c r="AS519" s="2" t="n"/>
       <c r="AT519" s="2" t="n"/>
-      <c r="AU519" s="2" t="n"/>
     </row>
     <row r="520">
       <c r="A520" s="2" t="n"/>
@@ -26157,7 +25633,6 @@
       <c r="AR520" s="2" t="n"/>
       <c r="AS520" s="2" t="n"/>
       <c r="AT520" s="2" t="n"/>
-      <c r="AU520" s="2" t="n"/>
     </row>
     <row r="521">
       <c r="A521" s="2" t="n"/>
@@ -26206,7 +25681,6 @@
       <c r="AR521" s="2" t="n"/>
       <c r="AS521" s="2" t="n"/>
       <c r="AT521" s="2" t="n"/>
-      <c r="AU521" s="2" t="n"/>
     </row>
     <row r="522">
       <c r="A522" s="2" t="n"/>
@@ -26255,7 +25729,6 @@
       <c r="AR522" s="2" t="n"/>
       <c r="AS522" s="2" t="n"/>
       <c r="AT522" s="2" t="n"/>
-      <c r="AU522" s="2" t="n"/>
     </row>
     <row r="523">
       <c r="A523" s="2" t="n"/>
@@ -26304,7 +25777,6 @@
       <c r="AR523" s="2" t="n"/>
       <c r="AS523" s="2" t="n"/>
       <c r="AT523" s="2" t="n"/>
-      <c r="AU523" s="2" t="n"/>
     </row>
     <row r="524">
       <c r="A524" s="2" t="n"/>
@@ -26353,7 +25825,6 @@
       <c r="AR524" s="2" t="n"/>
       <c r="AS524" s="2" t="n"/>
       <c r="AT524" s="2" t="n"/>
-      <c r="AU524" s="2" t="n"/>
     </row>
     <row r="525">
       <c r="A525" s="2" t="n"/>
@@ -26402,7 +25873,6 @@
       <c r="AR525" s="2" t="n"/>
       <c r="AS525" s="2" t="n"/>
       <c r="AT525" s="2" t="n"/>
-      <c r="AU525" s="2" t="n"/>
     </row>
     <row r="526">
       <c r="A526" s="2" t="n"/>
@@ -26451,7 +25921,6 @@
       <c r="AR526" s="2" t="n"/>
       <c r="AS526" s="2" t="n"/>
       <c r="AT526" s="2" t="n"/>
-      <c r="AU526" s="2" t="n"/>
     </row>
     <row r="527">
       <c r="A527" s="2" t="n"/>
@@ -26500,7 +25969,6 @@
       <c r="AR527" s="2" t="n"/>
       <c r="AS527" s="2" t="n"/>
       <c r="AT527" s="2" t="n"/>
-      <c r="AU527" s="2" t="n"/>
     </row>
     <row r="528">
       <c r="A528" s="2" t="n"/>
@@ -26549,7 +26017,6 @@
       <c r="AR528" s="2" t="n"/>
       <c r="AS528" s="2" t="n"/>
       <c r="AT528" s="2" t="n"/>
-      <c r="AU528" s="2" t="n"/>
     </row>
     <row r="529">
       <c r="A529" s="2" t="n"/>
@@ -26598,7 +26065,6 @@
       <c r="AR529" s="2" t="n"/>
       <c r="AS529" s="2" t="n"/>
       <c r="AT529" s="2" t="n"/>
-      <c r="AU529" s="2" t="n"/>
     </row>
     <row r="530">
       <c r="A530" s="2" t="n"/>
@@ -26647,7 +26113,6 @@
       <c r="AR530" s="2" t="n"/>
       <c r="AS530" s="2" t="n"/>
       <c r="AT530" s="2" t="n"/>
-      <c r="AU530" s="2" t="n"/>
     </row>
     <row r="531">
       <c r="A531" s="2" t="n"/>
@@ -26696,7 +26161,6 @@
       <c r="AR531" s="2" t="n"/>
       <c r="AS531" s="2" t="n"/>
       <c r="AT531" s="2" t="n"/>
-      <c r="AU531" s="2" t="n"/>
     </row>
     <row r="532">
       <c r="A532" s="2" t="n"/>
@@ -26745,7 +26209,6 @@
       <c r="AR532" s="2" t="n"/>
       <c r="AS532" s="2" t="n"/>
       <c r="AT532" s="2" t="n"/>
-      <c r="AU532" s="2" t="n"/>
     </row>
     <row r="533">
       <c r="A533" s="2" t="n"/>
@@ -26794,7 +26257,6 @@
       <c r="AR533" s="2" t="n"/>
       <c r="AS533" s="2" t="n"/>
       <c r="AT533" s="2" t="n"/>
-      <c r="AU533" s="2" t="n"/>
     </row>
     <row r="534">
       <c r="A534" s="2" t="n"/>
@@ -26843,7 +26305,6 @@
       <c r="AR534" s="2" t="n"/>
       <c r="AS534" s="2" t="n"/>
       <c r="AT534" s="2" t="n"/>
-      <c r="AU534" s="2" t="n"/>
     </row>
     <row r="535">
       <c r="A535" s="2" t="n"/>
@@ -26892,7 +26353,6 @@
       <c r="AR535" s="2" t="n"/>
       <c r="AS535" s="2" t="n"/>
       <c r="AT535" s="2" t="n"/>
-      <c r="AU535" s="2" t="n"/>
     </row>
     <row r="536">
       <c r="A536" s="2" t="n"/>
@@ -26941,7 +26401,6 @@
       <c r="AR536" s="2" t="n"/>
       <c r="AS536" s="2" t="n"/>
       <c r="AT536" s="2" t="n"/>
-      <c r="AU536" s="2" t="n"/>
     </row>
     <row r="537">
       <c r="A537" s="2" t="n"/>
@@ -26990,7 +26449,6 @@
       <c r="AR537" s="2" t="n"/>
       <c r="AS537" s="2" t="n"/>
       <c r="AT537" s="2" t="n"/>
-      <c r="AU537" s="2" t="n"/>
     </row>
     <row r="538">
       <c r="A538" s="2" t="n"/>
@@ -27039,7 +26497,6 @@
       <c r="AR538" s="2" t="n"/>
       <c r="AS538" s="2" t="n"/>
       <c r="AT538" s="2" t="n"/>
-      <c r="AU538" s="2" t="n"/>
     </row>
     <row r="539">
       <c r="A539" s="2" t="n"/>
@@ -27088,7 +26545,6 @@
       <c r="AR539" s="2" t="n"/>
       <c r="AS539" s="2" t="n"/>
       <c r="AT539" s="2" t="n"/>
-      <c r="AU539" s="2" t="n"/>
     </row>
     <row r="540">
       <c r="A540" s="2" t="n"/>
@@ -27137,7 +26593,6 @@
       <c r="AR540" s="2" t="n"/>
       <c r="AS540" s="2" t="n"/>
       <c r="AT540" s="2" t="n"/>
-      <c r="AU540" s="2" t="n"/>
     </row>
     <row r="541">
       <c r="A541" s="2" t="n"/>
@@ -27186,7 +26641,6 @@
       <c r="AR541" s="2" t="n"/>
       <c r="AS541" s="2" t="n"/>
       <c r="AT541" s="2" t="n"/>
-      <c r="AU541" s="2" t="n"/>
     </row>
     <row r="542">
       <c r="A542" s="2" t="n"/>
@@ -27235,7 +26689,6 @@
       <c r="AR542" s="2" t="n"/>
       <c r="AS542" s="2" t="n"/>
       <c r="AT542" s="2" t="n"/>
-      <c r="AU542" s="2" t="n"/>
     </row>
     <row r="543">
       <c r="A543" s="2" t="n"/>
@@ -27284,7 +26737,6 @@
       <c r="AR543" s="2" t="n"/>
       <c r="AS543" s="2" t="n"/>
       <c r="AT543" s="2" t="n"/>
-      <c r="AU543" s="2" t="n"/>
     </row>
     <row r="544">
       <c r="A544" s="2" t="n"/>
@@ -27333,7 +26785,6 @@
       <c r="AR544" s="2" t="n"/>
       <c r="AS544" s="2" t="n"/>
       <c r="AT544" s="2" t="n"/>
-      <c r="AU544" s="2" t="n"/>
     </row>
     <row r="545">
       <c r="A545" s="2" t="n"/>
@@ -27382,7 +26833,6 @@
       <c r="AR545" s="2" t="n"/>
       <c r="AS545" s="2" t="n"/>
       <c r="AT545" s="2" t="n"/>
-      <c r="AU545" s="2" t="n"/>
     </row>
     <row r="546">
       <c r="A546" s="2" t="n"/>
@@ -27431,7 +26881,6 @@
       <c r="AR546" s="2" t="n"/>
       <c r="AS546" s="2" t="n"/>
       <c r="AT546" s="2" t="n"/>
-      <c r="AU546" s="2" t="n"/>
     </row>
     <row r="547">
       <c r="A547" s="2" t="n"/>
@@ -27480,7 +26929,6 @@
       <c r="AR547" s="2" t="n"/>
       <c r="AS547" s="2" t="n"/>
       <c r="AT547" s="2" t="n"/>
-      <c r="AU547" s="2" t="n"/>
     </row>
     <row r="548">
       <c r="A548" s="2" t="n"/>
@@ -27529,7 +26977,6 @@
       <c r="AR548" s="2" t="n"/>
       <c r="AS548" s="2" t="n"/>
       <c r="AT548" s="2" t="n"/>
-      <c r="AU548" s="2" t="n"/>
     </row>
     <row r="549">
       <c r="A549" s="2" t="n"/>
@@ -27578,7 +27025,6 @@
       <c r="AR549" s="2" t="n"/>
       <c r="AS549" s="2" t="n"/>
       <c r="AT549" s="2" t="n"/>
-      <c r="AU549" s="2" t="n"/>
     </row>
     <row r="550">
       <c r="A550" s="2" t="n"/>
@@ -27627,7 +27073,6 @@
       <c r="AR550" s="2" t="n"/>
       <c r="AS550" s="2" t="n"/>
       <c r="AT550" s="2" t="n"/>
-      <c r="AU550" s="2" t="n"/>
     </row>
     <row r="551">
       <c r="A551" s="2" t="n"/>
@@ -27676,7 +27121,6 @@
       <c r="AR551" s="2" t="n"/>
       <c r="AS551" s="2" t="n"/>
       <c r="AT551" s="2" t="n"/>
-      <c r="AU551" s="2" t="n"/>
     </row>
     <row r="552">
       <c r="A552" s="2" t="n"/>
@@ -27725,7 +27169,6 @@
       <c r="AR552" s="2" t="n"/>
       <c r="AS552" s="2" t="n"/>
       <c r="AT552" s="2" t="n"/>
-      <c r="AU552" s="2" t="n"/>
     </row>
     <row r="553">
       <c r="A553" s="2" t="n"/>
@@ -27774,7 +27217,6 @@
       <c r="AR553" s="2" t="n"/>
       <c r="AS553" s="2" t="n"/>
       <c r="AT553" s="2" t="n"/>
-      <c r="AU553" s="2" t="n"/>
     </row>
     <row r="554">
       <c r="A554" s="2" t="n"/>
@@ -27823,7 +27265,6 @@
       <c r="AR554" s="2" t="n"/>
       <c r="AS554" s="2" t="n"/>
       <c r="AT554" s="2" t="n"/>
-      <c r="AU554" s="2" t="n"/>
     </row>
     <row r="555">
       <c r="A555" s="2" t="n"/>
@@ -27872,7 +27313,6 @@
       <c r="AR555" s="2" t="n"/>
       <c r="AS555" s="2" t="n"/>
       <c r="AT555" s="2" t="n"/>
-      <c r="AU555" s="2" t="n"/>
     </row>
     <row r="556">
       <c r="A556" s="2" t="n"/>
@@ -27921,7 +27361,6 @@
       <c r="AR556" s="2" t="n"/>
       <c r="AS556" s="2" t="n"/>
       <c r="AT556" s="2" t="n"/>
-      <c r="AU556" s="2" t="n"/>
     </row>
     <row r="557">
       <c r="A557" s="2" t="n"/>
@@ -27970,7 +27409,6 @@
       <c r="AR557" s="2" t="n"/>
       <c r="AS557" s="2" t="n"/>
       <c r="AT557" s="2" t="n"/>
-      <c r="AU557" s="2" t="n"/>
     </row>
     <row r="558">
       <c r="A558" s="2" t="n"/>
@@ -28019,7 +27457,6 @@
       <c r="AR558" s="2" t="n"/>
       <c r="AS558" s="2" t="n"/>
       <c r="AT558" s="2" t="n"/>
-      <c r="AU558" s="2" t="n"/>
     </row>
     <row r="559">
       <c r="A559" s="2" t="n"/>
@@ -28068,7 +27505,6 @@
       <c r="AR559" s="2" t="n"/>
       <c r="AS559" s="2" t="n"/>
       <c r="AT559" s="2" t="n"/>
-      <c r="AU559" s="2" t="n"/>
     </row>
     <row r="560">
       <c r="A560" s="2" t="n"/>
@@ -28117,7 +27553,6 @@
       <c r="AR560" s="2" t="n"/>
       <c r="AS560" s="2" t="n"/>
       <c r="AT560" s="2" t="n"/>
-      <c r="AU560" s="2" t="n"/>
     </row>
     <row r="561">
       <c r="A561" s="2" t="n"/>
@@ -28166,7 +27601,6 @@
       <c r="AR561" s="2" t="n"/>
       <c r="AS561" s="2" t="n"/>
       <c r="AT561" s="2" t="n"/>
-      <c r="AU561" s="2" t="n"/>
     </row>
     <row r="562">
       <c r="A562" s="2" t="n"/>
@@ -28215,7 +27649,6 @@
       <c r="AR562" s="2" t="n"/>
       <c r="AS562" s="2" t="n"/>
       <c r="AT562" s="2" t="n"/>
-      <c r="AU562" s="2" t="n"/>
     </row>
     <row r="563">
       <c r="A563" s="2" t="n"/>
@@ -28264,7 +27697,6 @@
       <c r="AR563" s="2" t="n"/>
       <c r="AS563" s="2" t="n"/>
       <c r="AT563" s="2" t="n"/>
-      <c r="AU563" s="2" t="n"/>
     </row>
     <row r="564">
       <c r="A564" s="2" t="n"/>
@@ -28313,7 +27745,6 @@
       <c r="AR564" s="2" t="n"/>
       <c r="AS564" s="2" t="n"/>
       <c r="AT564" s="2" t="n"/>
-      <c r="AU564" s="2" t="n"/>
     </row>
     <row r="565">
       <c r="A565" s="2" t="n"/>
@@ -28362,7 +27793,6 @@
       <c r="AR565" s="2" t="n"/>
       <c r="AS565" s="2" t="n"/>
       <c r="AT565" s="2" t="n"/>
-      <c r="AU565" s="2" t="n"/>
     </row>
     <row r="566">
       <c r="A566" s="2" t="n"/>
@@ -28411,7 +27841,6 @@
       <c r="AR566" s="2" t="n"/>
       <c r="AS566" s="2" t="n"/>
       <c r="AT566" s="2" t="n"/>
-      <c r="AU566" s="2" t="n"/>
     </row>
     <row r="567">
       <c r="A567" s="2" t="n"/>
@@ -28460,7 +27889,6 @@
       <c r="AR567" s="2" t="n"/>
       <c r="AS567" s="2" t="n"/>
       <c r="AT567" s="2" t="n"/>
-      <c r="AU567" s="2" t="n"/>
     </row>
     <row r="568">
       <c r="A568" s="2" t="n"/>
@@ -28509,7 +27937,6 @@
       <c r="AR568" s="2" t="n"/>
       <c r="AS568" s="2" t="n"/>
       <c r="AT568" s="2" t="n"/>
-      <c r="AU568" s="2" t="n"/>
     </row>
     <row r="569">
       <c r="A569" s="2" t="n"/>
@@ -28558,7 +27985,6 @@
       <c r="AR569" s="2" t="n"/>
       <c r="AS569" s="2" t="n"/>
       <c r="AT569" s="2" t="n"/>
-      <c r="AU569" s="2" t="n"/>
     </row>
     <row r="570">
       <c r="A570" s="2" t="n"/>
@@ -28607,7 +28033,6 @@
       <c r="AR570" s="2" t="n"/>
       <c r="AS570" s="2" t="n"/>
       <c r="AT570" s="2" t="n"/>
-      <c r="AU570" s="2" t="n"/>
     </row>
     <row r="571">
       <c r="A571" s="2" t="n"/>
@@ -28656,7 +28081,6 @@
       <c r="AR571" s="2" t="n"/>
       <c r="AS571" s="2" t="n"/>
       <c r="AT571" s="2" t="n"/>
-      <c r="AU571" s="2" t="n"/>
     </row>
     <row r="572">
       <c r="A572" s="2" t="n"/>
@@ -28705,7 +28129,6 @@
       <c r="AR572" s="2" t="n"/>
       <c r="AS572" s="2" t="n"/>
       <c r="AT572" s="2" t="n"/>
-      <c r="AU572" s="2" t="n"/>
     </row>
     <row r="573">
       <c r="A573" s="2" t="n"/>
@@ -28754,7 +28177,6 @@
       <c r="AR573" s="2" t="n"/>
       <c r="AS573" s="2" t="n"/>
       <c r="AT573" s="2" t="n"/>
-      <c r="AU573" s="2" t="n"/>
     </row>
     <row r="574">
       <c r="A574" s="2" t="n"/>
@@ -28803,7 +28225,6 @@
       <c r="AR574" s="2" t="n"/>
       <c r="AS574" s="2" t="n"/>
       <c r="AT574" s="2" t="n"/>
-      <c r="AU574" s="2" t="n"/>
     </row>
     <row r="575">
       <c r="A575" s="2" t="n"/>
@@ -28852,7 +28273,6 @@
       <c r="AR575" s="2" t="n"/>
       <c r="AS575" s="2" t="n"/>
       <c r="AT575" s="2" t="n"/>
-      <c r="AU575" s="2" t="n"/>
     </row>
     <row r="576">
       <c r="A576" s="2" t="n"/>
@@ -28901,7 +28321,6 @@
       <c r="AR576" s="2" t="n"/>
       <c r="AS576" s="2" t="n"/>
       <c r="AT576" s="2" t="n"/>
-      <c r="AU576" s="2" t="n"/>
     </row>
     <row r="577">
       <c r="A577" s="2" t="n"/>
@@ -28950,7 +28369,6 @@
       <c r="AR577" s="2" t="n"/>
       <c r="AS577" s="2" t="n"/>
       <c r="AT577" s="2" t="n"/>
-      <c r="AU577" s="2" t="n"/>
     </row>
     <row r="578">
       <c r="A578" s="2" t="n"/>
@@ -28999,7 +28417,6 @@
       <c r="AR578" s="2" t="n"/>
       <c r="AS578" s="2" t="n"/>
       <c r="AT578" s="2" t="n"/>
-      <c r="AU578" s="2" t="n"/>
     </row>
     <row r="579">
       <c r="A579" s="2" t="n"/>
@@ -29048,7 +28465,6 @@
       <c r="AR579" s="2" t="n"/>
       <c r="AS579" s="2" t="n"/>
       <c r="AT579" s="2" t="n"/>
-      <c r="AU579" s="2" t="n"/>
     </row>
     <row r="580">
       <c r="A580" s="2" t="n"/>
@@ -29097,7 +28513,6 @@
       <c r="AR580" s="2" t="n"/>
       <c r="AS580" s="2" t="n"/>
       <c r="AT580" s="2" t="n"/>
-      <c r="AU580" s="2" t="n"/>
     </row>
     <row r="581">
       <c r="A581" s="2" t="n"/>
@@ -29146,7 +28561,6 @@
       <c r="AR581" s="2" t="n"/>
       <c r="AS581" s="2" t="n"/>
       <c r="AT581" s="2" t="n"/>
-      <c r="AU581" s="2" t="n"/>
     </row>
     <row r="582">
       <c r="A582" s="2" t="n"/>
@@ -29195,7 +28609,6 @@
       <c r="AR582" s="2" t="n"/>
       <c r="AS582" s="2" t="n"/>
       <c r="AT582" s="2" t="n"/>
-      <c r="AU582" s="2" t="n"/>
     </row>
     <row r="583">
       <c r="A583" s="2" t="n"/>
@@ -29244,7 +28657,6 @@
       <c r="AR583" s="2" t="n"/>
       <c r="AS583" s="2" t="n"/>
       <c r="AT583" s="2" t="n"/>
-      <c r="AU583" s="2" t="n"/>
     </row>
     <row r="584">
       <c r="A584" s="2" t="n"/>
@@ -29293,7 +28705,6 @@
       <c r="AR584" s="2" t="n"/>
       <c r="AS584" s="2" t="n"/>
       <c r="AT584" s="2" t="n"/>
-      <c r="AU584" s="2" t="n"/>
     </row>
     <row r="585">
       <c r="A585" s="2" t="n"/>
@@ -29342,7 +28753,6 @@
       <c r="AR585" s="2" t="n"/>
       <c r="AS585" s="2" t="n"/>
       <c r="AT585" s="2" t="n"/>
-      <c r="AU585" s="2" t="n"/>
     </row>
     <row r="586">
       <c r="A586" s="2" t="n"/>
@@ -29391,7 +28801,6 @@
       <c r="AR586" s="2" t="n"/>
       <c r="AS586" s="2" t="n"/>
       <c r="AT586" s="2" t="n"/>
-      <c r="AU586" s="2" t="n"/>
     </row>
     <row r="587">
       <c r="A587" s="2" t="n"/>
@@ -29440,7 +28849,6 @@
       <c r="AR587" s="2" t="n"/>
       <c r="AS587" s="2" t="n"/>
       <c r="AT587" s="2" t="n"/>
-      <c r="AU587" s="2" t="n"/>
     </row>
     <row r="588">
       <c r="A588" s="2" t="n"/>
@@ -29489,7 +28897,6 @@
       <c r="AR588" s="2" t="n"/>
       <c r="AS588" s="2" t="n"/>
       <c r="AT588" s="2" t="n"/>
-      <c r="AU588" s="2" t="n"/>
     </row>
     <row r="589">
       <c r="A589" s="2" t="n"/>
@@ -29538,7 +28945,6 @@
       <c r="AR589" s="2" t="n"/>
       <c r="AS589" s="2" t="n"/>
       <c r="AT589" s="2" t="n"/>
-      <c r="AU589" s="2" t="n"/>
     </row>
     <row r="590">
       <c r="A590" s="2" t="n"/>
@@ -29587,7 +28993,6 @@
       <c r="AR590" s="2" t="n"/>
       <c r="AS590" s="2" t="n"/>
       <c r="AT590" s="2" t="n"/>
-      <c r="AU590" s="2" t="n"/>
     </row>
     <row r="591">
       <c r="A591" s="2" t="n"/>
@@ -29636,7 +29041,6 @@
       <c r="AR591" s="2" t="n"/>
       <c r="AS591" s="2" t="n"/>
       <c r="AT591" s="2" t="n"/>
-      <c r="AU591" s="2" t="n"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="n"/>
@@ -29685,7 +29089,6 @@
       <c r="AR592" s="2" t="n"/>
       <c r="AS592" s="2" t="n"/>
       <c r="AT592" s="2" t="n"/>
-      <c r="AU592" s="2" t="n"/>
     </row>
     <row r="593">
       <c r="A593" s="2" t="n"/>
@@ -29734,7 +29137,6 @@
       <c r="AR593" s="2" t="n"/>
       <c r="AS593" s="2" t="n"/>
       <c r="AT593" s="2" t="n"/>
-      <c r="AU593" s="2" t="n"/>
     </row>
     <row r="594">
       <c r="A594" s="2" t="n"/>
@@ -29783,7 +29185,6 @@
       <c r="AR594" s="2" t="n"/>
       <c r="AS594" s="2" t="n"/>
       <c r="AT594" s="2" t="n"/>
-      <c r="AU594" s="2" t="n"/>
     </row>
     <row r="595">
       <c r="A595" s="2" t="n"/>
@@ -29832,7 +29233,6 @@
       <c r="AR595" s="2" t="n"/>
       <c r="AS595" s="2" t="n"/>
       <c r="AT595" s="2" t="n"/>
-      <c r="AU595" s="2" t="n"/>
     </row>
     <row r="596">
       <c r="A596" s="2" t="n"/>
@@ -29881,7 +29281,6 @@
       <c r="AR596" s="2" t="n"/>
       <c r="AS596" s="2" t="n"/>
       <c r="AT596" s="2" t="n"/>
-      <c r="AU596" s="2" t="n"/>
     </row>
     <row r="597">
       <c r="A597" s="2" t="n"/>
@@ -29930,7 +29329,6 @@
       <c r="AR597" s="2" t="n"/>
       <c r="AS597" s="2" t="n"/>
       <c r="AT597" s="2" t="n"/>
-      <c r="AU597" s="2" t="n"/>
     </row>
     <row r="598">
       <c r="A598" s="2" t="n"/>
@@ -29979,7 +29377,6 @@
       <c r="AR598" s="2" t="n"/>
       <c r="AS598" s="2" t="n"/>
       <c r="AT598" s="2" t="n"/>
-      <c r="AU598" s="2" t="n"/>
     </row>
     <row r="599">
       <c r="A599" s="2" t="n"/>
@@ -30028,7 +29425,6 @@
       <c r="AR599" s="2" t="n"/>
       <c r="AS599" s="2" t="n"/>
       <c r="AT599" s="2" t="n"/>
-      <c r="AU599" s="2" t="n"/>
     </row>
     <row r="600">
       <c r="A600" s="2" t="n"/>
@@ -30077,7 +29473,6 @@
       <c r="AR600" s="2" t="n"/>
       <c r="AS600" s="2" t="n"/>
       <c r="AT600" s="2" t="n"/>
-      <c r="AU600" s="2" t="n"/>
     </row>
     <row r="601">
       <c r="A601" s="2" t="n"/>
@@ -30126,7 +29521,6 @@
       <c r="AR601" s="2" t="n"/>
       <c r="AS601" s="2" t="n"/>
       <c r="AT601" s="2" t="n"/>
-      <c r="AU601" s="2" t="n"/>
     </row>
     <row r="602">
       <c r="A602" s="2" t="n"/>
@@ -30175,7 +29569,6 @@
       <c r="AR602" s="2" t="n"/>
       <c r="AS602" s="2" t="n"/>
       <c r="AT602" s="2" t="n"/>
-      <c r="AU602" s="2" t="n"/>
     </row>
     <row r="603">
       <c r="A603" s="2" t="n"/>
@@ -30224,7 +29617,6 @@
       <c r="AR603" s="2" t="n"/>
       <c r="AS603" s="2" t="n"/>
       <c r="AT603" s="2" t="n"/>
-      <c r="AU603" s="2" t="n"/>
     </row>
     <row r="604">
       <c r="A604" s="2" t="n"/>
@@ -30273,7 +29665,6 @@
       <c r="AR604" s="2" t="n"/>
       <c r="AS604" s="2" t="n"/>
       <c r="AT604" s="2" t="n"/>
-      <c r="AU604" s="2" t="n"/>
     </row>
     <row r="605">
       <c r="A605" s="2" t="n"/>
@@ -30322,7 +29713,6 @@
       <c r="AR605" s="2" t="n"/>
       <c r="AS605" s="2" t="n"/>
       <c r="AT605" s="2" t="n"/>
-      <c r="AU605" s="2" t="n"/>
     </row>
     <row r="606">
       <c r="A606" s="2" t="n"/>
@@ -30371,7 +29761,6 @@
       <c r="AR606" s="2" t="n"/>
       <c r="AS606" s="2" t="n"/>
       <c r="AT606" s="2" t="n"/>
-      <c r="AU606" s="2" t="n"/>
     </row>
     <row r="607">
       <c r="A607" s="2" t="n"/>
@@ -30420,7 +29809,6 @@
       <c r="AR607" s="2" t="n"/>
       <c r="AS607" s="2" t="n"/>
       <c r="AT607" s="2" t="n"/>
-      <c r="AU607" s="2" t="n"/>
     </row>
     <row r="608">
       <c r="A608" s="2" t="n"/>
@@ -30469,7 +29857,6 @@
       <c r="AR608" s="2" t="n"/>
       <c r="AS608" s="2" t="n"/>
       <c r="AT608" s="2" t="n"/>
-      <c r="AU608" s="2" t="n"/>
     </row>
     <row r="609">
       <c r="A609" s="2" t="n"/>
@@ -30518,7 +29905,6 @@
       <c r="AR609" s="2" t="n"/>
       <c r="AS609" s="2" t="n"/>
       <c r="AT609" s="2" t="n"/>
-      <c r="AU609" s="2" t="n"/>
     </row>
     <row r="610">
       <c r="A610" s="2" t="n"/>
@@ -30567,7 +29953,6 @@
       <c r="AR610" s="2" t="n"/>
       <c r="AS610" s="2" t="n"/>
       <c r="AT610" s="2" t="n"/>
-      <c r="AU610" s="2" t="n"/>
     </row>
     <row r="611">
       <c r="A611" s="2" t="n"/>
@@ -30616,7 +30001,6 @@
       <c r="AR611" s="2" t="n"/>
       <c r="AS611" s="2" t="n"/>
       <c r="AT611" s="2" t="n"/>
-      <c r="AU611" s="2" t="n"/>
     </row>
     <row r="612">
       <c r="A612" s="2" t="n"/>
@@ -30665,7 +30049,6 @@
       <c r="AR612" s="2" t="n"/>
       <c r="AS612" s="2" t="n"/>
       <c r="AT612" s="2" t="n"/>
-      <c r="AU612" s="2" t="n"/>
     </row>
     <row r="613">
       <c r="A613" s="2" t="n"/>
@@ -30714,7 +30097,6 @@
       <c r="AR613" s="2" t="n"/>
       <c r="AS613" s="2" t="n"/>
       <c r="AT613" s="2" t="n"/>
-      <c r="AU613" s="2" t="n"/>
     </row>
     <row r="614">
       <c r="A614" s="2" t="n"/>
@@ -30763,7 +30145,6 @@
       <c r="AR614" s="2" t="n"/>
       <c r="AS614" s="2" t="n"/>
       <c r="AT614" s="2" t="n"/>
-      <c r="AU614" s="2" t="n"/>
     </row>
     <row r="615">
       <c r="A615" s="2" t="n"/>
@@ -30812,7 +30193,6 @@
       <c r="AR615" s="2" t="n"/>
       <c r="AS615" s="2" t="n"/>
       <c r="AT615" s="2" t="n"/>
-      <c r="AU615" s="2" t="n"/>
     </row>
     <row r="616">
       <c r="A616" s="2" t="n"/>
@@ -30861,7 +30241,6 @@
       <c r="AR616" s="2" t="n"/>
       <c r="AS616" s="2" t="n"/>
       <c r="AT616" s="2" t="n"/>
-      <c r="AU616" s="2" t="n"/>
     </row>
     <row r="617">
       <c r="A617" s="2" t="n"/>
@@ -30910,7 +30289,6 @@
       <c r="AR617" s="2" t="n"/>
       <c r="AS617" s="2" t="n"/>
       <c r="AT617" s="2" t="n"/>
-      <c r="AU617" s="2" t="n"/>
     </row>
     <row r="618">
       <c r="A618" s="2" t="n"/>
@@ -30959,7 +30337,6 @@
       <c r="AR618" s="2" t="n"/>
       <c r="AS618" s="2" t="n"/>
       <c r="AT618" s="2" t="n"/>
-      <c r="AU618" s="2" t="n"/>
     </row>
     <row r="619">
       <c r="A619" s="2" t="n"/>
@@ -31008,7 +30385,6 @@
       <c r="AR619" s="2" t="n"/>
       <c r="AS619" s="2" t="n"/>
       <c r="AT619" s="2" t="n"/>
-      <c r="AU619" s="2" t="n"/>
     </row>
     <row r="620">
       <c r="A620" s="2" t="n"/>
@@ -31057,7 +30433,6 @@
       <c r="AR620" s="2" t="n"/>
       <c r="AS620" s="2" t="n"/>
       <c r="AT620" s="2" t="n"/>
-      <c r="AU620" s="2" t="n"/>
     </row>
     <row r="621">
       <c r="A621" s="2" t="n"/>
@@ -31106,7 +30481,6 @@
       <c r="AR621" s="2" t="n"/>
       <c r="AS621" s="2" t="n"/>
       <c r="AT621" s="2" t="n"/>
-      <c r="AU621" s="2" t="n"/>
     </row>
     <row r="622">
       <c r="A622" s="2" t="n"/>
@@ -31155,7 +30529,6 @@
       <c r="AR622" s="2" t="n"/>
       <c r="AS622" s="2" t="n"/>
       <c r="AT622" s="2" t="n"/>
-      <c r="AU622" s="2" t="n"/>
     </row>
     <row r="623">
       <c r="A623" s="2" t="n"/>
@@ -31204,7 +30577,6 @@
       <c r="AR623" s="2" t="n"/>
       <c r="AS623" s="2" t="n"/>
       <c r="AT623" s="2" t="n"/>
-      <c r="AU623" s="2" t="n"/>
     </row>
     <row r="624">
       <c r="A624" s="2" t="n"/>
@@ -31253,7 +30625,6 @@
       <c r="AR624" s="2" t="n"/>
       <c r="AS624" s="2" t="n"/>
       <c r="AT624" s="2" t="n"/>
-      <c r="AU624" s="2" t="n"/>
     </row>
     <row r="625">
       <c r="A625" s="2" t="n"/>
@@ -31302,7 +30673,6 @@
       <c r="AR625" s="2" t="n"/>
       <c r="AS625" s="2" t="n"/>
       <c r="AT625" s="2" t="n"/>
-      <c r="AU625" s="2" t="n"/>
     </row>
     <row r="626">
       <c r="A626" s="2" t="n"/>
@@ -31351,7 +30721,6 @@
       <c r="AR626" s="2" t="n"/>
       <c r="AS626" s="2" t="n"/>
       <c r="AT626" s="2" t="n"/>
-      <c r="AU626" s="2" t="n"/>
     </row>
     <row r="627">
       <c r="A627" s="2" t="n"/>
@@ -31400,7 +30769,6 @@
       <c r="AR627" s="2" t="n"/>
       <c r="AS627" s="2" t="n"/>
       <c r="AT627" s="2" t="n"/>
-      <c r="AU627" s="2" t="n"/>
     </row>
     <row r="628">
       <c r="A628" s="2" t="n"/>
@@ -31449,7 +30817,6 @@
       <c r="AR628" s="2" t="n"/>
       <c r="AS628" s="2" t="n"/>
       <c r="AT628" s="2" t="n"/>
-      <c r="AU628" s="2" t="n"/>
     </row>
     <row r="629">
       <c r="A629" s="2" t="n"/>
@@ -31498,7 +30865,6 @@
       <c r="AR629" s="2" t="n"/>
       <c r="AS629" s="2" t="n"/>
       <c r="AT629" s="2" t="n"/>
-      <c r="AU629" s="2" t="n"/>
     </row>
     <row r="630">
       <c r="A630" s="2" t="n"/>
@@ -31547,7 +30913,6 @@
       <c r="AR630" s="2" t="n"/>
       <c r="AS630" s="2" t="n"/>
       <c r="AT630" s="2" t="n"/>
-      <c r="AU630" s="2" t="n"/>
     </row>
     <row r="631">
       <c r="A631" s="2" t="n"/>
@@ -31596,7 +30961,6 @@
       <c r="AR631" s="2" t="n"/>
       <c r="AS631" s="2" t="n"/>
       <c r="AT631" s="2" t="n"/>
-      <c r="AU631" s="2" t="n"/>
     </row>
     <row r="632">
       <c r="A632" s="2" t="n"/>
@@ -31645,7 +31009,6 @@
       <c r="AR632" s="2" t="n"/>
       <c r="AS632" s="2" t="n"/>
       <c r="AT632" s="2" t="n"/>
-      <c r="AU632" s="2" t="n"/>
     </row>
     <row r="633">
       <c r="A633" s="2" t="n"/>
@@ -31694,7 +31057,6 @@
       <c r="AR633" s="2" t="n"/>
       <c r="AS633" s="2" t="n"/>
       <c r="AT633" s="2" t="n"/>
-      <c r="AU633" s="2" t="n"/>
     </row>
     <row r="634">
       <c r="A634" s="2" t="n"/>
@@ -31743,7 +31105,6 @@
       <c r="AR634" s="2" t="n"/>
       <c r="AS634" s="2" t="n"/>
       <c r="AT634" s="2" t="n"/>
-      <c r="AU634" s="2" t="n"/>
     </row>
     <row r="635">
       <c r="A635" s="2" t="n"/>
@@ -31792,7 +31153,6 @@
       <c r="AR635" s="2" t="n"/>
       <c r="AS635" s="2" t="n"/>
       <c r="AT635" s="2" t="n"/>
-      <c r="AU635" s="2" t="n"/>
     </row>
     <row r="636">
       <c r="A636" s="2" t="n"/>
@@ -31841,7 +31201,6 @@
       <c r="AR636" s="2" t="n"/>
       <c r="AS636" s="2" t="n"/>
       <c r="AT636" s="2" t="n"/>
-      <c r="AU636" s="2" t="n"/>
     </row>
     <row r="637">
       <c r="A637" s="2" t="n"/>
@@ -31890,7 +31249,6 @@
       <c r="AR637" s="2" t="n"/>
       <c r="AS637" s="2" t="n"/>
       <c r="AT637" s="2" t="n"/>
-      <c r="AU637" s="2" t="n"/>
     </row>
     <row r="638">
       <c r="A638" s="2" t="n"/>
@@ -31939,7 +31297,6 @@
       <c r="AR638" s="2" t="n"/>
       <c r="AS638" s="2" t="n"/>
       <c r="AT638" s="2" t="n"/>
-      <c r="AU638" s="2" t="n"/>
     </row>
     <row r="639">
       <c r="A639" s="2" t="n"/>
@@ -31988,7 +31345,6 @@
       <c r="AR639" s="2" t="n"/>
       <c r="AS639" s="2" t="n"/>
       <c r="AT639" s="2" t="n"/>
-      <c r="AU639" s="2" t="n"/>
     </row>
     <row r="640">
       <c r="A640" s="2" t="n"/>
@@ -32037,7 +31393,6 @@
       <c r="AR640" s="2" t="n"/>
       <c r="AS640" s="2" t="n"/>
       <c r="AT640" s="2" t="n"/>
-      <c r="AU640" s="2" t="n"/>
     </row>
     <row r="641">
       <c r="A641" s="2" t="n"/>
@@ -32086,7 +31441,6 @@
       <c r="AR641" s="2" t="n"/>
       <c r="AS641" s="2" t="n"/>
       <c r="AT641" s="2" t="n"/>
-      <c r="AU641" s="2" t="n"/>
     </row>
     <row r="642">
       <c r="A642" s="2" t="n"/>
@@ -32135,7 +31489,6 @@
       <c r="AR642" s="2" t="n"/>
       <c r="AS642" s="2" t="n"/>
       <c r="AT642" s="2" t="n"/>
-      <c r="AU642" s="2" t="n"/>
     </row>
     <row r="643">
       <c r="A643" s="2" t="n"/>
@@ -32184,7 +31537,6 @@
       <c r="AR643" s="2" t="n"/>
       <c r="AS643" s="2" t="n"/>
       <c r="AT643" s="2" t="n"/>
-      <c r="AU643" s="2" t="n"/>
     </row>
     <row r="644">
       <c r="A644" s="2" t="n"/>
@@ -32233,7 +31585,6 @@
       <c r="AR644" s="2" t="n"/>
       <c r="AS644" s="2" t="n"/>
       <c r="AT644" s="2" t="n"/>
-      <c r="AU644" s="2" t="n"/>
     </row>
     <row r="645">
       <c r="A645" s="2" t="n"/>
@@ -32282,7 +31633,6 @@
       <c r="AR645" s="2" t="n"/>
       <c r="AS645" s="2" t="n"/>
       <c r="AT645" s="2" t="n"/>
-      <c r="AU645" s="2" t="n"/>
     </row>
     <row r="646">
       <c r="A646" s="2" t="n"/>
@@ -32331,7 +31681,6 @@
       <c r="AR646" s="2" t="n"/>
       <c r="AS646" s="2" t="n"/>
       <c r="AT646" s="2" t="n"/>
-      <c r="AU646" s="2" t="n"/>
     </row>
     <row r="647">
       <c r="A647" s="2" t="n"/>
@@ -32380,7 +31729,6 @@
       <c r="AR647" s="2" t="n"/>
       <c r="AS647" s="2" t="n"/>
       <c r="AT647" s="2" t="n"/>
-      <c r="AU647" s="2" t="n"/>
     </row>
     <row r="648">
       <c r="A648" s="2" t="n"/>
@@ -32429,7 +31777,6 @@
       <c r="AR648" s="2" t="n"/>
       <c r="AS648" s="2" t="n"/>
       <c r="AT648" s="2" t="n"/>
-      <c r="AU648" s="2" t="n"/>
     </row>
     <row r="649">
       <c r="A649" s="2" t="n"/>
@@ -32478,7 +31825,6 @@
       <c r="AR649" s="2" t="n"/>
       <c r="AS649" s="2" t="n"/>
       <c r="AT649" s="2" t="n"/>
-      <c r="AU649" s="2" t="n"/>
     </row>
     <row r="650">
       <c r="A650" s="2" t="n"/>
@@ -32527,7 +31873,6 @@
       <c r="AR650" s="2" t="n"/>
       <c r="AS650" s="2" t="n"/>
       <c r="AT650" s="2" t="n"/>
-      <c r="AU650" s="2" t="n"/>
     </row>
     <row r="651">
       <c r="A651" s="2" t="n"/>
@@ -32576,7 +31921,6 @@
       <c r="AR651" s="2" t="n"/>
       <c r="AS651" s="2" t="n"/>
       <c r="AT651" s="2" t="n"/>
-      <c r="AU651" s="2" t="n"/>
     </row>
     <row r="652">
       <c r="A652" s="2" t="n"/>
@@ -32625,7 +31969,6 @@
       <c r="AR652" s="2" t="n"/>
       <c r="AS652" s="2" t="n"/>
       <c r="AT652" s="2" t="n"/>
-      <c r="AU652" s="2" t="n"/>
     </row>
     <row r="653">
       <c r="A653" s="2" t="n"/>
@@ -32674,7 +32017,6 @@
       <c r="AR653" s="2" t="n"/>
       <c r="AS653" s="2" t="n"/>
       <c r="AT653" s="2" t="n"/>
-      <c r="AU653" s="2" t="n"/>
     </row>
     <row r="654">
       <c r="A654" s="2" t="n"/>
@@ -32723,7 +32065,6 @@
       <c r="AR654" s="2" t="n"/>
       <c r="AS654" s="2" t="n"/>
       <c r="AT654" s="2" t="n"/>
-      <c r="AU654" s="2" t="n"/>
     </row>
     <row r="655">
       <c r="A655" s="2" t="n"/>
@@ -32772,7 +32113,6 @@
       <c r="AR655" s="2" t="n"/>
       <c r="AS655" s="2" t="n"/>
       <c r="AT655" s="2" t="n"/>
-      <c r="AU655" s="2" t="n"/>
     </row>
     <row r="656">
       <c r="A656" s="2" t="n"/>
@@ -32821,7 +32161,6 @@
       <c r="AR656" s="2" t="n"/>
       <c r="AS656" s="2" t="n"/>
       <c r="AT656" s="2" t="n"/>
-      <c r="AU656" s="2" t="n"/>
     </row>
     <row r="657">
       <c r="A657" s="2" t="n"/>
@@ -32870,7 +32209,6 @@
       <c r="AR657" s="2" t="n"/>
       <c r="AS657" s="2" t="n"/>
       <c r="AT657" s="2" t="n"/>
-      <c r="AU657" s="2" t="n"/>
     </row>
     <row r="658">
       <c r="A658" s="2" t="n"/>
@@ -32919,7 +32257,6 @@
       <c r="AR658" s="2" t="n"/>
       <c r="AS658" s="2" t="n"/>
       <c r="AT658" s="2" t="n"/>
-      <c r="AU658" s="2" t="n"/>
     </row>
     <row r="659">
       <c r="A659" s="2" t="n"/>
@@ -32968,7 +32305,6 @@
       <c r="AR659" s="2" t="n"/>
       <c r="AS659" s="2" t="n"/>
       <c r="AT659" s="2" t="n"/>
-      <c r="AU659" s="2" t="n"/>
     </row>
     <row r="660">
       <c r="A660" s="2" t="n"/>
@@ -33017,7 +32353,6 @@
       <c r="AR660" s="2" t="n"/>
       <c r="AS660" s="2" t="n"/>
       <c r="AT660" s="2" t="n"/>
-      <c r="AU660" s="2" t="n"/>
     </row>
     <row r="661">
       <c r="A661" s="2" t="n"/>
@@ -33066,7 +32401,6 @@
       <c r="AR661" s="2" t="n"/>
       <c r="AS661" s="2" t="n"/>
       <c r="AT661" s="2" t="n"/>
-      <c r="AU661" s="2" t="n"/>
     </row>
     <row r="662">
       <c r="A662" s="2" t="n"/>
@@ -33115,7 +32449,6 @@
       <c r="AR662" s="2" t="n"/>
       <c r="AS662" s="2" t="n"/>
       <c r="AT662" s="2" t="n"/>
-      <c r="AU662" s="2" t="n"/>
     </row>
     <row r="663">
       <c r="A663" s="2" t="n"/>
@@ -33164,7 +32497,6 @@
       <c r="AR663" s="2" t="n"/>
       <c r="AS663" s="2" t="n"/>
       <c r="AT663" s="2" t="n"/>
-      <c r="AU663" s="2" t="n"/>
     </row>
     <row r="664">
       <c r="A664" s="2" t="n"/>
@@ -33213,7 +32545,6 @@
       <c r="AR664" s="2" t="n"/>
       <c r="AS664" s="2" t="n"/>
       <c r="AT664" s="2" t="n"/>
-      <c r="AU664" s="2" t="n"/>
     </row>
     <row r="665">
       <c r="A665" s="2" t="n"/>
@@ -33262,7 +32593,6 @@
       <c r="AR665" s="2" t="n"/>
       <c r="AS665" s="2" t="n"/>
       <c r="AT665" s="2" t="n"/>
-      <c r="AU665" s="2" t="n"/>
     </row>
     <row r="666">
       <c r="A666" s="2" t="n"/>
@@ -33311,7 +32641,6 @@
       <c r="AR666" s="2" t="n"/>
       <c r="AS666" s="2" t="n"/>
       <c r="AT666" s="2" t="n"/>
-      <c r="AU666" s="2" t="n"/>
     </row>
     <row r="667">
       <c r="A667" s="2" t="n"/>
@@ -33360,7 +32689,6 @@
       <c r="AR667" s="2" t="n"/>
       <c r="AS667" s="2" t="n"/>
       <c r="AT667" s="2" t="n"/>
-      <c r="AU667" s="2" t="n"/>
     </row>
     <row r="668">
       <c r="A668" s="2" t="n"/>
@@ -33409,7 +32737,6 @@
       <c r="AR668" s="2" t="n"/>
       <c r="AS668" s="2" t="n"/>
       <c r="AT668" s="2" t="n"/>
-      <c r="AU668" s="2" t="n"/>
     </row>
     <row r="669">
       <c r="A669" s="2" t="n"/>
@@ -33458,7 +32785,6 @@
       <c r="AR669" s="2" t="n"/>
       <c r="AS669" s="2" t="n"/>
       <c r="AT669" s="2" t="n"/>
-      <c r="AU669" s="2" t="n"/>
     </row>
     <row r="670">
       <c r="A670" s="2" t="n"/>
@@ -33507,7 +32833,6 @@
       <c r="AR670" s="2" t="n"/>
       <c r="AS670" s="2" t="n"/>
       <c r="AT670" s="2" t="n"/>
-      <c r="AU670" s="2" t="n"/>
     </row>
     <row r="671">
       <c r="A671" s="2" t="n"/>
@@ -33556,7 +32881,6 @@
       <c r="AR671" s="2" t="n"/>
       <c r="AS671" s="2" t="n"/>
       <c r="AT671" s="2" t="n"/>
-      <c r="AU671" s="2" t="n"/>
     </row>
     <row r="672">
       <c r="A672" s="2" t="n"/>
@@ -33605,7 +32929,6 @@
       <c r="AR672" s="2" t="n"/>
       <c r="AS672" s="2" t="n"/>
       <c r="AT672" s="2" t="n"/>
-      <c r="AU672" s="2" t="n"/>
     </row>
     <row r="673">
       <c r="A673" s="2" t="n"/>
@@ -33654,7 +32977,6 @@
       <c r="AR673" s="2" t="n"/>
       <c r="AS673" s="2" t="n"/>
       <c r="AT673" s="2" t="n"/>
-      <c r="AU673" s="2" t="n"/>
     </row>
     <row r="674">
       <c r="A674" s="2" t="n"/>
@@ -33703,7 +33025,6 @@
       <c r="AR674" s="2" t="n"/>
       <c r="AS674" s="2" t="n"/>
       <c r="AT674" s="2" t="n"/>
-      <c r="AU674" s="2" t="n"/>
     </row>
     <row r="675">
       <c r="A675" s="2" t="n"/>
@@ -33752,7 +33073,6 @@
       <c r="AR675" s="2" t="n"/>
       <c r="AS675" s="2" t="n"/>
       <c r="AT675" s="2" t="n"/>
-      <c r="AU675" s="2" t="n"/>
     </row>
     <row r="676">
       <c r="A676" s="2" t="n"/>
@@ -33801,7 +33121,6 @@
       <c r="AR676" s="2" t="n"/>
       <c r="AS676" s="2" t="n"/>
       <c r="AT676" s="2" t="n"/>
-      <c r="AU676" s="2" t="n"/>
     </row>
     <row r="677">
       <c r="A677" s="2" t="n"/>
@@ -33850,7 +33169,6 @@
       <c r="AR677" s="2" t="n"/>
       <c r="AS677" s="2" t="n"/>
       <c r="AT677" s="2" t="n"/>
-      <c r="AU677" s="2" t="n"/>
     </row>
     <row r="678">
       <c r="A678" s="2" t="n"/>
@@ -33899,7 +33217,6 @@
       <c r="AR678" s="2" t="n"/>
       <c r="AS678" s="2" t="n"/>
       <c r="AT678" s="2" t="n"/>
-      <c r="AU678" s="2" t="n"/>
     </row>
     <row r="679">
       <c r="A679" s="2" t="n"/>
@@ -33948,7 +33265,6 @@
       <c r="AR679" s="2" t="n"/>
       <c r="AS679" s="2" t="n"/>
       <c r="AT679" s="2" t="n"/>
-      <c r="AU679" s="2" t="n"/>
     </row>
     <row r="680">
       <c r="A680" s="2" t="n"/>
@@ -33997,7 +33313,6 @@
       <c r="AR680" s="2" t="n"/>
       <c r="AS680" s="2" t="n"/>
       <c r="AT680" s="2" t="n"/>
-      <c r="AU680" s="2" t="n"/>
     </row>
     <row r="681">
       <c r="A681" s="2" t="n"/>
@@ -34046,7 +33361,6 @@
       <c r="AR681" s="2" t="n"/>
       <c r="AS681" s="2" t="n"/>
       <c r="AT681" s="2" t="n"/>
-      <c r="AU681" s="2" t="n"/>
     </row>
     <row r="682">
       <c r="A682" s="2" t="n"/>
@@ -34095,7 +33409,6 @@
       <c r="AR682" s="2" t="n"/>
       <c r="AS682" s="2" t="n"/>
       <c r="AT682" s="2" t="n"/>
-      <c r="AU682" s="2" t="n"/>
     </row>
     <row r="683">
       <c r="A683" s="2" t="n"/>
@@ -34144,7 +33457,6 @@
       <c r="AR683" s="2" t="n"/>
       <c r="AS683" s="2" t="n"/>
       <c r="AT683" s="2" t="n"/>
-      <c r="AU683" s="2" t="n"/>
     </row>
     <row r="684">
       <c r="A684" s="2" t="n"/>
@@ -34193,7 +33505,6 @@
       <c r="AR684" s="2" t="n"/>
       <c r="AS684" s="2" t="n"/>
       <c r="AT684" s="2" t="n"/>
-      <c r="AU684" s="2" t="n"/>
     </row>
     <row r="685">
       <c r="A685" s="2" t="n"/>
@@ -34242,7 +33553,6 @@
       <c r="AR685" s="2" t="n"/>
       <c r="AS685" s="2" t="n"/>
       <c r="AT685" s="2" t="n"/>
-      <c r="AU685" s="2" t="n"/>
     </row>
     <row r="686">
       <c r="A686" s="2" t="n"/>
@@ -34291,7 +33601,6 @@
       <c r="AR686" s="2" t="n"/>
       <c r="AS686" s="2" t="n"/>
       <c r="AT686" s="2" t="n"/>
-      <c r="AU686" s="2" t="n"/>
     </row>
     <row r="687">
       <c r="A687" s="2" t="n"/>
@@ -34340,7 +33649,6 @@
       <c r="AR687" s="2" t="n"/>
       <c r="AS687" s="2" t="n"/>
       <c r="AT687" s="2" t="n"/>
-      <c r="AU687" s="2" t="n"/>
     </row>
     <row r="688">
       <c r="A688" s="2" t="n"/>
@@ -34389,7 +33697,6 @@
       <c r="AR688" s="2" t="n"/>
       <c r="AS688" s="2" t="n"/>
       <c r="AT688" s="2" t="n"/>
-      <c r="AU688" s="2" t="n"/>
     </row>
     <row r="689">
       <c r="A689" s="2" t="n"/>
@@ -34438,7 +33745,6 @@
       <c r="AR689" s="2" t="n"/>
       <c r="AS689" s="2" t="n"/>
       <c r="AT689" s="2" t="n"/>
-      <c r="AU689" s="2" t="n"/>
     </row>
     <row r="690">
       <c r="A690" s="2" t="n"/>
@@ -34487,7 +33793,6 @@
       <c r="AR690" s="2" t="n"/>
       <c r="AS690" s="2" t="n"/>
       <c r="AT690" s="2" t="n"/>
-      <c r="AU690" s="2" t="n"/>
     </row>
     <row r="691">
       <c r="A691" s="2" t="n"/>
@@ -34536,7 +33841,6 @@
       <c r="AR691" s="2" t="n"/>
       <c r="AS691" s="2" t="n"/>
       <c r="AT691" s="2" t="n"/>
-      <c r="AU691" s="2" t="n"/>
     </row>
     <row r="692">
       <c r="A692" s="2" t="n"/>
@@ -34585,7 +33889,6 @@
       <c r="AR692" s="2" t="n"/>
       <c r="AS692" s="2" t="n"/>
       <c r="AT692" s="2" t="n"/>
-      <c r="AU692" s="2" t="n"/>
     </row>
     <row r="693">
       <c r="A693" s="2" t="n"/>
@@ -34634,7 +33937,6 @@
       <c r="AR693" s="2" t="n"/>
       <c r="AS693" s="2" t="n"/>
       <c r="AT693" s="2" t="n"/>
-      <c r="AU693" s="2" t="n"/>
     </row>
     <row r="694">
       <c r="A694" s="2" t="n"/>
@@ -34683,7 +33985,6 @@
       <c r="AR694" s="2" t="n"/>
       <c r="AS694" s="2" t="n"/>
       <c r="AT694" s="2" t="n"/>
-      <c r="AU694" s="2" t="n"/>
     </row>
     <row r="695">
       <c r="A695" s="2" t="n"/>
@@ -34732,7 +34033,6 @@
       <c r="AR695" s="2" t="n"/>
       <c r="AS695" s="2" t="n"/>
       <c r="AT695" s="2" t="n"/>
-      <c r="AU695" s="2" t="n"/>
     </row>
     <row r="696">
       <c r="A696" s="2" t="n"/>
@@ -34781,7 +34081,6 @@
       <c r="AR696" s="2" t="n"/>
       <c r="AS696" s="2" t="n"/>
       <c r="AT696" s="2" t="n"/>
-      <c r="AU696" s="2" t="n"/>
     </row>
     <row r="697">
       <c r="A697" s="2" t="n"/>
@@ -34830,7 +34129,6 @@
       <c r="AR697" s="2" t="n"/>
       <c r="AS697" s="2" t="n"/>
       <c r="AT697" s="2" t="n"/>
-      <c r="AU697" s="2" t="n"/>
     </row>
     <row r="698">
       <c r="A698" s="2" t="n"/>
@@ -34879,7 +34177,6 @@
       <c r="AR698" s="2" t="n"/>
       <c r="AS698" s="2" t="n"/>
       <c r="AT698" s="2" t="n"/>
-      <c r="AU698" s="2" t="n"/>
     </row>
     <row r="699">
       <c r="A699" s="2" t="n"/>
@@ -34928,7 +34225,6 @@
       <c r="AR699" s="2" t="n"/>
       <c r="AS699" s="2" t="n"/>
       <c r="AT699" s="2" t="n"/>
-      <c r="AU699" s="2" t="n"/>
     </row>
     <row r="700">
       <c r="A700" s="2" t="n"/>
@@ -34977,7 +34273,6 @@
       <c r="AR700" s="2" t="n"/>
       <c r="AS700" s="2" t="n"/>
       <c r="AT700" s="2" t="n"/>
-      <c r="AU700" s="2" t="n"/>
     </row>
     <row r="701">
       <c r="A701" s="2" t="n"/>
@@ -35026,7 +34321,6 @@
       <c r="AR701" s="2" t="n"/>
       <c r="AS701" s="2" t="n"/>
       <c r="AT701" s="2" t="n"/>
-      <c r="AU701" s="2" t="n"/>
     </row>
     <row r="702">
       <c r="A702" s="2" t="n"/>
@@ -35075,7 +34369,6 @@
       <c r="AR702" s="2" t="n"/>
       <c r="AS702" s="2" t="n"/>
       <c r="AT702" s="2" t="n"/>
-      <c r="AU702" s="2" t="n"/>
     </row>
     <row r="703">
       <c r="A703" s="2" t="n"/>
@@ -35124,7 +34417,6 @@
       <c r="AR703" s="2" t="n"/>
       <c r="AS703" s="2" t="n"/>
       <c r="AT703" s="2" t="n"/>
-      <c r="AU703" s="2" t="n"/>
     </row>
     <row r="704">
       <c r="A704" s="2" t="n"/>
@@ -35173,7 +34465,6 @@
       <c r="AR704" s="2" t="n"/>
       <c r="AS704" s="2" t="n"/>
       <c r="AT704" s="2" t="n"/>
-      <c r="AU704" s="2" t="n"/>
     </row>
     <row r="705">
       <c r="A705" s="2" t="n"/>
@@ -35222,7 +34513,6 @@
       <c r="AR705" s="2" t="n"/>
       <c r="AS705" s="2" t="n"/>
       <c r="AT705" s="2" t="n"/>
-      <c r="AU705" s="2" t="n"/>
     </row>
     <row r="706">
       <c r="A706" s="2" t="n"/>
@@ -35271,7 +34561,6 @@
       <c r="AR706" s="2" t="n"/>
       <c r="AS706" s="2" t="n"/>
       <c r="AT706" s="2" t="n"/>
-      <c r="AU706" s="2" t="n"/>
     </row>
     <row r="707">
       <c r="A707" s="2" t="n"/>
@@ -35320,7 +34609,6 @@
       <c r="AR707" s="2" t="n"/>
       <c r="AS707" s="2" t="n"/>
       <c r="AT707" s="2" t="n"/>
-      <c r="AU707" s="2" t="n"/>
     </row>
     <row r="708">
       <c r="A708" s="2" t="n"/>
@@ -35369,7 +34657,6 @@
       <c r="AR708" s="2" t="n"/>
       <c r="AS708" s="2" t="n"/>
       <c r="AT708" s="2" t="n"/>
-      <c r="AU708" s="2" t="n"/>
     </row>
     <row r="709">
       <c r="A709" s="2" t="n"/>
@@ -35418,7 +34705,6 @@
       <c r="AR709" s="2" t="n"/>
       <c r="AS709" s="2" t="n"/>
       <c r="AT709" s="2" t="n"/>
-      <c r="AU709" s="2" t="n"/>
     </row>
     <row r="710">
       <c r="A710" s="2" t="n"/>
@@ -35467,7 +34753,6 @@
       <c r="AR710" s="2" t="n"/>
       <c r="AS710" s="2" t="n"/>
       <c r="AT710" s="2" t="n"/>
-      <c r="AU710" s="2" t="n"/>
     </row>
     <row r="711">
       <c r="A711" s="2" t="n"/>
@@ -35516,7 +34801,6 @@
       <c r="AR711" s="2" t="n"/>
       <c r="AS711" s="2" t="n"/>
       <c r="AT711" s="2" t="n"/>
-      <c r="AU711" s="2" t="n"/>
     </row>
     <row r="712">
       <c r="A712" s="2" t="n"/>
@@ -35565,7 +34849,6 @@
       <c r="AR712" s="2" t="n"/>
       <c r="AS712" s="2" t="n"/>
       <c r="AT712" s="2" t="n"/>
-      <c r="AU712" s="2" t="n"/>
     </row>
     <row r="713">
       <c r="A713" s="2" t="n"/>
@@ -35614,7 +34897,6 @@
       <c r="AR713" s="2" t="n"/>
       <c r="AS713" s="2" t="n"/>
       <c r="AT713" s="2" t="n"/>
-      <c r="AU713" s="2" t="n"/>
     </row>
     <row r="714">
       <c r="A714" s="2" t="n"/>
@@ -35663,7 +34945,6 @@
       <c r="AR714" s="2" t="n"/>
       <c r="AS714" s="2" t="n"/>
       <c r="AT714" s="2" t="n"/>
-      <c r="AU714" s="2" t="n"/>
     </row>
     <row r="715">
       <c r="A715" s="2" t="n"/>
@@ -35712,7 +34993,6 @@
       <c r="AR715" s="2" t="n"/>
       <c r="AS715" s="2" t="n"/>
       <c r="AT715" s="2" t="n"/>
-      <c r="AU715" s="2" t="n"/>
     </row>
     <row r="716">
       <c r="A716" s="2" t="n"/>
@@ -35761,7 +35041,6 @@
       <c r="AR716" s="2" t="n"/>
       <c r="AS716" s="2" t="n"/>
       <c r="AT716" s="2" t="n"/>
-      <c r="AU716" s="2" t="n"/>
     </row>
     <row r="717">
       <c r="A717" s="2" t="n"/>
@@ -35810,7 +35089,6 @@
       <c r="AR717" s="2" t="n"/>
       <c r="AS717" s="2" t="n"/>
       <c r="AT717" s="2" t="n"/>
-      <c r="AU717" s="2" t="n"/>
     </row>
     <row r="718">
       <c r="A718" s="2" t="n"/>
@@ -35859,7 +35137,6 @@
       <c r="AR718" s="2" t="n"/>
       <c r="AS718" s="2" t="n"/>
       <c r="AT718" s="2" t="n"/>
-      <c r="AU718" s="2" t="n"/>
     </row>
     <row r="719">
       <c r="A719" s="2" t="n"/>
@@ -35908,7 +35185,6 @@
       <c r="AR719" s="2" t="n"/>
       <c r="AS719" s="2" t="n"/>
       <c r="AT719" s="2" t="n"/>
-      <c r="AU719" s="2" t="n"/>
     </row>
     <row r="720">
       <c r="A720" s="2" t="n"/>
@@ -35957,7 +35233,6 @@
       <c r="AR720" s="2" t="n"/>
       <c r="AS720" s="2" t="n"/>
       <c r="AT720" s="2" t="n"/>
-      <c r="AU720" s="2" t="n"/>
     </row>
     <row r="721">
       <c r="A721" s="2" t="n"/>
@@ -36006,7 +35281,6 @@
       <c r="AR721" s="2" t="n"/>
       <c r="AS721" s="2" t="n"/>
       <c r="AT721" s="2" t="n"/>
-      <c r="AU721" s="2" t="n"/>
     </row>
     <row r="722">
       <c r="A722" s="2" t="n"/>
@@ -36055,7 +35329,6 @@
       <c r="AR722" s="2" t="n"/>
       <c r="AS722" s="2" t="n"/>
       <c r="AT722" s="2" t="n"/>
-      <c r="AU722" s="2" t="n"/>
     </row>
     <row r="723">
       <c r="A723" s="2" t="n"/>
@@ -36104,7 +35377,6 @@
       <c r="AR723" s="2" t="n"/>
       <c r="AS723" s="2" t="n"/>
       <c r="AT723" s="2" t="n"/>
-      <c r="AU723" s="2" t="n"/>
     </row>
     <row r="724">
       <c r="A724" s="2" t="n"/>
@@ -36153,7 +35425,6 @@
       <c r="AR724" s="2" t="n"/>
       <c r="AS724" s="2" t="n"/>
       <c r="AT724" s="2" t="n"/>
-      <c r="AU724" s="2" t="n"/>
     </row>
     <row r="725">
       <c r="A725" s="2" t="n"/>
@@ -36202,7 +35473,6 @@
       <c r="AR725" s="2" t="n"/>
       <c r="AS725" s="2" t="n"/>
       <c r="AT725" s="2" t="n"/>
-      <c r="AU725" s="2" t="n"/>
     </row>
     <row r="726">
       <c r="A726" s="2" t="n"/>
@@ -36251,7 +35521,6 @@
       <c r="AR726" s="2" t="n"/>
       <c r="AS726" s="2" t="n"/>
       <c r="AT726" s="2" t="n"/>
-      <c r="AU726" s="2" t="n"/>
     </row>
     <row r="727">
       <c r="A727" s="2" t="n"/>
@@ -36300,7 +35569,6 @@
       <c r="AR727" s="2" t="n"/>
       <c r="AS727" s="2" t="n"/>
       <c r="AT727" s="2" t="n"/>
-      <c r="AU727" s="2" t="n"/>
     </row>
     <row r="728">
       <c r="A728" s="2" t="n"/>
@@ -36349,7 +35617,6 @@
       <c r="AR728" s="2" t="n"/>
       <c r="AS728" s="2" t="n"/>
       <c r="AT728" s="2" t="n"/>
-      <c r="AU728" s="2" t="n"/>
     </row>
     <row r="729">
       <c r="A729" s="2" t="n"/>
@@ -36398,7 +35665,6 @@
       <c r="AR729" s="2" t="n"/>
       <c r="AS729" s="2" t="n"/>
       <c r="AT729" s="2" t="n"/>
-      <c r="AU729" s="2" t="n"/>
     </row>
     <row r="730">
       <c r="A730" s="2" t="n"/>
@@ -36447,7 +35713,6 @@
       <c r="AR730" s="2" t="n"/>
       <c r="AS730" s="2" t="n"/>
       <c r="AT730" s="2" t="n"/>
-      <c r="AU730" s="2" t="n"/>
     </row>
     <row r="731">
       <c r="A731" s="2" t="n"/>
@@ -36496,7 +35761,6 @@
       <c r="AR731" s="2" t="n"/>
       <c r="AS731" s="2" t="n"/>
       <c r="AT731" s="2" t="n"/>
-      <c r="AU731" s="2" t="n"/>
     </row>
     <row r="732">
       <c r="A732" s="2" t="n"/>
@@ -36545,7 +35809,6 @@
       <c r="AR732" s="2" t="n"/>
       <c r="AS732" s="2" t="n"/>
       <c r="AT732" s="2" t="n"/>
-      <c r="AU732" s="2" t="n"/>
     </row>
     <row r="733">
       <c r="A733" s="2" t="n"/>
@@ -36594,7 +35857,6 @@
       <c r="AR733" s="2" t="n"/>
       <c r="AS733" s="2" t="n"/>
       <c r="AT733" s="2" t="n"/>
-      <c r="AU733" s="2" t="n"/>
     </row>
     <row r="734">
       <c r="A734" s="2" t="n"/>
@@ -36643,7 +35905,6 @@
       <c r="AR734" s="2" t="n"/>
       <c r="AS734" s="2" t="n"/>
       <c r="AT734" s="2" t="n"/>
-      <c r="AU734" s="2" t="n"/>
     </row>
     <row r="735">
       <c r="A735" s="2" t="n"/>
@@ -36692,7 +35953,6 @@
       <c r="AR735" s="2" t="n"/>
       <c r="AS735" s="2" t="n"/>
       <c r="AT735" s="2" t="n"/>
-      <c r="AU735" s="2" t="n"/>
     </row>
     <row r="736">
       <c r="A736" s="2" t="n"/>
@@ -36741,7 +36001,6 @@
       <c r="AR736" s="2" t="n"/>
       <c r="AS736" s="2" t="n"/>
       <c r="AT736" s="2" t="n"/>
-      <c r="AU736" s="2" t="n"/>
     </row>
     <row r="737">
       <c r="A737" s="2" t="n"/>
@@ -36790,7 +36049,6 @@
       <c r="AR737" s="2" t="n"/>
       <c r="AS737" s="2" t="n"/>
       <c r="AT737" s="2" t="n"/>
-      <c r="AU737" s="2" t="n"/>
     </row>
     <row r="738">
       <c r="A738" s="2" t="n"/>
@@ -36839,7 +36097,6 @@
       <c r="AR738" s="2" t="n"/>
       <c r="AS738" s="2" t="n"/>
       <c r="AT738" s="2" t="n"/>
-      <c r="AU738" s="2" t="n"/>
     </row>
     <row r="739">
       <c r="A739" s="2" t="n"/>
@@ -36888,7 +36145,6 @@
       <c r="AR739" s="2" t="n"/>
       <c r="AS739" s="2" t="n"/>
       <c r="AT739" s="2" t="n"/>
-      <c r="AU739" s="2" t="n"/>
     </row>
     <row r="740">
       <c r="A740" s="2" t="n"/>
@@ -36937,7 +36193,6 @@
       <c r="AR740" s="2" t="n"/>
       <c r="AS740" s="2" t="n"/>
       <c r="AT740" s="2" t="n"/>
-      <c r="AU740" s="2" t="n"/>
     </row>
     <row r="741">
       <c r="A741" s="2" t="n"/>
@@ -36986,7 +36241,6 @@
       <c r="AR741" s="2" t="n"/>
       <c r="AS741" s="2" t="n"/>
       <c r="AT741" s="2" t="n"/>
-      <c r="AU741" s="2" t="n"/>
     </row>
     <row r="742">
       <c r="A742" s="2" t="n"/>
@@ -37035,7 +36289,6 @@
       <c r="AR742" s="2" t="n"/>
       <c r="AS742" s="2" t="n"/>
       <c r="AT742" s="2" t="n"/>
-      <c r="AU742" s="2" t="n"/>
     </row>
     <row r="743">
       <c r="A743" s="2" t="n"/>
@@ -37084,7 +36337,6 @@
       <c r="AR743" s="2" t="n"/>
       <c r="AS743" s="2" t="n"/>
       <c r="AT743" s="2" t="n"/>
-      <c r="AU743" s="2" t="n"/>
     </row>
     <row r="744">
       <c r="A744" s="2" t="n"/>
@@ -37133,7 +36385,6 @@
       <c r="AR744" s="2" t="n"/>
       <c r="AS744" s="2" t="n"/>
       <c r="AT744" s="2" t="n"/>
-      <c r="AU744" s="2" t="n"/>
     </row>
     <row r="745">
       <c r="A745" s="2" t="n"/>
@@ -37182,7 +36433,6 @@
       <c r="AR745" s="2" t="n"/>
       <c r="AS745" s="2" t="n"/>
       <c r="AT745" s="2" t="n"/>
-      <c r="AU745" s="2" t="n"/>
     </row>
     <row r="746">
       <c r="A746" s="2" t="n"/>
@@ -37231,7 +36481,6 @@
       <c r="AR746" s="2" t="n"/>
       <c r="AS746" s="2" t="n"/>
       <c r="AT746" s="2" t="n"/>
-      <c r="AU746" s="2" t="n"/>
     </row>
     <row r="747">
       <c r="A747" s="2" t="n"/>
@@ -37280,7 +36529,6 @@
       <c r="AR747" s="2" t="n"/>
       <c r="AS747" s="2" t="n"/>
       <c r="AT747" s="2" t="n"/>
-      <c r="AU747" s="2" t="n"/>
     </row>
     <row r="748">
       <c r="A748" s="2" t="n"/>
@@ -37329,7 +36577,6 @@
       <c r="AR748" s="2" t="n"/>
       <c r="AS748" s="2" t="n"/>
       <c r="AT748" s="2" t="n"/>
-      <c r="AU748" s="2" t="n"/>
     </row>
     <row r="749">
       <c r="A749" s="2" t="n"/>
@@ -37378,7 +36625,6 @@
       <c r="AR749" s="2" t="n"/>
       <c r="AS749" s="2" t="n"/>
       <c r="AT749" s="2" t="n"/>
-      <c r="AU749" s="2" t="n"/>
     </row>
     <row r="750">
       <c r="A750" s="2" t="n"/>
@@ -37427,7 +36673,6 @@
       <c r="AR750" s="2" t="n"/>
       <c r="AS750" s="2" t="n"/>
       <c r="AT750" s="2" t="n"/>
-      <c r="AU750" s="2" t="n"/>
     </row>
     <row r="751">
       <c r="A751" s="2" t="n"/>
@@ -37476,7 +36721,6 @@
       <c r="AR751" s="2" t="n"/>
       <c r="AS751" s="2" t="n"/>
       <c r="AT751" s="2" t="n"/>
-      <c r="AU751" s="2" t="n"/>
     </row>
     <row r="752">
       <c r="A752" s="2" t="n"/>
@@ -37525,7 +36769,6 @@
       <c r="AR752" s="2" t="n"/>
       <c r="AS752" s="2" t="n"/>
       <c r="AT752" s="2" t="n"/>
-      <c r="AU752" s="2" t="n"/>
     </row>
     <row r="753">
       <c r="A753" s="2" t="n"/>
@@ -37574,7 +36817,6 @@
       <c r="AR753" s="2" t="n"/>
       <c r="AS753" s="2" t="n"/>
       <c r="AT753" s="2" t="n"/>
-      <c r="AU753" s="2" t="n"/>
     </row>
     <row r="754">
       <c r="A754" s="2" t="n"/>
@@ -37623,7 +36865,6 @@
       <c r="AR754" s="2" t="n"/>
       <c r="AS754" s="2" t="n"/>
       <c r="AT754" s="2" t="n"/>
-      <c r="AU754" s="2" t="n"/>
     </row>
     <row r="755">
       <c r="A755" s="2" t="n"/>
@@ -37672,7 +36913,6 @@
       <c r="AR755" s="2" t="n"/>
       <c r="AS755" s="2" t="n"/>
       <c r="AT755" s="2" t="n"/>
-      <c r="AU755" s="2" t="n"/>
     </row>
     <row r="756">
       <c r="A756" s="2" t="n"/>
@@ -37721,7 +36961,6 @@
       <c r="AR756" s="2" t="n"/>
       <c r="AS756" s="2" t="n"/>
       <c r="AT756" s="2" t="n"/>
-      <c r="AU756" s="2" t="n"/>
     </row>
     <row r="757">
       <c r="A757" s="2" t="n"/>
@@ -37770,7 +37009,6 @@
       <c r="AR757" s="2" t="n"/>
       <c r="AS757" s="2" t="n"/>
       <c r="AT757" s="2" t="n"/>
-      <c r="AU757" s="2" t="n"/>
     </row>
     <row r="758">
       <c r="A758" s="2" t="n"/>
@@ -37819,7 +37057,6 @@
       <c r="AR758" s="2" t="n"/>
       <c r="AS758" s="2" t="n"/>
       <c r="AT758" s="2" t="n"/>
-      <c r="AU758" s="2" t="n"/>
     </row>
     <row r="759">
       <c r="A759" s="2" t="n"/>
@@ -37868,7 +37105,6 @@
       <c r="AR759" s="2" t="n"/>
       <c r="AS759" s="2" t="n"/>
       <c r="AT759" s="2" t="n"/>
-      <c r="AU759" s="2" t="n"/>
     </row>
     <row r="760">
       <c r="A760" s="2" t="n"/>
@@ -37917,7 +37153,6 @@
       <c r="AR760" s="2" t="n"/>
       <c r="AS760" s="2" t="n"/>
       <c r="AT760" s="2" t="n"/>
-      <c r="AU760" s="2" t="n"/>
     </row>
     <row r="761">
       <c r="A761" s="2" t="n"/>
@@ -37966,7 +37201,6 @@
       <c r="AR761" s="2" t="n"/>
       <c r="AS761" s="2" t="n"/>
       <c r="AT761" s="2" t="n"/>
-      <c r="AU761" s="2" t="n"/>
     </row>
     <row r="762">
       <c r="A762" s="2" t="n"/>
@@ -38015,7 +37249,6 @@
       <c r="AR762" s="2" t="n"/>
       <c r="AS762" s="2" t="n"/>
       <c r="AT762" s="2" t="n"/>
-      <c r="AU762" s="2" t="n"/>
     </row>
     <row r="763">
       <c r="A763" s="2" t="n"/>
@@ -38064,7 +37297,6 @@
       <c r="AR763" s="2" t="n"/>
       <c r="AS763" s="2" t="n"/>
       <c r="AT763" s="2" t="n"/>
-      <c r="AU763" s="2" t="n"/>
     </row>
     <row r="764">
       <c r="A764" s="2" t="n"/>
@@ -38113,7 +37345,6 @@
       <c r="AR764" s="2" t="n"/>
       <c r="AS764" s="2" t="n"/>
       <c r="AT764" s="2" t="n"/>
-      <c r="AU764" s="2" t="n"/>
     </row>
     <row r="765">
       <c r="A765" s="2" t="n"/>
@@ -38162,7 +37393,6 @@
       <c r="AR765" s="2" t="n"/>
       <c r="AS765" s="2" t="n"/>
       <c r="AT765" s="2" t="n"/>
-      <c r="AU765" s="2" t="n"/>
     </row>
     <row r="766">
       <c r="A766" s="2" t="n"/>
@@ -38211,7 +37441,6 @@
       <c r="AR766" s="2" t="n"/>
       <c r="AS766" s="2" t="n"/>
       <c r="AT766" s="2" t="n"/>
-      <c r="AU766" s="2" t="n"/>
     </row>
     <row r="767">
       <c r="A767" s="2" t="n"/>
@@ -38260,7 +37489,6 @@
       <c r="AR767" s="2" t="n"/>
       <c r="AS767" s="2" t="n"/>
       <c r="AT767" s="2" t="n"/>
-      <c r="AU767" s="2" t="n"/>
     </row>
     <row r="768">
       <c r="A768" s="2" t="n"/>
@@ -38309,7 +37537,6 @@
       <c r="AR768" s="2" t="n"/>
       <c r="AS768" s="2" t="n"/>
       <c r="AT768" s="2" t="n"/>
-      <c r="AU768" s="2" t="n"/>
     </row>
     <row r="769">
       <c r="A769" s="2" t="n"/>
@@ -38358,7 +37585,6 @@
       <c r="AR769" s="2" t="n"/>
       <c r="AS769" s="2" t="n"/>
       <c r="AT769" s="2" t="n"/>
-      <c r="AU769" s="2" t="n"/>
     </row>
     <row r="770">
       <c r="A770" s="2" t="n"/>
@@ -38407,7 +37633,6 @@
       <c r="AR770" s="2" t="n"/>
       <c r="AS770" s="2" t="n"/>
       <c r="AT770" s="2" t="n"/>
-      <c r="AU770" s="2" t="n"/>
     </row>
     <row r="771">
       <c r="A771" s="2" t="n"/>
@@ -38456,7 +37681,6 @@
       <c r="AR771" s="2" t="n"/>
       <c r="AS771" s="2" t="n"/>
       <c r="AT771" s="2" t="n"/>
-      <c r="AU771" s="2" t="n"/>
     </row>
     <row r="772">
       <c r="A772" s="2" t="n"/>
@@ -38505,7 +37729,6 @@
       <c r="AR772" s="2" t="n"/>
       <c r="AS772" s="2" t="n"/>
       <c r="AT772" s="2" t="n"/>
-      <c r="AU772" s="2" t="n"/>
     </row>
     <row r="773">
       <c r="A773" s="2" t="n"/>
@@ -38554,7 +37777,6 @@
       <c r="AR773" s="2" t="n"/>
       <c r="AS773" s="2" t="n"/>
       <c r="AT773" s="2" t="n"/>
-      <c r="AU773" s="2" t="n"/>
     </row>
     <row r="774">
       <c r="A774" s="2" t="n"/>
@@ -38603,7 +37825,6 @@
       <c r="AR774" s="2" t="n"/>
       <c r="AS774" s="2" t="n"/>
       <c r="AT774" s="2" t="n"/>
-      <c r="AU774" s="2" t="n"/>
     </row>
     <row r="775">
       <c r="A775" s="2" t="n"/>
@@ -38652,7 +37873,6 @@
       <c r="AR775" s="2" t="n"/>
       <c r="AS775" s="2" t="n"/>
       <c r="AT775" s="2" t="n"/>
-      <c r="AU775" s="2" t="n"/>
     </row>
     <row r="776">
       <c r="A776" s="2" t="n"/>
@@ -38701,7 +37921,6 @@
       <c r="AR776" s="2" t="n"/>
       <c r="AS776" s="2" t="n"/>
       <c r="AT776" s="2" t="n"/>
-      <c r="AU776" s="2" t="n"/>
     </row>
     <row r="777">
       <c r="A777" s="2" t="n"/>
@@ -38750,7 +37969,6 @@
       <c r="AR777" s="2" t="n"/>
       <c r="AS777" s="2" t="n"/>
       <c r="AT777" s="2" t="n"/>
-      <c r="AU777" s="2" t="n"/>
     </row>
     <row r="778">
       <c r="A778" s="2" t="n"/>
@@ -38799,7 +38017,6 @@
       <c r="AR778" s="2" t="n"/>
       <c r="AS778" s="2" t="n"/>
       <c r="AT778" s="2" t="n"/>
-      <c r="AU778" s="2" t="n"/>
     </row>
     <row r="779">
       <c r="A779" s="2" t="n"/>
@@ -38848,7 +38065,6 @@
       <c r="AR779" s="2" t="n"/>
       <c r="AS779" s="2" t="n"/>
       <c r="AT779" s="2" t="n"/>
-      <c r="AU779" s="2" t="n"/>
     </row>
     <row r="780">
       <c r="A780" s="2" t="n"/>
@@ -38897,7 +38113,6 @@
       <c r="AR780" s="2" t="n"/>
       <c r="AS780" s="2" t="n"/>
       <c r="AT780" s="2" t="n"/>
-      <c r="AU780" s="2" t="n"/>
     </row>
     <row r="781">
       <c r="A781" s="2" t="n"/>
@@ -38946,7 +38161,6 @@
       <c r="AR781" s="2" t="n"/>
       <c r="AS781" s="2" t="n"/>
       <c r="AT781" s="2" t="n"/>
-      <c r="AU781" s="2" t="n"/>
     </row>
     <row r="782">
       <c r="A782" s="2" t="n"/>
@@ -38995,7 +38209,6 @@
       <c r="AR782" s="2" t="n"/>
       <c r="AS782" s="2" t="n"/>
       <c r="AT782" s="2" t="n"/>
-      <c r="AU782" s="2" t="n"/>
     </row>
     <row r="783">
       <c r="A783" s="2" t="n"/>
@@ -39044,7 +38257,6 @@
       <c r="AR783" s="2" t="n"/>
       <c r="AS783" s="2" t="n"/>
       <c r="AT783" s="2" t="n"/>
-      <c r="AU783" s="2" t="n"/>
     </row>
     <row r="784">
       <c r="A784" s="2" t="n"/>
@@ -39093,7 +38305,6 @@
       <c r="AR784" s="2" t="n"/>
       <c r="AS784" s="2" t="n"/>
       <c r="AT784" s="2" t="n"/>
-      <c r="AU784" s="2" t="n"/>
     </row>
     <row r="785">
       <c r="A785" s="2" t="n"/>
@@ -39142,7 +38353,6 @@
       <c r="AR785" s="2" t="n"/>
       <c r="AS785" s="2" t="n"/>
       <c r="AT785" s="2" t="n"/>
-      <c r="AU785" s="2" t="n"/>
     </row>
     <row r="786">
       <c r="A786" s="2" t="n"/>
@@ -39191,7 +38401,6 @@
       <c r="AR786" s="2" t="n"/>
       <c r="AS786" s="2" t="n"/>
       <c r="AT786" s="2" t="n"/>
-      <c r="AU786" s="2" t="n"/>
     </row>
     <row r="787">
       <c r="A787" s="2" t="n"/>
@@ -39240,7 +38449,6 @@
       <c r="AR787" s="2" t="n"/>
       <c r="AS787" s="2" t="n"/>
       <c r="AT787" s="2" t="n"/>
-      <c r="AU787" s="2" t="n"/>
     </row>
     <row r="788">
       <c r="A788" s="2" t="n"/>
@@ -39289,7 +38497,6 @@
       <c r="AR788" s="2" t="n"/>
       <c r="AS788" s="2" t="n"/>
       <c r="AT788" s="2" t="n"/>
-      <c r="AU788" s="2" t="n"/>
     </row>
     <row r="789">
       <c r="A789" s="2" t="n"/>
@@ -39338,7 +38545,6 @@
       <c r="AR789" s="2" t="n"/>
       <c r="AS789" s="2" t="n"/>
       <c r="AT789" s="2" t="n"/>
-      <c r="AU789" s="2" t="n"/>
     </row>
     <row r="790">
       <c r="A790" s="2" t="n"/>
@@ -39387,7 +38593,6 @@
       <c r="AR790" s="2" t="n"/>
       <c r="AS790" s="2" t="n"/>
       <c r="AT790" s="2" t="n"/>
-      <c r="AU790" s="2" t="n"/>
     </row>
     <row r="791">
       <c r="A791" s="2" t="n"/>
@@ -39436,7 +38641,6 @@
       <c r="AR791" s="2" t="n"/>
       <c r="AS791" s="2" t="n"/>
       <c r="AT791" s="2" t="n"/>
-      <c r="AU791" s="2" t="n"/>
     </row>
     <row r="792">
       <c r="A792" s="2" t="n"/>
@@ -39485,7 +38689,6 @@
       <c r="AR792" s="2" t="n"/>
       <c r="AS792" s="2" t="n"/>
       <c r="AT792" s="2" t="n"/>
-      <c r="AU792" s="2" t="n"/>
     </row>
     <row r="793">
       <c r="A793" s="2" t="n"/>
@@ -39534,7 +38737,6 @@
       <c r="AR793" s="2" t="n"/>
       <c r="AS793" s="2" t="n"/>
       <c r="AT793" s="2" t="n"/>
-      <c r="AU793" s="2" t="n"/>
     </row>
     <row r="794">
       <c r="A794" s="2" t="n"/>
@@ -39583,7 +38785,6 @@
       <c r="AR794" s="2" t="n"/>
       <c r="AS794" s="2" t="n"/>
       <c r="AT794" s="2" t="n"/>
-      <c r="AU794" s="2" t="n"/>
     </row>
     <row r="795">
       <c r="A795" s="2" t="n"/>
@@ -39632,7 +38833,6 @@
       <c r="AR795" s="2" t="n"/>
       <c r="AS795" s="2" t="n"/>
       <c r="AT795" s="2" t="n"/>
-      <c r="AU795" s="2" t="n"/>
     </row>
     <row r="796">
       <c r="A796" s="2" t="n"/>
@@ -39681,7 +38881,6 @@
       <c r="AR796" s="2" t="n"/>
       <c r="AS796" s="2" t="n"/>
       <c r="AT796" s="2" t="n"/>
-      <c r="AU796" s="2" t="n"/>
     </row>
     <row r="797">
       <c r="A797" s="2" t="n"/>
@@ -39730,7 +38929,6 @@
       <c r="AR797" s="2" t="n"/>
       <c r="AS797" s="2" t="n"/>
       <c r="AT797" s="2" t="n"/>
-      <c r="AU797" s="2" t="n"/>
     </row>
     <row r="798">
       <c r="A798" s="2" t="n"/>
@@ -39779,7 +38977,6 @@
       <c r="AR798" s="2" t="n"/>
       <c r="AS798" s="2" t="n"/>
       <c r="AT798" s="2" t="n"/>
-      <c r="AU798" s="2" t="n"/>
     </row>
     <row r="799">
       <c r="A799" s="2" t="n"/>
@@ -39828,7 +39025,6 @@
       <c r="AR799" s="2" t="n"/>
       <c r="AS799" s="2" t="n"/>
       <c r="AT799" s="2" t="n"/>
-      <c r="AU799" s="2" t="n"/>
     </row>
     <row r="800">
       <c r="A800" s="2" t="n"/>
@@ -39877,7 +39073,6 @@
       <c r="AR800" s="2" t="n"/>
       <c r="AS800" s="2" t="n"/>
       <c r="AT800" s="2" t="n"/>
-      <c r="AU800" s="2" t="n"/>
     </row>
     <row r="801">
       <c r="A801" s="2" t="n"/>
@@ -39926,7 +39121,6 @@
       <c r="AR801" s="2" t="n"/>
       <c r="AS801" s="2" t="n"/>
       <c r="AT801" s="2" t="n"/>
-      <c r="AU801" s="2" t="n"/>
     </row>
     <row r="802">
       <c r="A802" s="2" t="n"/>
@@ -39975,7 +39169,6 @@
       <c r="AR802" s="2" t="n"/>
       <c r="AS802" s="2" t="n"/>
       <c r="AT802" s="2" t="n"/>
-      <c r="AU802" s="2" t="n"/>
     </row>
     <row r="803">
       <c r="A803" s="2" t="n"/>
@@ -40024,7 +39217,6 @@
       <c r="AR803" s="2" t="n"/>
       <c r="AS803" s="2" t="n"/>
       <c r="AT803" s="2" t="n"/>
-      <c r="AU803" s="2" t="n"/>
     </row>
     <row r="804">
       <c r="A804" s="2" t="n"/>
@@ -40073,7 +39265,6 @@
       <c r="AR804" s="2" t="n"/>
       <c r="AS804" s="2" t="n"/>
       <c r="AT804" s="2" t="n"/>
-      <c r="AU804" s="2" t="n"/>
     </row>
     <row r="805">
       <c r="A805" s="2" t="n"/>
@@ -40122,7 +39313,6 @@
       <c r="AR805" s="2" t="n"/>
       <c r="AS805" s="2" t="n"/>
       <c r="AT805" s="2" t="n"/>
-      <c r="AU805" s="2" t="n"/>
     </row>
     <row r="806">
       <c r="A806" s="2" t="n"/>
@@ -40171,7 +39361,6 @@
       <c r="AR806" s="2" t="n"/>
       <c r="AS806" s="2" t="n"/>
       <c r="AT806" s="2" t="n"/>
-      <c r="AU806" s="2" t="n"/>
     </row>
     <row r="807">
       <c r="A807" s="2" t="n"/>
@@ -40220,7 +39409,6 @@
       <c r="AR807" s="2" t="n"/>
       <c r="AS807" s="2" t="n"/>
       <c r="AT807" s="2" t="n"/>
-      <c r="AU807" s="2" t="n"/>
     </row>
     <row r="808">
       <c r="A808" s="2" t="n"/>
@@ -40269,7 +39457,6 @@
       <c r="AR808" s="2" t="n"/>
       <c r="AS808" s="2" t="n"/>
       <c r="AT808" s="2" t="n"/>
-      <c r="AU808" s="2" t="n"/>
     </row>
     <row r="809">
       <c r="A809" s="2" t="n"/>
@@ -40318,7 +39505,6 @@
       <c r="AR809" s="2" t="n"/>
       <c r="AS809" s="2" t="n"/>
       <c r="AT809" s="2" t="n"/>
-      <c r="AU809" s="2" t="n"/>
     </row>
     <row r="810">
       <c r="A810" s="2" t="n"/>
@@ -40367,7 +39553,6 @@
       <c r="AR810" s="2" t="n"/>
       <c r="AS810" s="2" t="n"/>
       <c r="AT810" s="2" t="n"/>
-      <c r="AU810" s="2" t="n"/>
     </row>
     <row r="811">
       <c r="A811" s="2" t="n"/>
@@ -40416,7 +39601,6 @@
       <c r="AR811" s="2" t="n"/>
       <c r="AS811" s="2" t="n"/>
       <c r="AT811" s="2" t="n"/>
-      <c r="AU811" s="2" t="n"/>
     </row>
     <row r="812">
       <c r="A812" s="2" t="n"/>
@@ -40465,7 +39649,6 @@
       <c r="AR812" s="2" t="n"/>
       <c r="AS812" s="2" t="n"/>
       <c r="AT812" s="2" t="n"/>
-      <c r="AU812" s="2" t="n"/>
     </row>
     <row r="813">
       <c r="A813" s="2" t="n"/>
@@ -40514,7 +39697,6 @@
       <c r="AR813" s="2" t="n"/>
       <c r="AS813" s="2" t="n"/>
       <c r="AT813" s="2" t="n"/>
-      <c r="AU813" s="2" t="n"/>
     </row>
     <row r="814">
       <c r="A814" s="2" t="n"/>
@@ -40563,7 +39745,6 @@
       <c r="AR814" s="2" t="n"/>
       <c r="AS814" s="2" t="n"/>
       <c r="AT814" s="2" t="n"/>
-      <c r="AU814" s="2" t="n"/>
     </row>
     <row r="815">
       <c r="A815" s="2" t="n"/>
@@ -40612,7 +39793,6 @@
       <c r="AR815" s="2" t="n"/>
       <c r="AS815" s="2" t="n"/>
       <c r="AT815" s="2" t="n"/>
-      <c r="AU815" s="2" t="n"/>
     </row>
     <row r="816">
       <c r="A816" s="2" t="n"/>
@@ -40661,7 +39841,6 @@
       <c r="AR816" s="2" t="n"/>
       <c r="AS816" s="2" t="n"/>
       <c r="AT816" s="2" t="n"/>
-      <c r="AU816" s="2" t="n"/>
     </row>
     <row r="817">
       <c r="A817" s="2" t="n"/>
@@ -40710,7 +39889,6 @@
       <c r="AR817" s="2" t="n"/>
       <c r="AS817" s="2" t="n"/>
       <c r="AT817" s="2" t="n"/>
-      <c r="AU817" s="2" t="n"/>
     </row>
     <row r="818">
       <c r="A818" s="2" t="n"/>
@@ -40759,7 +39937,6 @@
       <c r="AR818" s="2" t="n"/>
       <c r="AS818" s="2" t="n"/>
       <c r="AT818" s="2" t="n"/>
-      <c r="AU818" s="2" t="n"/>
     </row>
     <row r="819">
       <c r="A819" s="2" t="n"/>
@@ -40808,7 +39985,6 @@
       <c r="AR819" s="2" t="n"/>
       <c r="AS819" s="2" t="n"/>
       <c r="AT819" s="2" t="n"/>
-      <c r="AU819" s="2" t="n"/>
     </row>
     <row r="820">
       <c r="A820" s="2" t="n"/>
@@ -40857,7 +40033,6 @@
       <c r="AR820" s="2" t="n"/>
       <c r="AS820" s="2" t="n"/>
       <c r="AT820" s="2" t="n"/>
-      <c r="AU820" s="2" t="n"/>
     </row>
     <row r="821">
       <c r="A821" s="2" t="n"/>
@@ -40906,7 +40081,6 @@
       <c r="AR821" s="2" t="n"/>
       <c r="AS821" s="2" t="n"/>
       <c r="AT821" s="2" t="n"/>
-      <c r="AU821" s="2" t="n"/>
     </row>
     <row r="822">
       <c r="A822" s="2" t="n"/>
@@ -40955,7 +40129,6 @@
       <c r="AR822" s="2" t="n"/>
       <c r="AS822" s="2" t="n"/>
       <c r="AT822" s="2" t="n"/>
-      <c r="AU822" s="2" t="n"/>
     </row>
     <row r="823">
       <c r="A823" s="2" t="n"/>
@@ -41004,7 +40177,6 @@
       <c r="AR823" s="2" t="n"/>
       <c r="AS823" s="2" t="n"/>
       <c r="AT823" s="2" t="n"/>
-      <c r="AU823" s="2" t="n"/>
     </row>
     <row r="824">
       <c r="A824" s="2" t="n"/>
@@ -41053,7 +40225,6 @@
       <c r="AR824" s="2" t="n"/>
       <c r="AS824" s="2" t="n"/>
       <c r="AT824" s="2" t="n"/>
-      <c r="AU824" s="2" t="n"/>
     </row>
     <row r="825">
       <c r="A825" s="2" t="n"/>
@@ -41102,7 +40273,6 @@
       <c r="AR825" s="2" t="n"/>
       <c r="AS825" s="2" t="n"/>
       <c r="AT825" s="2" t="n"/>
-      <c r="AU825" s="2" t="n"/>
     </row>
     <row r="826">
       <c r="A826" s="2" t="n"/>
@@ -41151,7 +40321,6 @@
       <c r="AR826" s="2" t="n"/>
       <c r="AS826" s="2" t="n"/>
       <c r="AT826" s="2" t="n"/>
-      <c r="AU826" s="2" t="n"/>
     </row>
     <row r="827">
       <c r="A827" s="2" t="n"/>
@@ -41200,7 +40369,6 @@
       <c r="AR827" s="2" t="n"/>
       <c r="AS827" s="2" t="n"/>
       <c r="AT827" s="2" t="n"/>
-      <c r="AU827" s="2" t="n"/>
     </row>
     <row r="828">
       <c r="A828" s="2" t="n"/>
@@ -41249,7 +40417,6 @@
       <c r="AR828" s="2" t="n"/>
       <c r="AS828" s="2" t="n"/>
       <c r="AT828" s="2" t="n"/>
-      <c r="AU828" s="2" t="n"/>
     </row>
     <row r="829">
       <c r="A829" s="2" t="n"/>
@@ -41298,7 +40465,6 @@
       <c r="AR829" s="2" t="n"/>
       <c r="AS829" s="2" t="n"/>
       <c r="AT829" s="2" t="n"/>
-      <c r="AU829" s="2" t="n"/>
     </row>
     <row r="830">
       <c r="A830" s="2" t="n"/>
@@ -41347,7 +40513,6 @@
       <c r="AR830" s="2" t="n"/>
       <c r="AS830" s="2" t="n"/>
       <c r="AT830" s="2" t="n"/>
-      <c r="AU830" s="2" t="n"/>
     </row>
     <row r="831">
       <c r="A831" s="2" t="n"/>
@@ -41396,7 +40561,6 @@
       <c r="AR831" s="2" t="n"/>
       <c r="AS831" s="2" t="n"/>
       <c r="AT831" s="2" t="n"/>
-      <c r="AU831" s="2" t="n"/>
     </row>
     <row r="832">
       <c r="A832" s="2" t="n"/>
@@ -41445,7 +40609,6 @@
       <c r="AR832" s="2" t="n"/>
       <c r="AS832" s="2" t="n"/>
       <c r="AT832" s="2" t="n"/>
-      <c r="AU832" s="2" t="n"/>
     </row>
     <row r="833">
       <c r="A833" s="2" t="n"/>
@@ -41494,7 +40657,6 @@
       <c r="AR833" s="2" t="n"/>
       <c r="AS833" s="2" t="n"/>
       <c r="AT833" s="2" t="n"/>
-      <c r="AU833" s="2" t="n"/>
     </row>
     <row r="834">
       <c r="A834" s="2" t="n"/>
@@ -41543,7 +40705,6 @@
       <c r="AR834" s="2" t="n"/>
       <c r="AS834" s="2" t="n"/>
       <c r="AT834" s="2" t="n"/>
-      <c r="AU834" s="2" t="n"/>
     </row>
     <row r="835">
       <c r="A835" s="2" t="n"/>
@@ -41592,7 +40753,6 @@
       <c r="AR835" s="2" t="n"/>
       <c r="AS835" s="2" t="n"/>
       <c r="AT835" s="2" t="n"/>
-      <c r="AU835" s="2" t="n"/>
     </row>
     <row r="836">
       <c r="A836" s="2" t="n"/>
@@ -41641,7 +40801,6 @@
       <c r="AR836" s="2" t="n"/>
       <c r="AS836" s="2" t="n"/>
       <c r="AT836" s="2" t="n"/>
-      <c r="AU836" s="2" t="n"/>
     </row>
     <row r="837">
       <c r="A837" s="2" t="n"/>
@@ -41690,7 +40849,6 @@
       <c r="AR837" s="2" t="n"/>
       <c r="AS837" s="2" t="n"/>
       <c r="AT837" s="2" t="n"/>
-      <c r="AU837" s="2" t="n"/>
     </row>
     <row r="838">
       <c r="A838" s="2" t="n"/>
@@ -41739,7 +40897,6 @@
       <c r="AR838" s="2" t="n"/>
       <c r="AS838" s="2" t="n"/>
       <c r="AT838" s="2" t="n"/>
-      <c r="AU838" s="2" t="n"/>
     </row>
     <row r="839">
       <c r="A839" s="2" t="n"/>
@@ -41788,7 +40945,6 @@
       <c r="AR839" s="2" t="n"/>
       <c r="AS839" s="2" t="n"/>
       <c r="AT839" s="2" t="n"/>
-      <c r="AU839" s="2" t="n"/>
     </row>
     <row r="840">
       <c r="A840" s="2" t="n"/>
@@ -41837,7 +40993,6 @@
       <c r="AR840" s="2" t="n"/>
       <c r="AS840" s="2" t="n"/>
       <c r="AT840" s="2" t="n"/>
-      <c r="AU840" s="2" t="n"/>
     </row>
     <row r="841">
       <c r="A841" s="2" t="n"/>
@@ -41886,7 +41041,6 @@
       <c r="AR841" s="2" t="n"/>
       <c r="AS841" s="2" t="n"/>
       <c r="AT841" s="2" t="n"/>
-      <c r="AU841" s="2" t="n"/>
     </row>
     <row r="842">
       <c r="A842" s="2" t="n"/>
@@ -41935,7 +41089,6 @@
       <c r="AR842" s="2" t="n"/>
       <c r="AS842" s="2" t="n"/>
       <c r="AT842" s="2" t="n"/>
-      <c r="AU842" s="2" t="n"/>
     </row>
     <row r="843">
       <c r="A843" s="2" t="n"/>
@@ -41984,7 +41137,6 @@
       <c r="AR843" s="2" t="n"/>
       <c r="AS843" s="2" t="n"/>
       <c r="AT843" s="2" t="n"/>
-      <c r="AU843" s="2" t="n"/>
     </row>
     <row r="844">
       <c r="A844" s="2" t="n"/>
@@ -42033,7 +41185,6 @@
       <c r="AR844" s="2" t="n"/>
       <c r="AS844" s="2" t="n"/>
       <c r="AT844" s="2" t="n"/>
-      <c r="AU844" s="2" t="n"/>
     </row>
     <row r="845">
       <c r="A845" s="2" t="n"/>
@@ -42082,7 +41233,6 @@
       <c r="AR845" s="2" t="n"/>
       <c r="AS845" s="2" t="n"/>
       <c r="AT845" s="2" t="n"/>
-      <c r="AU845" s="2" t="n"/>
     </row>
     <row r="846">
       <c r="A846" s="2" t="n"/>
@@ -42131,7 +41281,6 @@
       <c r="AR846" s="2" t="n"/>
       <c r="AS846" s="2" t="n"/>
       <c r="AT846" s="2" t="n"/>
-      <c r="AU846" s="2" t="n"/>
     </row>
     <row r="847">
       <c r="A847" s="2" t="n"/>
@@ -42180,7 +41329,6 @@
       <c r="AR847" s="2" t="n"/>
       <c r="AS847" s="2" t="n"/>
       <c r="AT847" s="2" t="n"/>
-      <c r="AU847" s="2" t="n"/>
     </row>
     <row r="848">
       <c r="A848" s="2" t="n"/>
@@ -42229,7 +41377,6 @@
       <c r="AR848" s="2" t="n"/>
       <c r="AS848" s="2" t="n"/>
       <c r="AT848" s="2" t="n"/>
-      <c r="AU848" s="2" t="n"/>
     </row>
     <row r="849">
       <c r="A849" s="2" t="n"/>
@@ -42278,7 +41425,6 @@
       <c r="AR849" s="2" t="n"/>
       <c r="AS849" s="2" t="n"/>
       <c r="AT849" s="2" t="n"/>
-      <c r="AU849" s="2" t="n"/>
     </row>
     <row r="850">
       <c r="A850" s="2" t="n"/>
@@ -42327,7 +41473,6 @@
       <c r="AR850" s="2" t="n"/>
       <c r="AS850" s="2" t="n"/>
       <c r="AT850" s="2" t="n"/>
-      <c r="AU850" s="2" t="n"/>
     </row>
     <row r="851">
       <c r="A851" s="2" t="n"/>
@@ -42376,7 +41521,6 @@
       <c r="AR851" s="2" t="n"/>
       <c r="AS851" s="2" t="n"/>
       <c r="AT851" s="2" t="n"/>
-      <c r="AU851" s="2" t="n"/>
     </row>
     <row r="852">
       <c r="A852" s="2" t="n"/>
@@ -42425,7 +41569,6 @@
       <c r="AR852" s="2" t="n"/>
       <c r="AS852" s="2" t="n"/>
       <c r="AT852" s="2" t="n"/>
-      <c r="AU852" s="2" t="n"/>
     </row>
     <row r="853">
       <c r="A853" s="2" t="n"/>
@@ -42474,7 +41617,6 @@
       <c r="AR853" s="2" t="n"/>
       <c r="AS853" s="2" t="n"/>
       <c r="AT853" s="2" t="n"/>
-      <c r="AU853" s="2" t="n"/>
     </row>
     <row r="854">
       <c r="A854" s="2" t="n"/>
@@ -42523,7 +41665,6 @@
       <c r="AR854" s="2" t="n"/>
       <c r="AS854" s="2" t="n"/>
       <c r="AT854" s="2" t="n"/>
-      <c r="AU854" s="2" t="n"/>
     </row>
     <row r="855">
       <c r="A855" s="2" t="n"/>
@@ -42572,7 +41713,6 @@
       <c r="AR855" s="2" t="n"/>
       <c r="AS855" s="2" t="n"/>
       <c r="AT855" s="2" t="n"/>
-      <c r="AU855" s="2" t="n"/>
     </row>
     <row r="856">
       <c r="A856" s="2" t="n"/>
@@ -42621,7 +41761,6 @@
       <c r="AR856" s="2" t="n"/>
       <c r="AS856" s="2" t="n"/>
       <c r="AT856" s="2" t="n"/>
-      <c r="AU856" s="2" t="n"/>
     </row>
     <row r="857">
       <c r="A857" s="2" t="n"/>
@@ -42670,7 +41809,6 @@
       <c r="AR857" s="2" t="n"/>
       <c r="AS857" s="2" t="n"/>
       <c r="AT857" s="2" t="n"/>
-      <c r="AU857" s="2" t="n"/>
     </row>
     <row r="858">
       <c r="A858" s="2" t="n"/>
@@ -42719,7 +41857,6 @@
       <c r="AR858" s="2" t="n"/>
       <c r="AS858" s="2" t="n"/>
       <c r="AT858" s="2" t="n"/>
-      <c r="AU858" s="2" t="n"/>
     </row>
     <row r="859">
       <c r="A859" s="2" t="n"/>
@@ -42768,7 +41905,6 @@
       <c r="AR859" s="2" t="n"/>
       <c r="AS859" s="2" t="n"/>
       <c r="AT859" s="2" t="n"/>
-      <c r="AU859" s="2" t="n"/>
     </row>
     <row r="860">
       <c r="A860" s="2" t="n"/>
@@ -42817,7 +41953,6 @@
       <c r="AR860" s="2" t="n"/>
       <c r="AS860" s="2" t="n"/>
       <c r="AT860" s="2" t="n"/>
-      <c r="AU860" s="2" t="n"/>
     </row>
     <row r="861">
       <c r="A861" s="2" t="n"/>
@@ -42866,7 +42001,6 @@
       <c r="AR861" s="2" t="n"/>
       <c r="AS861" s="2" t="n"/>
       <c r="AT861" s="2" t="n"/>
-      <c r="AU861" s="2" t="n"/>
     </row>
     <row r="862">
       <c r="A862" s="2" t="n"/>
@@ -42915,7 +42049,6 @@
       <c r="AR862" s="2" t="n"/>
       <c r="AS862" s="2" t="n"/>
       <c r="AT862" s="2" t="n"/>
-      <c r="AU862" s="2" t="n"/>
     </row>
     <row r="863">
       <c r="A863" s="2" t="n"/>
@@ -42964,7 +42097,6 @@
       <c r="AR863" s="2" t="n"/>
       <c r="AS863" s="2" t="n"/>
       <c r="AT863" s="2" t="n"/>
-      <c r="AU863" s="2" t="n"/>
     </row>
     <row r="864">
       <c r="A864" s="2" t="n"/>
@@ -43013,7 +42145,6 @@
       <c r="AR864" s="2" t="n"/>
       <c r="AS864" s="2" t="n"/>
       <c r="AT864" s="2" t="n"/>
-      <c r="AU864" s="2" t="n"/>
     </row>
     <row r="865">
       <c r="A865" s="2" t="n"/>
@@ -43062,7 +42193,6 @@
       <c r="AR865" s="2" t="n"/>
       <c r="AS865" s="2" t="n"/>
       <c r="AT865" s="2" t="n"/>
-      <c r="AU865" s="2" t="n"/>
     </row>
     <row r="866">
       <c r="A866" s="2" t="n"/>
@@ -43111,7 +42241,6 @@
       <c r="AR866" s="2" t="n"/>
       <c r="AS866" s="2" t="n"/>
       <c r="AT866" s="2" t="n"/>
-      <c r="AU866" s="2" t="n"/>
     </row>
     <row r="867">
       <c r="A867" s="2" t="n"/>
@@ -43160,7 +42289,6 @@
       <c r="AR867" s="2" t="n"/>
       <c r="AS867" s="2" t="n"/>
       <c r="AT867" s="2" t="n"/>
-      <c r="AU867" s="2" t="n"/>
     </row>
     <row r="868">
       <c r="A868" s="2" t="n"/>
@@ -43209,7 +42337,6 @@
       <c r="AR868" s="2" t="n"/>
       <c r="AS868" s="2" t="n"/>
       <c r="AT868" s="2" t="n"/>
-      <c r="AU868" s="2" t="n"/>
     </row>
     <row r="869">
       <c r="A869" s="2" t="n"/>
@@ -43258,7 +42385,6 @@
       <c r="AR869" s="2" t="n"/>
       <c r="AS869" s="2" t="n"/>
       <c r="AT869" s="2" t="n"/>
-      <c r="AU869" s="2" t="n"/>
     </row>
     <row r="870">
       <c r="A870" s="2" t="n"/>
@@ -43307,7 +42433,6 @@
       <c r="AR870" s="2" t="n"/>
       <c r="AS870" s="2" t="n"/>
       <c r="AT870" s="2" t="n"/>
-      <c r="AU870" s="2" t="n"/>
     </row>
     <row r="871">
       <c r="A871" s="2" t="n"/>
@@ -43356,7 +42481,6 @@
       <c r="AR871" s="2" t="n"/>
       <c r="AS871" s="2" t="n"/>
       <c r="AT871" s="2" t="n"/>
-      <c r="AU871" s="2" t="n"/>
     </row>
     <row r="872">
       <c r="A872" s="2" t="n"/>
@@ -43405,7 +42529,6 @@
       <c r="AR872" s="2" t="n"/>
       <c r="AS872" s="2" t="n"/>
       <c r="AT872" s="2" t="n"/>
-      <c r="AU872" s="2" t="n"/>
     </row>
     <row r="873">
       <c r="A873" s="2" t="n"/>
@@ -43454,7 +42577,6 @@
       <c r="AR873" s="2" t="n"/>
       <c r="AS873" s="2" t="n"/>
       <c r="AT873" s="2" t="n"/>
-      <c r="AU873" s="2" t="n"/>
     </row>
     <row r="874">
       <c r="A874" s="2" t="n"/>
@@ -43503,7 +42625,6 @@
       <c r="AR874" s="2" t="n"/>
       <c r="AS874" s="2" t="n"/>
       <c r="AT874" s="2" t="n"/>
-      <c r="AU874" s="2" t="n"/>
     </row>
     <row r="875">
       <c r="A875" s="2" t="n"/>
@@ -43552,7 +42673,6 @@
       <c r="AR875" s="2" t="n"/>
       <c r="AS875" s="2" t="n"/>
       <c r="AT875" s="2" t="n"/>
-      <c r="AU875" s="2" t="n"/>
     </row>
     <row r="876">
       <c r="A876" s="2" t="n"/>
@@ -43601,7 +42721,6 @@
       <c r="AR876" s="2" t="n"/>
       <c r="AS876" s="2" t="n"/>
       <c r="AT876" s="2" t="n"/>
-      <c r="AU876" s="2" t="n"/>
     </row>
     <row r="877">
       <c r="A877" s="2" t="n"/>
@@ -43650,7 +42769,6 @@
       <c r="AR877" s="2" t="n"/>
       <c r="AS877" s="2" t="n"/>
       <c r="AT877" s="2" t="n"/>
-      <c r="AU877" s="2" t="n"/>
     </row>
     <row r="878">
       <c r="A878" s="2" t="n"/>
@@ -43699,7 +42817,6 @@
       <c r="AR878" s="2" t="n"/>
       <c r="AS878" s="2" t="n"/>
       <c r="AT878" s="2" t="n"/>
-      <c r="AU878" s="2" t="n"/>
     </row>
     <row r="879">
       <c r="A879" s="2" t="n"/>
@@ -43748,7 +42865,6 @@
       <c r="AR879" s="2" t="n"/>
       <c r="AS879" s="2" t="n"/>
       <c r="AT879" s="2" t="n"/>
-      <c r="AU879" s="2" t="n"/>
     </row>
     <row r="880">
       <c r="A880" s="2" t="n"/>
@@ -43797,7 +42913,6 @@
       <c r="AR880" s="2" t="n"/>
       <c r="AS880" s="2" t="n"/>
       <c r="AT880" s="2" t="n"/>
-      <c r="AU880" s="2" t="n"/>
     </row>
     <row r="881">
       <c r="A881" s="2" t="n"/>
@@ -43846,7 +42961,6 @@
       <c r="AR881" s="2" t="n"/>
       <c r="AS881" s="2" t="n"/>
       <c r="AT881" s="2" t="n"/>
-      <c r="AU881" s="2" t="n"/>
     </row>
     <row r="882">
       <c r="A882" s="2" t="n"/>
@@ -43895,7 +43009,6 @@
       <c r="AR882" s="2" t="n"/>
       <c r="AS882" s="2" t="n"/>
       <c r="AT882" s="2" t="n"/>
-      <c r="AU882" s="2" t="n"/>
     </row>
     <row r="883">
       <c r="A883" s="2" t="n"/>
@@ -43944,7 +43057,6 @@
       <c r="AR883" s="2" t="n"/>
       <c r="AS883" s="2" t="n"/>
       <c r="AT883" s="2" t="n"/>
-      <c r="AU883" s="2" t="n"/>
     </row>
     <row r="884">
       <c r="A884" s="2" t="n"/>
@@ -43993,7 +43105,6 @@
       <c r="AR884" s="2" t="n"/>
       <c r="AS884" s="2" t="n"/>
       <c r="AT884" s="2" t="n"/>
-      <c r="AU884" s="2" t="n"/>
     </row>
     <row r="885">
       <c r="A885" s="2" t="n"/>
@@ -44042,7 +43153,6 @@
       <c r="AR885" s="2" t="n"/>
       <c r="AS885" s="2" t="n"/>
       <c r="AT885" s="2" t="n"/>
-      <c r="AU885" s="2" t="n"/>
     </row>
     <row r="886">
       <c r="A886" s="2" t="n"/>
@@ -44091,7 +43201,6 @@
       <c r="AR886" s="2" t="n"/>
       <c r="AS886" s="2" t="n"/>
       <c r="AT886" s="2" t="n"/>
-      <c r="AU886" s="2" t="n"/>
     </row>
     <row r="887">
       <c r="A887" s="2" t="n"/>
@@ -44140,7 +43249,6 @@
       <c r="AR887" s="2" t="n"/>
       <c r="AS887" s="2" t="n"/>
       <c r="AT887" s="2" t="n"/>
-      <c r="AU887" s="2" t="n"/>
     </row>
     <row r="888">
       <c r="A888" s="2" t="n"/>
@@ -44189,7 +43297,6 @@
       <c r="AR888" s="2" t="n"/>
       <c r="AS888" s="2" t="n"/>
       <c r="AT888" s="2" t="n"/>
-      <c r="AU888" s="2" t="n"/>
     </row>
     <row r="889">
       <c r="A889" s="2" t="n"/>
@@ -44238,7 +43345,6 @@
       <c r="AR889" s="2" t="n"/>
       <c r="AS889" s="2" t="n"/>
       <c r="AT889" s="2" t="n"/>
-      <c r="AU889" s="2" t="n"/>
     </row>
     <row r="890">
       <c r="A890" s="2" t="n"/>
@@ -44287,7 +43393,6 @@
       <c r="AR890" s="2" t="n"/>
       <c r="AS890" s="2" t="n"/>
       <c r="AT890" s="2" t="n"/>
-      <c r="AU890" s="2" t="n"/>
     </row>
     <row r="891">
       <c r="A891" s="2" t="n"/>
@@ -44336,7 +43441,6 @@
       <c r="AR891" s="2" t="n"/>
       <c r="AS891" s="2" t="n"/>
       <c r="AT891" s="2" t="n"/>
-      <c r="AU891" s="2" t="n"/>
     </row>
     <row r="892">
       <c r="A892" s="2" t="n"/>
@@ -44385,7 +43489,6 @@
       <c r="AR892" s="2" t="n"/>
       <c r="AS892" s="2" t="n"/>
       <c r="AT892" s="2" t="n"/>
-      <c r="AU892" s="2" t="n"/>
     </row>
     <row r="893">
       <c r="A893" s="2" t="n"/>
@@ -44434,7 +43537,6 @@
       <c r="AR893" s="2" t="n"/>
       <c r="AS893" s="2" t="n"/>
       <c r="AT893" s="2" t="n"/>
-      <c r="AU893" s="2" t="n"/>
     </row>
     <row r="894">
       <c r="A894" s="2" t="n"/>
@@ -44483,7 +43585,6 @@
       <c r="AR894" s="2" t="n"/>
       <c r="AS894" s="2" t="n"/>
       <c r="AT894" s="2" t="n"/>
-      <c r="AU894" s="2" t="n"/>
     </row>
     <row r="895">
       <c r="A895" s="2" t="n"/>
@@ -44532,7 +43633,6 @@
       <c r="AR895" s="2" t="n"/>
       <c r="AS895" s="2" t="n"/>
       <c r="AT895" s="2" t="n"/>
-      <c r="AU895" s="2" t="n"/>
     </row>
     <row r="896">
       <c r="A896" s="2" t="n"/>
@@ -44581,7 +43681,6 @@
       <c r="AR896" s="2" t="n"/>
       <c r="AS896" s="2" t="n"/>
       <c r="AT896" s="2" t="n"/>
-      <c r="AU896" s="2" t="n"/>
     </row>
     <row r="897">
       <c r="A897" s="2" t="n"/>
@@ -44630,7 +43729,6 @@
       <c r="AR897" s="2" t="n"/>
       <c r="AS897" s="2" t="n"/>
       <c r="AT897" s="2" t="n"/>
-      <c r="AU897" s="2" t="n"/>
     </row>
     <row r="898">
       <c r="A898" s="2" t="n"/>
@@ -44679,7 +43777,6 @@
       <c r="AR898" s="2" t="n"/>
       <c r="AS898" s="2" t="n"/>
       <c r="AT898" s="2" t="n"/>
-      <c r="AU898" s="2" t="n"/>
     </row>
     <row r="899">
       <c r="A899" s="2" t="n"/>
@@ -44728,7 +43825,6 @@
       <c r="AR899" s="2" t="n"/>
       <c r="AS899" s="2" t="n"/>
       <c r="AT899" s="2" t="n"/>
-      <c r="AU899" s="2" t="n"/>
     </row>
     <row r="900">
       <c r="A900" s="2" t="n"/>
@@ -44777,7 +43873,6 @@
       <c r="AR900" s="2" t="n"/>
       <c r="AS900" s="2" t="n"/>
       <c r="AT900" s="2" t="n"/>
-      <c r="AU900" s="2" t="n"/>
     </row>
     <row r="901">
       <c r="A901" s="2" t="n"/>
@@ -44826,7 +43921,6 @@
       <c r="AR901" s="2" t="n"/>
       <c r="AS901" s="2" t="n"/>
       <c r="AT901" s="2" t="n"/>
-      <c r="AU901" s="2" t="n"/>
     </row>
     <row r="902">
       <c r="A902" s="2" t="n"/>
@@ -44875,7 +43969,6 @@
       <c r="AR902" s="2" t="n"/>
       <c r="AS902" s="2" t="n"/>
       <c r="AT902" s="2" t="n"/>
-      <c r="AU902" s="2" t="n"/>
     </row>
     <row r="903">
       <c r="A903" s="2" t="n"/>
@@ -44924,7 +44017,6 @@
       <c r="AR903" s="2" t="n"/>
       <c r="AS903" s="2" t="n"/>
       <c r="AT903" s="2" t="n"/>
-      <c r="AU903" s="2" t="n"/>
     </row>
     <row r="904">
       <c r="A904" s="2" t="n"/>
@@ -44973,7 +44065,6 @@
       <c r="AR904" s="2" t="n"/>
       <c r="AS904" s="2" t="n"/>
       <c r="AT904" s="2" t="n"/>
-      <c r="AU904" s="2" t="n"/>
     </row>
     <row r="905">
       <c r="A905" s="2" t="n"/>
@@ -45022,7 +44113,6 @@
       <c r="AR905" s="2" t="n"/>
       <c r="AS905" s="2" t="n"/>
       <c r="AT905" s="2" t="n"/>
-      <c r="AU905" s="2" t="n"/>
     </row>
     <row r="906">
       <c r="A906" s="2" t="n"/>
@@ -45071,7 +44161,6 @@
       <c r="AR906" s="2" t="n"/>
       <c r="AS906" s="2" t="n"/>
       <c r="AT906" s="2" t="n"/>
-      <c r="AU906" s="2" t="n"/>
     </row>
     <row r="907">
       <c r="A907" s="2" t="n"/>
@@ -45120,7 +44209,6 @@
       <c r="AR907" s="2" t="n"/>
       <c r="AS907" s="2" t="n"/>
       <c r="AT907" s="2" t="n"/>
-      <c r="AU907" s="2" t="n"/>
     </row>
     <row r="908">
       <c r="A908" s="2" t="n"/>
@@ -45169,7 +44257,6 @@
       <c r="AR908" s="2" t="n"/>
       <c r="AS908" s="2" t="n"/>
       <c r="AT908" s="2" t="n"/>
-      <c r="AU908" s="2" t="n"/>
     </row>
     <row r="909">
       <c r="A909" s="2" t="n"/>
@@ -45218,7 +44305,6 @@
       <c r="AR909" s="2" t="n"/>
       <c r="AS909" s="2" t="n"/>
       <c r="AT909" s="2" t="n"/>
-      <c r="AU909" s="2" t="n"/>
     </row>
     <row r="910">
       <c r="A910" s="2" t="n"/>
@@ -45267,7 +44353,6 @@
       <c r="AR910" s="2" t="n"/>
       <c r="AS910" s="2" t="n"/>
       <c r="AT910" s="2" t="n"/>
-      <c r="AU910" s="2" t="n"/>
     </row>
     <row r="911">
       <c r="A911" s="2" t="n"/>
@@ -45316,7 +44401,6 @@
       <c r="AR911" s="2" t="n"/>
       <c r="AS911" s="2" t="n"/>
       <c r="AT911" s="2" t="n"/>
-      <c r="AU911" s="2" t="n"/>
     </row>
     <row r="912">
       <c r="A912" s="2" t="n"/>
@@ -45365,7 +44449,6 @@
       <c r="AR912" s="2" t="n"/>
       <c r="AS912" s="2" t="n"/>
       <c r="AT912" s="2" t="n"/>
-      <c r="AU912" s="2" t="n"/>
     </row>
     <row r="913">
       <c r="A913" s="2" t="n"/>
@@ -45414,7 +44497,6 @@
       <c r="AR913" s="2" t="n"/>
       <c r="AS913" s="2" t="n"/>
       <c r="AT913" s="2" t="n"/>
-      <c r="AU913" s="2" t="n"/>
     </row>
     <row r="914">
       <c r="A914" s="2" t="n"/>
@@ -45463,7 +44545,6 @@
       <c r="AR914" s="2" t="n"/>
       <c r="AS914" s="2" t="n"/>
       <c r="AT914" s="2" t="n"/>
-      <c r="AU914" s="2" t="n"/>
     </row>
     <row r="915">
       <c r="A915" s="2" t="n"/>
@@ -45512,7 +44593,6 @@
       <c r="AR915" s="2" t="n"/>
       <c r="AS915" s="2" t="n"/>
       <c r="AT915" s="2" t="n"/>
-      <c r="AU915" s="2" t="n"/>
     </row>
     <row r="916">
       <c r="A916" s="2" t="n"/>
@@ -45561,7 +44641,6 @@
       <c r="AR916" s="2" t="n"/>
       <c r="AS916" s="2" t="n"/>
       <c r="AT916" s="2" t="n"/>
-      <c r="AU916" s="2" t="n"/>
     </row>
     <row r="917">
       <c r="A917" s="2" t="n"/>
@@ -45610,7 +44689,6 @@
       <c r="AR917" s="2" t="n"/>
       <c r="AS917" s="2" t="n"/>
       <c r="AT917" s="2" t="n"/>
-      <c r="AU917" s="2" t="n"/>
     </row>
     <row r="918">
       <c r="A918" s="2" t="n"/>
@@ -45659,7 +44737,6 @@
       <c r="AR918" s="2" t="n"/>
       <c r="AS918" s="2" t="n"/>
       <c r="AT918" s="2" t="n"/>
-      <c r="AU918" s="2" t="n"/>
     </row>
     <row r="919">
       <c r="A919" s="2" t="n"/>
@@ -45708,7 +44785,6 @@
       <c r="AR919" s="2" t="n"/>
       <c r="AS919" s="2" t="n"/>
       <c r="AT919" s="2" t="n"/>
-      <c r="AU919" s="2" t="n"/>
     </row>
     <row r="920">
       <c r="A920" s="2" t="n"/>
@@ -45757,7 +44833,6 @@
       <c r="AR920" s="2" t="n"/>
       <c r="AS920" s="2" t="n"/>
       <c r="AT920" s="2" t="n"/>
-      <c r="AU920" s="2" t="n"/>
     </row>
     <row r="921">
       <c r="A921" s="2" t="n"/>
@@ -45806,7 +44881,6 @@
       <c r="AR921" s="2" t="n"/>
       <c r="AS921" s="2" t="n"/>
       <c r="AT921" s="2" t="n"/>
-      <c r="AU921" s="2" t="n"/>
     </row>
     <row r="922">
       <c r="A922" s="2" t="n"/>
@@ -45855,7 +44929,6 @@
       <c r="AR922" s="2" t="n"/>
       <c r="AS922" s="2" t="n"/>
       <c r="AT922" s="2" t="n"/>
-      <c r="AU922" s="2" t="n"/>
     </row>
     <row r="923">
       <c r="A923" s="2" t="n"/>
@@ -45904,7 +44977,6 @@
       <c r="AR923" s="2" t="n"/>
       <c r="AS923" s="2" t="n"/>
       <c r="AT923" s="2" t="n"/>
-      <c r="AU923" s="2" t="n"/>
     </row>
     <row r="924">
       <c r="A924" s="2" t="n"/>
@@ -45953,7 +45025,6 @@
       <c r="AR924" s="2" t="n"/>
       <c r="AS924" s="2" t="n"/>
       <c r="AT924" s="2" t="n"/>
-      <c r="AU924" s="2" t="n"/>
     </row>
     <row r="925">
       <c r="A925" s="2" t="n"/>
@@ -46002,7 +45073,6 @@
       <c r="AR925" s="2" t="n"/>
       <c r="AS925" s="2" t="n"/>
       <c r="AT925" s="2" t="n"/>
-      <c r="AU925" s="2" t="n"/>
     </row>
     <row r="926">
       <c r="A926" s="2" t="n"/>
@@ -46051,7 +45121,6 @@
       <c r="AR926" s="2" t="n"/>
       <c r="AS926" s="2" t="n"/>
       <c r="AT926" s="2" t="n"/>
-      <c r="AU926" s="2" t="n"/>
     </row>
     <row r="927">
       <c r="A927" s="2" t="n"/>
@@ -46100,7 +45169,6 @@
       <c r="AR927" s="2" t="n"/>
       <c r="AS927" s="2" t="n"/>
       <c r="AT927" s="2" t="n"/>
-      <c r="AU927" s="2" t="n"/>
     </row>
     <row r="928">
       <c r="A928" s="2" t="n"/>
@@ -46149,7 +45217,6 @@
       <c r="AR928" s="2" t="n"/>
       <c r="AS928" s="2" t="n"/>
       <c r="AT928" s="2" t="n"/>
-      <c r="AU928" s="2" t="n"/>
     </row>
     <row r="929">
       <c r="A929" s="2" t="n"/>
@@ -46198,7 +45265,6 @@
       <c r="AR929" s="2" t="n"/>
       <c r="AS929" s="2" t="n"/>
       <c r="AT929" s="2" t="n"/>
-      <c r="AU929" s="2" t="n"/>
     </row>
     <row r="930">
       <c r="A930" s="2" t="n"/>
@@ -46247,7 +45313,6 @@
       <c r="AR930" s="2" t="n"/>
       <c r="AS930" s="2" t="n"/>
       <c r="AT930" s="2" t="n"/>
-      <c r="AU930" s="2" t="n"/>
     </row>
     <row r="931">
       <c r="A931" s="2" t="n"/>
@@ -46296,7 +45361,6 @@
       <c r="AR931" s="2" t="n"/>
       <c r="AS931" s="2" t="n"/>
       <c r="AT931" s="2" t="n"/>
-      <c r="AU931" s="2" t="n"/>
     </row>
     <row r="932">
       <c r="A932" s="2" t="n"/>
@@ -46345,7 +45409,6 @@
       <c r="AR932" s="2" t="n"/>
       <c r="AS932" s="2" t="n"/>
       <c r="AT932" s="2" t="n"/>
-      <c r="AU932" s="2" t="n"/>
     </row>
     <row r="933">
       <c r="A933" s="2" t="n"/>
@@ -46394,7 +45457,6 @@
       <c r="AR933" s="2" t="n"/>
       <c r="AS933" s="2" t="n"/>
       <c r="AT933" s="2" t="n"/>
-      <c r="AU933" s="2" t="n"/>
     </row>
     <row r="934">
       <c r="A934" s="2" t="n"/>
@@ -46443,7 +45505,6 @@
       <c r="AR934" s="2" t="n"/>
       <c r="AS934" s="2" t="n"/>
       <c r="AT934" s="2" t="n"/>
-      <c r="AU934" s="2" t="n"/>
     </row>
     <row r="935">
       <c r="A935" s="2" t="n"/>
@@ -46492,7 +45553,6 @@
       <c r="AR935" s="2" t="n"/>
       <c r="AS935" s="2" t="n"/>
       <c r="AT935" s="2" t="n"/>
-      <c r="AU935" s="2" t="n"/>
     </row>
     <row r="936">
       <c r="A936" s="2" t="n"/>
@@ -46541,7 +45601,6 @@
       <c r="AR936" s="2" t="n"/>
       <c r="AS936" s="2" t="n"/>
       <c r="AT936" s="2" t="n"/>
-      <c r="AU936" s="2" t="n"/>
     </row>
     <row r="937">
       <c r="A937" s="2" t="n"/>
@@ -46590,7 +45649,6 @@
       <c r="AR937" s="2" t="n"/>
       <c r="AS937" s="2" t="n"/>
       <c r="AT937" s="2" t="n"/>
-      <c r="AU937" s="2" t="n"/>
     </row>
     <row r="938">
       <c r="A938" s="2" t="n"/>
@@ -46639,7 +45697,6 @@
       <c r="AR938" s="2" t="n"/>
       <c r="AS938" s="2" t="n"/>
       <c r="AT938" s="2" t="n"/>
-      <c r="AU938" s="2" t="n"/>
     </row>
     <row r="939">
       <c r="A939" s="2" t="n"/>
@@ -46688,7 +45745,6 @@
       <c r="AR939" s="2" t="n"/>
       <c r="AS939" s="2" t="n"/>
       <c r="AT939" s="2" t="n"/>
-      <c r="AU939" s="2" t="n"/>
     </row>
     <row r="940">
       <c r="A940" s="2" t="n"/>
@@ -46737,7 +45793,6 @@
       <c r="AR940" s="2" t="n"/>
       <c r="AS940" s="2" t="n"/>
       <c r="AT940" s="2" t="n"/>
-      <c r="AU940" s="2" t="n"/>
     </row>
     <row r="941">
       <c r="A941" s="2" t="n"/>
@@ -46786,7 +45841,6 @@
       <c r="AR941" s="2" t="n"/>
       <c r="AS941" s="2" t="n"/>
       <c r="AT941" s="2" t="n"/>
-      <c r="AU941" s="2" t="n"/>
     </row>
     <row r="942">
       <c r="A942" s="2" t="n"/>
@@ -46835,7 +45889,6 @@
       <c r="AR942" s="2" t="n"/>
       <c r="AS942" s="2" t="n"/>
       <c r="AT942" s="2" t="n"/>
-      <c r="AU942" s="2" t="n"/>
     </row>
     <row r="943">
       <c r="A943" s="2" t="n"/>
@@ -46884,7 +45937,6 @@
       <c r="AR943" s="2" t="n"/>
       <c r="AS943" s="2" t="n"/>
       <c r="AT943" s="2" t="n"/>
-      <c r="AU943" s="2" t="n"/>
     </row>
     <row r="944">
       <c r="A944" s="2" t="n"/>
@@ -46933,7 +45985,6 @@
       <c r="AR944" s="2" t="n"/>
       <c r="AS944" s="2" t="n"/>
       <c r="AT944" s="2" t="n"/>
-      <c r="AU944" s="2" t="n"/>
     </row>
     <row r="945">
       <c r="A945" s="2" t="n"/>
@@ -46982,7 +46033,6 @@
       <c r="AR945" s="2" t="n"/>
       <c r="AS945" s="2" t="n"/>
       <c r="AT945" s="2" t="n"/>
-      <c r="AU945" s="2" t="n"/>
     </row>
     <row r="946">
       <c r="A946" s="2" t="n"/>
@@ -47031,7 +46081,6 @@
       <c r="AR946" s="2" t="n"/>
       <c r="AS946" s="2" t="n"/>
       <c r="AT946" s="2" t="n"/>
-      <c r="AU946" s="2" t="n"/>
     </row>
     <row r="947">
       <c r="A947" s="2" t="n"/>
@@ -47080,7 +46129,6 @@
       <c r="AR947" s="2" t="n"/>
       <c r="AS947" s="2" t="n"/>
       <c r="AT947" s="2" t="n"/>
-      <c r="AU947" s="2" t="n"/>
     </row>
     <row r="948">
       <c r="A948" s="2" t="n"/>
@@ -47129,7 +46177,6 @@
       <c r="AR948" s="2" t="n"/>
       <c r="AS948" s="2" t="n"/>
       <c r="AT948" s="2" t="n"/>
-      <c r="AU948" s="2" t="n"/>
     </row>
     <row r="949">
       <c r="A949" s="2" t="n"/>
@@ -47178,7 +46225,6 @@
       <c r="AR949" s="2" t="n"/>
       <c r="AS949" s="2" t="n"/>
       <c r="AT949" s="2" t="n"/>
-      <c r="AU949" s="2" t="n"/>
     </row>
     <row r="950">
       <c r="A950" s="2" t="n"/>
@@ -47227,7 +46273,6 @@
       <c r="AR950" s="2" t="n"/>
       <c r="AS950" s="2" t="n"/>
       <c r="AT950" s="2" t="n"/>
-      <c r="AU950" s="2" t="n"/>
     </row>
     <row r="951">
       <c r="A951" s="2" t="n"/>
@@ -47276,7 +46321,6 @@
       <c r="AR951" s="2" t="n"/>
       <c r="AS951" s="2" t="n"/>
       <c r="AT951" s="2" t="n"/>
-      <c r="AU951" s="2" t="n"/>
     </row>
     <row r="952">
       <c r="A952" s="2" t="n"/>
@@ -47325,7 +46369,6 @@
       <c r="AR952" s="2" t="n"/>
       <c r="AS952" s="2" t="n"/>
       <c r="AT952" s="2" t="n"/>
-      <c r="AU952" s="2" t="n"/>
     </row>
     <row r="953">
       <c r="A953" s="2" t="n"/>
@@ -47374,7 +46417,6 @@
       <c r="AR953" s="2" t="n"/>
       <c r="AS953" s="2" t="n"/>
       <c r="AT953" s="2" t="n"/>
-      <c r="AU953" s="2" t="n"/>
     </row>
     <row r="954">
       <c r="A954" s="2" t="n"/>
@@ -47423,7 +46465,6 @@
       <c r="AR954" s="2" t="n"/>
       <c r="AS954" s="2" t="n"/>
       <c r="AT954" s="2" t="n"/>
-      <c r="AU954" s="2" t="n"/>
     </row>
     <row r="955">
       <c r="A955" s="2" t="n"/>
@@ -47472,7 +46513,6 @@
       <c r="AR955" s="2" t="n"/>
       <c r="AS955" s="2" t="n"/>
       <c r="AT955" s="2" t="n"/>
-      <c r="AU955" s="2" t="n"/>
     </row>
     <row r="956">
       <c r="A956" s="2" t="n"/>
@@ -47521,7 +46561,6 @@
       <c r="AR956" s="2" t="n"/>
       <c r="AS956" s="2" t="n"/>
       <c r="AT956" s="2" t="n"/>
-      <c r="AU956" s="2" t="n"/>
     </row>
     <row r="957">
       <c r="A957" s="2" t="n"/>
@@ -47570,7 +46609,6 @@
       <c r="AR957" s="2" t="n"/>
       <c r="AS957" s="2" t="n"/>
       <c r="AT957" s="2" t="n"/>
-      <c r="AU957" s="2" t="n"/>
     </row>
     <row r="958">
       <c r="A958" s="2" t="n"/>
@@ -47619,7 +46657,6 @@
       <c r="AR958" s="2" t="n"/>
       <c r="AS958" s="2" t="n"/>
       <c r="AT958" s="2" t="n"/>
-      <c r="AU958" s="2" t="n"/>
     </row>
     <row r="959">
       <c r="A959" s="2" t="n"/>
@@ -47668,7 +46705,6 @@
       <c r="AR959" s="2" t="n"/>
       <c r="AS959" s="2" t="n"/>
       <c r="AT959" s="2" t="n"/>
-      <c r="AU959" s="2" t="n"/>
     </row>
     <row r="960">
       <c r="A960" s="2" t="n"/>
@@ -47717,7 +46753,6 @@
       <c r="AR960" s="2" t="n"/>
       <c r="AS960" s="2" t="n"/>
       <c r="AT960" s="2" t="n"/>
-      <c r="AU960" s="2" t="n"/>
     </row>
     <row r="961">
       <c r="A961" s="2" t="n"/>
@@ -47766,7 +46801,6 @@
       <c r="AR961" s="2" t="n"/>
       <c r="AS961" s="2" t="n"/>
       <c r="AT961" s="2" t="n"/>
-      <c r="AU961" s="2" t="n"/>
     </row>
     <row r="962">
       <c r="A962" s="2" t="n"/>
@@ -47815,7 +46849,6 @@
       <c r="AR962" s="2" t="n"/>
       <c r="AS962" s="2" t="n"/>
       <c r="AT962" s="2" t="n"/>
-      <c r="AU962" s="2" t="n"/>
     </row>
     <row r="963">
       <c r="A963" s="2" t="n"/>
@@ -47864,7 +46897,6 @@
       <c r="AR963" s="2" t="n"/>
       <c r="AS963" s="2" t="n"/>
       <c r="AT963" s="2" t="n"/>
-      <c r="AU963" s="2" t="n"/>
     </row>
     <row r="964">
       <c r="A964" s="2" t="n"/>
@@ -47913,7 +46945,6 @@
       <c r="AR964" s="2" t="n"/>
       <c r="AS964" s="2" t="n"/>
       <c r="AT964" s="2" t="n"/>
-      <c r="AU964" s="2" t="n"/>
     </row>
     <row r="965">
       <c r="A965" s="2" t="n"/>
@@ -47962,7 +46993,6 @@
       <c r="AR965" s="2" t="n"/>
       <c r="AS965" s="2" t="n"/>
       <c r="AT965" s="2" t="n"/>
-      <c r="AU965" s="2" t="n"/>
     </row>
     <row r="966">
       <c r="A966" s="2" t="n"/>
@@ -48011,7 +47041,6 @@
       <c r="AR966" s="2" t="n"/>
       <c r="AS966" s="2" t="n"/>
       <c r="AT966" s="2" t="n"/>
-      <c r="AU966" s="2" t="n"/>
     </row>
     <row r="967">
       <c r="A967" s="2" t="n"/>
@@ -48060,7 +47089,6 @@
       <c r="AR967" s="2" t="n"/>
       <c r="AS967" s="2" t="n"/>
       <c r="AT967" s="2" t="n"/>
-      <c r="AU967" s="2" t="n"/>
     </row>
     <row r="968">
       <c r="A968" s="2" t="n"/>
@@ -48109,7 +47137,6 @@
       <c r="AR968" s="2" t="n"/>
       <c r="AS968" s="2" t="n"/>
       <c r="AT968" s="2" t="n"/>
-      <c r="AU968" s="2" t="n"/>
     </row>
     <row r="969">
       <c r="A969" s="2" t="n"/>
@@ -48158,7 +47185,6 @@
       <c r="AR969" s="2" t="n"/>
       <c r="AS969" s="2" t="n"/>
       <c r="AT969" s="2" t="n"/>
-      <c r="AU969" s="2" t="n"/>
     </row>
     <row r="970">
       <c r="A970" s="2" t="n"/>
@@ -48207,7 +47233,6 @@
       <c r="AR970" s="2" t="n"/>
       <c r="AS970" s="2" t="n"/>
       <c r="AT970" s="2" t="n"/>
-      <c r="AU970" s="2" t="n"/>
     </row>
     <row r="971">
       <c r="A971" s="2" t="n"/>
@@ -48256,7 +47281,6 @@
       <c r="AR971" s="2" t="n"/>
       <c r="AS971" s="2" t="n"/>
       <c r="AT971" s="2" t="n"/>
-      <c r="AU971" s="2" t="n"/>
     </row>
     <row r="972">
       <c r="A972" s="2" t="n"/>
@@ -48305,7 +47329,6 @@
       <c r="AR972" s="2" t="n"/>
       <c r="AS972" s="2" t="n"/>
       <c r="AT972" s="2" t="n"/>
-      <c r="AU972" s="2" t="n"/>
     </row>
     <row r="973">
       <c r="A973" s="2" t="n"/>
@@ -48354,7 +47377,6 @@
       <c r="AR973" s="2" t="n"/>
       <c r="AS973" s="2" t="n"/>
       <c r="AT973" s="2" t="n"/>
-      <c r="AU973" s="2" t="n"/>
     </row>
     <row r="974">
       <c r="A974" s="2" t="n"/>
@@ -48403,7 +47425,6 @@
       <c r="AR974" s="2" t="n"/>
       <c r="AS974" s="2" t="n"/>
       <c r="AT974" s="2" t="n"/>
-      <c r="AU974" s="2" t="n"/>
     </row>
     <row r="975">
       <c r="A975" s="2" t="n"/>
@@ -48452,7 +47473,6 @@
       <c r="AR975" s="2" t="n"/>
       <c r="AS975" s="2" t="n"/>
       <c r="AT975" s="2" t="n"/>
-      <c r="AU975" s="2" t="n"/>
     </row>
     <row r="976">
       <c r="A976" s="2" t="n"/>
@@ -48501,7 +47521,6 @@
       <c r="AR976" s="2" t="n"/>
       <c r="AS976" s="2" t="n"/>
       <c r="AT976" s="2" t="n"/>
-      <c r="AU976" s="2" t="n"/>
     </row>
     <row r="977">
       <c r="A977" s="2" t="n"/>
@@ -48550,7 +47569,6 @@
       <c r="AR977" s="2" t="n"/>
       <c r="AS977" s="2" t="n"/>
       <c r="AT977" s="2" t="n"/>
-      <c r="AU977" s="2" t="n"/>
     </row>
     <row r="978">
       <c r="A978" s="2" t="n"/>
@@ -48599,7 +47617,6 @@
       <c r="AR978" s="2" t="n"/>
       <c r="AS978" s="2" t="n"/>
       <c r="AT978" s="2" t="n"/>
-      <c r="AU978" s="2" t="n"/>
     </row>
     <row r="979">
       <c r="A979" s="2" t="n"/>
@@ -48648,7 +47665,6 @@
       <c r="AR979" s="2" t="n"/>
       <c r="AS979" s="2" t="n"/>
       <c r="AT979" s="2" t="n"/>
-      <c r="AU979" s="2" t="n"/>
     </row>
     <row r="980">
       <c r="A980" s="2" t="n"/>
@@ -48697,7 +47713,6 @@
       <c r="AR980" s="2" t="n"/>
       <c r="AS980" s="2" t="n"/>
       <c r="AT980" s="2" t="n"/>
-      <c r="AU980" s="2" t="n"/>
     </row>
     <row r="981">
       <c r="A981" s="2" t="n"/>
@@ -48746,7 +47761,6 @@
       <c r="AR981" s="2" t="n"/>
       <c r="AS981" s="2" t="n"/>
       <c r="AT981" s="2" t="n"/>
-      <c r="AU981" s="2" t="n"/>
     </row>
     <row r="982">
       <c r="A982" s="2" t="n"/>
@@ -48795,7 +47809,6 @@
       <c r="AR982" s="2" t="n"/>
       <c r="AS982" s="2" t="n"/>
       <c r="AT982" s="2" t="n"/>
-      <c r="AU982" s="2" t="n"/>
     </row>
     <row r="983">
       <c r="A983" s="2" t="n"/>
@@ -48844,7 +47857,6 @@
       <c r="AR983" s="2" t="n"/>
       <c r="AS983" s="2" t="n"/>
       <c r="AT983" s="2" t="n"/>
-      <c r="AU983" s="2" t="n"/>
     </row>
     <row r="984">
       <c r="A984" s="2" t="n"/>
@@ -48893,7 +47905,6 @@
       <c r="AR984" s="2" t="n"/>
       <c r="AS984" s="2" t="n"/>
       <c r="AT984" s="2" t="n"/>
-      <c r="AU984" s="2" t="n"/>
     </row>
     <row r="985">
       <c r="A985" s="2" t="n"/>
@@ -48942,7 +47953,6 @@
       <c r="AR985" s="2" t="n"/>
       <c r="AS985" s="2" t="n"/>
       <c r="AT985" s="2" t="n"/>
-      <c r="AU985" s="2" t="n"/>
     </row>
     <row r="986">
       <c r="A986" s="2" t="n"/>
@@ -48991,7 +48001,6 @@
       <c r="AR986" s="2" t="n"/>
       <c r="AS986" s="2" t="n"/>
       <c r="AT986" s="2" t="n"/>
-      <c r="AU986" s="2" t="n"/>
     </row>
     <row r="987">
       <c r="A987" s="2" t="n"/>
@@ -49040,7 +48049,6 @@
       <c r="AR987" s="2" t="n"/>
       <c r="AS987" s="2" t="n"/>
       <c r="AT987" s="2" t="n"/>
-      <c r="AU987" s="2" t="n"/>
     </row>
     <row r="988">
       <c r="A988" s="2" t="n"/>
@@ -49089,7 +48097,6 @@
       <c r="AR988" s="2" t="n"/>
       <c r="AS988" s="2" t="n"/>
       <c r="AT988" s="2" t="n"/>
-      <c r="AU988" s="2" t="n"/>
     </row>
     <row r="989">
       <c r="A989" s="2" t="n"/>
@@ -49138,7 +48145,6 @@
       <c r="AR989" s="2" t="n"/>
       <c r="AS989" s="2" t="n"/>
       <c r="AT989" s="2" t="n"/>
-      <c r="AU989" s="2" t="n"/>
     </row>
     <row r="990">
       <c r="A990" s="2" t="n"/>
@@ -49187,7 +48193,6 @@
       <c r="AR990" s="2" t="n"/>
       <c r="AS990" s="2" t="n"/>
       <c r="AT990" s="2" t="n"/>
-      <c r="AU990" s="2" t="n"/>
     </row>
     <row r="991">
       <c r="A991" s="2" t="n"/>
@@ -49236,7 +48241,6 @@
       <c r="AR991" s="2" t="n"/>
       <c r="AS991" s="2" t="n"/>
       <c r="AT991" s="2" t="n"/>
-      <c r="AU991" s="2" t="n"/>
     </row>
     <row r="992">
       <c r="A992" s="2" t="n"/>
@@ -49285,7 +48289,6 @@
       <c r="AR992" s="2" t="n"/>
       <c r="AS992" s="2" t="n"/>
       <c r="AT992" s="2" t="n"/>
-      <c r="AU992" s="2" t="n"/>
     </row>
     <row r="993">
       <c r="A993" s="2" t="n"/>
@@ -49334,7 +48337,6 @@
       <c r="AR993" s="2" t="n"/>
       <c r="AS993" s="2" t="n"/>
       <c r="AT993" s="2" t="n"/>
-      <c r="AU993" s="2" t="n"/>
     </row>
     <row r="994">
       <c r="A994" s="2" t="n"/>
@@ -49383,7 +48385,6 @@
       <c r="AR994" s="2" t="n"/>
       <c r="AS994" s="2" t="n"/>
       <c r="AT994" s="2" t="n"/>
-      <c r="AU994" s="2" t="n"/>
     </row>
     <row r="995">
       <c r="A995" s="2" t="n"/>
@@ -49432,7 +48433,6 @@
       <c r="AR995" s="2" t="n"/>
       <c r="AS995" s="2" t="n"/>
       <c r="AT995" s="2" t="n"/>
-      <c r="AU995" s="2" t="n"/>
     </row>
     <row r="996">
       <c r="A996" s="2" t="n"/>
@@ -49481,7 +48481,6 @@
       <c r="AR996" s="2" t="n"/>
       <c r="AS996" s="2" t="n"/>
       <c r="AT996" s="2" t="n"/>
-      <c r="AU996" s="2" t="n"/>
     </row>
     <row r="997">
       <c r="A997" s="2" t="n"/>
@@ -49530,7 +48529,6 @@
       <c r="AR997" s="2" t="n"/>
       <c r="AS997" s="2" t="n"/>
       <c r="AT997" s="2" t="n"/>
-      <c r="AU997" s="2" t="n"/>
     </row>
     <row r="998">
       <c r="A998" s="2" t="n"/>
@@ -49579,7 +48577,6 @@
       <c r="AR998" s="2" t="n"/>
       <c r="AS998" s="2" t="n"/>
       <c r="AT998" s="2" t="n"/>
-      <c r="AU998" s="2" t="n"/>
     </row>
     <row r="999">
       <c r="A999" s="2" t="n"/>
@@ -49628,7 +48625,6 @@
       <c r="AR999" s="2" t="n"/>
       <c r="AS999" s="2" t="n"/>
       <c r="AT999" s="2" t="n"/>
-      <c r="AU999" s="2" t="n"/>
     </row>
     <row r="1000">
       <c r="A1000" s="2" t="n"/>
@@ -49677,7 +48673,6 @@
       <c r="AR1000" s="2" t="n"/>
       <c r="AS1000" s="2" t="n"/>
       <c r="AT1000" s="2" t="n"/>
-      <c r="AU1000" s="2" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="3">
